--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1966" uniqueCount="1966">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1967" uniqueCount="1967">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59865641593933</t>
+    <t xml:space="preserve">3.59865665435791</t>
   </si>
   <si>
     <t xml:space="preserve">CPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65898251533508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60329723358154</t>
+    <t xml:space="preserve">3.6589822769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60329651832581</t>
   </si>
   <si>
     <t xml:space="preserve">3.51976919174194</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">3.54993224143982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62881946563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68450498580933</t>
+    <t xml:space="preserve">3.62881994247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68450450897217</t>
   </si>
   <si>
     <t xml:space="preserve">3.57313442230225</t>
@@ -71,64 +71,64 @@
     <t xml:space="preserve">3.52673006057739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48264575004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56617331504822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43392109870911</t>
+    <t xml:space="preserve">3.4826455116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5661735534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43392133712769</t>
   </si>
   <si>
     <t xml:space="preserve">3.50584745407104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56153321266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64274096488953</t>
+    <t xml:space="preserve">3.56153345108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64274072647095</t>
   </si>
   <si>
     <t xml:space="preserve">3.66594290733337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56849384307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74250960350037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72162842750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70770716667175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47104454040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44320178031921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28078699111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33183145523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40839862823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22046089172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26918578147888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32487106323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24366331100464</t>
+    <t xml:space="preserve">3.56849431991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7425103187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72162795066833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70770668983459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47104477882385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44320225715637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28078675270081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33183169364929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40839886665344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22046136856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2691855430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32487082481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24366354942322</t>
   </si>
   <si>
     <t xml:space="preserve">3.32255077362061</t>
@@ -137,76 +137,76 @@
     <t xml:space="preserve">3.28774785995483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31790995597839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36663508415222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36199450492859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40607833862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38287663459778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36431455612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53137063980103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60561728477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61257791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56385350227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61489820480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63810062408447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68914484977722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476301193237</t>
+    <t xml:space="preserve">3.31791067123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36663460731506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36199474334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40607857704163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38287615776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36431479454041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53137040138245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60561752319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61257815361023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56385278701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61489796638489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63810014724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6891450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476277351379</t>
   </si>
   <si>
     <t xml:space="preserve">3.95596981048584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00701522827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04877805709839</t>
+    <t xml:space="preserve">4.00701570510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04877853393555</t>
   </si>
   <si>
     <t xml:space="preserve">4.03485727310181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0418176651001</t>
+    <t xml:space="preserve">4.04181814193726</t>
   </si>
   <si>
     <t xml:space="preserve">4.03717756271362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05109882354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01861619949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09286308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0766224861145</t>
+    <t xml:space="preserve">4.05109834671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01861572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0928635597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07662105560303</t>
   </si>
   <si>
     <t xml:space="preserve">4.03949737548828</t>
@@ -215,28 +215,28 @@
     <t xml:space="preserve">4.08358192443848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02325582504272</t>
+    <t xml:space="preserve">4.02325630187988</t>
   </si>
   <si>
     <t xml:space="preserve">4.00005435943604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06037950515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99541401863098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94436883926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97453117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00237512588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9374086856842</t>
+    <t xml:space="preserve">4.06037998199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99541354179382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94436955451965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97453165054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00237417221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93740820884705</t>
   </si>
   <si>
     <t xml:space="preserve">3.94668936729431</t>
@@ -248,7 +248,7 @@
     <t xml:space="preserve">4.05341911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00933456420898</t>
+    <t xml:space="preserve">4.00933504104614</t>
   </si>
   <si>
     <t xml:space="preserve">3.95828986167908</t>
@@ -260,82 +260,82 @@
     <t xml:space="preserve">4.02557611465454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96989154815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91188597679138</t>
+    <t xml:space="preserve">3.969890832901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9118857383728</t>
   </si>
   <si>
     <t xml:space="preserve">3.89796495437622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87708234786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91420674324036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92812705039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95132970809937</t>
+    <t xml:space="preserve">3.87708210945129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91420602798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92812728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95132994651794</t>
   </si>
   <si>
     <t xml:space="preserve">4.06734037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08126211166382</t>
+    <t xml:space="preserve">4.08126163482666</t>
   </si>
   <si>
     <t xml:space="preserve">3.99309277534485</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96757078170776</t>
+    <t xml:space="preserve">3.96757173538208</t>
   </si>
   <si>
     <t xml:space="preserve">3.98149275779724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96293139457703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88868451118469</t>
+    <t xml:space="preserve">3.96292972564697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88868403434753</t>
   </si>
   <si>
     <t xml:space="preserve">3.89332437515259</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79587531089783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89309906959534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02677774429321</t>
+    <t xml:space="preserve">3.79587483406067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89309883117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02677822113037</t>
   </si>
   <si>
     <t xml:space="preserve">4.08540821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07602739334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08306264877319</t>
+    <t xml:space="preserve">4.07602787017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08306312561035</t>
   </si>
   <si>
     <t xml:space="preserve">4.09948015213013</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07368278503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09009885787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10182476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08775424957275</t>
+    <t xml:space="preserve">4.07368230819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0900993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10182523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0877537727356</t>
   </si>
   <si>
     <t xml:space="preserve">4.11355209350586</t>
@@ -344,58 +344,58 @@
     <t xml:space="preserve">4.08071851730347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01974105834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90482497215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85557532310486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85792088508606</t>
+    <t xml:space="preserve">4.01974248886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90482521057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8555748462677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85792064666748</t>
   </si>
   <si>
     <t xml:space="preserve">3.86495614051819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8719916343689</t>
+    <t xml:space="preserve">3.87199211120605</t>
   </si>
   <si>
     <t xml:space="preserve">3.86964654922485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00567102432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00801563262939</t>
+    <t xml:space="preserve">4.00567054748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00801610946655</t>
   </si>
   <si>
     <t xml:space="preserve">3.95876526832581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05961084365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88606286048889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88840842247009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04084873199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16514682769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15576601028442</t>
+    <t xml:space="preserve">4.05961036682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88606309890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88840866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04084920883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1651463508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15576553344727</t>
   </si>
   <si>
     <t xml:space="preserve">4.14873075485229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13231372833252</t>
+    <t xml:space="preserve">4.13231420516968</t>
   </si>
   <si>
     <t xml:space="preserve">4.00332546234131</t>
@@ -404,43 +404,43 @@
     <t xml:space="preserve">4.04319429397583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16045570373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15811061859131</t>
+    <t xml:space="preserve">4.16045618057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15811109542847</t>
   </si>
   <si>
     <t xml:space="preserve">4.11589670181274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06899166107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13465785980225</t>
+    <t xml:space="preserve">4.06899213790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1346583366394</t>
   </si>
   <si>
     <t xml:space="preserve">4.14169454574585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18390893936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16280078887939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21908807754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29178953170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29648017883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31055212020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28710031509399</t>
+    <t xml:space="preserve">4.18390846252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16280269622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21908760070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29179048538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29647970199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31055164337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28709936141968</t>
   </si>
   <si>
     <t xml:space="preserve">4.33165884017944</t>
@@ -455,16 +455,16 @@
     <t xml:space="preserve">4.51458787918091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52162265777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43719482421875</t>
+    <t xml:space="preserve">4.5216236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43719434738159</t>
   </si>
   <si>
     <t xml:space="preserve">4.47940921783447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45595645904541</t>
+    <t xml:space="preserve">4.45595693588257</t>
   </si>
   <si>
     <t xml:space="preserve">4.66233777999878</t>
@@ -473,61 +473,61 @@
     <t xml:space="preserve">4.67171859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58963489532471</t>
+    <t xml:space="preserve">4.58963632583618</t>
   </si>
   <si>
     <t xml:space="preserve">4.55914735794067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56383800506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54976654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60370635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59667110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62012434005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59432554244995</t>
+    <t xml:space="preserve">4.5638370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5497670173645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60370683670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59667062759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57321929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62012338638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59432601928711</t>
   </si>
   <si>
     <t xml:space="preserve">4.65061187744141</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57556390762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70455169677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67406415939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70924234390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60136127471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48644495010376</t>
+    <t xml:space="preserve">4.57556438446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7045521736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67406463623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70924282073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6013617515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4864444732666</t>
   </si>
   <si>
     <t xml:space="preserve">4.4653377532959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39967060089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43250465393066</t>
+    <t xml:space="preserve">4.39967107772827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43250417709351</t>
   </si>
   <si>
     <t xml:space="preserve">4.50520658493042</t>
@@ -536,31 +536,31 @@
     <t xml:space="preserve">4.49113464355469</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51693296432495</t>
+    <t xml:space="preserve">4.51693344116211</t>
   </si>
   <si>
     <t xml:space="preserve">4.50286197662354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4887900352478</t>
+    <t xml:space="preserve">4.48878955841064</t>
   </si>
   <si>
     <t xml:space="preserve">4.65295648574829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66468191146851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73269414901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71393346786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69048166275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58729028701782</t>
+    <t xml:space="preserve">4.66468286514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73269462585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71393299102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69048023223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58728981018066</t>
   </si>
   <si>
     <t xml:space="preserve">4.56852769851685</t>
@@ -569,61 +569,61 @@
     <t xml:space="preserve">4.47471809387207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44657611846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54742193222046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44188499450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50051641464233</t>
+    <t xml:space="preserve">4.44657516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54742050170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44188547134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50051689147949</t>
   </si>
   <si>
     <t xml:space="preserve">4.52631330490112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36683797836304</t>
+    <t xml:space="preserve">4.36683750152588</t>
   </si>
   <si>
     <t xml:space="preserve">4.37152814865112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33400392532349</t>
+    <t xml:space="preserve">4.33400440216064</t>
   </si>
   <si>
     <t xml:space="preserve">4.32931280136108</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30586099624634</t>
+    <t xml:space="preserve">4.3058614730835</t>
   </si>
   <si>
     <t xml:space="preserve">4.30351686477661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25661087036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20736169815063</t>
+    <t xml:space="preserve">4.25661134719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20736122131348</t>
   </si>
   <si>
     <t xml:space="preserve">4.09478950500488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24253940582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20267009735107</t>
+    <t xml:space="preserve">4.24254035949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20267152786255</t>
   </si>
   <si>
     <t xml:space="preserve">3.95642113685608</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9540753364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0338134765625</t>
+    <t xml:space="preserve">3.95407509803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03381299972534</t>
   </si>
   <si>
     <t xml:space="preserve">4.12527799606323</t>
@@ -635,70 +635,70 @@
     <t xml:space="preserve">4.12996864318848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17218351364136</t>
+    <t xml:space="preserve">4.1721830368042</t>
   </si>
   <si>
     <t xml:space="preserve">4.21205139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18859958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2495756149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20501613616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26833772659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22846841812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24723052978516</t>
+    <t xml:space="preserve">4.18859910964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24957513809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20501565933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26833820343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2284688949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.247230052948</t>
   </si>
   <si>
     <t xml:space="preserve">4.31993293762207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36449289321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28944492340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27771759033203</t>
+    <t xml:space="preserve">4.36449241638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28944444656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27771806716919</t>
   </si>
   <si>
     <t xml:space="preserve">4.30117082595825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32227849960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35745716094971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34807538986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34338521957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39028978347778</t>
+    <t xml:space="preserve">4.32227802276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35745668411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34807634353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34338569641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39028930664062</t>
   </si>
   <si>
     <t xml:space="preserve">4.36214733123779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32462310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39732551574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37387323379517</t>
+    <t xml:space="preserve">4.32462358474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39732599258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37387371063232</t>
   </si>
   <si>
     <t xml:space="preserve">4.36918258666992</t>
@@ -713,37 +713,37 @@
     <t xml:space="preserve">4.42546892166138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43484973907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46768236160278</t>
+    <t xml:space="preserve">4.43484878540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46768283843994</t>
   </si>
   <si>
     <t xml:space="preserve">4.40201568603516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35276556015015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3855996131897</t>
+    <t xml:space="preserve">4.3527660369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38559913635254</t>
   </si>
   <si>
     <t xml:space="preserve">4.43953990936279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43015956878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49347972869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47237253189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52396869659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54272937774658</t>
+    <t xml:space="preserve">4.43015909194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49348115921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47237348556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52396821975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54273080825806</t>
   </si>
   <si>
     <t xml:space="preserve">4.53804016113281</t>
@@ -752,58 +752,58 @@
     <t xml:space="preserve">4.54507541656494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58260011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57790994644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55211210250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57087421417236</t>
+    <t xml:space="preserve">4.58259963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57790899276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55211114883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57087278366089</t>
   </si>
   <si>
     <t xml:space="preserve">4.53569507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50755167007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58494424819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65530204772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74207639694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75614738464355</t>
+    <t xml:space="preserve">4.5075511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58494520187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65530252456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74207592010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75614786148071</t>
   </si>
   <si>
     <t xml:space="preserve">4.80774259567261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83119440078735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8968620300293</t>
+    <t xml:space="preserve">4.83119535446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89686155319214</t>
   </si>
   <si>
     <t xml:space="preserve">4.94845724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09855222702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05164813995361</t>
+    <t xml:space="preserve">5.09855270385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05164766311646</t>
   </si>
   <si>
     <t xml:space="preserve">5.12200546264648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04695653915405</t>
+    <t xml:space="preserve">5.04695701599121</t>
   </si>
   <si>
     <t xml:space="preserve">5.0563383102417</t>
@@ -812,70 +812,70 @@
     <t xml:space="preserve">4.99536180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01881456375122</t>
+    <t xml:space="preserve">5.01881408691406</t>
   </si>
   <si>
     <t xml:space="preserve">5.02819585800171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03288555145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93907642364502</t>
+    <t xml:space="preserve">5.03288507461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93907594680786</t>
   </si>
   <si>
     <t xml:space="preserve">4.9766001701355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92500448226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96721935272217</t>
+    <t xml:space="preserve">4.92500495910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96721887588501</t>
   </si>
   <si>
     <t xml:space="preserve">5.08917188644409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17359972000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14545726776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15952825546265</t>
+    <t xml:space="preserve">5.17359924316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14545774459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15952920913696</t>
   </si>
   <si>
     <t xml:space="preserve">5.09386157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16421937942505</t>
+    <t xml:space="preserve">5.16421890258789</t>
   </si>
   <si>
     <t xml:space="preserve">5.25333833694458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18767261505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41750574111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67079162597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60043334960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62388610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66140937805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68486213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57698202133179</t>
+    <t xml:space="preserve">5.18767166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41750526428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6707911491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60043382644653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62388706207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66140985488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68486261367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57698106765747</t>
   </si>
   <si>
     <t xml:space="preserve">5.60512447357178</t>
@@ -884,46 +884,46 @@
     <t xml:space="preserve">5.72238636016846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6940336227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74128723144531</t>
+    <t xml:space="preserve">5.69403409957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74128675460815</t>
   </si>
   <si>
     <t xml:space="preserve">5.76491451263428</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7507381439209</t>
+    <t xml:space="preserve">5.75073862075806</t>
   </si>
   <si>
     <t xml:space="preserve">5.8783221244812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86887168884277</t>
+    <t xml:space="preserve">5.86887216567993</t>
   </si>
   <si>
     <t xml:space="preserve">5.88304758071899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02008247375488</t>
+    <t xml:space="preserve">6.02008295059204</t>
   </si>
   <si>
     <t xml:space="preserve">5.99173069000244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00118064880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9350266456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85942077636719</t>
+    <t xml:space="preserve">6.00118112564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93502712249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85942125320435</t>
   </si>
   <si>
     <t xml:space="preserve">5.8027172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75546360015869</t>
+    <t xml:space="preserve">5.75546407699585</t>
   </si>
   <si>
     <t xml:space="preserve">5.73183679580688</t>
@@ -935,13 +935,13 @@
     <t xml:space="preserve">5.81216764450073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95865297317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93030261993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9822793006897</t>
+    <t xml:space="preserve">5.95865345001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93030118942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98227977752686</t>
   </si>
   <si>
     <t xml:space="preserve">5.90194892883301</t>
@@ -953,64 +953,64 @@
     <t xml:space="preserve">5.91139984130859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83106899261475</t>
+    <t xml:space="preserve">5.8310694694519</t>
   </si>
   <si>
     <t xml:space="preserve">5.88777256011963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78381586074829</t>
+    <t xml:space="preserve">5.78381538391113</t>
   </si>
   <si>
     <t xml:space="preserve">5.80744218826294</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84524440765381</t>
+    <t xml:space="preserve">5.84524583816528</t>
   </si>
   <si>
     <t xml:space="preserve">5.77436494827271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82634449005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82161808013916</t>
+    <t xml:space="preserve">5.82634401321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82161855697632</t>
   </si>
   <si>
     <t xml:space="preserve">5.85469579696655</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79326677322388</t>
+    <t xml:space="preserve">5.79326629638672</t>
   </si>
   <si>
     <t xml:space="preserve">5.83579444885254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95392894744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92557573318481</t>
+    <t xml:space="preserve">5.95392799377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92557621002197</t>
   </si>
   <si>
     <t xml:space="preserve">5.94447660446167</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7790904045105</t>
+    <t xml:space="preserve">5.77908945083618</t>
   </si>
   <si>
     <t xml:space="preserve">5.74601364135742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71766042709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65150594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66095590591431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79799175262451</t>
+    <t xml:space="preserve">5.71766090393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6515064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66095638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79799127578735</t>
   </si>
   <si>
     <t xml:space="preserve">5.76018905639648</t>
@@ -1019,55 +1019,55 @@
     <t xml:space="preserve">5.69875955581665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66568231582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73656320571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78854036331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76964044570923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89249849319458</t>
+    <t xml:space="preserve">5.66568326950073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73656272888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78854084014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76963996887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89249897003174</t>
   </si>
   <si>
     <t xml:space="preserve">5.97282934188843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15239191055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14766693115234</t>
+    <t xml:space="preserve">6.15239286422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14766645431519</t>
   </si>
   <si>
     <t xml:space="preserve">6.28470182418823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13821649551392</t>
+    <t xml:space="preserve">6.13821601867676</t>
   </si>
   <si>
     <t xml:space="preserve">6.1240406036377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02953338623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10513877868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16656827926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11458969116211</t>
+    <t xml:space="preserve">6.02953386306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10513925552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16656875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11458873748779</t>
   </si>
   <si>
     <t xml:space="preserve">6.31777906417847</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34140586853027</t>
+    <t xml:space="preserve">6.34140634536743</t>
   </si>
   <si>
     <t xml:space="preserve">6.4075608253479</t>
@@ -1079,16 +1079,16 @@
     <t xml:space="preserve">6.42173671722412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30832862854004</t>
+    <t xml:space="preserve">6.30832815170288</t>
   </si>
   <si>
     <t xml:space="preserve">6.47844076156616</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31305360794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33667993545532</t>
+    <t xml:space="preserve">6.31305313110352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3366813659668</t>
   </si>
   <si>
     <t xml:space="preserve">6.37448263168335</t>
@@ -1097,13 +1097,13 @@
     <t xml:space="preserve">6.17601871490479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09096336364746</t>
+    <t xml:space="preserve">6.09096240997314</t>
   </si>
   <si>
     <t xml:space="preserve">6.23272275924683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03898286819458</t>
+    <t xml:space="preserve">6.03898429870605</t>
   </si>
   <si>
     <t xml:space="preserve">6.08623743057251</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">6.10041332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10986423492432</t>
+    <t xml:space="preserve">6.10986471176147</t>
   </si>
   <si>
     <t xml:space="preserve">6.00590658187866</t>
@@ -1121,16 +1121,16 @@
     <t xml:space="preserve">6.03425884246826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09568738937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06261110305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18074369430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08151197433472</t>
+    <t xml:space="preserve">6.09568786621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06261014938354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18074464797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08151149749756</t>
   </si>
   <si>
     <t xml:space="preserve">6.15711736679077</t>
@@ -1139,22 +1139,22 @@
     <t xml:space="preserve">6.21382141113281</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24217367172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24689912796021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20909643173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22799825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19964551925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12876510620117</t>
+    <t xml:space="preserve">6.24217414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24690008163452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20909595489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22799777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19964599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12876605987549</t>
   </si>
   <si>
     <t xml:space="preserve">6.07206201553345</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">6.13349056243896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14294147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01063299179077</t>
+    <t xml:space="preserve">6.14294195175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01063203811646</t>
   </si>
   <si>
     <t xml:space="preserve">5.94920301437378</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">5.97755479812622</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05315971374512</t>
+    <t xml:space="preserve">6.05316066741943</t>
   </si>
   <si>
     <t xml:space="preserve">5.99645566940308</t>
@@ -1187,37 +1187,37 @@
     <t xml:space="preserve">6.06733655929565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93975162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71293592453003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72711086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92085075378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5759015083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52864742279053</t>
+    <t xml:space="preserve">5.93975210189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71293544769287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72711133956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92085027694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57590103149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52864694595337</t>
   </si>
   <si>
     <t xml:space="preserve">5.42941522598267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50502061843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61370372772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63733053207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04370927810669</t>
+    <t xml:space="preserve">5.50502014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61370420455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63733005523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04370975494385</t>
   </si>
   <si>
     <t xml:space="preserve">5.98700571060181</t>
@@ -1229,40 +1229,40 @@
     <t xml:space="preserve">5.89722394943237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81689405441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87359809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86414623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90667486190796</t>
+    <t xml:space="preserve">5.81689357757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87359666824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86414670944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9066743850708</t>
   </si>
   <si>
     <t xml:space="preserve">5.96810388565063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01550674438477</t>
+    <t xml:space="preserve">6.01550722122192</t>
   </si>
   <si>
     <t xml:space="preserve">6.02027082443237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99169301986694</t>
+    <t xml:space="preserve">5.99169254302979</t>
   </si>
   <si>
     <t xml:space="preserve">6.08218765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20602226257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18697118759155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08695077896118</t>
+    <t xml:space="preserve">6.20602178573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18697071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08695030212402</t>
   </si>
   <si>
     <t xml:space="preserve">6.07266139984131</t>
@@ -1271,52 +1271,52 @@
     <t xml:space="preserve">6.16315603256226</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27270221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25365114212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13934230804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2917537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38701105117798</t>
+    <t xml:space="preserve">6.27270269393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25365161895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13934183120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29175424575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38701200485229</t>
   </si>
   <si>
     <t xml:space="preserve">6.52513456344604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59657764434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69183588027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69659900665283</t>
+    <t xml:space="preserve">6.5965781211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69183540344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69659852981567</t>
   </si>
   <si>
     <t xml:space="preserve">6.62039232254028</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57276344299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50608348846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58228874206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65373277664185</t>
+    <t xml:space="preserve">6.57276248931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5060830116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58228921890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65373182296753</t>
   </si>
   <si>
     <t xml:space="preserve">6.71088695526123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8251953125</t>
+    <t xml:space="preserve">6.82519626617432</t>
   </si>
   <si>
     <t xml:space="preserve">6.77280426025391</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">6.82995891571045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02523612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92521619796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92045307159424</t>
+    <t xml:space="preserve">7.02523708343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92521572113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9204535484314</t>
   </si>
   <si>
     <t xml:space="preserve">7.01094770431519</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">6.96808195114136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91092681884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01571083068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04905033111572</t>
+    <t xml:space="preserve">6.91092729568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.015709400177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04905128479004</t>
   </si>
   <si>
     <t xml:space="preserve">7.09667921066284</t>
@@ -1358,34 +1358,34 @@
     <t xml:space="preserve">7.28243112564087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22051382064819</t>
+    <t xml:space="preserve">7.22051334381104</t>
   </si>
   <si>
     <t xml:space="preserve">7.2395658493042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27766847610474</t>
+    <t xml:space="preserve">7.27766799926758</t>
   </si>
   <si>
     <t xml:space="preserve">7.12525653839111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94903087615967</t>
+    <t xml:space="preserve">6.94903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">6.86806154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0014214515686</t>
+    <t xml:space="preserve">7.00142240524292</t>
   </si>
   <si>
     <t xml:space="preserve">7.00618457794189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0633397102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760677337646</t>
+    <t xml:space="preserve">7.06333923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760772705078</t>
   </si>
   <si>
     <t xml:space="preserve">6.99189615249634</t>
@@ -1394,7 +1394,7 @@
     <t xml:space="preserve">7.0395245552063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02047395706177</t>
+    <t xml:space="preserve">7.02047348022461</t>
   </si>
   <si>
     <t xml:space="preserve">7.07762765884399</t>
@@ -1409,10 +1409,10 @@
     <t xml:space="preserve">7.41579151153564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29672050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26338005065918</t>
+    <t xml:space="preserve">7.29672002792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26337957382202</t>
   </si>
   <si>
     <t xml:space="preserve">7.24432802200317</t>
@@ -1421,58 +1421,58 @@
     <t xml:space="preserve">7.2729058265686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30624628067017</t>
+    <t xml:space="preserve">7.30624532699585</t>
   </si>
   <si>
     <t xml:space="preserve">7.18241119384766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25385284423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05857563018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10620498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14907169342041</t>
+    <t xml:space="preserve">7.25385475158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0585765838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10620546340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14907121658325</t>
   </si>
   <si>
     <t xml:space="preserve">7.1681227684021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90140151977539</t>
+    <t xml:space="preserve">6.90140199661255</t>
   </si>
   <si>
     <t xml:space="preserve">6.94426774978638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06810140609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98713302612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13002014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87758684158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7061243057251</t>
+    <t xml:space="preserve">7.06810235977173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98713397979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13001918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87758731842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70612382888794</t>
   </si>
   <si>
     <t xml:space="preserve">6.63944339752197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65849494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32985687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19649696350098</t>
+    <t xml:space="preserve">6.65849542617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32985734939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19649648666382</t>
   </si>
   <si>
     <t xml:space="preserve">6.11552762985229</t>
@@ -1490,13 +1490,13 @@
     <t xml:space="preserve">6.33461999893188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34414577484131</t>
+    <t xml:space="preserve">6.34414529800415</t>
   </si>
   <si>
     <t xml:space="preserve">6.12505292892456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15362977981567</t>
+    <t xml:space="preserve">6.15363121032715</t>
   </si>
   <si>
     <t xml:space="preserve">6.30604267120361</t>
@@ -1505,82 +1505,82 @@
     <t xml:space="preserve">6.35367155075073</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47274303436279</t>
+    <t xml:space="preserve">6.47274351119995</t>
   </si>
   <si>
     <t xml:space="preserve">6.4679799079895</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42987775802612</t>
+    <t xml:space="preserve">6.42987728118896</t>
   </si>
   <si>
     <t xml:space="preserve">6.52989768981934</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76804113388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08239126205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11096858978271</t>
+    <t xml:space="preserve">6.76804161071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08239078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1109676361084</t>
   </si>
   <si>
     <t xml:space="preserve">7.12049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32529735565186</t>
+    <t xml:space="preserve">7.32529783248901</t>
   </si>
   <si>
     <t xml:space="preserve">7.31577157974243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11573028564453</t>
+    <t xml:space="preserve">7.11573076248169</t>
   </si>
   <si>
     <t xml:space="preserve">7.03476238250732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15383434295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04428768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02999973297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17288541793823</t>
+    <t xml:space="preserve">7.15383386611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04428815841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02999925613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17288589477539</t>
   </si>
   <si>
     <t xml:space="preserve">7.36340045928955</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14430809020996</t>
+    <t xml:space="preserve">7.1443076133728</t>
   </si>
   <si>
     <t xml:space="preserve">7.20622587203979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32053375244141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09191656112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98237085342407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44913196563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38245153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33006000518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2157506942749</t>
+    <t xml:space="preserve">7.32053422927856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09191703796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98237037658691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913101196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3824520111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33006048202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21575117111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.33958625793457</t>
@@ -1589,22 +1589,22 @@
     <t xml:space="preserve">7.35387420654297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55391454696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60630750656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46342086791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49199819564819</t>
+    <t xml:space="preserve">7.55391550064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60630702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46342039108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49199771881104</t>
   </si>
   <si>
     <t xml:space="preserve">7.44436931610107</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42055463790894</t>
+    <t xml:space="preserve">7.42055511474609</t>
   </si>
   <si>
     <t xml:space="preserve">7.62535810470581</t>
@@ -1613,70 +1613,70 @@
     <t xml:space="preserve">7.53010082244873</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47294664382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48723459243774</t>
+    <t xml:space="preserve">7.47294616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4872350692749</t>
   </si>
   <si>
     <t xml:space="preserve">7.46818351745605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49676036834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51581192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61106967926025</t>
+    <t xml:space="preserve">7.49676084518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51581287384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6110692024231</t>
   </si>
   <si>
     <t xml:space="preserve">7.56344079971313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6444091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73490428924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80634737014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86826419830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85873985290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88731622695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92541933059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95399808883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83492565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9873366355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01115131378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06354236602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53486347198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52057456970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54438924789429</t>
+    <t xml:space="preserve">7.64440870285034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73490381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80634641647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86826515197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85873937606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88731575012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92541742324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9539966583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83492469787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98733711242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01115226745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06354331970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53486394882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52057504653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54438972473145</t>
   </si>
   <si>
     <t xml:space="preserve">7.62059545516968</t>
@@ -1685,22 +1685,22 @@
     <t xml:space="preserve">7.63964748382568</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77776956558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76824378967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90636825561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03496551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00638675689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04449081420898</t>
+    <t xml:space="preserve">7.77777004241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76824474334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90636730194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03496646881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00638771057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0444917678833</t>
   </si>
   <si>
     <t xml:space="preserve">8.06830596923828</t>
@@ -1715,43 +1715,43 @@
     <t xml:space="preserve">8.44457149505615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33978939056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38265609741211</t>
+    <t xml:space="preserve">8.33979034423828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38265514373779</t>
   </si>
   <si>
     <t xml:space="preserve">8.33502578735352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27787017822266</t>
+    <t xml:space="preserve">8.27787208557129</t>
   </si>
   <si>
     <t xml:space="preserve">8.23500633239746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25881958007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26358413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16832542419434</t>
+    <t xml:space="preserve">8.25882148742676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26358318328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16832447052002</t>
   </si>
   <si>
     <t xml:space="preserve">8.31121253967285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36836624145508</t>
+    <t xml:space="preserve">8.36836528778076</t>
   </si>
   <si>
     <t xml:space="preserve">8.35407829284668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37789154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28739738464355</t>
+    <t xml:space="preserve">8.37789249420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28739643096924</t>
   </si>
   <si>
     <t xml:space="preserve">8.21119213104248</t>
@@ -1760,7 +1760,7 @@
     <t xml:space="preserve">8.22071743011475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43150615692139</t>
+    <t xml:space="preserve">8.43150520324707</t>
   </si>
   <si>
     <t xml:space="preserve">8.445876121521</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">8.56085205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51294612884521</t>
+    <t xml:space="preserve">8.51294708251953</t>
   </si>
   <si>
     <t xml:space="preserve">8.48899269104004</t>
@@ -1781,19 +1781,19 @@
     <t xml:space="preserve">8.441086769104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49857330322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48420143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67103672027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81475448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74289512634277</t>
+    <t xml:space="preserve">8.49857425689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4842004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67103481292725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8147554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74289608001709</t>
   </si>
   <si>
     <t xml:space="preserve">8.83391761779785</t>
@@ -1808,13 +1808,13 @@
     <t xml:space="preserve">8.6854076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70456981658936</t>
+    <t xml:space="preserve">8.70457172393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.78122138977051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80996513366699</t>
+    <t xml:space="preserve">8.80996417999268</t>
   </si>
   <si>
     <t xml:space="preserve">8.77163982391357</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">8.65187358856201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53689765930176</t>
+    <t xml:space="preserve">8.53689861297607</t>
   </si>
   <si>
     <t xml:space="preserve">8.37880802154541</t>
@@ -1832,58 +1832,58 @@
     <t xml:space="preserve">8.37401676177979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40755081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41234302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32610988616943</t>
+    <t xml:space="preserve">8.40755176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4123420715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32611083984375</t>
   </si>
   <si>
     <t xml:space="preserve">8.45545768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41713333129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39318180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54648017883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58959579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27341461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25425243377686</t>
+    <t xml:space="preserve">8.41713237762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39317989349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54647922515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58959484100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27341365814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25425148010254</t>
   </si>
   <si>
     <t xml:space="preserve">8.35485553741455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47461986541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42192363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36922550201416</t>
+    <t xml:space="preserve">8.47462177276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42192459106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36922645568848</t>
   </si>
   <si>
     <t xml:space="preserve">8.31653022766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29736804962158</t>
+    <t xml:space="preserve">8.29736709594727</t>
   </si>
   <si>
     <t xml:space="preserve">8.28299617767334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17760181427002</t>
+    <t xml:space="preserve">8.1776008605957</t>
   </si>
   <si>
     <t xml:space="preserve">8.20155620574951</t>
@@ -1895,88 +1895,88 @@
     <t xml:space="preserve">8.24946022033691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18239212036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17281055450439</t>
+    <t xml:space="preserve">8.18239116668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17281150817871</t>
   </si>
   <si>
     <t xml:space="preserve">8.09616088867188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14885807037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06741809844971</t>
+    <t xml:space="preserve">8.14885711669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06741619110107</t>
   </si>
   <si>
     <t xml:space="preserve">8.03867435455322</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97160482406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78956127166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62188816070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61709833145142</t>
+    <t xml:space="preserve">7.97160387039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78956079483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62188911437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61709785461426</t>
   </si>
   <si>
     <t xml:space="preserve">7.66021394729614</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50212287902832</t>
+    <t xml:space="preserve">7.50212383270264</t>
   </si>
   <si>
     <t xml:space="preserve">7.72249174118042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5931453704834</t>
+    <t xml:space="preserve">7.59314489364624</t>
   </si>
   <si>
     <t xml:space="preserve">7.45900726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51170444488525</t>
+    <t xml:space="preserve">7.5117039680481</t>
   </si>
   <si>
     <t xml:space="preserve">7.65542316436768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59793519973755</t>
+    <t xml:space="preserve">7.59793567657471</t>
   </si>
   <si>
     <t xml:space="preserve">7.90932655334473</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95244264602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82309484481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88058376312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10574150085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20634460449219</t>
+    <t xml:space="preserve">7.95244216918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82309532165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8805832862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10574245452881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20634365081787</t>
   </si>
   <si>
     <t xml:space="preserve">8.16802024841309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26383399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3452730178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29257678985596</t>
+    <t xml:space="preserve">8.26383304595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34527397155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29257583618164</t>
   </si>
   <si>
     <t xml:space="preserve">8.12011432647705</t>
@@ -1985,85 +1985,85 @@
     <t xml:space="preserve">8.0338830947876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99555921554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80872297286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91411638259888</t>
+    <t xml:space="preserve">7.9955587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80872249603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91411733627319</t>
   </si>
   <si>
     <t xml:space="preserve">7.88537311553955</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82788610458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84704780578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00034999847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89974498748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90453672409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94286060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71770191192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85662889480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04346466064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11532402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12969589233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13448810577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00992870330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93327951431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75123596191406</t>
+    <t xml:space="preserve">7.82788562774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84704875946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0003490447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89974546432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9045352935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94286155700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71770095825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85662937164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04346370697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11532497406006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12969493865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13448619842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00993061065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93327903747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7512354850769</t>
   </si>
   <si>
     <t xml:space="preserve">7.578773021698</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64105129241943</t>
+    <t xml:space="preserve">7.64105176925659</t>
   </si>
   <si>
     <t xml:space="preserve">7.69374799728394</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8374662399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81351327896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87100172042847</t>
+    <t xml:space="preserve">7.83746719360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8135142326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87100124359131</t>
   </si>
   <si>
     <t xml:space="preserve">7.87579250335693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92369937896729</t>
+    <t xml:space="preserve">7.92369890213013</t>
   </si>
   <si>
     <t xml:space="preserve">7.89495420455933</t>
@@ -2072,25 +2072,25 @@
     <t xml:space="preserve">7.85183906555176</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86621141433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98597526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96681308746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92848968505859</t>
+    <t xml:space="preserve">7.86621046066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9859766960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96681356430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92848825454712</t>
   </si>
   <si>
     <t xml:space="preserve">8.11053276062012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04825305938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93806982040405</t>
+    <t xml:space="preserve">8.04825496673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93807029724121</t>
   </si>
   <si>
     <t xml:space="preserve">7.77997970581055</t>
@@ -2099,103 +2099,103 @@
     <t xml:space="preserve">7.81830406188965</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84225749969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79435157775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79914236068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94765090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9189076423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7129111289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77518844604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86142063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07699871063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21592617034912</t>
+    <t xml:space="preserve">7.8422589302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79435062408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7991418838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94765186309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91890811920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71291065216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77518892288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86142015457153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07699966430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21592712402344</t>
   </si>
   <si>
     <t xml:space="preserve">8.26862335205078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33569240570068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45066738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36443519592285</t>
+    <t xml:space="preserve">8.33569145202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4506664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36443614959717</t>
   </si>
   <si>
     <t xml:space="preserve">8.47941112518311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55127143859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59438705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66624546051025</t>
+    <t xml:space="preserve">8.55127048492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59438610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66624641418457</t>
   </si>
   <si>
     <t xml:space="preserve">8.64229297637939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69019985198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58480453491211</t>
+    <t xml:space="preserve">8.69019794464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58480548858643</t>
   </si>
   <si>
     <t xml:space="preserve">8.19197273254395</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74165439605713</t>
+    <t xml:space="preserve">7.74165534973145</t>
   </si>
   <si>
     <t xml:space="preserve">7.70332956314087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78477048873901</t>
+    <t xml:space="preserve">7.78477001190186</t>
   </si>
   <si>
     <t xml:space="preserve">7.44463586807251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22426700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1763596534729</t>
+    <t xml:space="preserve">7.22426652908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17636060714722</t>
   </si>
   <si>
     <t xml:space="preserve">7.30091667175293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36319446563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33924245834351</t>
+    <t xml:space="preserve">7.36319494247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33924150466919</t>
   </si>
   <si>
     <t xml:space="preserve">7.09492015838623</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6972975730896</t>
+    <t xml:space="preserve">6.69729709625244</t>
   </si>
   <si>
     <t xml:space="preserve">6.36195373535156</t>
@@ -2210,52 +2210,52 @@
     <t xml:space="preserve">5.37987518310547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30322551727295</t>
+    <t xml:space="preserve">5.30322456359863</t>
   </si>
   <si>
     <t xml:space="preserve">5.86851930618286</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45776557922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08409738540649</t>
+    <t xml:space="preserve">6.45776605606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08409690856934</t>
   </si>
   <si>
     <t xml:space="preserve">6.03619194030762</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29967546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76915740966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84101581573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53441667556763</t>
+    <t xml:space="preserve">6.29967498779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76915693283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84101629257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53441715240479</t>
   </si>
   <si>
     <t xml:space="preserve">6.3715353012085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27572250366211</t>
+    <t xml:space="preserve">6.27572298049927</t>
   </si>
   <si>
     <t xml:space="preserve">6.02852582931519</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11092519760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85606288909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45201778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38111639022827</t>
+    <t xml:space="preserve">6.11092472076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85606384277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45201730728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38111591339111</t>
   </si>
   <si>
     <t xml:space="preserve">6.32171249389648</t>
@@ -2264,22 +2264,22 @@
     <t xml:space="preserve">6.35237264633179</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40986061096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40794372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47309637069702</t>
+    <t xml:space="preserve">6.4098596572876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4079442024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47309684753418</t>
   </si>
   <si>
     <t xml:space="preserve">6.65897274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49962043762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44746923446655</t>
+    <t xml:space="preserve">6.49962091445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44746971130371</t>
   </si>
   <si>
     <t xml:space="preserve">6.43008470535278</t>
@@ -2288,28 +2288,28 @@
     <t xml:space="preserve">6.39338636398315</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44360637664795</t>
+    <t xml:space="preserve">6.44360589981079</t>
   </si>
   <si>
     <t xml:space="preserve">6.59619760513306</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61551332473755</t>
+    <t xml:space="preserve">6.61551284790039</t>
   </si>
   <si>
     <t xml:space="preserve">6.79321432113647</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82798194885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62323904037476</t>
+    <t xml:space="preserve">6.8279824256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6232385635376</t>
   </si>
   <si>
     <t xml:space="preserve">6.690842628479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76617240905762</t>
+    <t xml:space="preserve">6.76617288589478</t>
   </si>
   <si>
     <t xml:space="preserve">6.78935194015503</t>
@@ -2318,7 +2318,7 @@
     <t xml:space="preserve">6.94773721694946</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95932626724243</t>
+    <t xml:space="preserve">6.95932674407959</t>
   </si>
   <si>
     <t xml:space="preserve">7.08487606048584</t>
@@ -2327,22 +2327,22 @@
     <t xml:space="preserve">6.93807888031006</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70629549026489</t>
+    <t xml:space="preserve">6.70629501342773</t>
   </si>
   <si>
     <t xml:space="preserve">6.66766452789307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94001150131226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5112099647522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67345905303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53245687484741</t>
+    <t xml:space="preserve">6.9400110244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51121044158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67345857620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53245639801025</t>
   </si>
   <si>
     <t xml:space="preserve">6.6638011932373</t>
@@ -2351,22 +2351,22 @@
     <t xml:space="preserve">6.67732191085815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72947406768799</t>
+    <t xml:space="preserve">6.72947311401367</t>
   </si>
   <si>
     <t xml:space="preserve">6.71209001541138</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1466851234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05010890960693</t>
+    <t xml:space="preserve">7.14668560028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05010843276978</t>
   </si>
   <si>
     <t xml:space="preserve">6.9438738822937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1119179725647</t>
+    <t xml:space="preserve">7.11191749572754</t>
   </si>
   <si>
     <t xml:space="preserve">7.09839725494385</t>
@@ -2381,16 +2381,16 @@
     <t xml:space="preserve">7.1389594078064</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17759037017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05976581573486</t>
+    <t xml:space="preserve">7.17758989334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05976629257202</t>
   </si>
   <si>
     <t xml:space="preserve">7.20463132858276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06942415237427</t>
+    <t xml:space="preserve">7.06942367553711</t>
   </si>
   <si>
     <t xml:space="preserve">7.31279754638672</t>
@@ -2399,16 +2399,16 @@
     <t xml:space="preserve">7.33018159866333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38619613647461</t>
+    <t xml:space="preserve">7.38619565963745</t>
   </si>
   <si>
     <t xml:space="preserve">7.44800567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44027853012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58128118515015</t>
+    <t xml:space="preserve">7.44027948379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5812816619873</t>
   </si>
   <si>
     <t xml:space="preserve">7.27223539352417</t>
@@ -2426,13 +2426,13 @@
     <t xml:space="preserve">7.54844522476196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45379972457886</t>
+    <t xml:space="preserve">7.45380020141602</t>
   </si>
   <si>
     <t xml:space="preserve">7.62667226791382</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67013168334961</t>
+    <t xml:space="preserve">7.67013216018677</t>
   </si>
   <si>
     <t xml:space="preserve">7.70683145523071</t>
@@ -2441,16 +2441,16 @@
     <t xml:space="preserve">7.84203863143921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86425161361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81499671936035</t>
+    <t xml:space="preserve">7.86425065994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81499719619751</t>
   </si>
   <si>
     <t xml:space="preserve">7.75029039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92412805557251</t>
+    <t xml:space="preserve">7.92412900924683</t>
   </si>
   <si>
     <t xml:space="preserve">7.91350650787354</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">7.82851791381836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89322519302368</t>
+    <t xml:space="preserve">7.89322423934937</t>
   </si>
   <si>
     <t xml:space="preserve">7.98497152328491</t>
@@ -2468,10 +2468,10 @@
     <t xml:space="preserve">7.87294435501099</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02649974822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.885498046875</t>
+    <t xml:space="preserve">8.0265007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88549852371216</t>
   </si>
   <si>
     <t xml:space="preserve">7.83817577362061</t>
@@ -2489,10 +2489,10 @@
     <t xml:space="preserve">8.22158432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28146266937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23220920562744</t>
+    <t xml:space="preserve">8.28146362304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23220825195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.29594993591309</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">8.21868896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26601028442383</t>
+    <t xml:space="preserve">8.26601123809814</t>
   </si>
   <si>
     <t xml:space="preserve">8.43598556518555</t>
@@ -2522,10 +2522,10 @@
     <t xml:space="preserve">8.30753898620605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24283313751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34423828125</t>
+    <t xml:space="preserve">8.24283218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34423923492432</t>
   </si>
   <si>
     <t xml:space="preserve">8.22834587097168</t>
@@ -2534,61 +2534,61 @@
     <t xml:space="preserve">8.39059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34327220916748</t>
+    <t xml:space="preserve">8.3432731628418</t>
   </si>
   <si>
     <t xml:space="preserve">8.43405532836914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3104362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18102264404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29788208007812</t>
+    <t xml:space="preserve">8.31043529510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1810245513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29788112640381</t>
   </si>
   <si>
     <t xml:space="preserve">8.48330879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7711067199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58664512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47944641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71799087524414</t>
+    <t xml:space="preserve">8.77110767364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58664608001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4794454574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71799182891846</t>
   </si>
   <si>
     <t xml:space="preserve">8.65907764434814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75565528869629</t>
+    <t xml:space="preserve">8.75565624237061</t>
   </si>
   <si>
     <t xml:space="preserve">8.71412754058838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82132720947266</t>
+    <t xml:space="preserve">8.82132816314697</t>
   </si>
   <si>
     <t xml:space="preserve">8.94784355163574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01448059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03959083557129</t>
+    <t xml:space="preserve">9.01448154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03959178924561</t>
   </si>
   <si>
     <t xml:space="preserve">9.06083869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85319805145264</t>
+    <t xml:space="preserve">8.85319709777832</t>
   </si>
   <si>
     <t xml:space="preserve">8.94011688232422</t>
@@ -2597,16 +2597,16 @@
     <t xml:space="preserve">9.01641368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05118083953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80587577819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08884525299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0115852355957</t>
+    <t xml:space="preserve">9.05117988586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80587482452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08884620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01158428192139</t>
   </si>
   <si>
     <t xml:space="preserve">8.99999523162842</t>
@@ -2615,22 +2615,22 @@
     <t xml:space="preserve">9.04828357696533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04635143280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02896785736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95460414886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99613094329834</t>
+    <t xml:space="preserve">9.04635047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02896881103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95460319519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99613189697266</t>
   </si>
   <si>
     <t xml:space="preserve">8.97198867797852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04442024230957</t>
+    <t xml:space="preserve">9.04441928863525</t>
   </si>
   <si>
     <t xml:space="preserve">9.21342945098877</t>
@@ -2654,19 +2654,19 @@
     <t xml:space="preserve">9.07629013061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80008125305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93528938293457</t>
+    <t xml:space="preserve">8.80008220672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93528842926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.94687747955322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74020385742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88893222808838</t>
+    <t xml:space="preserve">8.74020195007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8889331817627</t>
   </si>
   <si>
     <t xml:space="preserve">8.66294193267822</t>
@@ -2675,16 +2675,16 @@
     <t xml:space="preserve">8.50262451171875</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65714645385742</t>
+    <t xml:space="preserve">8.65714740753174</t>
   </si>
   <si>
     <t xml:space="preserve">8.51035118103027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59726905822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76724529266357</t>
+    <t xml:space="preserve">8.59727001190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76724433898926</t>
   </si>
   <si>
     <t xml:space="preserve">8.89086437225342</t>
@@ -2696,10 +2696,10 @@
     <t xml:space="preserve">9.24626541137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51281929016113</t>
+    <t xml:space="preserve">9.26171779632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5128173828125</t>
   </si>
   <si>
     <t xml:space="preserve">9.35443210601807</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">9.4316930770874</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25012874603271</t>
+    <t xml:space="preserve">9.25012969970703</t>
   </si>
   <si>
     <t xml:space="preserve">9.13230514526367</t>
@@ -2735,13 +2735,13 @@
     <t xml:space="preserve">9.22694969177246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36215877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12651062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14775657653809</t>
+    <t xml:space="preserve">9.36215782165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12650966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1477575302124</t>
   </si>
   <si>
     <t xml:space="preserve">9.13037490844727</t>
@@ -2756,13 +2756,13 @@
     <t xml:space="preserve">9.0048246383667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13616943359375</t>
+    <t xml:space="preserve">9.13616847991943</t>
   </si>
   <si>
     <t xml:space="preserve">9.05890560150146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04538631439209</t>
+    <t xml:space="preserve">9.04538536071777</t>
   </si>
   <si>
     <t xml:space="preserve">8.83677959442139</t>
@@ -2777,25 +2777,25 @@
     <t xml:space="preserve">8.9391508102417</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86961650848389</t>
+    <t xml:space="preserve">8.86961555480957</t>
   </si>
   <si>
     <t xml:space="preserve">8.88120555877686</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96619319915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13809871673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02027606964111</t>
+    <t xml:space="preserve">8.96619415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13809967041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0202751159668</t>
   </si>
   <si>
     <t xml:space="preserve">8.90438365936279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66487312316895</t>
+    <t xml:space="preserve">8.66487216949463</t>
   </si>
   <si>
     <t xml:space="preserve">8.59340572357178</t>
@@ -2804,10 +2804,10 @@
     <t xml:space="preserve">8.54125499725342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55284404754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42149925231934</t>
+    <t xml:space="preserve">8.55284309387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42150020599365</t>
   </si>
   <si>
     <t xml:space="preserve">8.38093852996826</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">8.42343139648438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42536354064941</t>
+    <t xml:space="preserve">8.4253625869751</t>
   </si>
   <si>
     <t xml:space="preserve">8.5470495223999</t>
@@ -2831,13 +2831,13 @@
     <t xml:space="preserve">8.5856819152832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.512282371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5064868927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63590240478516</t>
+    <t xml:space="preserve">8.51228141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50648784637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63590145111084</t>
   </si>
   <si>
     <t xml:space="preserve">8.59533786773682</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">8.65328407287598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57215881347656</t>
+    <t xml:space="preserve">8.57215976715088</t>
   </si>
   <si>
     <t xml:space="preserve">8.57795333862305</t>
@@ -2855,22 +2855,22 @@
     <t xml:space="preserve">8.82712268829346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86768436431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94108486175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33704853057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31773376464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4027214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3447732925415</t>
+    <t xml:space="preserve">8.86768531799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94108390808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3370475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31773281097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40272045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34477424621582</t>
   </si>
   <si>
     <t xml:space="preserve">9.38533687591553</t>
@@ -2885,34 +2885,34 @@
     <t xml:space="preserve">9.42976188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44135189056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35250091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20570373535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28875827789307</t>
+    <t xml:space="preserve">9.44135093688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35249900817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20570278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28875923156738</t>
   </si>
   <si>
     <t xml:space="preserve">9.31580066680908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34091186523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05697631835938</t>
+    <t xml:space="preserve">9.34091091156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05697536468506</t>
   </si>
   <si>
     <t xml:space="preserve">9.19218254089355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16320991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04924869537354</t>
+    <t xml:space="preserve">9.16320896148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04924964904785</t>
   </si>
   <si>
     <t xml:space="preserve">9.26751327514648</t>
@@ -2930,22 +2930,22 @@
     <t xml:space="preserve">9.76391696929932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48963928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46839332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38726902008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42589855194092</t>
+    <t xml:space="preserve">9.48963832855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46839237213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38726806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42589950561523</t>
   </si>
   <si>
     <t xml:space="preserve">9.364089012146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2829647064209</t>
+    <t xml:space="preserve">9.28296566009521</t>
   </si>
   <si>
     <t xml:space="preserve">9.25978660583496</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">9.24240303039551</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26364898681641</t>
+    <t xml:space="preserve">9.26364994049072</t>
   </si>
   <si>
     <t xml:space="preserve">9.28682804107666</t>
@@ -2972,13 +2972,13 @@
     <t xml:space="preserve">9.32932186126709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46452808380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41624164581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63836669921875</t>
+    <t xml:space="preserve">9.4645299911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41624069213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63836765289307</t>
   </si>
   <si>
     <t xml:space="preserve">9.47225570678711</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">9.76943683624268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55384922027588</t>
+    <t xml:space="preserve">9.55384826660156</t>
   </si>
   <si>
     <t xml:space="preserve">9.73544692993164</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">9.83255958557129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70340061187744</t>
+    <t xml:space="preserve">9.70339965820312</t>
   </si>
   <si>
     <t xml:space="preserve">9.62959575653076</t>
@@ -3011,16 +3011,16 @@
     <t xml:space="preserve">9.60823154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52860069274902</t>
+    <t xml:space="preserve">9.52859973907471</t>
   </si>
   <si>
     <t xml:space="preserve">9.63348007202148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8811149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0025053024292</t>
+    <t xml:space="preserve">9.88111591339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0025043487549</t>
   </si>
   <si>
     <t xml:space="preserve">10.0947618484497</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">9.98308181762695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94423770904541</t>
+    <t xml:space="preserve">9.94423675537109</t>
   </si>
   <si>
     <t xml:space="preserve">9.7742919921875</t>
@@ -3044,10 +3044,10 @@
     <t xml:space="preserve">9.81313705444336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82770347595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79856872558594</t>
+    <t xml:space="preserve">9.82770252227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79856967926025</t>
   </si>
   <si>
     <t xml:space="preserve">9.79371452331543</t>
@@ -3062,16 +3062,16 @@
     <t xml:space="preserve">10.2355718612671</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2549953460693</t>
+    <t xml:space="preserve">10.254994392395</t>
   </si>
   <si>
     <t xml:space="preserve">10.1870164871216</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1481714248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2307176589966</t>
+    <t xml:space="preserve">10.1481704711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2307167053223</t>
   </si>
   <si>
     <t xml:space="preserve">10.2792730331421</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">10.3132619857788</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3909521102905</t>
+    <t xml:space="preserve">10.3909511566162</t>
   </si>
   <si>
     <t xml:space="preserve">10.5754642486572</t>
@@ -3092,10 +3092,10 @@
     <t xml:space="preserve">10.6337299346924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8133878707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8182430267334</t>
+    <t xml:space="preserve">10.8133869171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8182439804077</t>
   </si>
   <si>
     <t xml:space="preserve">10.8328084945679</t>
@@ -3107,10 +3107,10 @@
     <t xml:space="preserve">10.8570880889893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7551202774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7454090118408</t>
+    <t xml:space="preserve">10.7551193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7454080581665</t>
   </si>
   <si>
     <t xml:space="preserve">10.7842531204224</t>
@@ -3128,16 +3128,16 @@
     <t xml:space="preserve">11.0464553833008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9687652587891</t>
+    <t xml:space="preserve">10.9687662124634</t>
   </si>
   <si>
     <t xml:space="preserve">11.0027551651001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9104986190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8910779953003</t>
+    <t xml:space="preserve">10.9104976654053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.891077041626</t>
   </si>
   <si>
     <t xml:space="preserve">10.997899055481</t>
@@ -3146,10 +3146,10 @@
     <t xml:space="preserve">10.827953338623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9541988372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.978476524353</t>
+    <t xml:space="preserve">10.954197883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9784774780273</t>
   </si>
   <si>
     <t xml:space="preserve">10.8667984008789</t>
@@ -3158,19 +3158,19 @@
     <t xml:space="preserve">10.6531534194946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7162752151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9930429458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.162989616394</t>
+    <t xml:space="preserve">10.7162761688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9930438995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1629905700684</t>
   </si>
   <si>
     <t xml:space="preserve">11.0513105392456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4009122848511</t>
+    <t xml:space="preserve">11.4009113311768</t>
   </si>
   <si>
     <t xml:space="preserve">11.4688911437988</t>
@@ -3179,19 +3179,19 @@
     <t xml:space="preserve">11.4931688308716</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5174465179443</t>
+    <t xml:space="preserve">11.51744556427</t>
   </si>
   <si>
     <t xml:space="preserve">11.5951356887817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5611476898193</t>
+    <t xml:space="preserve">11.561146736145</t>
   </si>
   <si>
     <t xml:space="preserve">11.5028800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6048469543457</t>
+    <t xml:space="preserve">11.60484790802</t>
   </si>
   <si>
     <t xml:space="preserve">11.5805702209473</t>
@@ -3200,7 +3200,7 @@
     <t xml:space="preserve">11.5660028457642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6097030639648</t>
+    <t xml:space="preserve">11.6097040176392</t>
   </si>
   <si>
     <t xml:space="preserve">11.721381187439</t>
@@ -3209,13 +3209,13 @@
     <t xml:space="preserve">11.8621940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">11.745659828186</t>
+    <t xml:space="preserve">11.7456588745117</t>
   </si>
   <si>
     <t xml:space="preserve">11.6922483444214</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6825361251831</t>
+    <t xml:space="preserve">11.6825370788574</t>
   </si>
   <si>
     <t xml:space="preserve">11.3620681762695</t>
@@ -3224,10 +3224,10 @@
     <t xml:space="preserve">11.2552452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4834575653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4251918792725</t>
+    <t xml:space="preserve">11.4834585189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4251909255981</t>
   </si>
   <si>
     <t xml:space="preserve">11.3814907073975</t>
@@ -3245,22 +3245,22 @@
     <t xml:space="preserve">11.5902814865112</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6971044540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5708589553833</t>
+    <t xml:space="preserve">11.6971035003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.570858001709</t>
   </si>
   <si>
     <t xml:space="preserve">11.5757141113281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5125904083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4106245040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5514364242554</t>
+    <t xml:space="preserve">11.5125913619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.410623550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5514354705811</t>
   </si>
   <si>
     <t xml:space="preserve">11.7068157196045</t>
@@ -3269,70 +3269,70 @@
     <t xml:space="preserve">11.9495944976807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9301719665527</t>
+    <t xml:space="preserve">11.9301710128784</t>
   </si>
   <si>
     <t xml:space="preserve">11.7942161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7602243423462</t>
+    <t xml:space="preserve">11.7602262496948</t>
   </si>
   <si>
     <t xml:space="preserve">11.8087825775146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8282051086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7505149841309</t>
+    <t xml:space="preserve">11.8282060623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7505159378052</t>
   </si>
   <si>
     <t xml:space="preserve">11.9253168106079</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0175724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.05641746521</t>
+    <t xml:space="preserve">12.0175714492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0564165115356</t>
   </si>
   <si>
     <t xml:space="preserve">12.036994934082</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1875190734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1486721038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3865976333618</t>
+    <t xml:space="preserve">12.187518119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1486730575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3865966796875</t>
   </si>
   <si>
     <t xml:space="preserve">12.5565423965454</t>
   </si>
   <si>
-    <t xml:space="preserve">12.425440788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5274085998535</t>
+    <t xml:space="preserve">12.4254417419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5274076461792</t>
   </si>
   <si>
     <t xml:space="preserve">12.5322637557983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5662517547607</t>
+    <t xml:space="preserve">12.5662527084351</t>
   </si>
   <si>
     <t xml:space="preserve">11.9350271224976</t>
   </si>
   <si>
-    <t xml:space="preserve">12.012716293335</t>
+    <t xml:space="preserve">12.0127172470093</t>
   </si>
   <si>
     <t xml:space="preserve">12.0758390426636</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1729497909546</t>
+    <t xml:space="preserve">12.1729507446289</t>
   </si>
   <si>
     <t xml:space="preserve">12.3331851959229</t>
@@ -3341,10 +3341,10 @@
     <t xml:space="preserve">12.3137626647949</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4205846786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3040504455566</t>
+    <t xml:space="preserve">12.4205856323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.304051399231</t>
   </si>
   <si>
     <t xml:space="preserve">12.4108734130859</t>
@@ -3365,22 +3365,22 @@
     <t xml:space="preserve">12.7750434875488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9644107818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9595565795898</t>
+    <t xml:space="preserve">12.964412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9595556259155</t>
   </si>
   <si>
     <t xml:space="preserve">12.9401330947876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0760898590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5808210372925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5953874588013</t>
+    <t xml:space="preserve">13.0760889053345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5808200836182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.595386505127</t>
   </si>
   <si>
     <t xml:space="preserve">12.9109992980957</t>
@@ -3389,16 +3389,16 @@
     <t xml:space="preserve">12.4837083816528</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7070655822754</t>
+    <t xml:space="preserve">12.7070646286011</t>
   </si>
   <si>
     <t xml:space="preserve">12.4982748031616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4739971160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3428974151611</t>
+    <t xml:space="preserve">12.4739980697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3428955078125</t>
   </si>
   <si>
     <t xml:space="preserve">12.6390867233276</t>
@@ -3413,19 +3413,19 @@
     <t xml:space="preserve">12.585675239563</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3768844604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4885635375977</t>
+    <t xml:space="preserve">12.3768854141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4885625839233</t>
   </si>
   <si>
     <t xml:space="preserve">12.284628868103</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2797737121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2020845413208</t>
+    <t xml:space="preserve">12.2797746658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2020835876465</t>
   </si>
   <si>
     <t xml:space="preserve">12.4400081634521</t>
@@ -3458,22 +3458,22 @@
     <t xml:space="preserve">11.1532783508301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.216402053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0804443359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0658779144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.696852684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6434412002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6191654205322</t>
+    <t xml:space="preserve">11.2164011001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0804433822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.065878868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6968536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6434421539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6191644668579</t>
   </si>
   <si>
     <t xml:space="preserve">10.5171957015991</t>
@@ -3491,10 +3491,10 @@
     <t xml:space="preserve">10.7114191055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5269069671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4492177963257</t>
+    <t xml:space="preserve">10.5269079208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.44921875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5317640304565</t>
@@ -3503,19 +3503,19 @@
     <t xml:space="preserve">10.4880638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3375415802002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0899057388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821603775024</t>
+    <t xml:space="preserve">10.3375406265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0899047851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821613311768</t>
   </si>
   <si>
     <t xml:space="preserve">10.1918716430664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.264705657959</t>
+    <t xml:space="preserve">10.2647047042847</t>
   </si>
   <si>
     <t xml:space="preserve">9.95880508422852</t>
@@ -3524,7 +3524,7 @@
     <t xml:space="preserve">9.02556037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18870735168457</t>
+    <t xml:space="preserve">9.18870830535889</t>
   </si>
   <si>
     <t xml:space="preserve">9.4664478302002</t>
@@ -3533,7 +3533,7 @@
     <t xml:space="preserve">9.04304122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04498386383057</t>
+    <t xml:space="preserve">9.04498291015625</t>
   </si>
   <si>
     <t xml:space="preserve">9.06246280670166</t>
@@ -3557,10 +3557,10 @@
     <t xml:space="preserve">8.95369815826416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99836921691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03138828277588</t>
+    <t xml:space="preserve">8.99837017059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03138732910156</t>
   </si>
   <si>
     <t xml:space="preserve">9.58492469787598</t>
@@ -3569,19 +3569,19 @@
     <t xml:space="preserve">9.55190658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75001430511475</t>
+    <t xml:space="preserve">9.75001335144043</t>
   </si>
   <si>
     <t xml:space="preserve">9.621826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68203639984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63736438751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62571144104004</t>
+    <t xml:space="preserve">9.68203735351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63736534118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62571048736572</t>
   </si>
   <si>
     <t xml:space="preserve">10.0801935195923</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">10.4259405136108</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5333738327026</t>
+    <t xml:space="preserve">10.5333728790283</t>
   </si>
   <si>
     <t xml:space="preserve">10.2306051254272</t>
@@ -3641,13 +3641,13 @@
     <t xml:space="preserve">10.4601230621338</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0645723342896</t>
+    <t xml:space="preserve">10.0645732879639</t>
   </si>
   <si>
     <t xml:space="preserve">10.1720056533813</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5498685836792</t>
+    <t xml:space="preserve">9.54986763000488</t>
   </si>
   <si>
     <t xml:space="preserve">9.33890724182129</t>
@@ -3662,10 +3662,10 @@
     <t xml:space="preserve">9.669020652771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97178840637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0059728622437</t>
+    <t xml:space="preserve">9.97178936004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0059719085693</t>
   </si>
   <si>
     <t xml:space="preserve">9.91318893432617</t>
@@ -3692,13 +3692,13 @@
     <t xml:space="preserve">9.47368717193604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.659255027771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78622245788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71004199981689</t>
+    <t xml:space="preserve">9.65925407409668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78622150421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71004104614258</t>
   </si>
   <si>
     <t xml:space="preserve">9.51861476898193</t>
@@ -3731,10 +3731,10 @@
     <t xml:space="preserve">9.20607948303223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11427211761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52252101898193</t>
+    <t xml:space="preserve">9.11427307128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52252006530762</t>
   </si>
   <si>
     <t xml:space="preserve">9.5674467086792</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">9.91807174682617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81552124023438</t>
+    <t xml:space="preserve">9.81552219390869</t>
   </si>
   <si>
     <t xml:space="preserve">9.80087089538574</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">9.661208152771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95713806152344</t>
+    <t xml:space="preserve">9.95713901519775</t>
   </si>
   <si>
     <t xml:space="preserve">10.001088142395</t>
@@ -3779,10 +3779,10 @@
     <t xml:space="preserve">10.162239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2989730834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0499229431152</t>
+    <t xml:space="preserve">10.2989721298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0499219894409</t>
   </si>
   <si>
     <t xml:space="preserve">9.94248867034912</t>
@@ -3791,13 +3791,13 @@
     <t xml:space="preserve">9.9376049041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96690559387207</t>
+    <t xml:space="preserve">9.96690464019775</t>
   </si>
   <si>
     <t xml:space="preserve">9.88877201080322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1329393386841</t>
+    <t xml:space="preserve">10.1329383850098</t>
   </si>
   <si>
     <t xml:space="preserve">10.2354888916016</t>
@@ -3806,7 +3806,7 @@
     <t xml:space="preserve">10.4161729812622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.18665599823</t>
+    <t xml:space="preserve">10.1866550445557</t>
   </si>
   <si>
     <t xml:space="preserve">10.167121887207</t>
@@ -3836,31 +3836,31 @@
     <t xml:space="preserve">9.78133869171143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87900543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0352716445923</t>
+    <t xml:space="preserve">9.87900447845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.035270690918</t>
   </si>
   <si>
     <t xml:space="preserve">10.1134052276611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1475896835327</t>
+    <t xml:space="preserve">10.1475887298584</t>
   </si>
   <si>
     <t xml:space="preserve">10.152473449707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98155498504639</t>
+    <t xml:space="preserve">9.9815559387207</t>
   </si>
   <si>
     <t xml:space="preserve">9.83505439758301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57916736602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4482946395874</t>
+    <t xml:space="preserve">9.57916641235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44829368591309</t>
   </si>
   <si>
     <t xml:space="preserve">9.62409400939941</t>
@@ -3878,16 +3878,16 @@
     <t xml:space="preserve">9.33109378814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46001434326172</t>
+    <t xml:space="preserve">9.4600133895874</t>
   </si>
   <si>
     <t xml:space="preserve">9.29593372344971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31742000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9658203125</t>
+    <t xml:space="preserve">9.31742095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96581935882568</t>
   </si>
   <si>
     <t xml:space="preserve">9.00683975219727</t>
@@ -3899,10 +3899,10 @@
     <t xml:space="preserve">9.0752067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78025150299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68649291992188</t>
+    <t xml:space="preserve">8.78025245666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68649196624756</t>
   </si>
   <si>
     <t xml:space="preserve">8.89550018310547</t>
@@ -3914,7 +3914,7 @@
     <t xml:space="preserve">8.88377857208252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72360515594482</t>
+    <t xml:space="preserve">8.72360610961914</t>
   </si>
   <si>
     <t xml:space="preserve">8.89940738677979</t>
@@ -3929,13 +3929,13 @@
     <t xml:space="preserve">8.78806591033936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88964080810547</t>
+    <t xml:space="preserve">8.88963985443115</t>
   </si>
   <si>
     <t xml:space="preserve">8.79783344268799</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94628715515137</t>
+    <t xml:space="preserve">8.94628620147705</t>
   </si>
   <si>
     <t xml:space="preserve">8.98144626617432</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">8.98535346984863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96191215515137</t>
+    <t xml:space="preserve">8.96191310882568</t>
   </si>
   <si>
     <t xml:space="preserve">8.84080505371094</t>
@@ -3962,19 +3962,19 @@
     <t xml:space="preserve">8.72165298461914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90917301177979</t>
+    <t xml:space="preserve">8.90917205810547</t>
   </si>
   <si>
     <t xml:space="preserve">8.79587936401367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80173969268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70798015594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88182544708252</t>
+    <t xml:space="preserve">8.8017406463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70797920227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88182640075684</t>
   </si>
   <si>
     <t xml:space="preserve">8.99707317352295</t>
@@ -3983,13 +3983,13 @@
     <t xml:space="preserve">9.10841369628906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96386623382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09473991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11622619628906</t>
+    <t xml:space="preserve">8.9638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09474086761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11622524261475</t>
   </si>
   <si>
     <t xml:space="preserve">8.9755859375</t>
@@ -4004,7 +4004,7 @@
     <t xml:space="preserve">9.54205513000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4932222366333</t>
+    <t xml:space="preserve">9.49322128295898</t>
   </si>
   <si>
     <t xml:space="preserve">9.5654935836792</t>
@@ -4013,10 +4013,10 @@
     <t xml:space="preserve">9.73543548583984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76278209686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1280546188354</t>
+    <t xml:space="preserve">9.76278114318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1280555725098</t>
   </si>
   <si>
     <t xml:space="preserve">9.96202182769775</t>
@@ -4034,10 +4034,10 @@
     <t xml:space="preserve">9.72371387481689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75692176818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92783832550049</t>
+    <t xml:space="preserve">9.75692081451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9278392791748</t>
   </si>
   <si>
     <t xml:space="preserve">9.95225429534912</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">9.62214088439941</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31546783447266</t>
+    <t xml:space="preserve">9.31546688079834</t>
   </si>
   <si>
     <t xml:space="preserve">9.5108003616333</t>
@@ -4058,10 +4058,10 @@
     <t xml:space="preserve">9.40336799621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38774013519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42290115356445</t>
+    <t xml:space="preserve">9.38774108886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42290019989014</t>
   </si>
   <si>
     <t xml:space="preserve">9.45806121826172</t>
@@ -4085,46 +4085,46 @@
     <t xml:space="preserve">9.64948844909668</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65729999542236</t>
+    <t xml:space="preserve">9.65730094909668</t>
   </si>
   <si>
     <t xml:space="preserve">9.74324798583984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71199512481689</t>
+    <t xml:space="preserve">9.71199417114258</t>
   </si>
   <si>
     <t xml:space="preserve">9.71785354614258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44438648223877</t>
+    <t xml:space="preserve">9.44438743591309</t>
   </si>
   <si>
     <t xml:space="preserve">9.42876052856445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43852615356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71590137481689</t>
+    <t xml:space="preserve">9.43852710723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71590042114258</t>
   </si>
   <si>
     <t xml:space="preserve">10.0303888320923</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90342235565186</t>
+    <t xml:space="preserve">9.90342140197754</t>
   </si>
   <si>
     <t xml:space="preserve">9.83017158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1427068710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2696733474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2452554702759</t>
+    <t xml:space="preserve">10.1427059173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2696723937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2452564239502</t>
   </si>
   <si>
     <t xml:space="preserve">10.3038558959961</t>
@@ -4136,13 +4136,13 @@
     <t xml:space="preserve">10.3380393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4796562194824</t>
+    <t xml:space="preserve">10.4796552658081</t>
   </si>
   <si>
     <t xml:space="preserve">10.2550220489502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3722219467163</t>
+    <t xml:space="preserve">10.3722229003906</t>
   </si>
   <si>
     <t xml:space="preserve">10.3478059768677</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">10.4698905944824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405889511108</t>
+    <t xml:space="preserve">10.4405899047852</t>
   </si>
   <si>
     <t xml:space="preserve">10.3917560577393</t>
@@ -4178,25 +4178,25 @@
     <t xml:space="preserve">10.6261568069458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7580070495605</t>
+    <t xml:space="preserve">10.7580080032349</t>
   </si>
   <si>
     <t xml:space="preserve">10.8703241348267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.860556602478</t>
+    <t xml:space="preserve">10.8605575561523</t>
   </si>
   <si>
     <t xml:space="preserve">10.8312568664551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7775392532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.880090713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8361406326294</t>
+    <t xml:space="preserve">10.7775402069092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8800897598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8361396789551</t>
   </si>
   <si>
     <t xml:space="preserve">10.9875240325928</t>
@@ -4214,10 +4214,10 @@
     <t xml:space="preserve">11.2463417053223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2268085479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.212158203125</t>
+    <t xml:space="preserve">11.2268075942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2121572494507</t>
   </si>
   <si>
     <t xml:space="preserve">11.2072744369507</t>
@@ -4226,13 +4226,13 @@
     <t xml:space="preserve">11.2561082839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2854080200195</t>
+    <t xml:space="preserve">11.2854089736938</t>
   </si>
   <si>
     <t xml:space="preserve">11.3195915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3488922119141</t>
+    <t xml:space="preserve">11.3488912582397</t>
   </si>
   <si>
     <t xml:space="preserve">11.373309135437</t>
@@ -5910,6 +5910,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.44999980926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45800018310547</t>
   </si>
 </sst>
 </file>
@@ -70884,7 +70887,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6516898148</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>5376108</v>
@@ -70905,6 +70908,32 @@
         <v>1965</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6495138889</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>3414414</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>5.52400016784668</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>5.4520001411438</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>5.46999979019165</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>5.45800018310547</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>1966</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="1968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1969" uniqueCount="1969">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59865665435791</t>
+    <t xml:space="preserve">3.59865641593933</t>
   </si>
   <si>
     <t xml:space="preserve">CPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65898251533508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60329699516296</t>
+    <t xml:space="preserve">3.6589822769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60329675674438</t>
   </si>
   <si>
     <t xml:space="preserve">3.51976895332336</t>
@@ -56,7 +56,7 @@
     <t xml:space="preserve">3.51048851013184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54993200302124</t>
+    <t xml:space="preserve">3.5499324798584</t>
   </si>
   <si>
     <t xml:space="preserve">3.62881946563721</t>
@@ -68,28 +68,28 @@
     <t xml:space="preserve">3.57313394546509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52672982215881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48264575004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56617331504822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43392109870911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5058479309082</t>
+    <t xml:space="preserve">3.52673006057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4826455116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5661735534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43392133712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50584769248962</t>
   </si>
   <si>
     <t xml:space="preserve">3.56153321266174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64274024963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66594266891479</t>
+    <t xml:space="preserve">3.64274072647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66594290733337</t>
   </si>
   <si>
     <t xml:space="preserve">3.56849360466003</t>
@@ -98,25 +98,25 @@
     <t xml:space="preserve">3.74251008033752</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72162842750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70770645141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47104477882385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44320225715637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28078699111938</t>
+    <t xml:space="preserve">3.72162818908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70770692825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47104430198669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44320178031921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28078651428223</t>
   </si>
   <si>
     <t xml:space="preserve">3.33183121681213</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40839838981628</t>
+    <t xml:space="preserve">3.40839862823486</t>
   </si>
   <si>
     <t xml:space="preserve">3.22046136856079</t>
@@ -131,16 +131,16 @@
     <t xml:space="preserve">3.24366354942322</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32255053520203</t>
+    <t xml:space="preserve">3.32255077362061</t>
   </si>
   <si>
     <t xml:space="preserve">3.28774738311768</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31791043281555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36663460731506</t>
+    <t xml:space="preserve">3.31791019439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36663484573364</t>
   </si>
   <si>
     <t xml:space="preserve">3.36199450492859</t>
@@ -149,37 +149,37 @@
     <t xml:space="preserve">3.40607857704163</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3828763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36431431770325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53137016296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60561752319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61257791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56385326385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61489748954773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63810014724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68914484977722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476277351379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95596981048584</t>
+    <t xml:space="preserve">3.38287615776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36431455612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53137040138245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6056170463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61257767677307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5638530254364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61489796638489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63809990882874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6891450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476253509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95596933364868</t>
   </si>
   <si>
     <t xml:space="preserve">4.00701522827148</t>
@@ -194,25 +194,25 @@
     <t xml:space="preserve">4.04181814193726</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03717803955078</t>
+    <t xml:space="preserve">4.03717708587646</t>
   </si>
   <si>
     <t xml:space="preserve">4.05109882354736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01861524581909</t>
+    <t xml:space="preserve">4.01861572265625</t>
   </si>
   <si>
     <t xml:space="preserve">4.09286260604858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07662153244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03949737548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08358192443848</t>
+    <t xml:space="preserve">4.07662105560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03949689865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08358240127563</t>
   </si>
   <si>
     <t xml:space="preserve">4.02325677871704</t>
@@ -233,49 +233,49 @@
     <t xml:space="preserve">3.97453117370605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00237512588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93740773200989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94669008255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03021717071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05341958999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00933504104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9582896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98613357543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02557706832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96989178657532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91188526153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89796447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87708258628845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91420674324036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92812633514404</t>
+    <t xml:space="preserve">4.00237464904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9374086856842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94668865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03021764755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05341911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0093355178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95829010009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98613309860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0255765914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96989130973816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91188597679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89796423912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87708234786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9142062664032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92812824249268</t>
   </si>
   <si>
     <t xml:space="preserve">3.95133018493652</t>
@@ -287,34 +287,34 @@
     <t xml:space="preserve">4.08126211166382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99309277534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96757054328918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98149251937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96293044090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88868403434753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89332437515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79587507247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89309906959534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02677726745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08540868759155</t>
+    <t xml:space="preserve">3.99309372901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96757102012634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9814920425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96293091773987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8886833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89332485198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79587483406067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89309883117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0267767906189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08540821075439</t>
   </si>
   <si>
     <t xml:space="preserve">4.07602787017822</t>
@@ -332,28 +332,28 @@
     <t xml:space="preserve">4.0900993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10182476043701</t>
+    <t xml:space="preserve">4.10182523727417</t>
   </si>
   <si>
     <t xml:space="preserve">4.0877537727356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11355209350586</t>
+    <t xml:space="preserve">4.1135516166687</t>
   </si>
   <si>
     <t xml:space="preserve">4.08071851730347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01974248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90482497215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85557579994202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85792088508606</t>
+    <t xml:space="preserve">4.01974201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90482473373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85557508468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85792112350464</t>
   </si>
   <si>
     <t xml:space="preserve">3.86495614051819</t>
@@ -368,58 +368,58 @@
     <t xml:space="preserve">4.00567054748535</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00801515579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95876526832581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05961132049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88606357574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88840818405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04084920883179</t>
+    <t xml:space="preserve">4.00801467895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95876574516296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05961036682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88606262207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88840889930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04084873199463</t>
   </si>
   <si>
     <t xml:space="preserve">4.16514682769775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15576505661011</t>
+    <t xml:space="preserve">4.15576553344727</t>
   </si>
   <si>
     <t xml:space="preserve">4.14872980117798</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13231372833252</t>
+    <t xml:space="preserve">4.13231325149536</t>
   </si>
   <si>
     <t xml:space="preserve">4.00332450866699</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04319381713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16045618057251</t>
+    <t xml:space="preserve">4.04319429397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16045665740967</t>
   </si>
   <si>
     <t xml:space="preserve">4.15811157226562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1158971786499</t>
+    <t xml:space="preserve">4.11589670181274</t>
   </si>
   <si>
     <t xml:space="preserve">4.06899261474609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1346583366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14169454574585</t>
+    <t xml:space="preserve">4.13465881347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14169406890869</t>
   </si>
   <si>
     <t xml:space="preserve">4.18390893936157</t>
@@ -434,25 +434,25 @@
     <t xml:space="preserve">4.29178953170776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29648017883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31055164337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28709983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3316593170166</t>
+    <t xml:space="preserve">4.29647970199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31055068969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28709888458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33165884017944</t>
   </si>
   <si>
     <t xml:space="preserve">4.33869504928589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54038524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51458740234375</t>
+    <t xml:space="preserve">4.54038572311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51458692550659</t>
   </si>
   <si>
     <t xml:space="preserve">4.5216236114502</t>
@@ -461,22 +461,22 @@
     <t xml:space="preserve">4.43719434738159</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47940969467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45595598220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66233730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67171859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58963537216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55914783477783</t>
+    <t xml:space="preserve">4.47940921783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45595645904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66233777999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67171955108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58963441848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55914735794067</t>
   </si>
   <si>
     <t xml:space="preserve">4.56383752822876</t>
@@ -497,25 +497,25 @@
     <t xml:space="preserve">4.62012386322021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59432601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65061092376709</t>
+    <t xml:space="preserve">4.59432554244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65061140060425</t>
   </si>
   <si>
     <t xml:space="preserve">4.57556390762329</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70455169677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67406368255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70924234390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6013617515564</t>
+    <t xml:space="preserve">4.7045521736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67406415939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70924282073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60136222839355</t>
   </si>
   <si>
     <t xml:space="preserve">4.48644495010376</t>
@@ -524,7 +524,7 @@
     <t xml:space="preserve">4.46533823013306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39967060089111</t>
+    <t xml:space="preserve">4.39967107772827</t>
   </si>
   <si>
     <t xml:space="preserve">4.43250417709351</t>
@@ -533,13 +533,13 @@
     <t xml:space="preserve">4.50520658493042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49113512039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51693296432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50286197662354</t>
+    <t xml:space="preserve">4.491135597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51693344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50286149978638</t>
   </si>
   <si>
     <t xml:space="preserve">4.48878955841064</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">4.65295696258545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66468334197998</t>
+    <t xml:space="preserve">4.66468286514282</t>
   </si>
   <si>
     <t xml:space="preserve">4.73269510269165</t>
@@ -557,28 +557,28 @@
     <t xml:space="preserve">4.71393346786499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69048070907593</t>
+    <t xml:space="preserve">4.69048118591309</t>
   </si>
   <si>
     <t xml:space="preserve">4.58729028701782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56852912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47471857070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44657564163208</t>
+    <t xml:space="preserve">4.56852865219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47471809387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44657611846924</t>
   </si>
   <si>
     <t xml:space="preserve">4.54742097854614</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44188547134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50051546096802</t>
+    <t xml:space="preserve">4.44188451766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50051641464233</t>
   </si>
   <si>
     <t xml:space="preserve">4.52631330490112</t>
@@ -587,25 +587,25 @@
     <t xml:space="preserve">4.36683750152588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37152719497681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33400392532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32931327819824</t>
+    <t xml:space="preserve">4.37152767181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33400440216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32931280136108</t>
   </si>
   <si>
     <t xml:space="preserve">4.30586099624634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30351591110229</t>
+    <t xml:space="preserve">4.30351638793945</t>
   </si>
   <si>
     <t xml:space="preserve">4.25661087036133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20736122131348</t>
+    <t xml:space="preserve">4.20736074447632</t>
   </si>
   <si>
     <t xml:space="preserve">4.09478950500488</t>
@@ -614,16 +614,16 @@
     <t xml:space="preserve">4.24253988265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20267057418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9564208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95407462120056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03381395339966</t>
+    <t xml:space="preserve">4.20267105102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95642042160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95407605171204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0338134765625</t>
   </si>
   <si>
     <t xml:space="preserve">4.12527799606323</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">4.01739597320557</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12996864318848</t>
+    <t xml:space="preserve">4.12996816635132</t>
   </si>
   <si>
     <t xml:space="preserve">4.17218255996704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21205139160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18859958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2495756149292</t>
+    <t xml:space="preserve">4.2120509147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18860006332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24957609176636</t>
   </si>
   <si>
     <t xml:space="preserve">4.20501613616943</t>
@@ -662,13 +662,13 @@
     <t xml:space="preserve">4.31993293762207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36449289321899</t>
+    <t xml:space="preserve">4.36449241638184</t>
   </si>
   <si>
     <t xml:space="preserve">4.28944492340088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27771806716919</t>
+    <t xml:space="preserve">4.27771854400635</t>
   </si>
   <si>
     <t xml:space="preserve">4.30117130279541</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">4.35745716094971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34807682037354</t>
+    <t xml:space="preserve">4.34807586669922</t>
   </si>
   <si>
     <t xml:space="preserve">4.34338521957397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39028930664062</t>
+    <t xml:space="preserve">4.3902907371521</t>
   </si>
   <si>
     <t xml:space="preserve">4.36214733123779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32462310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39732551574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37387323379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36918258666992</t>
+    <t xml:space="preserve">4.32462406158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39732503890991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37387275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36918306350708</t>
   </si>
   <si>
     <t xml:space="preserve">4.47002792358398</t>
@@ -710,19 +710,19 @@
     <t xml:space="preserve">4.45830249786377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42546939849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43484926223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46768188476562</t>
+    <t xml:space="preserve">4.42546892166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43485021591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46768283843994</t>
   </si>
   <si>
     <t xml:space="preserve">4.40201616287231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35276556015015</t>
+    <t xml:space="preserve">4.3527660369873</t>
   </si>
   <si>
     <t xml:space="preserve">4.38559913635254</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">4.43954038619995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43015909194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49347925186157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47237300872803</t>
+    <t xml:space="preserve">4.4301586151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49348020553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47237348556519</t>
   </si>
   <si>
     <t xml:space="preserve">4.5239691734314</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">4.53803968429565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5450758934021</t>
+    <t xml:space="preserve">4.54507541656494</t>
   </si>
   <si>
     <t xml:space="preserve">4.58260011672974</t>
@@ -761,22 +761,22 @@
     <t xml:space="preserve">4.55211162567139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57087326049805</t>
+    <t xml:space="preserve">4.57087278366089</t>
   </si>
   <si>
     <t xml:space="preserve">4.53569507598877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50755167007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58494424819946</t>
+    <t xml:space="preserve">4.5075511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58494472503662</t>
   </si>
   <si>
     <t xml:space="preserve">4.65530204772949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74207544326782</t>
+    <t xml:space="preserve">4.74207592010498</t>
   </si>
   <si>
     <t xml:space="preserve">4.7561469078064</t>
@@ -785,61 +785,61 @@
     <t xml:space="preserve">4.80774259567261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83119630813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89686155319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94845724105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09855270385742</t>
+    <t xml:space="preserve">4.83119535446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89686107635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94845676422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09855222702026</t>
   </si>
   <si>
     <t xml:space="preserve">5.05164861679077</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12200498580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04695749282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05633735656738</t>
+    <t xml:space="preserve">5.12200450897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04695701599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0563383102417</t>
   </si>
   <si>
     <t xml:space="preserve">4.99536180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01881408691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02819585800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03288555145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93907642364502</t>
+    <t xml:space="preserve">5.01881456375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02819490432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03288602828979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93907594680786</t>
   </si>
   <si>
     <t xml:space="preserve">4.9766001701355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92500400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96721839904785</t>
+    <t xml:space="preserve">4.92500448226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96721935272217</t>
   </si>
   <si>
     <t xml:space="preserve">5.08917140960693</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17359972000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14545774459839</t>
+    <t xml:space="preserve">5.17360019683838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14545726776123</t>
   </si>
   <si>
     <t xml:space="preserve">5.15952920913696</t>
@@ -848,43 +848,43 @@
     <t xml:space="preserve">5.09386157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16421937942505</t>
+    <t xml:space="preserve">5.16421890258789</t>
   </si>
   <si>
     <t xml:space="preserve">5.25333786010742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18767166137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41750574111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67079067230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60043382644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6238865852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66140985488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68486261367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57698154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60512447357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72238683700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69403409957886</t>
+    <t xml:space="preserve">5.18767213821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41750526428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67079019546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60043334960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62388610839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66141033172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68486356735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57698202133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60512399673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72238636016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6940336227417</t>
   </si>
   <si>
     <t xml:space="preserve">5.74128770828247</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">5.8783221244812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86887216567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88304758071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0200834274292</t>
+    <t xml:space="preserve">5.86887121200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88304805755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02008247375488</t>
   </si>
   <si>
     <t xml:space="preserve">5.99173069000244</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">6.00118160247803</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93502712249756</t>
+    <t xml:space="preserve">5.9350266456604</t>
   </si>
   <si>
     <t xml:space="preserve">5.85942077636719</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">5.8027172088623</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75546360015869</t>
+    <t xml:space="preserve">5.75546312332153</t>
   </si>
   <si>
     <t xml:space="preserve">5.73183727264404</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">5.81216764450073</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95865345001221</t>
+    <t xml:space="preserve">5.95865297317505</t>
   </si>
   <si>
     <t xml:space="preserve">5.93030118942261</t>
@@ -947,31 +947,31 @@
     <t xml:space="preserve">5.90194940567017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91612529754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91139984130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8310694694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88777351379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78381586074829</t>
+    <t xml:space="preserve">5.9161262512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91140031814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83106899261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88777303695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78381633758545</t>
   </si>
   <si>
     <t xml:space="preserve">5.8074426651001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84524488449097</t>
+    <t xml:space="preserve">5.84524583816528</t>
   </si>
   <si>
     <t xml:space="preserve">5.77436494827271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82634353637695</t>
+    <t xml:space="preserve">5.82634305953979</t>
   </si>
   <si>
     <t xml:space="preserve">5.82161855697632</t>
@@ -983,34 +983,34 @@
     <t xml:space="preserve">5.79326629638672</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8357949256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95392799377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92557621002197</t>
+    <t xml:space="preserve">5.83579444885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95392894744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92557573318481</t>
   </si>
   <si>
     <t xml:space="preserve">5.94447708129883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77909135818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74601364135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71766090393066</t>
+    <t xml:space="preserve">5.7790904045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74601268768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71766042709351</t>
   </si>
   <si>
     <t xml:space="preserve">5.65150690078735</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66095685958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79799222946167</t>
+    <t xml:space="preserve">5.66095638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79799175262451</t>
   </si>
   <si>
     <t xml:space="preserve">5.76018857955933</t>
@@ -1022,37 +1022,37 @@
     <t xml:space="preserve">5.66568183898926</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73656272888184</t>
+    <t xml:space="preserve">5.73656225204468</t>
   </si>
   <si>
     <t xml:space="preserve">5.78854131698608</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76963996887207</t>
+    <t xml:space="preserve">5.76963949203491</t>
   </si>
   <si>
     <t xml:space="preserve">5.89249897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97282934188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15239238739014</t>
+    <t xml:space="preserve">5.97282981872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15239191055298</t>
   </si>
   <si>
     <t xml:space="preserve">6.14766693115234</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28470230102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1382155418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12403964996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02953290939331</t>
+    <t xml:space="preserve">6.28470182418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13821649551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12404012680054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02953386306763</t>
   </si>
   <si>
     <t xml:space="preserve">6.10513877868652</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">6.47844076156616</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31305360794067</t>
+    <t xml:space="preserve">6.31305313110352</t>
   </si>
   <si>
     <t xml:space="preserve">6.33668041229248</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">6.37448263168335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17601871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0909628868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23272228240967</t>
+    <t xml:space="preserve">6.17601823806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09096240997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23272180557251</t>
   </si>
   <si>
     <t xml:space="preserve">6.0389838218689</t>
@@ -1112,19 +1112,19 @@
     <t xml:space="preserve">6.10041284561157</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10986471176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0059061050415</t>
+    <t xml:space="preserve">6.10986423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00590753555298</t>
   </si>
   <si>
     <t xml:space="preserve">6.03425931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09568786621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06261014938354</t>
+    <t xml:space="preserve">6.09568738937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06261157989502</t>
   </si>
   <si>
     <t xml:space="preserve">6.18074417114258</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">6.08151197433472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15711641311646</t>
+    <t xml:space="preserve">6.15711688995361</t>
   </si>
   <si>
     <t xml:space="preserve">6.21382093429565</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24217367172241</t>
+    <t xml:space="preserve">6.24217319488525</t>
   </si>
   <si>
     <t xml:space="preserve">6.24689960479736</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">6.20909595489502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22799825668335</t>
+    <t xml:space="preserve">6.22799777984619</t>
   </si>
   <si>
     <t xml:space="preserve">6.19964551925659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12876605987549</t>
+    <t xml:space="preserve">6.12876558303833</t>
   </si>
   <si>
     <t xml:space="preserve">6.07206201553345</t>
@@ -1163,16 +1163,16 @@
     <t xml:space="preserve">6.05788564682007</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13349056243896</t>
+    <t xml:space="preserve">6.13349008560181</t>
   </si>
   <si>
     <t xml:space="preserve">6.14294147491455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01063203811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94920301437378</t>
+    <t xml:space="preserve">6.01063251495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94920349121094</t>
   </si>
   <si>
     <t xml:space="preserve">5.97755432128906</t>
@@ -1184,46 +1184,46 @@
     <t xml:space="preserve">5.99645662307739</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0673360824585</t>
+    <t xml:space="preserve">6.06733655929565</t>
   </si>
   <si>
     <t xml:space="preserve">5.93975162506104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71293592453003</t>
+    <t xml:space="preserve">5.71293544769287</t>
   </si>
   <si>
     <t xml:space="preserve">5.72711181640625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92085027694702</t>
+    <t xml:space="preserve">5.92085075378418</t>
   </si>
   <si>
     <t xml:space="preserve">5.5759015083313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52864742279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42941474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50502061843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61370420455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63733005523682</t>
+    <t xml:space="preserve">5.52864694595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42941522598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50502014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61370372772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63732957839966</t>
   </si>
   <si>
     <t xml:space="preserve">6.04370927810669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98700523376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01535701751709</t>
+    <t xml:space="preserve">5.98700571060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01535749435425</t>
   </si>
   <si>
     <t xml:space="preserve">5.89722394943237</t>
@@ -1238,19 +1238,19 @@
     <t xml:space="preserve">5.86414670944214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9066743850708</t>
+    <t xml:space="preserve">5.90667390823364</t>
   </si>
   <si>
     <t xml:space="preserve">5.96810388565063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01550769805908</t>
+    <t xml:space="preserve">6.01550817489624</t>
   </si>
   <si>
     <t xml:space="preserve">6.02027034759521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99169254302979</t>
+    <t xml:space="preserve">5.99169301986694</t>
   </si>
   <si>
     <t xml:space="preserve">6.08218765258789</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">6.20602226257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18697071075439</t>
+    <t xml:space="preserve">6.18697118759155</t>
   </si>
   <si>
     <t xml:space="preserve">6.08695077896118</t>
@@ -1268,25 +1268,25 @@
     <t xml:space="preserve">6.07266187667847</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16315650939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27270269393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2536506652832</t>
+    <t xml:space="preserve">6.16315603256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27270221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25365114212036</t>
   </si>
   <si>
     <t xml:space="preserve">6.13934230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29175424575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38701152801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52513408660889</t>
+    <t xml:space="preserve">6.2917537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38701200485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52513456344604</t>
   </si>
   <si>
     <t xml:space="preserve">6.5965781211853</t>
@@ -1295,22 +1295,22 @@
     <t xml:space="preserve">6.69183540344238</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69659852981567</t>
+    <t xml:space="preserve">6.69659900665283</t>
   </si>
   <si>
     <t xml:space="preserve">6.62039232254028</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57276344299316</t>
+    <t xml:space="preserve">6.57276391983032</t>
   </si>
   <si>
     <t xml:space="preserve">6.50608348846436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58228921890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65373229980469</t>
+    <t xml:space="preserve">6.58228874206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65373277664185</t>
   </si>
   <si>
     <t xml:space="preserve">6.71088647842407</t>
@@ -1319,7 +1319,7 @@
     <t xml:space="preserve">6.8251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77280473709106</t>
+    <t xml:space="preserve">6.77280426025391</t>
   </si>
   <si>
     <t xml:space="preserve">6.82995891571045</t>
@@ -1328,13 +1328,13 @@
     <t xml:space="preserve">7.0252366065979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92521667480469</t>
+    <t xml:space="preserve">6.92521619796753</t>
   </si>
   <si>
     <t xml:space="preserve">6.92045307159424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01094818115234</t>
+    <t xml:space="preserve">7.01094770431519</t>
   </si>
   <si>
     <t xml:space="preserve">6.96808195114136</t>
@@ -1346,22 +1346,22 @@
     <t xml:space="preserve">7.01571083068848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04905080795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17764854431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28243112564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22051382064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2395658493042</t>
+    <t xml:space="preserve">7.04905033111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09667921066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17764902114868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28243064880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22051334381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23956489562988</t>
   </si>
   <si>
     <t xml:space="preserve">7.27766847610474</t>
@@ -1373,37 +1373,37 @@
     <t xml:space="preserve">6.94903087615967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86806154251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00142192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00618457794189</t>
+    <t xml:space="preserve">6.86806201934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0014214515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00618505477905</t>
   </si>
   <si>
     <t xml:space="preserve">7.0633397102356</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97760820388794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99189710617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03952550888062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02047300338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07762765884399</t>
+    <t xml:space="preserve">6.97760772705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99189615249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03952503204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02047348022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07762718200684</t>
   </si>
   <si>
     <t xml:space="preserve">7.18717432022095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21098804473877</t>
+    <t xml:space="preserve">7.21098852157593</t>
   </si>
   <si>
     <t xml:space="preserve">7.4157919883728</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">7.29672002792358</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26337957382202</t>
+    <t xml:space="preserve">7.26338005065918</t>
   </si>
   <si>
     <t xml:space="preserve">7.24432849884033</t>
@@ -1430,31 +1430,31 @@
     <t xml:space="preserve">7.25385427474976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05857610702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10620450973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14907169342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1681227684021</t>
+    <t xml:space="preserve">7.05857563018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10620546340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14907073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16812229156494</t>
   </si>
   <si>
     <t xml:space="preserve">6.90140199661255</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94426679611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06810235977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98713397979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13001918792725</t>
+    <t xml:space="preserve">6.94426727294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06810188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98713302612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1300196647644</t>
   </si>
   <si>
     <t xml:space="preserve">6.87758731842041</t>
@@ -1466,19 +1466,19 @@
     <t xml:space="preserve">6.63944339752197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65849494934082</t>
+    <t xml:space="preserve">6.65849542617798</t>
   </si>
   <si>
     <t xml:space="preserve">6.32985687255859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1964955329895</t>
+    <t xml:space="preserve">6.19649648666382</t>
   </si>
   <si>
     <t xml:space="preserve">6.11552810668945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04884719848633</t>
+    <t xml:space="preserve">6.04884672164917</t>
   </si>
   <si>
     <t xml:space="preserve">6.21554803848267</t>
@@ -1487,22 +1487,22 @@
     <t xml:space="preserve">6.31556844711304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33461999893188</t>
+    <t xml:space="preserve">6.33461952209473</t>
   </si>
   <si>
     <t xml:space="preserve">6.34414577484131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12505340576172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15363073348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30604219436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35367202758789</t>
+    <t xml:space="preserve">6.12505292892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15363121032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30604267120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35367155075073</t>
   </si>
   <si>
     <t xml:space="preserve">6.47274303436279</t>
@@ -1511,16 +1511,16 @@
     <t xml:space="preserve">6.46798038482666</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42987775802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52989816665649</t>
+    <t xml:space="preserve">6.42987728118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52989721298218</t>
   </si>
   <si>
     <t xml:space="preserve">6.76804113388062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08239078521729</t>
+    <t xml:space="preserve">7.08238983154297</t>
   </si>
   <si>
     <t xml:space="preserve">7.11096858978271</t>
@@ -1529,28 +1529,28 @@
     <t xml:space="preserve">7.12049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32529735565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31577110290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11573028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03476238250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15383386611938</t>
+    <t xml:space="preserve">7.32529783248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31577062606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11573123931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03476285934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15383434295654</t>
   </si>
   <si>
     <t xml:space="preserve">7.04428815841675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02999925613403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17288494110107</t>
+    <t xml:space="preserve">7.02999877929688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17288541793823</t>
   </si>
   <si>
     <t xml:space="preserve">7.36340045928955</t>
@@ -1583,34 +1583,34 @@
     <t xml:space="preserve">7.21575117111206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33958578109741</t>
+    <t xml:space="preserve">7.33958530426025</t>
   </si>
   <si>
     <t xml:space="preserve">7.35387468338013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.55391502380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60630702972412</t>
+    <t xml:space="preserve">7.55391597747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60630655288696</t>
   </si>
   <si>
     <t xml:space="preserve">7.46342086791992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49199819564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44436883926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42055416107178</t>
+    <t xml:space="preserve">7.49199771881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44436931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42055511474609</t>
   </si>
   <si>
     <t xml:space="preserve">7.62535858154297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53010177612305</t>
+    <t xml:space="preserve">7.53010082244873</t>
   </si>
   <si>
     <t xml:space="preserve">7.47294569015503</t>
@@ -1631,10 +1631,10 @@
     <t xml:space="preserve">7.61106967926025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56344079971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64440965652466</t>
+    <t xml:space="preserve">7.56344127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64441013336182</t>
   </si>
   <si>
     <t xml:space="preserve">7.73490428924561</t>
@@ -1643,61 +1643,61 @@
     <t xml:space="preserve">7.80634737014771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86826515197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85873937606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88731622695923</t>
+    <t xml:space="preserve">7.86826419830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8587384223938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8873143196106</t>
   </si>
   <si>
     <t xml:space="preserve">7.92541885375977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95399713516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83492422103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9873366355896</t>
+    <t xml:space="preserve">7.95399808883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83492517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98733758926392</t>
   </si>
   <si>
     <t xml:space="preserve">8.01115036010742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06354141235352</t>
+    <t xml:space="preserve">8.06354427337646</t>
   </si>
   <si>
     <t xml:space="preserve">7.53486347198486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52057552337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54438972473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62059593200684</t>
+    <t xml:space="preserve">7.52057504653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54438877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62059545516968</t>
   </si>
   <si>
     <t xml:space="preserve">7.63964748382568</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77776908874512</t>
+    <t xml:space="preserve">7.77776956558228</t>
   </si>
   <si>
     <t xml:space="preserve">7.76824378967285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90636873245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0349645614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00638771057129</t>
+    <t xml:space="preserve">7.90636682510376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03496551513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00638866424561</t>
   </si>
   <si>
     <t xml:space="preserve">8.04449081420898</t>
@@ -1706,10 +1706,10 @@
     <t xml:space="preserve">8.06830596923828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2016658782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32550144195557</t>
+    <t xml:space="preserve">8.20166492462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32549953460693</t>
   </si>
   <si>
     <t xml:space="preserve">8.44457149505615</t>
@@ -1718,10 +1718,10 @@
     <t xml:space="preserve">8.33978939056396</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38265419006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33502674102783</t>
+    <t xml:space="preserve">8.38265514373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33502578735352</t>
   </si>
   <si>
     <t xml:space="preserve">8.27787113189697</t>
@@ -1730,10 +1730,10 @@
     <t xml:space="preserve">8.23500633239746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25881958007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26358318328857</t>
+    <t xml:space="preserve">8.25882053375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26358413696289</t>
   </si>
   <si>
     <t xml:space="preserve">8.16832637786865</t>
@@ -1751,49 +1751,49 @@
     <t xml:space="preserve">8.37789154052734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28739738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21119117736816</t>
+    <t xml:space="preserve">8.28739643096924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21119022369385</t>
   </si>
   <si>
     <t xml:space="preserve">8.22071838378906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43150424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.445876121521</t>
+    <t xml:space="preserve">8.43150520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44587516784668</t>
   </si>
   <si>
     <t xml:space="preserve">8.56085205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51294708251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48899269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6087589263916</t>
+    <t xml:space="preserve">8.51294612884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48899173736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60875797271729</t>
   </si>
   <si>
     <t xml:space="preserve">8.441086769104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49857425689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48420238494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67103576660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81475448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74289512634277</t>
+    <t xml:space="preserve">8.49857521057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4842004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67103672027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8147554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74289608001709</t>
   </si>
   <si>
     <t xml:space="preserve">8.83391761779785</t>
@@ -1805,10 +1805,10 @@
     <t xml:space="preserve">8.7093620300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6854076385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70457077026367</t>
+    <t xml:space="preserve">8.68540668487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70456981658936</t>
   </si>
   <si>
     <t xml:space="preserve">8.78122138977051</t>
@@ -1817,10 +1817,10 @@
     <t xml:space="preserve">8.80996513366699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77163887023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65187454223633</t>
+    <t xml:space="preserve">8.77163982391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65187358856201</t>
   </si>
   <si>
     <t xml:space="preserve">8.53689861297607</t>
@@ -1832,31 +1832,31 @@
     <t xml:space="preserve">8.37401676177979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40755081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41234302520752</t>
+    <t xml:space="preserve">8.40755176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4123420715332</t>
   </si>
   <si>
     <t xml:space="preserve">8.32610988616943</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45545864105225</t>
+    <t xml:space="preserve">8.45545768737793</t>
   </si>
   <si>
     <t xml:space="preserve">8.41713237762451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39318084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54647922515869</t>
+    <t xml:space="preserve">8.39317989349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54648017883301</t>
   </si>
   <si>
     <t xml:space="preserve">8.58959674835205</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27341556549072</t>
+    <t xml:space="preserve">8.27341651916504</t>
   </si>
   <si>
     <t xml:space="preserve">8.22071743011475</t>
@@ -1868,10 +1868,10 @@
     <t xml:space="preserve">8.35485553741455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4746208190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42192268371582</t>
+    <t xml:space="preserve">8.47462177276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42192363739014</t>
   </si>
   <si>
     <t xml:space="preserve">8.36922645568848</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">8.31653118133545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29736709594727</t>
+    <t xml:space="preserve">8.29736804962158</t>
   </si>
   <si>
     <t xml:space="preserve">8.28299522399902</t>
@@ -1889,37 +1889,37 @@
     <t xml:space="preserve">8.17760181427002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2015552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16322994232178</t>
+    <t xml:space="preserve">8.20155620574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16323089599609</t>
   </si>
   <si>
     <t xml:space="preserve">8.24946022033691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18239212036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17281150817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09616088867188</t>
+    <t xml:space="preserve">8.18239116668701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17281055450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09616184234619</t>
   </si>
   <si>
     <t xml:space="preserve">8.14885711669922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06741809844971</t>
+    <t xml:space="preserve">8.06741714477539</t>
   </si>
   <si>
     <t xml:space="preserve">8.03867435455322</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97160482406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78956031799316</t>
+    <t xml:space="preserve">7.97160387039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78956079483032</t>
   </si>
   <si>
     <t xml:space="preserve">7.62188911437988</t>
@@ -1937,61 +1937,61 @@
     <t xml:space="preserve">7.72249174118042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5931453704834</t>
+    <t xml:space="preserve">7.59314489364624</t>
   </si>
   <si>
     <t xml:space="preserve">7.45900726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5117039680481</t>
+    <t xml:space="preserve">7.51170444488525</t>
   </si>
   <si>
     <t xml:space="preserve">7.65542316436768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59793567657471</t>
+    <t xml:space="preserve">7.59793615341187</t>
   </si>
   <si>
     <t xml:space="preserve">7.90932559967041</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95244264602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82309484481812</t>
+    <t xml:space="preserve">7.95244169235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82309532165527</t>
   </si>
   <si>
     <t xml:space="preserve">7.8805832862854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10574245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20634365081787</t>
+    <t xml:space="preserve">8.10574150085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2063455581665</t>
   </si>
   <si>
     <t xml:space="preserve">8.16802024841309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26383304595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34527397155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29257583618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12011528015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0338830947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99555730819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80872249603271</t>
+    <t xml:space="preserve">8.26383209228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3452730178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29257678985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12011432647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03388404846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99555826187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80872344970703</t>
   </si>
   <si>
     <t xml:space="preserve">7.91411733627319</t>
@@ -2000,37 +2000,37 @@
     <t xml:space="preserve">7.88537263870239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82788610458374</t>
+    <t xml:space="preserve">7.82788515090942</t>
   </si>
   <si>
     <t xml:space="preserve">7.84704828262329</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0003490447998</t>
+    <t xml:space="preserve">8.00034999847412</t>
   </si>
   <si>
     <t xml:space="preserve">7.89974498748779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90453672409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94286155700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71770191192627</t>
+    <t xml:space="preserve">7.90453577041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94286060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71770143508911</t>
   </si>
   <si>
     <t xml:space="preserve">7.85663032531738</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04346466064453</t>
+    <t xml:space="preserve">8.04346370697021</t>
   </si>
   <si>
     <t xml:space="preserve">8.11532497406006</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12969493865967</t>
+    <t xml:space="preserve">8.12969589233398</t>
   </si>
   <si>
     <t xml:space="preserve">8.13448524475098</t>
@@ -2039,7 +2039,7 @@
     <t xml:space="preserve">8.00992870330811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93328046798706</t>
+    <t xml:space="preserve">7.93327951431274</t>
   </si>
   <si>
     <t xml:space="preserve">7.7512354850769</t>
@@ -2051,46 +2051,46 @@
     <t xml:space="preserve">7.64105129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69374847412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83746767044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8135142326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87100028991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87579298019409</t>
+    <t xml:space="preserve">7.69374799728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83746719360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81351375579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87100124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87579202651978</t>
   </si>
   <si>
     <t xml:space="preserve">7.92369937896729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89495468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85183954238892</t>
+    <t xml:space="preserve">7.8949556350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85183906555176</t>
   </si>
   <si>
     <t xml:space="preserve">7.8662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98597621917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96681308746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92848873138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1105318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04825496673584</t>
+    <t xml:space="preserve">7.98597717285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9668140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92848968505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11053276062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04825401306152</t>
   </si>
   <si>
     <t xml:space="preserve">7.93806982040405</t>
@@ -2099,43 +2099,43 @@
     <t xml:space="preserve">7.77997922897339</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81830358505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84225797653198</t>
+    <t xml:space="preserve">7.81830453872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84225845336914</t>
   </si>
   <si>
     <t xml:space="preserve">7.79435110092163</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79914236068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94765186309814</t>
+    <t xml:space="preserve">7.7991418838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94765090942383</t>
   </si>
   <si>
     <t xml:space="preserve">7.9189076423645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7129111289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77518939971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86142063140869</t>
+    <t xml:space="preserve">7.71291065216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77518844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86142015457153</t>
   </si>
   <si>
     <t xml:space="preserve">8.07699966430664</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21592712402344</t>
+    <t xml:space="preserve">8.21592617034912</t>
   </si>
   <si>
     <t xml:space="preserve">8.2686243057251</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33569240570068</t>
+    <t xml:space="preserve">8.33569145202637</t>
   </si>
   <si>
     <t xml:space="preserve">8.45066738128662</t>
@@ -2150,19 +2150,19 @@
     <t xml:space="preserve">8.55127143859863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59438705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66624546051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64229202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69019889831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58480548858643</t>
+    <t xml:space="preserve">8.59438610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66624450683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64229297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69019794464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58480453491211</t>
   </si>
   <si>
     <t xml:space="preserve">8.19197273254395</t>
@@ -2174,13 +2174,13 @@
     <t xml:space="preserve">7.70332956314087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78477048873901</t>
+    <t xml:space="preserve">7.78477096557617</t>
   </si>
   <si>
     <t xml:space="preserve">7.44463539123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22426652908325</t>
+    <t xml:space="preserve">7.22426605224609</t>
   </si>
   <si>
     <t xml:space="preserve">7.17636013031006</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">7.33924198150635</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09492015838623</t>
+    <t xml:space="preserve">7.09492063522339</t>
   </si>
   <si>
     <t xml:space="preserve">6.6972975730896</t>
@@ -2204,13 +2204,13 @@
     <t xml:space="preserve">6.36195421218872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33675956726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54754638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37987422943115</t>
+    <t xml:space="preserve">5.3367600440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54754686355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37987470626831</t>
   </si>
   <si>
     <t xml:space="preserve">5.30322504043579</t>
@@ -2228,55 +2228,55 @@
     <t xml:space="preserve">6.0361909866333</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29967498779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76915693283081</t>
+    <t xml:space="preserve">6.29967451095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76915740966797</t>
   </si>
   <si>
     <t xml:space="preserve">6.84101629257202</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53441619873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3715353012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27572250366211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02852630615234</t>
+    <t xml:space="preserve">6.53441667556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37153482437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27572202682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02852582931519</t>
   </si>
   <si>
     <t xml:space="preserve">6.11092472076416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85606336593628</t>
+    <t xml:space="preserve">5.85606288909912</t>
   </si>
   <si>
     <t xml:space="preserve">6.45201730728149</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38111639022827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32171297073364</t>
+    <t xml:space="preserve">6.38111686706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32171249389648</t>
   </si>
   <si>
     <t xml:space="preserve">6.35237264633179</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40986061096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40794467926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47309637069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65897274017334</t>
+    <t xml:space="preserve">6.40986013412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40794372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47309589385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65897226333618</t>
   </si>
   <si>
     <t xml:space="preserve">6.49962091445923</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">6.44746971130371</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43008518218994</t>
+    <t xml:space="preserve">6.43008470535278</t>
   </si>
   <si>
     <t xml:space="preserve">6.39338636398315</t>
@@ -2321,19 +2321,19 @@
     <t xml:space="preserve">6.94773721694946</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95932626724243</t>
+    <t xml:space="preserve">6.95932674407959</t>
   </si>
   <si>
     <t xml:space="preserve">7.08487606048584</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93807935714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70629549026489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66766500473022</t>
+    <t xml:space="preserve">6.93807888031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70629501342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66766452789307</t>
   </si>
   <si>
     <t xml:space="preserve">6.9400110244751</t>
@@ -2348,7 +2348,7 @@
     <t xml:space="preserve">6.53245639801025</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66380071640015</t>
+    <t xml:space="preserve">6.6638011932373</t>
   </si>
   <si>
     <t xml:space="preserve">6.67732191085815</t>
@@ -2357,13 +2357,13 @@
     <t xml:space="preserve">6.72947311401367</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71208953857422</t>
+    <t xml:space="preserve">6.71209001541138</t>
   </si>
   <si>
     <t xml:space="preserve">7.14668560028076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05010890960693</t>
+    <t xml:space="preserve">7.05010843276978</t>
   </si>
   <si>
     <t xml:space="preserve">6.9438738822937</t>
@@ -2375,22 +2375,22 @@
     <t xml:space="preserve">7.09839725494385</t>
   </si>
   <si>
-    <t xml:space="preserve">7.142822265625</t>
+    <t xml:space="preserve">7.14282274246216</t>
   </si>
   <si>
     <t xml:space="preserve">7.14475393295288</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13895988464355</t>
+    <t xml:space="preserve">7.1389594078064</t>
   </si>
   <si>
     <t xml:space="preserve">7.17758989334106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05976676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20463180541992</t>
+    <t xml:space="preserve">7.05976629257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20463132858276</t>
   </si>
   <si>
     <t xml:space="preserve">7.06942367553711</t>
@@ -2402,22 +2402,22 @@
     <t xml:space="preserve">7.33018159866333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38619518280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44800519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44027900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58128070831299</t>
+    <t xml:space="preserve">7.38619565963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44800567626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44027948379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5812816619873</t>
   </si>
   <si>
     <t xml:space="preserve">7.27223539352417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26837205886841</t>
+    <t xml:space="preserve">7.26837253570557</t>
   </si>
   <si>
     <t xml:space="preserve">7.24326229095459</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">7.34370231628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54844570159912</t>
+    <t xml:space="preserve">7.54844522476196</t>
   </si>
   <si>
     <t xml:space="preserve">7.45380020141602</t>
@@ -2435,7 +2435,7 @@
     <t xml:space="preserve">7.62667226791382</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67013168334961</t>
+    <t xml:space="preserve">7.67013216018677</t>
   </si>
   <si>
     <t xml:space="preserve">7.70683145523071</t>
@@ -2444,13 +2444,13 @@
     <t xml:space="preserve">7.84203863143921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86425161361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81499767303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7502908706665</t>
+    <t xml:space="preserve">7.86425065994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81499719619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75029039382935</t>
   </si>
   <si>
     <t xml:space="preserve">7.92412900924683</t>
@@ -2459,25 +2459,25 @@
     <t xml:space="preserve">7.91350650787354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82851839065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89322519302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98497247695923</t>
+    <t xml:space="preserve">7.82851791381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89322423934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98497152328491</t>
   </si>
   <si>
     <t xml:space="preserve">7.87294435501099</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02649974822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88549757003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83817672729492</t>
+    <t xml:space="preserve">8.0265007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88549852371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83817577362061</t>
   </si>
   <si>
     <t xml:space="preserve">8.2631139755249</t>
@@ -2486,7 +2486,7 @@
     <t xml:space="preserve">8.42729377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21965312957764</t>
+    <t xml:space="preserve">8.21965408325195</t>
   </si>
   <si>
     <t xml:space="preserve">8.22158432006836</t>
@@ -2495,10 +2495,10 @@
     <t xml:space="preserve">8.28146362304688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23220920562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29594898223877</t>
+    <t xml:space="preserve">8.23220825195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29594993591309</t>
   </si>
   <si>
     <t xml:space="preserve">8.13659858703613</t>
@@ -2510,22 +2510,22 @@
     <t xml:space="preserve">8.21868896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26601028442383</t>
+    <t xml:space="preserve">8.26601123809814</t>
   </si>
   <si>
     <t xml:space="preserve">8.43598556518555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39735317230225</t>
+    <t xml:space="preserve">8.39735412597656</t>
   </si>
   <si>
     <t xml:space="preserve">8.27760028839111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30753993988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24283313751221</t>
+    <t xml:space="preserve">8.30753898620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24283218383789</t>
   </si>
   <si>
     <t xml:space="preserve">8.34423923492432</t>
@@ -2537,58 +2537,58 @@
     <t xml:space="preserve">8.39059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34327220916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43405437469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3104362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18102359771729</t>
+    <t xml:space="preserve">8.3432731628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43405532836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31043529510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1810245513916</t>
   </si>
   <si>
     <t xml:space="preserve">8.29788112640381</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48330974578857</t>
+    <t xml:space="preserve">8.48330879211426</t>
   </si>
   <si>
     <t xml:space="preserve">8.77110767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58664703369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47944641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71799087524414</t>
+    <t xml:space="preserve">8.58664608001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4794454574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71799182891846</t>
   </si>
   <si>
     <t xml:space="preserve">8.65907764434814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75565528869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71412563323975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82132720947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94784450531006</t>
+    <t xml:space="preserve">8.75565624237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71412754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82132816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94784355163574</t>
   </si>
   <si>
     <t xml:space="preserve">9.01448154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03959083557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0608377456665</t>
+    <t xml:space="preserve">9.03959178924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06083869934082</t>
   </si>
   <si>
     <t xml:space="preserve">8.85319709777832</t>
@@ -2597,13 +2597,13 @@
     <t xml:space="preserve">8.94011688232422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01641464233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05118083953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80587577819824</t>
+    <t xml:space="preserve">9.01641368865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05117988586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80587482452393</t>
   </si>
   <si>
     <t xml:space="preserve">9.08884620666504</t>
@@ -2615,7 +2615,7 @@
     <t xml:space="preserve">8.99999523162842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04828453063965</t>
+    <t xml:space="preserve">9.04828357696533</t>
   </si>
   <si>
     <t xml:space="preserve">9.04635047912598</t>
@@ -2624,19 +2624,19 @@
     <t xml:space="preserve">9.02896881103516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95460414886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99613094329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9719877243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04442024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21343040466309</t>
+    <t xml:space="preserve">8.95460319519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99613189697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97198867797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04441928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21342945098877</t>
   </si>
   <si>
     <t xml:space="preserve">9.23853969573975</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">9.1747989654541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06180477142334</t>
+    <t xml:space="preserve">9.06180381774902</t>
   </si>
   <si>
     <t xml:space="preserve">9.12554550170898</t>
@@ -2669,10 +2669,10 @@
     <t xml:space="preserve">8.74020195007324</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88893127441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66294097900391</t>
+    <t xml:space="preserve">8.8889331817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66294193267822</t>
   </si>
   <si>
     <t xml:space="preserve">8.50262451171875</t>
@@ -2696,13 +2696,13 @@
     <t xml:space="preserve">8.96426105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24626445770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51281833648682</t>
+    <t xml:space="preserve">9.24626541137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26171779632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5128173828125</t>
   </si>
   <si>
     <t xml:space="preserve">9.35443210601807</t>
@@ -2711,25 +2711,25 @@
     <t xml:space="preserve">9.29841709136963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44328212738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43169403076172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25012874603271</t>
+    <t xml:space="preserve">9.44328308105469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4316930770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25012969970703</t>
   </si>
   <si>
     <t xml:space="preserve">9.13230514526367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22501850128174</t>
+    <t xml:space="preserve">9.22501945495605</t>
   </si>
   <si>
     <t xml:space="preserve">9.06856441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19411563873291</t>
+    <t xml:space="preserve">9.19411468505859</t>
   </si>
   <si>
     <t xml:space="preserve">9.17286777496338</t>
@@ -2738,22 +2738,22 @@
     <t xml:space="preserve">9.22694969177246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36215877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12651062011719</t>
+    <t xml:space="preserve">9.36215782165527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12650966644287</t>
   </si>
   <si>
     <t xml:space="preserve">9.1477575302124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13037395477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15934658050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12264823913574</t>
+    <t xml:space="preserve">9.13037490844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15934753417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12264728546143</t>
   </si>
   <si>
     <t xml:space="preserve">9.0048246383667</t>
@@ -2765,13 +2765,13 @@
     <t xml:space="preserve">9.05890560150146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04538631439209</t>
+    <t xml:space="preserve">9.04538536071777</t>
   </si>
   <si>
     <t xml:space="preserve">8.83677959442139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87347984313965</t>
+    <t xml:space="preserve">8.87347888946533</t>
   </si>
   <si>
     <t xml:space="preserve">8.95267200469971</t>
@@ -2780,7 +2780,7 @@
     <t xml:space="preserve">8.9391508102417</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86961650848389</t>
+    <t xml:space="preserve">8.86961555480957</t>
   </si>
   <si>
     <t xml:space="preserve">8.88120555877686</t>
@@ -2798,16 +2798,16 @@
     <t xml:space="preserve">8.90438365936279</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66487312316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59340667724609</t>
+    <t xml:space="preserve">8.66487216949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59340572357178</t>
   </si>
   <si>
     <t xml:space="preserve">8.54125499725342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55284404754639</t>
+    <t xml:space="preserve">8.55284309387207</t>
   </si>
   <si>
     <t xml:space="preserve">8.42150020599365</t>
@@ -2816,25 +2816,25 @@
     <t xml:space="preserve">8.38093852996826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47365093231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42343044281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42536354064941</t>
+    <t xml:space="preserve">8.47365188598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42343139648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4253625869751</t>
   </si>
   <si>
     <t xml:space="preserve">8.5470495223999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4929666519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58568096160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.512282371521</t>
+    <t xml:space="preserve">8.49296569824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5856819152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51228141784668</t>
   </si>
   <si>
     <t xml:space="preserve">8.50648784637451</t>
@@ -2843,13 +2843,13 @@
     <t xml:space="preserve">8.63590145111084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5953369140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65328311920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57215881347656</t>
+    <t xml:space="preserve">8.59533786773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65328407287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57215976715088</t>
   </si>
   <si>
     <t xml:space="preserve">8.57795333862305</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">8.86768531799316</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94108486175537</t>
+    <t xml:space="preserve">8.94108390808105</t>
   </si>
   <si>
     <t xml:space="preserve">9.3370475769043</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">9.38533687591553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44521427154541</t>
+    <t xml:space="preserve">9.44521331787109</t>
   </si>
   <si>
     <t xml:space="preserve">9.58235263824463</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">9.44135093688965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35249996185303</t>
+    <t xml:space="preserve">9.35249900817871</t>
   </si>
   <si>
     <t xml:space="preserve">9.20570278167725</t>
@@ -2900,22 +2900,22 @@
     <t xml:space="preserve">9.28875923156738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3158016204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34091186523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05697441101074</t>
+    <t xml:space="preserve">9.31580066680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34091091156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05697536468506</t>
   </si>
   <si>
     <t xml:space="preserve">9.19218254089355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16320991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04924869537354</t>
+    <t xml:space="preserve">9.16320896148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04924964904785</t>
   </si>
   <si>
     <t xml:space="preserve">9.26751327514648</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">9.16900539398193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36795330047607</t>
+    <t xml:space="preserve">9.36795234680176</t>
   </si>
   <si>
     <t xml:space="preserve">9.52440738677979</t>
@@ -2933,7 +2933,7 @@
     <t xml:space="preserve">9.76391696929932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48963928222656</t>
+    <t xml:space="preserve">9.48963832855225</t>
   </si>
   <si>
     <t xml:space="preserve">9.46839237213135</t>
@@ -2942,16 +2942,16 @@
     <t xml:space="preserve">9.38726806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42589855194092</t>
+    <t xml:space="preserve">9.42589950561523</t>
   </si>
   <si>
     <t xml:space="preserve">9.364089012146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2829647064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25978755950928</t>
+    <t xml:space="preserve">9.28296566009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25978660583496</t>
   </si>
   <si>
     <t xml:space="preserve">9.24240303039551</t>
@@ -2960,10 +2960,10 @@
     <t xml:space="preserve">9.26364994049072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28682899475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35056781768799</t>
+    <t xml:space="preserve">9.28682804107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3505687713623</t>
   </si>
   <si>
     <t xml:space="preserve">9.23081302642822</t>
@@ -2975,10 +2975,10 @@
     <t xml:space="preserve">9.32932186126709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46452903747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41624164581299</t>
+    <t xml:space="preserve">9.4645299911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41624069213867</t>
   </si>
   <si>
     <t xml:space="preserve">9.63836765289307</t>
@@ -5916,6 +5916,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.45800018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.43400001525879</t>
   </si>
 </sst>
 </file>
@@ -70942,7 +70945,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6523726852</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>4676826</v>
@@ -70963,6 +70966,32 @@
         <v>1960</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6510648148</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>6194627</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>5.53200006484985</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>5.38199996948242</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>5.38199996948242</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>5.43400001525879</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>1968</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1968" uniqueCount="1968">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1969" uniqueCount="1969">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59865689277649</t>
+    <t xml:space="preserve">3.59865665435791</t>
   </si>
   <si>
     <t xml:space="preserve">CPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6589822769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60329699516296</t>
+    <t xml:space="preserve">3.65898251533508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60329723358154</t>
   </si>
   <si>
     <t xml:space="preserve">3.51976919174194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51048827171326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54993224143982</t>
+    <t xml:space="preserve">3.51048874855042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54993200302124</t>
   </si>
   <si>
     <t xml:space="preserve">3.62881970405579</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">3.68450450897217</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57313418388367</t>
+    <t xml:space="preserve">3.57313442230225</t>
   </si>
   <si>
     <t xml:space="preserve">3.52672958374023</t>
@@ -77,145 +77,145 @@
     <t xml:space="preserve">3.5661735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43392109870911</t>
+    <t xml:space="preserve">3.43392133712769</t>
   </si>
   <si>
     <t xml:space="preserve">3.50584769248962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56153345108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64274096488953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66594290733337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56849431991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7425103187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72162818908691</t>
+    <t xml:space="preserve">3.56153321266174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64274072647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66594314575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56849455833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74250984191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72162842750549</t>
   </si>
   <si>
     <t xml:space="preserve">3.70770668983459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47104454040527</t>
+    <t xml:space="preserve">3.47104477882385</t>
   </si>
   <si>
     <t xml:space="preserve">3.44320225715637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28078699111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33183169364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40839862823486</t>
+    <t xml:space="preserve">3.28078675270081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33183145523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40839886665344</t>
   </si>
   <si>
     <t xml:space="preserve">3.22046136856079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26918601989746</t>
+    <t xml:space="preserve">3.26918578147888</t>
   </si>
   <si>
     <t xml:space="preserve">3.32487106323242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24366354942322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32255029678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28774738311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31791067123413</t>
+    <t xml:space="preserve">3.24366331100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32255053520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28774762153625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31791043281555</t>
   </si>
   <si>
     <t xml:space="preserve">3.36663484573364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36199474334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40607881546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3828763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36431503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5313708782196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6056170463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61257767677307</t>
+    <t xml:space="preserve">3.36199426651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40607833862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38287663459778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36431455612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53137040138245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60561728477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61257791519165</t>
   </si>
   <si>
     <t xml:space="preserve">3.56385326385498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61489820480347</t>
+    <t xml:space="preserve">3.61489796638489</t>
   </si>
   <si>
     <t xml:space="preserve">3.63810038566589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6891450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476301193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9559690952301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00701570510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04877853393555</t>
+    <t xml:space="preserve">3.68914484977722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476253509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95596981048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00701522827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04877901077271</t>
   </si>
   <si>
     <t xml:space="preserve">4.03485679626465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04181814193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03717708587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05109834671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01861667633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09286308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07662057876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03949785232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08358287811279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02325630187988</t>
+    <t xml:space="preserve">4.04181861877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03717756271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05109882354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01861619949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09286212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07662200927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0394983291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08358192443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02325677871704</t>
   </si>
   <si>
     <t xml:space="preserve">4.00005435943604</t>
@@ -224,94 +224,94 @@
     <t xml:space="preserve">4.06037998199463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99541354179382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94436931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97453165054321</t>
+    <t xml:space="preserve">3.9954149723053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94436836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97453141212463</t>
   </si>
   <si>
     <t xml:space="preserve">4.00237417221069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93740797042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94668889045715</t>
+    <t xml:space="preserve">3.93740820884705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94668936729431</t>
   </si>
   <si>
     <t xml:space="preserve">4.03021717071533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05341815948486</t>
+    <t xml:space="preserve">4.05341911315918</t>
   </si>
   <si>
     <t xml:space="preserve">4.00933504104614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95828986167908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98613262176514</t>
+    <t xml:space="preserve">3.95829010009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98613286018372</t>
   </si>
   <si>
     <t xml:space="preserve">4.0255765914917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.969890832901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91188669204712</t>
+    <t xml:space="preserve">3.96989107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91188645362854</t>
   </si>
   <si>
     <t xml:space="preserve">3.8979651927948</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87708210945129</t>
+    <t xml:space="preserve">3.87708258628845</t>
   </si>
   <si>
     <t xml:space="preserve">3.9142062664032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92812776565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95132994651794</t>
+    <t xml:space="preserve">3.92812752723694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95132970809937</t>
   </si>
   <si>
     <t xml:space="preserve">4.06734085083008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08126163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99309325218201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96757173538208</t>
+    <t xml:space="preserve">4.08126258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99309372901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96757102012634</t>
   </si>
   <si>
     <t xml:space="preserve">3.98149228096008</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96293067932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88868403434753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89332509040833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79587483406067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89309859275818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02677726745605</t>
+    <t xml:space="preserve">3.96293044090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8886833190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89332389831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79587554931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89309906959534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02677822113037</t>
   </si>
   <si>
     <t xml:space="preserve">4.08540868759155</t>
@@ -332,58 +332,58 @@
     <t xml:space="preserve">4.09009981155396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10182571411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08775472640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11355209350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08071804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01974201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90482473373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85557508468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85792088508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86495614051819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87199187278748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86964654922485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00567054748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00801515579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95876574516296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05961084365845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88606309890747</t>
+    <t xml:space="preserve">4.10182523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0877537727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1135516166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08071851730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01974153518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90482497215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85557532310486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85792016983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86495590209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8719916343689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86964631080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00567007064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00801610946655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95876502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05961132049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88606286048889</t>
   </si>
   <si>
     <t xml:space="preserve">3.88840818405151</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04084920883179</t>
+    <t xml:space="preserve">4.04084873199463</t>
   </si>
   <si>
     <t xml:space="preserve">4.16514730453491</t>
@@ -392,52 +392,52 @@
     <t xml:space="preserve">4.15576601028442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14873027801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13231420516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00332450866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04319429397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16045713424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15811061859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11589622497559</t>
+    <t xml:space="preserve">4.14873075485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13231372833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00332593917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04319381713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16045570373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15811109542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1158971786499</t>
   </si>
   <si>
     <t xml:space="preserve">4.06899213790894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1346583366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14169549942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18390846252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16280126571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21908760070801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29178905487061</t>
+    <t xml:space="preserve">4.13465881347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14169502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18390941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16280174255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21908712387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29179000854492</t>
   </si>
   <si>
     <t xml:space="preserve">4.29648017883301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31055116653442</t>
+    <t xml:space="preserve">4.31055164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.28709983825684</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">4.33165836334229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33869504928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54038667678833</t>
+    <t xml:space="preserve">4.33869457244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54038524627686</t>
   </si>
   <si>
     <t xml:space="preserve">4.51458787918091</t>
@@ -458,31 +458,31 @@
     <t xml:space="preserve">4.5216236114502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43719434738159</t>
+    <t xml:space="preserve">4.43719482421875</t>
   </si>
   <si>
     <t xml:space="preserve">4.47940874099731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45595645904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66233825683594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67171907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58963537216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55914783477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56383848190308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54976606369019</t>
+    <t xml:space="preserve">4.45595741271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66233777999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67171859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58963489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55914735794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56383800506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54976558685303</t>
   </si>
   <si>
     <t xml:space="preserve">4.60370635986328</t>
@@ -491,25 +491,25 @@
     <t xml:space="preserve">4.59667158126831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62012386322021</t>
+    <t xml:space="preserve">4.57321929931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62012338638306</t>
   </si>
   <si>
     <t xml:space="preserve">4.59432554244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65061092376709</t>
+    <t xml:space="preserve">4.65061140060425</t>
   </si>
   <si>
     <t xml:space="preserve">4.57556343078613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70455169677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67406463623047</t>
+    <t xml:space="preserve">4.7045521736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67406368255615</t>
   </si>
   <si>
     <t xml:space="preserve">4.70924234390259</t>
@@ -518,40 +518,40 @@
     <t xml:space="preserve">4.6013617515564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48644495010376</t>
+    <t xml:space="preserve">4.4864444732666</t>
   </si>
   <si>
     <t xml:space="preserve">4.4653377532959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39967107772827</t>
+    <t xml:space="preserve">4.39967155456543</t>
   </si>
   <si>
     <t xml:space="preserve">4.43250465393066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50520610809326</t>
+    <t xml:space="preserve">4.50520658493042</t>
   </si>
   <si>
     <t xml:space="preserve">4.49113512039185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51693248748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50286197662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4887900352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65295696258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66468238830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73269605636597</t>
+    <t xml:space="preserve">4.51693296432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50286149978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48878955841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65295648574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66468286514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73269462585449</t>
   </si>
   <si>
     <t xml:space="preserve">4.71393346786499</t>
@@ -563,40 +563,40 @@
     <t xml:space="preserve">4.58729028701782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.568528175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47471857070923</t>
+    <t xml:space="preserve">4.56852769851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47471904754639</t>
   </si>
   <si>
     <t xml:space="preserve">4.44657564163208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54742050170898</t>
+    <t xml:space="preserve">4.5474214553833</t>
   </si>
   <si>
     <t xml:space="preserve">4.44188547134399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50051641464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52631425857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36683797836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37152862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3340048789978</t>
+    <t xml:space="preserve">4.50051689147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52631378173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36683702468872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37152767181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33400392532349</t>
   </si>
   <si>
     <t xml:space="preserve">4.3293137550354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30586051940918</t>
+    <t xml:space="preserve">4.3058614730835</t>
   </si>
   <si>
     <t xml:space="preserve">4.30351638793945</t>
@@ -608,10 +608,10 @@
     <t xml:space="preserve">4.20736169815063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09478902816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24254035949707</t>
+    <t xml:space="preserve">4.09478950500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24253988265991</t>
   </si>
   <si>
     <t xml:space="preserve">4.20267105102539</t>
@@ -626,31 +626,31 @@
     <t xml:space="preserve">4.03381395339966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12527751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01739645004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12996864318848</t>
+    <t xml:space="preserve">4.12527799606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01739597320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12996816635132</t>
   </si>
   <si>
     <t xml:space="preserve">4.1721830368042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2120509147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18859958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24957656860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20501565933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26833772659302</t>
+    <t xml:space="preserve">4.21205139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1885986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24957513809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20501613616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26833820343018</t>
   </si>
   <si>
     <t xml:space="preserve">4.22846841812134</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">4.24723052978516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31993246078491</t>
+    <t xml:space="preserve">4.31993293762207</t>
   </si>
   <si>
     <t xml:space="preserve">4.36449289321899</t>
@@ -668,37 +668,37 @@
     <t xml:space="preserve">4.28944444656372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27771854400635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30117130279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32227802276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35745620727539</t>
+    <t xml:space="preserve">4.27771759033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30117034912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32227849960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35745668411255</t>
   </si>
   <si>
     <t xml:space="preserve">4.34807586669922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34338521957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39029026031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36214733123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32462358474731</t>
+    <t xml:space="preserve">4.34338569641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39028930664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36214637756348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32462310791016</t>
   </si>
   <si>
     <t xml:space="preserve">4.39732503890991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37387323379517</t>
+    <t xml:space="preserve">4.37387371063232</t>
   </si>
   <si>
     <t xml:space="preserve">4.36918258666992</t>
@@ -713,127 +713,127 @@
     <t xml:space="preserve">4.42546939849854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43485021591187</t>
+    <t xml:space="preserve">4.43484973907471</t>
   </si>
   <si>
     <t xml:space="preserve">4.46768283843994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40201568603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35276699066162</t>
+    <t xml:space="preserve">4.40201616287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3527660369873</t>
   </si>
   <si>
     <t xml:space="preserve">4.3855996131897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43953990936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43015909194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49348115921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47237396240234</t>
+    <t xml:space="preserve">4.43954086303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4301586151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49348020553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47237205505371</t>
   </si>
   <si>
     <t xml:space="preserve">4.52396869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5427303314209</t>
+    <t xml:space="preserve">4.54273080825806</t>
   </si>
   <si>
     <t xml:space="preserve">4.53804016113281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5450758934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58259963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57790994644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55211162567139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57087326049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53569507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50755167007446</t>
+    <t xml:space="preserve">4.54507541656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58260011672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57790946960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55211210250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57087469100952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53569459915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5075511932373</t>
   </si>
   <si>
     <t xml:space="preserve">4.58494472503662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65530300140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74207592010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75614833831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80774259567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83119487762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89686107635498</t>
+    <t xml:space="preserve">4.65530252456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74207639694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75614738464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80774211883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83119535446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89686155319214</t>
   </si>
   <si>
     <t xml:space="preserve">4.94845724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09855222702026</t>
+    <t xml:space="preserve">5.09855318069458</t>
   </si>
   <si>
     <t xml:space="preserve">5.0516471862793</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12200450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04695749282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05633783340454</t>
+    <t xml:space="preserve">5.12200498580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04695701599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05633735656738</t>
   </si>
   <si>
     <t xml:space="preserve">4.99536180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01881456375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02819538116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03288507461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93907690048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9766001701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92500448226929</t>
+    <t xml:space="preserve">5.01881408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02819585800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03288555145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93907594680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97660064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92500495910645</t>
   </si>
   <si>
     <t xml:space="preserve">4.96721935272217</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08917140960693</t>
+    <t xml:space="preserve">5.08917188644409</t>
   </si>
   <si>
     <t xml:space="preserve">5.17359972000122</t>
@@ -842,43 +842,43 @@
     <t xml:space="preserve">5.14545774459839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1595287322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09386110305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16421937942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25333786010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18767213821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41750526428223</t>
+    <t xml:space="preserve">5.15952920913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09386253356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16421890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25333833694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18767166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41750574111938</t>
   </si>
   <si>
     <t xml:space="preserve">5.6707911491394</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60043382644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62388563156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66140985488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68486261367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57698106765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60512447357178</t>
+    <t xml:space="preserve">5.60043334960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62388610839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66141080856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68486213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57698202133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60512495040894</t>
   </si>
   <si>
     <t xml:space="preserve">5.7223858833313</t>
@@ -887,22 +887,22 @@
     <t xml:space="preserve">5.69403409957886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74128770828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76491403579712</t>
+    <t xml:space="preserve">5.74128818511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76491355895996</t>
   </si>
   <si>
     <t xml:space="preserve">5.7507381439209</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8783221244812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86887216567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88304758071899</t>
+    <t xml:space="preserve">5.87832260131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86887168884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88304805755615</t>
   </si>
   <si>
     <t xml:space="preserve">6.02008247375488</t>
@@ -914,22 +914,22 @@
     <t xml:space="preserve">6.00118112564087</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9350266456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85942125320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8027172088623</t>
+    <t xml:space="preserve">5.93502759933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8594217300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80271673202515</t>
   </si>
   <si>
     <t xml:space="preserve">5.75546360015869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73183679580688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84997034072876</t>
+    <t xml:space="preserve">5.73183727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84997081756592</t>
   </si>
   <si>
     <t xml:space="preserve">5.81216764450073</t>
@@ -938,13 +938,13 @@
     <t xml:space="preserve">5.95865297317505</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93030118942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98227977752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90194940567017</t>
+    <t xml:space="preserve">5.93030166625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9822793006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90194892883301</t>
   </si>
   <si>
     <t xml:space="preserve">5.91612577438354</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">5.8310694694519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88777351379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78381538391113</t>
+    <t xml:space="preserve">5.88777303695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78381490707397</t>
   </si>
   <si>
     <t xml:space="preserve">5.80744218826294</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">5.84524536132812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77436447143555</t>
+    <t xml:space="preserve">5.77436494827271</t>
   </si>
   <si>
     <t xml:space="preserve">5.82634353637695</t>
@@ -977,19 +977,19 @@
     <t xml:space="preserve">5.82161855697632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85469675064087</t>
+    <t xml:space="preserve">5.85469532012939</t>
   </si>
   <si>
     <t xml:space="preserve">5.79326629638672</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83579540252686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95392847061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92557573318481</t>
+    <t xml:space="preserve">5.83579397201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95392799377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92557525634766</t>
   </si>
   <si>
     <t xml:space="preserve">5.94447660446167</t>
@@ -998,37 +998,37 @@
     <t xml:space="preserve">5.7790904045105</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74601268768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71766042709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65150594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66095733642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79799175262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76018857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69875907897949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66568183898926</t>
+    <t xml:space="preserve">5.74601316452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71766090393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6515064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66095638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79799222946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76018953323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69875955581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66568231582642</t>
   </si>
   <si>
     <t xml:space="preserve">5.73656177520752</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78854036331177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76963901519775</t>
+    <t xml:space="preserve">5.78854084014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76963996887207</t>
   </si>
   <si>
     <t xml:space="preserve">5.89249849319458</t>
@@ -1037,52 +1037,52 @@
     <t xml:space="preserve">5.97282934188843</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15239191055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14766693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28470134735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13821601867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12404012680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02953386306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10513830184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16656827926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11458921432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31777906417847</t>
+    <t xml:space="preserve">6.15239286422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14766645431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28470182418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13821649551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1240406036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02953290939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10513877868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16656875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11458969116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31777858734131</t>
   </si>
   <si>
     <t xml:space="preserve">6.34140634536743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40756130218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50206756591797</t>
+    <t xml:space="preserve">6.4075608253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50206708908081</t>
   </si>
   <si>
     <t xml:space="preserve">6.42173671722412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30832815170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47844076156616</t>
+    <t xml:space="preserve">6.3083291053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.478440284729</t>
   </si>
   <si>
     <t xml:space="preserve">6.31305313110352</t>
@@ -1091,25 +1091,25 @@
     <t xml:space="preserve">6.33668041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37448310852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17601776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09096240997314</t>
+    <t xml:space="preserve">6.37448263168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17601871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0909628868103</t>
   </si>
   <si>
     <t xml:space="preserve">6.23272275924683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0389838218689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08623743057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10041332244873</t>
+    <t xml:space="preserve">6.03898334503174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08623695373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10041379928589</t>
   </si>
   <si>
     <t xml:space="preserve">6.10986423492432</t>
@@ -1118,28 +1118,28 @@
     <t xml:space="preserve">6.00590705871582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03425931930542</t>
+    <t xml:space="preserve">6.03425884246826</t>
   </si>
   <si>
     <t xml:space="preserve">6.09568786621094</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06261157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18074464797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08151197433472</t>
+    <t xml:space="preserve">6.06261110305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18074417114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08151245117188</t>
   </si>
   <si>
     <t xml:space="preserve">6.15711736679077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21382093429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24217367172241</t>
+    <t xml:space="preserve">6.21382188796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24217319488525</t>
   </si>
   <si>
     <t xml:space="preserve">6.24689912796021</t>
@@ -1148,10 +1148,10 @@
     <t xml:space="preserve">6.20909643173218</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22799730300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19964551925659</t>
+    <t xml:space="preserve">6.22799825668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19964504241943</t>
   </si>
   <si>
     <t xml:space="preserve">6.12876558303833</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">6.07206153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05788564682007</t>
+    <t xml:space="preserve">6.05788469314575</t>
   </si>
   <si>
     <t xml:space="preserve">6.13349056243896</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">6.14294147491455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01063251495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94920301437378</t>
+    <t xml:space="preserve">6.0106315612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94920253753662</t>
   </si>
   <si>
     <t xml:space="preserve">5.97755479812622</t>
@@ -1184,43 +1184,43 @@
     <t xml:space="preserve">5.99645566940308</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0673360824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93975210189819</t>
+    <t xml:space="preserve">6.06733560562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93975114822388</t>
   </si>
   <si>
     <t xml:space="preserve">5.71293544769287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72711133956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92085027694702</t>
+    <t xml:space="preserve">5.72711086273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92085075378418</t>
   </si>
   <si>
     <t xml:space="preserve">5.57590103149414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52864694595337</t>
+    <t xml:space="preserve">5.52864742279053</t>
   </si>
   <si>
     <t xml:space="preserve">5.42941522598267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50502014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61370325088501</t>
+    <t xml:space="preserve">5.50502061843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61370372772217</t>
   </si>
   <si>
     <t xml:space="preserve">5.63733005523682</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04370975494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98700571060181</t>
+    <t xml:space="preserve">6.04371023178101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98700618743896</t>
   </si>
   <si>
     <t xml:space="preserve">6.01535701751709</t>
@@ -1232,7 +1232,7 @@
     <t xml:space="preserve">5.81689357757568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87359714508057</t>
+    <t xml:space="preserve">5.87359762191772</t>
   </si>
   <si>
     <t xml:space="preserve">5.86414670944214</t>
@@ -1241,31 +1241,31 @@
     <t xml:space="preserve">5.9066743850708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96810436248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01550769805908</t>
+    <t xml:space="preserve">5.96810388565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01550722122192</t>
   </si>
   <si>
     <t xml:space="preserve">6.02027034759521</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99169254302979</t>
+    <t xml:space="preserve">5.99169301986694</t>
   </si>
   <si>
     <t xml:space="preserve">6.08218765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20602178573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18697023391724</t>
+    <t xml:space="preserve">6.20602226257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18697071075439</t>
   </si>
   <si>
     <t xml:space="preserve">6.08695030212402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07266187667847</t>
+    <t xml:space="preserve">6.07266283035278</t>
   </si>
   <si>
     <t xml:space="preserve">6.16315650939941</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">6.27270269393921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25365114212036</t>
+    <t xml:space="preserve">6.2536506652832</t>
   </si>
   <si>
     <t xml:space="preserve">6.13934230804443</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">6.52513456344604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5965781211853</t>
+    <t xml:space="preserve">6.59657764434814</t>
   </si>
   <si>
     <t xml:space="preserve">6.69183588027954</t>
@@ -1301,25 +1301,25 @@
     <t xml:space="preserve">6.62039184570312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57276344299316</t>
+    <t xml:space="preserve">6.57276391983032</t>
   </si>
   <si>
     <t xml:space="preserve">6.5060830116272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58228921890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.653733253479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71088743209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82519578933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77280426025391</t>
+    <t xml:space="preserve">6.58228969573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65373277664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71088647842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77280378341675</t>
   </si>
   <si>
     <t xml:space="preserve">6.82995891571045</t>
@@ -1328,16 +1328,16 @@
     <t xml:space="preserve">7.0252366065979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92521572113037</t>
+    <t xml:space="preserve">6.92521619796753</t>
   </si>
   <si>
     <t xml:space="preserve">6.92045307159424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01094722747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96808195114136</t>
+    <t xml:space="preserve">7.01094818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96808242797852</t>
   </si>
   <si>
     <t xml:space="preserve">6.91092729568481</t>
@@ -1349,13 +1349,13 @@
     <t xml:space="preserve">7.04905080795288</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0966796875</t>
+    <t xml:space="preserve">7.09667921066284</t>
   </si>
   <si>
     <t xml:space="preserve">7.17764806747437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28243160247803</t>
+    <t xml:space="preserve">7.28243112564087</t>
   </si>
   <si>
     <t xml:space="preserve">7.22051429748535</t>
@@ -1370,46 +1370,46 @@
     <t xml:space="preserve">7.12525653839111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94903039932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86806201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00142192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00618505477905</t>
+    <t xml:space="preserve">6.94903087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86806154251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00142097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00618553161621</t>
   </si>
   <si>
     <t xml:space="preserve">7.06333923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97760772705078</t>
+    <t xml:space="preserve">6.97760677337646</t>
   </si>
   <si>
     <t xml:space="preserve">6.99189615249634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0395245552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02047348022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07762861251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18717336654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21098899841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41579103469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29672002792358</t>
+    <t xml:space="preserve">7.03952503204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02047395706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07762765884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18717384338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21098804473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41579151153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29671955108643</t>
   </si>
   <si>
     <t xml:space="preserve">7.26338005065918</t>
@@ -1421,49 +1421,49 @@
     <t xml:space="preserve">7.27290630340576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30624628067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18241119384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25385475158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05857706069946</t>
+    <t xml:space="preserve">7.30624580383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1824107170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2538537979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0585765838623</t>
   </si>
   <si>
     <t xml:space="preserve">7.10620498657227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14907169342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16812229156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90140247344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94426774978638</t>
+    <t xml:space="preserve">7.14907121658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1681227684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90140199661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94426727294922</t>
   </si>
   <si>
     <t xml:space="preserve">7.06810235977173</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98713350296021</t>
+    <t xml:space="preserve">6.98713302612305</t>
   </si>
   <si>
     <t xml:space="preserve">7.13002014160156</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87758684158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7061243057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63944387435913</t>
+    <t xml:space="preserve">6.87758731842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70612382888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63944339752197</t>
   </si>
   <si>
     <t xml:space="preserve">6.65849494934082</t>
@@ -1475,13 +1475,13 @@
     <t xml:space="preserve">6.19649648666382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11552762985229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04884767532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21554803848267</t>
+    <t xml:space="preserve">6.11552810668945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04884719848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21554851531982</t>
   </si>
   <si>
     <t xml:space="preserve">6.31556844711304</t>
@@ -1490,22 +1490,22 @@
     <t xml:space="preserve">6.33461999893188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34414577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12505292892456</t>
+    <t xml:space="preserve">6.34414529800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12505388259888</t>
   </si>
   <si>
     <t xml:space="preserve">6.15363073348999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30604267120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35367155075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47274351119995</t>
+    <t xml:space="preserve">6.30604314804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35367202758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47274255752563</t>
   </si>
   <si>
     <t xml:space="preserve">6.46798038482666</t>
@@ -1526,16 +1526,16 @@
     <t xml:space="preserve">7.11096858978271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12049388885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32529830932617</t>
+    <t xml:space="preserve">7.12049293518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32529735565186</t>
   </si>
   <si>
     <t xml:space="preserve">7.31577157974243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11573028564453</t>
+    <t xml:space="preserve">7.11573076248169</t>
   </si>
   <si>
     <t xml:space="preserve">7.03476238250732</t>
@@ -1547,13 +1547,13 @@
     <t xml:space="preserve">7.04428815841675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02999925613403</t>
+    <t xml:space="preserve">7.02999973297119</t>
   </si>
   <si>
     <t xml:space="preserve">7.17288541793823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36339998245239</t>
+    <t xml:space="preserve">7.36340045928955</t>
   </si>
   <si>
     <t xml:space="preserve">7.14430809020996</t>
@@ -1562,13 +1562,13 @@
     <t xml:space="preserve">7.20622539520264</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32053422927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09191751480103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98236989974976</t>
+    <t xml:space="preserve">7.32053470611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09191656112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98237037658691</t>
   </si>
   <si>
     <t xml:space="preserve">7.44913244247437</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">7.3824520111084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33006048202515</t>
+    <t xml:space="preserve">7.33006000518799</t>
   </si>
   <si>
     <t xml:space="preserve">7.21575117111206</t>
@@ -1586,55 +1586,55 @@
     <t xml:space="preserve">7.33958625793457</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35387420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55391550064087</t>
+    <t xml:space="preserve">7.35387468338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55391502380371</t>
   </si>
   <si>
     <t xml:space="preserve">7.60630702972412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46342134475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49199771881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44436931610107</t>
+    <t xml:space="preserve">7.46342086791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49199676513672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44436883926392</t>
   </si>
   <si>
     <t xml:space="preserve">7.42055463790894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62535858154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53010129928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47294616699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4872350692749</t>
+    <t xml:space="preserve">7.62535810470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53010082244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47294569015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48723459243774</t>
   </si>
   <si>
     <t xml:space="preserve">7.46818351745605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49676084518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51581287384033</t>
+    <t xml:space="preserve">7.49676036834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51581239700317</t>
   </si>
   <si>
     <t xml:space="preserve">7.6110692024231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56344127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6444091796875</t>
+    <t xml:space="preserve">7.56344079971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64440965652466</t>
   </si>
   <si>
     <t xml:space="preserve">7.73490428924561</t>
@@ -1643,76 +1643,76 @@
     <t xml:space="preserve">7.80634689331055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86826419830322</t>
+    <t xml:space="preserve">7.86826467514038</t>
   </si>
   <si>
     <t xml:space="preserve">7.85873889923096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88731622695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92541980743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9539966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83492565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98733711242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01115131378174</t>
+    <t xml:space="preserve">7.88731527328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92542028427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95399618148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83492469787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98733758926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01115036010742</t>
   </si>
   <si>
     <t xml:space="preserve">8.06354236602783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53486394882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52057504653931</t>
+    <t xml:space="preserve">7.53486347198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52057552337646</t>
   </si>
   <si>
     <t xml:space="preserve">7.54438972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62059545516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63964748382568</t>
+    <t xml:space="preserve">7.62059497833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63964700698853</t>
   </si>
   <si>
     <t xml:space="preserve">7.77777004241943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76824426651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90636730194092</t>
+    <t xml:space="preserve">7.76824378967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90636825561523</t>
   </si>
   <si>
     <t xml:space="preserve">8.03496551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00638771057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04449081420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0683069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20166492462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32549858093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44457054138184</t>
+    <t xml:space="preserve">8.00638675689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04448986053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06830596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2016658782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32550048828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44457340240479</t>
   </si>
   <si>
     <t xml:space="preserve">8.33978939056396</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">8.38265609741211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33502674102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27787208557129</t>
+    <t xml:space="preserve">8.33502578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27787113189697</t>
   </si>
   <si>
     <t xml:space="preserve">8.23500633239746</t>
@@ -1742,10 +1742,10 @@
     <t xml:space="preserve">8.31121253967285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36836528778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35407829284668</t>
+    <t xml:space="preserve">8.36836719512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.354079246521</t>
   </si>
   <si>
     <t xml:space="preserve">8.37789154052734</t>
@@ -1754,10 +1754,10 @@
     <t xml:space="preserve">8.28739643096924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21119213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22071743011475</t>
+    <t xml:space="preserve">8.2111930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22071838378906</t>
   </si>
   <si>
     <t xml:space="preserve">8.43150615692139</t>
@@ -1769,19 +1769,19 @@
     <t xml:space="preserve">8.56085205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51294612884521</t>
+    <t xml:space="preserve">8.5129451751709</t>
   </si>
   <si>
     <t xml:space="preserve">8.48899269104004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60875606536865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.441086769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49857521057129</t>
+    <t xml:space="preserve">8.60875797271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44108581542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49857234954834</t>
   </si>
   <si>
     <t xml:space="preserve">8.48420143127441</t>
@@ -1793,49 +1793,49 @@
     <t xml:space="preserve">8.8147554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74289512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83391857147217</t>
+    <t xml:space="preserve">8.74289703369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83391761779785</t>
   </si>
   <si>
     <t xml:space="preserve">8.77643013000488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7093620300293</t>
+    <t xml:space="preserve">8.70936012268066</t>
   </si>
   <si>
     <t xml:space="preserve">8.6854076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70457172393799</t>
+    <t xml:space="preserve">8.70457077026367</t>
   </si>
   <si>
     <t xml:space="preserve">8.78122043609619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80996513366699</t>
+    <t xml:space="preserve">8.80996322631836</t>
   </si>
   <si>
     <t xml:space="preserve">8.77163982391357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65187454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53689956665039</t>
+    <t xml:space="preserve">8.65187358856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53689861297607</t>
   </si>
   <si>
     <t xml:space="preserve">8.37880802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37401676177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40755081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41234111785889</t>
+    <t xml:space="preserve">8.3740177154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40755176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4123420715332</t>
   </si>
   <si>
     <t xml:space="preserve">8.32611083984375</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">8.45545768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41713237762451</t>
+    <t xml:space="preserve">8.41713428497314</t>
   </si>
   <si>
     <t xml:space="preserve">8.39317989349365</t>
@@ -1853,13 +1853,13 @@
     <t xml:space="preserve">8.54648017883301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58959484100342</t>
+    <t xml:space="preserve">8.58959579467773</t>
   </si>
   <si>
     <t xml:space="preserve">8.27341461181641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25425052642822</t>
+    <t xml:space="preserve">8.25425148010254</t>
   </si>
   <si>
     <t xml:space="preserve">8.35485553741455</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">8.4746208190918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42192459106445</t>
+    <t xml:space="preserve">8.42192268371582</t>
   </si>
   <si>
     <t xml:space="preserve">8.36922645568848</t>
@@ -1877,13 +1877,13 @@
     <t xml:space="preserve">8.31653022766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29736804962158</t>
+    <t xml:space="preserve">8.29736709594727</t>
   </si>
   <si>
     <t xml:space="preserve">8.28299617767334</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17759990692139</t>
+    <t xml:space="preserve">8.17760181427002</t>
   </si>
   <si>
     <t xml:space="preserve">8.2015552520752</t>
@@ -1892,31 +1892,31 @@
     <t xml:space="preserve">8.16323089599609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24946022033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18239212036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17281150817871</t>
+    <t xml:space="preserve">8.24946117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18239307403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17280960083008</t>
   </si>
   <si>
     <t xml:space="preserve">8.09616088867188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14885711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06741714477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03867435455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97160482406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78956079483032</t>
+    <t xml:space="preserve">8.14885807037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06741619110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03867244720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97160577774048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78956127166748</t>
   </si>
   <si>
     <t xml:space="preserve">7.62188863754272</t>
@@ -1925,67 +1925,67 @@
     <t xml:space="preserve">7.61709833145142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66021394729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50212383270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72249221801758</t>
+    <t xml:space="preserve">7.66021347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50212335586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72249174118042</t>
   </si>
   <si>
     <t xml:space="preserve">7.5931453704834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45900678634644</t>
+    <t xml:space="preserve">7.45900726318359</t>
   </si>
   <si>
     <t xml:space="preserve">7.51170444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65542316436768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59793615341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90932655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95244216918945</t>
+    <t xml:space="preserve">7.65542268753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59793567657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90932607650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95244264602661</t>
   </si>
   <si>
     <t xml:space="preserve">7.82309532165527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88058376312256</t>
+    <t xml:space="preserve">7.88058280944824</t>
   </si>
   <si>
     <t xml:space="preserve">8.10574245452881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20634460449219</t>
+    <t xml:space="preserve">8.2063455581665</t>
   </si>
   <si>
     <t xml:space="preserve">8.16802024841309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26383209228516</t>
+    <t xml:space="preserve">8.26383304595947</t>
   </si>
   <si>
     <t xml:space="preserve">8.34527397155762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29257678985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12011432647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0338830947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9955587387085</t>
+    <t xml:space="preserve">8.29257583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12011528015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03388404846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99555969238281</t>
   </si>
   <si>
     <t xml:space="preserve">7.80872344970703</t>
@@ -1997,37 +1997,37 @@
     <t xml:space="preserve">7.88537263870239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82788610458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84704875946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0003490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89974498748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90453624725342</t>
+    <t xml:space="preserve">7.82788515090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84704828262329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00034809112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89974451065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90453577041626</t>
   </si>
   <si>
     <t xml:space="preserve">7.94286155700684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71770143508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85662937164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04346370697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11532497406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12969493865967</t>
+    <t xml:space="preserve">7.71770191192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85662889480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04346466064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11532402038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12969589233398</t>
   </si>
   <si>
     <t xml:space="preserve">8.13448619842529</t>
@@ -2036,34 +2036,34 @@
     <t xml:space="preserve">8.00993061065674</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93327951431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75123596191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57877349853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64105176925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69374752044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83746719360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8135142326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87100124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87579202651978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92369890213013</t>
+    <t xml:space="preserve">7.93327856063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75123643875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.578773021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64105129241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69374799728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83746814727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81351327896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87100028991699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87579345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92369842529297</t>
   </si>
   <si>
     <t xml:space="preserve">7.89495468139648</t>
@@ -2072,37 +2072,37 @@
     <t xml:space="preserve">7.8518385887146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86621046066284</t>
+    <t xml:space="preserve">7.86621141433716</t>
   </si>
   <si>
     <t xml:space="preserve">7.9859766960144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96681356430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92848825454712</t>
+    <t xml:space="preserve">7.9668140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92848920822144</t>
   </si>
   <si>
     <t xml:space="preserve">8.11053276062012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04825496673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93807029724121</t>
+    <t xml:space="preserve">8.04825401306152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93807077407837</t>
   </si>
   <si>
     <t xml:space="preserve">7.77997970581055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81830453872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8422589302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79435062408447</t>
+    <t xml:space="preserve">7.81830501556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84225702285767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79435157775879</t>
   </si>
   <si>
     <t xml:space="preserve">7.7991418838501</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">7.91890859603882</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7129111289978</t>
+    <t xml:space="preserve">7.71291065216064</t>
   </si>
   <si>
     <t xml:space="preserve">7.77518892288208</t>
@@ -2123,19 +2123,19 @@
     <t xml:space="preserve">7.86142015457153</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07699966430664</t>
+    <t xml:space="preserve">8.07699871063232</t>
   </si>
   <si>
     <t xml:space="preserve">8.21592617034912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26862335205078</t>
+    <t xml:space="preserve">8.2686243057251</t>
   </si>
   <si>
     <t xml:space="preserve">8.33569145202637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45066738128662</t>
+    <t xml:space="preserve">8.4506664276123</t>
   </si>
   <si>
     <t xml:space="preserve">8.36443614959717</t>
@@ -2156,19 +2156,19 @@
     <t xml:space="preserve">8.64229393005371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69019794464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58480548858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19197368621826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74165487289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70333003997803</t>
+    <t xml:space="preserve">8.69019889831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58480453491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19197463989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74165439605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70332956314087</t>
   </si>
   <si>
     <t xml:space="preserve">7.7847695350647</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">7.44463539123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22426700592041</t>
+    <t xml:space="preserve">7.22426652908325</t>
   </si>
   <si>
     <t xml:space="preserve">7.17636013031006</t>
@@ -2186,25 +2186,25 @@
     <t xml:space="preserve">7.30091714859009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36319494247437</t>
+    <t xml:space="preserve">7.36319541931152</t>
   </si>
   <si>
     <t xml:space="preserve">7.33924150466919</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09492063522339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69729709625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36195373535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33675956726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54754686355591</t>
+    <t xml:space="preserve">7.09491968154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6972975730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36195421218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3367600440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54754734039307</t>
   </si>
   <si>
     <t xml:space="preserve">5.37987470626831</t>
@@ -2213,10 +2213,10 @@
     <t xml:space="preserve">5.30322456359863</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8685188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45776605606079</t>
+    <t xml:space="preserve">5.86851930618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45776557922363</t>
   </si>
   <si>
     <t xml:space="preserve">6.08409690856934</t>
@@ -2225,31 +2225,31 @@
     <t xml:space="preserve">6.03619146347046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29967546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76915693283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84101581573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53441715240479</t>
+    <t xml:space="preserve">6.29967498779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76915645599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84101629257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53441667556763</t>
   </si>
   <si>
     <t xml:space="preserve">6.3715353012085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27572298049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02852630615234</t>
+    <t xml:space="preserve">6.27572202682495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02852582931519</t>
   </si>
   <si>
     <t xml:space="preserve">6.110924243927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85606336593628</t>
+    <t xml:space="preserve">5.85606288909912</t>
   </si>
   <si>
     <t xml:space="preserve">6.45201778411865</t>
@@ -2258,19 +2258,19 @@
     <t xml:space="preserve">6.38111591339111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32171201705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35237216949463</t>
+    <t xml:space="preserve">6.32171249389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35237264633179</t>
   </si>
   <si>
     <t xml:space="preserve">6.40986013412476</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40794372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47309637069702</t>
+    <t xml:space="preserve">6.4079442024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47309589385986</t>
   </si>
   <si>
     <t xml:space="preserve">6.65897226333618</t>
@@ -2279,25 +2279,25 @@
     <t xml:space="preserve">6.49962091445923</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44746923446655</t>
+    <t xml:space="preserve">6.44746971130371</t>
   </si>
   <si>
     <t xml:space="preserve">6.4300856590271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39338636398315</t>
+    <t xml:space="preserve">6.39338684082031</t>
   </si>
   <si>
     <t xml:space="preserve">6.44360637664795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59619760513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61551284790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79321479797363</t>
+    <t xml:space="preserve">6.5961971282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61551332473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79321384429932</t>
   </si>
   <si>
     <t xml:space="preserve">6.82798194885254</t>
@@ -2315,43 +2315,43 @@
     <t xml:space="preserve">6.78935146331787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9477367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95932626724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08487606048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93807935714722</t>
+    <t xml:space="preserve">6.94773721694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95932674407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08487701416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93807888031006</t>
   </si>
   <si>
     <t xml:space="preserve">6.70629501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66766452789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9400110244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51121044158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67345905303955</t>
+    <t xml:space="preserve">6.66766405105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94001197814941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51120948791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67345857620239</t>
   </si>
   <si>
     <t xml:space="preserve">6.53245687484741</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6638011932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67732238769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72947311401367</t>
+    <t xml:space="preserve">6.66380167007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67732191085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72947359085083</t>
   </si>
   <si>
     <t xml:space="preserve">6.71208953857422</t>
@@ -2363,64 +2363,64 @@
     <t xml:space="preserve">7.05010890960693</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94387483596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11191749572754</t>
+    <t xml:space="preserve">6.94387435913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1119179725647</t>
   </si>
   <si>
     <t xml:space="preserve">7.09839725494385</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14282274246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14475345611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13895988464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17759037017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05976629257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20463180541992</t>
+    <t xml:space="preserve">7.142822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14475440979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1389594078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17758989334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05976676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20463228225708</t>
   </si>
   <si>
     <t xml:space="preserve">7.06942415237427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31279802322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33018159866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38619565963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44800567626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44027900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5812816619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27223587036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26837205886841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24326229095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34370183944702</t>
+    <t xml:space="preserve">7.31279754638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33018112182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38619613647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44800472259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44027948379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58128118515015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27223539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26837253570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24326276779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34370279312134</t>
   </si>
   <si>
     <t xml:space="preserve">7.54844522476196</t>
@@ -2429,49 +2429,49 @@
     <t xml:space="preserve">7.45380020141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62667226791382</t>
+    <t xml:space="preserve">7.62667274475098</t>
   </si>
   <si>
     <t xml:space="preserve">7.67013120651245</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70683145523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84203863143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86425065994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81499719619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75028991699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92412900924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91350698471069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82851791381836</t>
+    <t xml:space="preserve">7.70683097839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84203910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86425113677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81499671936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75029039382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92412948608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91350650787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82851886749268</t>
   </si>
   <si>
     <t xml:space="preserve">7.89322471618652</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98497152328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87294340133667</t>
+    <t xml:space="preserve">7.98497247695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87294387817383</t>
   </si>
   <si>
     <t xml:space="preserve">8.02649974822998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88549852371216</t>
+    <t xml:space="preserve">7.88549757003784</t>
   </si>
   <si>
     <t xml:space="preserve">7.83817577362061</t>
@@ -2483,31 +2483,31 @@
     <t xml:space="preserve">8.42729377746582</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21965408325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22158527374268</t>
+    <t xml:space="preserve">8.21965503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22158432006836</t>
   </si>
   <si>
     <t xml:space="preserve">8.28146266937256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23221015930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29594993591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13659763336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20806503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21868991851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26601123809814</t>
+    <t xml:space="preserve">8.23220825195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29594898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1365966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20806407928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21868896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26601028442383</t>
   </si>
   <si>
     <t xml:space="preserve">8.43598556518555</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">8.2775993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30753803253174</t>
+    <t xml:space="preserve">8.30753898620605</t>
   </si>
   <si>
     <t xml:space="preserve">8.24283123016357</t>
@@ -2531,49 +2531,49 @@
     <t xml:space="preserve">8.228346824646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39059543609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34327220916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43405532836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3104362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18102359771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29788112640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48330974578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7711067199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58664512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47944450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71799182891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65907859802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75565624237061</t>
+    <t xml:space="preserve">8.39059448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34327125549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43405437469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31043529510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18102264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29788208007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48330879211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77110862731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58664703369141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4794454574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71799087524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65907955169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75565528869629</t>
   </si>
   <si>
     <t xml:space="preserve">8.71412754058838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82132720947266</t>
+    <t xml:space="preserve">8.82132816314697</t>
   </si>
   <si>
     <t xml:space="preserve">8.94784355163574</t>
@@ -2582,7 +2582,7 @@
     <t xml:space="preserve">9.01448059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03959274291992</t>
+    <t xml:space="preserve">9.03959083557129</t>
   </si>
   <si>
     <t xml:space="preserve">9.06083869934082</t>
@@ -2591,49 +2591,49 @@
     <t xml:space="preserve">8.85319805145264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94011783599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01641273498535</t>
+    <t xml:space="preserve">8.94011688232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01641368865967</t>
   </si>
   <si>
     <t xml:space="preserve">9.05117988586426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80587482452393</t>
+    <t xml:space="preserve">8.80587577819824</t>
   </si>
   <si>
     <t xml:space="preserve">9.08884525299072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01158332824707</t>
+    <t xml:space="preserve">9.01158428192139</t>
   </si>
   <si>
     <t xml:space="preserve">8.99999523162842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04828453063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04635238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02896785736084</t>
+    <t xml:space="preserve">9.04828357696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04635143280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02896690368652</t>
   </si>
   <si>
     <t xml:space="preserve">8.95460414886475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99613094329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9719877243042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04442024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21343040466309</t>
+    <t xml:space="preserve">8.99613189697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97198867797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04442119598389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21342945098877</t>
   </si>
   <si>
     <t xml:space="preserve">9.23854064941406</t>
@@ -2642,31 +2642,31 @@
     <t xml:space="preserve">9.1747989654541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06180477142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12554550170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03186511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07629013061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80008029937744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93528842926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94687747955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74020385742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88893222808838</t>
+    <t xml:space="preserve">9.06180381774902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12554454803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03186702728271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07629108428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80008125305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93528938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94687843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74020290374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88893127441406</t>
   </si>
   <si>
     <t xml:space="preserve">8.66294193267822</t>
@@ -2693,13 +2693,13 @@
     <t xml:space="preserve">8.96426105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24626636505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26171779632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51281833648682</t>
+    <t xml:space="preserve">9.24626541137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51281929016113</t>
   </si>
   <si>
     <t xml:space="preserve">9.35443115234375</t>
@@ -2714,13 +2714,13 @@
     <t xml:space="preserve">9.4316930770874</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25012874603271</t>
+    <t xml:space="preserve">9.25012969970703</t>
   </si>
   <si>
     <t xml:space="preserve">9.13230609893799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22501945495605</t>
+    <t xml:space="preserve">9.22501850128174</t>
   </si>
   <si>
     <t xml:space="preserve">9.06856536865234</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">9.19411468505859</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17286777496338</t>
+    <t xml:space="preserve">9.17286682128906</t>
   </si>
   <si>
     <t xml:space="preserve">9.22695064544678</t>
@@ -2738,40 +2738,40 @@
     <t xml:space="preserve">9.36215782165527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12651062011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1477575302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13037300109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15934753417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12264823913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00482368469238</t>
+    <t xml:space="preserve">9.12650966644287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14775657653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13037395477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15934658050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12264633178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0048246383667</t>
   </si>
   <si>
     <t xml:space="preserve">9.13616847991943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0589075088501</t>
+    <t xml:space="preserve">9.05890655517578</t>
   </si>
   <si>
     <t xml:space="preserve">9.04538631439209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83677864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87347888946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95267295837402</t>
+    <t xml:space="preserve">8.83677959442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87347793579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95267200469971</t>
   </si>
   <si>
     <t xml:space="preserve">8.9391508102417</t>
@@ -2780,31 +2780,31 @@
     <t xml:space="preserve">8.86961650848389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88120651245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96619319915771</t>
+    <t xml:space="preserve">8.88120555877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96619415283203</t>
   </si>
   <si>
     <t xml:space="preserve">9.13809967041016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02027606964111</t>
+    <t xml:space="preserve">9.02027702331543</t>
   </si>
   <si>
     <t xml:space="preserve">8.90438461303711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66487216949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59340667724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54125595092773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55284404754639</t>
+    <t xml:space="preserve">8.66487407684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59340572357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54125499725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5528450012207</t>
   </si>
   <si>
     <t xml:space="preserve">8.42150020599365</t>
@@ -2813,7 +2813,7 @@
     <t xml:space="preserve">8.38093757629395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47365188598633</t>
+    <t xml:space="preserve">8.47365093231201</t>
   </si>
   <si>
     <t xml:space="preserve">8.42343139648438</t>
@@ -2822,22 +2822,22 @@
     <t xml:space="preserve">8.42536354064941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54705047607422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49296569824219</t>
+    <t xml:space="preserve">8.5470495223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4929666519165</t>
   </si>
   <si>
     <t xml:space="preserve">8.58568096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.512282371521</t>
+    <t xml:space="preserve">8.51228141784668</t>
   </si>
   <si>
     <t xml:space="preserve">8.50648593902588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63590049743652</t>
+    <t xml:space="preserve">8.63590145111084</t>
   </si>
   <si>
     <t xml:space="preserve">8.59533786773682</t>
@@ -2846,28 +2846,28 @@
     <t xml:space="preserve">8.65328407287598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57215976715088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57795429229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82712268829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86768627166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94108295440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3370475769043</t>
+    <t xml:space="preserve">8.57215881347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57795333862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82712364196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86768436431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94108390808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33704853057861</t>
   </si>
   <si>
     <t xml:space="preserve">9.3177318572998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40272045135498</t>
+    <t xml:space="preserve">9.40271949768066</t>
   </si>
   <si>
     <t xml:space="preserve">9.34477424621582</t>
@@ -2885,37 +2885,37 @@
     <t xml:space="preserve">9.42976093292236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44135093688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35249900817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20570278167725</t>
+    <t xml:space="preserve">9.44135189056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35249996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20570373535156</t>
   </si>
   <si>
     <t xml:space="preserve">9.28875923156738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31580066680908</t>
+    <t xml:space="preserve">9.3158016204834</t>
   </si>
   <si>
     <t xml:space="preserve">9.34091091156006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05697631835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19218158721924</t>
+    <t xml:space="preserve">9.05697536468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19218254089355</t>
   </si>
   <si>
     <t xml:space="preserve">9.16320896148682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04924964904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26751327514648</t>
+    <t xml:space="preserve">9.04924869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26751136779785</t>
   </si>
   <si>
     <t xml:space="preserve">9.16900444030762</t>
@@ -2924,55 +2924,55 @@
     <t xml:space="preserve">9.36795234680176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52440643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76391792297363</t>
+    <t xml:space="preserve">9.52440738677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76391696929932</t>
   </si>
   <si>
     <t xml:space="preserve">9.48964023590088</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46839141845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38726997375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42590045928955</t>
+    <t xml:space="preserve">9.46839237213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38726806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42589855194092</t>
   </si>
   <si>
     <t xml:space="preserve">9.364089012146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28296566009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25978660583496</t>
+    <t xml:space="preserve">9.2829647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25978755950928</t>
   </si>
   <si>
     <t xml:space="preserve">9.24240303039551</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26364994049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28682804107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3505687713623</t>
+    <t xml:space="preserve">9.26364898681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28682899475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35056972503662</t>
   </si>
   <si>
     <t xml:space="preserve">9.23081302642822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39885807037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32932186126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46453094482422</t>
+    <t xml:space="preserve">9.39885711669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32932090759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46452903747559</t>
   </si>
   <si>
     <t xml:space="preserve">9.41624164581299</t>
@@ -2984,7 +2984,7 @@
     <t xml:space="preserve">9.47225475311279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56497001647949</t>
+    <t xml:space="preserve">9.56496906280518</t>
   </si>
   <si>
     <t xml:space="preserve">9.64416217803955</t>
@@ -2993,10 +2993,10 @@
     <t xml:space="preserve">9.76943683624268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55384826660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73544692993164</t>
+    <t xml:space="preserve">9.55384922027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73544788360596</t>
   </si>
   <si>
     <t xml:space="preserve">9.83255958557129</t>
@@ -3011,16 +3011,16 @@
     <t xml:space="preserve">9.60823059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52859973907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63347911834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8811149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0025053024292</t>
+    <t xml:space="preserve">9.52860069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63348007202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88111591339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0025043487549</t>
   </si>
   <si>
     <t xml:space="preserve">10.0947608947754</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">9.98308181762695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94423675537109</t>
+    <t xml:space="preserve">9.94423770904541</t>
   </si>
   <si>
     <t xml:space="preserve">9.7742919921875</t>
@@ -3038,10 +3038,10 @@
     <t xml:space="preserve">9.86654758453369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82284736633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81313514709473</t>
+    <t xml:space="preserve">9.82284832000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81313705444336</t>
   </si>
   <si>
     <t xml:space="preserve">9.82770347595215</t>
@@ -3050,49 +3050,49 @@
     <t xml:space="preserve">9.79856967926025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79371452331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0656270980835</t>
+    <t xml:space="preserve">9.79371356964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0656261444092</t>
   </si>
   <si>
     <t xml:space="preserve">10.1675939559937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2355718612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2549953460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1870174407959</t>
+    <t xml:space="preserve">10.2355728149414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2549962997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1870164871216</t>
   </si>
   <si>
     <t xml:space="preserve">10.14817237854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2307167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2792720794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2744178771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3132619857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3909511566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5754642486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6337299346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8133869171143</t>
+    <t xml:space="preserve">10.2307176589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2792730331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2744169235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3132610321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3909521102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5754632949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6337308883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8133878707886</t>
   </si>
   <si>
     <t xml:space="preserve">10.8182430267334</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">10.8230991363525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8570880889893</t>
+    <t xml:space="preserve">10.8570871353149</t>
   </si>
   <si>
     <t xml:space="preserve">10.7551202774048</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7454080581665</t>
+    <t xml:space="preserve">10.7454090118408</t>
   </si>
   <si>
     <t xml:space="preserve">10.7842531204224</t>
@@ -3122,7 +3122,7 @@
     <t xml:space="preserve">11.0755882263184</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0610227584839</t>
+    <t xml:space="preserve">11.0610218048096</t>
   </si>
   <si>
     <t xml:space="preserve">11.0464553833008</t>
@@ -3137,22 +3137,22 @@
     <t xml:space="preserve">10.9104986190796</t>
   </si>
   <si>
-    <t xml:space="preserve">10.891077041626</t>
+    <t xml:space="preserve">10.8910760879517</t>
   </si>
   <si>
     <t xml:space="preserve">10.997899055481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8279542922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9541988372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9784784317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8667984008789</t>
+    <t xml:space="preserve">10.827953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.954197883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.978476524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8667993545532</t>
   </si>
   <si>
     <t xml:space="preserve">10.6531524658203</t>
@@ -3161,31 +3161,31 @@
     <t xml:space="preserve">10.7162752151489</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9930438995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1629886627197</t>
+    <t xml:space="preserve">10.9930429458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.162989616394</t>
   </si>
   <si>
     <t xml:space="preserve">11.0513105392456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4009132385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4688920974731</t>
+    <t xml:space="preserve">11.4009122848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4688911437988</t>
   </si>
   <si>
     <t xml:space="preserve">11.4931688308716</t>
   </si>
   <si>
-    <t xml:space="preserve">11.51744556427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5951366424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.561146736145</t>
+    <t xml:space="preserve">11.5174465179443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5951356887817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5611476898193</t>
   </si>
   <si>
     <t xml:space="preserve">11.5028800964355</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">11.6048469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5805702209473</t>
+    <t xml:space="preserve">11.5805692672729</t>
   </si>
   <si>
     <t xml:space="preserve">11.5660028457642</t>
@@ -3218,7 +3218,7 @@
     <t xml:space="preserve">11.6825370788574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3620672225952</t>
+    <t xml:space="preserve">11.3620681762695</t>
   </si>
   <si>
     <t xml:space="preserve">11.2552452087402</t>
@@ -3230,37 +3230,37 @@
     <t xml:space="preserve">11.4251909255981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3814916610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.36692237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3329343795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3717794418335</t>
+    <t xml:space="preserve">11.3814907073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3669233322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.332935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3717784881592</t>
   </si>
   <si>
     <t xml:space="preserve">11.5902814865112</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6971035003662</t>
+    <t xml:space="preserve">11.6971044540405</t>
   </si>
   <si>
     <t xml:space="preserve">11.570858001709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5757131576538</t>
+    <t xml:space="preserve">11.5757141113281</t>
   </si>
   <si>
     <t xml:space="preserve">11.5125904083252</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4106245040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5514373779297</t>
+    <t xml:space="preserve">11.410623550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5514364242554</t>
   </si>
   <si>
     <t xml:space="preserve">11.7068157196045</t>
@@ -3269,16 +3269,16 @@
     <t xml:space="preserve">11.9495944976807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9301710128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7942152023315</t>
+    <t xml:space="preserve">11.9301719665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7942171096802</t>
   </si>
   <si>
     <t xml:space="preserve">11.7602262496948</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8087816238403</t>
+    <t xml:space="preserve">11.8087825775146</t>
   </si>
   <si>
     <t xml:space="preserve">11.8282060623169</t>
@@ -3299,46 +3299,46 @@
     <t xml:space="preserve">12.036994934082</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1875171661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1486740112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3865976333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5565433502197</t>
+    <t xml:space="preserve">12.187518119812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1486730575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3865966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5565423965454</t>
   </si>
   <si>
     <t xml:space="preserve">12.425440788269</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5274085998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5322647094727</t>
+    <t xml:space="preserve">12.5274076461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5322637557983</t>
   </si>
   <si>
     <t xml:space="preserve">12.5662527084351</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9350261688232</t>
+    <t xml:space="preserve">11.9350271224976</t>
   </si>
   <si>
     <t xml:space="preserve">12.012716293335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0758390426636</t>
+    <t xml:space="preserve">12.0758399963379</t>
   </si>
   <si>
     <t xml:space="preserve">12.1729507446289</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3331842422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3137626647949</t>
+    <t xml:space="preserve">12.3331851959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3137645721436</t>
   </si>
   <si>
     <t xml:space="preserve">12.4205856323242</t>
@@ -3350,28 +3350,28 @@
     <t xml:space="preserve">12.4108743667603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.444863319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4157304763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5468311309814</t>
+    <t xml:space="preserve">12.4448642730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4157295227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5468301773071</t>
   </si>
   <si>
     <t xml:space="preserve">12.6439428329468</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7750425338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9644117355347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9595565795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9401330947876</t>
+    <t xml:space="preserve">12.7750434875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9644107818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9595556259155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9401321411133</t>
   </si>
   <si>
     <t xml:space="preserve">13.0760898590088</t>
@@ -3380,13 +3380,13 @@
     <t xml:space="preserve">12.5808200836182</t>
   </si>
   <si>
-    <t xml:space="preserve">12.595386505127</t>
+    <t xml:space="preserve">12.5953874588013</t>
   </si>
   <si>
     <t xml:space="preserve">12.9109992980957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4837074279785</t>
+    <t xml:space="preserve">12.4837083816528</t>
   </si>
   <si>
     <t xml:space="preserve">12.7070655822754</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">12.4982748031616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4739980697632</t>
+    <t xml:space="preserve">12.4739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">12.3428964614868</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">12.639087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8721542358398</t>
+    <t xml:space="preserve">12.8721551895142</t>
   </si>
   <si>
     <t xml:space="preserve">12.6099529266357</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">12.5856761932373</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3768863677979</t>
+    <t xml:space="preserve">12.3768854141235</t>
   </si>
   <si>
     <t xml:space="preserve">12.4885635375977</t>
@@ -3422,46 +3422,46 @@
     <t xml:space="preserve">12.284628868103</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2797737121582</t>
+    <t xml:space="preserve">12.2797746658325</t>
   </si>
   <si>
     <t xml:space="preserve">12.2020835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4400081634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3720302581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4351530075073</t>
+    <t xml:space="preserve">12.4400072097778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3720293045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.435152053833</t>
   </si>
   <si>
     <t xml:space="preserve">12.3963079452515</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4060192108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7553691864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6728258132935</t>
+    <t xml:space="preserve">12.4060173034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7553701400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6728267669678</t>
   </si>
   <si>
     <t xml:space="preserve">11.6388359069824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4397573471069</t>
+    <t xml:space="preserve">11.4397563934326</t>
   </si>
   <si>
     <t xml:space="preserve">11.1532783508301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2164001464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0804433822632</t>
+    <t xml:space="preserve">11.2164011001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0804443359375</t>
   </si>
   <si>
     <t xml:space="preserve">11.0658779144287</t>
@@ -3476,7 +3476,7 @@
     <t xml:space="preserve">10.6191644668579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5171966552734</t>
+    <t xml:space="preserve">10.5171957015991</t>
   </si>
   <si>
     <t xml:space="preserve">10.7696876525879</t>
@@ -3485,31 +3485,31 @@
     <t xml:space="preserve">10.9833326339722</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8619441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7114200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5269069671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4492197036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5317640304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4880619049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3375396728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0899047851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821603775024</t>
+    <t xml:space="preserve">10.8619432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7114191055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5269079208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4492177963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5317630767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4880638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3375406265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0899057388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821613311768</t>
   </si>
   <si>
     <t xml:space="preserve">10.1918716430664</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">10.264705657959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95880317687988</t>
+    <t xml:space="preserve">9.9588041305542</t>
   </si>
   <si>
     <t xml:space="preserve">9.02556133270264</t>
@@ -3530,19 +3530,19 @@
     <t xml:space="preserve">9.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04304218292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04498291015625</t>
+    <t xml:space="preserve">9.04304027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04498386383057</t>
   </si>
   <si>
     <t xml:space="preserve">9.06246280670166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84299087524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83910751342773</t>
+    <t xml:space="preserve">8.84299182891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83910655975342</t>
   </si>
   <si>
     <t xml:space="preserve">8.5438871383667</t>
@@ -3551,25 +3551,25 @@
     <t xml:space="preserve">9.1440372467041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9906005859375</t>
+    <t xml:space="preserve">8.99060153961182</t>
   </si>
   <si>
     <t xml:space="preserve">8.95369815826416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99837017059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03138828277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58492469787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55190658569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75001335144043</t>
+    <t xml:space="preserve">8.99836921691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03138732910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58492374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55190563201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75001430511475</t>
   </si>
   <si>
     <t xml:space="preserve">9.621826171875</t>
@@ -3578,34 +3578,34 @@
     <t xml:space="preserve">9.68203639984131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63736343383789</t>
+    <t xml:space="preserve">9.63736438751221</t>
   </si>
   <si>
     <t xml:space="preserve">9.62571144104004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0801935195923</t>
+    <t xml:space="preserve">10.0801944732666</t>
   </si>
   <si>
     <t xml:space="preserve">10.2598505020142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2501392364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4200849533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3860950469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5074853897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346523284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4152297973633</t>
+    <t xml:space="preserve">10.2501401901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4200839996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3860960006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5074844360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4346504211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.415228843689</t>
   </si>
   <si>
     <t xml:space="preserve">10.3278293609619</t>
@@ -3614,13 +3614,13 @@
     <t xml:space="preserve">10.2110719680786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.528489112854</t>
+    <t xml:space="preserve">10.5284900665283</t>
   </si>
   <si>
     <t xml:space="preserve">10.3429231643677</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3819885253906</t>
+    <t xml:space="preserve">10.3819894790649</t>
   </si>
   <si>
     <t xml:space="preserve">10.4308233261108</t>
@@ -3632,10 +3632,10 @@
     <t xml:space="preserve">10.4259395599365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5333728790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2306060791016</t>
+    <t xml:space="preserve">10.5333738327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2306051254272</t>
   </si>
   <si>
     <t xml:space="preserve">10.4601230621338</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">10.0645723342896</t>
   </si>
   <si>
-    <t xml:space="preserve">10.172004699707</t>
+    <t xml:space="preserve">10.1720056533813</t>
   </si>
   <si>
     <t xml:space="preserve">9.54986763000488</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">9.33890724182129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58893394470215</t>
+    <t xml:space="preserve">9.58893489837646</t>
   </si>
   <si>
     <t xml:space="preserve">9.68855476379395</t>
@@ -3665,25 +3665,25 @@
     <t xml:space="preserve">9.97178840637207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0059719085693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91318893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59870147705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39750671386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36234760284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6182336807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40532112121582</t>
+    <t xml:space="preserve">10.0059728622437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91318798065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59870052337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3975076675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36234664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61823463439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4053201675415</t>
   </si>
   <si>
     <t xml:space="preserve">9.47173500061035</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">9.659255027771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78622150421143</t>
+    <t xml:space="preserve">9.78622245788574</t>
   </si>
   <si>
     <t xml:space="preserve">9.71004199981689</t>
@@ -3707,16 +3707,16 @@
     <t xml:space="preserve">9.69441413879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66511344909668</t>
+    <t xml:space="preserve">9.66511535644531</t>
   </si>
   <si>
     <t xml:space="preserve">9.87412166595459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68074035644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54791450500488</t>
+    <t xml:space="preserve">9.68074131011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54791355133057</t>
   </si>
   <si>
     <t xml:space="preserve">9.03418636322021</t>
@@ -3728,13 +3728,13 @@
     <t xml:space="preserve">8.8154125213623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20607948303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11427307128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52252006530762</t>
+    <t xml:space="preserve">9.20608043670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11427211761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52252101898193</t>
   </si>
   <si>
     <t xml:space="preserve">9.56744766235352</t>
@@ -3749,22 +3749,22 @@
     <t xml:space="preserve">9.4541540145874</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79110527038574</t>
+    <t xml:space="preserve">9.79110431671143</t>
   </si>
   <si>
     <t xml:space="preserve">9.85947227478027</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91807079315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81552219390869</t>
+    <t xml:space="preserve">9.91807174682617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81552124023438</t>
   </si>
   <si>
     <t xml:space="preserve">9.80087089538574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72566890716553</t>
+    <t xml:space="preserve">9.72566795349121</t>
   </si>
   <si>
     <t xml:space="preserve">9.66120910644531</t>
@@ -3773,16 +3773,16 @@
     <t xml:space="preserve">9.95713806152344</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001088142395</t>
+    <t xml:space="preserve">10.0010890960693</t>
   </si>
   <si>
     <t xml:space="preserve">10.162239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2989721298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0499210357666</t>
+    <t xml:space="preserve">10.2989730834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0499219894409</t>
   </si>
   <si>
     <t xml:space="preserve">9.94248867034912</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">9.88877201080322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1329383850098</t>
+    <t xml:space="preserve">10.1329393386841</t>
   </si>
   <si>
     <t xml:space="preserve">10.2354879379272</t>
@@ -3821,31 +3821,31 @@
     <t xml:space="preserve">10.1182880401611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.19642162323</t>
+    <t xml:space="preserve">10.1964225769043</t>
   </si>
   <si>
     <t xml:space="preserve">9.97667217254639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81063747406006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79598712921143</t>
+    <t xml:space="preserve">9.81063842773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79598808288574</t>
   </si>
   <si>
     <t xml:space="preserve">9.78133869171143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87900447845459</t>
+    <t xml:space="preserve">9.87900543212891</t>
   </si>
   <si>
     <t xml:space="preserve">10.0352716445923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1134052276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1475887298584</t>
+    <t xml:space="preserve">10.1134042739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1475896835327</t>
   </si>
   <si>
     <t xml:space="preserve">10.152473449707</t>
@@ -3854,13 +3854,13 @@
     <t xml:space="preserve">9.9815559387207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83505535125732</t>
+    <t xml:space="preserve">9.83505439758301</t>
   </si>
   <si>
     <t xml:space="preserve">9.57916736602783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44829368591309</t>
+    <t xml:space="preserve">9.4482946395874</t>
   </si>
   <si>
     <t xml:space="preserve">9.62409400939941</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">9.20803356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32914161682129</t>
+    <t xml:space="preserve">9.32913970947266</t>
   </si>
   <si>
     <t xml:space="preserve">9.1298999786377</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">8.9658203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00683975219727</t>
+    <t xml:space="preserve">9.00684070587158</t>
   </si>
   <si>
     <t xml:space="preserve">8.94042682647705</t>
@@ -3902,7 +3902,7 @@
     <t xml:space="preserve">8.78025245666504</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68649196624756</t>
+    <t xml:space="preserve">8.68649291992188</t>
   </si>
   <si>
     <t xml:space="preserve">8.89549922943115</t>
@@ -3914,22 +3914,22 @@
     <t xml:space="preserve">8.88377952575684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72360610961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89940738677979</t>
+    <t xml:space="preserve">8.72360515594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89940643310547</t>
   </si>
   <si>
     <t xml:space="preserve">8.73532581329346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01074600219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78806591033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88963985443115</t>
+    <t xml:space="preserve">9.01074695587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78806686401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88964080810547</t>
   </si>
   <si>
     <t xml:space="preserve">8.79783248901367</t>
@@ -3944,10 +3944,10 @@
     <t xml:space="preserve">8.78611278533936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98535251617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96191310882568</t>
+    <t xml:space="preserve">8.98535346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96191215515137</t>
   </si>
   <si>
     <t xml:space="preserve">8.84080600738525</t>
@@ -3959,31 +3959,31 @@
     <t xml:space="preserve">8.45209217071533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72165298461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90917205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79587936401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80173969268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70797920227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88182640075684</t>
+    <t xml:space="preserve">8.72165203094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90917301177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79587841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80173873901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70798015594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88182544708252</t>
   </si>
   <si>
     <t xml:space="preserve">8.99707317352295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10841369628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9638671875</t>
+    <t xml:space="preserve">9.10841464996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96386623382568</t>
   </si>
   <si>
     <t xml:space="preserve">9.09473991394043</t>
@@ -3995,7 +3995,7 @@
     <t xml:space="preserve">8.9755859375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05958080291748</t>
+    <t xml:space="preserve">9.05957984924316</t>
   </si>
   <si>
     <t xml:space="preserve">9.41704082489014</t>
@@ -4004,49 +4004,49 @@
     <t xml:space="preserve">9.54205513000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49322032928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56549453735352</t>
+    <t xml:space="preserve">9.49322128295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5654935836792</t>
   </si>
   <si>
     <t xml:space="preserve">9.73543548583984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76278114318848</t>
+    <t xml:space="preserve">9.76278209686279</t>
   </si>
   <si>
     <t xml:space="preserve">10.1280555725098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96202182769775</t>
+    <t xml:space="preserve">9.96202087402344</t>
   </si>
   <si>
     <t xml:space="preserve">9.83993721008301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80575561523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69050788879395</t>
+    <t xml:space="preserve">9.80575466156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69050884246826</t>
   </si>
   <si>
     <t xml:space="preserve">9.72371482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75692081451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9278392791748</t>
+    <t xml:space="preserve">9.75692176818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92783832550049</t>
   </si>
   <si>
     <t xml:space="preserve">9.95225429534912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58502769470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62214183807373</t>
+    <t xml:space="preserve">9.58502864837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62214088439941</t>
   </si>
   <si>
     <t xml:space="preserve">9.31546783447266</t>
@@ -4055,25 +4055,25 @@
     <t xml:space="preserve">9.5108003616333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40336799621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38774108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42290019989014</t>
+    <t xml:space="preserve">9.4033670425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38774013519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42290115356445</t>
   </si>
   <si>
     <t xml:space="preserve">9.45806121826172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26272773742676</t>
+    <t xml:space="preserve">9.26272678375244</t>
   </si>
   <si>
     <t xml:space="preserve">9.33500003814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43462085723877</t>
+    <t xml:space="preserve">9.43461990356445</t>
   </si>
   <si>
     <t xml:space="preserve">9.59088706970215</t>
@@ -4085,10 +4085,10 @@
     <t xml:space="preserve">9.64948749542236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.65730094909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74324798583984</t>
+    <t xml:space="preserve">9.65729999542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74324703216553</t>
   </si>
   <si>
     <t xml:space="preserve">9.71199512481689</t>
@@ -4103,28 +4103,28 @@
     <t xml:space="preserve">9.42876052856445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43852710723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71590137481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0303888320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90342140197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83017158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1427049636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2696723937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2452564239502</t>
+    <t xml:space="preserve">9.43852615356445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71590232849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0303897857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90342235565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83017063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1427059173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2696733474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2452554702759</t>
   </si>
   <si>
     <t xml:space="preserve">10.3038558959961</t>
@@ -4145,10 +4145,10 @@
     <t xml:space="preserve">10.3722229003906</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3478059768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5870895385742</t>
+    <t xml:space="preserve">10.347806930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5870904922485</t>
   </si>
   <si>
     <t xml:space="preserve">10.5382566452026</t>
@@ -4157,10 +4157,10 @@
     <t xml:space="preserve">10.4698905944824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405889511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3917570114136</t>
+    <t xml:space="preserve">10.4405899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3917560577393</t>
   </si>
   <si>
     <t xml:space="preserve">10.4747734069824</t>
@@ -4184,7 +4184,7 @@
     <t xml:space="preserve">10.8703241348267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8605575561523</t>
+    <t xml:space="preserve">10.860556602478</t>
   </si>
   <si>
     <t xml:space="preserve">10.8312578201294</t>
@@ -4196,37 +4196,37 @@
     <t xml:space="preserve">10.880090713501</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8361396789551</t>
+    <t xml:space="preserve">10.8361406326294</t>
   </si>
   <si>
     <t xml:space="preserve">10.9875240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0314741134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.00705909729</t>
+    <t xml:space="preserve">11.03147315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0070571899414</t>
   </si>
   <si>
     <t xml:space="preserve">11.1291408538818</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2463426589966</t>
+    <t xml:space="preserve">11.2463417053223</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268075942993</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2121572494507</t>
+    <t xml:space="preserve">11.212158203125</t>
   </si>
   <si>
     <t xml:space="preserve">11.207275390625</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2561082839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2854089736938</t>
+    <t xml:space="preserve">11.2561073303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2854080200195</t>
   </si>
   <si>
     <t xml:space="preserve">11.3195915222168</t>
@@ -4235,22 +4235,22 @@
     <t xml:space="preserve">11.3488912582397</t>
   </si>
   <si>
-    <t xml:space="preserve">11.373309135437</t>
+    <t xml:space="preserve">11.3733081817627</t>
   </si>
   <si>
     <t xml:space="preserve">11.5295753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5737495422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6670074462891</t>
+    <t xml:space="preserve">11.5737504959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6670083999634</t>
   </si>
   <si>
     <t xml:space="preserve">11.5982913970947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6326503753662</t>
+    <t xml:space="preserve">11.6326494216919</t>
   </si>
   <si>
     <t xml:space="preserve">11.4657678604126</t>
@@ -4259,13 +4259,13 @@
     <t xml:space="preserve">11.7700815200806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9418716430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.902606010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0645790100098</t>
+    <t xml:space="preserve">11.9418725967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9026050567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0645799636841</t>
   </si>
   <si>
     <t xml:space="preserve">12.1038455963135</t>
@@ -4280,10 +4280,10 @@
     <t xml:space="preserve">12.054762840271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.162745475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9173307418823</t>
+    <t xml:space="preserve">12.1627445220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9173316955566</t>
   </si>
   <si>
     <t xml:space="preserve">11.9467802047729</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">11.9369640350342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9860458374023</t>
+    <t xml:space="preserve">11.9860467910767</t>
   </si>
   <si>
     <t xml:space="preserve">12.2314615249634</t>
@@ -4322,28 +4322,28 @@
     <t xml:space="preserve">12.467059135437</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4130687713623</t>
+    <t xml:space="preserve">12.413067817688</t>
   </si>
   <si>
     <t xml:space="preserve">12.5701332092285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5652256011963</t>
+    <t xml:space="preserve">12.565224647522</t>
   </si>
   <si>
     <t xml:space="preserve">12.6633901596069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6143074035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6241235733032</t>
+    <t xml:space="preserve">12.6143083572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6241245269775</t>
   </si>
   <si>
     <t xml:space="preserve">12.2658185958862</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0596704483032</t>
+    <t xml:space="preserve">12.0596714019775</t>
   </si>
   <si>
     <t xml:space="preserve">12.0694875717163</t>
@@ -4367,16 +4367,16 @@
     <t xml:space="preserve">12.3050851821899</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3296270370483</t>
+    <t xml:space="preserve">12.3296279907227</t>
   </si>
   <si>
     <t xml:space="preserve">12.2216444015503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1921939849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4376096725464</t>
+    <t xml:space="preserve">12.1921949386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4376087188721</t>
   </si>
   <si>
     <t xml:space="preserve">12.4228839874268</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">12.4866924285889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6928415298462</t>
+    <t xml:space="preserve">12.6928405761719</t>
   </si>
   <si>
     <t xml:space="preserve">12.4817838668823</t>
@@ -4409,13 +4409,13 @@
     <t xml:space="preserve">12.0940284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9762306213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9124231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.794623374939</t>
+    <t xml:space="preserve">11.9762296676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9124221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7946243286133</t>
   </si>
   <si>
     <t xml:space="preserve">11.8044395446777</t>
@@ -4424,7 +4424,7 @@
     <t xml:space="preserve">11.7995319366455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.819164276123</t>
+    <t xml:space="preserve">11.8191652297974</t>
   </si>
   <si>
     <t xml:space="preserve">11.8927888870239</t>
@@ -4436,7 +4436,7 @@
     <t xml:space="preserve">11.4461345672607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3970508575439</t>
+    <t xml:space="preserve">11.3970518112183</t>
   </si>
   <si>
     <t xml:space="preserve">11.4706764221191</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">11.3872356414795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5639324188232</t>
+    <t xml:space="preserve">11.5639333724976</t>
   </si>
   <si>
     <t xml:space="preserve">11.5835666656494</t>
@@ -4457,13 +4457,13 @@
     <t xml:space="preserve">11.9075136184692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0007724761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.848614692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7749900817871</t>
+    <t xml:space="preserve">12.000771522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8486137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7749891281128</t>
   </si>
   <si>
     <t xml:space="preserve">11.8535223007202</t>
@@ -4475,10 +4475,10 @@
     <t xml:space="preserve">11.5344839096069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.642466545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1516361236572</t>
+    <t xml:space="preserve">11.6424655914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1516370773315</t>
   </si>
   <si>
     <t xml:space="preserve">11.1025543212891</t>
@@ -4490,10 +4490,10 @@
     <t xml:space="preserve">11.1712703704834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.269434928894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.284161567688</t>
+    <t xml:space="preserve">11.2694358825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2841606140137</t>
   </si>
   <si>
     <t xml:space="preserve">11.54430103302</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">11.1909027099609</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0092964172363</t>
+    <t xml:space="preserve">11.0092973709106</t>
   </si>
   <si>
     <t xml:space="preserve">10.842414855957</t>
@@ -4511,7 +4511,7 @@
     <t xml:space="preserve">10.68044090271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7687902450562</t>
+    <t xml:space="preserve">10.7687911987305</t>
   </si>
   <si>
     <t xml:space="preserve">10.9602136611938</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">10.9454879760742</t>
   </si>
   <si>
-    <t xml:space="preserve">11.254711151123</t>
+    <t xml:space="preserve">11.2547121047974</t>
   </si>
   <si>
     <t xml:space="preserve">11.3087024688721</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">10.7786064147949</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7393398284912</t>
+    <t xml:space="preserve">10.7393407821655</t>
   </si>
   <si>
     <t xml:space="preserve">10.7344331741333</t>
@@ -4562,13 +4562,13 @@
     <t xml:space="preserve">10.7246160507202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7589731216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.886589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8571395874023</t>
+    <t xml:space="preserve">10.7589740753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8865900039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8571405410767</t>
   </si>
   <si>
     <t xml:space="preserve">10.1208963394165</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">9.98346424102783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1945199966431</t>
+    <t xml:space="preserve">10.1945209503174</t>
   </si>
   <si>
     <t xml:space="preserve">10.2386951446533</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">10.48410987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871829986572</t>
+    <t xml:space="preserve">10.5871839523315</t>
   </si>
   <si>
     <t xml:space="preserve">10.5381002426147</t>
@@ -4598,22 +4598,22 @@
     <t xml:space="preserve">10.7295246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7000741958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3466768264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2877779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4055776596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3270444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0669040679932</t>
+    <t xml:space="preserve">10.7000732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3466777801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2877769470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4055767059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3270454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0669050216675</t>
   </si>
   <si>
     <t xml:space="preserve">10.086537361145</t>
@@ -4637,13 +4637,13 @@
     <t xml:space="preserve">9.75375556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83621501922607</t>
+    <t xml:space="preserve">9.83621597290039</t>
   </si>
   <si>
     <t xml:space="preserve">9.83130741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86075592041016</t>
+    <t xml:space="preserve">9.86075687408447</t>
   </si>
   <si>
     <t xml:space="preserve">9.90493106842041</t>
@@ -4667,7 +4667,7 @@
     <t xml:space="preserve">9.8263988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9147481918335</t>
+    <t xml:space="preserve">9.91474723815918</t>
   </si>
   <si>
     <t xml:space="preserve">9.96382999420166</t>
@@ -4685,19 +4685,19 @@
     <t xml:space="preserve">10.0276384353638</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8902063369751</t>
+    <t xml:space="preserve">9.89020538330078</t>
   </si>
   <si>
     <t xml:space="preserve">9.76357269287109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86566543579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76553535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74001216888428</t>
+    <t xml:space="preserve">9.8656644821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76553630828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74001312255859</t>
   </si>
   <si>
     <t xml:space="preserve">9.74393844604492</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">9.10782432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15494441986084</t>
+    <t xml:space="preserve">9.15494537353516</t>
   </si>
   <si>
     <t xml:space="preserve">9.14905452728271</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">9.00769519805908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08033752441406</t>
+    <t xml:space="preserve">9.08033847808838</t>
   </si>
   <si>
     <t xml:space="preserve">9.06463146209717</t>
@@ -4736,19 +4736,19 @@
     <t xml:space="preserve">8.85455799102783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8152904510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29630279541016</t>
+    <t xml:space="preserve">8.81528949737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29630374908447</t>
   </si>
   <si>
     <t xml:space="preserve">9.22758674621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23740386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21580600738525</t>
+    <t xml:space="preserve">9.23740291595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21580696105957</t>
   </si>
   <si>
     <t xml:space="preserve">9.37090873718262</t>
@@ -4772,19 +4772,19 @@
     <t xml:space="preserve">9.61043357849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56527709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76749897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78909492492676</t>
+    <t xml:space="preserve">9.56527805328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76749801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78909587860107</t>
   </si>
   <si>
     <t xml:space="preserve">9.63988304138184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63791942596436</t>
+    <t xml:space="preserve">9.63792037963867</t>
   </si>
   <si>
     <t xml:space="preserve">9.6909294128418</t>
@@ -4796,16 +4796,16 @@
     <t xml:space="preserve">9.59080123901367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3807258605957</t>
+    <t xml:space="preserve">9.38072490692139</t>
   </si>
   <si>
     <t xml:space="preserve">9.65559005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32967948913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20009994506836</t>
+    <t xml:space="preserve">9.32967853546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20010089874268</t>
   </si>
   <si>
     <t xml:space="preserve">9.30023002624512</t>
@@ -4826,7 +4826,7 @@
     <t xml:space="preserve">9.36109256744385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40232276916504</t>
+    <t xml:space="preserve">9.40232181549072</t>
   </si>
   <si>
     <t xml:space="preserve">9.39054203033447</t>
@@ -4835,7 +4835,7 @@
     <t xml:space="preserve">9.47300148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47103786468506</t>
+    <t xml:space="preserve">9.47103881835938</t>
   </si>
   <si>
     <t xml:space="preserve">9.37876224517822</t>
@@ -4844,7 +4844,7 @@
     <t xml:space="preserve">9.27667045593262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08426475524902</t>
+    <t xml:space="preserve">9.08426380157471</t>
   </si>
   <si>
     <t xml:space="preserve">9.1254940032959</t>
@@ -4862,7 +4862,7 @@
     <t xml:space="preserve">9.06855869293213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14316368103027</t>
+    <t xml:space="preserve">9.14316463470459</t>
   </si>
   <si>
     <t xml:space="preserve">9.00573253631592</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">8.89382362365723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02340316772461</t>
+    <t xml:space="preserve">9.02340221405029</t>
   </si>
   <si>
     <t xml:space="preserve">8.92523670196533</t>
@@ -4883,7 +4883,7 @@
     <t xml:space="preserve">8.92327308654785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88400650024414</t>
+    <t xml:space="preserve">8.88400745391846</t>
   </si>
   <si>
     <t xml:space="preserve">8.80743789672852</t>
@@ -4892,7 +4892,7 @@
     <t xml:space="preserve">8.73479461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7681713104248</t>
+    <t xml:space="preserve">8.76817035675049</t>
   </si>
   <si>
     <t xml:space="preserve">8.77995109558105</t>
@@ -4901,10 +4901,10 @@
     <t xml:space="preserve">8.9821720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21188068389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30219268798828</t>
+    <t xml:space="preserve">9.21187973022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3021936416626</t>
   </si>
   <si>
     <t xml:space="preserve">9.42377090454102</t>
@@ -5916,6 +5916,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.43400001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80000019073486</t>
   </si>
 </sst>
 </file>
@@ -70994,7 +70997,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6499768519</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>11727239</v>
@@ -71015,6 +71018,32 @@
         <v>1889</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6496990741</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>9027014</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>5.83799982070923</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>5.61999988555908</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>5.67000007629395</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>1968</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1969" uniqueCount="1969">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="1970">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59865665435791</t>
+    <t xml:space="preserve">3.59865617752075</t>
   </si>
   <si>
     <t xml:space="preserve">CPR.MI</t>
@@ -47,82 +47,82 @@
     <t xml:space="preserve">3.65898251533508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60329723358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51976919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51048874855042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54993200302124</t>
+    <t xml:space="preserve">3.60329699516296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51976871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51048851013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54993224143982</t>
   </si>
   <si>
     <t xml:space="preserve">3.62881970405579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68450450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57313442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52672958374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48264575004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5661735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43392133712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50584769248962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56153321266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64274072647095</t>
+    <t xml:space="preserve">3.68450474739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57313418388367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52673006057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48264598846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56617403030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43392086029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50584745407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56153297424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64274024963379</t>
   </si>
   <si>
     <t xml:space="preserve">3.66594314575195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56849455833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74250984191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72162842750549</t>
+    <t xml:space="preserve">3.56849384307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74251008033752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72162818908691</t>
   </si>
   <si>
     <t xml:space="preserve">3.70770668983459</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47104477882385</t>
+    <t xml:space="preserve">3.47104454040527</t>
   </si>
   <si>
     <t xml:space="preserve">3.44320225715637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28078675270081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33183145523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40839886665344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22046136856079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26918578147888</t>
+    <t xml:space="preserve">3.28078699111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33183217048645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40839838981628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22046184539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26918601989746</t>
   </si>
   <si>
     <t xml:space="preserve">3.32487106323242</t>
@@ -131,34 +131,34 @@
     <t xml:space="preserve">3.24366331100464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32255053520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28774762153625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31791043281555</t>
+    <t xml:space="preserve">3.32255077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28774785995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31791067123413</t>
   </si>
   <si>
     <t xml:space="preserve">3.36663484573364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36199426651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40607833862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38287663459778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36431455612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53137040138245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60561728477478</t>
+    <t xml:space="preserve">3.36199450492859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40607857704163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38287615776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36431479454041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53137016296387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60561752319336</t>
   </si>
   <si>
     <t xml:space="preserve">3.61257791519165</t>
@@ -167,22 +167,22 @@
     <t xml:space="preserve">3.56385326385498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61489796638489</t>
+    <t xml:space="preserve">3.61489820480347</t>
   </si>
   <si>
     <t xml:space="preserve">3.63810038566589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68914484977722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476253509521</t>
+    <t xml:space="preserve">3.6891450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476205825806</t>
   </si>
   <si>
     <t xml:space="preserve">3.95596981048584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00701522827148</t>
+    <t xml:space="preserve">4.00701475143433</t>
   </si>
   <si>
     <t xml:space="preserve">4.04877901077271</t>
@@ -191,61 +191,61 @@
     <t xml:space="preserve">4.03485679626465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04181861877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03717756271362</t>
+    <t xml:space="preserve">4.04181814193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03717708587646</t>
   </si>
   <si>
     <t xml:space="preserve">4.05109882354736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01861619949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09286212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07662200927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0394983291626</t>
+    <t xml:space="preserve">4.01861572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09286260604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07662105560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03949785232544</t>
   </si>
   <si>
     <t xml:space="preserve">4.08358192443848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02325677871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00005435943604</t>
+    <t xml:space="preserve">4.02325630187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00005388259888</t>
   </si>
   <si>
     <t xml:space="preserve">4.06037998199463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9954149723053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94436836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97453141212463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00237417221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93740820884705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94668936729431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03021717071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05341911315918</t>
+    <t xml:space="preserve">3.99541306495667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94436883926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97453165054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00237512588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93740844726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94668889045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03021764755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05341958999634</t>
   </si>
   <si>
     <t xml:space="preserve">4.00933504104614</t>
@@ -254,19 +254,19 @@
     <t xml:space="preserve">3.95829010009766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98613286018372</t>
+    <t xml:space="preserve">3.98613309860229</t>
   </si>
   <si>
     <t xml:space="preserve">4.0255765914917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96989107131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91188645362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8979651927948</t>
+    <t xml:space="preserve">3.96989178657532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91188597679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89796471595764</t>
   </si>
   <si>
     <t xml:space="preserve">3.87708258628845</t>
@@ -275,34 +275,34 @@
     <t xml:space="preserve">3.9142062664032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92812752723694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95132970809937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06734085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08126258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99309372901917</t>
+    <t xml:space="preserve">3.92812776565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95132923126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06734037399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08126211166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99309277534485</t>
   </si>
   <si>
     <t xml:space="preserve">3.96757102012634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98149228096008</t>
+    <t xml:space="preserve">3.98149251937866</t>
   </si>
   <si>
     <t xml:space="preserve">3.96293044090271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8886833190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89332389831543</t>
+    <t xml:space="preserve">3.88868379592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89332485198975</t>
   </si>
   <si>
     <t xml:space="preserve">3.79587554931641</t>
@@ -311,10 +311,10 @@
     <t xml:space="preserve">3.89309906959534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02677822113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08540868759155</t>
+    <t xml:space="preserve">4.02677726745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08540821075439</t>
   </si>
   <si>
     <t xml:space="preserve">4.07602739334106</t>
@@ -329,64 +329,64 @@
     <t xml:space="preserve">4.07368278503418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09009981155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10182523727417</t>
+    <t xml:space="preserve">4.0900993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10182428359985</t>
   </si>
   <si>
     <t xml:space="preserve">4.0877537727356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1135516166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08071851730347</t>
+    <t xml:space="preserve">4.11355257034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08071756362915</t>
   </si>
   <si>
     <t xml:space="preserve">4.01974153518677</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90482497215271</t>
+    <t xml:space="preserve">3.90482425689697</t>
   </si>
   <si>
     <t xml:space="preserve">3.85557532310486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85792016983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86495590209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8719916343689</t>
+    <t xml:space="preserve">3.85792088508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86495614051819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87199139595032</t>
   </si>
   <si>
     <t xml:space="preserve">3.86964631080627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00567007064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00801610946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95876502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05961132049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88606286048889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88840818405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04084873199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16514730453491</t>
+    <t xml:space="preserve">4.00567054748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00801515579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95876526832581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05961084365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88606333732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88840794563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04084968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16514682769775</t>
   </si>
   <si>
     <t xml:space="preserve">4.15576601028442</t>
@@ -395,16 +395,16 @@
     <t xml:space="preserve">4.14873075485229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13231372833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00332593917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04319381713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16045570373535</t>
+    <t xml:space="preserve">4.13231420516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00332498550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04319429397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16045618057251</t>
   </si>
   <si>
     <t xml:space="preserve">4.15811109542847</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">4.1158971786499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06899213790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13465881347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14169502258301</t>
+    <t xml:space="preserve">4.06899166107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1346583366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14169406890869</t>
   </si>
   <si>
     <t xml:space="preserve">4.18390941619873</t>
@@ -431,49 +431,49 @@
     <t xml:space="preserve">4.21908712387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29179000854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29648017883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31055164337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28709983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33165836334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33869457244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54038524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51458787918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5216236114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43719482421875</t>
+    <t xml:space="preserve">4.29178953170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29648065567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31055116653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28709936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33165884017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33869504928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5403847694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51458740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52162313461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43719530105591</t>
   </si>
   <si>
     <t xml:space="preserve">4.47940874099731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45595741271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66233777999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67171859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58963489532471</t>
+    <t xml:space="preserve">4.45595598220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66233730316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67171907424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58963537216187</t>
   </si>
   <si>
     <t xml:space="preserve">4.55914735794067</t>
@@ -482,16 +482,16 @@
     <t xml:space="preserve">4.56383800506592</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54976558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60370635986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59667158126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57321929931641</t>
+    <t xml:space="preserve">4.54976606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60370683670044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59667062759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57321834564209</t>
   </si>
   <si>
     <t xml:space="preserve">4.62012338638306</t>
@@ -500,10 +500,10 @@
     <t xml:space="preserve">4.59432554244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65061140060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57556343078613</t>
+    <t xml:space="preserve">4.65061092376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57556295394897</t>
   </si>
   <si>
     <t xml:space="preserve">4.7045521736145</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">4.6013617515564</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4864444732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4653377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39967155456543</t>
+    <t xml:space="preserve">4.48644495010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46533823013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39967060089111</t>
   </si>
   <si>
     <t xml:space="preserve">4.43250465393066</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">4.50520658493042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49113512039185</t>
+    <t xml:space="preserve">4.49113464355469</t>
   </si>
   <si>
     <t xml:space="preserve">4.51693296432495</t>
@@ -542,19 +542,19 @@
     <t xml:space="preserve">4.50286149978638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48878955841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65295648574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66468286514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73269462585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71393346786499</t>
+    <t xml:space="preserve">4.48879051208496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65295696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66468238830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73269414901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71393251419067</t>
   </si>
   <si>
     <t xml:space="preserve">4.69048023223877</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">4.56852769851685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47471904754639</t>
+    <t xml:space="preserve">4.47471809387207</t>
   </si>
   <si>
     <t xml:space="preserve">4.44657564163208</t>
@@ -578,16 +578,16 @@
     <t xml:space="preserve">4.44188547134399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50051689147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52631378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36683702468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37152767181396</t>
+    <t xml:space="preserve">4.50051593780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52631282806396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36683797836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37152814865112</t>
   </si>
   <si>
     <t xml:space="preserve">4.33400392532349</t>
@@ -599,13 +599,13 @@
     <t xml:space="preserve">4.3058614730835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30351638793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25661182403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20736169815063</t>
+    <t xml:space="preserve">4.30351686477661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25661134719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20736074447632</t>
   </si>
   <si>
     <t xml:space="preserve">4.09478950500488</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">4.24253988265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20267105102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95642066001892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95407581329346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03381395339966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12527799606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01739597320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12996816635132</t>
+    <t xml:space="preserve">4.20267057418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9564208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95407557487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0338134765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12527751922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01739645004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12996912002563</t>
   </si>
   <si>
     <t xml:space="preserve">4.1721830368042</t>
@@ -641,40 +641,40 @@
     <t xml:space="preserve">4.21205139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1885986328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24957513809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20501613616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26833820343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22846841812134</t>
+    <t xml:space="preserve">4.18860006332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24957656860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20501565933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26833772659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2284688949585</t>
   </si>
   <si>
     <t xml:space="preserve">4.24723052978516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31993293762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36449289321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28944444656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27771759033203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30117034912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32227849960327</t>
+    <t xml:space="preserve">4.31993341445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449241638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28944492340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27771854400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30117082595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32227802276611</t>
   </si>
   <si>
     <t xml:space="preserve">4.35745668411255</t>
@@ -683,37 +683,37 @@
     <t xml:space="preserve">4.34807586669922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34338569641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39028930664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36214637756348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32462310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39732503890991</t>
+    <t xml:space="preserve">4.34338521957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39029026031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36214733123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32462358474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39732646942139</t>
   </si>
   <si>
     <t xml:space="preserve">4.37387371063232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36918258666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47002840042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45830154418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42546939849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43484973907471</t>
+    <t xml:space="preserve">4.36918306350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47002792358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45830202102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42546892166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43484926223755</t>
   </si>
   <si>
     <t xml:space="preserve">4.46768283843994</t>
@@ -728,22 +728,22 @@
     <t xml:space="preserve">4.3855996131897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43954086303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4301586151123</t>
+    <t xml:space="preserve">4.43953990936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43015909194946</t>
   </si>
   <si>
     <t xml:space="preserve">4.49348020553589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47237205505371</t>
+    <t xml:space="preserve">4.47237348556519</t>
   </si>
   <si>
     <t xml:space="preserve">4.52396869659424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54273080825806</t>
+    <t xml:space="preserve">4.5427303314209</t>
   </si>
   <si>
     <t xml:space="preserve">4.53804016113281</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">4.55211210250854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57087469100952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53569459915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5075511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58494472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65530252456665</t>
+    <t xml:space="preserve">4.57087326049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53569507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50755214691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58494424819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65530157089233</t>
   </si>
   <si>
     <t xml:space="preserve">4.74207639694214</t>
@@ -785,31 +785,31 @@
     <t xml:space="preserve">4.80774211883545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83119535446167</t>
+    <t xml:space="preserve">4.83119487762451</t>
   </si>
   <si>
     <t xml:space="preserve">4.89686155319214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94845724105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09855318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0516471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12200498580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04695701599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05633735656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99536180496216</t>
+    <t xml:space="preserve">4.94845676422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09855270385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05164813995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12200546264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04695749282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05633878707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99536228179932</t>
   </si>
   <si>
     <t xml:space="preserve">5.01881408691406</t>
@@ -818,22 +818,22 @@
     <t xml:space="preserve">5.02819585800171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03288555145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93907594680786</t>
+    <t xml:space="preserve">5.03288507461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93907642364502</t>
   </si>
   <si>
     <t xml:space="preserve">4.97660064697266</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92500495910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96721935272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08917188644409</t>
+    <t xml:space="preserve">4.92500448226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96721887588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08917093276978</t>
   </si>
   <si>
     <t xml:space="preserve">5.17359972000122</t>
@@ -842,10 +842,10 @@
     <t xml:space="preserve">5.14545774459839</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15952920913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09386253356934</t>
+    <t xml:space="preserve">5.1595287322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09386157989502</t>
   </si>
   <si>
     <t xml:space="preserve">5.16421890258789</t>
@@ -854,22 +854,22 @@
     <t xml:space="preserve">5.25333833694458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18767166137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41750574111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6707911491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60043334960938</t>
+    <t xml:space="preserve">5.18767213821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41750526428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67079162597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60043382644653</t>
   </si>
   <si>
     <t xml:space="preserve">5.62388610839844</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66141080856323</t>
+    <t xml:space="preserve">5.66141033172607</t>
   </si>
   <si>
     <t xml:space="preserve">5.68486213684082</t>
@@ -878,31 +878,31 @@
     <t xml:space="preserve">5.57698202133179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60512495040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7223858833313</t>
+    <t xml:space="preserve">5.60512399673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72238636016846</t>
   </si>
   <si>
     <t xml:space="preserve">5.69403409957886</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74128818511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76491355895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7507381439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87832260131836</t>
+    <t xml:space="preserve">5.74128770828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76491403579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75073862075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8783221244812</t>
   </si>
   <si>
     <t xml:space="preserve">5.86887168884277</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88304805755615</t>
+    <t xml:space="preserve">5.88304710388184</t>
   </si>
   <si>
     <t xml:space="preserve">6.02008247375488</t>
@@ -911,19 +911,19 @@
     <t xml:space="preserve">5.9917311668396</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00118112564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93502759933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8594217300415</t>
+    <t xml:space="preserve">6.00118160247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93502712249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85942077636719</t>
   </si>
   <si>
     <t xml:space="preserve">5.80271673202515</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75546360015869</t>
+    <t xml:space="preserve">5.75546407699585</t>
   </si>
   <si>
     <t xml:space="preserve">5.73183727264404</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">5.84997081756592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81216764450073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95865297317505</t>
+    <t xml:space="preserve">5.81216812133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95865249633789</t>
   </si>
   <si>
     <t xml:space="preserve">5.93030166625977</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">5.9822793006897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90194892883301</t>
+    <t xml:space="preserve">5.90194940567017</t>
   </si>
   <si>
     <t xml:space="preserve">5.91612577438354</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">5.8310694694519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88777303695679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78381490707397</t>
+    <t xml:space="preserve">5.88777351379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78381538391113</t>
   </si>
   <si>
     <t xml:space="preserve">5.80744218826294</t>
@@ -968,70 +968,70 @@
     <t xml:space="preserve">5.84524536132812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77436494827271</t>
+    <t xml:space="preserve">5.77436542510986</t>
   </si>
   <si>
     <t xml:space="preserve">5.82634353637695</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82161855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85469532012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79326629638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83579397201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95392799377441</t>
+    <t xml:space="preserve">5.82161808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85469627380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79326677322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83579444885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95392847061157</t>
   </si>
   <si>
     <t xml:space="preserve">5.92557525634766</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94447660446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7790904045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74601316452026</t>
+    <t xml:space="preserve">5.94447708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77909088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74601268768311</t>
   </si>
   <si>
     <t xml:space="preserve">5.71766090393066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6515064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66095638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79799222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76018953323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69875955581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66568231582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73656177520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78854084014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76963996887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89249849319458</t>
+    <t xml:space="preserve">5.65150594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66095590591431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79799175262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76018857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69876003265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6656813621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73656272888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78854131698608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76963949203491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89249897003174</t>
   </si>
   <si>
     <t xml:space="preserve">5.97282934188843</t>
@@ -1040,16 +1040,16 @@
     <t xml:space="preserve">6.15239286422729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14766645431519</t>
+    <t xml:space="preserve">6.14766693115234</t>
   </si>
   <si>
     <t xml:space="preserve">6.28470182418823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13821649551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1240406036377</t>
+    <t xml:space="preserve">6.13821601867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12404012680054</t>
   </si>
   <si>
     <t xml:space="preserve">6.02953290939331</t>
@@ -1058,37 +1058,37 @@
     <t xml:space="preserve">6.10513877868652</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16656875610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11458969116211</t>
+    <t xml:space="preserve">6.16656923294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11458921432495</t>
   </si>
   <si>
     <t xml:space="preserve">6.31777858734131</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34140634536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4075608253479</t>
+    <t xml:space="preserve">6.34140586853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40756034851074</t>
   </si>
   <si>
     <t xml:space="preserve">6.50206708908081</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42173671722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3083291053772</t>
+    <t xml:space="preserve">6.42173624038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30832862854004</t>
   </si>
   <si>
     <t xml:space="preserve">6.478440284729</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31305313110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33668041229248</t>
+    <t xml:space="preserve">6.31305360794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33667993545532</t>
   </si>
   <si>
     <t xml:space="preserve">6.37448263168335</t>
@@ -1097,37 +1097,37 @@
     <t xml:space="preserve">6.17601871490479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0909628868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23272275924683</t>
+    <t xml:space="preserve">6.09096336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23272323608398</t>
   </si>
   <si>
     <t xml:space="preserve">6.03898334503174</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08623695373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10041379928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10986423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00590705871582</t>
+    <t xml:space="preserve">6.08623790740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10041236877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10986471176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00590658187866</t>
   </si>
   <si>
     <t xml:space="preserve">6.03425884246826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09568786621094</t>
+    <t xml:space="preserve">6.09568738937378</t>
   </si>
   <si>
     <t xml:space="preserve">6.06261110305786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18074417114258</t>
+    <t xml:space="preserve">6.18074369430542</t>
   </si>
   <si>
     <t xml:space="preserve">6.08151245117188</t>
@@ -1136,7 +1136,7 @@
     <t xml:space="preserve">6.15711736679077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21382188796997</t>
+    <t xml:space="preserve">6.21382093429565</t>
   </si>
   <si>
     <t xml:space="preserve">6.24217319488525</t>
@@ -1151,46 +1151,46 @@
     <t xml:space="preserve">6.22799825668335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19964504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12876558303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07206153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05788469314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13349056243896</t>
+    <t xml:space="preserve">6.19964599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12876605987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07206201553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05788612365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13349151611328</t>
   </si>
   <si>
     <t xml:space="preserve">6.14294147491455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0106315612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94920253753662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97755479812622</t>
+    <t xml:space="preserve">6.01063299179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94920301437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9775538444519</t>
   </si>
   <si>
     <t xml:space="preserve">6.05316019058228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99645566940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06733560562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93975114822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71293544769287</t>
+    <t xml:space="preserve">5.99645614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06733655929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93975162506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71293592453003</t>
   </si>
   <si>
     <t xml:space="preserve">5.72711086273193</t>
@@ -1202,55 +1202,55 @@
     <t xml:space="preserve">5.57590103149414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52864742279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42941522598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50502061843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61370372772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63733005523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04371023178101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98700618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01535701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89722347259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81689357757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87359762191772</t>
+    <t xml:space="preserve">5.52864694595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42941474914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50502014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61370420455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63733100891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04370927810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98700571060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01535749435425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89722394943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81689262390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87359714508057</t>
   </si>
   <si>
     <t xml:space="preserve">5.86414670944214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9066743850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96810388565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01550722122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02027034759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99169301986694</t>
+    <t xml:space="preserve">5.90667390823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96810436248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01550674438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02027082443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99169254302979</t>
   </si>
   <si>
     <t xml:space="preserve">6.08218765258789</t>
@@ -1265,31 +1265,31 @@
     <t xml:space="preserve">6.08695030212402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07266283035278</t>
+    <t xml:space="preserve">6.07266187667847</t>
   </si>
   <si>
     <t xml:space="preserve">6.16315650939941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27270269393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2536506652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13934230804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2917537689209</t>
+    <t xml:space="preserve">6.27270221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25365114212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13934183120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29175424575806</t>
   </si>
   <si>
     <t xml:space="preserve">6.38701152801514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52513456344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59657764434814</t>
+    <t xml:space="preserve">6.52513408660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59657716751099</t>
   </si>
   <si>
     <t xml:space="preserve">6.69183588027954</t>
@@ -1298,40 +1298,40 @@
     <t xml:space="preserve">6.69659852981567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62039184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57276391983032</t>
+    <t xml:space="preserve">6.62039232254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57276344299316</t>
   </si>
   <si>
     <t xml:space="preserve">6.5060830116272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58228969573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65373277664185</t>
+    <t xml:space="preserve">6.58228921890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65373229980469</t>
   </si>
   <si>
     <t xml:space="preserve">6.71088647842407</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77280378341675</t>
+    <t xml:space="preserve">6.82519483566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77280426025391</t>
   </si>
   <si>
     <t xml:space="preserve">6.82995891571045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0252366065979</t>
+    <t xml:space="preserve">7.02523612976074</t>
   </si>
   <si>
     <t xml:space="preserve">6.92521619796753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92045307159424</t>
+    <t xml:space="preserve">6.9204535484314</t>
   </si>
   <si>
     <t xml:space="preserve">7.01094818115234</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">6.96808242797852</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91092729568481</t>
+    <t xml:space="preserve">6.91092681884766</t>
   </si>
   <si>
     <t xml:space="preserve">7.01571083068848</t>
@@ -1349,10 +1349,10 @@
     <t xml:space="preserve">7.04905080795288</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09667921066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17764806747437</t>
+    <t xml:space="preserve">7.0966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17764854431152</t>
   </si>
   <si>
     <t xml:space="preserve">7.28243112564087</t>
@@ -1361,31 +1361,31 @@
     <t xml:space="preserve">7.22051429748535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23956489562988</t>
+    <t xml:space="preserve">7.2395658493042</t>
   </si>
   <si>
     <t xml:space="preserve">7.27766847610474</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12525653839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94903087615967</t>
+    <t xml:space="preserve">7.12525701522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94903135299683</t>
   </si>
   <si>
     <t xml:space="preserve">6.86806154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00142097473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00618553161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06333923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760677337646</t>
+    <t xml:space="preserve">7.0014214515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00618505477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0633397102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760725021362</t>
   </si>
   <si>
     <t xml:space="preserve">6.99189615249634</t>
@@ -1394,25 +1394,25 @@
     <t xml:space="preserve">7.03952503204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02047395706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07762765884399</t>
+    <t xml:space="preserve">7.02047348022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07762813568115</t>
   </si>
   <si>
     <t xml:space="preserve">7.18717384338379</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21098804473877</t>
+    <t xml:space="preserve">7.21098852157593</t>
   </si>
   <si>
     <t xml:space="preserve">7.41579151153564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29671955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26338005065918</t>
+    <t xml:space="preserve">7.29672002792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26338052749634</t>
   </si>
   <si>
     <t xml:space="preserve">7.24432802200317</t>
@@ -1421,25 +1421,25 @@
     <t xml:space="preserve">7.27290630340576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30624580383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1824107170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2538537979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0585765838623</t>
+    <t xml:space="preserve">7.30624628067017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18241167068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25385332107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05857610702515</t>
   </si>
   <si>
     <t xml:space="preserve">7.10620498657227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14907121658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1681227684021</t>
+    <t xml:space="preserve">7.14907169342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16812229156494</t>
   </si>
   <si>
     <t xml:space="preserve">6.90140199661255</t>
@@ -1448,40 +1448,40 @@
     <t xml:space="preserve">6.94426727294922</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06810235977173</t>
+    <t xml:space="preserve">7.06810188293457</t>
   </si>
   <si>
     <t xml:space="preserve">6.98713302612305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13002014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87758731842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70612382888794</t>
+    <t xml:space="preserve">7.1300196647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87758684158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7061243057251</t>
   </si>
   <si>
     <t xml:space="preserve">6.63944339752197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65849494934082</t>
+    <t xml:space="preserve">6.65849542617798</t>
   </si>
   <si>
     <t xml:space="preserve">6.32985687255859</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19649648666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11552810668945</t>
+    <t xml:space="preserve">6.19649696350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11552858352661</t>
   </si>
   <si>
     <t xml:space="preserve">6.04884719848633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21554851531982</t>
+    <t xml:space="preserve">6.21554803848267</t>
   </si>
   <si>
     <t xml:space="preserve">6.31556844711304</t>
@@ -1490,91 +1490,91 @@
     <t xml:space="preserve">6.33461999893188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34414529800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12505388259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15363073348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30604314804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35367202758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47274255752563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46798038482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42987680435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52989816665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76804161071777</t>
+    <t xml:space="preserve">6.34414577484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12505340576172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15363025665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30604219436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35367107391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47274303436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4679799079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42987823486328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52989721298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76804113388062</t>
   </si>
   <si>
     <t xml:space="preserve">7.08239078521729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11096858978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12049293518066</t>
+    <t xml:space="preserve">7.11096811294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12049341201782</t>
   </si>
   <si>
     <t xml:space="preserve">7.32529735565186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31577157974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11573076248169</t>
+    <t xml:space="preserve">7.31577062606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11573028564453</t>
   </si>
   <si>
     <t xml:space="preserve">7.03476238250732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15383434295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04428815841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02999973297119</t>
+    <t xml:space="preserve">7.15383386611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04428768157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02999925613403</t>
   </si>
   <si>
     <t xml:space="preserve">7.17288541793823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36340045928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14430809020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20622539520264</t>
+    <t xml:space="preserve">7.36339998245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14430856704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20622587203979</t>
   </si>
   <si>
     <t xml:space="preserve">7.32053470611572</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09191656112671</t>
+    <t xml:space="preserve">7.09191703796387</t>
   </si>
   <si>
     <t xml:space="preserve">6.98237037658691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44913244247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3824520111084</t>
+    <t xml:space="preserve">7.44913196563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38245105743408</t>
   </si>
   <si>
     <t xml:space="preserve">7.33006000518799</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">7.21575117111206</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33958625793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35387468338013</t>
+    <t xml:space="preserve">7.33958578109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35387516021729</t>
   </si>
   <si>
     <t xml:space="preserve">7.55391502380371</t>
@@ -1598,25 +1598,25 @@
     <t xml:space="preserve">7.46342086791992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49199676513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44436883926392</t>
+    <t xml:space="preserve">7.49199771881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44436979293823</t>
   </si>
   <si>
     <t xml:space="preserve">7.42055463790894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62535810470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53010082244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47294569015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48723459243774</t>
+    <t xml:space="preserve">7.62535762786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53010177612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47294616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4872350692749</t>
   </si>
   <si>
     <t xml:space="preserve">7.46818351745605</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">7.49676036834717</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51581239700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6110692024231</t>
+    <t xml:space="preserve">7.51581192016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61106967926025</t>
   </si>
   <si>
     <t xml:space="preserve">7.56344079971313</t>
@@ -1637,82 +1637,82 @@
     <t xml:space="preserve">7.64440965652466</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73490428924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80634689331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86826467514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85873889923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88731527328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92542028427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95399618148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83492469787598</t>
+    <t xml:space="preserve">7.73490476608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80634641647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86826515197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85873985290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88731479644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9254207611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95399713516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83492565155029</t>
   </si>
   <si>
     <t xml:space="preserve">7.98733758926392</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01115036010742</t>
+    <t xml:space="preserve">8.01115131378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.06354236602783</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53486347198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52057552337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54438972473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62059497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63964700698853</t>
+    <t xml:space="preserve">7.53486394882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52057504653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54438877105713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62059593200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63964748382568</t>
   </si>
   <si>
     <t xml:space="preserve">7.77777004241943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76824378967285</t>
+    <t xml:space="preserve">7.76824331283569</t>
   </si>
   <si>
     <t xml:space="preserve">7.90636825561523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03496551513672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00638675689697</t>
+    <t xml:space="preserve">8.0349645614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00638771057129</t>
   </si>
   <si>
     <t xml:space="preserve">8.04448986053467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06830596923828</t>
+    <t xml:space="preserve">8.06830501556396</t>
   </si>
   <si>
     <t xml:space="preserve">8.2016658782959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32550048828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44457340240479</t>
+    <t xml:space="preserve">8.32549953460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44457149505615</t>
   </si>
   <si>
     <t xml:space="preserve">8.33978939056396</t>
@@ -1724,13 +1724,13 @@
     <t xml:space="preserve">8.33502578735352</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27787113189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23500633239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25882053375244</t>
+    <t xml:space="preserve">8.27787208557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23500728607178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25881958007812</t>
   </si>
   <si>
     <t xml:space="preserve">8.26358318328857</t>
@@ -1745,43 +1745,43 @@
     <t xml:space="preserve">8.36836719512939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.354079246521</t>
+    <t xml:space="preserve">8.35407829284668</t>
   </si>
   <si>
     <t xml:space="preserve">8.37789154052734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28739643096924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2111930847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22071838378906</t>
+    <t xml:space="preserve">8.28739738464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21119213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22071743011475</t>
   </si>
   <si>
     <t xml:space="preserve">8.43150615692139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.445876121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56085205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5129451751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48899269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60875797271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44108581542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49857234954834</t>
+    <t xml:space="preserve">8.44587516784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56085300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51294612884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48899173736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60875701904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.441086769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49857330322266</t>
   </si>
   <si>
     <t xml:space="preserve">8.48420143127441</t>
@@ -1790,10 +1790,10 @@
     <t xml:space="preserve">8.67103672027588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8147554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74289703369141</t>
+    <t xml:space="preserve">8.81475448608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74289512634277</t>
   </si>
   <si>
     <t xml:space="preserve">8.83391761779785</t>
@@ -1802,25 +1802,25 @@
     <t xml:space="preserve">8.77643013000488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70936012268066</t>
+    <t xml:space="preserve">8.70936107635498</t>
   </si>
   <si>
     <t xml:space="preserve">8.6854076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70457077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78122043609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80996322631836</t>
+    <t xml:space="preserve">8.70456981658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78122138977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80996513366699</t>
   </si>
   <si>
     <t xml:space="preserve">8.77163982391357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65187358856201</t>
+    <t xml:space="preserve">8.65187454223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.53689861297607</t>
@@ -1829,55 +1829,55 @@
     <t xml:space="preserve">8.37880802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3740177154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40755176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4123420715332</t>
+    <t xml:space="preserve">8.37401676177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40755081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41234302520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.32611083984375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45545768737793</t>
+    <t xml:space="preserve">8.45545864105225</t>
   </si>
   <si>
     <t xml:space="preserve">8.41713428497314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39317989349365</t>
+    <t xml:space="preserve">8.39318084716797</t>
   </si>
   <si>
     <t xml:space="preserve">8.54648017883301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58959579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27341461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25425148010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35485553741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4746208190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42192268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36922645568848</t>
+    <t xml:space="preserve">8.58959674835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27341556549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25425243377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35485458374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47461986541748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42192363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36922550201416</t>
   </si>
   <si>
     <t xml:space="preserve">8.31653022766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29736709594727</t>
+    <t xml:space="preserve">8.29736804962158</t>
   </si>
   <si>
     <t xml:space="preserve">8.28299617767334</t>
@@ -1889,16 +1889,16 @@
     <t xml:space="preserve">8.2015552520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16323089599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24946117401123</t>
+    <t xml:space="preserve">8.16322994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24946022033691</t>
   </si>
   <si>
     <t xml:space="preserve">8.18239307403564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17280960083008</t>
+    <t xml:space="preserve">8.17281055450439</t>
   </si>
   <si>
     <t xml:space="preserve">8.09616088867188</t>
@@ -1907,10 +1907,10 @@
     <t xml:space="preserve">8.14885807037354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06741619110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03867244720459</t>
+    <t xml:space="preserve">8.06741714477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03867340087891</t>
   </si>
   <si>
     <t xml:space="preserve">7.97160577774048</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">7.78956127166748</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62188863754272</t>
+    <t xml:space="preserve">7.62188816070557</t>
   </si>
   <si>
     <t xml:space="preserve">7.61709833145142</t>
@@ -1943,13 +1943,13 @@
     <t xml:space="preserve">7.51170444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65542268753052</t>
+    <t xml:space="preserve">7.65542316436768</t>
   </si>
   <si>
     <t xml:space="preserve">7.59793567657471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90932607650757</t>
+    <t xml:space="preserve">7.90932559967041</t>
   </si>
   <si>
     <t xml:space="preserve">7.95244264602661</t>
@@ -1958,13 +1958,13 @@
     <t xml:space="preserve">7.82309532165527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88058280944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10574245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2063455581665</t>
+    <t xml:space="preserve">7.88058376312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10574150085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20634460449219</t>
   </si>
   <si>
     <t xml:space="preserve">8.16802024841309</t>
@@ -1973,46 +1973,46 @@
     <t xml:space="preserve">8.26383304595947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34527397155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29257583618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12011528015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03388404846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99555969238281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80872344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91411685943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88537263870239</t>
+    <t xml:space="preserve">8.3452730178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29257678985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12011432647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0338830947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99555921554565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80872297286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91411733627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88537216186523</t>
   </si>
   <si>
     <t xml:space="preserve">7.82788515090942</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84704828262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00034809112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89974451065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90453577041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94286155700684</t>
+    <t xml:space="preserve">7.84704780578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0003490447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89974498748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90453672409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94286060333252</t>
   </si>
   <si>
     <t xml:space="preserve">7.71770191192627</t>
@@ -2030,43 +2030,43 @@
     <t xml:space="preserve">8.12969589233398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13448619842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00993061065674</t>
+    <t xml:space="preserve">8.13448715209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00992965698242</t>
   </si>
   <si>
     <t xml:space="preserve">7.93327856063843</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75123643875122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.578773021698</t>
+    <t xml:space="preserve">7.75123596191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57877349853516</t>
   </si>
   <si>
     <t xml:space="preserve">7.64105129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69374799728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83746814727783</t>
+    <t xml:space="preserve">7.69374752044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83746671676636</t>
   </si>
   <si>
     <t xml:space="preserve">7.81351327896118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87100028991699</t>
+    <t xml:space="preserve">7.87100172042847</t>
   </si>
   <si>
     <t xml:space="preserve">7.87579345703125</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92369842529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89495468139648</t>
+    <t xml:space="preserve">7.92369937896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89495420455933</t>
   </si>
   <si>
     <t xml:space="preserve">7.8518385887146</t>
@@ -2075,52 +2075,52 @@
     <t xml:space="preserve">7.86621141433716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9859766960144</t>
+    <t xml:space="preserve">7.98597526550293</t>
   </si>
   <si>
     <t xml:space="preserve">7.9668140411377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92848920822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11053276062012</t>
+    <t xml:space="preserve">7.92848968505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1105318069458</t>
   </si>
   <si>
     <t xml:space="preserve">8.04825401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93807077407837</t>
+    <t xml:space="preserve">7.93806982040405</t>
   </si>
   <si>
     <t xml:space="preserve">7.77997970581055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81830501556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84225702285767</t>
+    <t xml:space="preserve">7.81830358505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84225749969482</t>
   </si>
   <si>
     <t xml:space="preserve">7.79435157775879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7991418838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94765186309814</t>
+    <t xml:space="preserve">7.79914236068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94765090942383</t>
   </si>
   <si>
     <t xml:space="preserve">7.91890859603882</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71291065216064</t>
+    <t xml:space="preserve">7.7129111289978</t>
   </si>
   <si>
     <t xml:space="preserve">7.77518892288208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86142015457153</t>
+    <t xml:space="preserve">7.86142063140869</t>
   </si>
   <si>
     <t xml:space="preserve">8.07699871063232</t>
@@ -2129,40 +2129,40 @@
     <t xml:space="preserve">8.21592617034912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2686243057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33569145202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4506664276123</t>
+    <t xml:space="preserve">8.26862335205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33569240570068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">8.36443614959717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47941207885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55127048492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59438610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66624641418457</t>
+    <t xml:space="preserve">8.47941112518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55127143859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59438705444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66624546051025</t>
   </si>
   <si>
     <t xml:space="preserve">8.64229393005371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69019889831543</t>
+    <t xml:space="preserve">8.69019985198975</t>
   </si>
   <si>
     <t xml:space="preserve">8.58480453491211</t>
   </si>
   <si>
-    <t xml:space="preserve">8.19197463989258</t>
+    <t xml:space="preserve">8.19197368621826</t>
   </si>
   <si>
     <t xml:space="preserve">7.74165439605713</t>
@@ -2171,67 +2171,67 @@
     <t xml:space="preserve">7.70332956314087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7847695350647</t>
+    <t xml:space="preserve">7.78477048873901</t>
   </si>
   <si>
     <t xml:space="preserve">7.44463539123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22426652908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17636013031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30091714859009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36319541931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33924150466919</t>
+    <t xml:space="preserve">7.22426700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1763596534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30091667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36319494247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33924198150635</t>
   </si>
   <si>
     <t xml:space="preserve">7.09491968154907</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6972975730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36195421218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3367600440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54754734039307</t>
+    <t xml:space="preserve">6.69729804992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36195373535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33675956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54754686355591</t>
   </si>
   <si>
     <t xml:space="preserve">5.37987470626831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30322456359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86851930618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45776557922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08409690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03619146347046</t>
+    <t xml:space="preserve">5.30322504043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8685188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45776510238647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08409738540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03619194030762</t>
   </si>
   <si>
     <t xml:space="preserve">6.29967498779297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76915645599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84101629257202</t>
+    <t xml:space="preserve">6.76915693283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84101581573486</t>
   </si>
   <si>
     <t xml:space="preserve">6.53441667556763</t>
@@ -2240,13 +2240,13 @@
     <t xml:space="preserve">6.3715353012085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27572202682495</t>
+    <t xml:space="preserve">6.27572250366211</t>
   </si>
   <si>
     <t xml:space="preserve">6.02852582931519</t>
   </si>
   <si>
-    <t xml:space="preserve">6.110924243927</t>
+    <t xml:space="preserve">6.11092472076416</t>
   </si>
   <si>
     <t xml:space="preserve">5.85606288909912</t>
@@ -2255,7 +2255,7 @@
     <t xml:space="preserve">6.45201778411865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38111591339111</t>
+    <t xml:space="preserve">6.38111639022827</t>
   </si>
   <si>
     <t xml:space="preserve">6.32171249389648</t>
@@ -2264,25 +2264,25 @@
     <t xml:space="preserve">6.35237264633179</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40986013412476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4079442024231</t>
+    <t xml:space="preserve">6.40986061096191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40794372558594</t>
   </si>
   <si>
     <t xml:space="preserve">6.47309589385986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65897226333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49962091445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44746971130371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4300856590271</t>
+    <t xml:space="preserve">6.65897274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49962043762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44746923446655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43008518218994</t>
   </si>
   <si>
     <t xml:space="preserve">6.39338684082031</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">6.44360637664795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5961971282959</t>
+    <t xml:space="preserve">6.59619760513306</t>
   </si>
   <si>
     <t xml:space="preserve">6.61551332473755</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79321384429932</t>
+    <t xml:space="preserve">6.79321432113647</t>
   </si>
   <si>
     <t xml:space="preserve">6.82798194885254</t>
@@ -2321,7 +2321,7 @@
     <t xml:space="preserve">6.95932674407959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08487701416016</t>
+    <t xml:space="preserve">7.08487606048584</t>
   </si>
   <si>
     <t xml:space="preserve">6.93807888031006</t>
@@ -2330,13 +2330,13 @@
     <t xml:space="preserve">6.70629501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66766405105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94001197814941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51120948791504</t>
+    <t xml:space="preserve">6.66766452789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94001150131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5112099647522</t>
   </si>
   <si>
     <t xml:space="preserve">6.67345857620239</t>
@@ -2351,10 +2351,10 @@
     <t xml:space="preserve">6.67732191085815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72947359085083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71208953857422</t>
+    <t xml:space="preserve">6.72947406768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71209001541138</t>
   </si>
   <si>
     <t xml:space="preserve">7.14668560028076</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">7.05010890960693</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94387435913086</t>
+    <t xml:space="preserve">6.9438738822937</t>
   </si>
   <si>
     <t xml:space="preserve">7.1119179725647</t>
@@ -2372,40 +2372,40 @@
     <t xml:space="preserve">7.09839725494385</t>
   </si>
   <si>
-    <t xml:space="preserve">7.142822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14475440979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1389594078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17758989334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05976676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20463228225708</t>
+    <t xml:space="preserve">7.14282274246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14475393295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13895988464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17759037017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05976581573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20463180541992</t>
   </si>
   <si>
     <t xml:space="preserve">7.06942415237427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31279754638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33018112182617</t>
+    <t xml:space="preserve">7.31279706954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33018159866333</t>
   </si>
   <si>
     <t xml:space="preserve">7.38619613647461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44800472259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44027948379517</t>
+    <t xml:space="preserve">7.44800567626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44027900695801</t>
   </si>
   <si>
     <t xml:space="preserve">7.58128118515015</t>
@@ -2417,10 +2417,10 @@
     <t xml:space="preserve">7.26837253570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24326276779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34370279312134</t>
+    <t xml:space="preserve">7.24326229095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34370231628418</t>
   </si>
   <si>
     <t xml:space="preserve">7.54844522476196</t>
@@ -2429,19 +2429,19 @@
     <t xml:space="preserve">7.45380020141602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62667274475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67013120651245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70683097839355</t>
+    <t xml:space="preserve">7.62667226791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67013168334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70683145523071</t>
   </si>
   <si>
     <t xml:space="preserve">7.84203910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86425113677979</t>
+    <t xml:space="preserve">7.86425161361694</t>
   </si>
   <si>
     <t xml:space="preserve">7.81499671936035</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">7.75029039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92412948608398</t>
+    <t xml:space="preserve">7.92412900924683</t>
   </si>
   <si>
     <t xml:space="preserve">7.91350650787354</t>
@@ -2459,19 +2459,19 @@
     <t xml:space="preserve">7.82851886749268</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89322471618652</t>
+    <t xml:space="preserve">7.89322519302368</t>
   </si>
   <si>
     <t xml:space="preserve">7.98497247695923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87294387817383</t>
+    <t xml:space="preserve">7.87294340133667</t>
   </si>
   <si>
     <t xml:space="preserve">8.02649974822998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88549757003784</t>
+    <t xml:space="preserve">7.885498046875</t>
   </si>
   <si>
     <t xml:space="preserve">7.83817577362061</t>
@@ -2480,10 +2480,10 @@
     <t xml:space="preserve">8.2631139755249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42729377746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21965503692627</t>
+    <t xml:space="preserve">8.4272928237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21965408325195</t>
   </si>
   <si>
     <t xml:space="preserve">8.22158432006836</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">8.29594898223877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1365966796875</t>
+    <t xml:space="preserve">8.13659763336182</t>
   </si>
   <si>
     <t xml:space="preserve">8.20806407928467</t>
@@ -2513,34 +2513,34 @@
     <t xml:space="preserve">8.43598556518555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39735507965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2775993347168</t>
+    <t xml:space="preserve">8.39735412597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27760028839111</t>
   </si>
   <si>
     <t xml:space="preserve">8.30753898620605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24283123016357</t>
+    <t xml:space="preserve">8.24283313751221</t>
   </si>
   <si>
     <t xml:space="preserve">8.34423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.228346824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39059448242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34327125549316</t>
+    <t xml:space="preserve">8.22834587097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39059352874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34327220916748</t>
   </si>
   <si>
     <t xml:space="preserve">8.43405437469482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31043529510498</t>
+    <t xml:space="preserve">8.3104362487793</t>
   </si>
   <si>
     <t xml:space="preserve">8.18102264404297</t>
@@ -2552,31 +2552,31 @@
     <t xml:space="preserve">8.48330879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77110862731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58664703369141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4794454574585</t>
+    <t xml:space="preserve">8.77110767364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58664608001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47944641113281</t>
   </si>
   <si>
     <t xml:space="preserve">8.71799087524414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65907955169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75565528869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71412754058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82132816314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94784355163574</t>
+    <t xml:space="preserve">8.65907859802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75565624237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71412658691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82132720947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94784450531006</t>
   </si>
   <si>
     <t xml:space="preserve">9.01448059082031</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">9.06083869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85319805145264</t>
+    <t xml:space="preserve">8.85319709777832</t>
   </si>
   <si>
     <t xml:space="preserve">8.94011688232422</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">9.01641368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05117988586426</t>
+    <t xml:space="preserve">9.05118083953857</t>
   </si>
   <si>
     <t xml:space="preserve">8.80587577819824</t>
@@ -2618,7 +2618,7 @@
     <t xml:space="preserve">9.04635143280029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02896690368652</t>
+    <t xml:space="preserve">9.02896785736084</t>
   </si>
   <si>
     <t xml:space="preserve">8.95460414886475</t>
@@ -2630,28 +2630,28 @@
     <t xml:space="preserve">8.97198867797852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04442119598389</t>
+    <t xml:space="preserve">9.04442024230957</t>
   </si>
   <si>
     <t xml:space="preserve">9.21342945098877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23854064941406</t>
+    <t xml:space="preserve">9.23853969573975</t>
   </si>
   <si>
     <t xml:space="preserve">9.1747989654541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06180381774902</t>
+    <t xml:space="preserve">9.06180477142334</t>
   </si>
   <si>
     <t xml:space="preserve">9.12554454803467</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03186702728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07629108428955</t>
+    <t xml:space="preserve">9.0318660736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07629013061523</t>
   </si>
   <si>
     <t xml:space="preserve">8.80008125305176</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">8.74020290374756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88893127441406</t>
+    <t xml:space="preserve">8.88893222808838</t>
   </si>
   <si>
     <t xml:space="preserve">8.66294193267822</t>
@@ -2678,16 +2678,16 @@
     <t xml:space="preserve">8.65714645385742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035022735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59727001190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76724433898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8908634185791</t>
+    <t xml:space="preserve">8.51035118103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59726905822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76724529266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89086437225342</t>
   </si>
   <si>
     <t xml:space="preserve">8.96426105499268</t>
@@ -2714,13 +2714,13 @@
     <t xml:space="preserve">9.4316930770874</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25012969970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13230609893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22501850128174</t>
+    <t xml:space="preserve">9.25012874603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13230514526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22501945495605</t>
   </si>
   <si>
     <t xml:space="preserve">9.06856536865234</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">9.22695064544678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36215782165527</t>
+    <t xml:space="preserve">9.36215877532959</t>
   </si>
   <si>
     <t xml:space="preserve">9.12650966644287</t>
@@ -2744,31 +2744,31 @@
     <t xml:space="preserve">9.14775657653809</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13037395477295</t>
+    <t xml:space="preserve">9.13037490844727</t>
   </si>
   <si>
     <t xml:space="preserve">9.15934658050537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12264633178711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0048246383667</t>
+    <t xml:space="preserve">9.12264728546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00482368469238</t>
   </si>
   <si>
     <t xml:space="preserve">9.13616847991943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05890655517578</t>
+    <t xml:space="preserve">9.05890560150146</t>
   </si>
   <si>
     <t xml:space="preserve">9.04538631439209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83677959442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87347793579102</t>
+    <t xml:space="preserve">8.83677864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87347888946533</t>
   </si>
   <si>
     <t xml:space="preserve">8.95267200469971</t>
@@ -2786,16 +2786,16 @@
     <t xml:space="preserve">8.96619415283203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13809967041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02027702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90438461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66487407684326</t>
+    <t xml:space="preserve">9.13809871673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02027606964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90438365936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66487312316895</t>
   </si>
   <si>
     <t xml:space="preserve">8.59340572357178</t>
@@ -2804,16 +2804,16 @@
     <t xml:space="preserve">8.54125499725342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5528450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42150020599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38093757629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47365093231201</t>
+    <t xml:space="preserve">8.55284404754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42149925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38093852996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47365188598633</t>
   </si>
   <si>
     <t xml:space="preserve">8.42343139648438</t>
@@ -2825,19 +2825,19 @@
     <t xml:space="preserve">8.5470495223999</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4929666519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58568096160889</t>
+    <t xml:space="preserve">8.49296569824219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5856819152832</t>
   </si>
   <si>
     <t xml:space="preserve">8.51228141784668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50648593902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63590145111084</t>
+    <t xml:space="preserve">8.5064868927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63590240478516</t>
   </si>
   <si>
     <t xml:space="preserve">8.59533786773682</t>
@@ -2852,7 +2852,7 @@
     <t xml:space="preserve">8.57795333862305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82712364196777</t>
+    <t xml:space="preserve">8.82712268829346</t>
   </si>
   <si>
     <t xml:space="preserve">8.86768436431885</t>
@@ -2864,34 +2864,34 @@
     <t xml:space="preserve">9.33704853057861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3177318572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40271949768066</t>
+    <t xml:space="preserve">9.31773281097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4027214050293</t>
   </si>
   <si>
     <t xml:space="preserve">9.34477424621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38533687591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44521427154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58235359191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42976093292236</t>
+    <t xml:space="preserve">9.38533782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44521331787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58235263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42976188659668</t>
   </si>
   <si>
     <t xml:space="preserve">9.44135189056396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35249996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20570373535156</t>
+    <t xml:space="preserve">9.35250091552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20570278167725</t>
   </si>
   <si>
     <t xml:space="preserve">9.28875923156738</t>
@@ -2900,40 +2900,40 @@
     <t xml:space="preserve">9.3158016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34091091156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05697536468506</t>
+    <t xml:space="preserve">9.34091186523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05697631835938</t>
   </si>
   <si>
     <t xml:space="preserve">9.19218254089355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16320896148682</t>
+    <t xml:space="preserve">9.16320991516113</t>
   </si>
   <si>
     <t xml:space="preserve">9.04924869537354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26751136779785</t>
+    <t xml:space="preserve">9.26751327514648</t>
   </si>
   <si>
     <t xml:space="preserve">9.16900444030762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36795234680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52440738677979</t>
+    <t xml:space="preserve">9.36795330047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5244083404541</t>
   </si>
   <si>
     <t xml:space="preserve">9.76391696929932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48964023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46839237213135</t>
+    <t xml:space="preserve">9.48963928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46839332580566</t>
   </si>
   <si>
     <t xml:space="preserve">9.38726806640625</t>
@@ -2942,25 +2942,25 @@
     <t xml:space="preserve">9.42589855194092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.364089012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2829647064209</t>
+    <t xml:space="preserve">9.36408805847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28296375274658</t>
   </si>
   <si>
     <t xml:space="preserve">9.25978755950928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24240303039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26364898681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28682899475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35056972503662</t>
+    <t xml:space="preserve">9.24240207672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26364994049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28682804107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3505687713623</t>
   </si>
   <si>
     <t xml:space="preserve">9.23081302642822</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">9.39885711669922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32932090759277</t>
+    <t xml:space="preserve">9.32932186126709</t>
   </si>
   <si>
     <t xml:space="preserve">9.46452903747559</t>
@@ -2981,13 +2981,13 @@
     <t xml:space="preserve">9.63836765289307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47225475311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56496906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64416217803955</t>
+    <t xml:space="preserve">9.47225570678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56497001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64416122436523</t>
   </si>
   <si>
     <t xml:space="preserve">9.76943683624268</t>
@@ -3014,16 +3014,16 @@
     <t xml:space="preserve">9.52860069274902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63348007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88111591339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0025043487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0947608947754</t>
+    <t xml:space="preserve">9.63347911834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8811149597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0025053024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0947618484497</t>
   </si>
   <si>
     <t xml:space="preserve">9.98308181762695</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">9.94423770904541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7742919921875</t>
+    <t xml:space="preserve">9.77429103851318</t>
   </si>
   <si>
     <t xml:space="preserve">9.86654758453369</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">9.79371356964111</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656261444092</t>
+    <t xml:space="preserve">10.0656270980835</t>
   </si>
   <si>
     <t xml:space="preserve">10.1675939559937</t>
@@ -3062,13 +3062,13 @@
     <t xml:space="preserve">10.2355728149414</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2549962997437</t>
+    <t xml:space="preserve">10.2549953460693</t>
   </si>
   <si>
     <t xml:space="preserve">10.1870164871216</t>
   </si>
   <si>
-    <t xml:space="preserve">10.14817237854</t>
+    <t xml:space="preserve">10.1481714248657</t>
   </si>
   <si>
     <t xml:space="preserve">10.2307176589966</t>
@@ -3083,10 +3083,10 @@
     <t xml:space="preserve">10.3132610321045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3909521102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5754632949829</t>
+    <t xml:space="preserve">10.3909511566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5754642486572</t>
   </si>
   <si>
     <t xml:space="preserve">10.6337308883667</t>
@@ -3098,10 +3098,10 @@
     <t xml:space="preserve">10.8182430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8328094482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8230991363525</t>
+    <t xml:space="preserve">10.8328084945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8230981826782</t>
   </si>
   <si>
     <t xml:space="preserve">10.8570871353149</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">10.9104986190796</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8910760879517</t>
+    <t xml:space="preserve">10.891077041626</t>
   </si>
   <si>
     <t xml:space="preserve">10.997899055481</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">10.978476524353</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8667993545532</t>
+    <t xml:space="preserve">10.8667984008789</t>
   </si>
   <si>
     <t xml:space="preserve">10.6531524658203</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">11.4009122848511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4688911437988</t>
+    <t xml:space="preserve">11.4688920974731</t>
   </si>
   <si>
     <t xml:space="preserve">11.4931688308716</t>
@@ -3200,7 +3200,7 @@
     <t xml:space="preserve">11.5660028457642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6097030639648</t>
+    <t xml:space="preserve">11.6097040176392</t>
   </si>
   <si>
     <t xml:space="preserve">11.721381187439</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">11.745659828186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6922483444214</t>
+    <t xml:space="preserve">11.6922473907471</t>
   </si>
   <si>
     <t xml:space="preserve">11.6825370788574</t>
@@ -3227,19 +3227,19 @@
     <t xml:space="preserve">11.4834575653076</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4251909255981</t>
+    <t xml:space="preserve">11.4251918792725</t>
   </si>
   <si>
     <t xml:space="preserve">11.3814907073975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3669233322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.332935333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3717784881592</t>
+    <t xml:space="preserve">11.36692237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3329343795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3717794418335</t>
   </si>
   <si>
     <t xml:space="preserve">11.5902814865112</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">11.5757141113281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5125904083252</t>
+    <t xml:space="preserve">11.5125913619995</t>
   </si>
   <si>
     <t xml:space="preserve">11.410623550415</t>
@@ -3266,7 +3266,7 @@
     <t xml:space="preserve">11.7068157196045</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9495944976807</t>
+    <t xml:space="preserve">11.949595451355</t>
   </si>
   <si>
     <t xml:space="preserve">11.9301719665527</t>
@@ -3275,25 +3275,25 @@
     <t xml:space="preserve">11.7942171096802</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7602262496948</t>
+    <t xml:space="preserve">11.7602252960205</t>
   </si>
   <si>
     <t xml:space="preserve">11.8087825775146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8282060623169</t>
+    <t xml:space="preserve">11.8282051086426</t>
   </si>
   <si>
     <t xml:space="preserve">11.7505149841309</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9253158569336</t>
+    <t xml:space="preserve">11.9253168106079</t>
   </si>
   <si>
     <t xml:space="preserve">12.0175714492798</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0564165115356</t>
+    <t xml:space="preserve">12.05641746521</t>
   </si>
   <si>
     <t xml:space="preserve">12.036994934082</t>
@@ -3329,16 +3329,16 @@
     <t xml:space="preserve">12.012716293335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0758399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1729507446289</t>
+    <t xml:space="preserve">12.0758390426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1729497909546</t>
   </si>
   <si>
     <t xml:space="preserve">12.3331851959229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3137645721436</t>
+    <t xml:space="preserve">12.3137636184692</t>
   </si>
   <si>
     <t xml:space="preserve">12.4205856323242</t>
@@ -3356,10 +3356,10 @@
     <t xml:space="preserve">12.4157295227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5468301773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6439428329468</t>
+    <t xml:space="preserve">12.5468311309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6439437866211</t>
   </si>
   <si>
     <t xml:space="preserve">12.7750434875488</t>
@@ -3377,7 +3377,7 @@
     <t xml:space="preserve">13.0760898590088</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5808200836182</t>
+    <t xml:space="preserve">12.5808210372925</t>
   </si>
   <si>
     <t xml:space="preserve">12.5953874588013</t>
@@ -3395,7 +3395,7 @@
     <t xml:space="preserve">12.4982748031616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4739971160889</t>
+    <t xml:space="preserve">12.4739980697632</t>
   </si>
   <si>
     <t xml:space="preserve">12.3428964614868</t>
@@ -3410,7 +3410,7 @@
     <t xml:space="preserve">12.6099529266357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5856761932373</t>
+    <t xml:space="preserve">12.585675239563</t>
   </si>
   <si>
     <t xml:space="preserve">12.3768854141235</t>
@@ -3422,37 +3422,37 @@
     <t xml:space="preserve">12.284628868103</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2797746658325</t>
+    <t xml:space="preserve">12.2797737121582</t>
   </si>
   <si>
     <t xml:space="preserve">12.2020835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4400072097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3720293045044</t>
+    <t xml:space="preserve">12.4400081634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3720302581787</t>
   </si>
   <si>
     <t xml:space="preserve">12.435152053833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3963079452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4060173034668</t>
+    <t xml:space="preserve">12.3963088989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4060182571411</t>
   </si>
   <si>
     <t xml:space="preserve">11.7553701400757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6728267669678</t>
+    <t xml:space="preserve">11.6728258132935</t>
   </si>
   <si>
     <t xml:space="preserve">11.6388359069824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4397563934326</t>
+    <t xml:space="preserve">11.4397573471069</t>
   </si>
   <si>
     <t xml:space="preserve">11.1532783508301</t>
@@ -3464,7 +3464,7 @@
     <t xml:space="preserve">11.0804443359375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0658779144287</t>
+    <t xml:space="preserve">11.065878868103</t>
   </si>
   <si>
     <t xml:space="preserve">10.6968536376953</t>
@@ -3473,7 +3473,7 @@
     <t xml:space="preserve">10.6434421539307</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6191644668579</t>
+    <t xml:space="preserve">10.6191654205322</t>
   </si>
   <si>
     <t xml:space="preserve">10.5171957015991</t>
@@ -3494,7 +3494,7 @@
     <t xml:space="preserve">10.5269079208374</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4492177963257</t>
+    <t xml:space="preserve">10.44921875</t>
   </si>
   <si>
     <t xml:space="preserve">10.5317630767822</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">10.1821613311768</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1918716430664</t>
+    <t xml:space="preserve">10.1918706893921</t>
   </si>
   <si>
     <t xml:space="preserve">10.264705657959</t>
@@ -3521,10 +3521,10 @@
     <t xml:space="preserve">9.9588041305542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02556133270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18870830535889</t>
+    <t xml:space="preserve">9.02556037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18870735168457</t>
   </si>
   <si>
     <t xml:space="preserve">9.4664478302002</t>
@@ -3539,19 +3539,19 @@
     <t xml:space="preserve">9.06246280670166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84299182891846</t>
+    <t xml:space="preserve">8.84299087524414</t>
   </si>
   <si>
     <t xml:space="preserve">8.83910655975342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5438871383667</t>
+    <t xml:space="preserve">8.54388618469238</t>
   </si>
   <si>
     <t xml:space="preserve">9.1440372467041</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99060153961182</t>
+    <t xml:space="preserve">8.9906005859375</t>
   </si>
   <si>
     <t xml:space="preserve">8.95369815826416</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">9.03138732910156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58492374420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55190563201904</t>
+    <t xml:space="preserve">9.58492469787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55190658569336</t>
   </si>
   <si>
     <t xml:space="preserve">9.75001430511475</t>
@@ -3581,7 +3581,7 @@
     <t xml:space="preserve">9.63736438751221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62571144104004</t>
+    <t xml:space="preserve">9.62571239471436</t>
   </si>
   <si>
     <t xml:space="preserve">10.0801944732666</t>
@@ -3596,16 +3596,16 @@
     <t xml:space="preserve">10.4200839996338</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3860960006714</t>
+    <t xml:space="preserve">10.3860950469971</t>
   </si>
   <si>
     <t xml:space="preserve">10.5074844360352</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4346504211426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.415228843689</t>
+    <t xml:space="preserve">10.4346513748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4152297973633</t>
   </si>
   <si>
     <t xml:space="preserve">10.3278293609619</t>
@@ -3629,7 +3629,7 @@
     <t xml:space="preserve">10.4210567474365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4259395599365</t>
+    <t xml:space="preserve">10.4259405136108</t>
   </si>
   <si>
     <t xml:space="preserve">10.5333738327026</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">10.1720056533813</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54986763000488</t>
+    <t xml:space="preserve">9.5498685836792</t>
   </si>
   <si>
     <t xml:space="preserve">9.33890724182129</t>
@@ -3668,28 +3668,28 @@
     <t xml:space="preserve">10.0059728622437</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91318798065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59870052337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3975076675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36234664916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61823463439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4053201675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47173500061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47368812561035</t>
+    <t xml:space="preserve">9.91318893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59870147705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39750671386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36234760284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6182336807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40532112121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47173404693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47368717193604</t>
   </si>
   <si>
     <t xml:space="preserve">9.659255027771</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">9.69441413879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66511535644531</t>
+    <t xml:space="preserve">9.665114402771</t>
   </si>
   <si>
     <t xml:space="preserve">9.87412166595459</t>
@@ -3716,7 +3716,7 @@
     <t xml:space="preserve">9.68074131011963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54791355133057</t>
+    <t xml:space="preserve">9.54791450500488</t>
   </si>
   <si>
     <t xml:space="preserve">9.03418636322021</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">8.8154125213623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20608043670654</t>
+    <t xml:space="preserve">9.20607948303223</t>
   </si>
   <si>
     <t xml:space="preserve">9.11427211761475</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">9.52252101898193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56744766235352</t>
+    <t xml:space="preserve">9.5674467086792</t>
   </si>
   <si>
     <t xml:space="preserve">9.46782779693604</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">9.79110431671143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85947227478027</t>
+    <t xml:space="preserve">9.85947132110596</t>
   </si>
   <si>
     <t xml:space="preserve">9.91807174682617</t>
@@ -3764,16 +3764,16 @@
     <t xml:space="preserve">9.80087089538574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72566795349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66120910644531</t>
+    <t xml:space="preserve">9.72566890716553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.661208152771</t>
   </si>
   <si>
     <t xml:space="preserve">9.95713806152344</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0010890960693</t>
+    <t xml:space="preserve">10.001088142395</t>
   </si>
   <si>
     <t xml:space="preserve">10.162239074707</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">10.2989730834961</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0499219894409</t>
+    <t xml:space="preserve">10.0499229431152</t>
   </si>
   <si>
     <t xml:space="preserve">9.94248867034912</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">9.9376049041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96690464019775</t>
+    <t xml:space="preserve">9.96690559387207</t>
   </si>
   <si>
     <t xml:space="preserve">9.88877201080322</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">10.1329393386841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2354879379272</t>
+    <t xml:space="preserve">10.2354888916016</t>
   </si>
   <si>
     <t xml:space="preserve">10.4161729812622</t>
@@ -3809,13 +3809,13 @@
     <t xml:space="preserve">10.18665599823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1671228408813</t>
+    <t xml:space="preserve">10.167121887207</t>
   </si>
   <si>
     <t xml:space="preserve">10.5675563812256</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3673391342163</t>
+    <t xml:space="preserve">10.367338180542</t>
   </si>
   <si>
     <t xml:space="preserve">10.1182880401611</t>
@@ -3827,7 +3827,7 @@
     <t xml:space="preserve">9.97667217254639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81063842773438</t>
+    <t xml:space="preserve">9.81063747406006</t>
   </si>
   <si>
     <t xml:space="preserve">9.79598808288574</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">10.0352716445923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1134042739868</t>
+    <t xml:space="preserve">10.1134052276611</t>
   </si>
   <si>
     <t xml:space="preserve">10.1475896835327</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">10.152473449707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9815559387207</t>
+    <t xml:space="preserve">9.98155498504639</t>
   </si>
   <si>
     <t xml:space="preserve">9.83505439758301</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">9.20803356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32913970947266</t>
+    <t xml:space="preserve">9.32914066314697</t>
   </si>
   <si>
     <t xml:space="preserve">9.1298999786377</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">9.33109378814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4600133895874</t>
+    <t xml:space="preserve">9.46001434326172</t>
   </si>
   <si>
     <t xml:space="preserve">9.29593372344971</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">8.9658203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00684070587158</t>
+    <t xml:space="preserve">9.00683975219727</t>
   </si>
   <si>
     <t xml:space="preserve">8.94042682647705</t>
@@ -3899,46 +3899,46 @@
     <t xml:space="preserve">9.0752067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78025245666504</t>
+    <t xml:space="preserve">8.78025150299072</t>
   </si>
   <si>
     <t xml:space="preserve">8.68649291992188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89549922943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84471225738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88377952575684</t>
+    <t xml:space="preserve">8.89550018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84471321105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88377857208252</t>
   </si>
   <si>
     <t xml:space="preserve">8.72360515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89940643310547</t>
+    <t xml:space="preserve">8.89940738677979</t>
   </si>
   <si>
     <t xml:space="preserve">8.73532581329346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01074695587158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78806686401367</t>
+    <t xml:space="preserve">9.01074600219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78806591033936</t>
   </si>
   <si>
     <t xml:space="preserve">8.88964080810547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79783248901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94628620147705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98144721984863</t>
+    <t xml:space="preserve">8.79783344268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94628715515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98144626617432</t>
   </si>
   <si>
     <t xml:space="preserve">8.78611278533936</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">8.96191215515137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84080600738525</t>
+    <t xml:space="preserve">8.84080505371094</t>
   </si>
   <si>
     <t xml:space="preserve">8.60054492950439</t>
@@ -3959,16 +3959,16 @@
     <t xml:space="preserve">8.45209217071533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72165203094482</t>
+    <t xml:space="preserve">8.72165298461914</t>
   </si>
   <si>
     <t xml:space="preserve">8.90917301177979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79587841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80173873901367</t>
+    <t xml:space="preserve">8.79587936401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80173969268799</t>
   </si>
   <si>
     <t xml:space="preserve">8.70798015594482</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">8.99707317352295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10841464996338</t>
+    <t xml:space="preserve">9.10841369628906</t>
   </si>
   <si>
     <t xml:space="preserve">8.96386623382568</t>
@@ -4004,7 +4004,7 @@
     <t xml:space="preserve">9.54205513000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49322128295898</t>
+    <t xml:space="preserve">9.4932222366333</t>
   </si>
   <si>
     <t xml:space="preserve">9.5654935836792</t>
@@ -4016,22 +4016,22 @@
     <t xml:space="preserve">9.76278209686279</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1280555725098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96202087402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83993721008301</t>
+    <t xml:space="preserve">10.1280546188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96202182769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83993816375732</t>
   </si>
   <si>
     <t xml:space="preserve">9.80575466156006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69050884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72371482849121</t>
+    <t xml:space="preserve">9.69050788879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72371387481689</t>
   </si>
   <si>
     <t xml:space="preserve">9.75692176818848</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">9.95225429534912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58502864837646</t>
+    <t xml:space="preserve">9.58502769470215</t>
   </si>
   <si>
     <t xml:space="preserve">9.62214088439941</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">9.5108003616333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4033670425415</t>
+    <t xml:space="preserve">9.40336799621582</t>
   </si>
   <si>
     <t xml:space="preserve">9.38774013519287</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">9.45806121826172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26272678375244</t>
+    <t xml:space="preserve">9.26272773742676</t>
   </si>
   <si>
     <t xml:space="preserve">9.33500003814697</t>
@@ -4082,13 +4082,13 @@
     <t xml:space="preserve">9.63190841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64948749542236</t>
+    <t xml:space="preserve">9.64948844909668</t>
   </si>
   <si>
     <t xml:space="preserve">9.65729999542236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74324703216553</t>
+    <t xml:space="preserve">9.74324798583984</t>
   </si>
   <si>
     <t xml:space="preserve">9.71199512481689</t>
@@ -4097,7 +4097,7 @@
     <t xml:space="preserve">9.71785354614258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44438743591309</t>
+    <t xml:space="preserve">9.44438648223877</t>
   </si>
   <si>
     <t xml:space="preserve">9.42876052856445</t>
@@ -4106,19 +4106,19 @@
     <t xml:space="preserve">9.43852615356445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71590232849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0303897857666</t>
+    <t xml:space="preserve">9.71590137481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0303888320923</t>
   </si>
   <si>
     <t xml:space="preserve">9.90342235565186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83017063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1427059173584</t>
+    <t xml:space="preserve">9.83017158508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1427068710327</t>
   </si>
   <si>
     <t xml:space="preserve">10.2696733474731</t>
@@ -4136,19 +4136,19 @@
     <t xml:space="preserve">10.3380393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4796552658081</t>
+    <t xml:space="preserve">10.4796562194824</t>
   </si>
   <si>
     <t xml:space="preserve">10.2550220489502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3722229003906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.347806930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5870904922485</t>
+    <t xml:space="preserve">10.3722219467163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3478059768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5870895385742</t>
   </si>
   <si>
     <t xml:space="preserve">10.5382566452026</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">10.4698905944824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405899047852</t>
+    <t xml:space="preserve">10.4405889511108</t>
   </si>
   <si>
     <t xml:space="preserve">10.3917560577393</t>
@@ -4187,10 +4187,10 @@
     <t xml:space="preserve">10.860556602478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8312578201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7775402069092</t>
+    <t xml:space="preserve">10.8312568664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7775392532349</t>
   </si>
   <si>
     <t xml:space="preserve">10.880090713501</t>
@@ -4202,28 +4202,28 @@
     <t xml:space="preserve">10.9875240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.03147315979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0070571899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1291408538818</t>
+    <t xml:space="preserve">11.0314741134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0070581436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1291418075562</t>
   </si>
   <si>
     <t xml:space="preserve">11.2463417053223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2268075942993</t>
+    <t xml:space="preserve">11.2268085479736</t>
   </si>
   <si>
     <t xml:space="preserve">11.212158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.207275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2561073303223</t>
+    <t xml:space="preserve">11.2072744369507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2561082839966</t>
   </si>
   <si>
     <t xml:space="preserve">11.2854080200195</t>
@@ -4232,10 +4232,10 @@
     <t xml:space="preserve">11.3195915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3488912582397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3733081817627</t>
+    <t xml:space="preserve">11.3488922119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.373309135437</t>
   </si>
   <si>
     <t xml:space="preserve">11.5295753479004</t>
@@ -5919,6 +5919,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.80000019073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88199996948242</t>
   </si>
 </sst>
 </file>
@@ -71023,7 +71026,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6496990741</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>9027014</v>
@@ -71044,6 +71047,32 @@
         <v>1968</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6496180556</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>6104205</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>5.88199996948242</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>5.75600004196167</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>5.78999996185303</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>5.88199996948242</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1969</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1970" uniqueCount="1970">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1971" uniqueCount="1971">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59865617752075</t>
+    <t xml:space="preserve">3.59865689277649</t>
   </si>
   <si>
     <t xml:space="preserve">CPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65898251533508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60329699516296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51976871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51048851013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54993224143982</t>
+    <t xml:space="preserve">3.6589822769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60329675674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51976919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51048874855042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5499324798584</t>
   </si>
   <si>
     <t xml:space="preserve">3.62881970405579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68450474739075</t>
+    <t xml:space="preserve">3.68450498580933</t>
   </si>
   <si>
     <t xml:space="preserve">3.57313418388367</t>
@@ -71,40 +71,40 @@
     <t xml:space="preserve">3.52673006057739</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48264598846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56617403030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43392086029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50584745407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56153297424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64274024963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66594314575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56849384307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74251008033752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72162818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70770668983459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47104454040527</t>
+    <t xml:space="preserve">3.48264575004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5661735534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43392133712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50584769248962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56153321266174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64274048805237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66594290733337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56849408149719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74250984191895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72162842750549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70770692825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47104477882385</t>
   </si>
   <si>
     <t xml:space="preserve">3.44320225715637</t>
@@ -113,241 +113,241 @@
     <t xml:space="preserve">3.28078699111938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33183217048645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40839838981628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22046184539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26918601989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32487106323242</t>
+    <t xml:space="preserve">3.33183193206787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40839886665344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22046113014221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2691855430603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.324871301651</t>
   </si>
   <si>
     <t xml:space="preserve">3.24366331100464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32255077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28774785995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31791067123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36663484573364</t>
+    <t xml:space="preserve">3.32255053520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28774762153625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31791019439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36663460731506</t>
   </si>
   <si>
     <t xml:space="preserve">3.36199450492859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40607857704163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38287615776062</t>
+    <t xml:space="preserve">3.40607833862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38287663459778</t>
   </si>
   <si>
     <t xml:space="preserve">3.36431479454041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53137016296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60561752319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61257791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56385326385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61489820480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63810038566589</t>
+    <t xml:space="preserve">3.53137063980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60561728477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61257767677307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56385278701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61489796638489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63810014724731</t>
   </si>
   <si>
     <t xml:space="preserve">3.6891450881958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87476205825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95596981048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00701475143433</t>
+    <t xml:space="preserve">3.87476277351379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95597052574158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00701522827148</t>
   </si>
   <si>
     <t xml:space="preserve">4.04877901077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03485679626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04181814193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03717708587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05109882354736</t>
+    <t xml:space="preserve">4.03485727310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04181861877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03717756271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05109977722168</t>
   </si>
   <si>
     <t xml:space="preserve">4.01861572265625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09286260604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07662105560303</t>
+    <t xml:space="preserve">4.09286308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07662153244019</t>
   </si>
   <si>
     <t xml:space="preserve">4.03949785232544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08358192443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02325630187988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00005388259888</t>
+    <t xml:space="preserve">4.08358097076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02325677871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00005483627319</t>
   </si>
   <si>
     <t xml:space="preserve">4.06037998199463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99541306495667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94436883926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97453165054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00237512588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93740844726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94668889045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03021764755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05341958999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00933504104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95829010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98613309860229</t>
+    <t xml:space="preserve">3.99541354179382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94436931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97453093528748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00237417221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93740820884705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94668865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03021669387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05341911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00933456420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95828938484192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98613286018372</t>
   </si>
   <si>
     <t xml:space="preserve">4.0255765914917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96989178657532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91188597679138</t>
+    <t xml:space="preserve">3.96989226341248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91188669204712</t>
   </si>
   <si>
     <t xml:space="preserve">3.89796471595764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87708258628845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9142062664032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92812776565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95132923126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06734037399292</t>
+    <t xml:space="preserve">3.87708234786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91420578956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92812752723694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95132994651794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06733989715576</t>
   </si>
   <si>
     <t xml:space="preserve">4.08126211166382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99309277534485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96757102012634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98149251937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96293044090271</t>
+    <t xml:space="preserve">3.99309349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96757078170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98149275779724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96293115615845</t>
   </si>
   <si>
     <t xml:space="preserve">3.88868379592896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89332485198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79587554931641</t>
+    <t xml:space="preserve">3.89332389831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79587507247925</t>
   </si>
   <si>
     <t xml:space="preserve">3.89309906959534</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02677726745605</t>
+    <t xml:space="preserve">4.02677774429321</t>
   </si>
   <si>
     <t xml:space="preserve">4.08540821075439</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07602739334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08306312561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09947967529297</t>
+    <t xml:space="preserve">4.07602834701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08306407928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09948015213013</t>
   </si>
   <si>
     <t xml:space="preserve">4.07368278503418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0900993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10182428359985</t>
+    <t xml:space="preserve">4.09009981155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10182571411133</t>
   </si>
   <si>
     <t xml:space="preserve">4.0877537727356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11355257034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08071756362915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01974153518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90482425689697</t>
+    <t xml:space="preserve">4.11355209350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08071851730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01974201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90482497215271</t>
   </si>
   <si>
     <t xml:space="preserve">3.85557532310486</t>
@@ -359,34 +359,34 @@
     <t xml:space="preserve">3.86495614051819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87199139595032</t>
+    <t xml:space="preserve">3.87199187278748</t>
   </si>
   <si>
     <t xml:space="preserve">3.86964631080627</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00567054748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00801515579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95876526832581</t>
+    <t xml:space="preserve">4.00567007064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00801563262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95876502990723</t>
   </si>
   <si>
     <t xml:space="preserve">4.05961084365845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88606333732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88840794563293</t>
+    <t xml:space="preserve">3.88606309890747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88840842247009</t>
   </si>
   <si>
     <t xml:space="preserve">4.04084968566895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16514682769775</t>
+    <t xml:space="preserve">4.16514730453491</t>
   </si>
   <si>
     <t xml:space="preserve">4.15576601028442</t>
@@ -395,40 +395,40 @@
     <t xml:space="preserve">4.14873075485229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13231420516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00332498550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04319429397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16045618057251</t>
+    <t xml:space="preserve">4.13231325149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00332450866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04319477081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16045713424683</t>
   </si>
   <si>
     <t xml:space="preserve">4.15811109542847</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1158971786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06899166107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1346583366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14169406890869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18390941619873</t>
+    <t xml:space="preserve">4.11589670181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06899213790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13465881347656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14169502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18390798568726</t>
   </si>
   <si>
     <t xml:space="preserve">4.16280174255371</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21908712387085</t>
+    <t xml:space="preserve">4.21908760070801</t>
   </si>
   <si>
     <t xml:space="preserve">4.29178953170776</t>
@@ -440,31 +440,31 @@
     <t xml:space="preserve">4.31055116653442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28709936141968</t>
+    <t xml:space="preserve">4.28709983825684</t>
   </si>
   <si>
     <t xml:space="preserve">4.33165884017944</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33869504928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5403847694397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51458740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52162313461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43719530105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47940874099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45595598220825</t>
+    <t xml:space="preserve">4.33869457244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54038572311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51458787918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5216236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43719434738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47940921783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45595645904541</t>
   </si>
   <si>
     <t xml:space="preserve">4.66233730316162</t>
@@ -473,67 +473,67 @@
     <t xml:space="preserve">4.67171907424927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58963537216187</t>
+    <t xml:space="preserve">4.58963489532471</t>
   </si>
   <si>
     <t xml:space="preserve">4.55914735794067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56383800506592</t>
+    <t xml:space="preserve">4.56383752822876</t>
   </si>
   <si>
     <t xml:space="preserve">4.54976606369019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60370683670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59667062759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62012338638306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59432554244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65061092376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57556295394897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7045521736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67406368255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70924234390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6013617515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48644495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46533823013306</t>
+    <t xml:space="preserve">4.60370635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59667110443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57321882247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6201229095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59432601928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65061187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57556438446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70455169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67406415939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7092432975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60136127471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4864444732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4653377532959</t>
   </si>
   <si>
     <t xml:space="preserve">4.39967060089111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43250465393066</t>
+    <t xml:space="preserve">4.43250417709351</t>
   </si>
   <si>
     <t xml:space="preserve">4.50520658493042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49113464355469</t>
+    <t xml:space="preserve">4.491135597229</t>
   </si>
   <si>
     <t xml:space="preserve">4.51693296432495</t>
@@ -542,19 +542,19 @@
     <t xml:space="preserve">4.50286149978638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48879051208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65295696258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66468238830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73269414901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71393251419067</t>
+    <t xml:space="preserve">4.4887900352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65295743942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66468334197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73269462585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71393299102783</t>
   </si>
   <si>
     <t xml:space="preserve">4.69048023223877</t>
@@ -563,25 +563,25 @@
     <t xml:space="preserve">4.58729028701782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56852769851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47471809387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44657564163208</t>
+    <t xml:space="preserve">4.568528175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47471904754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44657516479492</t>
   </si>
   <si>
     <t xml:space="preserve">4.5474214553833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44188547134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50051593780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52631282806396</t>
+    <t xml:space="preserve">4.44188499450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50051689147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52631425857544</t>
   </si>
   <si>
     <t xml:space="preserve">4.36683797836304</t>
@@ -593,22 +593,22 @@
     <t xml:space="preserve">4.33400392532349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3293137550354</t>
+    <t xml:space="preserve">4.32931327819824</t>
   </si>
   <si>
     <t xml:space="preserve">4.3058614730835</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30351686477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25661134719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20736074447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09478950500488</t>
+    <t xml:space="preserve">4.30351591110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25661039352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20736169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09478998184204</t>
   </si>
   <si>
     <t xml:space="preserve">4.24253988265991</t>
@@ -617,22 +617,22 @@
     <t xml:space="preserve">4.20267057418823</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9564208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95407557487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0338134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12527751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01739645004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12996912002563</t>
+    <t xml:space="preserve">3.95642066001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9540753364563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03381443023682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12527799606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01739692687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12996816635132</t>
   </si>
   <si>
     <t xml:space="preserve">4.1721830368042</t>
@@ -641,16 +641,16 @@
     <t xml:space="preserve">4.21205139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18860006332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24957656860352</t>
+    <t xml:space="preserve">4.18859958648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24957609176636</t>
   </si>
   <si>
     <t xml:space="preserve">4.20501565933228</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26833772659302</t>
+    <t xml:space="preserve">4.26833724975586</t>
   </si>
   <si>
     <t xml:space="preserve">4.2284688949585</t>
@@ -659,64 +659,64 @@
     <t xml:space="preserve">4.24723052978516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31993341445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36449241638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28944492340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27771854400635</t>
+    <t xml:space="preserve">4.31993293762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449193954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28944540023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27771806716919</t>
   </si>
   <si>
     <t xml:space="preserve">4.30117082595825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32227802276611</t>
+    <t xml:space="preserve">4.32227754592896</t>
   </si>
   <si>
     <t xml:space="preserve">4.35745668411255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34807586669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34338521957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39029026031494</t>
+    <t xml:space="preserve">4.3480749130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34338474273682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39028978347778</t>
   </si>
   <si>
     <t xml:space="preserve">4.36214733123779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32462358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39732646942139</t>
+    <t xml:space="preserve">4.32462310791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39732599258423</t>
   </si>
   <si>
     <t xml:space="preserve">4.37387371063232</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36918306350708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47002792358398</t>
+    <t xml:space="preserve">4.36918258666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47002840042114</t>
   </si>
   <si>
     <t xml:space="preserve">4.45830202102661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42546892166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43484926223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46768283843994</t>
+    <t xml:space="preserve">4.42546844482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43484878540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4676833152771</t>
   </si>
   <si>
     <t xml:space="preserve">4.40201616287231</t>
@@ -725,19 +725,19 @@
     <t xml:space="preserve">4.3527660369873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3855996131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43953990936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43015909194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49348020553589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47237348556519</t>
+    <t xml:space="preserve">4.38559913635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43954086303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4301586151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49348068237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47237300872803</t>
   </si>
   <si>
     <t xml:space="preserve">4.52396869659424</t>
@@ -746,22 +746,22 @@
     <t xml:space="preserve">4.5427303314209</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53804016113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54507541656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58260011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57790946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55211210250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57087326049805</t>
+    <t xml:space="preserve">4.53804063796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5450758934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58259963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57790994644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55211162567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57087373733521</t>
   </si>
   <si>
     <t xml:space="preserve">4.53569507598877</t>
@@ -770,13 +770,13 @@
     <t xml:space="preserve">4.50755214691162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58494424819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65530157089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74207639694214</t>
+    <t xml:space="preserve">4.58494520187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65530252456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74207544326782</t>
   </si>
   <si>
     <t xml:space="preserve">4.75614738464355</t>
@@ -791,187 +791,187 @@
     <t xml:space="preserve">4.89686155319214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94845676422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09855270385742</t>
+    <t xml:space="preserve">4.94845724105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09855222702026</t>
   </si>
   <si>
     <t xml:space="preserve">5.05164813995361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12200546264648</t>
+    <t xml:space="preserve">5.12200498580933</t>
   </si>
   <si>
     <t xml:space="preserve">5.04695749282837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05633878707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99536228179932</t>
+    <t xml:space="preserve">5.0563383102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99536180496216</t>
   </si>
   <si>
     <t xml:space="preserve">5.01881408691406</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02819585800171</t>
+    <t xml:space="preserve">5.02819538116455</t>
   </si>
   <si>
     <t xml:space="preserve">5.03288507461548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93907642364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97660064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92500448226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96721887588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08917093276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17359972000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14545774459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1595287322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09386157989502</t>
+    <t xml:space="preserve">4.9390754699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9766001701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9250054359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96721935272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08917188644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1736011505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14545726776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15952825546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09386205673218</t>
   </si>
   <si>
     <t xml:space="preserve">5.16421890258789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25333833694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18767213821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41750526428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67079162597656</t>
+    <t xml:space="preserve">5.25333881378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18767166137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41750478744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6707911491394</t>
   </si>
   <si>
     <t xml:space="preserve">5.60043382644653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62388610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66141033172607</t>
+    <t xml:space="preserve">5.6238865852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66140985488892</t>
   </si>
   <si>
     <t xml:space="preserve">5.68486213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57698202133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60512399673462</t>
+    <t xml:space="preserve">5.57698154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60512495040894</t>
   </si>
   <si>
     <t xml:space="preserve">5.72238636016846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69403409957886</t>
+    <t xml:space="preserve">5.69403457641602</t>
   </si>
   <si>
     <t xml:space="preserve">5.74128770828247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76491403579712</t>
+    <t xml:space="preserve">5.76491451263428</t>
   </si>
   <si>
     <t xml:space="preserve">5.75073862075806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8783221244812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86887168884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88304710388184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02008247375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9917311668396</t>
+    <t xml:space="preserve">5.87832164764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86887216567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88304805755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02008295059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99173069000244</t>
   </si>
   <si>
     <t xml:space="preserve">6.00118160247803</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93502712249756</t>
+    <t xml:space="preserve">5.9350266456604</t>
   </si>
   <si>
     <t xml:space="preserve">5.85942077636719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80271673202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75546407699585</t>
+    <t xml:space="preserve">5.80271768569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75546360015869</t>
   </si>
   <si>
     <t xml:space="preserve">5.73183727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84997081756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81216812133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95865249633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93030166625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9822793006897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90194940567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91612577438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91139984130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8310694694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88777351379395</t>
+    <t xml:space="preserve">5.84997034072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81216859817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95865345001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93030214309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98227977752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90194845199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91612529754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91140031814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83106899261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88777303695679</t>
   </si>
   <si>
     <t xml:space="preserve">5.78381538391113</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80744218826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84524536132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77436542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82634353637695</t>
+    <t xml:space="preserve">5.8074426651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84524488449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77436494827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82634449005127</t>
   </si>
   <si>
     <t xml:space="preserve">5.82161808013916</t>
@@ -980,13 +980,13 @@
     <t xml:space="preserve">5.85469627380371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79326677322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83579444885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95392847061157</t>
+    <t xml:space="preserve">5.79326629638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8357949256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95392799377441</t>
   </si>
   <si>
     <t xml:space="preserve">5.92557525634766</t>
@@ -995,130 +995,130 @@
     <t xml:space="preserve">5.94447708129883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77909088134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74601268768311</t>
+    <t xml:space="preserve">5.7790904045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74601316452026</t>
   </si>
   <si>
     <t xml:space="preserve">5.71766090393066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65150594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66095590591431</t>
+    <t xml:space="preserve">5.6515064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66095685958862</t>
   </si>
   <si>
     <t xml:space="preserve">5.79799175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76018857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69876003265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6656813621521</t>
+    <t xml:space="preserve">5.76018905639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69875955581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66568183898926</t>
   </si>
   <si>
     <t xml:space="preserve">5.73656272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78854131698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76963949203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89249897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97282934188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15239286422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14766693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28470182418823</t>
+    <t xml:space="preserve">5.78854084014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76963901519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89249849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97282886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15239238739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1476674079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28470134735107</t>
   </si>
   <si>
     <t xml:space="preserve">6.13821601867676</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12404012680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02953290939331</t>
+    <t xml:space="preserve">6.1240406036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02953338623047</t>
   </si>
   <si>
     <t xml:space="preserve">6.10513877868652</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16656923294067</t>
+    <t xml:space="preserve">6.16656875610352</t>
   </si>
   <si>
     <t xml:space="preserve">6.11458921432495</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31777858734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34140586853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40756034851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50206708908081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42173624038696</t>
+    <t xml:space="preserve">6.31777954101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34140539169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40756130218506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50206661224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42173719406128</t>
   </si>
   <si>
     <t xml:space="preserve">6.30832862854004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.478440284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31305360794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33667993545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37448263168335</t>
+    <t xml:space="preserve">6.47844076156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31305408477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33668041229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37448310852051</t>
   </si>
   <si>
     <t xml:space="preserve">6.17601871490479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09096336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23272323608398</t>
+    <t xml:space="preserve">6.0909628868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23272228240967</t>
   </si>
   <si>
     <t xml:space="preserve">6.03898334503174</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08623790740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10041236877441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10986471176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00590658187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03425884246826</t>
+    <t xml:space="preserve">6.08623743057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10041332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10986423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00590705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03425931930542</t>
   </si>
   <si>
     <t xml:space="preserve">6.09568738937378</t>
@@ -1127,31 +1127,31 @@
     <t xml:space="preserve">6.06261110305786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18074369430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08151245117188</t>
+    <t xml:space="preserve">6.18074417114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08151197433472</t>
   </si>
   <si>
     <t xml:space="preserve">6.15711736679077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21382093429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24217319488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24689912796021</t>
+    <t xml:space="preserve">6.21382141113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24217414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24689865112305</t>
   </si>
   <si>
     <t xml:space="preserve">6.20909643173218</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22799825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19964599609375</t>
+    <t xml:space="preserve">6.22799777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19964551925659</t>
   </si>
   <si>
     <t xml:space="preserve">6.12876605987549</t>
@@ -1160,58 +1160,58 @@
     <t xml:space="preserve">6.07206201553345</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05788612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13349151611328</t>
+    <t xml:space="preserve">6.05788564682007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13349103927612</t>
   </si>
   <si>
     <t xml:space="preserve">6.14294147491455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01063299179077</t>
+    <t xml:space="preserve">6.01063203811646</t>
   </si>
   <si>
     <t xml:space="preserve">5.94920301437378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9775538444519</t>
+    <t xml:space="preserve">5.97755479812622</t>
   </si>
   <si>
     <t xml:space="preserve">6.05316019058228</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99645614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06733655929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93975162506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71293592453003</t>
+    <t xml:space="preserve">5.99645566940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06733560562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93975210189819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71293544769287</t>
   </si>
   <si>
     <t xml:space="preserve">5.72711086273193</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92085075378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57590103149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52864694595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42941474914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50502014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61370420455933</t>
+    <t xml:space="preserve">5.92085027694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57590055465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52864742279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42941570281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50502061843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61370372772217</t>
   </si>
   <si>
     <t xml:space="preserve">5.63733100891113</t>
@@ -1220,82 +1220,82 @@
     <t xml:space="preserve">6.04370927810669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98700571060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01535749435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89722394943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81689262390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87359714508057</t>
+    <t xml:space="preserve">5.98700523376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01535701751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89722347259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81689357757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87359762191772</t>
   </si>
   <si>
     <t xml:space="preserve">5.86414670944214</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90667390823364</t>
+    <t xml:space="preserve">5.9066743850708</t>
   </si>
   <si>
     <t xml:space="preserve">5.96810436248779</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01550674438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02027082443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99169254302979</t>
+    <t xml:space="preserve">6.01550722122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02027034759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99169301986694</t>
   </si>
   <si>
     <t xml:space="preserve">6.08218765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20602226257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18697071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08695030212402</t>
+    <t xml:space="preserve">6.20602178573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18697118759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08694982528687</t>
   </si>
   <si>
     <t xml:space="preserve">6.07266187667847</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16315650939941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27270221710205</t>
+    <t xml:space="preserve">6.1631555557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27270269393921</t>
   </si>
   <si>
     <t xml:space="preserve">6.25365114212036</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13934183120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29175424575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38701152801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52513408660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59657716751099</t>
+    <t xml:space="preserve">6.13934230804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29175472259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38701200485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5251350402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59657764434814</t>
   </si>
   <si>
     <t xml:space="preserve">6.69183588027954</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69659852981567</t>
+    <t xml:space="preserve">6.69659805297852</t>
   </si>
   <si>
     <t xml:space="preserve">6.62039232254028</t>
@@ -1304,10 +1304,10 @@
     <t xml:space="preserve">6.57276344299316</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5060830116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58228921890259</t>
+    <t xml:space="preserve">6.50608396530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58228874206543</t>
   </si>
   <si>
     <t xml:space="preserve">6.65373229980469</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">6.71088647842407</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82519483566284</t>
+    <t xml:space="preserve">6.82519626617432</t>
   </si>
   <si>
     <t xml:space="preserve">6.77280426025391</t>
@@ -1325,67 +1325,67 @@
     <t xml:space="preserve">6.82995891571045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02523612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92521619796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9204535484314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01094818115234</t>
+    <t xml:space="preserve">7.02523708343506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92521572113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92045307159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0109486579895</t>
   </si>
   <si>
     <t xml:space="preserve">6.96808242797852</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91092681884766</t>
+    <t xml:space="preserve">6.91092729568481</t>
   </si>
   <si>
     <t xml:space="preserve">7.01571083068848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04905080795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17764854431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28243112564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22051429748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2395658493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27766847610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12525701522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94903135299683</t>
+    <t xml:space="preserve">7.04905128479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09667921066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17764806747437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28243160247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22051382064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23956537246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27766799926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12525653839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">6.86806154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0014214515686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00618505477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0633397102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760725021362</t>
+    <t xml:space="preserve">7.00142192840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00618457794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06333923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760820388794</t>
   </si>
   <si>
     <t xml:space="preserve">6.99189615249634</t>
@@ -1394,10 +1394,10 @@
     <t xml:space="preserve">7.03952503204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02047348022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07762813568115</t>
+    <t xml:space="preserve">7.02047395706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07762765884399</t>
   </si>
   <si>
     <t xml:space="preserve">7.18717384338379</t>
@@ -1406,55 +1406,55 @@
     <t xml:space="preserve">7.21098852157593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41579151153564</t>
+    <t xml:space="preserve">7.4157919883728</t>
   </si>
   <si>
     <t xml:space="preserve">7.29672002792358</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26338052749634</t>
+    <t xml:space="preserve">7.26337957382202</t>
   </si>
   <si>
     <t xml:space="preserve">7.24432802200317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27290630340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30624628067017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18241167068481</t>
+    <t xml:space="preserve">7.2729058265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30624580383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18241024017334</t>
   </si>
   <si>
     <t xml:space="preserve">7.25385332107544</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05857610702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10620498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14907169342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16812229156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90140199661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94426727294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06810188293457</t>
+    <t xml:space="preserve">7.0585765838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10620546340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14907073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16812181472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90140151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94426774978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06810235977173</t>
   </si>
   <si>
     <t xml:space="preserve">6.98713302612305</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1300196647644</t>
+    <t xml:space="preserve">7.13002014160156</t>
   </si>
   <si>
     <t xml:space="preserve">6.87758684158325</t>
@@ -1463,85 +1463,85 @@
     <t xml:space="preserve">6.7061243057251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63944339752197</t>
+    <t xml:space="preserve">6.63944292068481</t>
   </si>
   <si>
     <t xml:space="preserve">6.65849542617798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32985687255859</t>
+    <t xml:space="preserve">6.32985734939575</t>
   </si>
   <si>
     <t xml:space="preserve">6.19649696350098</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11552858352661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04884719848633</t>
+    <t xml:space="preserve">6.11552715301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04884767532349</t>
   </si>
   <si>
     <t xml:space="preserve">6.21554803848267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31556844711304</t>
+    <t xml:space="preserve">6.3155689239502</t>
   </si>
   <si>
     <t xml:space="preserve">6.33461999893188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34414577484131</t>
+    <t xml:space="preserve">6.34414482116699</t>
   </si>
   <si>
     <t xml:space="preserve">6.12505340576172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15363025665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30604219436646</t>
+    <t xml:space="preserve">6.15363073348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30604267120361</t>
   </si>
   <si>
     <t xml:space="preserve">6.35367107391357</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47274303436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4679799079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42987823486328</t>
+    <t xml:space="preserve">6.47274398803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46798086166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42987775802612</t>
   </si>
   <si>
     <t xml:space="preserve">6.52989721298218</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76804113388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08239078521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11096811294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12049341201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32529735565186</t>
+    <t xml:space="preserve">6.76804065704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08239126205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11096858978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12049388885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3252968788147</t>
   </si>
   <si>
     <t xml:space="preserve">7.31577062606812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11573028564453</t>
+    <t xml:space="preserve">7.11573123931885</t>
   </si>
   <si>
     <t xml:space="preserve">7.03476238250732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15383386611938</t>
+    <t xml:space="preserve">7.15383434295654</t>
   </si>
   <si>
     <t xml:space="preserve">7.04428768157959</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">7.02999925613403</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17288541793823</t>
+    <t xml:space="preserve">7.17288494110107</t>
   </si>
   <si>
     <t xml:space="preserve">7.36339998245239</t>
@@ -1559,34 +1559,34 @@
     <t xml:space="preserve">7.14430856704712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20622587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32053470611572</t>
+    <t xml:space="preserve">7.20622539520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32053375244141</t>
   </si>
   <si>
     <t xml:space="preserve">7.09191703796387</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98237037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44913196563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38245105743408</t>
+    <t xml:space="preserve">6.98237085342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913148880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3824520111084</t>
   </si>
   <si>
     <t xml:space="preserve">7.33006000518799</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21575117111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33958578109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35387516021729</t>
+    <t xml:space="preserve">7.2157506942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33958625793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35387420654297</t>
   </si>
   <si>
     <t xml:space="preserve">7.55391502380371</t>
@@ -1601,28 +1601,28 @@
     <t xml:space="preserve">7.49199771881104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44436979293823</t>
+    <t xml:space="preserve">7.44436883926392</t>
   </si>
   <si>
     <t xml:space="preserve">7.42055463790894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62535762786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53010177612305</t>
+    <t xml:space="preserve">7.62535858154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53010129928589</t>
   </si>
   <si>
     <t xml:space="preserve">7.47294616699219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4872350692749</t>
+    <t xml:space="preserve">7.48723554611206</t>
   </si>
   <si>
     <t xml:space="preserve">7.46818351745605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49676036834717</t>
+    <t xml:space="preserve">7.49675989151001</t>
   </si>
   <si>
     <t xml:space="preserve">7.51581192016602</t>
@@ -1631,109 +1631,109 @@
     <t xml:space="preserve">7.61106967926025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56344079971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64440965652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73490476608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80634641647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86826515197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85873985290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88731479644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9254207611084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95399713516235</t>
+    <t xml:space="preserve">7.56344127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6444091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73490428924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80634689331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86826419830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85873889923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88731670379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92541933059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95399808883667</t>
   </si>
   <si>
     <t xml:space="preserve">7.83492565155029</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98733758926392</t>
+    <t xml:space="preserve">7.9873366355896</t>
   </si>
   <si>
     <t xml:space="preserve">8.01115131378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06354236602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53486394882202</t>
+    <t xml:space="preserve">8.06354141235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53486347198486</t>
   </si>
   <si>
     <t xml:space="preserve">7.52057504653931</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54438877105713</t>
+    <t xml:space="preserve">7.54438924789429</t>
   </si>
   <si>
     <t xml:space="preserve">7.62059593200684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63964748382568</t>
+    <t xml:space="preserve">7.63964700698853</t>
   </si>
   <si>
     <t xml:space="preserve">7.77777004241943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76824331283569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90636825561523</t>
+    <t xml:space="preserve">7.76824426651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90636777877808</t>
   </si>
   <si>
     <t xml:space="preserve">8.0349645614624</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00638771057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04448986053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06830501556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2016658782959</t>
+    <t xml:space="preserve">8.00638866424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04449081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06830596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20166492462158</t>
   </si>
   <si>
     <t xml:space="preserve">8.32549953460693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44457149505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33978939056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38265609741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33502578735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27787208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23500728607178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25881958007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26358318328857</t>
+    <t xml:space="preserve">8.44457244873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33978843688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38265514373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33502674102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27787113189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23500823974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25882053375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26358413696289</t>
   </si>
   <si>
     <t xml:space="preserve">8.16832542419434</t>
@@ -1742,55 +1742,55 @@
     <t xml:space="preserve">8.31121253967285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36836719512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35407829284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37789154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28739738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21119213104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22071743011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43150615692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44587516784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56085300445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51294612884521</t>
+    <t xml:space="preserve">8.36836624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.354079246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37789344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28739833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21119117736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22071647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4315071105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.445876121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56085109710693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5129451751709</t>
   </si>
   <si>
     <t xml:space="preserve">8.48899173736572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60875701904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.441086769104</t>
+    <t xml:space="preserve">8.60875797271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44108581542969</t>
   </si>
   <si>
     <t xml:space="preserve">8.49857330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48420143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67103672027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81475448608398</t>
+    <t xml:space="preserve">8.4842004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6710376739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8147554397583</t>
   </si>
   <si>
     <t xml:space="preserve">8.74289512634277</t>
@@ -1805,10 +1805,10 @@
     <t xml:space="preserve">8.70936107635498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6854076385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70456981658936</t>
+    <t xml:space="preserve">8.68540859222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70457172393799</t>
   </si>
   <si>
     <t xml:space="preserve">8.78122138977051</t>
@@ -1817,10 +1817,10 @@
     <t xml:space="preserve">8.80996513366699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77163982391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65187454223633</t>
+    <t xml:space="preserve">8.77163887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65187358856201</t>
   </si>
   <si>
     <t xml:space="preserve">8.53689861297607</t>
@@ -1832,40 +1832,40 @@
     <t xml:space="preserve">8.37401676177979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40755081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41234302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32611083984375</t>
+    <t xml:space="preserve">8.40755176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4123420715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32610988616943</t>
   </si>
   <si>
     <t xml:space="preserve">8.45545864105225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41713428497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39318084716797</t>
+    <t xml:space="preserve">8.41713237762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39317989349365</t>
   </si>
   <si>
     <t xml:space="preserve">8.54648017883301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58959674835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27341556549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25425243377686</t>
+    <t xml:space="preserve">8.58959579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27341365814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25425148010254</t>
   </si>
   <si>
     <t xml:space="preserve">8.35485458374023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47461986541748</t>
+    <t xml:space="preserve">8.4746208190918</t>
   </si>
   <si>
     <t xml:space="preserve">8.42192363739014</t>
@@ -1874,52 +1874,52 @@
     <t xml:space="preserve">8.36922550201416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31653022766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29736804962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28299617767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17760181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2015552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16322994232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24946022033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18239307403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17281055450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09616088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14885807037354</t>
+    <t xml:space="preserve">8.31652927398682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29736709594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28299713134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1776008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20155429840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16323089599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24946117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18239212036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17280960083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09616184234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14885711669922</t>
   </si>
   <si>
     <t xml:space="preserve">8.06741714477539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03867340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97160577774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78956127166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62188816070557</t>
+    <t xml:space="preserve">8.03867435455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97160387039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78956079483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62188863754272</t>
   </si>
   <si>
     <t xml:space="preserve">7.61709833145142</t>
@@ -1928,16 +1928,16 @@
     <t xml:space="preserve">7.66021347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50212335586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72249174118042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5931453704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45900726318359</t>
+    <t xml:space="preserve">7.50212287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72249221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59314584732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45900774002075</t>
   </si>
   <si>
     <t xml:space="preserve">7.51170444488525</t>
@@ -1946,13 +1946,13 @@
     <t xml:space="preserve">7.65542316436768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59793567657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90932559967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95244264602661</t>
+    <t xml:space="preserve">7.59793519973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90932750701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95244216918945</t>
   </si>
   <si>
     <t xml:space="preserve">7.82309532165527</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">7.88058376312256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10574150085449</t>
+    <t xml:space="preserve">8.10574054718018</t>
   </si>
   <si>
     <t xml:space="preserve">8.20634460449219</t>
@@ -1970,34 +1970,34 @@
     <t xml:space="preserve">8.16802024841309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26383304595947</t>
+    <t xml:space="preserve">8.26383399963379</t>
   </si>
   <si>
     <t xml:space="preserve">8.3452730178833</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29257678985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12011432647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0338830947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99555921554565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80872297286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91411733627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88537216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82788515090942</t>
+    <t xml:space="preserve">8.29257488250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12011528015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03388214111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9955587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80872344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91411685943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88537359237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82788562774658</t>
   </si>
   <si>
     <t xml:space="preserve">7.84704780578613</t>
@@ -2006,37 +2006,37 @@
     <t xml:space="preserve">8.0003490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89974498748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90453672409058</t>
+    <t xml:space="preserve">7.89974546432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90453624725342</t>
   </si>
   <si>
     <t xml:space="preserve">7.94286060333252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71770191192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85662889480591</t>
+    <t xml:space="preserve">7.71770143508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85662984848022</t>
   </si>
   <si>
     <t xml:space="preserve">8.04346466064453</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11532402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12969589233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13448715209961</t>
+    <t xml:space="preserve">8.11532306671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12969493865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13448524475098</t>
   </si>
   <si>
     <t xml:space="preserve">8.00992965698242</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93327856063843</t>
+    <t xml:space="preserve">7.9332799911499</t>
   </si>
   <si>
     <t xml:space="preserve">7.75123596191406</t>
@@ -2045,58 +2045,58 @@
     <t xml:space="preserve">7.57877349853516</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64105129241943</t>
+    <t xml:space="preserve">7.64105176925659</t>
   </si>
   <si>
     <t xml:space="preserve">7.69374752044678</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83746671676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81351327896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87100172042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87579345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92369937896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89495420455933</t>
+    <t xml:space="preserve">7.83746719360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81351375579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87100124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87579298019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92369890213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89495372772217</t>
   </si>
   <si>
     <t xml:space="preserve">7.8518385887146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86621141433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98597526550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9668140411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92848968505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1105318069458</t>
+    <t xml:space="preserve">7.8662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98597478866577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96681356430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92848873138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11053276062012</t>
   </si>
   <si>
     <t xml:space="preserve">8.04825401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93806982040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77997970581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81830358505249</t>
+    <t xml:space="preserve">7.93806934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77997922897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81830406188965</t>
   </si>
   <si>
     <t xml:space="preserve">7.84225749969482</t>
@@ -2108,82 +2108,82 @@
     <t xml:space="preserve">7.79914236068726</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94765090942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91890859603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7129111289978</t>
+    <t xml:space="preserve">7.94765186309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91890811920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71291160583496</t>
   </si>
   <si>
     <t xml:space="preserve">7.77518892288208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86142063140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07699871063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21592617034912</t>
+    <t xml:space="preserve">7.86142110824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07699966430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21592712402344</t>
   </si>
   <si>
     <t xml:space="preserve">8.26862335205078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33569240570068</t>
+    <t xml:space="preserve">8.335693359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.45066738128662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36443614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47941112518311</t>
+    <t xml:space="preserve">8.36443519592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47941207885742</t>
   </si>
   <si>
     <t xml:space="preserve">8.55127143859863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59438705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66624546051025</t>
+    <t xml:space="preserve">8.59438610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66624641418457</t>
   </si>
   <si>
     <t xml:space="preserve">8.64229393005371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69019985198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58480453491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19197368621826</t>
+    <t xml:space="preserve">8.69019889831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58480548858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19197559356689</t>
   </si>
   <si>
     <t xml:space="preserve">7.74165439605713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70332956314087</t>
+    <t xml:space="preserve">7.70333003997803</t>
   </si>
   <si>
     <t xml:space="preserve">7.78477048873901</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44463539123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22426700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1763596534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30091667175293</t>
+    <t xml:space="preserve">7.44463586807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22426605224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17636013031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30091619491577</t>
   </si>
   <si>
     <t xml:space="preserve">7.36319494247437</t>
@@ -2195,7 +2195,7 @@
     <t xml:space="preserve">7.09491968154907</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69729804992676</t>
+    <t xml:space="preserve">6.6972975730896</t>
   </si>
   <si>
     <t xml:space="preserve">6.36195373535156</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">5.33675956726074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.54754686355591</t>
+    <t xml:space="preserve">5.54754638671875</t>
   </si>
   <si>
     <t xml:space="preserve">5.37987470626831</t>
@@ -2216,37 +2216,37 @@
     <t xml:space="preserve">5.8685188293457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45776510238647</t>
+    <t xml:space="preserve">6.45776605606079</t>
   </si>
   <si>
     <t xml:space="preserve">6.08409738540649</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03619194030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29967498779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76915693283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84101581573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53441667556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3715353012085</t>
+    <t xml:space="preserve">6.03619146347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29967546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76915740966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84101676940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53441619873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37153482437134</t>
   </si>
   <si>
     <t xml:space="preserve">6.27572250366211</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02852582931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11092472076416</t>
+    <t xml:space="preserve">6.02852630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11092519760132</t>
   </si>
   <si>
     <t xml:space="preserve">5.85606288909912</t>
@@ -2255,19 +2255,19 @@
     <t xml:space="preserve">6.45201778411865</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38111639022827</t>
+    <t xml:space="preserve">6.38111543655396</t>
   </si>
   <si>
     <t xml:space="preserve">6.32171249389648</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35237264633179</t>
+    <t xml:space="preserve">6.35237312316895</t>
   </si>
   <si>
     <t xml:space="preserve">6.40986061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40794372558594</t>
+    <t xml:space="preserve">6.4079442024231</t>
   </si>
   <si>
     <t xml:space="preserve">6.47309589385986</t>
@@ -2276,37 +2276,37 @@
     <t xml:space="preserve">6.65897274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49962043762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44746923446655</t>
+    <t xml:space="preserve">6.49962091445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44746971130371</t>
   </si>
   <si>
     <t xml:space="preserve">6.43008518218994</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39338684082031</t>
+    <t xml:space="preserve">6.39338636398315</t>
   </si>
   <si>
     <t xml:space="preserve">6.44360637664795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59619760513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61551332473755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79321432113647</t>
+    <t xml:space="preserve">6.59619808197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61551284790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79321384429932</t>
   </si>
   <si>
     <t xml:space="preserve">6.82798194885254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62323904037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.690842628479</t>
+    <t xml:space="preserve">6.6232385635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69084310531616</t>
   </si>
   <si>
     <t xml:space="preserve">6.76617288589478</t>
@@ -2318,13 +2318,13 @@
     <t xml:space="preserve">6.94773721694946</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95932674407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08487606048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93807888031006</t>
+    <t xml:space="preserve">6.95932626724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.084876537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93807935714722</t>
   </si>
   <si>
     <t xml:space="preserve">6.70629501342773</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">6.66766452789307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94001150131226</t>
+    <t xml:space="preserve">6.9400110244751</t>
   </si>
   <si>
     <t xml:space="preserve">6.5112099647522</t>
@@ -2351,7 +2351,7 @@
     <t xml:space="preserve">6.67732191085815</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72947406768799</t>
+    <t xml:space="preserve">6.72947359085083</t>
   </si>
   <si>
     <t xml:space="preserve">6.71209001541138</t>
@@ -2363,13 +2363,13 @@
     <t xml:space="preserve">7.05010890960693</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9438738822937</t>
+    <t xml:space="preserve">6.94387435913086</t>
   </si>
   <si>
     <t xml:space="preserve">7.1119179725647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09839725494385</t>
+    <t xml:space="preserve">7.09839677810669</t>
   </si>
   <si>
     <t xml:space="preserve">7.14282274246216</t>
@@ -2378,13 +2378,13 @@
     <t xml:space="preserve">7.14475393295288</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13895988464355</t>
+    <t xml:space="preserve">7.1389594078064</t>
   </si>
   <si>
     <t xml:space="preserve">7.17759037017822</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05976581573486</t>
+    <t xml:space="preserve">7.05976676940918</t>
   </si>
   <si>
     <t xml:space="preserve">7.20463180541992</t>
@@ -2393,10 +2393,10 @@
     <t xml:space="preserve">7.06942415237427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31279706954956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33018159866333</t>
+    <t xml:space="preserve">7.31279754638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33018112182617</t>
   </si>
   <si>
     <t xml:space="preserve">7.38619613647461</t>
@@ -2405,19 +2405,19 @@
     <t xml:space="preserve">7.44800567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44027900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58128118515015</t>
+    <t xml:space="preserve">7.44027853012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5812816619873</t>
   </si>
   <si>
     <t xml:space="preserve">7.27223539352417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26837253570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24326229095459</t>
+    <t xml:space="preserve">7.26837301254272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24326276779175</t>
   </si>
   <si>
     <t xml:space="preserve">7.34370231628418</t>
@@ -2426,10 +2426,10 @@
     <t xml:space="preserve">7.54844522476196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45380020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62667226791382</t>
+    <t xml:space="preserve">7.45379972457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62667274475098</t>
   </si>
   <si>
     <t xml:space="preserve">7.67013168334961</t>
@@ -2438,10 +2438,10 @@
     <t xml:space="preserve">7.70683145523071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84203910827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86425161361694</t>
+    <t xml:space="preserve">7.84203863143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86425065994263</t>
   </si>
   <si>
     <t xml:space="preserve">7.81499671936035</t>
@@ -2450,61 +2450,61 @@
     <t xml:space="preserve">7.75029039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92412900924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91350650787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82851886749268</t>
+    <t xml:space="preserve">7.92412996292114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91350603103638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82851839065552</t>
   </si>
   <si>
     <t xml:space="preserve">7.89322519302368</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98497247695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87294340133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02649974822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.885498046875</t>
+    <t xml:space="preserve">7.98497152328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87294435501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0265007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88549852371216</t>
   </si>
   <si>
     <t xml:space="preserve">7.83817577362061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2631139755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4272928237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21965408325195</t>
+    <t xml:space="preserve">8.26311302185059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42729473114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21965503692627</t>
   </si>
   <si>
     <t xml:space="preserve">8.22158432006836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28146266937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23220825195312</t>
+    <t xml:space="preserve">8.28146362304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23220920562744</t>
   </si>
   <si>
     <t xml:space="preserve">8.29594898223877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13659763336182</t>
+    <t xml:space="preserve">8.13659954071045</t>
   </si>
   <si>
     <t xml:space="preserve">8.20806407928467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21868896484375</t>
+    <t xml:space="preserve">8.21868801116943</t>
   </si>
   <si>
     <t xml:space="preserve">8.26601028442383</t>
@@ -2513,34 +2513,34 @@
     <t xml:space="preserve">8.43598556518555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39735412597656</t>
+    <t xml:space="preserve">8.39735507965088</t>
   </si>
   <si>
     <t xml:space="preserve">8.27760028839111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30753898620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24283313751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22834587097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39059352874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34327220916748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43405437469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3104362487793</t>
+    <t xml:space="preserve">8.30753993988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24283218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34423923492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22834777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39059448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3432731628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43405342102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31043434143066</t>
   </si>
   <si>
     <t xml:space="preserve">8.18102264404297</t>
@@ -2558,28 +2558,28 @@
     <t xml:space="preserve">8.58664608001709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47944641113281</t>
+    <t xml:space="preserve">8.47944450378418</t>
   </si>
   <si>
     <t xml:space="preserve">8.71799087524414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65907859802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75565624237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71412658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82132720947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94784450531006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01448059082031</t>
+    <t xml:space="preserve">8.65907764434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75565528869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71412754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82132816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94784355163574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01448154449463</t>
   </si>
   <si>
     <t xml:space="preserve">9.03959083557129</t>
@@ -2588,13 +2588,13 @@
     <t xml:space="preserve">9.06083869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85319709777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94011688232422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01641368865967</t>
+    <t xml:space="preserve">8.85319805145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94011783599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01641273498535</t>
   </si>
   <si>
     <t xml:space="preserve">9.05118083953857</t>
@@ -2645,25 +2645,25 @@
     <t xml:space="preserve">9.06180477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12554454803467</t>
+    <t xml:space="preserve">9.12554550170898</t>
   </si>
   <si>
     <t xml:space="preserve">9.0318660736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07629013061523</t>
+    <t xml:space="preserve">9.07629108428955</t>
   </si>
   <si>
     <t xml:space="preserve">8.80008125305176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93528938293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94687843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74020290374756</t>
+    <t xml:space="preserve">8.93528842926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94687747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74020385742188</t>
   </si>
   <si>
     <t xml:space="preserve">8.88893222808838</t>
@@ -2672,34 +2672,34 @@
     <t xml:space="preserve">8.66294193267822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50262451171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65714645385742</t>
+    <t xml:space="preserve">8.50262355804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65714740753174</t>
   </si>
   <si>
     <t xml:space="preserve">8.51035118103027</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59726905822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76724529266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89086437225342</t>
+    <t xml:space="preserve">8.59727001190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76724338531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8908634185791</t>
   </si>
   <si>
     <t xml:space="preserve">8.96426105499268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24626541137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51281929016113</t>
+    <t xml:space="preserve">9.24626636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26171970367432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5128173828125</t>
   </si>
   <si>
     <t xml:space="preserve">9.35443115234375</t>
@@ -2708,19 +2708,19 @@
     <t xml:space="preserve">9.29841709136963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44328308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4316930770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25012874603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13230514526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22501945495605</t>
+    <t xml:space="preserve">9.44328212738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43169403076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2501277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13230609893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22501850128174</t>
   </si>
   <si>
     <t xml:space="preserve">9.06856536865234</t>
@@ -2738,76 +2738,76 @@
     <t xml:space="preserve">9.36215877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12650966644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14775657653809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13037490844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15934658050537</t>
+    <t xml:space="preserve">9.12651062011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1477575302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13037395477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15934562683105</t>
   </si>
   <si>
     <t xml:space="preserve">9.12264728546143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00482368469238</t>
+    <t xml:space="preserve">9.0048246383667</t>
   </si>
   <si>
     <t xml:space="preserve">9.13616847991943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05890560150146</t>
+    <t xml:space="preserve">9.05890655517578</t>
   </si>
   <si>
     <t xml:space="preserve">9.04538631439209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83677864074707</t>
+    <t xml:space="preserve">8.83677959442139</t>
   </si>
   <si>
     <t xml:space="preserve">8.87347888946533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95267200469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9391508102417</t>
+    <t xml:space="preserve">8.95267295837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93914985656738</t>
   </si>
   <si>
     <t xml:space="preserve">8.86961650848389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88120555877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96619415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13809871673584</t>
+    <t xml:space="preserve">8.88120651245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96619319915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13809967041016</t>
   </si>
   <si>
     <t xml:space="preserve">9.02027606964111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90438365936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66487312316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59340572357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54125499725342</t>
+    <t xml:space="preserve">8.90438461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66487407684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59340667724609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5412540435791</t>
   </si>
   <si>
     <t xml:space="preserve">8.55284404754639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42149925231934</t>
+    <t xml:space="preserve">8.42150020599365</t>
   </si>
   <si>
     <t xml:space="preserve">8.38093852996826</t>
@@ -2819,25 +2819,25 @@
     <t xml:space="preserve">8.42343139648438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42536354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5470495223999</t>
+    <t xml:space="preserve">8.4253625869751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54705047607422</t>
   </si>
   <si>
     <t xml:space="preserve">8.49296569824219</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5856819152832</t>
+    <t xml:space="preserve">8.58568096160889</t>
   </si>
   <si>
     <t xml:space="preserve">8.51228141784668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5064868927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63590240478516</t>
+    <t xml:space="preserve">8.50648593902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63590145111084</t>
   </si>
   <si>
     <t xml:space="preserve">8.59533786773682</t>
@@ -2846,10 +2846,10 @@
     <t xml:space="preserve">8.65328407287598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57215881347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57795333862305</t>
+    <t xml:space="preserve">8.57215976715088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57795429229736</t>
   </si>
   <si>
     <t xml:space="preserve">8.82712268829346</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">8.86768436431885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94108390808105</t>
+    <t xml:space="preserve">8.94108295440674</t>
   </si>
   <si>
     <t xml:space="preserve">9.33704853057861</t>
@@ -2867,49 +2867,49 @@
     <t xml:space="preserve">9.31773281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4027214050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34477424621582</t>
+    <t xml:space="preserve">9.40272045135498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3447732925415</t>
   </si>
   <si>
     <t xml:space="preserve">9.38533782958984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44521331787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58235263824463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42976188659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44135189056396</t>
+    <t xml:space="preserve">9.44521427154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58235454559326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42976093292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44134998321533</t>
   </si>
   <si>
     <t xml:space="preserve">9.35250091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20570278167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28875923156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3158016204834</t>
+    <t xml:space="preserve">9.20570373535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2887601852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31580257415771</t>
   </si>
   <si>
     <t xml:space="preserve">9.34091186523438</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05697631835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19218254089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16320991516113</t>
+    <t xml:space="preserve">9.05697536468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19218349456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16320896148682</t>
   </si>
   <si>
     <t xml:space="preserve">9.04924869537354</t>
@@ -2918,46 +2918,46 @@
     <t xml:space="preserve">9.26751327514648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16900444030762</t>
+    <t xml:space="preserve">9.16900539398193</t>
   </si>
   <si>
     <t xml:space="preserve">9.36795330047607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5244083404541</t>
+    <t xml:space="preserve">9.52440738677979</t>
   </si>
   <si>
     <t xml:space="preserve">9.76391696929932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48963928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46839332580566</t>
+    <t xml:space="preserve">9.48963832855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46839237213135</t>
   </si>
   <si>
     <t xml:space="preserve">9.38726806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42589855194092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36408805847168</t>
+    <t xml:space="preserve">9.42589950561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36408996582031</t>
   </si>
   <si>
     <t xml:space="preserve">9.28296375274658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25978755950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24240207672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26364994049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28682804107666</t>
+    <t xml:space="preserve">9.25978660583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24240303039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26364898681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28682899475098</t>
   </si>
   <si>
     <t xml:space="preserve">9.3505687713623</t>
@@ -2966,16 +2966,16 @@
     <t xml:space="preserve">9.23081302642822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39885711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32932186126709</t>
+    <t xml:space="preserve">9.39885807037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32932090759277</t>
   </si>
   <si>
     <t xml:space="preserve">9.46452903747559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41624164581299</t>
+    <t xml:space="preserve">9.41624069213867</t>
   </si>
   <si>
     <t xml:space="preserve">9.63836765289307</t>
@@ -2984,10 +2984,10 @@
     <t xml:space="preserve">9.47225570678711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56497001647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64416122436523</t>
+    <t xml:space="preserve">9.56496906280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64416217803955</t>
   </si>
   <si>
     <t xml:space="preserve">9.76943683624268</t>
@@ -2996,31 +2996,31 @@
     <t xml:space="preserve">9.55384922027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73544788360596</t>
+    <t xml:space="preserve">9.73544692993164</t>
   </si>
   <si>
     <t xml:space="preserve">9.83255958557129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70340061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62959671020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60823059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52860069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63347911834717</t>
+    <t xml:space="preserve">9.70339965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62959575653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60823154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52859973907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63348007202148</t>
   </si>
   <si>
     <t xml:space="preserve">9.8811149597168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0025053024292</t>
+    <t xml:space="preserve">10.0025043487549</t>
   </si>
   <si>
     <t xml:space="preserve">10.0947618484497</t>
@@ -3041,22 +3041,22 @@
     <t xml:space="preserve">9.82284832000732</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81313705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82770347595215</t>
+    <t xml:space="preserve">9.81313610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82770442962646</t>
   </si>
   <si>
     <t xml:space="preserve">9.79856967926025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79371356964111</t>
+    <t xml:space="preserve">9.79371452331543</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656270980835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1675939559937</t>
+    <t xml:space="preserve">10.167594909668</t>
   </si>
   <si>
     <t xml:space="preserve">10.2355728149414</t>
@@ -3080,25 +3080,25 @@
     <t xml:space="preserve">10.2744169235229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3132610321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3909511566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5754642486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6337308883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8133878707886</t>
+    <t xml:space="preserve">10.3132619857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3909502029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5754632949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6337299346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8133869171143</t>
   </si>
   <si>
     <t xml:space="preserve">10.8182430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8328084945679</t>
+    <t xml:space="preserve">10.8328094482422</t>
   </si>
   <si>
     <t xml:space="preserve">10.8230981826782</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">10.8570871353149</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7551202774048</t>
+    <t xml:space="preserve">10.7551193237305</t>
   </si>
   <si>
     <t xml:space="preserve">10.7454090118408</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">10.7842531204224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0852994918823</t>
+    <t xml:space="preserve">11.0853004455566</t>
   </si>
   <si>
     <t xml:space="preserve">11.0755882263184</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">11.0464553833008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9687662124634</t>
+    <t xml:space="preserve">10.9687652587891</t>
   </si>
   <si>
     <t xml:space="preserve">11.0027551651001</t>
@@ -3146,16 +3146,16 @@
     <t xml:space="preserve">10.827953338623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.954197883606</t>
+    <t xml:space="preserve">10.9541988372803</t>
   </si>
   <si>
     <t xml:space="preserve">10.978476524353</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8667984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6531524658203</t>
+    <t xml:space="preserve">10.8667993545532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6531543731689</t>
   </si>
   <si>
     <t xml:space="preserve">10.7162752151489</t>
@@ -3164,28 +3164,28 @@
     <t xml:space="preserve">10.9930429458618</t>
   </si>
   <si>
-    <t xml:space="preserve">11.162989616394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0513105392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4009122848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4688920974731</t>
+    <t xml:space="preserve">11.1629886627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0513114929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4009132385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4688911437988</t>
   </si>
   <si>
     <t xml:space="preserve">11.4931688308716</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5174465179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5951356887817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5611476898193</t>
+    <t xml:space="preserve">11.51744556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5951366424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.561146736145</t>
   </si>
   <si>
     <t xml:space="preserve">11.5028800964355</t>
@@ -3200,19 +3200,19 @@
     <t xml:space="preserve">11.5660028457642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6097040176392</t>
+    <t xml:space="preserve">11.6097021102905</t>
   </si>
   <si>
     <t xml:space="preserve">11.721381187439</t>
   </si>
   <si>
-    <t xml:space="preserve">11.862193107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.745659828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6922473907471</t>
+    <t xml:space="preserve">11.8621940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7456588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6922483444214</t>
   </si>
   <si>
     <t xml:space="preserve">11.6825370788574</t>
@@ -3227,13 +3227,13 @@
     <t xml:space="preserve">11.4834575653076</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4251918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3814907073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.36692237854</t>
+    <t xml:space="preserve">11.4251909255981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3814897537231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3669233322144</t>
   </si>
   <si>
     <t xml:space="preserve">11.3329343795776</t>
@@ -3245,58 +3245,58 @@
     <t xml:space="preserve">11.5902814865112</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6971044540405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.570858001709</t>
+    <t xml:space="preserve">11.6971035003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5708589553833</t>
   </si>
   <si>
     <t xml:space="preserve">11.5757141113281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5125913619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.410623550415</t>
+    <t xml:space="preserve">11.5125904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4106245040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.5514364242554</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7068157196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.949595451355</t>
+    <t xml:space="preserve">11.7068147659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9495944976807</t>
   </si>
   <si>
     <t xml:space="preserve">11.9301719665527</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7942171096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7602252960205</t>
+    <t xml:space="preserve">11.7942152023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7602262496948</t>
   </si>
   <si>
     <t xml:space="preserve">11.8087825775146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8282051086426</t>
+    <t xml:space="preserve">11.8282041549683</t>
   </si>
   <si>
     <t xml:space="preserve">11.7505149841309</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9253168106079</t>
+    <t xml:space="preserve">11.9253158569336</t>
   </si>
   <si>
     <t xml:space="preserve">12.0175714492798</t>
   </si>
   <si>
-    <t xml:space="preserve">12.05641746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.036994934082</t>
+    <t xml:space="preserve">12.0564165115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0369939804077</t>
   </si>
   <si>
     <t xml:space="preserve">12.187518119812</t>
@@ -3320,19 +3320,19 @@
     <t xml:space="preserve">12.5322637557983</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5662527084351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9350271224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.012716293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0758390426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1729497909546</t>
+    <t xml:space="preserve">12.5662517547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9350280761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0127153396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0758399963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1729507446289</t>
   </si>
   <si>
     <t xml:space="preserve">12.3331851959229</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">12.3137636184692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4205856323242</t>
+    <t xml:space="preserve">12.4205846786499</t>
   </si>
   <si>
     <t xml:space="preserve">12.304051399231</t>
@@ -3350,28 +3350,28 @@
     <t xml:space="preserve">12.4108743667603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4448642730713</t>
+    <t xml:space="preserve">12.444863319397</t>
   </si>
   <si>
     <t xml:space="preserve">12.4157295227051</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5468311309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6439437866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7750434875488</t>
+    <t xml:space="preserve">12.5468301773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6439428329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7750425338745</t>
   </si>
   <si>
     <t xml:space="preserve">12.9644107818604</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9595556259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9401321411133</t>
+    <t xml:space="preserve">12.9595546722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9401330947876</t>
   </si>
   <si>
     <t xml:space="preserve">13.0760898590088</t>
@@ -3380,7 +3380,7 @@
     <t xml:space="preserve">12.5808210372925</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5953874588013</t>
+    <t xml:space="preserve">12.595386505127</t>
   </si>
   <si>
     <t xml:space="preserve">12.9109992980957</t>
@@ -3389,37 +3389,37 @@
     <t xml:space="preserve">12.4837083816528</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7070655822754</t>
+    <t xml:space="preserve">12.7070665359497</t>
   </si>
   <si>
     <t xml:space="preserve">12.4982748031616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4739980697632</t>
+    <t xml:space="preserve">12.4739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">12.3428964614868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.639087677002</t>
+    <t xml:space="preserve">12.6390867233276</t>
   </si>
   <si>
     <t xml:space="preserve">12.8721551895142</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6099529266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.585675239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3768854141235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4885635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.284628868103</t>
+    <t xml:space="preserve">12.6099538803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5856771469116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3768844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.488564491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2846279144287</t>
   </si>
   <si>
     <t xml:space="preserve">12.2797737121582</t>
@@ -3431,13 +3431,13 @@
     <t xml:space="preserve">12.4400081634521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3720302581787</t>
+    <t xml:space="preserve">12.3720293045044</t>
   </si>
   <si>
     <t xml:space="preserve">12.435152053833</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3963088989258</t>
+    <t xml:space="preserve">12.3963079452515</t>
   </si>
   <si>
     <t xml:space="preserve">12.4060182571411</t>
@@ -3449,22 +3449,22 @@
     <t xml:space="preserve">11.6728258132935</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6388359069824</t>
+    <t xml:space="preserve">11.6388368606567</t>
   </si>
   <si>
     <t xml:space="preserve">11.4397573471069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1532783508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2164011001587</t>
+    <t xml:space="preserve">11.1532773971558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2164001464844</t>
   </si>
   <si>
     <t xml:space="preserve">11.0804443359375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.065878868103</t>
+    <t xml:space="preserve">11.0658769607544</t>
   </si>
   <si>
     <t xml:space="preserve">10.6968536376953</t>
@@ -3473,10 +3473,10 @@
     <t xml:space="preserve">10.6434421539307</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6191654205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5171957015991</t>
+    <t xml:space="preserve">10.6191644668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5171966552734</t>
   </si>
   <si>
     <t xml:space="preserve">10.7696876525879</t>
@@ -3494,25 +3494,25 @@
     <t xml:space="preserve">10.5269079208374</t>
   </si>
   <si>
-    <t xml:space="preserve">10.44921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5317630767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4880638122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3375406265259</t>
+    <t xml:space="preserve">10.4492177963257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5317640304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4880628585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3375415802002</t>
   </si>
   <si>
     <t xml:space="preserve">10.0899057388306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1821613311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1918706893921</t>
+    <t xml:space="preserve">10.1821603775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1918725967407</t>
   </si>
   <si>
     <t xml:space="preserve">10.264705657959</t>
@@ -3530,22 +3530,22 @@
     <t xml:space="preserve">9.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04304027557373</t>
+    <t xml:space="preserve">9.04304122924805</t>
   </si>
   <si>
     <t xml:space="preserve">9.04498386383057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06246280670166</t>
+    <t xml:space="preserve">9.06246185302734</t>
   </si>
   <si>
     <t xml:space="preserve">8.84299087524414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83910655975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54388618469238</t>
+    <t xml:space="preserve">8.83910751342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5438871383667</t>
   </si>
   <si>
     <t xml:space="preserve">9.1440372467041</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">8.99836921691895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03138732910156</t>
+    <t xml:space="preserve">9.0313892364502</t>
   </si>
   <si>
     <t xml:space="preserve">9.58492469787598</t>
@@ -3581,16 +3581,16 @@
     <t xml:space="preserve">9.63736438751221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62571239471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0801944732666</t>
+    <t xml:space="preserve">9.62571144104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0801935195923</t>
   </si>
   <si>
     <t xml:space="preserve">10.2598505020142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2501401901245</t>
+    <t xml:space="preserve">10.2501392364502</t>
   </si>
   <si>
     <t xml:space="preserve">10.4200839996338</t>
@@ -3599,7 +3599,7 @@
     <t xml:space="preserve">10.3860950469971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5074844360352</t>
+    <t xml:space="preserve">10.5074853897095</t>
   </si>
   <si>
     <t xml:space="preserve">10.4346513748169</t>
@@ -3608,7 +3608,7 @@
     <t xml:space="preserve">10.4152297973633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3278293609619</t>
+    <t xml:space="preserve">10.3278284072876</t>
   </si>
   <si>
     <t xml:space="preserve">10.2110719680786</t>
@@ -3629,7 +3629,7 @@
     <t xml:space="preserve">10.4210567474365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4259405136108</t>
+    <t xml:space="preserve">10.4259395599365</t>
   </si>
   <si>
     <t xml:space="preserve">10.5333738327026</t>
@@ -3647,7 +3647,7 @@
     <t xml:space="preserve">10.1720056533813</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5498685836792</t>
+    <t xml:space="preserve">9.54986763000488</t>
   </si>
   <si>
     <t xml:space="preserve">9.33890724182129</t>
@@ -3668,28 +3668,28 @@
     <t xml:space="preserve">10.0059728622437</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91318893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59870147705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39750671386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36234760284424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6182336807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40532112121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47173404693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47368717193604</t>
+    <t xml:space="preserve">9.91318798065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59870052337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3975076675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36234664916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61823463439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4053201675415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47173500061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47368812561035</t>
   </si>
   <si>
     <t xml:space="preserve">9.659255027771</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">9.69441413879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.665114402771</t>
+    <t xml:space="preserve">9.66511535644531</t>
   </si>
   <si>
     <t xml:space="preserve">9.87412166595459</t>
@@ -3716,7 +3716,7 @@
     <t xml:space="preserve">9.68074131011963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54791450500488</t>
+    <t xml:space="preserve">9.54791355133057</t>
   </si>
   <si>
     <t xml:space="preserve">9.03418636322021</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">8.8154125213623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20607948303223</t>
+    <t xml:space="preserve">9.20608043670654</t>
   </si>
   <si>
     <t xml:space="preserve">9.11427211761475</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">9.52252101898193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5674467086792</t>
+    <t xml:space="preserve">9.56744766235352</t>
   </si>
   <si>
     <t xml:space="preserve">9.46782779693604</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">9.79110431671143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85947132110596</t>
+    <t xml:space="preserve">9.85947227478027</t>
   </si>
   <si>
     <t xml:space="preserve">9.91807174682617</t>
@@ -3764,16 +3764,16 @@
     <t xml:space="preserve">9.80087089538574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72566890716553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.661208152771</t>
+    <t xml:space="preserve">9.72566795349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66120910644531</t>
   </si>
   <si>
     <t xml:space="preserve">9.95713806152344</t>
   </si>
   <si>
-    <t xml:space="preserve">10.001088142395</t>
+    <t xml:space="preserve">10.0010890960693</t>
   </si>
   <si>
     <t xml:space="preserve">10.162239074707</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">10.2989730834961</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0499229431152</t>
+    <t xml:space="preserve">10.0499219894409</t>
   </si>
   <si>
     <t xml:space="preserve">9.94248867034912</t>
@@ -3791,7 +3791,7 @@
     <t xml:space="preserve">9.9376049041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96690559387207</t>
+    <t xml:space="preserve">9.96690464019775</t>
   </si>
   <si>
     <t xml:space="preserve">9.88877201080322</t>
@@ -3800,7 +3800,7 @@
     <t xml:space="preserve">10.1329393386841</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2354888916016</t>
+    <t xml:space="preserve">10.2354879379272</t>
   </si>
   <si>
     <t xml:space="preserve">10.4161729812622</t>
@@ -3809,13 +3809,13 @@
     <t xml:space="preserve">10.18665599823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.167121887207</t>
+    <t xml:space="preserve">10.1671228408813</t>
   </si>
   <si>
     <t xml:space="preserve">10.5675563812256</t>
   </si>
   <si>
-    <t xml:space="preserve">10.367338180542</t>
+    <t xml:space="preserve">10.3673391342163</t>
   </si>
   <si>
     <t xml:space="preserve">10.1182880401611</t>
@@ -3827,7 +3827,7 @@
     <t xml:space="preserve">9.97667217254639</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81063747406006</t>
+    <t xml:space="preserve">9.81063842773438</t>
   </si>
   <si>
     <t xml:space="preserve">9.79598808288574</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">10.0352716445923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1134052276611</t>
+    <t xml:space="preserve">10.1134042739868</t>
   </si>
   <si>
     <t xml:space="preserve">10.1475896835327</t>
@@ -3851,7 +3851,7 @@
     <t xml:space="preserve">10.152473449707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98155498504639</t>
+    <t xml:space="preserve">9.9815559387207</t>
   </si>
   <si>
     <t xml:space="preserve">9.83505439758301</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">9.20803356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32914066314697</t>
+    <t xml:space="preserve">9.32913970947266</t>
   </si>
   <si>
     <t xml:space="preserve">9.1298999786377</t>
@@ -3878,7 +3878,7 @@
     <t xml:space="preserve">9.33109378814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46001434326172</t>
+    <t xml:space="preserve">9.4600133895874</t>
   </si>
   <si>
     <t xml:space="preserve">9.29593372344971</t>
@@ -3890,7 +3890,7 @@
     <t xml:space="preserve">8.9658203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00683975219727</t>
+    <t xml:space="preserve">9.00684070587158</t>
   </si>
   <si>
     <t xml:space="preserve">8.94042682647705</t>
@@ -3899,46 +3899,46 @@
     <t xml:space="preserve">9.0752067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78025150299072</t>
+    <t xml:space="preserve">8.78025245666504</t>
   </si>
   <si>
     <t xml:space="preserve">8.68649291992188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89550018310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84471321105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88377857208252</t>
+    <t xml:space="preserve">8.89549922943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84471225738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88377952575684</t>
   </si>
   <si>
     <t xml:space="preserve">8.72360515594482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89940738677979</t>
+    <t xml:space="preserve">8.89940643310547</t>
   </si>
   <si>
     <t xml:space="preserve">8.73532581329346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01074600219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78806591033936</t>
+    <t xml:space="preserve">9.01074695587158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78806686401367</t>
   </si>
   <si>
     <t xml:space="preserve">8.88964080810547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79783344268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94628715515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98144626617432</t>
+    <t xml:space="preserve">8.79783248901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94628620147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98144721984863</t>
   </si>
   <si>
     <t xml:space="preserve">8.78611278533936</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">8.96191215515137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84080505371094</t>
+    <t xml:space="preserve">8.84080600738525</t>
   </si>
   <si>
     <t xml:space="preserve">8.60054492950439</t>
@@ -3959,16 +3959,16 @@
     <t xml:space="preserve">8.45209217071533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72165298461914</t>
+    <t xml:space="preserve">8.72165203094482</t>
   </si>
   <si>
     <t xml:space="preserve">8.90917301177979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79587936401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80173969268799</t>
+    <t xml:space="preserve">8.79587841033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80173873901367</t>
   </si>
   <si>
     <t xml:space="preserve">8.70798015594482</t>
@@ -3980,7 +3980,7 @@
     <t xml:space="preserve">8.99707317352295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10841369628906</t>
+    <t xml:space="preserve">9.10841464996338</t>
   </si>
   <si>
     <t xml:space="preserve">8.96386623382568</t>
@@ -4004,7 +4004,7 @@
     <t xml:space="preserve">9.54205513000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4932222366333</t>
+    <t xml:space="preserve">9.49322128295898</t>
   </si>
   <si>
     <t xml:space="preserve">9.5654935836792</t>
@@ -4016,22 +4016,22 @@
     <t xml:space="preserve">9.76278209686279</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1280546188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96202182769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83993816375732</t>
+    <t xml:space="preserve">10.1280555725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96202087402344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83993721008301</t>
   </si>
   <si>
     <t xml:space="preserve">9.80575466156006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69050788879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72371387481689</t>
+    <t xml:space="preserve">9.69050884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72371482849121</t>
   </si>
   <si>
     <t xml:space="preserve">9.75692176818848</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">9.95225429534912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58502769470215</t>
+    <t xml:space="preserve">9.58502864837646</t>
   </si>
   <si>
     <t xml:space="preserve">9.62214088439941</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">9.5108003616333</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40336799621582</t>
+    <t xml:space="preserve">9.4033670425415</t>
   </si>
   <si>
     <t xml:space="preserve">9.38774013519287</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">9.45806121826172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26272773742676</t>
+    <t xml:space="preserve">9.26272678375244</t>
   </si>
   <si>
     <t xml:space="preserve">9.33500003814697</t>
@@ -4082,13 +4082,13 @@
     <t xml:space="preserve">9.63190841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64948844909668</t>
+    <t xml:space="preserve">9.64948749542236</t>
   </si>
   <si>
     <t xml:space="preserve">9.65729999542236</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74324798583984</t>
+    <t xml:space="preserve">9.74324703216553</t>
   </si>
   <si>
     <t xml:space="preserve">9.71199512481689</t>
@@ -4097,7 +4097,7 @@
     <t xml:space="preserve">9.71785354614258</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44438648223877</t>
+    <t xml:space="preserve">9.44438743591309</t>
   </si>
   <si>
     <t xml:space="preserve">9.42876052856445</t>
@@ -4106,19 +4106,19 @@
     <t xml:space="preserve">9.43852615356445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71590137481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0303888320923</t>
+    <t xml:space="preserve">9.71590232849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0303897857666</t>
   </si>
   <si>
     <t xml:space="preserve">9.90342235565186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83017158508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1427068710327</t>
+    <t xml:space="preserve">9.83017063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1427059173584</t>
   </si>
   <si>
     <t xml:space="preserve">10.2696733474731</t>
@@ -4136,19 +4136,19 @@
     <t xml:space="preserve">10.3380393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4796562194824</t>
+    <t xml:space="preserve">10.4796552658081</t>
   </si>
   <si>
     <t xml:space="preserve">10.2550220489502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3722219467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3478059768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5870895385742</t>
+    <t xml:space="preserve">10.3722229003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.347806930542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5870904922485</t>
   </si>
   <si>
     <t xml:space="preserve">10.5382566452026</t>
@@ -4157,7 +4157,7 @@
     <t xml:space="preserve">10.4698905944824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405889511108</t>
+    <t xml:space="preserve">10.4405899047852</t>
   </si>
   <si>
     <t xml:space="preserve">10.3917560577393</t>
@@ -4187,10 +4187,10 @@
     <t xml:space="preserve">10.860556602478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8312568664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7775392532349</t>
+    <t xml:space="preserve">10.8312578201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7775402069092</t>
   </si>
   <si>
     <t xml:space="preserve">10.880090713501</t>
@@ -4202,28 +4202,28 @@
     <t xml:space="preserve">10.9875240325928</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0314741134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0070581436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1291418075562</t>
+    <t xml:space="preserve">11.03147315979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0070571899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1291408538818</t>
   </si>
   <si>
     <t xml:space="preserve">11.2463417053223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2268085479736</t>
+    <t xml:space="preserve">11.2268075942993</t>
   </si>
   <si>
     <t xml:space="preserve">11.212158203125</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2072744369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2561082839966</t>
+    <t xml:space="preserve">11.207275390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2561073303223</t>
   </si>
   <si>
     <t xml:space="preserve">11.2854080200195</t>
@@ -4232,10 +4232,10 @@
     <t xml:space="preserve">11.3195915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3488922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.373309135437</t>
+    <t xml:space="preserve">11.3488912582397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3733081817627</t>
   </si>
   <si>
     <t xml:space="preserve">11.5295753479004</t>
@@ -5922,6 +5922,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.88199996948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89799976348877</t>
   </si>
 </sst>
 </file>
@@ -71052,7 +71055,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6496180556</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>6104205</v>
@@ -71073,6 +71076,32 @@
         <v>1969</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.6494328704</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>5105913</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>5.92600011825562</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>5.85200023651123</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>5.88800001144409</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>5.89799976348877</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>1970</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1973" uniqueCount="1973">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1974" uniqueCount="1974">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59865665435791</t>
+    <t xml:space="preserve">3.59865641593933</t>
   </si>
   <si>
     <t xml:space="preserve">CPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65898203849792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60329699516296</t>
+    <t xml:space="preserve">3.65898251533508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60329723358154</t>
   </si>
   <si>
     <t xml:space="preserve">3.51976919174194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51048898696899</t>
+    <t xml:space="preserve">3.51048851013184</t>
   </si>
   <si>
     <t xml:space="preserve">3.54993200302124</t>
@@ -71,73 +71,73 @@
     <t xml:space="preserve">3.52672958374023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48264575004578</t>
+    <t xml:space="preserve">3.48264598846436</t>
   </si>
   <si>
     <t xml:space="preserve">3.56617331504822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43392109870911</t>
+    <t xml:space="preserve">3.43392157554626</t>
   </si>
   <si>
     <t xml:space="preserve">3.50584769248962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56153321266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64274072647095</t>
+    <t xml:space="preserve">3.56153345108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64274096488953</t>
   </si>
   <si>
     <t xml:space="preserve">3.66594290733337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56849360466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74250984191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72162818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70770645141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47104454040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44320225715637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28078699111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33183193206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40839862823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22046113014221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26918601989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32487106323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24366354942322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32255053520203</t>
+    <t xml:space="preserve">3.56849384307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74250960350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72162842750549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70770692825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47104477882385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44320201873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28078722953796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33183145523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40839886665344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22046089172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26918578147888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32487082481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24366331100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32255077362061</t>
   </si>
   <si>
     <t xml:space="preserve">3.28774785995483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31791067123413</t>
+    <t xml:space="preserve">3.31791019439697</t>
   </si>
   <si>
     <t xml:space="preserve">3.36663460731506</t>
@@ -146,151 +146,151 @@
     <t xml:space="preserve">3.36199450492859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40607881546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38287687301636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36431431770325</t>
+    <t xml:space="preserve">3.40607857704163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3828763961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36431479454041</t>
   </si>
   <si>
     <t xml:space="preserve">3.53137040138245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60561752319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61257791519165</t>
+    <t xml:space="preserve">3.60561728477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61257767677307</t>
   </si>
   <si>
     <t xml:space="preserve">3.56385326385498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61489772796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63810086250305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6891450881958</t>
+    <t xml:space="preserve">3.61489844322205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63810038566589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68914484977722</t>
   </si>
   <si>
     <t xml:space="preserve">3.87476253509521</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95597004890442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00701475143433</t>
+    <t xml:space="preserve">3.95596957206726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00701570510864</t>
   </si>
   <si>
     <t xml:space="preserve">4.04877853393555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03485679626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04181718826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03717756271362</t>
+    <t xml:space="preserve">4.03485727310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04181814193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03717803955078</t>
   </si>
   <si>
     <t xml:space="preserve">4.05109882354736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01861572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09286212921143</t>
+    <t xml:space="preserve">4.01861619949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09286260604858</t>
   </si>
   <si>
     <t xml:space="preserve">4.07662105560303</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03949785232544</t>
+    <t xml:space="preserve">4.03949737548828</t>
   </si>
   <si>
     <t xml:space="preserve">4.08358240127563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02325677871704</t>
+    <t xml:space="preserve">4.02325582504272</t>
   </si>
   <si>
     <t xml:space="preserve">4.00005435943604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06038093566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99541306495667</t>
+    <t xml:space="preserve">4.06037998199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99541449546814</t>
   </si>
   <si>
     <t xml:space="preserve">3.94436931610107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97453212738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00237464904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93740773200989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94668984413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03021669387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05341863632202</t>
+    <t xml:space="preserve">3.97453141212463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00237417221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93740820884705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94668936729431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03021717071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05341911315918</t>
   </si>
   <si>
     <t xml:space="preserve">4.00933504104614</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95828986167908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98613357543945</t>
+    <t xml:space="preserve">3.95829033851624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98613286018372</t>
   </si>
   <si>
     <t xml:space="preserve">4.0255765914917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96989178657532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9118857383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89796471595764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87708210945129</t>
+    <t xml:space="preserve">3.96989226341248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91188621520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8979651927948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87708282470703</t>
   </si>
   <si>
     <t xml:space="preserve">3.9142062664032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9281268119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9513304233551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06733989715576</t>
+    <t xml:space="preserve">3.92812728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95132946968079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06734132766724</t>
   </si>
   <si>
     <t xml:space="preserve">4.08126211166382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99309325218201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96757054328918</t>
+    <t xml:space="preserve">3.99309372901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96757102012634</t>
   </si>
   <si>
     <t xml:space="preserve">3.98149228096008</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">3.96293091773987</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8886833190918</t>
+    <t xml:space="preserve">3.88868355751038</t>
   </si>
   <si>
     <t xml:space="preserve">3.89332413673401</t>
@@ -308,31 +308,31 @@
     <t xml:space="preserve">3.79587531089783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89309930801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02677726745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08540821075439</t>
+    <t xml:space="preserve">3.89309906959534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02677774429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08540868759155</t>
   </si>
   <si>
     <t xml:space="preserve">4.07602739334106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08306312561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09947967529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07368230819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0900993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10182476043701</t>
+    <t xml:space="preserve">4.08306264877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09948062896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07368278503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09009838104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10182523727417</t>
   </si>
   <si>
     <t xml:space="preserve">4.0877537727356</t>
@@ -344,58 +344,58 @@
     <t xml:space="preserve">4.08071851730347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01974153518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90482521057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85557532310486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85792112350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86495590209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87199211120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86964631080627</t>
+    <t xml:space="preserve">4.01974201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90482497215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85557579994202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85792064666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86495542526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87199187278748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86964702606201</t>
   </si>
   <si>
     <t xml:space="preserve">4.00567054748535</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00801610946655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95876574516296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05961179733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88606333732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88840842247009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04084968566895</t>
+    <t xml:space="preserve">4.00801563262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95876502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05961084365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88606262207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88840794563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04084920883179</t>
   </si>
   <si>
     <t xml:space="preserve">4.1651463508606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15576601028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14873075485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13231420516968</t>
+    <t xml:space="preserve">4.15576553344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14872980117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13231372833252</t>
   </si>
   <si>
     <t xml:space="preserve">4.00332546234131</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">4.04319429397583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16045665740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15811109542847</t>
+    <t xml:space="preserve">4.16045570373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15811157226562</t>
   </si>
   <si>
     <t xml:space="preserve">4.11589622497559</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06899213790894</t>
+    <t xml:space="preserve">4.06899166107178</t>
   </si>
   <si>
     <t xml:space="preserve">4.13465881347656</t>
@@ -422,55 +422,55 @@
     <t xml:space="preserve">4.14169406890869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18390846252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16280174255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21908712387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29179000854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29648017883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31055164337158</t>
+    <t xml:space="preserve">4.18390893936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16280126571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21908807754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29178905487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29648113250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31055212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.28709936141968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33165884017944</t>
+    <t xml:space="preserve">4.33165836334229</t>
   </si>
   <si>
     <t xml:space="preserve">4.33869457244873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5403847694397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51458787918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52162408828735</t>
+    <t xml:space="preserve">4.54038524627686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51458740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52162313461304</t>
   </si>
   <si>
     <t xml:space="preserve">4.43719482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47940874099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45595645904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66233682632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67171859741211</t>
+    <t xml:space="preserve">4.47940921783447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45595598220825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66233777999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67171812057495</t>
   </si>
   <si>
     <t xml:space="preserve">4.58963537216187</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">4.55914783477783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56383848190308</t>
+    <t xml:space="preserve">4.56383800506592</t>
   </si>
   <si>
     <t xml:space="preserve">4.54976558685303</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">4.60370683670044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59667110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57321977615356</t>
+    <t xml:space="preserve">4.59667062759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57321882247925</t>
   </si>
   <si>
     <t xml:space="preserve">4.62012434005737</t>
@@ -503,13 +503,13 @@
     <t xml:space="preserve">4.65061140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57556343078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70455169677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67406368255615</t>
+    <t xml:space="preserve">4.57556390762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70455265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67406320571899</t>
   </si>
   <si>
     <t xml:space="preserve">4.70924234390259</t>
@@ -518,40 +518,40 @@
     <t xml:space="preserve">4.60136127471924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48644399642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46533823013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39967107772827</t>
+    <t xml:space="preserve">4.4864444732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46533727645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39967060089111</t>
   </si>
   <si>
     <t xml:space="preserve">4.43250417709351</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50520706176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.491135597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51693296432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50286149978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4887900352478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65295648574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66468334197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73269462585449</t>
+    <t xml:space="preserve">4.50520610809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49113464355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51693344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50286197662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48878955841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65295696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66468238830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73269510269165</t>
   </si>
   <si>
     <t xml:space="preserve">4.71393299102783</t>
@@ -560,82 +560,82 @@
     <t xml:space="preserve">4.69048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58728981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56852865219116</t>
+    <t xml:space="preserve">4.58729028701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.568528175354</t>
   </si>
   <si>
     <t xml:space="preserve">4.47471857070923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44657468795776</t>
+    <t xml:space="preserve">4.4465765953064</t>
   </si>
   <si>
     <t xml:space="preserve">4.54742097854614</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44188594818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50051641464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52631378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36683797836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37152767181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33400440216064</t>
+    <t xml:space="preserve">4.44188547134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50051689147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52631330490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36683750152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37152814865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33400392532349</t>
   </si>
   <si>
     <t xml:space="preserve">4.3293137550354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3058614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30351591110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25661134719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20736122131348</t>
+    <t xml:space="preserve">4.30586099624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30351638793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25661039352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20736074447632</t>
   </si>
   <si>
     <t xml:space="preserve">4.09478950500488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24253940582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20267152786255</t>
+    <t xml:space="preserve">4.24254035949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20267057418823</t>
   </si>
   <si>
     <t xml:space="preserve">3.95642066001892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95407485961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03381299972534</t>
+    <t xml:space="preserve">3.95407557487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0338134765625</t>
   </si>
   <si>
     <t xml:space="preserve">4.12527799606323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01739692687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12996912002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17218399047852</t>
+    <t xml:space="preserve">4.01739645004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12996864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17218351364136</t>
   </si>
   <si>
     <t xml:space="preserve">4.21205139160156</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">4.2495756149292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20501518249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26833724975586</t>
+    <t xml:space="preserve">4.20501661300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26833820343018</t>
   </si>
   <si>
     <t xml:space="preserve">4.22846794128418</t>
   </si>
   <si>
-    <t xml:space="preserve">4.247230052948</t>
+    <t xml:space="preserve">4.24723052978516</t>
   </si>
   <si>
     <t xml:space="preserve">4.31993246078491</t>
@@ -665,73 +665,73 @@
     <t xml:space="preserve">4.36449241638184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28944444656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27771759033203</t>
+    <t xml:space="preserve">4.28944492340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27771854400635</t>
   </si>
   <si>
     <t xml:space="preserve">4.30117130279541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32227897644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35745668411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34807538986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34338474273682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39028978347778</t>
+    <t xml:space="preserve">4.32227754592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35745716094971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3480749130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34338521957397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39028930664062</t>
   </si>
   <si>
     <t xml:space="preserve">4.36214780807495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32462358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39732599258423</t>
+    <t xml:space="preserve">4.324622631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39732456207275</t>
   </si>
   <si>
     <t xml:space="preserve">4.37387323379517</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36918210983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47002792358398</t>
+    <t xml:space="preserve">4.36918258666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4700288772583</t>
   </si>
   <si>
     <t xml:space="preserve">4.45830202102661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42546939849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43484926223755</t>
+    <t xml:space="preserve">4.42546892166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43485021591187</t>
   </si>
   <si>
     <t xml:space="preserve">4.46768236160278</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40201663970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3527660369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3855996131897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43953943252563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43015956878662</t>
+    <t xml:space="preserve">4.40201616287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35276508331299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38560009002686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43953990936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43015909194946</t>
   </si>
   <si>
     <t xml:space="preserve">4.49348068237305</t>
@@ -749,28 +749,28 @@
     <t xml:space="preserve">4.53804016113281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54507493972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58260011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57790899276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55211210250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57087278366089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53569459915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50755167007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58494472503662</t>
+    <t xml:space="preserve">4.5450758934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58259916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57790946960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55211162567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57087373733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53569412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50755214691162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58494424819946</t>
   </si>
   <si>
     <t xml:space="preserve">4.65530252456665</t>
@@ -779,61 +779,61 @@
     <t xml:space="preserve">4.74207592010498</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75614786148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80774259567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83119630813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8968620300293</t>
+    <t xml:space="preserve">4.75614738464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80774307250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83119487762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89686155319214</t>
   </si>
   <si>
     <t xml:space="preserve">4.94845724105835</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09855222702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0516471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12200450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04695701599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0563383102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99536180496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01881456375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02819538116455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03288507461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93907690048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9766001701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92500400543213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96721935272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08917236328125</t>
+    <t xml:space="preserve">5.09855270385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05164813995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12200546264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04695653915405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05633878707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99536228179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01881408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02819633483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03288555145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93907642364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97659921646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92500448226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96721982955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08917140960693</t>
   </si>
   <si>
     <t xml:space="preserve">5.17359972000122</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">5.14545726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1595287322998</t>
+    <t xml:space="preserve">5.15952825546265</t>
   </si>
   <si>
     <t xml:space="preserve">5.09386157989502</t>
@@ -866,52 +866,52 @@
     <t xml:space="preserve">5.60043382644653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6238865852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66140937805176</t>
+    <t xml:space="preserve">5.62388563156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66141033172607</t>
   </si>
   <si>
     <t xml:space="preserve">5.68486213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57698202133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60512495040894</t>
+    <t xml:space="preserve">5.57698154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60512447357178</t>
   </si>
   <si>
     <t xml:space="preserve">5.7223858833313</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69403457641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74128770828247</t>
+    <t xml:space="preserve">5.69403409957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74128723144531</t>
   </si>
   <si>
     <t xml:space="preserve">5.76491403579712</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75073862075806</t>
+    <t xml:space="preserve">5.7507381439209</t>
   </si>
   <si>
     <t xml:space="preserve">5.87832260131836</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86887264251709</t>
+    <t xml:space="preserve">5.86887168884277</t>
   </si>
   <si>
     <t xml:space="preserve">5.88304758071899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02008295059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99173069000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00118160247803</t>
+    <t xml:space="preserve">6.02008199691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9917311668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00118112564087</t>
   </si>
   <si>
     <t xml:space="preserve">5.93502712249756</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">5.85942077636719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80271768569946</t>
+    <t xml:space="preserve">5.80271673202515</t>
   </si>
   <si>
     <t xml:space="preserve">5.75546407699585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73183727264404</t>
+    <t xml:space="preserve">5.73183679580688</t>
   </si>
   <si>
     <t xml:space="preserve">5.84997034072876</t>
@@ -938,16 +938,16 @@
     <t xml:space="preserve">5.95865345001221</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93030214309692</t>
+    <t xml:space="preserve">5.93030166625977</t>
   </si>
   <si>
     <t xml:space="preserve">5.98227977752686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90194892883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91612482070923</t>
+    <t xml:space="preserve">5.90194940567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91612577438354</t>
   </si>
   <si>
     <t xml:space="preserve">5.91139984130859</t>
@@ -962,7 +962,7 @@
     <t xml:space="preserve">5.78381538391113</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80744218826294</t>
+    <t xml:space="preserve">5.8074426651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.84524536132812</t>
@@ -971,43 +971,43 @@
     <t xml:space="preserve">5.77436494827271</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82634449005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82161903381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85469579696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79326677322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8357949256897</t>
+    <t xml:space="preserve">5.82634401321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82161855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85469627380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79326581954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83579444885254</t>
   </si>
   <si>
     <t xml:space="preserve">5.95392847061157</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92557621002197</t>
+    <t xml:space="preserve">5.92557525634766</t>
   </si>
   <si>
     <t xml:space="preserve">5.94447708129883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77908992767334</t>
+    <t xml:space="preserve">5.77908945083618</t>
   </si>
   <si>
     <t xml:space="preserve">5.74601364135742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71766138076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65150594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66095733642578</t>
+    <t xml:space="preserve">5.71766090393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6515064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66095685958862</t>
   </si>
   <si>
     <t xml:space="preserve">5.79799175262451</t>
@@ -1019,40 +1019,40 @@
     <t xml:space="preserve">5.69876003265381</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66568231582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73656320571899</t>
+    <t xml:space="preserve">5.66568183898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73656225204468</t>
   </si>
   <si>
     <t xml:space="preserve">5.78854036331177</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76963949203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89249897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97282886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15239286422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1476674079895</t>
+    <t xml:space="preserve">5.76963996887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8924994468689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97282934188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15239238739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14766693115234</t>
   </si>
   <si>
     <t xml:space="preserve">6.28470182418823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13821601867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12404012680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02953386306763</t>
+    <t xml:space="preserve">6.13821649551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12404108047485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02953338623047</t>
   </si>
   <si>
     <t xml:space="preserve">6.10513877868652</t>
@@ -1061,16 +1061,16 @@
     <t xml:space="preserve">6.16656827926636</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11458921432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31777906417847</t>
+    <t xml:space="preserve">6.11458873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31777954101562</t>
   </si>
   <si>
     <t xml:space="preserve">6.34140634536743</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4075608253479</t>
+    <t xml:space="preserve">6.40756034851074</t>
   </si>
   <si>
     <t xml:space="preserve">6.50206756591797</t>
@@ -1079,16 +1079,16 @@
     <t xml:space="preserve">6.42173671722412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30832815170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47844076156616</t>
+    <t xml:space="preserve">6.30832862854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.478440284729</t>
   </si>
   <si>
     <t xml:space="preserve">6.31305360794067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33668088912964</t>
+    <t xml:space="preserve">6.33667993545532</t>
   </si>
   <si>
     <t xml:space="preserve">6.37448215484619</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">6.17601871490479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09096193313599</t>
+    <t xml:space="preserve">6.09096240997314</t>
   </si>
   <si>
     <t xml:space="preserve">6.23272323608398</t>
@@ -1112,22 +1112,22 @@
     <t xml:space="preserve">6.10041332244873</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10986423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00590705871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03425884246826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09568786621094</t>
+    <t xml:space="preserve">6.10986375808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00590658187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0342583656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09568738937378</t>
   </si>
   <si>
     <t xml:space="preserve">6.06261110305786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18074321746826</t>
+    <t xml:space="preserve">6.18074464797974</t>
   </si>
   <si>
     <t xml:space="preserve">6.08151197433472</t>
@@ -1139,19 +1139,19 @@
     <t xml:space="preserve">6.21382188796997</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24217367172241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24689865112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20909643173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22799730300903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19964551925659</t>
+    <t xml:space="preserve">6.24217319488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24689912796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20909690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22799777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19964504241943</t>
   </si>
   <si>
     <t xml:space="preserve">6.12876605987549</t>
@@ -1160,10 +1160,10 @@
     <t xml:space="preserve">6.07206153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05788612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13349103927612</t>
+    <t xml:space="preserve">6.05788469314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13349056243896</t>
   </si>
   <si>
     <t xml:space="preserve">6.14294195175171</t>
@@ -1172,22 +1172,22 @@
     <t xml:space="preserve">6.01063251495361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94920301437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97755432128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05316019058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99645614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06733655929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93975210189819</t>
+    <t xml:space="preserve">5.94920253753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97755479812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05315971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99645566940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0673360824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93975257873535</t>
   </si>
   <si>
     <t xml:space="preserve">5.71293544769287</t>
@@ -1196,97 +1196,97 @@
     <t xml:space="preserve">5.72711133956909</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92085027694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57590055465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52864694595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.42941522598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50502061843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61370372772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63733005523682</t>
+    <t xml:space="preserve">5.92084980010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5759015083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52864742279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.42941570281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50502014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61370420455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63733053207397</t>
   </si>
   <si>
     <t xml:space="preserve">6.04370927810669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98700428009033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01535749435425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89722347259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81689310073853</t>
+    <t xml:space="preserve">5.98700571060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01535654067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89722394943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81689357757568</t>
   </si>
   <si>
     <t xml:space="preserve">5.87359762191772</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8641471862793</t>
+    <t xml:space="preserve">5.86414670944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.9066743850708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96810436248779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01550769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02027034759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99169301986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08218765258789</t>
+    <t xml:space="preserve">5.96810388565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01550722122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02027082443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9916934967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08218717575073</t>
   </si>
   <si>
     <t xml:space="preserve">6.20602226257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18697023391724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08694982528687</t>
+    <t xml:space="preserve">6.18697071075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08695077896118</t>
   </si>
   <si>
     <t xml:space="preserve">6.07266187667847</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16315603256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27270269393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25365161895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13934183120728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2917537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38701200485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52513456344604</t>
+    <t xml:space="preserve">6.16315650939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27270317077637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25365114212036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13934278488159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29175329208374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38701152801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5251350402832</t>
   </si>
   <si>
     <t xml:space="preserve">6.59657764434814</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">6.5060830116272</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58228921890259</t>
+    <t xml:space="preserve">6.58228874206543</t>
   </si>
   <si>
     <t xml:space="preserve">6.65373277664185</t>
@@ -1322,10 +1322,10 @@
     <t xml:space="preserve">6.77280426025391</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82995843887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0252366065979</t>
+    <t xml:space="preserve">6.82995891571045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02523612976074</t>
   </si>
   <si>
     <t xml:space="preserve">6.92521572113037</t>
@@ -1334,10 +1334,10 @@
     <t xml:space="preserve">6.92045259475708</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01094770431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96808195114136</t>
+    <t xml:space="preserve">7.01094818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96808242797852</t>
   </si>
   <si>
     <t xml:space="preserve">6.91092729568481</t>
@@ -1349,10 +1349,10 @@
     <t xml:space="preserve">7.04905080795288</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09667873382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17764759063721</t>
+    <t xml:space="preserve">7.09667921066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17764854431152</t>
   </si>
   <si>
     <t xml:space="preserve">7.28243160247803</t>
@@ -1370,127 +1370,127 @@
     <t xml:space="preserve">7.12525701522827</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94903039932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86806154251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00142240524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00618457794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06333923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760725021362</t>
+    <t xml:space="preserve">6.94903087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86806106567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0014214515686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00618505477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0633397102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760677337646</t>
   </si>
   <si>
     <t xml:space="preserve">6.9918966293335</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03952407836914</t>
+    <t xml:space="preserve">7.0395245552063</t>
   </si>
   <si>
     <t xml:space="preserve">7.02047395706177</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07762813568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18717336654663</t>
+    <t xml:space="preserve">7.07762765884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18717384338379</t>
   </si>
   <si>
     <t xml:space="preserve">7.21098852157593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41579151153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29672002792358</t>
+    <t xml:space="preserve">7.4157919883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29671955108643</t>
   </si>
   <si>
     <t xml:space="preserve">7.26338005065918</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24432802200317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27290630340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30624580383301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18241119384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2538537979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05857610702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10620546340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14907121658325</t>
+    <t xml:space="preserve">7.24432849884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2729058265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30624532699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1824107170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25385332107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0585765838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10620498657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14907073974609</t>
   </si>
   <si>
     <t xml:space="preserve">7.1681227684021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90140151977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94426822662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06810235977173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98713397979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13001918792725</t>
+    <t xml:space="preserve">6.90140199661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94426727294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06810140609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98713302612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1300196647644</t>
   </si>
   <si>
     <t xml:space="preserve">6.87758684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7061243057251</t>
+    <t xml:space="preserve">6.70612382888794</t>
   </si>
   <si>
     <t xml:space="preserve">6.63944339752197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65849494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32985782623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19649696350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11552858352661</t>
+    <t xml:space="preserve">6.65849447250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32985687255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19649648666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11552762985229</t>
   </si>
   <si>
     <t xml:space="preserve">6.04884719848633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21554803848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3155689239502</t>
+    <t xml:space="preserve">6.21554851531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31556844711304</t>
   </si>
   <si>
     <t xml:space="preserve">6.33461999893188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34414529800415</t>
+    <t xml:space="preserve">6.34414482116699</t>
   </si>
   <si>
     <t xml:space="preserve">6.12505340576172</t>
@@ -1499,79 +1499,79 @@
     <t xml:space="preserve">6.15363073348999</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30604219436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35367155075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47274351119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46798086166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42987775802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52989816665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76804113388062</t>
+    <t xml:space="preserve">6.30604267120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35367107391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47274303436279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46798038482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42987728118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52989721298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76804161071777</t>
   </si>
   <si>
     <t xml:space="preserve">7.08239126205444</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11096811294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12049436569214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32529735565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31577062606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11573028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03476238250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15383386611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04428815841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02999973297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17288541793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36339998245239</t>
+    <t xml:space="preserve">7.11096858978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12049293518066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3252968788147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31577157974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11573076248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03476285934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15383434295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04428768157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02999925613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17288494110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36340093612671</t>
   </si>
   <si>
     <t xml:space="preserve">7.14430809020996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20622634887695</t>
+    <t xml:space="preserve">7.20622587203979</t>
   </si>
   <si>
     <t xml:space="preserve">7.32053422927856</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09191703796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98236989974976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44913148880005</t>
+    <t xml:space="preserve">7.09191608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98237085342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913196563721</t>
   </si>
   <si>
     <t xml:space="preserve">7.38245153427124</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">7.55391454696655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60630702972412</t>
+    <t xml:space="preserve">7.60630655288696</t>
   </si>
   <si>
     <t xml:space="preserve">7.46342086791992</t>
@@ -1601,40 +1601,40 @@
     <t xml:space="preserve">7.49199771881104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44436931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42055463790894</t>
+    <t xml:space="preserve">7.44436883926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42055511474609</t>
   </si>
   <si>
     <t xml:space="preserve">7.62535858154297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53010129928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47294616699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48723554611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46818351745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49676036834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51581239700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6110692024231</t>
+    <t xml:space="preserve">7.53010082244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47294664382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4872350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46818399429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49676132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51581192016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61107015609741</t>
   </si>
   <si>
     <t xml:space="preserve">7.56344079971313</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64440870285034</t>
+    <t xml:space="preserve">7.6444091796875</t>
   </si>
   <si>
     <t xml:space="preserve">7.73490428924561</t>
@@ -1643,58 +1643,58 @@
     <t xml:space="preserve">7.80634546279907</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86826419830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8587384223938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88731575012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92541885375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95399713516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83492565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98733711242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01115036010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06354236602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53486394882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52057456970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54438972473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62059545516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63964748382568</t>
+    <t xml:space="preserve">7.86826515197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85873937606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88731622695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92541837692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95399618148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83492517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9873366355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01115131378174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06354331970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53486347198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52057504653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5443902015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62059497833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63964653015137</t>
   </si>
   <si>
     <t xml:space="preserve">7.77777051925659</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76824378967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90636873245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03496646881104</t>
+    <t xml:space="preserve">7.76824474334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90636777877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03496551513672</t>
   </si>
   <si>
     <t xml:space="preserve">8.00638771057129</t>
@@ -1709,10 +1709,10 @@
     <t xml:space="preserve">8.2016658782959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32549858093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44457054138184</t>
+    <t xml:space="preserve">8.32549953460693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44457149505615</t>
   </si>
   <si>
     <t xml:space="preserve">8.33979034423828</t>
@@ -1721,10 +1721,10 @@
     <t xml:space="preserve">8.38265514373779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33502769470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27787113189697</t>
+    <t xml:space="preserve">8.33502674102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27787017822266</t>
   </si>
   <si>
     <t xml:space="preserve">8.23500633239746</t>
@@ -1733,22 +1733,22 @@
     <t xml:space="preserve">8.25882053375244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26358318328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16832447052002</t>
+    <t xml:space="preserve">8.26358413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16832637786865</t>
   </si>
   <si>
     <t xml:space="preserve">8.31121253967285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36836528778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35407829284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37789344787598</t>
+    <t xml:space="preserve">8.36836624145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.354079246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37789154052734</t>
   </si>
   <si>
     <t xml:space="preserve">8.28739643096924</t>
@@ -1757,37 +1757,37 @@
     <t xml:space="preserve">8.21119213104248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22071838378906</t>
+    <t xml:space="preserve">8.22071743011475</t>
   </si>
   <si>
     <t xml:space="preserve">8.43150520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44587802886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56085300445557</t>
+    <t xml:space="preserve">8.445876121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56085205078125</t>
   </si>
   <si>
     <t xml:space="preserve">8.51294612884521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48899269104004</t>
+    <t xml:space="preserve">8.48899173736572</t>
   </si>
   <si>
     <t xml:space="preserve">8.60875701904297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.441086769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49857425689697</t>
+    <t xml:space="preserve">8.44108581542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49857330322266</t>
   </si>
   <si>
     <t xml:space="preserve">8.4842004776001</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6710376739502</t>
+    <t xml:space="preserve">8.67103672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.81475448608398</t>
@@ -1805,10 +1805,10 @@
     <t xml:space="preserve">8.70936107635498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68540668487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70457172393799</t>
+    <t xml:space="preserve">8.6854076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70457077026367</t>
   </si>
   <si>
     <t xml:space="preserve">8.78122138977051</t>
@@ -1826,37 +1826,37 @@
     <t xml:space="preserve">8.53689861297607</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37880802154541</t>
+    <t xml:space="preserve">8.37880706787109</t>
   </si>
   <si>
     <t xml:space="preserve">8.37401676177979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40755081176758</t>
+    <t xml:space="preserve">8.40755176544189</t>
   </si>
   <si>
     <t xml:space="preserve">8.41234302520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32611083984375</t>
+    <t xml:space="preserve">8.32610988616943</t>
   </si>
   <si>
     <t xml:space="preserve">8.45545768737793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41713237762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39318084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54648017883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58959484100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27341461181641</t>
+    <t xml:space="preserve">8.41713333129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39317989349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54647922515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58959579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27341365814209</t>
   </si>
   <si>
     <t xml:space="preserve">8.25425148010254</t>
@@ -1865,10 +1865,10 @@
     <t xml:space="preserve">8.35485458374023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47461986541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42192459106445</t>
+    <t xml:space="preserve">8.4746208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42192363739014</t>
   </si>
   <si>
     <t xml:space="preserve">8.36922645568848</t>
@@ -1880,7 +1880,7 @@
     <t xml:space="preserve">8.29736804962158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28299713134766</t>
+    <t xml:space="preserve">8.28299617767334</t>
   </si>
   <si>
     <t xml:space="preserve">8.17760181427002</t>
@@ -1889,13 +1889,13 @@
     <t xml:space="preserve">8.2015552520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16322994232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24946022033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18239116668701</t>
+    <t xml:space="preserve">8.16323089599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24946117401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18239212036133</t>
   </si>
   <si>
     <t xml:space="preserve">8.17281055450439</t>
@@ -1904,31 +1904,31 @@
     <t xml:space="preserve">8.09616088867188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14885902404785</t>
+    <t xml:space="preserve">8.14885711669922</t>
   </si>
   <si>
     <t xml:space="preserve">8.06741714477539</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03867340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97160482406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78956031799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62188863754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61709785461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66021347045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50212335586548</t>
+    <t xml:space="preserve">8.03867435455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97160387039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78956079483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62188816070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61709833145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66021394729614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50212287902832</t>
   </si>
   <si>
     <t xml:space="preserve">7.72249221801758</t>
@@ -1943,40 +1943,40 @@
     <t xml:space="preserve">7.51170492172241</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65542268753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59793567657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90932750701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95244264602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82309484481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88058423995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10574340820312</t>
+    <t xml:space="preserve">7.65542364120483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59793519973755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90932607650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95244216918945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82309579849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8805832862854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10574150085449</t>
   </si>
   <si>
     <t xml:space="preserve">8.20634460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1680212020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26383304595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34527206420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29257678985596</t>
+    <t xml:space="preserve">8.16802024841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26383399963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34527397155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29257583618164</t>
   </si>
   <si>
     <t xml:space="preserve">8.12011337280273</t>
@@ -1991,13 +1991,13 @@
     <t xml:space="preserve">7.80872297286987</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91411685943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88537263870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82788610458374</t>
+    <t xml:space="preserve">7.91411733627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88537359237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82788562774658</t>
   </si>
   <si>
     <t xml:space="preserve">7.84704828262329</t>
@@ -2006,16 +2006,16 @@
     <t xml:space="preserve">8.00034809112549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89974594116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9045352935791</t>
+    <t xml:space="preserve">7.89974546432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90453624725342</t>
   </si>
   <si>
     <t xml:space="preserve">7.94286155700684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71770191192627</t>
+    <t xml:space="preserve">7.71770143508911</t>
   </si>
   <si>
     <t xml:space="preserve">7.85662937164307</t>
@@ -2024,22 +2024,22 @@
     <t xml:space="preserve">8.04346370697021</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11532306671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12969398498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13448619842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00992965698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93327903747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7512354850769</t>
+    <t xml:space="preserve">8.11532402038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12969493865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13448524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00993061065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93327951431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75123596191406</t>
   </si>
   <si>
     <t xml:space="preserve">7.578773021698</t>
@@ -2048,34 +2048,34 @@
     <t xml:space="preserve">7.64105176925659</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69374752044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83746767044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81351375579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87100172042847</t>
+    <t xml:space="preserve">7.69374847412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83746719360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8135142326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87100219726562</t>
   </si>
   <si>
     <t xml:space="preserve">7.87579250335693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92369842529297</t>
+    <t xml:space="preserve">7.92369890213013</t>
   </si>
   <si>
     <t xml:space="preserve">7.89495372772217</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85183763504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86621141433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9859766960144</t>
+    <t xml:space="preserve">7.85183715820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98597574234009</t>
   </si>
   <si>
     <t xml:space="preserve">7.96681356430054</t>
@@ -2084,31 +2084,31 @@
     <t xml:space="preserve">7.92848873138428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11053276062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04825401306152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93806934356689</t>
+    <t xml:space="preserve">8.11053371429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04825496673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93806886672974</t>
   </si>
   <si>
     <t xml:space="preserve">7.77997970581055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81830406188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84225749969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79435157775879</t>
+    <t xml:space="preserve">7.81830358505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84225797653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79435205459595</t>
   </si>
   <si>
     <t xml:space="preserve">7.7991418838501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94765090942383</t>
+    <t xml:space="preserve">7.94765186309814</t>
   </si>
   <si>
     <t xml:space="preserve">7.91890811920166</t>
@@ -2117,16 +2117,16 @@
     <t xml:space="preserve">7.7129111289978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77518939971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86141967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07699775695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21592617034912</t>
+    <t xml:space="preserve">7.77518844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86142063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07699871063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21592712402344</t>
   </si>
   <si>
     <t xml:space="preserve">8.26862335205078</t>
@@ -2135,13 +2135,13 @@
     <t xml:space="preserve">8.33569145202637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4506664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36443519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47941112518311</t>
+    <t xml:space="preserve">8.45066738128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36443614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47941017150879</t>
   </si>
   <si>
     <t xml:space="preserve">8.55127143859863</t>
@@ -2159,22 +2159,22 @@
     <t xml:space="preserve">8.69019794464111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58480548858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19197273254395</t>
+    <t xml:space="preserve">8.58480453491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19197368621826</t>
   </si>
   <si>
     <t xml:space="preserve">7.74165487289429</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70332908630371</t>
+    <t xml:space="preserve">7.70332956314087</t>
   </si>
   <si>
     <t xml:space="preserve">7.78477001190186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44463586807251</t>
+    <t xml:space="preserve">7.44463539123535</t>
   </si>
   <si>
     <t xml:space="preserve">7.22426652908325</t>
@@ -2186,31 +2186,31 @@
     <t xml:space="preserve">7.30091667175293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36319446563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33924198150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09492015838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6972975730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36195373535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33675956726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54754686355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37987470626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30322551727295</t>
+    <t xml:space="preserve">7.36319494247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33924150466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09491968154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69729709625244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36195421218872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33675909042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54754638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37987518310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30322504043579</t>
   </si>
   <si>
     <t xml:space="preserve">5.8685188293457</t>
@@ -2219,16 +2219,16 @@
     <t xml:space="preserve">6.45776605606079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08409738540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03619146347046</t>
+    <t xml:space="preserve">6.08409690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0361909866333</t>
   </si>
   <si>
     <t xml:space="preserve">6.29967546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76915693283081</t>
+    <t xml:space="preserve">6.76915740966797</t>
   </si>
   <si>
     <t xml:space="preserve">6.84101629257202</t>
@@ -2237,28 +2237,28 @@
     <t xml:space="preserve">6.53441667556763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37153577804565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27572298049927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02852630615234</t>
+    <t xml:space="preserve">6.3715353012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27572250366211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02852582931519</t>
   </si>
   <si>
     <t xml:space="preserve">6.11092472076416</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85606336593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45201730728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38111591339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32171201705933</t>
+    <t xml:space="preserve">5.85606288909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45201778411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38111543655396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32171249389648</t>
   </si>
   <si>
     <t xml:space="preserve">6.35237264633179</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">6.40986013412476</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40794372558594</t>
+    <t xml:space="preserve">6.4079442024231</t>
   </si>
   <si>
     <t xml:space="preserve">6.47309637069702</t>
@@ -2276,10 +2276,10 @@
     <t xml:space="preserve">6.65897274017334</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49962043762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44746923446655</t>
+    <t xml:space="preserve">6.49961996078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44746971130371</t>
   </si>
   <si>
     <t xml:space="preserve">6.43008518218994</t>
@@ -2288,10 +2288,10 @@
     <t xml:space="preserve">6.393385887146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44360589981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59619760513306</t>
+    <t xml:space="preserve">6.44360637664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59619808197021</t>
   </si>
   <si>
     <t xml:space="preserve">6.61551284790039</t>
@@ -2303,25 +2303,25 @@
     <t xml:space="preserve">6.82798194885254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62323951721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.690842628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76617240905762</t>
+    <t xml:space="preserve">6.62323904037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69084310531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76617288589478</t>
   </si>
   <si>
     <t xml:space="preserve">6.78935146331787</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94773721694946</t>
+    <t xml:space="preserve">6.94773769378662</t>
   </si>
   <si>
     <t xml:space="preserve">6.95932626724243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.084876537323</t>
+    <t xml:space="preserve">7.08487701416016</t>
   </si>
   <si>
     <t xml:space="preserve">6.93807935714722</t>
@@ -2336,16 +2336,16 @@
     <t xml:space="preserve">6.9400110244751</t>
   </si>
   <si>
-    <t xml:space="preserve">6.51121044158936</t>
+    <t xml:space="preserve">6.5112099647522</t>
   </si>
   <si>
     <t xml:space="preserve">6.67345905303955</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53245687484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6638011932373</t>
+    <t xml:space="preserve">6.53245639801025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66380167007446</t>
   </si>
   <si>
     <t xml:space="preserve">6.67732191085815</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">6.71209001541138</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1466851234436</t>
+    <t xml:space="preserve">7.14668560028076</t>
   </si>
   <si>
     <t xml:space="preserve">7.05010890960693</t>
@@ -2369,16 +2369,16 @@
     <t xml:space="preserve">7.1119179725647</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09839677810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14282274246216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14475393295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1389594078064</t>
+    <t xml:space="preserve">7.09839630126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.142822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14475440979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13895893096924</t>
   </si>
   <si>
     <t xml:space="preserve">7.17759037017822</t>
@@ -2399,28 +2399,28 @@
     <t xml:space="preserve">7.33018159866333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38619565963745</t>
+    <t xml:space="preserve">7.38619613647461</t>
   </si>
   <si>
     <t xml:space="preserve">7.44800519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44027853012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58128070831299</t>
+    <t xml:space="preserve">7.44027900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58128118515015</t>
   </si>
   <si>
     <t xml:space="preserve">7.27223539352417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26837301254272</t>
+    <t xml:space="preserve">7.26837253570557</t>
   </si>
   <si>
     <t xml:space="preserve">7.24326229095459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34370279312134</t>
+    <t xml:space="preserve">7.34370183944702</t>
   </si>
   <si>
     <t xml:space="preserve">7.54844522476196</t>
@@ -2438,25 +2438,25 @@
     <t xml:space="preserve">7.70683145523071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84203863143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86425161361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81499719619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75028991699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92412853240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91350650787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82851791381836</t>
+    <t xml:space="preserve">7.84203910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86425065994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81499671936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75029039382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92412948608398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91350555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82851839065552</t>
   </si>
   <si>
     <t xml:space="preserve">7.89322519302368</t>
@@ -2468,34 +2468,34 @@
     <t xml:space="preserve">7.87294435501099</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02649974822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.885498046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83817577362061</t>
+    <t xml:space="preserve">8.0265007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88549852371216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83817625045776</t>
   </si>
   <si>
     <t xml:space="preserve">8.2631139755249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42729473114014</t>
+    <t xml:space="preserve">8.42729377746582</t>
   </si>
   <si>
     <t xml:space="preserve">8.21965503692627</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22158432006836</t>
+    <t xml:space="preserve">8.22158527374268</t>
   </si>
   <si>
     <t xml:space="preserve">8.28146266937256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23221015930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29594993591309</t>
+    <t xml:space="preserve">8.23220825195312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29594898223877</t>
   </si>
   <si>
     <t xml:space="preserve">8.13659858703613</t>
@@ -2507,7 +2507,7 @@
     <t xml:space="preserve">8.21868896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26601028442383</t>
+    <t xml:space="preserve">8.26601123809814</t>
   </si>
   <si>
     <t xml:space="preserve">8.43598556518555</t>
@@ -2519,22 +2519,22 @@
     <t xml:space="preserve">8.27760028839111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30753898620605</t>
+    <t xml:space="preserve">8.30753993988037</t>
   </si>
   <si>
     <t xml:space="preserve">8.24283313751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22834587097168</t>
+    <t xml:space="preserve">8.34423923492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.228346824646</t>
   </si>
   <si>
     <t xml:space="preserve">8.39059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34327220916748</t>
+    <t xml:space="preserve">8.3432731628418</t>
   </si>
   <si>
     <t xml:space="preserve">8.43405437469482</t>
@@ -2543,10 +2543,10 @@
     <t xml:space="preserve">8.31043529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18102264404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29788112640381</t>
+    <t xml:space="preserve">8.18102169036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29788208007812</t>
   </si>
   <si>
     <t xml:space="preserve">8.48330879211426</t>
@@ -2555,13 +2555,13 @@
     <t xml:space="preserve">8.77110767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58664512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47944641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71799182891846</t>
+    <t xml:space="preserve">8.58664608001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4794454574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71799087524414</t>
   </si>
   <si>
     <t xml:space="preserve">8.65907764434814</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">8.75565528869629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71412754058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82132720947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94784355163574</t>
+    <t xml:space="preserve">8.71412658691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82132911682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94784259796143</t>
   </si>
   <si>
     <t xml:space="preserve">9.01448154449463</t>
@@ -2585,7 +2585,7 @@
     <t xml:space="preserve">9.03959083557129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06083869934082</t>
+    <t xml:space="preserve">9.0608377456665</t>
   </si>
   <si>
     <t xml:space="preserve">8.85319805145264</t>
@@ -2594,40 +2594,40 @@
     <t xml:space="preserve">8.94011783599854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01641368865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05118083953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80587577819824</t>
+    <t xml:space="preserve">9.01641273498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05118179321289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80587482452393</t>
   </si>
   <si>
     <t xml:space="preserve">9.08884525299072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01158618927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99999523162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04828262329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04635238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02896785736084</t>
+    <t xml:space="preserve">9.0115852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99999618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04828357696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04635143280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02896881103516</t>
   </si>
   <si>
     <t xml:space="preserve">8.95460414886475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99613094329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97198867797852</t>
+    <t xml:space="preserve">8.99613285064697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9719877243042</t>
   </si>
   <si>
     <t xml:space="preserve">9.04442024230957</t>
@@ -2636,16 +2636,16 @@
     <t xml:space="preserve">9.21342849731445</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23854064941406</t>
+    <t xml:space="preserve">9.23853969573975</t>
   </si>
   <si>
     <t xml:space="preserve">9.1747989654541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06180381774902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12554550170898</t>
+    <t xml:space="preserve">9.06180477142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12554454803467</t>
   </si>
   <si>
     <t xml:space="preserve">9.0318660736084</t>
@@ -2657,13 +2657,13 @@
     <t xml:space="preserve">8.80008125305176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93528938293457</t>
+    <t xml:space="preserve">8.93528842926025</t>
   </si>
   <si>
     <t xml:space="preserve">8.94687747955322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74020481109619</t>
+    <t xml:space="preserve">8.74020385742188</t>
   </si>
   <si>
     <t xml:space="preserve">8.88893222808838</t>
@@ -2672,25 +2672,25 @@
     <t xml:space="preserve">8.66294193267822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50262451171875</t>
+    <t xml:space="preserve">8.50262355804443</t>
   </si>
   <si>
     <t xml:space="preserve">8.65714645385742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51035022735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59726905822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76724529266357</t>
+    <t xml:space="preserve">8.51035118103027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59727001190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76724433898926</t>
   </si>
   <si>
     <t xml:space="preserve">8.89086437225342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96426010131836</t>
+    <t xml:space="preserve">8.96426105499268</t>
   </si>
   <si>
     <t xml:space="preserve">9.24626541137695</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">9.26171875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51281929016113</t>
+    <t xml:space="preserve">9.51281833648682</t>
   </si>
   <si>
     <t xml:space="preserve">9.35443210601807</t>
@@ -2708,16 +2708,16 @@
     <t xml:space="preserve">9.29841709136963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.443284034729</t>
+    <t xml:space="preserve">9.44328308105469</t>
   </si>
   <si>
     <t xml:space="preserve">9.43169403076172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25012874603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13230609893799</t>
+    <t xml:space="preserve">9.2501277923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1323070526123</t>
   </si>
   <si>
     <t xml:space="preserve">9.22501850128174</t>
@@ -2726,61 +2726,61 @@
     <t xml:space="preserve">9.06856441497803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19411563873291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17286777496338</t>
+    <t xml:space="preserve">9.19411468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17286682128906</t>
   </si>
   <si>
     <t xml:space="preserve">9.22695064544678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36215877532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12651062011719</t>
+    <t xml:space="preserve">9.36215972900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12650966644287</t>
   </si>
   <si>
     <t xml:space="preserve">9.14775657653809</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13037490844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15934753417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12264728546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0048246383667</t>
+    <t xml:space="preserve">9.13037395477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15934562683105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12264633178711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00482368469238</t>
   </si>
   <si>
     <t xml:space="preserve">9.13616847991943</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05890655517578</t>
+    <t xml:space="preserve">9.0589075088501</t>
   </si>
   <si>
     <t xml:space="preserve">9.04538631439209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8367805480957</t>
+    <t xml:space="preserve">8.83677864074707</t>
   </si>
   <si>
     <t xml:space="preserve">8.87347888946533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95267200469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9391508102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86961650848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88120651245117</t>
+    <t xml:space="preserve">8.95267295837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93914985656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86961555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88120555877686</t>
   </si>
   <si>
     <t xml:space="preserve">8.96619319915771</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">9.13809871673584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02027702331543</t>
+    <t xml:space="preserve">9.02027606964111</t>
   </si>
   <si>
     <t xml:space="preserve">8.90438365936279</t>
@@ -2801,25 +2801,25 @@
     <t xml:space="preserve">8.59340572357178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5412540435791</t>
+    <t xml:space="preserve">8.54125499725342</t>
   </si>
   <si>
     <t xml:space="preserve">8.55284404754639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42149925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38093852996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47365188598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42343044281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42536354064941</t>
+    <t xml:space="preserve">8.42150020599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38093757629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47365093231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42343139648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4253625869751</t>
   </si>
   <si>
     <t xml:space="preserve">8.5470495223999</t>
@@ -2831,13 +2831,13 @@
     <t xml:space="preserve">8.58568096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.512282371521</t>
+    <t xml:space="preserve">8.51228141784668</t>
   </si>
   <si>
     <t xml:space="preserve">8.5064868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63590145111084</t>
+    <t xml:space="preserve">8.63590049743652</t>
   </si>
   <si>
     <t xml:space="preserve">8.59533786773682</t>
@@ -2846,22 +2846,22 @@
     <t xml:space="preserve">8.65328407287598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57215881347656</t>
+    <t xml:space="preserve">8.57215976715088</t>
   </si>
   <si>
     <t xml:space="preserve">8.57795429229736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82712364196777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86768341064453</t>
+    <t xml:space="preserve">8.82712173461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86768436431885</t>
   </si>
   <si>
     <t xml:space="preserve">8.94108390808105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33704948425293</t>
+    <t xml:space="preserve">9.33704853057861</t>
   </si>
   <si>
     <t xml:space="preserve">9.31773376464844</t>
@@ -2870,16 +2870,16 @@
     <t xml:space="preserve">9.40272045135498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3447732925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38533592224121</t>
+    <t xml:space="preserve">9.34477424621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38533687591553</t>
   </si>
   <si>
     <t xml:space="preserve">9.44521331787109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58235263824463</t>
+    <t xml:space="preserve">9.58235359191895</t>
   </si>
   <si>
     <t xml:space="preserve">9.42976093292236</t>
@@ -2894,37 +2894,37 @@
     <t xml:space="preserve">9.20570373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28875827789307</t>
+    <t xml:space="preserve">9.2887601852417</t>
   </si>
   <si>
     <t xml:space="preserve">9.31580066680908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34091091156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05697631835938</t>
+    <t xml:space="preserve">9.34091186523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05697536468506</t>
   </si>
   <si>
     <t xml:space="preserve">9.19218254089355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16320991516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04924869537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26751232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16900444030762</t>
+    <t xml:space="preserve">9.16320896148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04924774169922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26751327514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16900539398193</t>
   </si>
   <si>
     <t xml:space="preserve">9.36795234680176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52440738677979</t>
+    <t xml:space="preserve">9.52440643310547</t>
   </si>
   <si>
     <t xml:space="preserve">9.76391792297363</t>
@@ -2939,52 +2939,52 @@
     <t xml:space="preserve">9.38726902008057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42589950561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36408996582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28296566009521</t>
+    <t xml:space="preserve">9.42589855194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.364089012146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28296375274658</t>
   </si>
   <si>
     <t xml:space="preserve">9.25978660583496</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24240303039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26364898681641</t>
+    <t xml:space="preserve">9.24240398406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26364994049072</t>
   </si>
   <si>
     <t xml:space="preserve">9.28682804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3505687713623</t>
+    <t xml:space="preserve">9.35056972503662</t>
   </si>
   <si>
     <t xml:space="preserve">9.23081398010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39885711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32932090759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46452903747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41624164581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63836765289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47225475311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56497001647949</t>
+    <t xml:space="preserve">9.39885807037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32932186126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4645299911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41624069213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63836669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47225570678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56496906280518</t>
   </si>
   <si>
     <t xml:space="preserve">9.64416217803955</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">9.83255958557129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70340061187744</t>
+    <t xml:space="preserve">9.70339965820312</t>
   </si>
   <si>
     <t xml:space="preserve">9.62959575653076</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">9.60823154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52860069274902</t>
+    <t xml:space="preserve">9.52859973907471</t>
   </si>
   <si>
     <t xml:space="preserve">9.63348007202148</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">9.98308181762695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94423770904541</t>
+    <t xml:space="preserve">9.94423675537109</t>
   </si>
   <si>
     <t xml:space="preserve">9.7742919921875</t>
@@ -3059,7 +3059,7 @@
     <t xml:space="preserve">10.1675939559937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2355718612671</t>
+    <t xml:space="preserve">10.2355728149414</t>
   </si>
   <si>
     <t xml:space="preserve">10.2549953460693</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">10.1870164871216</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1481714248657</t>
+    <t xml:space="preserve">10.14817237854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2307176589966</t>
@@ -3077,34 +3077,34 @@
     <t xml:space="preserve">10.2792730331421</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2744169235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3132619857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3909521102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5754642486572</t>
+    <t xml:space="preserve">10.2744178771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3132610321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3909511566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5754632949829</t>
   </si>
   <si>
     <t xml:space="preserve">10.6337299346924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8133878707886</t>
+    <t xml:space="preserve">10.8133869171143</t>
   </si>
   <si>
     <t xml:space="preserve">10.8182430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8328084945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8230981826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8570880889893</t>
+    <t xml:space="preserve">10.8328094482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8230991363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8570871353149</t>
   </si>
   <si>
     <t xml:space="preserve">10.7551202774048</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">10.7454090118408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7842531204224</t>
+    <t xml:space="preserve">10.7842540740967</t>
   </si>
   <si>
     <t xml:space="preserve">11.0852994918823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0755891799927</t>
+    <t xml:space="preserve">11.0755882263184</t>
   </si>
   <si>
     <t xml:space="preserve">11.0610218048096</t>
@@ -3128,7 +3128,7 @@
     <t xml:space="preserve">11.0464553833008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9687652587891</t>
+    <t xml:space="preserve">10.9687662124634</t>
   </si>
   <si>
     <t xml:space="preserve">11.0027551651001</t>
@@ -3137,13 +3137,13 @@
     <t xml:space="preserve">10.9104986190796</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8910779953003</t>
+    <t xml:space="preserve">10.891077041626</t>
   </si>
   <si>
     <t xml:space="preserve">10.997899055481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.827953338623</t>
+    <t xml:space="preserve">10.8279542922974</t>
   </si>
   <si>
     <t xml:space="preserve">10.9541988372803</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">10.6531534194946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7162752151489</t>
+    <t xml:space="preserve">10.7162742614746</t>
   </si>
   <si>
     <t xml:space="preserve">10.9930429458618</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">11.0513105392456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4009122848511</t>
+    <t xml:space="preserve">11.4009132385254</t>
   </si>
   <si>
     <t xml:space="preserve">11.4688911437988</t>
@@ -3185,13 +3185,13 @@
     <t xml:space="preserve">11.5951356887817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5611476898193</t>
+    <t xml:space="preserve">11.561146736145</t>
   </si>
   <si>
     <t xml:space="preserve">11.5028800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6048469543457</t>
+    <t xml:space="preserve">11.6048460006714</t>
   </si>
   <si>
     <t xml:space="preserve">11.5805702209473</t>
@@ -3209,13 +3209,13 @@
     <t xml:space="preserve">11.8621940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">11.745659828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6922483444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6825361251831</t>
+    <t xml:space="preserve">11.7456588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6922473907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6825370788574</t>
   </si>
   <si>
     <t xml:space="preserve">11.3620681762695</t>
@@ -3245,7 +3245,7 @@
     <t xml:space="preserve">11.5902814865112</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6971044540405</t>
+    <t xml:space="preserve">11.6971035003662</t>
   </si>
   <si>
     <t xml:space="preserve">11.5708589553833</t>
@@ -3254,7 +3254,7 @@
     <t xml:space="preserve">11.5757141113281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5125904083252</t>
+    <t xml:space="preserve">11.5125894546509</t>
   </si>
   <si>
     <t xml:space="preserve">11.4106245040894</t>
@@ -3269,106 +3269,106 @@
     <t xml:space="preserve">11.9495944976807</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9301719665527</t>
+    <t xml:space="preserve">11.9301710128784</t>
   </si>
   <si>
     <t xml:space="preserve">11.7942161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7602243423462</t>
+    <t xml:space="preserve">11.7602252960205</t>
   </si>
   <si>
     <t xml:space="preserve">11.8087825775146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8282051086426</t>
+    <t xml:space="preserve">11.8282041549683</t>
   </si>
   <si>
     <t xml:space="preserve">11.7505149841309</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9253168106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0175724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.05641746521</t>
+    <t xml:space="preserve">11.9253158569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0175714492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0564165115356</t>
   </si>
   <si>
     <t xml:space="preserve">12.036994934082</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1875190734863</t>
+    <t xml:space="preserve">12.187518119812</t>
   </si>
   <si>
     <t xml:space="preserve">12.1486721038818</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3865976333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5565423965454</t>
+    <t xml:space="preserve">12.3865966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5565414428711</t>
   </si>
   <si>
     <t xml:space="preserve">12.425440788269</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5274085998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5322637557983</t>
+    <t xml:space="preserve">12.5274076461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5322647094727</t>
   </si>
   <si>
     <t xml:space="preserve">12.5662517547607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9350271224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.012716293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0758390426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1729497909546</t>
+    <t xml:space="preserve">11.9350280761719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0127153396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0758399963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1729507446289</t>
   </si>
   <si>
     <t xml:space="preserve">12.3331851959229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3137626647949</t>
+    <t xml:space="preserve">12.3137636184692</t>
   </si>
   <si>
     <t xml:space="preserve">12.4205846786499</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3040504455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4108734130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.444863319397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4157304763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5468311309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6439437866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7750434875488</t>
+    <t xml:space="preserve">12.304051399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4108743667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4448642730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4157295227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5468301773071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6439428329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7750425338745</t>
   </si>
   <si>
     <t xml:space="preserve">12.9644107818604</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9595565795898</t>
+    <t xml:space="preserve">12.9595556259155</t>
   </si>
   <si>
     <t xml:space="preserve">12.9401330947876</t>
@@ -3386,19 +3386,19 @@
     <t xml:space="preserve">12.9109992980957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4837083816528</t>
+    <t xml:space="preserve">12.4837074279785</t>
   </si>
   <si>
     <t xml:space="preserve">12.7070655822754</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4982748031616</t>
+    <t xml:space="preserve">12.4982757568359</t>
   </si>
   <si>
     <t xml:space="preserve">12.4739971160889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3428974151611</t>
+    <t xml:space="preserve">12.3428964614868</t>
   </si>
   <si>
     <t xml:space="preserve">12.6390867233276</t>
@@ -3410,28 +3410,28 @@
     <t xml:space="preserve">12.6099529266357</t>
   </si>
   <si>
-    <t xml:space="preserve">12.585675239563</t>
+    <t xml:space="preserve">12.5856761932373</t>
   </si>
   <si>
     <t xml:space="preserve">12.3768844604492</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4885635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.284628868103</t>
+    <t xml:space="preserve">12.488564491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2846279144287</t>
   </si>
   <si>
     <t xml:space="preserve">12.2797737121582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2020845413208</t>
+    <t xml:space="preserve">12.2020835876465</t>
   </si>
   <si>
     <t xml:space="preserve">12.4400081634521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3720302581787</t>
+    <t xml:space="preserve">12.3720293045044</t>
   </si>
   <si>
     <t xml:space="preserve">12.435152053833</t>
@@ -3446,7 +3446,7 @@
     <t xml:space="preserve">11.7553701400757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6728258132935</t>
+    <t xml:space="preserve">11.6728267669678</t>
   </si>
   <si>
     <t xml:space="preserve">11.6388359069824</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">11.1532783508301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.216402053833</t>
+    <t xml:space="preserve">11.2164011001587</t>
   </si>
   <si>
     <t xml:space="preserve">11.0804443359375</t>
@@ -3467,19 +3467,19 @@
     <t xml:space="preserve">11.0658779144287</t>
   </si>
   <si>
-    <t xml:space="preserve">10.696852684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6434412002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6191654205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5171957015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7696876525879</t>
+    <t xml:space="preserve">10.6968536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6434421539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6191644668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5171966552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7696866989136</t>
   </si>
   <si>
     <t xml:space="preserve">10.9833326339722</t>
@@ -3497,10 +3497,10 @@
     <t xml:space="preserve">10.4492177963257</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5317640304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4880638122559</t>
+    <t xml:space="preserve">10.5317630767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4880628585815</t>
   </si>
   <si>
     <t xml:space="preserve">10.3375415802002</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">10.1821603775024</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1918716430664</t>
+    <t xml:space="preserve">10.1918725967407</t>
   </si>
   <si>
     <t xml:space="preserve">10.264705657959</t>
@@ -3527,7 +3527,7 @@
     <t xml:space="preserve">9.18870735168457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4664478302002</t>
+    <t xml:space="preserve">9.46644687652588</t>
   </si>
   <si>
     <t xml:space="preserve">9.04304122924805</t>
@@ -3536,13 +3536,13 @@
     <t xml:space="preserve">9.04498386383057</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06246280670166</t>
+    <t xml:space="preserve">9.06246185302734</t>
   </si>
   <si>
     <t xml:space="preserve">8.84299087524414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83910655975342</t>
+    <t xml:space="preserve">8.83910751342773</t>
   </si>
   <si>
     <t xml:space="preserve">8.5438871383667</t>
@@ -3560,7 +3560,7 @@
     <t xml:space="preserve">8.99836921691895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03138828277588</t>
+    <t xml:space="preserve">9.0313892364502</t>
   </si>
   <si>
     <t xml:space="preserve">9.58492469787598</t>
@@ -3587,25 +3587,25 @@
     <t xml:space="preserve">10.0801935195923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2598505020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2501401901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4200839996338</t>
+    <t xml:space="preserve">10.2598495483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2501392364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4200849533081</t>
   </si>
   <si>
     <t xml:space="preserve">10.3860950469971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5074844360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346513748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.415228843689</t>
+    <t xml:space="preserve">10.5074853897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4346504211426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4152297973633</t>
   </si>
   <si>
     <t xml:space="preserve">10.3278293609619</t>
@@ -5931,6 +5931,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.81799983978271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55000019073486</t>
   </si>
 </sst>
 </file>
@@ -71191,7 +71194,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6911805556</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>7253746</v>
@@ -71212,6 +71215,32 @@
         <v>1888</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6910069444</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>7909905</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>5.69199991226196</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>5.55000019073486</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>5.69199991226196</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>5.55000019073486</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1973</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1976" uniqueCount="1976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1977" uniqueCount="1977">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,121 +38,121 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59865665435791</t>
+    <t xml:space="preserve">3.59865689277649</t>
   </si>
   <si>
     <t xml:space="preserve">CPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6589822769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60329675674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51976895332336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51048851013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54993200302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62881994247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68450427055359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57313418388367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52673006057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4826455116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56617331504822</t>
+    <t xml:space="preserve">3.65898251533508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60329699516296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51976871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51048827171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54993224143982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62881946563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68450474739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57313442230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52672982215881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48264575004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56617379188538</t>
   </si>
   <si>
     <t xml:space="preserve">3.43392133712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50584769248962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56153297424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64274096488953</t>
+    <t xml:space="preserve">3.50584816932678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56153321266174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64274048805237</t>
   </si>
   <si>
     <t xml:space="preserve">3.66594314575195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56849384307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74251008033752</t>
+    <t xml:space="preserve">3.56849408149719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74250984191895</t>
   </si>
   <si>
     <t xml:space="preserve">3.72162842750549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70770645141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47104477882385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44320178031921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28078675270081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33183169364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40839838981628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22046136856079</t>
+    <t xml:space="preserve">3.70770692825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47104454040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44320201873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28078699111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33183121681213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40839886665344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22046113014221</t>
   </si>
   <si>
     <t xml:space="preserve">3.26918578147888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.324871301651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24366354942322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32255077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28774738311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31791043281555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36663460731506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36199426651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40607857704163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3828763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36431455612183</t>
+    <t xml:space="preserve">3.32487106323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24366307258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32255101203918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28774785995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31791090965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3666353225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36199450492859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40607905387878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38287663459778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36431479454041</t>
   </si>
   <si>
     <t xml:space="preserve">3.53137040138245</t>
@@ -173,76 +173,76 @@
     <t xml:space="preserve">3.63810038566589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68914484977722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476301193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95596981048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00701522827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04877853393555</t>
+    <t xml:space="preserve">3.6891450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476253509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95596957206726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00701427459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04877948760986</t>
   </si>
   <si>
     <t xml:space="preserve">4.03485727310181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04181718826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03717756271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05109834671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01861572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09286260604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07662057876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0394983291626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08358192443848</t>
+    <t xml:space="preserve">4.04181814193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03717803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05109882354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01861619949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09286212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07662200927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03949880599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08358240127563</t>
   </si>
   <si>
     <t xml:space="preserve">4.02325630187988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00005435943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06038045883179</t>
+    <t xml:space="preserve">4.00005388259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06037998199463</t>
   </si>
   <si>
     <t xml:space="preserve">3.99541354179382</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94436860084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97453117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00237464904785</t>
+    <t xml:space="preserve">3.9443690776825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97453188896179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00237321853638</t>
   </si>
   <si>
     <t xml:space="preserve">3.93740844726562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94668912887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03021669387817</t>
+    <t xml:space="preserve">3.94668841362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03021717071533</t>
   </si>
   <si>
     <t xml:space="preserve">4.05341911315918</t>
@@ -251,73 +251,73 @@
     <t xml:space="preserve">4.00933456420898</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95829033851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98613262176514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02557706832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96989130973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91188645362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89796447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87708234786987</t>
+    <t xml:space="preserve">3.95829010009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98613286018372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02557611465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96989154815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91188621520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89796423912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87708282470703</t>
   </si>
   <si>
     <t xml:space="preserve">3.91420650482178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92812728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95132970809937</t>
+    <t xml:space="preserve">3.92812752723694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95132994651794</t>
   </si>
   <si>
     <t xml:space="preserve">4.06734037399292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08126163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99309325218201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96757197380066</t>
+    <t xml:space="preserve">4.08126211166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99309349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96757125854492</t>
   </si>
   <si>
     <t xml:space="preserve">3.98149228096008</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96292972564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88868355751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89332461357117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79587554931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89309978485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0267767906189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08540821075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07602691650391</t>
+    <t xml:space="preserve">3.96293091773987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88868427276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89332437515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79587507247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89309930801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02677774429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08540868759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07602787017822</t>
   </si>
   <si>
     <t xml:space="preserve">4.08306360244751</t>
@@ -326,10 +326,10 @@
     <t xml:space="preserve">4.09947967529297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07368230819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09009981155396</t>
+    <t xml:space="preserve">4.07368278503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0900993347168</t>
   </si>
   <si>
     <t xml:space="preserve">4.10182571411133</t>
@@ -338,49 +338,49 @@
     <t xml:space="preserve">4.0877537727356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1135516166687</t>
+    <t xml:space="preserve">4.11355257034302</t>
   </si>
   <si>
     <t xml:space="preserve">4.08071851730347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01974201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90482544898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85557556152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8579204082489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86495590209961</t>
+    <t xml:space="preserve">4.01974153518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90482473373413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85557508468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85792064666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86495614051819</t>
   </si>
   <si>
     <t xml:space="preserve">3.8719916343689</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86964678764343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00566959381104</t>
+    <t xml:space="preserve">3.86964654922485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00567054748535</t>
   </si>
   <si>
     <t xml:space="preserve">4.00801563262939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95876526832581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05961132049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88606357574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88840794563293</t>
+    <t xml:space="preserve">3.95876455307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05961084365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88606286048889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88840866088867</t>
   </si>
   <si>
     <t xml:space="preserve">4.04084920883179</t>
@@ -389,7 +389,7 @@
     <t xml:space="preserve">4.16514682769775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15576601028442</t>
+    <t xml:space="preserve">4.15576553344727</t>
   </si>
   <si>
     <t xml:space="preserve">4.14873027801514</t>
@@ -404,34 +404,34 @@
     <t xml:space="preserve">4.04319429397583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16045618057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15811157226562</t>
+    <t xml:space="preserve">4.16045665740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15811109542847</t>
   </si>
   <si>
     <t xml:space="preserve">4.11589670181274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06899261474609</t>
+    <t xml:space="preserve">4.06899118423462</t>
   </si>
   <si>
     <t xml:space="preserve">4.13465881347656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14169454574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18390846252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16280174255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21908712387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29179000854492</t>
+    <t xml:space="preserve">4.14169502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18390798568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16280126571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21908760070801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29178953170776</t>
   </si>
   <si>
     <t xml:space="preserve">4.29647970199585</t>
@@ -440,25 +440,25 @@
     <t xml:space="preserve">4.31055212020874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28709983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3316593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33869409561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5403847694397</t>
+    <t xml:space="preserve">4.28709936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33165884017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33869504928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54038524627686</t>
   </si>
   <si>
     <t xml:space="preserve">4.51458740234375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5216236114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43719530105591</t>
+    <t xml:space="preserve">4.52162313461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43719482421875</t>
   </si>
   <si>
     <t xml:space="preserve">4.47940921783447</t>
@@ -467,13 +467,13 @@
     <t xml:space="preserve">4.45595693588257</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66233730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67171907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58963537216187</t>
+    <t xml:space="preserve">4.66233777999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67171955108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58963489532471</t>
   </si>
   <si>
     <t xml:space="preserve">4.55914688110352</t>
@@ -482,10 +482,10 @@
     <t xml:space="preserve">4.56383752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54976654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60370683670044</t>
+    <t xml:space="preserve">4.54976606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60370635986328</t>
   </si>
   <si>
     <t xml:space="preserve">4.59667158126831</t>
@@ -494,19 +494,19 @@
     <t xml:space="preserve">4.57321929931641</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6201229095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59432601928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65061187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57556390762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70455169677734</t>
+    <t xml:space="preserve">4.62012338638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59432554244995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65061140060425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57556438446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7045521736145</t>
   </si>
   <si>
     <t xml:space="preserve">4.67406415939331</t>
@@ -518,40 +518,40 @@
     <t xml:space="preserve">4.60136079788208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48644495010376</t>
+    <t xml:space="preserve">4.4864444732666</t>
   </si>
   <si>
     <t xml:space="preserve">4.4653377532959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39967012405396</t>
+    <t xml:space="preserve">4.39967107772827</t>
   </si>
   <si>
     <t xml:space="preserve">4.43250417709351</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50520706176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49113464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51693248748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50286197662354</t>
+    <t xml:space="preserve">4.50520658493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49113512039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51693296432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50286102294922</t>
   </si>
   <si>
     <t xml:space="preserve">4.4887900352478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65295743942261</t>
+    <t xml:space="preserve">4.65295791625977</t>
   </si>
   <si>
     <t xml:space="preserve">4.66468286514282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73269510269165</t>
+    <t xml:space="preserve">4.73269462585449</t>
   </si>
   <si>
     <t xml:space="preserve">4.71393346786499</t>
@@ -560,40 +560,40 @@
     <t xml:space="preserve">4.69048118591309</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58728933334351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.568528175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47471857070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44657468795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54742097854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44188594818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50051641464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52631425857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36683702468872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37152862548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33400440216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32931327819824</t>
+    <t xml:space="preserve">4.58728981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56852769851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47471904754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44657564163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54742050170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44188547134399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50051593780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52631330490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36683797836304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37152767181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3340048789978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3293137550354</t>
   </si>
   <si>
     <t xml:space="preserve">4.30586099624634</t>
@@ -602,16 +602,16 @@
     <t xml:space="preserve">4.30351638793945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25661087036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20736122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09478902816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24254083633423</t>
+    <t xml:space="preserve">4.25661134719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20736074447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09478950500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24253940582275</t>
   </si>
   <si>
     <t xml:space="preserve">4.20267057418823</t>
@@ -620,19 +620,19 @@
     <t xml:space="preserve">3.9564208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9540753364563</t>
+    <t xml:space="preserve">3.95407509803772</t>
   </si>
   <si>
     <t xml:space="preserve">4.0338134765625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12527704238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01739597320557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12996864318848</t>
+    <t xml:space="preserve">4.12527799606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01739692687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12996816635132</t>
   </si>
   <si>
     <t xml:space="preserve">4.17218255996704</t>
@@ -641,40 +641,40 @@
     <t xml:space="preserve">4.21205139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18859958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2495756149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20501661300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26833772659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2284688949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.247230052948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31993198394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36449241638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28944444656372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27771806716919</t>
+    <t xml:space="preserve">4.1885986328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24957609176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20501613616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26833820343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22846746444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24722957611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31993341445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449289321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28944492340088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27771854400635</t>
   </si>
   <si>
     <t xml:space="preserve">4.30117082595825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32227897644043</t>
+    <t xml:space="preserve">4.32227802276611</t>
   </si>
   <si>
     <t xml:space="preserve">4.35745620727539</t>
@@ -683,43 +683,43 @@
     <t xml:space="preserve">4.34807586669922</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34338521957397</t>
+    <t xml:space="preserve">4.34338474273682</t>
   </si>
   <si>
     <t xml:space="preserve">4.39028978347778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36214733123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32462358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39732551574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37387323379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36918306350708</t>
+    <t xml:space="preserve">4.36214685440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32462310791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39732599258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37387228012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36918258666992</t>
   </si>
   <si>
     <t xml:space="preserve">4.47002744674683</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45830202102661</t>
+    <t xml:space="preserve">4.45830249786377</t>
   </si>
   <si>
     <t xml:space="preserve">4.42546892166138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43484926223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46768236160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40201663970947</t>
+    <t xml:space="preserve">4.43484878540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46768283843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40201568603516</t>
   </si>
   <si>
     <t xml:space="preserve">4.3527660369873</t>
@@ -728,49 +728,49 @@
     <t xml:space="preserve">4.38559913635254</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43954086303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4301586151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49347972869873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47237300872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5239691734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54273128509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53803968429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54507637023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58260011672974</t>
+    <t xml:space="preserve">4.43954038619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43015813827515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49348068237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47237348556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52396965026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5427303314209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53804063796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54507541656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58259963989258</t>
   </si>
   <si>
     <t xml:space="preserve">4.57790899276733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55211067199707</t>
+    <t xml:space="preserve">4.55211114883423</t>
   </si>
   <si>
     <t xml:space="preserve">4.57087326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53569555282593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50755167007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58494520187378</t>
+    <t xml:space="preserve">4.53569507598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50755262374878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58494472503662</t>
   </si>
   <si>
     <t xml:space="preserve">4.65530204772949</t>
@@ -782,46 +782,46 @@
     <t xml:space="preserve">4.75614786148071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80774307250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83119535446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8968620300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94845676422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09855318069458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05164766311646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12200498580933</t>
+    <t xml:space="preserve">4.80774211883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83119583129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89686155319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94845724105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09855222702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05164861679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12200403213501</t>
   </si>
   <si>
     <t xml:space="preserve">5.04695701599121</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05633783340454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99536180496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01881456375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02819490432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03288602828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93907690048218</t>
+    <t xml:space="preserve">5.05633878707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99536323547363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01881408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02819585800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03288555145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93907642364502</t>
   </si>
   <si>
     <t xml:space="preserve">4.9766001701355</t>
@@ -836,19 +836,19 @@
     <t xml:space="preserve">5.08917188644409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17359972000122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14545726776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15952920913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09386157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16421985626221</t>
+    <t xml:space="preserve">5.17360067367554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14545679092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15952825546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09386253356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16422033309937</t>
   </si>
   <si>
     <t xml:space="preserve">5.25333881378174</t>
@@ -857,37 +857,37 @@
     <t xml:space="preserve">5.18767166137695</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41750526428223</t>
+    <t xml:space="preserve">5.41750478744507</t>
   </si>
   <si>
     <t xml:space="preserve">5.67079067230225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60043382644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6238865852356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66141033172607</t>
+    <t xml:space="preserve">5.60043430328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62388610839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66140985488892</t>
   </si>
   <si>
     <t xml:space="preserve">5.68486261367798</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57698106765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60512495040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72238636016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69403409957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74128675460815</t>
+    <t xml:space="preserve">5.57698154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60512447357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72238683700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69403457641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74128723144531</t>
   </si>
   <si>
     <t xml:space="preserve">5.76491451263428</t>
@@ -899,52 +899,52 @@
     <t xml:space="preserve">5.8783221244812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86887168884277</t>
+    <t xml:space="preserve">5.86887216567993</t>
   </si>
   <si>
     <t xml:space="preserve">5.88304758071899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02008295059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99173021316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00118064880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9350266456604</t>
+    <t xml:space="preserve">6.02008247375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99173069000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00118112564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93502759933472</t>
   </si>
   <si>
     <t xml:space="preserve">5.85942077636719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80271673202515</t>
+    <t xml:space="preserve">5.80271768569946</t>
   </si>
   <si>
     <t xml:space="preserve">5.75546407699585</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73183727264404</t>
+    <t xml:space="preserve">5.73183679580688</t>
   </si>
   <si>
     <t xml:space="preserve">5.84997034072876</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81216812133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95865392684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93030214309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98227977752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90194988250732</t>
+    <t xml:space="preserve">5.81216859817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95865297317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93030118942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98228073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90194940567017</t>
   </si>
   <si>
     <t xml:space="preserve">5.91612529754639</t>
@@ -953,40 +953,40 @@
     <t xml:space="preserve">5.91139984130859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8310694694519</t>
+    <t xml:space="preserve">5.83106851577759</t>
   </si>
   <si>
     <t xml:space="preserve">5.88777256011963</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78381586074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80744218826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84524488449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77436542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82634305953979</t>
+    <t xml:space="preserve">5.78381538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8074426651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84524536132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77436494827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82634401321411</t>
   </si>
   <si>
     <t xml:space="preserve">5.82161855697632</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85469627380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79326677322388</t>
+    <t xml:space="preserve">5.85469579696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79326629638672</t>
   </si>
   <si>
     <t xml:space="preserve">5.8357949256897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95392847061157</t>
+    <t xml:space="preserve">5.95392799377441</t>
   </si>
   <si>
     <t xml:space="preserve">5.92557621002197</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">5.94447708129883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77908945083618</t>
+    <t xml:space="preserve">5.7790904045105</t>
   </si>
   <si>
     <t xml:space="preserve">5.74601316452026</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">5.79799175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76018905639648</t>
+    <t xml:space="preserve">5.76018953323364</t>
   </si>
   <si>
     <t xml:space="preserve">5.69875955581665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66568279266357</t>
+    <t xml:space="preserve">5.66568183898926</t>
   </si>
   <si>
     <t xml:space="preserve">5.73656272888184</t>
@@ -1028,13 +1028,13 @@
     <t xml:space="preserve">5.78854084014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76963996887207</t>
+    <t xml:space="preserve">5.76963949203491</t>
   </si>
   <si>
     <t xml:space="preserve">5.89249849319458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97282981872559</t>
+    <t xml:space="preserve">5.97282886505127</t>
   </si>
   <si>
     <t xml:space="preserve">6.15239286422729</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">6.1476674079895</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28470230102539</t>
+    <t xml:space="preserve">6.28470134735107</t>
   </si>
   <si>
     <t xml:space="preserve">6.1382155418396</t>
@@ -1055,22 +1055,22 @@
     <t xml:space="preserve">6.02953338623047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10513925552368</t>
+    <t xml:space="preserve">6.10513830184937</t>
   </si>
   <si>
     <t xml:space="preserve">6.16656875610352</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11458969116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31777858734131</t>
+    <t xml:space="preserve">6.11458921432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31777906417847</t>
   </si>
   <si>
     <t xml:space="preserve">6.34140586853027</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40756034851074</t>
+    <t xml:space="preserve">6.4075608253479</t>
   </si>
   <si>
     <t xml:space="preserve">6.50206756591797</t>
@@ -1079,61 +1079,61 @@
     <t xml:space="preserve">6.42173671722412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30832862854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47844076156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31305408477783</t>
+    <t xml:space="preserve">6.3083291053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.478440284729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31305360794067</t>
   </si>
   <si>
     <t xml:space="preserve">6.33668041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37448310852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17601919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0909628868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23272323608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03898429870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08623743057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10041332244873</t>
+    <t xml:space="preserve">6.37448358535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17601871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09096240997314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23272275924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0389838218689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08623790740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10041379928589</t>
   </si>
   <si>
     <t xml:space="preserve">6.10986423492432</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0059061050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03425931930542</t>
+    <t xml:space="preserve">6.00590658187866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03425884246826</t>
   </si>
   <si>
     <t xml:space="preserve">6.09568786621094</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06261110305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18074369430542</t>
+    <t xml:space="preserve">6.0626106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18074464797974</t>
   </si>
   <si>
     <t xml:space="preserve">6.08151197433472</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15711736679077</t>
+    <t xml:space="preserve">6.15711832046509</t>
   </si>
   <si>
     <t xml:space="preserve">6.21382141113281</t>
@@ -1142,13 +1142,13 @@
     <t xml:space="preserve">6.24217414855957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24689960479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20909643173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22799777984619</t>
+    <t xml:space="preserve">6.24689912796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20909738540649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22799730300903</t>
   </si>
   <si>
     <t xml:space="preserve">6.19964551925659</t>
@@ -1157,34 +1157,34 @@
     <t xml:space="preserve">6.12876605987549</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07206106185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05788564682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13349008560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14294147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01063251495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94920349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97755432128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05316019058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99645614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06733703613281</t>
+    <t xml:space="preserve">6.07206153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05788469314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13349056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14294195175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01063203811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94920301437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97755479812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05315923690796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99645566940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06733655929565</t>
   </si>
   <si>
     <t xml:space="preserve">5.93975162506104</t>
@@ -1193,25 +1193,25 @@
     <t xml:space="preserve">5.71293497085571</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72711181640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92085027694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57590055465698</t>
+    <t xml:space="preserve">5.72711133956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92085075378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5759015083313</t>
   </si>
   <si>
     <t xml:space="preserve">5.52864742279053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42941522598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50502061843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61370372772217</t>
+    <t xml:space="preserve">5.42941570281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50502014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61370325088501</t>
   </si>
   <si>
     <t xml:space="preserve">5.63733100891113</t>
@@ -1220,22 +1220,22 @@
     <t xml:space="preserve">6.04371023178101</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98700523376465</t>
+    <t xml:space="preserve">5.98700571060181</t>
   </si>
   <si>
     <t xml:space="preserve">6.01535701751709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89722299575806</t>
+    <t xml:space="preserve">5.89722347259521</t>
   </si>
   <si>
     <t xml:space="preserve">5.81689357757568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87359666824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8641471862793</t>
+    <t xml:space="preserve">5.87359714508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86414623260498</t>
   </si>
   <si>
     <t xml:space="preserve">5.9066743850708</t>
@@ -1244,13 +1244,13 @@
     <t xml:space="preserve">5.96810436248779</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01550769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02027082443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99169254302979</t>
+    <t xml:space="preserve">6.01550817489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02027034759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9916934967041</t>
   </si>
   <si>
     <t xml:space="preserve">6.08218765258789</t>
@@ -1265,49 +1265,49 @@
     <t xml:space="preserve">6.08695030212402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07266139984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16315698623657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27270317077637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25365114212036</t>
+    <t xml:space="preserve">6.07266187667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16315603256226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27270221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2536506652832</t>
   </si>
   <si>
     <t xml:space="preserve">6.13934230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2917537689209</t>
+    <t xml:space="preserve">6.29175424575806</t>
   </si>
   <si>
     <t xml:space="preserve">6.38701152801514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52513408660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59657764434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69183540344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69659852981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62039232254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57276296615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50608348846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58228874206543</t>
+    <t xml:space="preserve">6.5251350402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5965781211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69183492660522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69659805297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62039136886597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57276344299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5060830116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58228921890259</t>
   </si>
   <si>
     <t xml:space="preserve">6.65373229980469</t>
@@ -1316,40 +1316,40 @@
     <t xml:space="preserve">6.71088695526123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82519578933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77280426025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82995891571045</t>
+    <t xml:space="preserve">6.82519626617432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77280378341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82995843887329</t>
   </si>
   <si>
     <t xml:space="preserve">7.02523612976074</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92521619796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92045259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01094770431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9680814743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91092681884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01571083068848</t>
+    <t xml:space="preserve">6.92521667480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9204535484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01094818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96808195114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91092824935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01571035385132</t>
   </si>
   <si>
     <t xml:space="preserve">7.04905080795288</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09667873382568</t>
+    <t xml:space="preserve">7.0966796875</t>
   </si>
   <si>
     <t xml:space="preserve">7.17764806747437</t>
@@ -1358,37 +1358,37 @@
     <t xml:space="preserve">7.28243160247803</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22051429748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23956632614136</t>
+    <t xml:space="preserve">7.22051382064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23956537246704</t>
   </si>
   <si>
     <t xml:space="preserve">7.27766847610474</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12525653839111</t>
+    <t xml:space="preserve">7.12525606155396</t>
   </si>
   <si>
     <t xml:space="preserve">6.94903039932251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86806201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00142192840576</t>
+    <t xml:space="preserve">6.86806154251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0014214515686</t>
   </si>
   <si>
     <t xml:space="preserve">7.00618457794189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0633397102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760725021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99189615249634</t>
+    <t xml:space="preserve">7.06333875656128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760772705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9918966293335</t>
   </si>
   <si>
     <t xml:space="preserve">7.03952407836914</t>
@@ -1397,58 +1397,58 @@
     <t xml:space="preserve">7.02047348022461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07762813568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18717432022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21098852157593</t>
+    <t xml:space="preserve">7.07762765884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18717384338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21098899841309</t>
   </si>
   <si>
     <t xml:space="preserve">7.41579151153564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29672002792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26337909698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24432897567749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27290534973145</t>
+    <t xml:space="preserve">7.29672050476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26338005065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24432849884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27290630340576</t>
   </si>
   <si>
     <t xml:space="preserve">7.30624532699585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18241119384766</t>
+    <t xml:space="preserve">7.1824107170105</t>
   </si>
   <si>
     <t xml:space="preserve">7.25385427474976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0585765838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10620498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14907121658325</t>
+    <t xml:space="preserve">7.05857610702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10620546340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14907169342041</t>
   </si>
   <si>
     <t xml:space="preserve">7.16812229156494</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90140199661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94426822662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06810188293457</t>
+    <t xml:space="preserve">6.90140151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94426727294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06810235977173</t>
   </si>
   <si>
     <t xml:space="preserve">6.98713397979736</t>
@@ -1463,16 +1463,16 @@
     <t xml:space="preserve">6.70612382888794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63944387435913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65849447250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32985734939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19649648666382</t>
+    <t xml:space="preserve">6.63944339752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65849494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32985639572144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19649744033813</t>
   </si>
   <si>
     <t xml:space="preserve">6.11552810668945</t>
@@ -1484,49 +1484,49 @@
     <t xml:space="preserve">6.21554851531982</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3155689239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33462047576904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34414577484131</t>
+    <t xml:space="preserve">6.31556844711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33461999893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34414482116699</t>
   </si>
   <si>
     <t xml:space="preserve">6.12505340576172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15363121032715</t>
+    <t xml:space="preserve">6.15363073348999</t>
   </si>
   <si>
     <t xml:space="preserve">6.30604219436646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35367155075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47274303436279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46797943115234</t>
+    <t xml:space="preserve">6.35367107391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47274351119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46798038482666</t>
   </si>
   <si>
     <t xml:space="preserve">6.42987728118896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52989768981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76804208755493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08239030838013</t>
+    <t xml:space="preserve">6.52989721298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76804161071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08239078521729</t>
   </si>
   <si>
     <t xml:space="preserve">7.11096858978271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12049436569214</t>
+    <t xml:space="preserve">7.12049388885498</t>
   </si>
   <si>
     <t xml:space="preserve">7.32529735565186</t>
@@ -1538,10 +1538,10 @@
     <t xml:space="preserve">7.11573076248169</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03476285934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15383386611938</t>
+    <t xml:space="preserve">7.03476238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1538348197937</t>
   </si>
   <si>
     <t xml:space="preserve">7.04428768157959</t>
@@ -1553,46 +1553,46 @@
     <t xml:space="preserve">7.17288541793823</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36339998245239</t>
+    <t xml:space="preserve">7.36340045928955</t>
   </si>
   <si>
     <t xml:space="preserve">7.14430809020996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20622587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32053422927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09191656112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98237037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44913244247437</t>
+    <t xml:space="preserve">7.20622539520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32053470611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09191703796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98237085342407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913148880005</t>
   </si>
   <si>
     <t xml:space="preserve">7.3824520111084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33006048202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21575117111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33958625793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35387468338013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55391454696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60630655288696</t>
+    <t xml:space="preserve">7.3300609588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2157506942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33958578109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35387420654297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55391502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60630750656128</t>
   </si>
   <si>
     <t xml:space="preserve">7.46342086791992</t>
@@ -1604,70 +1604,70 @@
     <t xml:space="preserve">7.44436883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42055463790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62535858154297</t>
+    <t xml:space="preserve">7.42055511474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62535810470581</t>
   </si>
   <si>
     <t xml:space="preserve">7.53010129928589</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47294664382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4872350692749</t>
+    <t xml:space="preserve">7.47294616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48723554611206</t>
   </si>
   <si>
     <t xml:space="preserve">7.46818351745605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49676084518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51581239700317</t>
+    <t xml:space="preserve">7.49676132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51581192016602</t>
   </si>
   <si>
     <t xml:space="preserve">7.6110692024231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56344032287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6444091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73490476608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80634784698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86826515197754</t>
+    <t xml:space="preserve">7.56344079971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64440965652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73490381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80634689331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86826467514038</t>
   </si>
   <si>
     <t xml:space="preserve">7.8587384223938</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88731670379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92542028427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9539966583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83492469787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98733615875244</t>
+    <t xml:space="preserve">7.88731527328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92541885375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95399618148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83492517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98733758926392</t>
   </si>
   <si>
     <t xml:space="preserve">8.01115131378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06354331970215</t>
+    <t xml:space="preserve">8.06354236602783</t>
   </si>
   <si>
     <t xml:space="preserve">7.53486347198486</t>
@@ -1676,19 +1676,19 @@
     <t xml:space="preserve">7.52057552337646</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54438924789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62059497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63964796066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77777004241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76824426651001</t>
+    <t xml:space="preserve">7.54438972473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62059545516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63964748382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77776956558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76824331283569</t>
   </si>
   <si>
     <t xml:space="preserve">7.90636825561523</t>
@@ -1706,7 +1706,7 @@
     <t xml:space="preserve">8.0683069229126</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20166492462158</t>
+    <t xml:space="preserve">8.20166397094727</t>
   </si>
   <si>
     <t xml:space="preserve">8.32549953460693</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">8.44457149505615</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33978939056396</t>
+    <t xml:space="preserve">8.33978843688965</t>
   </si>
   <si>
     <t xml:space="preserve">8.38265419006348</t>
@@ -1724,7 +1724,7 @@
     <t xml:space="preserve">8.33502674102783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27787208557129</t>
+    <t xml:space="preserve">8.27787113189697</t>
   </si>
   <si>
     <t xml:space="preserve">8.23500633239746</t>
@@ -1733,28 +1733,28 @@
     <t xml:space="preserve">8.25881958007812</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26358413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16832637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31121253967285</t>
+    <t xml:space="preserve">8.26358127593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16832542419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31121349334717</t>
   </si>
   <si>
     <t xml:space="preserve">8.36836624145508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35407733917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37789154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28739738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21119117736816</t>
+    <t xml:space="preserve">8.354079246521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37789249420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28739833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21119022369385</t>
   </si>
   <si>
     <t xml:space="preserve">8.22071743011475</t>
@@ -1769,43 +1769,43 @@
     <t xml:space="preserve">8.56085205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51294708251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48899269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60875797271729</t>
+    <t xml:space="preserve">8.5129451751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48899173736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60875701904297</t>
   </si>
   <si>
     <t xml:space="preserve">8.441086769104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49857330322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4842004776001</t>
+    <t xml:space="preserve">8.49857425689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48420143127441</t>
   </si>
   <si>
     <t xml:space="preserve">8.67103672027588</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81475448608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74289417266846</t>
+    <t xml:space="preserve">8.8147554397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74289608001709</t>
   </si>
   <si>
     <t xml:space="preserve">8.83391761779785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77643013000488</t>
+    <t xml:space="preserve">8.77642917633057</t>
   </si>
   <si>
     <t xml:space="preserve">8.7093620300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68540668487549</t>
+    <t xml:space="preserve">8.6854076385498</t>
   </si>
   <si>
     <t xml:space="preserve">8.70457077026367</t>
@@ -1814,13 +1814,13 @@
     <t xml:space="preserve">8.78122138977051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80996417999268</t>
+    <t xml:space="preserve">8.80996513366699</t>
   </si>
   <si>
     <t xml:space="preserve">8.77163982391357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65187454223633</t>
+    <t xml:space="preserve">8.6518726348877</t>
   </si>
   <si>
     <t xml:space="preserve">8.53689861297607</t>
@@ -1829,25 +1829,25 @@
     <t xml:space="preserve">8.37880802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3740177154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40755081176758</t>
+    <t xml:space="preserve">8.37401676177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40755176544189</t>
   </si>
   <si>
     <t xml:space="preserve">8.41234302520752</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32611083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45545673370361</t>
+    <t xml:space="preserve">8.32610988616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45545864105225</t>
   </si>
   <si>
     <t xml:space="preserve">8.41713333129883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39317989349365</t>
+    <t xml:space="preserve">8.39318084716797</t>
   </si>
   <si>
     <t xml:space="preserve">8.54647922515869</t>
@@ -1856,67 +1856,67 @@
     <t xml:space="preserve">8.58959579467773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27341461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22071838378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25425148010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35485458374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47461986541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42192459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36922740936279</t>
+    <t xml:space="preserve">8.27341365814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22071647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25425052642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35485553741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4746208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42192268371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36922645568848</t>
   </si>
   <si>
     <t xml:space="preserve">8.31653022766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29736804962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28299617767334</t>
+    <t xml:space="preserve">8.29736709594727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28299522399902</t>
   </si>
   <si>
     <t xml:space="preserve">8.17760181427002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2015552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16322898864746</t>
+    <t xml:space="preserve">8.20155429840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16322994232178</t>
   </si>
   <si>
     <t xml:space="preserve">8.24946022033691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18239116668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17281150817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09616184234619</t>
+    <t xml:space="preserve">8.18239307403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17281055450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09616088867188</t>
   </si>
   <si>
     <t xml:space="preserve">8.14885711669922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06741809844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03867340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97160577774048</t>
+    <t xml:space="preserve">8.06741714477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03867435455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97160387039185</t>
   </si>
   <si>
     <t xml:space="preserve">7.78956031799316</t>
@@ -1925,13 +1925,13 @@
     <t xml:space="preserve">7.62188863754272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61709785461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66021394729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50212383270264</t>
+    <t xml:space="preserve">7.61709833145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66021347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50212287902832</t>
   </si>
   <si>
     <t xml:space="preserve">7.72249221801758</t>
@@ -1949,22 +1949,22 @@
     <t xml:space="preserve">7.65542268753052</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59793519973755</t>
+    <t xml:space="preserve">7.59793567657471</t>
   </si>
   <si>
     <t xml:space="preserve">7.90932655334473</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95244264602661</t>
+    <t xml:space="preserve">7.95244216918945</t>
   </si>
   <si>
     <t xml:space="preserve">7.82309484481812</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8805832862854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10574245452881</t>
+    <t xml:space="preserve">7.88058376312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10574150085449</t>
   </si>
   <si>
     <t xml:space="preserve">8.20634460449219</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">8.16802024841309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26383304595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3452730178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29257678985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12011337280273</t>
+    <t xml:space="preserve">8.26383209228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34527397155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29257583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12011432647705</t>
   </si>
   <si>
     <t xml:space="preserve">8.0338830947876</t>
@@ -1994,145 +1994,145 @@
     <t xml:space="preserve">7.80872297286987</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91411781311035</t>
+    <t xml:space="preserve">7.91411685943604</t>
   </si>
   <si>
     <t xml:space="preserve">7.88537263870239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82788515090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84704732894897</t>
+    <t xml:space="preserve">7.82788610458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84704828262329</t>
   </si>
   <si>
     <t xml:space="preserve">8.00034809112549</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89974594116211</t>
+    <t xml:space="preserve">7.89974546432495</t>
   </si>
   <si>
     <t xml:space="preserve">7.9045352935791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94286060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71770095825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85663032531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04346370697021</t>
+    <t xml:space="preserve">7.94286108016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71770143508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85662889480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04346466064453</t>
   </si>
   <si>
     <t xml:space="preserve">8.11532402038574</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12969493865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13448524475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00992870330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9332799911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75123596191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57877254486084</t>
+    <t xml:space="preserve">8.12969589233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13448619842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00992965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93327903747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75123643875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.578773021698</t>
   </si>
   <si>
     <t xml:space="preserve">7.64105129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69374799728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83746767044067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81351375579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87100124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87579250335693</t>
+    <t xml:space="preserve">7.69374847412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83746671676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81351280212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87100219726562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87579202651978</t>
   </si>
   <si>
     <t xml:space="preserve">7.92369842529297</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89495372772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85183954238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86621046066284</t>
+    <t xml:space="preserve">7.89495468139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85183811187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8662109375</t>
   </si>
   <si>
     <t xml:space="preserve">7.9859766960144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.96681261062622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92848873138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11053371429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04825401306152</t>
+    <t xml:space="preserve">7.96681451797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92848777770996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11053276062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04825496673584</t>
   </si>
   <si>
     <t xml:space="preserve">7.93806934356689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77998018264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81830406188965</t>
+    <t xml:space="preserve">7.77997970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81830501556396</t>
   </si>
   <si>
     <t xml:space="preserve">7.84225845336914</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79435157775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79914331436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94765186309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91890811920166</t>
+    <t xml:space="preserve">7.79435110092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79914236068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94765043258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9189076423645</t>
   </si>
   <si>
     <t xml:space="preserve">7.7129111289978</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7751898765564</t>
+    <t xml:space="preserve">7.77518844604492</t>
   </si>
   <si>
     <t xml:space="preserve">7.86141967773438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07699871063232</t>
+    <t xml:space="preserve">8.07699966430664</t>
   </si>
   <si>
     <t xml:space="preserve">8.21592712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26862335205078</t>
+    <t xml:space="preserve">8.2686243057251</t>
   </si>
   <si>
     <t xml:space="preserve">8.33569240570068</t>
@@ -2141,13 +2141,13 @@
     <t xml:space="preserve">8.45066738128662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36443519592285</t>
+    <t xml:space="preserve">8.36443614959717</t>
   </si>
   <si>
     <t xml:space="preserve">8.47941112518311</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55127143859863</t>
+    <t xml:space="preserve">8.55127048492432</t>
   </si>
   <si>
     <t xml:space="preserve">8.59438610076904</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">7.74165439605713</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70332908630371</t>
+    <t xml:space="preserve">7.70332956314087</t>
   </si>
   <si>
     <t xml:space="preserve">7.78477001190186</t>
@@ -2180,34 +2180,34 @@
     <t xml:space="preserve">7.44463539123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22426700592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17636013031006</t>
+    <t xml:space="preserve">7.22426605224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17636060714722</t>
   </si>
   <si>
     <t xml:space="preserve">7.30091667175293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36319494247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33924150466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09492015838623</t>
+    <t xml:space="preserve">7.36319541931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33924198150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09491968154907</t>
   </si>
   <si>
     <t xml:space="preserve">6.69729709625244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36195373535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3367600440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54754686355591</t>
+    <t xml:space="preserve">6.3619532585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33675956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54754734039307</t>
   </si>
   <si>
     <t xml:space="preserve">5.37987470626831</t>
@@ -2219,43 +2219,43 @@
     <t xml:space="preserve">5.8685188293457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45776653289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08409738540649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03619146347046</t>
+    <t xml:space="preserve">6.45776605606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08409690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0361909866333</t>
   </si>
   <si>
     <t xml:space="preserve">6.29967546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76915693283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84101581573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53441667556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37153577804565</t>
+    <t xml:space="preserve">6.76915740966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84101629257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53441572189331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37153482437134</t>
   </si>
   <si>
     <t xml:space="preserve">6.27572298049927</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02852582931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.110924243927</t>
+    <t xml:space="preserve">6.02852630615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11092519760132</t>
   </si>
   <si>
     <t xml:space="preserve">5.85606336593628</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45201683044434</t>
+    <t xml:space="preserve">6.45201730728149</t>
   </si>
   <si>
     <t xml:space="preserve">6.38111591339111</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">6.40986061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40794372558594</t>
+    <t xml:space="preserve">6.4079442024231</t>
   </si>
   <si>
     <t xml:space="preserve">6.47309637069702</t>
@@ -2279,10 +2279,10 @@
     <t xml:space="preserve">6.65897226333618</t>
   </si>
   <si>
-    <t xml:space="preserve">6.49962091445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44746923446655</t>
+    <t xml:space="preserve">6.49962043762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44746971130371</t>
   </si>
   <si>
     <t xml:space="preserve">6.43008518218994</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">6.393385887146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44360542297363</t>
+    <t xml:space="preserve">6.44360637664795</t>
   </si>
   <si>
     <t xml:space="preserve">6.59619760513306</t>
   </si>
   <si>
-    <t xml:space="preserve">6.61551237106323</t>
+    <t xml:space="preserve">6.61551332473755</t>
   </si>
   <si>
     <t xml:space="preserve">6.79321384429932</t>
@@ -2309,16 +2309,16 @@
     <t xml:space="preserve">6.62323951721191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69084310531616</t>
+    <t xml:space="preserve">6.690842628479</t>
   </si>
   <si>
     <t xml:space="preserve">6.76617288589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78935146331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94773721694946</t>
+    <t xml:space="preserve">6.78935194015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9477367401123</t>
   </si>
   <si>
     <t xml:space="preserve">6.95932626724243</t>
@@ -2330,31 +2330,31 @@
     <t xml:space="preserve">6.93807983398438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70629501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66766452789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94001054763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.51121044158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67345857620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53245687484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6638011932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67732191085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72947359085083</t>
+    <t xml:space="preserve">6.70629549026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66766405105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9400110244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5112099647522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67345905303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53245735168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66380167007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67732238769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72947406768799</t>
   </si>
   <si>
     <t xml:space="preserve">6.71208953857422</t>
@@ -2375,34 +2375,34 @@
     <t xml:space="preserve">7.09839677810669</t>
   </si>
   <si>
-    <t xml:space="preserve">7.142822265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14475393295288</t>
+    <t xml:space="preserve">7.14282274246216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14475345611572</t>
   </si>
   <si>
     <t xml:space="preserve">7.13895988464355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17759037017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05976676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20463132858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06942415237427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31279754638672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33018207550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38619518280029</t>
+    <t xml:space="preserve">7.17758989334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05976629257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20463180541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06942462921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31279802322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33018112182617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38619565963745</t>
   </si>
   <si>
     <t xml:space="preserve">7.44800519943237</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">7.44027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58128070831299</t>
+    <t xml:space="preserve">7.58128118515015</t>
   </si>
   <si>
     <t xml:space="preserve">7.27223539352417</t>
@@ -2423,31 +2423,31 @@
     <t xml:space="preserve">7.24326229095459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34370279312134</t>
+    <t xml:space="preserve">7.34370183944702</t>
   </si>
   <si>
     <t xml:space="preserve">7.54844522476196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45380020141602</t>
+    <t xml:space="preserve">7.45379972457886</t>
   </si>
   <si>
     <t xml:space="preserve">7.62667179107666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67013168334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70683097839355</t>
+    <t xml:space="preserve">7.67013216018677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70683145523071</t>
   </si>
   <si>
     <t xml:space="preserve">7.84203910827637</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86425161361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81499767303467</t>
+    <t xml:space="preserve">7.86425113677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81499719619751</t>
   </si>
   <si>
     <t xml:space="preserve">7.75029039382935</t>
@@ -2456,22 +2456,22 @@
     <t xml:space="preserve">7.92412853240967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91350650787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82851791381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89322519302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98497247695923</t>
+    <t xml:space="preserve">7.91350698471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8285174369812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89322471618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98497152328491</t>
   </si>
   <si>
     <t xml:space="preserve">7.87294340133667</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02649974822998</t>
+    <t xml:space="preserve">8.0265007019043</t>
   </si>
   <si>
     <t xml:space="preserve">7.885498046875</t>
@@ -2480,22 +2480,22 @@
     <t xml:space="preserve">7.83817577362061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2631139755249</t>
+    <t xml:space="preserve">8.26311302185059</t>
   </si>
   <si>
     <t xml:space="preserve">8.42729473114014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21965503692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22158432006836</t>
+    <t xml:space="preserve">8.21965312957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22158527374268</t>
   </si>
   <si>
     <t xml:space="preserve">8.28146362304688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23221015930176</t>
+    <t xml:space="preserve">8.23220920562744</t>
   </si>
   <si>
     <t xml:space="preserve">8.29594993591309</t>
@@ -2507,52 +2507,52 @@
     <t xml:space="preserve">8.20806503295898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21868896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26601028442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43598651885986</t>
+    <t xml:space="preserve">8.21868801116943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26601219177246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43598556518555</t>
   </si>
   <si>
     <t xml:space="preserve">8.39735507965088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2775993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30753993988037</t>
+    <t xml:space="preserve">8.27760028839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30753898620605</t>
   </si>
   <si>
     <t xml:space="preserve">8.24283313751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22834491729736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39059448242188</t>
+    <t xml:space="preserve">8.34423923492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.228346824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39059543609619</t>
   </si>
   <si>
     <t xml:space="preserve">8.34327220916748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43405342102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31043529510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18102359771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29788112640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48330879211426</t>
+    <t xml:space="preserve">8.43405437469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3104362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18102264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29788208007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48330974578857</t>
   </si>
   <si>
     <t xml:space="preserve">8.77110862731934</t>
@@ -2561,61 +2561,61 @@
     <t xml:space="preserve">8.58664608001709</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47944641113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71799087524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65907859802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75565528869629</t>
+    <t xml:space="preserve">8.4794454574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71799182891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65907764434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75565433502197</t>
   </si>
   <si>
     <t xml:space="preserve">8.71412658691406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82132720947266</t>
+    <t xml:space="preserve">8.82132816314697</t>
   </si>
   <si>
     <t xml:space="preserve">8.94784450531006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01448249816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03959178924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0608377456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85319709777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94011688232422</t>
+    <t xml:space="preserve">9.01448059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03959083557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06083869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85319805145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94011783599854</t>
   </si>
   <si>
     <t xml:space="preserve">9.01641368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05118083953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80587482452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08884620666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01158428192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99999523162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04828262329102</t>
+    <t xml:space="preserve">9.05117988586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80587577819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08884716033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01158332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99999618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04828357696533</t>
   </si>
   <si>
     <t xml:space="preserve">9.04635238647461</t>
@@ -2633,13 +2633,13 @@
     <t xml:space="preserve">8.9719877243042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04442024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21342849731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23854064941406</t>
+    <t xml:space="preserve">9.04441928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21342945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23853969573975</t>
   </si>
   <si>
     <t xml:space="preserve">9.1747989654541</t>
@@ -2648,34 +2648,34 @@
     <t xml:space="preserve">9.06180381774902</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12554454803467</t>
+    <t xml:space="preserve">9.12554550170898</t>
   </si>
   <si>
     <t xml:space="preserve">9.0318660736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07629108428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80008125305176</t>
+    <t xml:space="preserve">9.07629013061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80008029937744</t>
   </si>
   <si>
     <t xml:space="preserve">8.93528842926025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94687747955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74020385742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88893127441406</t>
+    <t xml:space="preserve">8.94687843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74020290374756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88893222808838</t>
   </si>
   <si>
     <t xml:space="preserve">8.66294193267822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50262451171875</t>
+    <t xml:space="preserve">8.50262355804443</t>
   </si>
   <si>
     <t xml:space="preserve">8.65714740753174</t>
@@ -2690,46 +2690,46 @@
     <t xml:space="preserve">8.76724529266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8908634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96426010131836</t>
+    <t xml:space="preserve">8.89086437225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96426105499268</t>
   </si>
   <si>
     <t xml:space="preserve">9.24626541137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51281833648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35443115234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29841709136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44328308105469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43169403076172</t>
+    <t xml:space="preserve">9.26171779632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51281642913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35443210601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29841804504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44328212738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4316930770874</t>
   </si>
   <si>
     <t xml:space="preserve">9.25012874603271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13230514526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22501850128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06856536865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19411563873291</t>
+    <t xml:space="preserve">9.13230609893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22501945495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06856441497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19411468505859</t>
   </si>
   <si>
     <t xml:space="preserve">9.17286777496338</t>
@@ -2741,19 +2741,19 @@
     <t xml:space="preserve">9.36215877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12650966644287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1477575302124</t>
+    <t xml:space="preserve">9.12651062011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14775657653809</t>
   </si>
   <si>
     <t xml:space="preserve">9.13037395477295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15934658050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12264823913574</t>
+    <t xml:space="preserve">9.15934753417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12264728546143</t>
   </si>
   <si>
     <t xml:space="preserve">9.00482368469238</t>
@@ -2768,10 +2768,10 @@
     <t xml:space="preserve">9.04538631439209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8367805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87347984313965</t>
+    <t xml:space="preserve">8.83677864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87347888946533</t>
   </si>
   <si>
     <t xml:space="preserve">8.95267200469971</t>
@@ -2780,61 +2780,61 @@
     <t xml:space="preserve">8.9391508102417</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86961650848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88120651245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96619415283203</t>
+    <t xml:space="preserve">8.86961460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88120555877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9661922454834</t>
   </si>
   <si>
     <t xml:space="preserve">9.13809967041016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02027702331543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90438365936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66487407684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59340572357178</t>
+    <t xml:space="preserve">9.02027606964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90438461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66487503051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59340667724609</t>
   </si>
   <si>
     <t xml:space="preserve">8.5412540435791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55284404754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42149925231934</t>
+    <t xml:space="preserve">8.5528450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42150020599365</t>
   </si>
   <si>
     <t xml:space="preserve">8.38093852996826</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47365188598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42343044281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42536354064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5470495223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49296569824219</t>
+    <t xml:space="preserve">8.47365093231201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42343139648438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42536163330078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54705047607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4929666519165</t>
   </si>
   <si>
     <t xml:space="preserve">8.58568000793457</t>
   </si>
   <si>
-    <t xml:space="preserve">8.512282371521</t>
+    <t xml:space="preserve">8.51228141784668</t>
   </si>
   <si>
     <t xml:space="preserve">8.5064868927002</t>
@@ -2843,13 +2843,13 @@
     <t xml:space="preserve">8.63590049743652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59533786773682</t>
+    <t xml:space="preserve">8.59533882141113</t>
   </si>
   <si>
     <t xml:space="preserve">8.65328407287598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57215881347656</t>
+    <t xml:space="preserve">8.57215976715088</t>
   </si>
   <si>
     <t xml:space="preserve">8.57795429229736</t>
@@ -2858,34 +2858,34 @@
     <t xml:space="preserve">8.82712364196777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86768436431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94108295440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33704948425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31773281097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40272045135498</t>
+    <t xml:space="preserve">8.86768531799316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94108390808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33704853057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3177318572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40271949768066</t>
   </si>
   <si>
     <t xml:space="preserve">9.34477424621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38533687591553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44521331787109</t>
+    <t xml:space="preserve">9.38533782958984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44521427154541</t>
   </si>
   <si>
     <t xml:space="preserve">9.58235263824463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42975997924805</t>
+    <t xml:space="preserve">9.42976093292236</t>
   </si>
   <si>
     <t xml:space="preserve">9.44135093688965</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">9.35250091552734</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20570278167725</t>
+    <t xml:space="preserve">9.20570373535156</t>
   </si>
   <si>
     <t xml:space="preserve">9.2887601852417</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">9.3158016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34091091156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05697536468506</t>
+    <t xml:space="preserve">9.34091186523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05697631835938</t>
   </si>
   <si>
     <t xml:space="preserve">9.19218254089355</t>
@@ -2915,25 +2915,25 @@
     <t xml:space="preserve">9.16320991516113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04924869537354</t>
+    <t xml:space="preserve">9.04924964904785</t>
   </si>
   <si>
     <t xml:space="preserve">9.26751232147217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1690034866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36795234680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5244083404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76391792297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48963928222656</t>
+    <t xml:space="preserve">9.16900539398193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36795330047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52440738677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.763916015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48963832855225</t>
   </si>
   <si>
     <t xml:space="preserve">9.46839237213135</t>
@@ -2948,64 +2948,64 @@
     <t xml:space="preserve">9.36408996582031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2829647064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25978755950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24240207672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26365089416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28682804107666</t>
+    <t xml:space="preserve">9.28296566009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25978660583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24240303039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26364898681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28682708740234</t>
   </si>
   <si>
     <t xml:space="preserve">9.3505687713623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23081398010254</t>
+    <t xml:space="preserve">9.23081207275391</t>
   </si>
   <si>
     <t xml:space="preserve">9.39885711669922</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32932090759277</t>
+    <t xml:space="preserve">9.32932186126709</t>
   </si>
   <si>
     <t xml:space="preserve">9.4645299911499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41624164581299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63836860656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47225475311279</t>
+    <t xml:space="preserve">9.41624069213867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63836669921875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47225570678711</t>
   </si>
   <si>
     <t xml:space="preserve">9.56497001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64416217803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76943778991699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55384826660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73544788360596</t>
+    <t xml:space="preserve">9.64416313171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76943588256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5538501739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73544692993164</t>
   </si>
   <si>
     <t xml:space="preserve">9.83255958557129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70340061187744</t>
+    <t xml:space="preserve">9.70339965820312</t>
   </si>
   <si>
     <t xml:space="preserve">9.62959575653076</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">9.52859973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63348007202148</t>
+    <t xml:space="preserve">9.6334810256958</t>
   </si>
   <si>
     <t xml:space="preserve">9.8811149597168</t>
@@ -3026,16 +3026,16 @@
     <t xml:space="preserve">10.0025053024292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0947618484497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98308181762695</t>
+    <t xml:space="preserve">10.0947608947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98308086395264</t>
   </si>
   <si>
     <t xml:space="preserve">9.94423675537109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77429103851318</t>
+    <t xml:space="preserve">9.7742919921875</t>
   </si>
   <si>
     <t xml:space="preserve">9.86654758453369</t>
@@ -3044,16 +3044,16 @@
     <t xml:space="preserve">9.82284736633301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81313705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82770252227783</t>
+    <t xml:space="preserve">9.81313610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82770347595215</t>
   </si>
   <si>
     <t xml:space="preserve">9.79856967926025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79371452331543</t>
+    <t xml:space="preserve">9.79371356964111</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656270980835</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">10.1870164871216</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1481704711914</t>
+    <t xml:space="preserve">10.14817237854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2307167053223</t>
@@ -3080,34 +3080,34 @@
     <t xml:space="preserve">10.2792730331421</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2744178771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3132619857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3909502029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5754652023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6337299346924</t>
+    <t xml:space="preserve">10.2744169235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3132610321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3909511566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5754632949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6337308883667</t>
   </si>
   <si>
     <t xml:space="preserve">10.8133869171143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8182439804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8328084945679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8230981826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8570880889893</t>
+    <t xml:space="preserve">10.8182430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8328094482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8230991363525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8570871353149</t>
   </si>
   <si>
     <t xml:space="preserve">10.7551193237305</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">10.7454090118408</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7842531204224</t>
+    <t xml:space="preserve">10.7842540740967</t>
   </si>
   <si>
     <t xml:space="preserve">11.0852994918823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0755882263184</t>
+    <t xml:space="preserve">11.0755891799927</t>
   </si>
   <si>
     <t xml:space="preserve">11.0610218048096</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">11.0027551651001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9104976654053</t>
+    <t xml:space="preserve">10.9104986190796</t>
   </si>
   <si>
     <t xml:space="preserve">10.891077041626</t>
@@ -3149,37 +3149,37 @@
     <t xml:space="preserve">10.827953338623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.954197883606</t>
+    <t xml:space="preserve">10.9541988372803</t>
   </si>
   <si>
     <t xml:space="preserve">10.9784774780273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8667984008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6531524658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7162761688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9930429458618</t>
+    <t xml:space="preserve">10.8667974472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6531534194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7162752151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9930438995361</t>
   </si>
   <si>
     <t xml:space="preserve">11.162989616394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0513105392456</t>
+    <t xml:space="preserve">11.0513114929199</t>
   </si>
   <si>
     <t xml:space="preserve">11.4009122848511</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4688920974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4931688308716</t>
+    <t xml:space="preserve">11.4688911437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4931697845459</t>
   </si>
   <si>
     <t xml:space="preserve">11.5174465179443</t>
@@ -3188,13 +3188,13 @@
     <t xml:space="preserve">11.5951356887817</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5611476898193</t>
+    <t xml:space="preserve">11.561146736145</t>
   </si>
   <si>
     <t xml:space="preserve">11.5028800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.60484790802</t>
+    <t xml:space="preserve">11.6048469543457</t>
   </si>
   <si>
     <t xml:space="preserve">11.5805702209473</t>
@@ -3203,10 +3203,10 @@
     <t xml:space="preserve">11.5660028457642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6097040176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.721381187439</t>
+    <t xml:space="preserve">11.6097021102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7213821411133</t>
   </si>
   <si>
     <t xml:space="preserve">11.8621940612793</t>
@@ -3221,22 +3221,22 @@
     <t xml:space="preserve">11.6825370788574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3620691299438</t>
+    <t xml:space="preserve">11.3620681762695</t>
   </si>
   <si>
     <t xml:space="preserve">11.2552452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4834585189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4251918792725</t>
+    <t xml:space="preserve">11.4834575653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4251899719238</t>
   </si>
   <si>
     <t xml:space="preserve">11.3814907073975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3669233322144</t>
+    <t xml:space="preserve">11.3669242858887</t>
   </si>
   <si>
     <t xml:space="preserve">11.3329343795776</t>
@@ -3257,55 +3257,55 @@
     <t xml:space="preserve">11.5757141113281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5125913619995</t>
+    <t xml:space="preserve">11.5125904083252</t>
   </si>
   <si>
     <t xml:space="preserve">11.410623550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5514354705811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7068157196045</t>
+    <t xml:space="preserve">11.5514373779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7068147659302</t>
   </si>
   <si>
     <t xml:space="preserve">11.949595451355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9301719665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7942161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7602252960205</t>
+    <t xml:space="preserve">11.9301710128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7942152023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7602262496948</t>
   </si>
   <si>
     <t xml:space="preserve">11.8087825775146</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8282051086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7505149841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9253168106079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0175714492798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.05641746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.036994934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.187518119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1486740112305</t>
+    <t xml:space="preserve">11.8282041549683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7505159378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9253149032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0175724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0564165115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0369958877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1875171661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1486730575562</t>
   </si>
   <si>
     <t xml:space="preserve">12.3865966796875</t>
@@ -3314,16 +3314,16 @@
     <t xml:space="preserve">12.5565423965454</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4254417419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5274085998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5322637557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5662536621094</t>
+    <t xml:space="preserve">12.425440788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5274076461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5322647094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5662527084351</t>
   </si>
   <si>
     <t xml:space="preserve">11.9350271224976</t>
@@ -3332,7 +3332,7 @@
     <t xml:space="preserve">12.012716293335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0758390426636</t>
+    <t xml:space="preserve">12.0758399963379</t>
   </si>
   <si>
     <t xml:space="preserve">12.1729507446289</t>
@@ -3347,7 +3347,7 @@
     <t xml:space="preserve">12.4205856323242</t>
   </si>
   <si>
-    <t xml:space="preserve">12.304051399231</t>
+    <t xml:space="preserve">12.3040523529053</t>
   </si>
   <si>
     <t xml:space="preserve">12.4108743667603</t>
@@ -3356,28 +3356,28 @@
     <t xml:space="preserve">12.444863319397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4157295227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5468320846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6439437866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7750434875488</t>
+    <t xml:space="preserve">12.4157285690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5468311309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6439418792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7750425338745</t>
   </si>
   <si>
     <t xml:space="preserve">12.9644117355347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9595556259155</t>
+    <t xml:space="preserve">12.9595546722412</t>
   </si>
   <si>
     <t xml:space="preserve">12.9401330947876</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0760898590088</t>
+    <t xml:space="preserve">13.0760908126831</t>
   </si>
   <si>
     <t xml:space="preserve">12.5808200836182</t>
@@ -3386,76 +3386,76 @@
     <t xml:space="preserve">12.5953874588013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9109992980957</t>
+    <t xml:space="preserve">12.91100025177</t>
   </si>
   <si>
     <t xml:space="preserve">12.4837074279785</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7070655822754</t>
+    <t xml:space="preserve">12.7070646286011</t>
   </si>
   <si>
     <t xml:space="preserve">12.4982748031616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4739980697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3428955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6390867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8721551895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6099529266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5856742858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3768854141235</t>
+    <t xml:space="preserve">12.4739971160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3428964614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.639087677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8721542358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6099538803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5856761932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3768844604492</t>
   </si>
   <si>
     <t xml:space="preserve">12.4885635375977</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2846298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2797737121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2020835876465</t>
+    <t xml:space="preserve">12.2846279144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2797746658325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2020845413208</t>
   </si>
   <si>
     <t xml:space="preserve">12.4400081634521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3720302581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.435152053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3963088989258</t>
+    <t xml:space="preserve">12.3720293045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4351530075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3963079452515</t>
   </si>
   <si>
     <t xml:space="preserve">12.4060192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7553701400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6728248596191</t>
+    <t xml:space="preserve">11.7553691864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6728267669678</t>
   </si>
   <si>
     <t xml:space="preserve">11.6388359069824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4397583007812</t>
+    <t xml:space="preserve">11.4397563934326</t>
   </si>
   <si>
     <t xml:space="preserve">11.1532773971558</t>
@@ -3464,58 +3464,58 @@
     <t xml:space="preserve">11.2164011001587</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0804443359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.065878868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6968545913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6434421539307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6191654205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5171957015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7696876525879</t>
+    <t xml:space="preserve">11.0804433822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0658769607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6968536376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6434412002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6191644668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5171976089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7696866989136</t>
   </si>
   <si>
     <t xml:space="preserve">10.9833326339722</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8619432449341</t>
+    <t xml:space="preserve">10.8619441986084</t>
   </si>
   <si>
     <t xml:space="preserve">10.7114191055298</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5269079208374</t>
+    <t xml:space="preserve">10.5269069671631</t>
   </si>
   <si>
     <t xml:space="preserve">10.44921875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5317630767822</t>
+    <t xml:space="preserve">10.5317640304565</t>
   </si>
   <si>
     <t xml:space="preserve">10.4880628585815</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3375406265259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0899047851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821613311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1918716430664</t>
+    <t xml:space="preserve">10.3375396728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0899057388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821603775024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1918725967407</t>
   </si>
   <si>
     <t xml:space="preserve">10.264705657959</t>
@@ -3524,19 +3524,19 @@
     <t xml:space="preserve">9.9588041305542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02556037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18870830535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46644878387451</t>
+    <t xml:space="preserve">9.025559425354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18870735168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4664478302002</t>
   </si>
   <si>
     <t xml:space="preserve">9.04304122924805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04498386383057</t>
+    <t xml:space="preserve">9.04498291015625</t>
   </si>
   <si>
     <t xml:space="preserve">9.06246280670166</t>
@@ -3545,13 +3545,13 @@
     <t xml:space="preserve">8.84299087524414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8391056060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54388618469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1440372467041</t>
+    <t xml:space="preserve">8.83910751342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5438871383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14403820037842</t>
   </si>
   <si>
     <t xml:space="preserve">8.9906005859375</t>
@@ -3563,10 +3563,10 @@
     <t xml:space="preserve">8.99836921691895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03138732910156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58492469787598</t>
+    <t xml:space="preserve">9.03138828277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58492374420166</t>
   </si>
   <si>
     <t xml:space="preserve">9.55190658569336</t>
@@ -3575,7 +3575,7 @@
     <t xml:space="preserve">9.75001430511475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62182712554932</t>
+    <t xml:space="preserve">9.621826171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.68203639984131</t>
@@ -3587,25 +3587,25 @@
     <t xml:space="preserve">9.62571144104004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0801944732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2598505020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2501401901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4200839996338</t>
+    <t xml:space="preserve">10.0801935195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2598495483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2501392364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4200849533081</t>
   </si>
   <si>
     <t xml:space="preserve">10.3860950469971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5074844360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346523284912</t>
+    <t xml:space="preserve">10.5074863433838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4346513748169</t>
   </si>
   <si>
     <t xml:space="preserve">10.4152297973633</t>
@@ -3617,13 +3617,13 @@
     <t xml:space="preserve">10.2110719680786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5284900665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3429231643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3819894790649</t>
+    <t xml:space="preserve">10.528489112854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3429222106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3819885253906</t>
   </si>
   <si>
     <t xml:space="preserve">10.4308233261108</t>
@@ -3632,34 +3632,34 @@
     <t xml:space="preserve">10.4210567474365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4259405136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5333738327026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2306051254272</t>
+    <t xml:space="preserve">10.4259395599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5333728790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2306060791016</t>
   </si>
   <si>
     <t xml:space="preserve">10.4601230621338</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0645723342896</t>
+    <t xml:space="preserve">10.0645713806152</t>
   </si>
   <si>
     <t xml:space="preserve">10.1720056533813</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5498685836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33890724182129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58893489837646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68855476379395</t>
+    <t xml:space="preserve">9.54986763000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33890819549561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58893394470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68855571746826</t>
   </si>
   <si>
     <t xml:space="preserve">9.669020652771</t>
@@ -3671,40 +3671,40 @@
     <t xml:space="preserve">10.0059728622437</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91318893432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59870147705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39750671386719</t>
+    <t xml:space="preserve">9.91318798065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59870052337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39750576019287</t>
   </si>
   <si>
     <t xml:space="preserve">9.36234760284424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6182336807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40532112121582</t>
+    <t xml:space="preserve">9.61823463439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4053201675415</t>
   </si>
   <si>
     <t xml:space="preserve">9.47173404693604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47368717193604</t>
+    <t xml:space="preserve">9.47368812561035</t>
   </si>
   <si>
     <t xml:space="preserve">9.659255027771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78622245788574</t>
+    <t xml:space="preserve">9.78622150421143</t>
   </si>
   <si>
     <t xml:space="preserve">9.71004199981689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51861476898193</t>
+    <t xml:space="preserve">9.51861381530762</t>
   </si>
   <si>
     <t xml:space="preserve">9.69441413879395</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">9.68074131011963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54791450500488</t>
+    <t xml:space="preserve">9.54791355133057</t>
   </si>
   <si>
     <t xml:space="preserve">9.03418636322021</t>
@@ -3731,22 +3731,22 @@
     <t xml:space="preserve">8.8154125213623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20607948303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11427211761475</t>
+    <t xml:space="preserve">9.20608043670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11427307128906</t>
   </si>
   <si>
     <t xml:space="preserve">9.52252101898193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5674467086792</t>
+    <t xml:space="preserve">9.56744766235352</t>
   </si>
   <si>
     <t xml:space="preserve">9.46782779693604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5557279586792</t>
+    <t xml:space="preserve">9.55572891235352</t>
   </si>
   <si>
     <t xml:space="preserve">9.4541540145874</t>
@@ -3755,19 +3755,19 @@
     <t xml:space="preserve">9.79110431671143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85947132110596</t>
+    <t xml:space="preserve">9.85947227478027</t>
   </si>
   <si>
     <t xml:space="preserve">9.91807174682617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81552124023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80087089538574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72566890716553</t>
+    <t xml:space="preserve">9.81552219390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80087184906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72566795349121</t>
   </si>
   <si>
     <t xml:space="preserve">9.661208152771</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">10.2989730834961</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0499229431152</t>
+    <t xml:space="preserve">10.0499210357666</t>
   </si>
   <si>
     <t xml:space="preserve">9.94248867034912</t>
@@ -3815,16 +3815,16 @@
     <t xml:space="preserve">10.167121887207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5675563812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.367338180542</t>
+    <t xml:space="preserve">10.5675573348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3673391342163</t>
   </si>
   <si>
     <t xml:space="preserve">10.1182880401611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1964225769043</t>
+    <t xml:space="preserve">10.19642162323</t>
   </si>
   <si>
     <t xml:space="preserve">9.97667217254639</t>
@@ -3833,16 +3833,16 @@
     <t xml:space="preserve">9.81063747406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79598808288574</t>
+    <t xml:space="preserve">9.79598712921143</t>
   </si>
   <si>
     <t xml:space="preserve">9.78133869171143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87900543212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0352716445923</t>
+    <t xml:space="preserve">9.87900447845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0352725982666</t>
   </si>
   <si>
     <t xml:space="preserve">10.1134052276611</t>
@@ -3851,16 +3851,16 @@
     <t xml:space="preserve">10.1475896835327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.152473449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98155498504639</t>
+    <t xml:space="preserve">10.1524724960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9815559387207</t>
   </si>
   <si>
     <t xml:space="preserve">9.83505439758301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57916736602783</t>
+    <t xml:space="preserve">9.57916831970215</t>
   </si>
   <si>
     <t xml:space="preserve">9.4482946395874</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">9.46001434326172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29593372344971</t>
+    <t xml:space="preserve">9.29593276977539</t>
   </si>
   <si>
     <t xml:space="preserve">9.31742000579834</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">8.9658203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00683975219727</t>
+    <t xml:space="preserve">9.00684070587158</t>
   </si>
   <si>
     <t xml:space="preserve">8.94042682647705</t>
@@ -3902,25 +3902,25 @@
     <t xml:space="preserve">9.0752067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78025150299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68649291992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89550018310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84471321105957</t>
+    <t xml:space="preserve">8.78025245666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68649196624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89549922943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84471225738525</t>
   </si>
   <si>
     <t xml:space="preserve">8.88377857208252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72360515594482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89940738677979</t>
+    <t xml:space="preserve">8.72360610961914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89940643310547</t>
   </si>
   <si>
     <t xml:space="preserve">8.73532581329346</t>
@@ -3935,25 +3935,25 @@
     <t xml:space="preserve">8.88964080810547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79783344268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94628715515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98144626617432</t>
+    <t xml:space="preserve">8.79783248901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94628524780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98144721984863</t>
   </si>
   <si>
     <t xml:space="preserve">8.78611278533936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98535346984863</t>
+    <t xml:space="preserve">8.98535251617432</t>
   </si>
   <si>
     <t xml:space="preserve">8.96191215515137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84080505371094</t>
+    <t xml:space="preserve">8.84080600738525</t>
   </si>
   <si>
     <t xml:space="preserve">8.60054492950439</t>
@@ -3965,10 +3965,10 @@
     <t xml:space="preserve">8.72165298461914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90917301177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79587936401367</t>
+    <t xml:space="preserve">8.90917205810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79587841033936</t>
   </si>
   <si>
     <t xml:space="preserve">8.80173969268799</t>
@@ -3977,10 +3977,10 @@
     <t xml:space="preserve">8.70798015594482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88182544708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99707317352295</t>
+    <t xml:space="preserve">8.88182640075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99707221984863</t>
   </si>
   <si>
     <t xml:space="preserve">9.10841369628906</t>
@@ -3992,7 +3992,7 @@
     <t xml:space="preserve">9.09473991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11622619628906</t>
+    <t xml:space="preserve">9.11622714996338</t>
   </si>
   <si>
     <t xml:space="preserve">8.9755859375</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">9.54205513000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4932222366333</t>
+    <t xml:space="preserve">9.49322032928467</t>
   </si>
   <si>
     <t xml:space="preserve">9.5654935836792</t>
@@ -4016,10 +4016,10 @@
     <t xml:space="preserve">9.73543548583984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76278209686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1280546188354</t>
+    <t xml:space="preserve">9.76278114318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1280555725098</t>
   </si>
   <si>
     <t xml:space="preserve">9.96202182769775</t>
@@ -4031,16 +4031,16 @@
     <t xml:space="preserve">9.80575466156006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69050788879395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72371387481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75692176818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92783832550049</t>
+    <t xml:space="preserve">9.69050693511963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72371482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75692081451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9278392791748</t>
   </si>
   <si>
     <t xml:space="preserve">9.95225429534912</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">9.58502769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62214088439941</t>
+    <t xml:space="preserve">9.62214183807373</t>
   </si>
   <si>
     <t xml:space="preserve">9.31546783447266</t>
@@ -4061,10 +4061,10 @@
     <t xml:space="preserve">9.40336799621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38774013519287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42290115356445</t>
+    <t xml:space="preserve">9.38774108886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42290019989014</t>
   </si>
   <si>
     <t xml:space="preserve">9.45806121826172</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">9.33500003814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43461990356445</t>
+    <t xml:space="preserve">9.43462085723877</t>
   </si>
   <si>
     <t xml:space="preserve">9.59088706970215</t>
@@ -4085,10 +4085,10 @@
     <t xml:space="preserve">9.63190841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64948844909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65729999542236</t>
+    <t xml:space="preserve">9.64948749542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65730094909668</t>
   </si>
   <si>
     <t xml:space="preserve">9.74324798583984</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">9.71199512481689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71785354614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44438648223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42876052856445</t>
+    <t xml:space="preserve">9.71785449981689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4443883895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42876148223877</t>
   </si>
   <si>
     <t xml:space="preserve">9.43852615356445</t>
@@ -4112,7 +4112,7 @@
     <t xml:space="preserve">9.71590137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0303888320923</t>
+    <t xml:space="preserve">10.0303897857666</t>
   </si>
   <si>
     <t xml:space="preserve">9.90342235565186</t>
@@ -4121,10 +4121,10 @@
     <t xml:space="preserve">9.83017158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1427068710327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2696733474731</t>
+    <t xml:space="preserve">10.1427049636841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2696723937988</t>
   </si>
   <si>
     <t xml:space="preserve">10.2452554702759</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">10.3722219467163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3478059768677</t>
+    <t xml:space="preserve">10.347806930542</t>
   </si>
   <si>
     <t xml:space="preserve">10.5870895385742</t>
@@ -4157,28 +4157,28 @@
     <t xml:space="preserve">10.5382566452026</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4698905944824</t>
+    <t xml:space="preserve">10.4698896408081</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405889511108</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3917560577393</t>
+    <t xml:space="preserve">10.3917570114136</t>
   </si>
   <si>
     <t xml:space="preserve">10.4747734069824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6749906539917</t>
+    <t xml:space="preserve">10.6749897003174</t>
   </si>
   <si>
     <t xml:space="preserve">10.518723487854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6310396194458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6261568069458</t>
+    <t xml:space="preserve">10.6310405731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6261558532715</t>
   </si>
   <si>
     <t xml:space="preserve">10.7580070495605</t>
@@ -4187,13 +4187,13 @@
     <t xml:space="preserve">10.8703241348267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.860556602478</t>
+    <t xml:space="preserve">10.8605575561523</t>
   </si>
   <si>
     <t xml:space="preserve">10.8312568664551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7775392532349</t>
+    <t xml:space="preserve">10.7775402069092</t>
   </si>
   <si>
     <t xml:space="preserve">10.880090713501</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">11.0070581436157</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1291418075562</t>
+    <t xml:space="preserve">11.1291408538818</t>
   </si>
   <si>
     <t xml:space="preserve">11.2463417053223</t>
@@ -4220,22 +4220,22 @@
     <t xml:space="preserve">11.2268085479736</t>
   </si>
   <si>
-    <t xml:space="preserve">11.212158203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2072744369507</t>
+    <t xml:space="preserve">11.2121572494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.207275390625</t>
   </si>
   <si>
     <t xml:space="preserve">11.2561082839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2854080200195</t>
+    <t xml:space="preserve">11.2854089736938</t>
   </si>
   <si>
     <t xml:space="preserve">11.3195915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3488922119141</t>
+    <t xml:space="preserve">11.3488912582397</t>
   </si>
   <si>
     <t xml:space="preserve">11.373309135437</t>
@@ -4244,16 +4244,16 @@
     <t xml:space="preserve">11.5295753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5737504959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6670083999634</t>
+    <t xml:space="preserve">11.5737495422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6670074462891</t>
   </si>
   <si>
     <t xml:space="preserve">11.5982913970947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6326494216919</t>
+    <t xml:space="preserve">11.6326503753662</t>
   </si>
   <si>
     <t xml:space="preserve">11.4657678604126</t>
@@ -4262,13 +4262,13 @@
     <t xml:space="preserve">11.7700815200806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9418725967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9026050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0645799636841</t>
+    <t xml:space="preserve">11.9418716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.902606010437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0645790100098</t>
   </si>
   <si>
     <t xml:space="preserve">12.1038455963135</t>
@@ -4283,10 +4283,10 @@
     <t xml:space="preserve">12.054762840271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1627445220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9173316955566</t>
+    <t xml:space="preserve">12.162745475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9173307418823</t>
   </si>
   <si>
     <t xml:space="preserve">11.9467802047729</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">11.9369640350342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9860467910767</t>
+    <t xml:space="preserve">11.9860458374023</t>
   </si>
   <si>
     <t xml:space="preserve">12.2314615249634</t>
@@ -4325,28 +4325,28 @@
     <t xml:space="preserve">12.467059135437</t>
   </si>
   <si>
-    <t xml:space="preserve">12.413067817688</t>
+    <t xml:space="preserve">12.4130687713623</t>
   </si>
   <si>
     <t xml:space="preserve">12.5701332092285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.565224647522</t>
+    <t xml:space="preserve">12.5652256011963</t>
   </si>
   <si>
     <t xml:space="preserve">12.6633901596069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6143083572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6241245269775</t>
+    <t xml:space="preserve">12.6143074035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6241235733032</t>
   </si>
   <si>
     <t xml:space="preserve">12.2658185958862</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0596714019775</t>
+    <t xml:space="preserve">12.0596704483032</t>
   </si>
   <si>
     <t xml:space="preserve">12.0694875717163</t>
@@ -4370,16 +4370,16 @@
     <t xml:space="preserve">12.3050851821899</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3296279907227</t>
+    <t xml:space="preserve">12.3296270370483</t>
   </si>
   <si>
     <t xml:space="preserve">12.2216444015503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1921949386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4376087188721</t>
+    <t xml:space="preserve">12.1921939849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4376096725464</t>
   </si>
   <si>
     <t xml:space="preserve">12.4228839874268</t>
@@ -4388,7 +4388,7 @@
     <t xml:space="preserve">12.4866924285889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6928405761719</t>
+    <t xml:space="preserve">12.6928415298462</t>
   </si>
   <si>
     <t xml:space="preserve">12.4817838668823</t>
@@ -4412,13 +4412,13 @@
     <t xml:space="preserve">12.0940284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9762296676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9124221801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7946243286133</t>
+    <t xml:space="preserve">11.9762306213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9124231338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.794623374939</t>
   </si>
   <si>
     <t xml:space="preserve">11.8044395446777</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">11.7995319366455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8191652297974</t>
+    <t xml:space="preserve">11.819164276123</t>
   </si>
   <si>
     <t xml:space="preserve">11.8927888870239</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">11.4461345672607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3970518112183</t>
+    <t xml:space="preserve">11.3970508575439</t>
   </si>
   <si>
     <t xml:space="preserve">11.4706764221191</t>
@@ -4448,7 +4448,7 @@
     <t xml:space="preserve">11.3872356414795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5639333724976</t>
+    <t xml:space="preserve">11.5639324188232</t>
   </si>
   <si>
     <t xml:space="preserve">11.5835666656494</t>
@@ -4460,13 +4460,13 @@
     <t xml:space="preserve">11.9075136184692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.000771522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8486137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7749891281128</t>
+    <t xml:space="preserve">12.0007724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.848614692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7749900817871</t>
   </si>
   <si>
     <t xml:space="preserve">11.8535223007202</t>
@@ -4478,10 +4478,10 @@
     <t xml:space="preserve">11.5344839096069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6424655914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1516370773315</t>
+    <t xml:space="preserve">11.642466545105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1516361236572</t>
   </si>
   <si>
     <t xml:space="preserve">11.1025543212891</t>
@@ -4493,10 +4493,10 @@
     <t xml:space="preserve">11.1712703704834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2694358825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2841606140137</t>
+    <t xml:space="preserve">11.269434928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.284161567688</t>
   </si>
   <si>
     <t xml:space="preserve">11.54430103302</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">11.1909027099609</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0092973709106</t>
+    <t xml:space="preserve">11.0092964172363</t>
   </si>
   <si>
     <t xml:space="preserve">10.842414855957</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">10.68044090271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7687911987305</t>
+    <t xml:space="preserve">10.7687902450562</t>
   </si>
   <si>
     <t xml:space="preserve">10.9602136611938</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">10.9454879760742</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2547121047974</t>
+    <t xml:space="preserve">11.254711151123</t>
   </si>
   <si>
     <t xml:space="preserve">11.3087024688721</t>
@@ -4556,7 +4556,7 @@
     <t xml:space="preserve">10.7786064147949</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7393407821655</t>
+    <t xml:space="preserve">10.7393398284912</t>
   </si>
   <si>
     <t xml:space="preserve">10.7344331741333</t>
@@ -4565,13 +4565,13 @@
     <t xml:space="preserve">10.7246160507202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7589740753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8865900039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8571405410767</t>
+    <t xml:space="preserve">10.7589731216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.886589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8571395874023</t>
   </si>
   <si>
     <t xml:space="preserve">10.1208963394165</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">9.98346424102783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1945209503174</t>
+    <t xml:space="preserve">10.1945199966431</t>
   </si>
   <si>
     <t xml:space="preserve">10.2386951446533</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">10.48410987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871839523315</t>
+    <t xml:space="preserve">10.5871829986572</t>
   </si>
   <si>
     <t xml:space="preserve">10.5381002426147</t>
@@ -4601,22 +4601,22 @@
     <t xml:space="preserve">10.7295246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7000732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3466777801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2877769470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4055767059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3270454406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0669050216675</t>
+    <t xml:space="preserve">10.7000741958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3466768264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2877779006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4055776596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3270444869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0669040679932</t>
   </si>
   <si>
     <t xml:space="preserve">10.086537361145</t>
@@ -4640,13 +4640,13 @@
     <t xml:space="preserve">9.75375556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83621597290039</t>
+    <t xml:space="preserve">9.83621501922607</t>
   </si>
   <si>
     <t xml:space="preserve">9.83130741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86075687408447</t>
+    <t xml:space="preserve">9.86075592041016</t>
   </si>
   <si>
     <t xml:space="preserve">9.90493106842041</t>
@@ -4670,7 +4670,7 @@
     <t xml:space="preserve">9.8263988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91474723815918</t>
+    <t xml:space="preserve">9.9147481918335</t>
   </si>
   <si>
     <t xml:space="preserve">9.96382999420166</t>
@@ -4688,19 +4688,19 @@
     <t xml:space="preserve">10.0276384353638</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89020538330078</t>
+    <t xml:space="preserve">9.8902063369751</t>
   </si>
   <si>
     <t xml:space="preserve">9.76357269287109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8656644821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76553630828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74001312255859</t>
+    <t xml:space="preserve">9.86566543579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76553535461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74001216888428</t>
   </si>
   <si>
     <t xml:space="preserve">9.74393844604492</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">9.10782432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15494537353516</t>
+    <t xml:space="preserve">9.15494441986084</t>
   </si>
   <si>
     <t xml:space="preserve">9.14905452728271</t>
@@ -4718,7 +4718,7 @@
     <t xml:space="preserve">9.00769519805908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08033847808838</t>
+    <t xml:space="preserve">9.08033752441406</t>
   </si>
   <si>
     <t xml:space="preserve">9.06463146209717</t>
@@ -4739,19 +4739,19 @@
     <t xml:space="preserve">8.85455799102783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81528949737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29630374908447</t>
+    <t xml:space="preserve">8.8152904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29630279541016</t>
   </si>
   <si>
     <t xml:space="preserve">9.22758674621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23740291595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21580696105957</t>
+    <t xml:space="preserve">9.23740386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21580600738525</t>
   </si>
   <si>
     <t xml:space="preserve">9.37090873718262</t>
@@ -4775,19 +4775,19 @@
     <t xml:space="preserve">9.61043357849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56527805328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76749801635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78909587860107</t>
+    <t xml:space="preserve">9.56527709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76749897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78909492492676</t>
   </si>
   <si>
     <t xml:space="preserve">9.63988304138184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63792037963867</t>
+    <t xml:space="preserve">9.63791942596436</t>
   </si>
   <si>
     <t xml:space="preserve">9.6909294128418</t>
@@ -4799,16 +4799,16 @@
     <t xml:space="preserve">9.59080123901367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38072490692139</t>
+    <t xml:space="preserve">9.3807258605957</t>
   </si>
   <si>
     <t xml:space="preserve">9.65559005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32967853546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20010089874268</t>
+    <t xml:space="preserve">9.32967948913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20009994506836</t>
   </si>
   <si>
     <t xml:space="preserve">9.30023002624512</t>
@@ -4829,7 +4829,7 @@
     <t xml:space="preserve">9.36109256744385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40232181549072</t>
+    <t xml:space="preserve">9.40232276916504</t>
   </si>
   <si>
     <t xml:space="preserve">9.39054203033447</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">9.47300148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47103881835938</t>
+    <t xml:space="preserve">9.47103786468506</t>
   </si>
   <si>
     <t xml:space="preserve">9.37876224517822</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">9.27667045593262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08426380157471</t>
+    <t xml:space="preserve">9.08426475524902</t>
   </si>
   <si>
     <t xml:space="preserve">9.1254940032959</t>
@@ -4865,7 +4865,7 @@
     <t xml:space="preserve">9.06855869293213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14316463470459</t>
+    <t xml:space="preserve">9.14316368103027</t>
   </si>
   <si>
     <t xml:space="preserve">9.00573253631592</t>
@@ -4874,7 +4874,7 @@
     <t xml:space="preserve">8.89382362365723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02340221405029</t>
+    <t xml:space="preserve">9.02340316772461</t>
   </si>
   <si>
     <t xml:space="preserve">8.92523670196533</t>
@@ -4886,7 +4886,7 @@
     <t xml:space="preserve">8.92327308654785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88400745391846</t>
+    <t xml:space="preserve">8.88400650024414</t>
   </si>
   <si>
     <t xml:space="preserve">8.80743789672852</t>
@@ -4895,7 +4895,7 @@
     <t xml:space="preserve">8.73479461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76817035675049</t>
+    <t xml:space="preserve">8.7681713104248</t>
   </si>
   <si>
     <t xml:space="preserve">8.77995109558105</t>
@@ -4904,10 +4904,10 @@
     <t xml:space="preserve">8.9821720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21187973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3021936416626</t>
+    <t xml:space="preserve">9.21188068389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30219268798828</t>
   </si>
   <si>
     <t xml:space="preserve">9.42377090454102</t>
@@ -5940,6 +5940,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.44000005722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03999996185303</t>
   </si>
 </sst>
 </file>
@@ -71252,7 +71255,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6922800926</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>10513093</v>
@@ -71273,6 +71276,32 @@
         <v>1975</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.6940046296</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>35993452</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>6.09999990463257</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>5.7480001449585</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>5.82000017166138</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>6.03999996185303</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>1976</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1979" uniqueCount="1979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="1980">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,91 +38,91 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59865617752075</t>
+    <t xml:space="preserve">3.59865665435791</t>
   </si>
   <si>
     <t xml:space="preserve">CPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6589822769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60329675674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51976871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51048827171326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54993224143982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62881946563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68450450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57313442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52673006057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48264575004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5661735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43392109870911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5058479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56153321266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64274048805237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66594290733337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56849360466003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74250984191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72162842750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70770692825317</t>
+    <t xml:space="preserve">3.65898251533508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60329699516296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51976943016052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51048803329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54993176460266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62881922721863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68450498580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57313418388367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52672958374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48264598846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56617379188538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43392157554626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50584816932678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56153345108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64274096488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66594314575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56849408149719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74250960350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72162890434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70770668983459</t>
   </si>
   <si>
     <t xml:space="preserve">3.47104477882385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44320201873779</t>
+    <t xml:space="preserve">3.44320225715637</t>
   </si>
   <si>
     <t xml:space="preserve">3.28078675270081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33183193206787</t>
+    <t xml:space="preserve">3.33183145523071</t>
   </si>
   <si>
     <t xml:space="preserve">3.40839886665344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22046113014221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26918578147888</t>
+    <t xml:space="preserve">3.22046089172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26918625831604</t>
   </si>
   <si>
     <t xml:space="preserve">3.32487106323242</t>
@@ -131,151 +131,151 @@
     <t xml:space="preserve">3.24366307258606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32255101203918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28774738311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31791043281555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36663508415222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36199426651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40607881546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38287615776062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36431431770325</t>
+    <t xml:space="preserve">3.32255077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28774785995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31791067123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36663484573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36199450492859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40607857704163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3828763961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36431455612183</t>
   </si>
   <si>
     <t xml:space="preserve">3.53137016296387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60561752319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61257791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56385374069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61489748954773</t>
+    <t xml:space="preserve">3.60561728477478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61257767677307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5638530254364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61489844322205</t>
   </si>
   <si>
     <t xml:space="preserve">3.63810014724731</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68914532661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476229667664</t>
+    <t xml:space="preserve">3.68914484977722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8747615814209</t>
   </si>
   <si>
     <t xml:space="preserve">3.95597004890442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00701475143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04877853393555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03485679626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0418176651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03717803955078</t>
+    <t xml:space="preserve">4.00701522827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04877948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03485727310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04181814193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03717756271362</t>
   </si>
   <si>
     <t xml:space="preserve">4.05109882354736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01861572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09286260604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07662200927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0394983291626</t>
+    <t xml:space="preserve">4.01861619949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09286308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07662057876587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03949880599976</t>
   </si>
   <si>
     <t xml:space="preserve">4.08358240127563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02325677871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00005435943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06037998199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99541258811951</t>
+    <t xml:space="preserve">4.02325582504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00005483627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06037950515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99541354179382</t>
   </si>
   <si>
     <t xml:space="preserve">3.94436931610107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97453117370605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00237417221069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9374086856842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94668889045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03021764755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05341911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00933456420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9582896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98613309860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02557611465454</t>
+    <t xml:space="preserve">3.97453188896179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00237369537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93740773200989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94668936729431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03021669387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05341863632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0093355178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95829033851624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98613333702087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0255765914917</t>
   </si>
   <si>
     <t xml:space="preserve">3.96989130973816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91188597679138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89796423912048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87708210945129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91420602798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9281280040741</t>
+    <t xml:space="preserve">3.91188621520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89796447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87708330154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91420650482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92812776565552</t>
   </si>
   <si>
     <t xml:space="preserve">3.95132946968079</t>
@@ -284,73 +284,73 @@
     <t xml:space="preserve">4.06734085083008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08126163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99309301376343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96757078170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98149299621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96293020248413</t>
+    <t xml:space="preserve">4.08126211166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99309372901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9675714969635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98149228096008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96293091773987</t>
   </si>
   <si>
     <t xml:space="preserve">3.88868379592896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89332413673401</t>
+    <t xml:space="preserve">3.89332437515259</t>
   </si>
   <si>
     <t xml:space="preserve">3.79587531089783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89309906959534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02677726745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08540916442871</t>
+    <t xml:space="preserve">3.89309930801392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02677774429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08540868759155</t>
   </si>
   <si>
     <t xml:space="preserve">4.07602739334106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08306360244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09947967529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07368278503418</t>
+    <t xml:space="preserve">4.08306407928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09948015213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07368230819702</t>
   </si>
   <si>
     <t xml:space="preserve">4.0900993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10182523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0877537727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1135516166687</t>
+    <t xml:space="preserve">4.10182476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08775329589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11355257034302</t>
   </si>
   <si>
     <t xml:space="preserve">4.08071804046631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01974201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90482521057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85557556152344</t>
+    <t xml:space="preserve">4.01974153518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90482497215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85557508468628</t>
   </si>
   <si>
     <t xml:space="preserve">3.85792064666748</t>
@@ -359,133 +359,133 @@
     <t xml:space="preserve">3.86495614051819</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8719916343689</t>
+    <t xml:space="preserve">3.87199187278748</t>
   </si>
   <si>
     <t xml:space="preserve">3.86964678764343</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00567007064819</t>
+    <t xml:space="preserve">4.00567054748535</t>
   </si>
   <si>
     <t xml:space="preserve">4.00801515579224</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95876526832581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05961084365845</t>
+    <t xml:space="preserve">3.95876479148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05961132049561</t>
   </si>
   <si>
     <t xml:space="preserve">3.88606309890747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88840818405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0408501625061</t>
+    <t xml:space="preserve">3.88840866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04084873199463</t>
   </si>
   <si>
     <t xml:space="preserve">4.16514682769775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15576505661011</t>
+    <t xml:space="preserve">4.15576553344727</t>
   </si>
   <si>
     <t xml:space="preserve">4.14873027801514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13231372833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00332593917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04319429397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16045665740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15811109542847</t>
+    <t xml:space="preserve">4.13231325149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00332546234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04319477081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16045618057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15811061859131</t>
   </si>
   <si>
     <t xml:space="preserve">4.11589670181274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06899261474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13465785980225</t>
+    <t xml:space="preserve">4.06899166107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13465881347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.14169454574585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18390893936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16280221939087</t>
+    <t xml:space="preserve">4.18390941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16280174255371</t>
   </si>
   <si>
     <t xml:space="preserve">4.21908760070801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29179000854492</t>
+    <t xml:space="preserve">4.29178953170776</t>
   </si>
   <si>
     <t xml:space="preserve">4.29648017883301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31055116653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28709983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33165788650513</t>
+    <t xml:space="preserve">4.31055212020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28709936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33165884017944</t>
   </si>
   <si>
     <t xml:space="preserve">4.33869409561157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54038524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51458787918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5216236114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43719387054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47940921783447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45595788955688</t>
+    <t xml:space="preserve">4.5403847694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51458740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52162265777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43719434738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47940826416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45595645904541</t>
   </si>
   <si>
     <t xml:space="preserve">4.66233730316162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67171907424927</t>
+    <t xml:space="preserve">4.67171955108643</t>
   </si>
   <si>
     <t xml:space="preserve">4.58963489532471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55914688110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56383752822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54976606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60370588302612</t>
+    <t xml:space="preserve">4.55914735794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56383800506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54976654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60370683670044</t>
   </si>
   <si>
     <t xml:space="preserve">4.59667158126831</t>
@@ -503,22 +503,22 @@
     <t xml:space="preserve">4.65061140060425</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57556390762329</t>
+    <t xml:space="preserve">4.57556438446045</t>
   </si>
   <si>
     <t xml:space="preserve">4.7045521736145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67406463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70924282073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60136222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48644495010376</t>
+    <t xml:space="preserve">4.67406320571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70924234390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6013617515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4864444732666</t>
   </si>
   <si>
     <t xml:space="preserve">4.4653377532959</t>
@@ -527,19 +527,19 @@
     <t xml:space="preserve">4.39967060089111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43250513076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50520753860474</t>
+    <t xml:space="preserve">4.43250417709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50520706176758</t>
   </si>
   <si>
     <t xml:space="preserve">4.49113512039185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51693248748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50286197662354</t>
+    <t xml:space="preserve">4.51693344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50286149978638</t>
   </si>
   <si>
     <t xml:space="preserve">4.4887900352478</t>
@@ -551,13 +551,13 @@
     <t xml:space="preserve">4.66468286514282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73269462585449</t>
+    <t xml:space="preserve">4.73269510269165</t>
   </si>
   <si>
     <t xml:space="preserve">4.71393346786499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69048118591309</t>
+    <t xml:space="preserve">4.69048070907593</t>
   </si>
   <si>
     <t xml:space="preserve">4.58728981018066</t>
@@ -566,67 +566,67 @@
     <t xml:space="preserve">4.56852769851685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47471857070923</t>
+    <t xml:space="preserve">4.47471904754639</t>
   </si>
   <si>
     <t xml:space="preserve">4.44657564163208</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54742002487183</t>
+    <t xml:space="preserve">4.54742050170898</t>
   </si>
   <si>
     <t xml:space="preserve">4.44188547134399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50051689147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52631378173828</t>
+    <t xml:space="preserve">4.50051641464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52631330490112</t>
   </si>
   <si>
     <t xml:space="preserve">4.36683750152588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37152767181396</t>
+    <t xml:space="preserve">4.37152814865112</t>
   </si>
   <si>
     <t xml:space="preserve">4.33400440216064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3293137550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30586194992065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30351686477661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25661182403564</t>
+    <t xml:space="preserve">4.32931327819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30586099624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30351638793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25661134719849</t>
   </si>
   <si>
     <t xml:space="preserve">4.20736122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09478855133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2425389289856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20267009735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95642066001892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95407438278198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03381443023682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12527704238892</t>
+    <t xml:space="preserve">4.09478950500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24253940582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20267105102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9564208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95407557487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0338134765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12527799606323</t>
   </si>
   <si>
     <t xml:space="preserve">4.01739692687988</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">4.21205186843872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18859958648682</t>
+    <t xml:space="preserve">4.1885986328125</t>
   </si>
   <si>
     <t xml:space="preserve">4.2495756149292</t>
@@ -650,25 +650,25 @@
     <t xml:space="preserve">4.20501613616943</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26833772659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22846841812134</t>
+    <t xml:space="preserve">4.26833820343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22846794128418</t>
   </si>
   <si>
     <t xml:space="preserve">4.24723052978516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31993198394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36449241638184</t>
+    <t xml:space="preserve">4.31993293762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449337005615</t>
   </si>
   <si>
     <t xml:space="preserve">4.28944492340088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27771854400635</t>
+    <t xml:space="preserve">4.27771902084351</t>
   </si>
   <si>
     <t xml:space="preserve">4.30117082595825</t>
@@ -677,16 +677,16 @@
     <t xml:space="preserve">4.32227802276611</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35745668411255</t>
+    <t xml:space="preserve">4.35745620727539</t>
   </si>
   <si>
     <t xml:space="preserve">4.34807538986206</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34338521957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39028930664062</t>
+    <t xml:space="preserve">4.34338569641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39029026031494</t>
   </si>
   <si>
     <t xml:space="preserve">4.36214637756348</t>
@@ -695,37 +695,37 @@
     <t xml:space="preserve">4.32462310791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39732599258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37387323379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36918163299561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47002840042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45830154418945</t>
+    <t xml:space="preserve">4.39732551574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37387275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36918210983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47002792358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45830202102661</t>
   </si>
   <si>
     <t xml:space="preserve">4.42546939849854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43484926223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46768236160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40201663970947</t>
+    <t xml:space="preserve">4.43484973907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46768283843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40201616287231</t>
   </si>
   <si>
     <t xml:space="preserve">4.3527660369873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38559913635254</t>
+    <t xml:space="preserve">4.38560009002686</t>
   </si>
   <si>
     <t xml:space="preserve">4.43953990936279</t>
@@ -734,52 +734,52 @@
     <t xml:space="preserve">4.4301586151123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49348115921021</t>
+    <t xml:space="preserve">4.49348020553589</t>
   </si>
   <si>
     <t xml:space="preserve">4.47237348556519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52396965026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54273080825806</t>
+    <t xml:space="preserve">4.52396869659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5427303314209</t>
   </si>
   <si>
     <t xml:space="preserve">4.53804016113281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54507541656494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58259963989258</t>
+    <t xml:space="preserve">4.5450758934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58259916305542</t>
   </si>
   <si>
     <t xml:space="preserve">4.57790899276733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55211114883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57087326049805</t>
+    <t xml:space="preserve">4.55211162567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57087373733521</t>
   </si>
   <si>
     <t xml:space="preserve">4.53569459915161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50755214691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58494424819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65530157089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74207639694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75614738464355</t>
+    <t xml:space="preserve">4.5075511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58494567871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65530204772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74207544326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75614786148071</t>
   </si>
   <si>
     <t xml:space="preserve">4.80774259567261</t>
@@ -791,124 +791,124 @@
     <t xml:space="preserve">4.8968620300293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94845724105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09855318069458</t>
+    <t xml:space="preserve">4.94845676422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09855270385742</t>
   </si>
   <si>
     <t xml:space="preserve">5.05164813995361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12200450897217</t>
+    <t xml:space="preserve">5.12200403213501</t>
   </si>
   <si>
     <t xml:space="preserve">5.04695749282837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0563383102417</t>
+    <t xml:space="preserve">5.05633783340454</t>
   </si>
   <si>
     <t xml:space="preserve">4.99536180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01881408691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02819490432739</t>
+    <t xml:space="preserve">5.01881456375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02819538116455</t>
   </si>
   <si>
     <t xml:space="preserve">5.03288602828979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93907642364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97659921646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92500495910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96721887588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08917140960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17360067367554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14545774459839</t>
+    <t xml:space="preserve">4.93907690048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9766001701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9250054359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96721982955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08917093276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17359972000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14545726776123</t>
   </si>
   <si>
     <t xml:space="preserve">5.15952920913696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09386157989502</t>
+    <t xml:space="preserve">5.09386205673218</t>
   </si>
   <si>
     <t xml:space="preserve">5.16421890258789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25333881378174</t>
+    <t xml:space="preserve">5.25333833694458</t>
   </si>
   <si>
     <t xml:space="preserve">5.18767213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41750526428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6707911491394</t>
+    <t xml:space="preserve">5.41750478744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67079067230225</t>
   </si>
   <si>
     <t xml:space="preserve">5.60043382644653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62388563156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66140937805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68486261367798</t>
+    <t xml:space="preserve">5.62388610839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66141080856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68486213684082</t>
   </si>
   <si>
     <t xml:space="preserve">5.57698202133179</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60512447357178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72238683700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69403409957886</t>
+    <t xml:space="preserve">5.60512399673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72238636016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69403457641602</t>
   </si>
   <si>
     <t xml:space="preserve">5.74128723144531</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76491451263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75073766708374</t>
+    <t xml:space="preserve">5.76491498947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7507381439209</t>
   </si>
   <si>
     <t xml:space="preserve">5.87832307815552</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86887216567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88304853439331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02008295059204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99173069000244</t>
+    <t xml:space="preserve">5.86887168884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88304758071899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02008199691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99173021316528</t>
   </si>
   <si>
     <t xml:space="preserve">6.00118112564087</t>
@@ -920,13 +920,13 @@
     <t xml:space="preserve">5.85942077636719</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8027172088623</t>
+    <t xml:space="preserve">5.80271768569946</t>
   </si>
   <si>
     <t xml:space="preserve">5.75546360015869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73183679580688</t>
+    <t xml:space="preserve">5.73183727264404</t>
   </si>
   <si>
     <t xml:space="preserve">5.84997034072876</t>
@@ -935,40 +935,40 @@
     <t xml:space="preserve">5.81216716766357</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95865297317505</t>
+    <t xml:space="preserve">5.95865249633789</t>
   </si>
   <si>
     <t xml:space="preserve">5.93030118942261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98228073120117</t>
+    <t xml:space="preserve">5.98228025436401</t>
   </si>
   <si>
     <t xml:space="preserve">5.90194892883301</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91612529754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91139984130859</t>
+    <t xml:space="preserve">5.91612577438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91140031814575</t>
   </si>
   <si>
     <t xml:space="preserve">5.83106899261475</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88777351379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78381538391113</t>
+    <t xml:space="preserve">5.88777256011963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78381586074829</t>
   </si>
   <si>
     <t xml:space="preserve">5.80744218826294</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84524536132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77436494827271</t>
+    <t xml:space="preserve">5.84524583816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77436447143555</t>
   </si>
   <si>
     <t xml:space="preserve">5.82634353637695</t>
@@ -992,31 +992,31 @@
     <t xml:space="preserve">5.92557573318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94447755813599</t>
+    <t xml:space="preserve">5.94447708129883</t>
   </si>
   <si>
     <t xml:space="preserve">5.77908992767334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74601268768311</t>
+    <t xml:space="preserve">5.74601316452026</t>
   </si>
   <si>
     <t xml:space="preserve">5.71766090393066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65150594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66095781326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79799175262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76018857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69876003265381</t>
+    <t xml:space="preserve">5.6515064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66095638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79799222946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76018953323364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69876050949097</t>
   </si>
   <si>
     <t xml:space="preserve">5.66568183898926</t>
@@ -1028,22 +1028,22 @@
     <t xml:space="preserve">5.78854084014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76963996887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89249897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97282981872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15239191055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14766693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28470277786255</t>
+    <t xml:space="preserve">5.76963949203491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89249849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97282934188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15239238739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1476674079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28470230102539</t>
   </si>
   <si>
     <t xml:space="preserve">6.13821601867676</t>
@@ -1055,46 +1055,46 @@
     <t xml:space="preserve">6.02953338623047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10513877868652</t>
+    <t xml:space="preserve">6.10513830184937</t>
   </si>
   <si>
     <t xml:space="preserve">6.16656827926636</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11458921432495</t>
+    <t xml:space="preserve">6.11458873748779</t>
   </si>
   <si>
     <t xml:space="preserve">6.31777954101562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34140634536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40756130218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50206756591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42173671722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30832958221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.478440284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31305408477783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33668041229248</t>
+    <t xml:space="preserve">6.34140586853027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4075608253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50206708908081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42173719406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3083291053772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47844076156616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31305360794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33667993545532</t>
   </si>
   <si>
     <t xml:space="preserve">6.37448310852051</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17601823806763</t>
+    <t xml:space="preserve">6.17601871490479</t>
   </si>
   <si>
     <t xml:space="preserve">6.0909628868103</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">6.08623838424683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10041379928589</t>
+    <t xml:space="preserve">6.10041427612305</t>
   </si>
   <si>
     <t xml:space="preserve">6.10986423492432</t>
@@ -1118,10 +1118,10 @@
     <t xml:space="preserve">6.00590658187866</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03425931930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0956883430481</t>
+    <t xml:space="preserve">6.03425884246826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09568786621094</t>
   </si>
   <si>
     <t xml:space="preserve">6.0626106262207</t>
@@ -1133,31 +1133,31 @@
     <t xml:space="preserve">6.08151245117188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15711688995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21382093429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24217367172241</t>
+    <t xml:space="preserve">6.15711784362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21382188796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24217414855957</t>
   </si>
   <si>
     <t xml:space="preserve">6.24689960479736</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20909643173218</t>
+    <t xml:space="preserve">6.20909690856934</t>
   </si>
   <si>
     <t xml:space="preserve">6.22799777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19964504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12876605987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07206153869629</t>
+    <t xml:space="preserve">6.19964599609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12876558303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07206106185913</t>
   </si>
   <si>
     <t xml:space="preserve">6.05788516998291</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">6.13349056243896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14294099807739</t>
+    <t xml:space="preserve">6.14294147491455</t>
   </si>
   <si>
     <t xml:space="preserve">6.01063203811646</t>
@@ -1175,31 +1175,31 @@
     <t xml:space="preserve">5.94920301437378</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97755432128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05316019058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99645566940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0673360824585</t>
+    <t xml:space="preserve">5.97755479812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05315971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99645519256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06733655929565</t>
   </si>
   <si>
     <t xml:space="preserve">5.93975162506104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71293592453003</t>
+    <t xml:space="preserve">5.71293544769287</t>
   </si>
   <si>
     <t xml:space="preserve">5.72711133956909</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92085075378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5759015083313</t>
+    <t xml:space="preserve">5.92085027694702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57590103149414</t>
   </si>
   <si>
     <t xml:space="preserve">5.52864694595337</t>
@@ -1208,55 +1208,55 @@
     <t xml:space="preserve">5.42941522598267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50502061843872</t>
+    <t xml:space="preserve">5.50502014160156</t>
   </si>
   <si>
     <t xml:space="preserve">5.61370372772217</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63733100891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04370927810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98700618743896</t>
+    <t xml:space="preserve">5.63733053207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04370975494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98700571060181</t>
   </si>
   <si>
     <t xml:space="preserve">6.01535701751709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89722394943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81689310073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87359809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86414575576782</t>
+    <t xml:space="preserve">5.89722347259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81689405441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87359714508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86414670944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.90667486190796</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96810388565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01550722122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02027082443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9916934967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08218812942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20602178573608</t>
+    <t xml:space="preserve">5.96810483932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01550769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02027034759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99169301986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08218765258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20602226257324</t>
   </si>
   <si>
     <t xml:space="preserve">6.18697071075439</t>
@@ -1283,55 +1283,55 @@
     <t xml:space="preserve">6.29175424575806</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38701152801514</t>
+    <t xml:space="preserve">6.38701105117798</t>
   </si>
   <si>
     <t xml:space="preserve">6.52513456344604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5965781211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69183492660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69659805297852</t>
+    <t xml:space="preserve">6.59657764434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69183540344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69659852981567</t>
   </si>
   <si>
     <t xml:space="preserve">6.62039184570312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57276344299316</t>
+    <t xml:space="preserve">6.57276296615601</t>
   </si>
   <si>
     <t xml:space="preserve">6.50608348846436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58228921890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65373229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71088695526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82519626617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77280473709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82995891571045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0252366065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92521667480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92045307159424</t>
+    <t xml:space="preserve">6.58228969573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65373277664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71088743209839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82519578933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77280378341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82995843887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02523612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92521619796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9204535484314</t>
   </si>
   <si>
     <t xml:space="preserve">7.01094770431519</t>
@@ -1355,16 +1355,16 @@
     <t xml:space="preserve">7.17764854431152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28243207931519</t>
+    <t xml:space="preserve">7.28243112564087</t>
   </si>
   <si>
     <t xml:space="preserve">7.22051429748535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23956632614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27766895294189</t>
+    <t xml:space="preserve">7.23956537246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27766847610474</t>
   </si>
   <si>
     <t xml:space="preserve">7.12525653839111</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">6.86806154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0014214515686</t>
+    <t xml:space="preserve">7.00142097473145</t>
   </si>
   <si>
     <t xml:space="preserve">7.00618457794189</t>
@@ -1388,25 +1388,25 @@
     <t xml:space="preserve">6.97760725021362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9918966293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03952407836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02047348022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07762718200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18717432022095</t>
+    <t xml:space="preserve">6.99189710617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0395245552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02047395706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07762813568115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18717384338379</t>
   </si>
   <si>
     <t xml:space="preserve">7.21098899841309</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41579151153564</t>
+    <t xml:space="preserve">7.41579103469849</t>
   </si>
   <si>
     <t xml:space="preserve">7.29671955108643</t>
@@ -1424,166 +1424,166 @@
     <t xml:space="preserve">7.30624532699585</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18241119384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25385427474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0585765838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10620498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14907121658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16812229156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90140104293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94426727294922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06810188293457</t>
+    <t xml:space="preserve">7.1824107170105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2538537979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05857610702515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10620546340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14907073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1681227684021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90140151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94426774978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06810235977173</t>
   </si>
   <si>
     <t xml:space="preserve">6.98713350296021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13001918792725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87758684158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70612382888794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63944292068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65849494934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32985734939575</t>
+    <t xml:space="preserve">7.1300196647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87758731842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70612335205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63944339752197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65849447250366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32985687255859</t>
   </si>
   <si>
     <t xml:space="preserve">6.19649648666382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11552762985229</t>
+    <t xml:space="preserve">6.11552810668945</t>
   </si>
   <si>
     <t xml:space="preserve">6.04884719848633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21554803848267</t>
+    <t xml:space="preserve">6.21554851531982</t>
   </si>
   <si>
     <t xml:space="preserve">6.31556844711304</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3346209526062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34414577484131</t>
+    <t xml:space="preserve">6.33461999893188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34414482116699</t>
   </si>
   <si>
     <t xml:space="preserve">6.12505340576172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15363073348999</t>
+    <t xml:space="preserve">6.15363025665283</t>
   </si>
   <si>
     <t xml:space="preserve">6.30604219436646</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35367202758789</t>
+    <t xml:space="preserve">6.35367155075073</t>
   </si>
   <si>
     <t xml:space="preserve">6.47274351119995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4679799079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42987680435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52989721298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76804161071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08239030838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11096811294556</t>
+    <t xml:space="preserve">6.46798038482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42987728118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52989768981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76804208755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08239078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11096858978271</t>
   </si>
   <si>
     <t xml:space="preserve">7.12049293518066</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3252968788147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31577110290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11572980880737</t>
+    <t xml:space="preserve">7.32529735565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31577157974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11573028564453</t>
   </si>
   <si>
     <t xml:space="preserve">7.03476285934448</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15383386611938</t>
+    <t xml:space="preserve">7.1538348197937</t>
   </si>
   <si>
     <t xml:space="preserve">7.04428768157959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02999973297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17288589477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36340045928955</t>
+    <t xml:space="preserve">7.02999925613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17288541793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36340093612671</t>
   </si>
   <si>
     <t xml:space="preserve">7.14430809020996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20622539520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32053422927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09191608428955</t>
+    <t xml:space="preserve">7.20622491836548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32053470611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09191656112671</t>
   </si>
   <si>
     <t xml:space="preserve">6.98237037658691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44913196563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38245153427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33006000518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21575117111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33958578109741</t>
+    <t xml:space="preserve">7.44913148880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3824520111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3300609588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21575164794922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33958530426025</t>
   </si>
   <si>
     <t xml:space="preserve">7.35387420654297</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">7.55391550064087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60630702972412</t>
+    <t xml:space="preserve">7.60630750656128</t>
   </si>
   <si>
     <t xml:space="preserve">7.46342086791992</t>
@@ -1601,16 +1601,16 @@
     <t xml:space="preserve">7.49199724197388</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44436931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42055463790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62535905838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53009986877441</t>
+    <t xml:space="preserve">7.44436883926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42055511474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62535810470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53010082244873</t>
   </si>
   <si>
     <t xml:space="preserve">7.47294616699219</t>
@@ -1619,94 +1619,94 @@
     <t xml:space="preserve">7.4872350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4681830406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49676084518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51581239700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6110692024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56344127655029</t>
+    <t xml:space="preserve">7.46818351745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49676132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51581192016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61106967926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56344079971313</t>
   </si>
   <si>
     <t xml:space="preserve">7.6444091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73490476608276</t>
+    <t xml:space="preserve">7.73490428924561</t>
   </si>
   <si>
     <t xml:space="preserve">7.80634689331055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86826467514038</t>
+    <t xml:space="preserve">7.8682656288147</t>
   </si>
   <si>
     <t xml:space="preserve">7.85873889923096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88731527328491</t>
+    <t xml:space="preserve">7.88731575012207</t>
   </si>
   <si>
     <t xml:space="preserve">7.92541790008545</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95399570465088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83492517471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9873366355896</t>
+    <t xml:space="preserve">7.95399522781372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83492565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98733568191528</t>
   </si>
   <si>
     <t xml:space="preserve">8.01115131378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06354141235352</t>
+    <t xml:space="preserve">8.06354236602783</t>
   </si>
   <si>
     <t xml:space="preserve">7.53486299514771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52057409286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54438924789429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62059545516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63964748382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77777004241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76824378967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90636777877808</t>
+    <t xml:space="preserve">7.52057504653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5443902015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62059497833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63964700698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77776956558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76824331283569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90636873245239</t>
   </si>
   <si>
     <t xml:space="preserve">8.03496551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00638866424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04448986053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0683069229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20166492462158</t>
+    <t xml:space="preserve">8.00638771057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04449081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06830596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2016658782959</t>
   </si>
   <si>
     <t xml:space="preserve">8.32549953460693</t>
@@ -1721,22 +1721,22 @@
     <t xml:space="preserve">8.38265514373779</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3350248336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27787113189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23500823974609</t>
+    <t xml:space="preserve">8.33502578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27787017822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23500633239746</t>
   </si>
   <si>
     <t xml:space="preserve">8.25882053375244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26358413696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16832542419434</t>
+    <t xml:space="preserve">8.26358318328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16832637786865</t>
   </si>
   <si>
     <t xml:space="preserve">8.31121349334717</t>
@@ -1745,16 +1745,16 @@
     <t xml:space="preserve">8.36836624145508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35407733917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37789154052734</t>
+    <t xml:space="preserve">8.35408020019531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37789249420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.28739738464355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21119117736816</t>
+    <t xml:space="preserve">8.21119213104248</t>
   </si>
   <si>
     <t xml:space="preserve">8.22071838378906</t>
@@ -1763,10 +1763,10 @@
     <t xml:space="preserve">8.43150520324707</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44587516784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56085205078125</t>
+    <t xml:space="preserve">8.445876121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56085300445557</t>
   </si>
   <si>
     <t xml:space="preserve">8.51294612884521</t>
@@ -1796,25 +1796,25 @@
     <t xml:space="preserve">8.74289512634277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83391666412354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77642917633057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7093620300293</t>
+    <t xml:space="preserve">8.83391761779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77642822265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70936107635498</t>
   </si>
   <si>
     <t xml:space="preserve">8.6854076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70457172393799</t>
+    <t xml:space="preserve">8.70457077026367</t>
   </si>
   <si>
     <t xml:space="preserve">8.78122234344482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80996322631836</t>
+    <t xml:space="preserve">8.80996417999268</t>
   </si>
   <si>
     <t xml:space="preserve">8.77163887023926</t>
@@ -1835,19 +1835,19 @@
     <t xml:space="preserve">8.40755176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41234111785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32611083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45545768737793</t>
+    <t xml:space="preserve">8.4123420715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32610988616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45545864105225</t>
   </si>
   <si>
     <t xml:space="preserve">8.41713333129883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39317989349365</t>
+    <t xml:space="preserve">8.39318084716797</t>
   </si>
   <si>
     <t xml:space="preserve">8.54648017883301</t>
@@ -1859,34 +1859,34 @@
     <t xml:space="preserve">8.27341365814209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22071743011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25425243377686</t>
+    <t xml:space="preserve">8.22071647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25425148010254</t>
   </si>
   <si>
     <t xml:space="preserve">8.35485553741455</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47461986541748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42192363739014</t>
+    <t xml:space="preserve">8.4746208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42192268371582</t>
   </si>
   <si>
     <t xml:space="preserve">8.36922645568848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31653118133545</t>
+    <t xml:space="preserve">8.31653022766113</t>
   </si>
   <si>
     <t xml:space="preserve">8.29736709594727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28299713134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17760181427002</t>
+    <t xml:space="preserve">8.28299617767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1776008605957</t>
   </si>
   <si>
     <t xml:space="preserve">8.2015552520752</t>
@@ -1898,7 +1898,7 @@
     <t xml:space="preserve">8.24946117401123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18239212036133</t>
+    <t xml:space="preserve">8.18239307403564</t>
   </si>
   <si>
     <t xml:space="preserve">8.17281055450439</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">8.09616088867188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14885807037354</t>
+    <t xml:space="preserve">8.14885711669922</t>
   </si>
   <si>
     <t xml:space="preserve">8.06741714477539</t>
@@ -1925,16 +1925,16 @@
     <t xml:space="preserve">7.62188863754272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6170973777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66021394729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50212335586548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72249269485474</t>
+    <t xml:space="preserve">7.61709785461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66021347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50212287902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72249221801758</t>
   </si>
   <si>
     <t xml:space="preserve">7.59314489364624</t>
@@ -1946,19 +1946,19 @@
     <t xml:space="preserve">7.51170444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65542268753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59793567657471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90932655334473</t>
+    <t xml:space="preserve">7.65542316436768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59793615341187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90932750701904</t>
   </si>
   <si>
     <t xml:space="preserve">7.95244312286377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82309532165527</t>
+    <t xml:space="preserve">7.82309484481812</t>
   </si>
   <si>
     <t xml:space="preserve">7.88058376312256</t>
@@ -1973,10 +1973,10 @@
     <t xml:space="preserve">8.16802024841309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26383304595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34527492523193</t>
+    <t xml:space="preserve">8.26383209228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34527397155762</t>
   </si>
   <si>
     <t xml:space="preserve">8.29257678985596</t>
@@ -1991,16 +1991,16 @@
     <t xml:space="preserve">7.99555730819702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80872297286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91411685943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88537311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8278865814209</t>
+    <t xml:space="preserve">7.80872344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91411781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88537216186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82788610458374</t>
   </si>
   <si>
     <t xml:space="preserve">7.84704828262329</t>
@@ -2015,16 +2015,16 @@
     <t xml:space="preserve">7.90453577041626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94286060333252</t>
+    <t xml:space="preserve">7.94286155700684</t>
   </si>
   <si>
     <t xml:space="preserve">7.71770143508911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85663032531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04346561431885</t>
+    <t xml:space="preserve">7.85662937164307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04346466064453</t>
   </si>
   <si>
     <t xml:space="preserve">8.11532402038574</t>
@@ -2048,7 +2048,7 @@
     <t xml:space="preserve">7.57877254486084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64105081558228</t>
+    <t xml:space="preserve">7.64105129241943</t>
   </si>
   <si>
     <t xml:space="preserve">7.69374799728394</t>
@@ -2057,16 +2057,16 @@
     <t xml:space="preserve">7.83746719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81351327896118</t>
+    <t xml:space="preserve">7.81351280212402</t>
   </si>
   <si>
     <t xml:space="preserve">7.87100219726562</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87579250335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92369747161865</t>
+    <t xml:space="preserve">7.87579154968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92369842529297</t>
   </si>
   <si>
     <t xml:space="preserve">7.89495515823364</t>
@@ -2075,10 +2075,10 @@
     <t xml:space="preserve">7.8518385887146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86621141433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98597621917725</t>
+    <t xml:space="preserve">7.86621046066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98597717285156</t>
   </si>
   <si>
     <t xml:space="preserve">7.9668140411377</t>
@@ -2090,19 +2090,19 @@
     <t xml:space="preserve">8.11053276062012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04825401306152</t>
+    <t xml:space="preserve">8.04825496673584</t>
   </si>
   <si>
     <t xml:space="preserve">7.93806934356689</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77998018264771</t>
+    <t xml:space="preserve">7.77997970581055</t>
   </si>
   <si>
     <t xml:space="preserve">7.81830501556396</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8422589302063</t>
+    <t xml:space="preserve">7.84225845336914</t>
   </si>
   <si>
     <t xml:space="preserve">7.79435157775879</t>
@@ -2117,16 +2117,16 @@
     <t xml:space="preserve">7.9189076423645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7129111289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77518892288208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86142015457153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07699775695801</t>
+    <t xml:space="preserve">7.71291065216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77518844604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86141920089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07699871063232</t>
   </si>
   <si>
     <t xml:space="preserve">8.21592712402344</t>
@@ -2141,7 +2141,7 @@
     <t xml:space="preserve">8.4506664276123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36443424224854</t>
+    <t xml:space="preserve">8.36443519592285</t>
   </si>
   <si>
     <t xml:space="preserve">8.47941207885742</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">8.64229393005371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69019889831543</t>
+    <t xml:space="preserve">8.69019794464111</t>
   </si>
   <si>
     <t xml:space="preserve">8.58480453491211</t>
@@ -2189,10 +2189,10 @@
     <t xml:space="preserve">7.30091714859009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36319494247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33924102783203</t>
+    <t xml:space="preserve">7.36319541931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33924150466919</t>
   </si>
   <si>
     <t xml:space="preserve">7.09492015838623</t>
@@ -2204,10 +2204,10 @@
     <t xml:space="preserve">6.36195373535156</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33675909042358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54754686355591</t>
+    <t xml:space="preserve">5.33675956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54754734039307</t>
   </si>
   <si>
     <t xml:space="preserve">5.37987470626831</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">5.30322504043579</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86851930618286</t>
+    <t xml:space="preserve">5.8685188293457</t>
   </si>
   <si>
     <t xml:space="preserve">6.45776605606079</t>
@@ -2231,13 +2231,13 @@
     <t xml:space="preserve">6.29967546463013</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76915740966797</t>
+    <t xml:space="preserve">6.76915693283081</t>
   </si>
   <si>
     <t xml:space="preserve">6.84101676940918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53441667556763</t>
+    <t xml:space="preserve">6.53441619873047</t>
   </si>
   <si>
     <t xml:space="preserve">6.3715353012085</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">6.27572298049927</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02852582931519</t>
+    <t xml:space="preserve">6.02852630615234</t>
   </si>
   <si>
     <t xml:space="preserve">6.11092519760132</t>
@@ -2255,10 +2255,10 @@
     <t xml:space="preserve">5.85606336593628</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45201778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38111591339111</t>
+    <t xml:space="preserve">6.45201730728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38111543655396</t>
   </si>
   <si>
     <t xml:space="preserve">6.32171249389648</t>
@@ -5949,6 +5949,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.88800001144409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95800018310547</t>
   </si>
 </sst>
 </file>
@@ -71339,7 +71342,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.6928009259</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>12854893</v>
@@ -71360,6 +71363,32 @@
         <v>1978</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6920833333</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>8544884</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>6.05600023269653</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>5.89799976348877</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>5.90000009536743</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>5.95800018310547</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>1979</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1980" uniqueCount="1980">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="1981">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,61 +44,61 @@
     <t xml:space="preserve">CPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65898251533508</t>
+    <t xml:space="preserve">3.65898275375366</t>
   </si>
   <si>
     <t xml:space="preserve">3.60329699516296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51976943016052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51048803329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54993176460266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62881922721863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68450498580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57313418388367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52672958374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48264598846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56617379188538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43392157554626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50584816932678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56153345108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64274096488953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66594314575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56849408149719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74250960350037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72162890434265</t>
+    <t xml:space="preserve">3.51976919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51048851013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54993224143982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62881946563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68450474739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57313394546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52672982215881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48264575004578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56617403030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43392109870911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5058479309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56153297424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64274072647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66594290733337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56849384307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74251008033752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72162818908691</t>
   </si>
   <si>
     <t xml:space="preserve">3.70770668983459</t>
@@ -107,40 +107,40 @@
     <t xml:space="preserve">3.47104477882385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44320225715637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28078675270081</t>
+    <t xml:space="preserve">3.44320201873779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28078722953796</t>
   </si>
   <si>
     <t xml:space="preserve">3.33183145523071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40839886665344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22046089172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26918625831604</t>
+    <t xml:space="preserve">3.40839862823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22046160697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26918601989746</t>
   </si>
   <si>
     <t xml:space="preserve">3.32487106323242</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24366307258606</t>
+    <t xml:space="preserve">3.24366354942322</t>
   </si>
   <si>
     <t xml:space="preserve">3.32255077362061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28774785995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31791067123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36663484573364</t>
+    <t xml:space="preserve">3.28774762153625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31791019439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36663508415222</t>
   </si>
   <si>
     <t xml:space="preserve">3.36199450492859</t>
@@ -152,124 +152,124 @@
     <t xml:space="preserve">3.3828763961792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36431455612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53137016296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60561728477478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61257767677307</t>
+    <t xml:space="preserve">3.36431479454041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53137040138245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6056170463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61257839202881</t>
   </si>
   <si>
     <t xml:space="preserve">3.5638530254364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61489844322205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63810014724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68914484977722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8747615814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95597004890442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00701522827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04877948760986</t>
+    <t xml:space="preserve">3.61489796638489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63810038566589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6891450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476205825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95596933364868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00701570510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04877853393555</t>
   </si>
   <si>
     <t xml:space="preserve">4.03485727310181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04181814193726</t>
+    <t xml:space="preserve">4.04181718826294</t>
   </si>
   <si>
     <t xml:space="preserve">4.03717756271362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05109882354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01861619949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09286308288574</t>
+    <t xml:space="preserve">4.05109930038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01861572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0928635597229</t>
   </si>
   <si>
     <t xml:space="preserve">4.07662057876587</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03949880599976</t>
+    <t xml:space="preserve">4.03949737548828</t>
   </si>
   <si>
     <t xml:space="preserve">4.08358240127563</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02325582504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00005483627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06037950515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99541354179382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94436931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97453188896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00237369537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93740773200989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94668936729431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03021669387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05341863632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0093355178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95829033851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98613333702087</t>
+    <t xml:space="preserve">4.02325677871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00005388259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06037998199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99541401863098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94436883926392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97453165054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00237464904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93740916252136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94668960571289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03021717071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05341958999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00933456420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9582896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98613262176514</t>
   </si>
   <si>
     <t xml:space="preserve">4.0255765914917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96989130973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91188621520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89796447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87708330154419</t>
+    <t xml:space="preserve">3.96989226341248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91188645362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89796495437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87708210945129</t>
   </si>
   <si>
     <t xml:space="preserve">3.91420650482178</t>
@@ -278,52 +278,52 @@
     <t xml:space="preserve">3.92812776565552</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95132946968079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06734085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08126211166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99309372901917</t>
+    <t xml:space="preserve">3.9513304233551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06733989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0812611579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99309325218201</t>
   </si>
   <si>
     <t xml:space="preserve">3.9675714969635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98149228096008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96293091773987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88868379592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89332437515259</t>
+    <t xml:space="preserve">3.9814920425415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96293044090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88868355751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89332461357117</t>
   </si>
   <si>
     <t xml:space="preserve">3.79587531089783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89309930801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02677774429321</t>
+    <t xml:space="preserve">3.89309906959534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02677726745605</t>
   </si>
   <si>
     <t xml:space="preserve">4.08540868759155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07602739334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08306407928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09948015213013</t>
+    <t xml:space="preserve">4.07602834701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08306360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09947967529297</t>
   </si>
   <si>
     <t xml:space="preserve">4.07368230819702</t>
@@ -332,55 +332,55 @@
     <t xml:space="preserve">4.0900993347168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10182476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08775329589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11355257034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08071804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01974153518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90482497215271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85557508468628</t>
+    <t xml:space="preserve">4.10182523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08775424957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1135516166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08071851730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01974201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90482544898987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85557532310486</t>
   </si>
   <si>
     <t xml:space="preserve">3.85792064666748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86495614051819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87199187278748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86964678764343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00567054748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00801515579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95876479148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05961132049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88606309890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88840866088867</t>
+    <t xml:space="preserve">3.86495590209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87199211120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86964631080627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00567007064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00801563262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95876526832581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05961084365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88606286048889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88840794563293</t>
   </si>
   <si>
     <t xml:space="preserve">4.04084873199463</t>
@@ -389,31 +389,31 @@
     <t xml:space="preserve">4.16514682769775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15576553344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14873027801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13231325149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00332546234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04319477081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16045618057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15811061859131</t>
+    <t xml:space="preserve">4.15576601028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14873123168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13231372833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00332593917847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04319429397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16045665740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15811109542847</t>
   </si>
   <si>
     <t xml:space="preserve">4.11589670181274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06899166107178</t>
+    <t xml:space="preserve">4.06899213790894</t>
   </si>
   <si>
     <t xml:space="preserve">4.13465881347656</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">4.14169454574585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18390941619873</t>
+    <t xml:space="preserve">4.18390846252441</t>
   </si>
   <si>
     <t xml:space="preserve">4.16280174255371</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">4.29648017883301</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31055212020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28709936141968</t>
+    <t xml:space="preserve">4.31055116653442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28710031509399</t>
   </si>
   <si>
     <t xml:space="preserve">4.33165884017944</t>
@@ -452,97 +452,97 @@
     <t xml:space="preserve">4.5403847694397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51458740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52162265777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43719434738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47940826416016</t>
+    <t xml:space="preserve">4.51458787918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5216236114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43719482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47940921783447</t>
   </si>
   <si>
     <t xml:space="preserve">4.45595645904541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66233730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67171955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58963489532471</t>
+    <t xml:space="preserve">4.66233777999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67171812057495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58963584899902</t>
   </si>
   <si>
     <t xml:space="preserve">4.55914735794067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56383800506592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54976654052734</t>
+    <t xml:space="preserve">4.56383752822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54976558685303</t>
   </si>
   <si>
     <t xml:space="preserve">4.60370683670044</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59667158126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57321882247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6201229095459</t>
+    <t xml:space="preserve">4.59667110443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57321834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62012386322021</t>
   </si>
   <si>
     <t xml:space="preserve">4.59432554244995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65061140060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57556438446045</t>
+    <t xml:space="preserve">4.65061187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57556390762329</t>
   </si>
   <si>
     <t xml:space="preserve">4.7045521736145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67406320571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70924234390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6013617515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4864444732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4653377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39967060089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43250417709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50520706176758</t>
+    <t xml:space="preserve">4.67406463623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7092432975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60136222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48644351959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46533823013306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39967012405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43250370025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50520610809326</t>
   </si>
   <si>
     <t xml:space="preserve">4.49113512039185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51693344116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50286149978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4887900352478</t>
+    <t xml:space="preserve">4.51693296432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50286197662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48878955841064</t>
   </si>
   <si>
     <t xml:space="preserve">4.65295648574829</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">4.66468286514282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73269510269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71393346786499</t>
+    <t xml:space="preserve">4.73269462585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71393394470215</t>
   </si>
   <si>
     <t xml:space="preserve">4.69048070907593</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">4.58728981018066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56852769851685</t>
+    <t xml:space="preserve">4.56852865219116</t>
   </si>
   <si>
     <t xml:space="preserve">4.47471904754639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44657564163208</t>
+    <t xml:space="preserve">4.44657468795776</t>
   </si>
   <si>
     <t xml:space="preserve">4.54742050170898</t>
@@ -578,34 +578,34 @@
     <t xml:space="preserve">4.44188547134399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50051641464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52631330490112</t>
+    <t xml:space="preserve">4.50051689147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52631378173828</t>
   </si>
   <si>
     <t xml:space="preserve">4.36683750152588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37152814865112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33400440216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32931327819824</t>
+    <t xml:space="preserve">4.37152767181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33400392532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3293137550354</t>
   </si>
   <si>
     <t xml:space="preserve">4.30586099624634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30351638793945</t>
+    <t xml:space="preserve">4.30351591110229</t>
   </si>
   <si>
     <t xml:space="preserve">4.25661134719849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20736122131348</t>
+    <t xml:space="preserve">4.20736169815063</t>
   </si>
   <si>
     <t xml:space="preserve">4.09478950500488</t>
@@ -617,10 +617,10 @@
     <t xml:space="preserve">4.20267105102539</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9564208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95407557487488</t>
+    <t xml:space="preserve">3.95642137527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9540753364563</t>
   </si>
   <si>
     <t xml:space="preserve">4.0338134765625</t>
@@ -629,106 +629,106 @@
     <t xml:space="preserve">4.12527799606323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01739692687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12996816635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17218255996704</t>
+    <t xml:space="preserve">4.01739645004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12996912002563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1721830368042</t>
   </si>
   <si>
     <t xml:space="preserve">4.21205186843872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1885986328125</t>
+    <t xml:space="preserve">4.18860006332397</t>
   </si>
   <si>
     <t xml:space="preserve">4.2495756149292</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20501613616943</t>
+    <t xml:space="preserve">4.20501565933228</t>
   </si>
   <si>
     <t xml:space="preserve">4.26833820343018</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22846794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24723052978516</t>
+    <t xml:space="preserve">4.22846841812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.247230052948</t>
   </si>
   <si>
     <t xml:space="preserve">4.31993293762207</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36449337005615</t>
+    <t xml:space="preserve">4.36449241638184</t>
   </si>
   <si>
     <t xml:space="preserve">4.28944492340088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27771902084351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30117082595825</t>
+    <t xml:space="preserve">4.27771806716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30117034912109</t>
   </si>
   <si>
     <t xml:space="preserve">4.32227802276611</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35745620727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34807538986206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34338569641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39029026031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36214637756348</t>
+    <t xml:space="preserve">4.35745668411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34807586669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34338617324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39028978347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36214733123779</t>
   </si>
   <si>
     <t xml:space="preserve">4.32462310791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39732551574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37387275695801</t>
+    <t xml:space="preserve">4.39732599258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37387323379517</t>
   </si>
   <si>
     <t xml:space="preserve">4.36918210983276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47002792358398</t>
+    <t xml:space="preserve">4.47002840042114</t>
   </si>
   <si>
     <t xml:space="preserve">4.45830202102661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42546939849854</t>
+    <t xml:space="preserve">4.42546892166138</t>
   </si>
   <si>
     <t xml:space="preserve">4.43484973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46768283843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40201616287231</t>
+    <t xml:space="preserve">4.46768236160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40201663970947</t>
   </si>
   <si>
     <t xml:space="preserve">4.3527660369873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38560009002686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43953990936279</t>
+    <t xml:space="preserve">4.3855996131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43953943252563</t>
   </si>
   <si>
     <t xml:space="preserve">4.4301586151123</t>
@@ -737,106 +737,106 @@
     <t xml:space="preserve">4.49348020553589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47237348556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52396869659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5427303314209</t>
+    <t xml:space="preserve">4.47237300872803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5239691734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54273128509521</t>
   </si>
   <si>
     <t xml:space="preserve">4.53804016113281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5450758934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58259916305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57790899276733</t>
+    <t xml:space="preserve">4.54507493972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58260059356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57790946960449</t>
   </si>
   <si>
     <t xml:space="preserve">4.55211162567139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57087373733521</t>
+    <t xml:space="preserve">4.57087326049805</t>
   </si>
   <si>
     <t xml:space="preserve">4.53569459915161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5075511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58494567871094</t>
+    <t xml:space="preserve">4.50755167007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58494424819946</t>
   </si>
   <si>
     <t xml:space="preserve">4.65530204772949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74207544326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75614786148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80774259567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83119487762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8968620300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94845676422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09855270385742</t>
+    <t xml:space="preserve">4.74207639694214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7561469078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80774307250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83119535446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89686250686646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94845724105835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09855222702026</t>
   </si>
   <si>
     <t xml:space="preserve">5.05164813995361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12200403213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04695749282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05633783340454</t>
+    <t xml:space="preserve">5.12200546264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04695701599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0563383102417</t>
   </si>
   <si>
     <t xml:space="preserve">4.99536180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01881456375122</t>
+    <t xml:space="preserve">5.01881408691406</t>
   </si>
   <si>
     <t xml:space="preserve">5.02819538116455</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03288602828979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93907690048218</t>
+    <t xml:space="preserve">5.03288507461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93907594680786</t>
   </si>
   <si>
     <t xml:space="preserve">4.9766001701355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9250054359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96721982955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08917093276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17359972000122</t>
+    <t xml:space="preserve">4.92500448226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96721887588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08917188644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17360019683838</t>
   </si>
   <si>
     <t xml:space="preserve">5.14545726776123</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">5.15952920913696</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09386205673218</t>
+    <t xml:space="preserve">5.09386157989502</t>
   </si>
   <si>
     <t xml:space="preserve">5.16421890258789</t>
@@ -854,73 +854,73 @@
     <t xml:space="preserve">5.25333833694458</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18767213821411</t>
+    <t xml:space="preserve">5.18767166137695</t>
   </si>
   <si>
     <t xml:space="preserve">5.41750478744507</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67079067230225</t>
+    <t xml:space="preserve">5.6707911491394</t>
   </si>
   <si>
     <t xml:space="preserve">5.60043382644653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62388610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66141080856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68486213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57698202133179</t>
+    <t xml:space="preserve">5.6238865852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66140985488892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68486166000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57698154449463</t>
   </si>
   <si>
     <t xml:space="preserve">5.60512399673462</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72238636016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69403457641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74128723144531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76491498947144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7507381439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87832307815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86887168884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88304758071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02008199691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99173021316528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00118112564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93502712249756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85942077636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80271768569946</t>
+    <t xml:space="preserve">5.72238683700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69403409957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74128770828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76491451263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75073862075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87832260131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86887216567993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88304805755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02008247375488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99173069000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00118017196655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9350266456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85942125320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8027172088623</t>
   </si>
   <si>
     <t xml:space="preserve">5.75546360015869</t>
@@ -929,58 +929,58 @@
     <t xml:space="preserve">5.73183727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84997034072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81216716766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95865249633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93030118942261</t>
+    <t xml:space="preserve">5.84997081756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81216812133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95865297317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93030166625977</t>
   </si>
   <si>
     <t xml:space="preserve">5.98228025436401</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90194892883301</t>
+    <t xml:space="preserve">5.90194940567017</t>
   </si>
   <si>
     <t xml:space="preserve">5.91612577438354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91140031814575</t>
+    <t xml:space="preserve">5.91139984130859</t>
   </si>
   <si>
     <t xml:space="preserve">5.83106899261475</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88777256011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78381586074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80744218826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84524583816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77436447143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82634353637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82161855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85469579696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79326629638672</t>
+    <t xml:space="preserve">5.88777303695679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78381633758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80744171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84524536132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77436494827271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82634449005127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82161808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85469532012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79326677322388</t>
   </si>
   <si>
     <t xml:space="preserve">5.8357949256897</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">5.95392799377441</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92557573318481</t>
+    <t xml:space="preserve">5.92557621002197</t>
   </si>
   <si>
     <t xml:space="preserve">5.94447708129883</t>
@@ -998,40 +998,40 @@
     <t xml:space="preserve">5.77908992767334</t>
   </si>
   <si>
-    <t xml:space="preserve">5.74601316452026</t>
+    <t xml:space="preserve">5.74601268768311</t>
   </si>
   <si>
     <t xml:space="preserve">5.71766090393066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6515064239502</t>
+    <t xml:space="preserve">5.65150594711304</t>
   </si>
   <si>
     <t xml:space="preserve">5.66095638275146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79799222946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76018953323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69876050949097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66568183898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73656225204468</t>
+    <t xml:space="preserve">5.79799175262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76018905639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69876003265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66568231582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73656272888184</t>
   </si>
   <si>
     <t xml:space="preserve">5.78854084014893</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76963949203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89249849319458</t>
+    <t xml:space="preserve">5.76963996887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89249897003174</t>
   </si>
   <si>
     <t xml:space="preserve">5.97282934188843</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">6.13821601867676</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12404012680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02953338623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10513830184937</t>
+    <t xml:space="preserve">6.1240406036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02953386306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10513925552368</t>
   </si>
   <si>
     <t xml:space="preserve">6.16656827926636</t>
@@ -1064,124 +1064,124 @@
     <t xml:space="preserve">6.11458873748779</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31777954101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34140586853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4075608253479</t>
+    <t xml:space="preserve">6.31777906417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34140634536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40756130218506</t>
   </si>
   <si>
     <t xml:space="preserve">6.50206708908081</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42173719406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3083291053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47844076156616</t>
+    <t xml:space="preserve">6.42173671722412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30832815170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.478440284729</t>
   </si>
   <si>
     <t xml:space="preserve">6.31305360794067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33667993545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37448310852051</t>
+    <t xml:space="preserve">6.33668041229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37448358535767</t>
   </si>
   <si>
     <t xml:space="preserve">6.17601871490479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0909628868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23272323608398</t>
+    <t xml:space="preserve">6.09096336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23272275924683</t>
   </si>
   <si>
     <t xml:space="preserve">6.0389838218689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08623838424683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10041427612305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10986423492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00590658187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03425884246826</t>
+    <t xml:space="preserve">6.08623743057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10041379928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10986471176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00590705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0342583656311</t>
   </si>
   <si>
     <t xml:space="preserve">6.09568786621094</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0626106262207</t>
+    <t xml:space="preserve">6.06261110305786</t>
   </si>
   <si>
     <t xml:space="preserve">6.18074417114258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08151245117188</t>
+    <t xml:space="preserve">6.08151149749756</t>
   </si>
   <si>
     <t xml:space="preserve">6.15711784362793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21382188796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24217414855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24689960479736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20909690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22799777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19964599609375</t>
+    <t xml:space="preserve">6.21382141113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24217319488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24689912796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20909643173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22799730300903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19964504241943</t>
   </si>
   <si>
     <t xml:space="preserve">6.12876558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07206106185913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05788516998291</t>
+    <t xml:space="preserve">6.07206201553345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05788564682007</t>
   </si>
   <si>
     <t xml:space="preserve">6.13349056243896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14294147491455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01063203811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94920301437378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97755479812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05315971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99645519256592</t>
+    <t xml:space="preserve">6.14294195175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01063299179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94920253753662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97755527496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05316066741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99645614624023</t>
   </si>
   <si>
     <t xml:space="preserve">6.06733655929565</t>
@@ -1199,49 +1199,49 @@
     <t xml:space="preserve">5.92085027694702</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57590103149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52864694595337</t>
+    <t xml:space="preserve">5.57590055465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52864742279053</t>
   </si>
   <si>
     <t xml:space="preserve">5.42941522598267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50502014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61370372772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63733053207397</t>
+    <t xml:space="preserve">5.50502061843872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61370420455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63732957839966</t>
   </si>
   <si>
     <t xml:space="preserve">6.04370975494385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98700571060181</t>
+    <t xml:space="preserve">5.98700523376465</t>
   </si>
   <si>
     <t xml:space="preserve">6.01535701751709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89722347259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81689405441284</t>
+    <t xml:space="preserve">5.89722394943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81689357757568</t>
   </si>
   <si>
     <t xml:space="preserve">5.87359714508057</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86414670944214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90667486190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96810483932495</t>
+    <t xml:space="preserve">5.86414575576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90667390823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96810388565063</t>
   </si>
   <si>
     <t xml:space="preserve">6.01550769805908</t>
@@ -1259,79 +1259,79 @@
     <t xml:space="preserve">6.20602226257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18697071075439</t>
+    <t xml:space="preserve">6.18697118759155</t>
   </si>
   <si>
     <t xml:space="preserve">6.08695030212402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07266235351562</t>
+    <t xml:space="preserve">6.07266187667847</t>
   </si>
   <si>
     <t xml:space="preserve">6.16315603256226</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27270221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25365114212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13934230804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29175424575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38701105117798</t>
+    <t xml:space="preserve">6.27270269393921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25365161895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13934183120728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2917537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38701057434082</t>
   </si>
   <si>
     <t xml:space="preserve">6.52513456344604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59657764434814</t>
+    <t xml:space="preserve">6.59657716751099</t>
   </si>
   <si>
     <t xml:space="preserve">6.69183540344238</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69659852981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62039184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57276296615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50608348846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58228969573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65373277664185</t>
+    <t xml:space="preserve">6.69659900665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62039279937744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57276391983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50608253479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58228874206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65373229980469</t>
   </si>
   <si>
     <t xml:space="preserve">6.71088743209839</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82519578933716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77280378341675</t>
+    <t xml:space="preserve">6.8251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77280426025391</t>
   </si>
   <si>
     <t xml:space="preserve">6.82995843887329</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02523612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92521619796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9204535484314</t>
+    <t xml:space="preserve">7.0252366065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92521572113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92045259475708</t>
   </si>
   <si>
     <t xml:space="preserve">7.01094770431519</t>
@@ -1340,19 +1340,19 @@
     <t xml:space="preserve">6.96808195114136</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91092777252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01571035385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04905080795288</t>
+    <t xml:space="preserve">6.91092681884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01570987701416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04905033111572</t>
   </si>
   <si>
     <t xml:space="preserve">7.09667921066284</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17764854431152</t>
+    <t xml:space="preserve">7.17764759063721</t>
   </si>
   <si>
     <t xml:space="preserve">7.28243112564087</t>
@@ -1364,49 +1364,49 @@
     <t xml:space="preserve">7.23956537246704</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27766847610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12525653839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94903039932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86806154251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00142097473145</t>
+    <t xml:space="preserve">7.27766799926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12525701522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94903087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86806201934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0014214515686</t>
   </si>
   <si>
     <t xml:space="preserve">7.00618457794189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06333923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760725021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99189710617065</t>
+    <t xml:space="preserve">7.0633397102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760820388794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9918966293335</t>
   </si>
   <si>
     <t xml:space="preserve">7.0395245552063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02047395706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07762813568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18717384338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21098899841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41579103469849</t>
+    <t xml:space="preserve">7.02047348022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07762861251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18717432022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21098804473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4157919883728</t>
   </si>
   <si>
     <t xml:space="preserve">7.29671955108643</t>
@@ -1418,37 +1418,37 @@
     <t xml:space="preserve">7.24432849884033</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2729058265686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30624532699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1824107170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2538537979126</t>
+    <t xml:space="preserve">7.27290630340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30624580383301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18241119384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25385427474976</t>
   </si>
   <si>
     <t xml:space="preserve">7.05857610702515</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10620546340942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14907073974609</t>
+    <t xml:space="preserve">7.10620498657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14907026290894</t>
   </si>
   <si>
     <t xml:space="preserve">7.1681227684021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90140151977539</t>
+    <t xml:space="preserve">6.90140199661255</t>
   </si>
   <si>
     <t xml:space="preserve">6.94426774978638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06810235977173</t>
+    <t xml:space="preserve">7.06810283660889</t>
   </si>
   <si>
     <t xml:space="preserve">6.98713350296021</t>
@@ -1457,52 +1457,52 @@
     <t xml:space="preserve">7.1300196647644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87758731842041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70612335205078</t>
+    <t xml:space="preserve">6.87758684158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7061243057251</t>
   </si>
   <si>
     <t xml:space="preserve">6.63944339752197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65849447250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32985687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19649648666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11552810668945</t>
+    <t xml:space="preserve">6.65849494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32985734939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19649744033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11552762985229</t>
   </si>
   <si>
     <t xml:space="preserve">6.04884719848633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21554851531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31556844711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33461999893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34414482116699</t>
+    <t xml:space="preserve">6.21554803848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3155689239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33462047576904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34414577484131</t>
   </si>
   <si>
     <t xml:space="preserve">6.12505340576172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15363025665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30604219436646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35367155075073</t>
+    <t xml:space="preserve">6.15363121032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30604267120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35367107391357</t>
   </si>
   <si>
     <t xml:space="preserve">6.47274351119995</t>
@@ -1514,10 +1514,10 @@
     <t xml:space="preserve">6.42987728118896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52989768981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76804208755493</t>
+    <t xml:space="preserve">6.52989816665649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76804113388062</t>
   </si>
   <si>
     <t xml:space="preserve">7.08239078521729</t>
@@ -1526,40 +1526,40 @@
     <t xml:space="preserve">7.11096858978271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12049293518066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32529735565186</t>
+    <t xml:space="preserve">7.12049388885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32529783248901</t>
   </si>
   <si>
     <t xml:space="preserve">7.31577157974243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11573028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03476285934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1538348197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04428768157959</t>
+    <t xml:space="preserve">7.11573076248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03476238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15383434295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04428815841675</t>
   </si>
   <si>
     <t xml:space="preserve">7.02999925613403</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17288541793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36340093612671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14430809020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20622491836548</t>
+    <t xml:space="preserve">7.17288589477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36339998245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14430856704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20622634887695</t>
   </si>
   <si>
     <t xml:space="preserve">7.32053470611572</t>
@@ -1571,58 +1571,58 @@
     <t xml:space="preserve">6.98237037658691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44913148880005</t>
+    <t xml:space="preserve">7.44913196563721</t>
   </si>
   <si>
     <t xml:space="preserve">7.3824520111084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3300609588623</t>
+    <t xml:space="preserve">7.33006000518799</t>
   </si>
   <si>
     <t xml:space="preserve">7.21575164794922</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33958530426025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35387420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55391550064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60630750656128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46342086791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49199724197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44436883926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42055511474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62535810470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53010082244873</t>
+    <t xml:space="preserve">7.33958578109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35387468338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55391454696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60630702972412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46342039108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49199771881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44436979293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42055416107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62535858154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53010129928589</t>
   </si>
   <si>
     <t xml:space="preserve">7.47294616699219</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4872350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46818351745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49676132202148</t>
+    <t xml:space="preserve">7.48723554611206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4681830406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49676036834717</t>
   </si>
   <si>
     <t xml:space="preserve">7.51581192016602</t>
@@ -1631,70 +1631,70 @@
     <t xml:space="preserve">7.61106967926025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56344079971313</t>
+    <t xml:space="preserve">7.56344127655029</t>
   </si>
   <si>
     <t xml:space="preserve">7.6444091796875</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73490428924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80634689331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8682656288147</t>
+    <t xml:space="preserve">7.73490381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80634641647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86826372146606</t>
   </si>
   <si>
     <t xml:space="preserve">7.85873889923096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88731575012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92541790008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95399522781372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83492565155029</t>
+    <t xml:space="preserve">7.88731670379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92541933059692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95399713516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83492517471313</t>
   </si>
   <si>
     <t xml:space="preserve">7.98733568191528</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01115131378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06354236602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53486299514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52057504653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5443902015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62059497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63964700698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77776956558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76824331283569</t>
+    <t xml:space="preserve">8.01114940643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06354331970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53486347198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52057552337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54438924789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62059545516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63964796066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77777099609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76824426651001</t>
   </si>
   <si>
     <t xml:space="preserve">7.90636873245239</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03496551513672</t>
+    <t xml:space="preserve">8.03496646881104</t>
   </si>
   <si>
     <t xml:space="preserve">8.00638771057129</t>
@@ -1703,31 +1703,31 @@
     <t xml:space="preserve">8.04449081420898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06830596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2016658782959</t>
+    <t xml:space="preserve">8.06830501556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20166492462158</t>
   </si>
   <si>
     <t xml:space="preserve">8.32549953460693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44457244873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33978843688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38265514373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33502578735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27787017822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23500633239746</t>
+    <t xml:space="preserve">8.44457149505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33978939056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38265419006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33502769470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27787208557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23500537872314</t>
   </si>
   <si>
     <t xml:space="preserve">8.25882053375244</t>
@@ -1739,25 +1739,25 @@
     <t xml:space="preserve">8.16832637786865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31121349334717</t>
+    <t xml:space="preserve">8.31121158599854</t>
   </si>
   <si>
     <t xml:space="preserve">8.36836624145508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35408020019531</t>
+    <t xml:space="preserve">8.35407829284668</t>
   </si>
   <si>
     <t xml:space="preserve">8.37789249420166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28739738464355</t>
+    <t xml:space="preserve">8.28739643096924</t>
   </si>
   <si>
     <t xml:space="preserve">8.21119213104248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22071838378906</t>
+    <t xml:space="preserve">8.22071647644043</t>
   </si>
   <si>
     <t xml:space="preserve">8.43150520324707</t>
@@ -1769,25 +1769,25 @@
     <t xml:space="preserve">8.56085300445557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51294612884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48899173736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60875797271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44108581542969</t>
+    <t xml:space="preserve">8.51294422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48899269104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60875701904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.441086769104</t>
   </si>
   <si>
     <t xml:space="preserve">8.49857425689697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48420143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67103672027588</t>
+    <t xml:space="preserve">8.4842004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6710376739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.8147554397583</t>
@@ -1799,34 +1799,34 @@
     <t xml:space="preserve">8.83391761779785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77642822265625</t>
+    <t xml:space="preserve">8.77643013000488</t>
   </si>
   <si>
     <t xml:space="preserve">8.70936107635498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6854076385498</t>
+    <t xml:space="preserve">8.68540668487549</t>
   </si>
   <si>
     <t xml:space="preserve">8.70457077026367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78122234344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80996417999268</t>
+    <t xml:space="preserve">8.78122043609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80996322631836</t>
   </si>
   <si>
     <t xml:space="preserve">8.77163887023926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65187358856201</t>
+    <t xml:space="preserve">8.65187454223633</t>
   </si>
   <si>
     <t xml:space="preserve">8.53689765930176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37880706787109</t>
+    <t xml:space="preserve">8.37880802154541</t>
   </si>
   <si>
     <t xml:space="preserve">8.37401676177979</t>
@@ -1835,19 +1835,19 @@
     <t xml:space="preserve">8.40755176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4123420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32610988616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45545864105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41713333129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39318084716797</t>
+    <t xml:space="preserve">8.41234302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32611083984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45545768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41713237762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39318180084229</t>
   </si>
   <si>
     <t xml:space="preserve">8.54648017883301</t>
@@ -1856,25 +1856,25 @@
     <t xml:space="preserve">8.58959579467773</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27341365814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22071647644043</t>
+    <t xml:space="preserve">8.27341461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22071743011475</t>
   </si>
   <si>
     <t xml:space="preserve">8.25425148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35485553741455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4746208190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42192268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36922645568848</t>
+    <t xml:space="preserve">8.35485458374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47462177276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42192363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36922740936279</t>
   </si>
   <si>
     <t xml:space="preserve">8.31653022766113</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">8.29736709594727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28299617767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1776008605957</t>
+    <t xml:space="preserve">8.28299522399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17760181427002</t>
   </si>
   <si>
     <t xml:space="preserve">8.2015552520752</t>
@@ -1895,10 +1895,10 @@
     <t xml:space="preserve">8.16322994232178</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24946117401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18239307403564</t>
+    <t xml:space="preserve">8.24946022033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18239116668701</t>
   </si>
   <si>
     <t xml:space="preserve">8.17281055450439</t>
@@ -1907,40 +1907,40 @@
     <t xml:space="preserve">8.09616088867188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14885711669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06741714477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03867340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97160339355469</t>
+    <t xml:space="preserve">8.14885997772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06741809844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03867435455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97160530090332</t>
   </si>
   <si>
     <t xml:space="preserve">7.78956031799316</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62188863754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61709785461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66021347045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50212287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72249221801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59314489364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45900678634644</t>
+    <t xml:space="preserve">7.62188911437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61709833145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66021299362183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50212335586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72249174118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5931453704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45900726318359</t>
   </si>
   <si>
     <t xml:space="preserve">7.51170444488525</t>
@@ -1949,22 +1949,22 @@
     <t xml:space="preserve">7.65542316436768</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59793615341187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90932750701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95244312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82309484481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88058376312256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10574245452881</t>
+    <t xml:space="preserve">7.59793567657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90932703018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95244264602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82309579849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88058280944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10574340820312</t>
   </si>
   <si>
     <t xml:space="preserve">8.2063455581665</t>
@@ -1973,118 +1973,118 @@
     <t xml:space="preserve">8.16802024841309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26383209228516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34527397155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29257678985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12011528015137</t>
+    <t xml:space="preserve">8.26383304595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3452730178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29257583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12011337280273</t>
   </si>
   <si>
     <t xml:space="preserve">8.03388214111328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99555730819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80872344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91411781311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88537216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82788610458374</t>
+    <t xml:space="preserve">7.99555778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80872297286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91411685943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88537359237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8278865814209</t>
   </si>
   <si>
     <t xml:space="preserve">7.84704828262329</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00034713745117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89974498748779</t>
+    <t xml:space="preserve">8.00034809112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89974451065063</t>
   </si>
   <si>
     <t xml:space="preserve">7.90453577041626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94286155700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71770143508911</t>
+    <t xml:space="preserve">7.94286108016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71770191192627</t>
   </si>
   <si>
     <t xml:space="preserve">7.85662937164307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04346466064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11532402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12969589233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13448715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00992965698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93327903747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75123596191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57877254486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64105129241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69374799728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83746719360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81351280212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87100219726562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87579154968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92369842529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89495515823364</t>
+    <t xml:space="preserve">8.04346561431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11532306671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12969493865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13448619842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00992870330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9332799911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7512354850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.578773021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64105081558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69374752044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83746767044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81351327896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87100172042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87579250335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92369890213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89495372772217</t>
   </si>
   <si>
     <t xml:space="preserve">7.8518385887146</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86621046066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98597717285156</t>
+    <t xml:space="preserve">7.86621141433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98597764968872</t>
   </si>
   <si>
     <t xml:space="preserve">7.9668140411377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92848825454712</t>
+    <t xml:space="preserve">7.92848873138428</t>
   </si>
   <si>
     <t xml:space="preserve">8.11053276062012</t>
@@ -2093,52 +2093,52 @@
     <t xml:space="preserve">8.04825496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93806934356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77997970581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81830501556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84225845336914</t>
+    <t xml:space="preserve">7.93806982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77997922897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81830358505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84225797653198</t>
   </si>
   <si>
     <t xml:space="preserve">7.79435157775879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7991418838501</t>
+    <t xml:space="preserve">7.79914283752441</t>
   </si>
   <si>
     <t xml:space="preserve">7.94765138626099</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9189076423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71291065216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77518844604492</t>
+    <t xml:space="preserve">7.91890811920166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71291160583496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77518892288208</t>
   </si>
   <si>
     <t xml:space="preserve">7.86141920089722</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07699871063232</t>
+    <t xml:space="preserve">8.07699775695801</t>
   </si>
   <si>
     <t xml:space="preserve">8.21592712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2686243057251</t>
+    <t xml:space="preserve">8.26862335205078</t>
   </si>
   <si>
     <t xml:space="preserve">8.33569240570068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4506664276123</t>
+    <t xml:space="preserve">8.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">8.36443519592285</t>
@@ -2147,7 +2147,7 @@
     <t xml:space="preserve">8.47941207885742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55127048492432</t>
+    <t xml:space="preserve">8.55127143859863</t>
   </si>
   <si>
     <t xml:space="preserve">8.59438610076904</t>
@@ -2156,85 +2156,85 @@
     <t xml:space="preserve">8.66624546051025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64229393005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69019794464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58480453491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19197463989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74165439605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70332956314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78477048873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44463539123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22426652908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17636013031006</t>
+    <t xml:space="preserve">8.64229202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6901969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58480548858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19197368621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74165487289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70332908630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78477001190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44463634490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22426700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1763596534729</t>
   </si>
   <si>
     <t xml:space="preserve">7.30091714859009</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36319541931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33924150466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09492015838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69729709625244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.36195373535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33675956726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54754734039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37987470626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30322504043579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8685188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45776605606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08409690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0361909866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29967546463013</t>
+    <t xml:space="preserve">7.36319494247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33924198150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09491968154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6972975730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.36195278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33675909042358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54754686355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37987518310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30322456359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86851930618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45776557922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08409643173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03619146347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29967594146729</t>
   </si>
   <si>
     <t xml:space="preserve">6.76915693283081</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84101676940918</t>
+    <t xml:space="preserve">6.84101629257202</t>
   </si>
   <si>
     <t xml:space="preserve">6.53441619873047</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">6.02852630615234</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11092519760132</t>
+    <t xml:space="preserve">6.11092472076416</t>
   </si>
   <si>
     <t xml:space="preserve">5.85606336593628</t>
@@ -2258,61 +2258,61 @@
     <t xml:space="preserve">6.45201730728149</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38111543655396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32171249389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35237264633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40986061096191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4079442024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47309637069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65897226333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49962091445923</t>
+    <t xml:space="preserve">6.38111639022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32171297073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35237312316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40986013412476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40794372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47309589385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65897274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49962043762207</t>
   </si>
   <si>
     <t xml:space="preserve">6.44746923446655</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4300856590271</t>
+    <t xml:space="preserve">6.43008518218994</t>
   </si>
   <si>
     <t xml:space="preserve">6.393385887146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44360637664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59619808197021</t>
+    <t xml:space="preserve">6.44360589981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59619760513306</t>
   </si>
   <si>
     <t xml:space="preserve">6.61551284790039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79321432113647</t>
+    <t xml:space="preserve">6.79321384429932</t>
   </si>
   <si>
     <t xml:space="preserve">6.82798194885254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62323904037476</t>
+    <t xml:space="preserve">6.62323951721191</t>
   </si>
   <si>
     <t xml:space="preserve">6.690842628479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76617288589478</t>
+    <t xml:space="preserve">6.76617240905762</t>
   </si>
   <si>
     <t xml:space="preserve">6.78935146331787</t>
@@ -2324,28 +2324,28 @@
     <t xml:space="preserve">6.95932626724243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08487606048584</t>
+    <t xml:space="preserve">7.084876537323</t>
   </si>
   <si>
     <t xml:space="preserve">6.93807983398438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70629501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66766405105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94001150131226</t>
+    <t xml:space="preserve">6.70629549026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66766452789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94001054763794</t>
   </si>
   <si>
     <t xml:space="preserve">6.51121044158936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67345905303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53245687484741</t>
+    <t xml:space="preserve">6.67345857620239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53245735168457</t>
   </si>
   <si>
     <t xml:space="preserve">6.6638011932373</t>
@@ -2357,19 +2357,19 @@
     <t xml:space="preserve">6.72947359085083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71208953857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14668560028076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05010890960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94387435913086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11191844940186</t>
+    <t xml:space="preserve">6.71209001541138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1466851234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05010843276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94387483596802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11191749572754</t>
   </si>
   <si>
     <t xml:space="preserve">7.09839677810669</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">7.142822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14475297927856</t>
+    <t xml:space="preserve">7.14475393295288</t>
   </si>
   <si>
     <t xml:space="preserve">7.13895988464355</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">7.05976629257202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20463180541992</t>
+    <t xml:space="preserve">7.20463132858276</t>
   </si>
   <si>
     <t xml:space="preserve">7.06942415237427</t>
@@ -2399,97 +2399,97 @@
     <t xml:space="preserve">7.31279802322388</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33018112182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38619613647461</t>
+    <t xml:space="preserve">7.33018159866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38619565963745</t>
   </si>
   <si>
     <t xml:space="preserve">7.44800519943237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44027900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58128118515015</t>
+    <t xml:space="preserve">7.44027853012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58128070831299</t>
   </si>
   <si>
     <t xml:space="preserve">7.27223587036133</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26837205886841</t>
+    <t xml:space="preserve">7.26837253570557</t>
   </si>
   <si>
     <t xml:space="preserve">7.24326229095459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34370183944702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54844522476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45380020141602</t>
+    <t xml:space="preserve">7.34370279312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5484447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45379972457886</t>
   </si>
   <si>
     <t xml:space="preserve">7.62667226791382</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67013216018677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70683145523071</t>
+    <t xml:space="preserve">7.67013168334961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70683097839355</t>
   </si>
   <si>
     <t xml:space="preserve">7.84203863143921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86425113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81499719619751</t>
+    <t xml:space="preserve">7.86425161361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81499767303467</t>
   </si>
   <si>
     <t xml:space="preserve">7.75029039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92412900924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91350603103638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8285174369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89322519302368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98497152328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87294387817383</t>
+    <t xml:space="preserve">7.92412757873535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91350555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82851791381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89322423934937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98497247695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87294435501099</t>
   </si>
   <si>
     <t xml:space="preserve">8.0265007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">7.885498046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83817529678345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26311302185059</t>
+    <t xml:space="preserve">7.88549900054932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83817577362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2631139755249</t>
   </si>
   <si>
     <t xml:space="preserve">8.42729473114014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21965312957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22158527374268</t>
+    <t xml:space="preserve">8.21965503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22158432006836</t>
   </si>
   <si>
     <t xml:space="preserve">8.28146362304688</t>
@@ -2501,52 +2501,52 @@
     <t xml:space="preserve">8.29594993591309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13659763336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20806503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21868991851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26601123809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43598556518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3973560333252</t>
+    <t xml:space="preserve">8.13659858703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2080659866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21868896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26601028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43598651885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39735507965088</t>
   </si>
   <si>
     <t xml:space="preserve">8.27760028839111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.30753898620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24283218383789</t>
+    <t xml:space="preserve">8.30753993988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24283313751221</t>
   </si>
   <si>
     <t xml:space="preserve">8.34423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.228346824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39059543609619</t>
+    <t xml:space="preserve">8.22834587097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39059448242188</t>
   </si>
   <si>
     <t xml:space="preserve">8.34327220916748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43405437469482</t>
+    <t xml:space="preserve">8.43405342102051</t>
   </si>
   <si>
     <t xml:space="preserve">8.3104362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18102264404297</t>
+    <t xml:space="preserve">8.18102359771729</t>
   </si>
   <si>
     <t xml:space="preserve">8.29788112640381</t>
@@ -2558,43 +2558,43 @@
     <t xml:space="preserve">8.77110767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58664608001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4794454574585</t>
+    <t xml:space="preserve">8.58664512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47944641113281</t>
   </si>
   <si>
     <t xml:space="preserve">8.71799182891846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65907764434814</t>
+    <t xml:space="preserve">8.65907859802246</t>
   </si>
   <si>
     <t xml:space="preserve">8.75565528869629</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71412658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82132816314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94784450531006</t>
+    <t xml:space="preserve">8.71412754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82132625579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94784355163574</t>
   </si>
   <si>
     <t xml:space="preserve">9.01448059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03959178924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0608377456665</t>
+    <t xml:space="preserve">9.03959083557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06083869934082</t>
   </si>
   <si>
     <t xml:space="preserve">8.85319709777832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94011688232422</t>
+    <t xml:space="preserve">8.94011783599854</t>
   </si>
   <si>
     <t xml:space="preserve">9.01641368865967</t>
@@ -2606,22 +2606,22 @@
     <t xml:space="preserve">8.80587577819824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08884620666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01158332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99999618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04828453063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04635143280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02896690368652</t>
+    <t xml:space="preserve">9.08884525299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0115852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99999523162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04828357696533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04635238647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02896881103516</t>
   </si>
   <si>
     <t xml:space="preserve">8.95460414886475</t>
@@ -2630,58 +2630,58 @@
     <t xml:space="preserve">8.99613094329834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97198677062988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04442024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21343040466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23853969573975</t>
+    <t xml:space="preserve">8.9719877243042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04441928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21342945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23854064941406</t>
   </si>
   <si>
     <t xml:space="preserve">9.1747989654541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06180477142334</t>
+    <t xml:space="preserve">9.06180381774902</t>
   </si>
   <si>
     <t xml:space="preserve">9.12554550170898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03186511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07629108428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80008029937744</t>
+    <t xml:space="preserve">9.0318660736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07629013061523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80008125305176</t>
   </si>
   <si>
     <t xml:space="preserve">8.93528842926025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94687843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74020385742188</t>
+    <t xml:space="preserve">8.94687747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74020481109619</t>
   </si>
   <si>
     <t xml:space="preserve">8.88893222808838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66294097900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50262355804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65714740753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51035022735596</t>
+    <t xml:space="preserve">8.66294193267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50262451171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65714645385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51034927368164</t>
   </si>
   <si>
     <t xml:space="preserve">8.59727001190186</t>
@@ -2699,37 +2699,37 @@
     <t xml:space="preserve">9.24626541137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51281642913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35443210601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29841804504395</t>
+    <t xml:space="preserve">9.26171779632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51281833648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35443115234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29841709136963</t>
   </si>
   <si>
     <t xml:space="preserve">9.44328308105469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4316930770874</t>
+    <t xml:space="preserve">9.43169403076172</t>
   </si>
   <si>
     <t xml:space="preserve">9.25012874603271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13230609893799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22501945495605</t>
+    <t xml:space="preserve">9.13230514526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22501850128174</t>
   </si>
   <si>
     <t xml:space="preserve">9.06856536865234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19411373138428</t>
+    <t xml:space="preserve">9.19411563873291</t>
   </si>
   <si>
     <t xml:space="preserve">9.17286777496338</t>
@@ -2738,28 +2738,28 @@
     <t xml:space="preserve">9.22695064544678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.36215782165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12651062011719</t>
+    <t xml:space="preserve">9.36215877532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12650966644287</t>
   </si>
   <si>
     <t xml:space="preserve">9.1477575302124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13037395477295</t>
+    <t xml:space="preserve">9.13037490844727</t>
   </si>
   <si>
     <t xml:space="preserve">9.15934753417969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12264728546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00482273101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13616752624512</t>
+    <t xml:space="preserve">9.12264823913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0048246383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13616847991943</t>
   </si>
   <si>
     <t xml:space="preserve">9.05890655517578</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">9.04538631439209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83677959442139</t>
+    <t xml:space="preserve">8.8367805480957</t>
   </si>
   <si>
     <t xml:space="preserve">8.87347984313965</t>
@@ -2777,31 +2777,31 @@
     <t xml:space="preserve">8.95267295837402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93915176391602</t>
+    <t xml:space="preserve">8.93914985656738</t>
   </si>
   <si>
     <t xml:space="preserve">8.86961650848389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88120555877686</t>
+    <t xml:space="preserve">8.88120651245117</t>
   </si>
   <si>
     <t xml:space="preserve">8.96619319915771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13809967041016</t>
+    <t xml:space="preserve">9.13809871673584</t>
   </si>
   <si>
     <t xml:space="preserve">9.02027606964111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90438461303711</t>
+    <t xml:space="preserve">8.90438365936279</t>
   </si>
   <si>
     <t xml:space="preserve">8.66487407684326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59340667724609</t>
+    <t xml:space="preserve">8.59340572357178</t>
   </si>
   <si>
     <t xml:space="preserve">8.54125499725342</t>
@@ -2810,55 +2810,55 @@
     <t xml:space="preserve">8.55284404754639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42150020599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38093852996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47365093231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42343139648438</t>
+    <t xml:space="preserve">8.42149925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38093948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47365188598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42343044281006</t>
   </si>
   <si>
     <t xml:space="preserve">8.4253625869751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54705142974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4929666519165</t>
+    <t xml:space="preserve">8.54705047607422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49296569824219</t>
   </si>
   <si>
     <t xml:space="preserve">8.58568096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51228046417236</t>
+    <t xml:space="preserve">8.512282371521</t>
   </si>
   <si>
     <t xml:space="preserve">8.5064868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63589954376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59533882141113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65328407287598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57215976715088</t>
+    <t xml:space="preserve">8.63590049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5953369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65328502655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57215881347656</t>
   </si>
   <si>
     <t xml:space="preserve">8.57795429229736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82712268829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86768531799316</t>
+    <t xml:space="preserve">8.82712364196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86768436431885</t>
   </si>
   <si>
     <t xml:space="preserve">8.94108295440674</t>
@@ -2870,19 +2870,19 @@
     <t xml:space="preserve">9.31773281097412</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40271949768066</t>
+    <t xml:space="preserve">9.40272045135498</t>
   </si>
   <si>
     <t xml:space="preserve">9.34477424621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38533782958984</t>
+    <t xml:space="preserve">9.38533592224121</t>
   </si>
   <si>
     <t xml:space="preserve">9.44521331787109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58235168457031</t>
+    <t xml:space="preserve">9.58235263824463</t>
   </si>
   <si>
     <t xml:space="preserve">9.42976093292236</t>
@@ -2891,13 +2891,13 @@
     <t xml:space="preserve">9.44135093688965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35249996185303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20570468902588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2887601852417</t>
+    <t xml:space="preserve">9.35250091552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20570278167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28875923156738</t>
   </si>
   <si>
     <t xml:space="preserve">9.3158016204834</t>
@@ -2906,19 +2906,19 @@
     <t xml:space="preserve">9.34091091156006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05697631835938</t>
+    <t xml:space="preserve">9.05697536468506</t>
   </si>
   <si>
     <t xml:space="preserve">9.19218254089355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16320896148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04925060272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26751327514648</t>
+    <t xml:space="preserve">9.16320991516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04924964904785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26751136779785</t>
   </si>
   <si>
     <t xml:space="preserve">9.16900444030762</t>
@@ -2930,49 +2930,49 @@
     <t xml:space="preserve">9.52440738677979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76391696929932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48963928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46839237213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38726902008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42589855194092</t>
+    <t xml:space="preserve">9.76391792297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48963832855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46839332580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38726806640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42589950561523</t>
   </si>
   <si>
     <t xml:space="preserve">9.36408996582031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28296566009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25978660583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24240303039551</t>
+    <t xml:space="preserve">9.28296661376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25978755950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24240207672119</t>
   </si>
   <si>
     <t xml:space="preserve">9.26364898681641</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28682708740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35056972503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23081302642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39885807037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32932186126709</t>
+    <t xml:space="preserve">9.28682804107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3505687713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23081398010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39885711669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32932090759277</t>
   </si>
   <si>
     <t xml:space="preserve">9.4645299911499</t>
@@ -2981,40 +2981,40 @@
     <t xml:space="preserve">9.41624069213867</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63836669921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47225475311279</t>
+    <t xml:space="preserve">9.63836765289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47225379943848</t>
   </si>
   <si>
     <t xml:space="preserve">9.56497001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64416217803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76943588256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55384826660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73544788360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83255863189697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70340061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62959671020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60823059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52859973907471</t>
+    <t xml:space="preserve">9.64416313171387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76943683624268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55384922027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73544692993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83255958557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70340156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62959575653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60823154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52860069274902</t>
   </si>
   <si>
     <t xml:space="preserve">9.63348007202148</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">9.8811149597168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0025043487549</t>
+    <t xml:space="preserve">10.0025053024292</t>
   </si>
   <si>
     <t xml:space="preserve">10.0947618484497</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98308086395264</t>
+    <t xml:space="preserve">9.98308181762695</t>
   </si>
   <si>
     <t xml:space="preserve">9.94423770904541</t>
@@ -3050,49 +3050,49 @@
     <t xml:space="preserve">9.82770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79857063293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79371356964111</t>
+    <t xml:space="preserve">9.79856872558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79371452331543</t>
   </si>
   <si>
     <t xml:space="preserve">10.0656270980835</t>
   </si>
   <si>
-    <t xml:space="preserve">10.167594909668</t>
+    <t xml:space="preserve">10.1675939559937</t>
   </si>
   <si>
     <t xml:space="preserve">10.2355718612671</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2549953460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1870164871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.14817237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2307167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2792720794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2744178771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3132610321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3909521102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5754632949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6337308883667</t>
+    <t xml:space="preserve">10.254994392395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1870174407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1481714248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2307176589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2792730331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2744169235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3132629394531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3909511566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5754642486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6337299346924</t>
   </si>
   <si>
     <t xml:space="preserve">10.8133878707886</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">10.8182420730591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8328094482422</t>
+    <t xml:space="preserve">10.8328084945679</t>
   </si>
   <si>
     <t xml:space="preserve">10.8230991363525</t>
@@ -3110,40 +3110,40 @@
     <t xml:space="preserve">10.8570880889893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7551193237305</t>
+    <t xml:space="preserve">10.7551202774048</t>
   </si>
   <si>
     <t xml:space="preserve">10.7454080581665</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7842540740967</t>
+    <t xml:space="preserve">10.7842531204224</t>
   </si>
   <si>
     <t xml:space="preserve">11.0852994918823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0755882263184</t>
+    <t xml:space="preserve">11.0755891799927</t>
   </si>
   <si>
     <t xml:space="preserve">11.0610218048096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0464544296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9687662124634</t>
+    <t xml:space="preserve">11.0464553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9687652587891</t>
   </si>
   <si>
     <t xml:space="preserve">11.0027551651001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9104995727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.891077041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9978981018066</t>
+    <t xml:space="preserve">10.9104986190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8910779953003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.997899055481</t>
   </si>
   <si>
     <t xml:space="preserve">10.827953338623</t>
@@ -3155,19 +3155,19 @@
     <t xml:space="preserve">10.9784774780273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8667974472046</t>
+    <t xml:space="preserve">10.8667984008789</t>
   </si>
   <si>
     <t xml:space="preserve">10.6531534194946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7162742614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9930438995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.162989616394</t>
+    <t xml:space="preserve">10.7162761688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9930429458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1629886627197</t>
   </si>
   <si>
     <t xml:space="preserve">11.0513105392456</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">11.4688920974731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4931697845459</t>
+    <t xml:space="preserve">11.4931688308716</t>
   </si>
   <si>
     <t xml:space="preserve">11.5174465179443</t>
@@ -3191,13 +3191,13 @@
     <t xml:space="preserve">11.561146736145</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5028810501099</t>
+    <t xml:space="preserve">11.5028800964355</t>
   </si>
   <si>
     <t xml:space="preserve">11.6048469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5805692672729</t>
+    <t xml:space="preserve">11.5805702209473</t>
   </si>
   <si>
     <t xml:space="preserve">11.5660028457642</t>
@@ -3215,13 +3215,13 @@
     <t xml:space="preserve">11.745659828186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6922473907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6825380325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3620672225952</t>
+    <t xml:space="preserve">11.6922483444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6825361251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3620681762695</t>
   </si>
   <si>
     <t xml:space="preserve">11.2552452087402</t>
@@ -3236,10 +3236,10 @@
     <t xml:space="preserve">11.3814907073975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3669242858887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3329343795776</t>
+    <t xml:space="preserve">11.3669233322144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.332935333252</t>
   </si>
   <si>
     <t xml:space="preserve">11.3717794418335</t>
@@ -3257,37 +3257,37 @@
     <t xml:space="preserve">11.5757141113281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5125904083252</t>
+    <t xml:space="preserve">11.5125913619995</t>
   </si>
   <si>
     <t xml:space="preserve">11.410623550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5514364242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7068147659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9495944976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9301710128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7942152023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7602262496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8087825775146</t>
+    <t xml:space="preserve">11.5514373779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7068157196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.949595451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9301719665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7942161560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7602252960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8087816238403</t>
   </si>
   <si>
     <t xml:space="preserve">11.8282051086426</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7505149841309</t>
+    <t xml:space="preserve">11.7505159378052</t>
   </si>
   <si>
     <t xml:space="preserve">11.9253158569336</t>
@@ -3299,10 +3299,10 @@
     <t xml:space="preserve">12.0564165115356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.036994934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1875171661377</t>
+    <t xml:space="preserve">12.0369958877563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.187518119812</t>
   </si>
   <si>
     <t xml:space="preserve">12.1486730575562</t>
@@ -3311,10 +3311,10 @@
     <t xml:space="preserve">12.3865966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5565423965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4254417419434</t>
+    <t xml:space="preserve">12.5565433502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.425440788269</t>
   </si>
   <si>
     <t xml:space="preserve">12.5274085998535</t>
@@ -3326,16 +3326,16 @@
     <t xml:space="preserve">12.5662517547607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9350271224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0127172470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0758399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1729497909546</t>
+    <t xml:space="preserve">11.9350261688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.012716293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0758390426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1729507446289</t>
   </si>
   <si>
     <t xml:space="preserve">12.3331842422485</t>
@@ -3350,31 +3350,31 @@
     <t xml:space="preserve">12.304051399231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4108743667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4448642730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4157295227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5468311309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6439428329468</t>
+    <t xml:space="preserve">12.4108734130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4448623657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4157304763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5468320846558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6439437866211</t>
   </si>
   <si>
     <t xml:space="preserve">12.7750434875488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.964412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9595556259155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9401330947876</t>
+    <t xml:space="preserve">12.9644107818604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9595565795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9401321411133</t>
   </si>
   <si>
     <t xml:space="preserve">13.0760898590088</t>
@@ -3383,46 +3383,46 @@
     <t xml:space="preserve">12.5808200836182</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5953874588013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9110012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4837074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7070655822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4982757568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4739980697632</t>
+    <t xml:space="preserve">12.595386505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9109992980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4837083816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7070646286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4982738494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">12.3428964614868</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6390867233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8721542358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6099529266357</t>
+    <t xml:space="preserve">12.639087677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8721551895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6099519729614</t>
   </si>
   <si>
     <t xml:space="preserve">12.585675239563</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3768844604492</t>
+    <t xml:space="preserve">12.3768854141235</t>
   </si>
   <si>
     <t xml:space="preserve">12.4885635375977</t>
   </si>
   <si>
-    <t xml:space="preserve">12.284628868103</t>
+    <t xml:space="preserve">12.2846298217773</t>
   </si>
   <si>
     <t xml:space="preserve">12.2797737121582</t>
@@ -3431,7 +3431,7 @@
     <t xml:space="preserve">12.2020845413208</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4400081634521</t>
+    <t xml:space="preserve">12.4400091171265</t>
   </si>
   <si>
     <t xml:space="preserve">12.3720302581787</t>
@@ -3440,19 +3440,19 @@
     <t xml:space="preserve">12.4351530075073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3963079452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4060182571411</t>
+    <t xml:space="preserve">12.3963088989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4060192108154</t>
   </si>
   <si>
     <t xml:space="preserve">11.7553701400757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6728267669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6388359069824</t>
+    <t xml:space="preserve">11.6728248596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6388368606567</t>
   </si>
   <si>
     <t xml:space="preserve">11.4397573471069</t>
@@ -3464,10 +3464,10 @@
     <t xml:space="preserve">11.2164011001587</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0804443359375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.065878868103</t>
+    <t xml:space="preserve">11.0804433822632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0658779144287</t>
   </si>
   <si>
     <t xml:space="preserve">10.6968536376953</t>
@@ -3482,19 +3482,19 @@
     <t xml:space="preserve">10.5171966552734</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7696866989136</t>
+    <t xml:space="preserve">10.7696876525879</t>
   </si>
   <si>
     <t xml:space="preserve">10.9833326339722</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8619441986084</t>
+    <t xml:space="preserve">10.8619432449341</t>
   </si>
   <si>
     <t xml:space="preserve">10.7114200592041</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5269079208374</t>
+    <t xml:space="preserve">10.5269069671631</t>
   </si>
   <si>
     <t xml:space="preserve">10.44921875</t>
@@ -3506,34 +3506,34 @@
     <t xml:space="preserve">10.4880628585815</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3375396728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0899057388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1821603775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1918725967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2647066116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9588041305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02556037902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1887092590332</t>
+    <t xml:space="preserve">10.3375406265259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0899047851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1821613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1918716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2647047042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95880508422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02556133270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18870735168457</t>
   </si>
   <si>
     <t xml:space="preserve">9.46644878387451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04304122924805</t>
+    <t xml:space="preserve">9.04304218292236</t>
   </si>
   <si>
     <t xml:space="preserve">9.04498291015625</t>
@@ -3542,16 +3542,16 @@
     <t xml:space="preserve">9.06246376037598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84298992156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83910751342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54388809204102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14403820037842</t>
+    <t xml:space="preserve">8.84299182891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8391056060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5438871383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14403629302979</t>
   </si>
   <si>
     <t xml:space="preserve">8.9906005859375</t>
@@ -3560,10 +3560,10 @@
     <t xml:space="preserve">8.95369815826416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99836826324463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03138732910156</t>
+    <t xml:space="preserve">8.99836921691895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03138828277588</t>
   </si>
   <si>
     <t xml:space="preserve">9.58492469787598</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">9.55190658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75001335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62182712554932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68203735351562</t>
+    <t xml:space="preserve">9.75001430511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.621826171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68203639984131</t>
   </si>
   <si>
     <t xml:space="preserve">9.63736438751221</t>
@@ -3590,40 +3590,40 @@
     <t xml:space="preserve">10.0801935195923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2598495483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2501392364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4200849533081</t>
+    <t xml:space="preserve">10.2598505020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2501401901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4200830459595</t>
   </si>
   <si>
     <t xml:space="preserve">10.3860950469971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5074863433838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346513748169</t>
+    <t xml:space="preserve">10.5074844360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4346523284912</t>
   </si>
   <si>
     <t xml:space="preserve">10.415228843689</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3278303146362</t>
+    <t xml:space="preserve">10.3278293609619</t>
   </si>
   <si>
     <t xml:space="preserve">10.2110719680786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.528489112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3429222106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3819885253906</t>
+    <t xml:space="preserve">10.5284900665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3429231643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3819894790649</t>
   </si>
   <si>
     <t xml:space="preserve">10.4308233261108</t>
@@ -3632,19 +3632,19 @@
     <t xml:space="preserve">10.4210567474365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4259395599365</t>
+    <t xml:space="preserve">10.4259405136108</t>
   </si>
   <si>
     <t xml:space="preserve">10.5333728790283</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2306060791016</t>
+    <t xml:space="preserve">10.2306051254272</t>
   </si>
   <si>
     <t xml:space="preserve">10.4601230621338</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0645713806152</t>
+    <t xml:space="preserve">10.0645732879639</t>
   </si>
   <si>
     <t xml:space="preserve">10.1720056533813</t>
@@ -3653,58 +3653,58 @@
     <t xml:space="preserve">9.54986763000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33890819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58893394470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68855571746826</t>
+    <t xml:space="preserve">9.33890724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58893489837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68855476379395</t>
   </si>
   <si>
     <t xml:space="preserve">9.669020652771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97178840637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0059728622437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91318798065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59870052337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39750576019287</t>
+    <t xml:space="preserve">9.97178936004639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0059719085693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91318893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59870147705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39750671386719</t>
   </si>
   <si>
     <t xml:space="preserve">9.36234760284424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61823463439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4053201675415</t>
+    <t xml:space="preserve">9.6182336807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40532112121582</t>
   </si>
   <si>
     <t xml:space="preserve">9.47173404693604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47368812561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.659255027771</t>
+    <t xml:space="preserve">9.47368717193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65925407409668</t>
   </si>
   <si>
     <t xml:space="preserve">9.78622150421143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71004199981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51861381530762</t>
+    <t xml:space="preserve">9.71004104614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51861476898193</t>
   </si>
   <si>
     <t xml:space="preserve">9.69441413879395</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">9.68074131011963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54791355133057</t>
+    <t xml:space="preserve">9.54791450500488</t>
   </si>
   <si>
     <t xml:space="preserve">9.03418636322021</t>
@@ -3731,22 +3731,22 @@
     <t xml:space="preserve">8.8154125213623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20608043670654</t>
+    <t xml:space="preserve">9.20607948303223</t>
   </si>
   <si>
     <t xml:space="preserve">9.11427307128906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52252101898193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56744766235352</t>
+    <t xml:space="preserve">9.52252006530762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5674467086792</t>
   </si>
   <si>
     <t xml:space="preserve">9.46782779693604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55572891235352</t>
+    <t xml:space="preserve">9.5557279586792</t>
   </si>
   <si>
     <t xml:space="preserve">9.4541540145874</t>
@@ -3755,7 +3755,7 @@
     <t xml:space="preserve">9.79110431671143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85947227478027</t>
+    <t xml:space="preserve">9.85947132110596</t>
   </si>
   <si>
     <t xml:space="preserve">9.91807174682617</t>
@@ -3764,16 +3764,16 @@
     <t xml:space="preserve">9.81552219390869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.80087184906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72566795349121</t>
+    <t xml:space="preserve">9.80087089538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72566890716553</t>
   </si>
   <si>
     <t xml:space="preserve">9.661208152771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95713806152344</t>
+    <t xml:space="preserve">9.95713901519775</t>
   </si>
   <si>
     <t xml:space="preserve">10.001088142395</t>
@@ -3782,10 +3782,10 @@
     <t xml:space="preserve">10.162239074707</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2989730834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0499210357666</t>
+    <t xml:space="preserve">10.2989721298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0499219894409</t>
   </si>
   <si>
     <t xml:space="preserve">9.94248867034912</t>
@@ -3794,13 +3794,13 @@
     <t xml:space="preserve">9.9376049041748</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96690559387207</t>
+    <t xml:space="preserve">9.96690464019775</t>
   </si>
   <si>
     <t xml:space="preserve">9.88877201080322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1329393386841</t>
+    <t xml:space="preserve">10.1329383850098</t>
   </si>
   <si>
     <t xml:space="preserve">10.2354888916016</t>
@@ -3809,22 +3809,22 @@
     <t xml:space="preserve">10.4161729812622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.18665599823</t>
+    <t xml:space="preserve">10.1866550445557</t>
   </si>
   <si>
     <t xml:space="preserve">10.167121887207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5675573348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3673391342163</t>
+    <t xml:space="preserve">10.5675563812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.367338180542</t>
   </si>
   <si>
     <t xml:space="preserve">10.1182880401611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.19642162323</t>
+    <t xml:space="preserve">10.1964225769043</t>
   </si>
   <si>
     <t xml:space="preserve">9.97667217254639</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">9.81063747406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79598712921143</t>
+    <t xml:space="preserve">9.79598808288574</t>
   </si>
   <si>
     <t xml:space="preserve">9.78133869171143</t>
@@ -3842,16 +3842,16 @@
     <t xml:space="preserve">9.87900447845459</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0352725982666</t>
+    <t xml:space="preserve">10.035270690918</t>
   </si>
   <si>
     <t xml:space="preserve">10.1134052276611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1475896835327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1524724960327</t>
+    <t xml:space="preserve">10.1475887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.152473449707</t>
   </si>
   <si>
     <t xml:space="preserve">9.9815559387207</t>
@@ -3860,10 +3860,10 @@
     <t xml:space="preserve">9.83505439758301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57916831970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4482946395874</t>
+    <t xml:space="preserve">9.57916641235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44829368591309</t>
   </si>
   <si>
     <t xml:space="preserve">9.62409400939941</t>
@@ -3881,19 +3881,19 @@
     <t xml:space="preserve">9.33109378814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46001434326172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29593276977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31742000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00684070587158</t>
+    <t xml:space="preserve">9.4600133895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29593372344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31742095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96581935882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00683975219727</t>
   </si>
   <si>
     <t xml:space="preserve">8.94042682647705</t>
@@ -3908,10 +3908,10 @@
     <t xml:space="preserve">8.68649196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89549922943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84471225738525</t>
+    <t xml:space="preserve">8.89550018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84471321105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.88377857208252</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">8.72360610961914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89940643310547</t>
+    <t xml:space="preserve">8.89940738677979</t>
   </si>
   <si>
     <t xml:space="preserve">8.73532581329346</t>
@@ -3932,28 +3932,28 @@
     <t xml:space="preserve">8.78806591033936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88964080810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79783248901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94628524780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98144721984863</t>
+    <t xml:space="preserve">8.88963985443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79783344268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94628620147705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98144626617432</t>
   </si>
   <si>
     <t xml:space="preserve">8.78611278533936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98535251617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96191215515137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84080600738525</t>
+    <t xml:space="preserve">8.98535346984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96191310882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84080505371094</t>
   </si>
   <si>
     <t xml:space="preserve">8.60054492950439</t>
@@ -3968,31 +3968,31 @@
     <t xml:space="preserve">8.90917205810547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79587841033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80173969268799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70798015594482</t>
+    <t xml:space="preserve">8.79587936401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8017406463623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70797920227051</t>
   </si>
   <si>
     <t xml:space="preserve">8.88182640075684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99707221984863</t>
+    <t xml:space="preserve">8.99707317352295</t>
   </si>
   <si>
     <t xml:space="preserve">9.10841369628906</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96386623382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09473991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11622714996338</t>
+    <t xml:space="preserve">8.9638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09474086761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11622524261475</t>
   </si>
   <si>
     <t xml:space="preserve">8.9755859375</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">9.54205513000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49322032928467</t>
+    <t xml:space="preserve">9.49322128295898</t>
   </si>
   <si>
     <t xml:space="preserve">9.5654935836792</t>
@@ -4031,10 +4031,10 @@
     <t xml:space="preserve">9.80575466156006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69050693511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72371482849121</t>
+    <t xml:space="preserve">9.69050788879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72371387481689</t>
   </si>
   <si>
     <t xml:space="preserve">9.75692081451416</t>
@@ -4049,10 +4049,10 @@
     <t xml:space="preserve">9.58502769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62214183807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31546783447266</t>
+    <t xml:space="preserve">9.62214088439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31546688079834</t>
   </si>
   <si>
     <t xml:space="preserve">9.5108003616333</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">9.33500003814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43462085723877</t>
+    <t xml:space="preserve">9.43461990356445</t>
   </si>
   <si>
     <t xml:space="preserve">9.59088706970215</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">9.63190841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64948749542236</t>
+    <t xml:space="preserve">9.64948844909668</t>
   </si>
   <si>
     <t xml:space="preserve">9.65730094909668</t>
@@ -4094,40 +4094,40 @@
     <t xml:space="preserve">9.74324798583984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71199512481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71785449981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4443883895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42876148223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43852615356445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71590137481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0303897857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90342235565186</t>
+    <t xml:space="preserve">9.71199417114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71785354614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44438743591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42876052856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43852710723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71590042114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0303888320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90342140197754</t>
   </si>
   <si>
     <t xml:space="preserve">9.83017158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1427049636841</t>
+    <t xml:space="preserve">10.1427059173584</t>
   </si>
   <si>
     <t xml:space="preserve">10.2696723937988</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2452554702759</t>
+    <t xml:space="preserve">10.2452564239502</t>
   </si>
   <si>
     <t xml:space="preserve">10.3038558959961</t>
@@ -4139,16 +4139,16 @@
     <t xml:space="preserve">10.3380393981934</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4796562194824</t>
+    <t xml:space="preserve">10.4796552658081</t>
   </si>
   <si>
     <t xml:space="preserve">10.2550220489502</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3722219467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.347806930542</t>
+    <t xml:space="preserve">10.3722229003906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3478059768677</t>
   </si>
   <si>
     <t xml:space="preserve">10.5870895385742</t>
@@ -4157,31 +4157,31 @@
     <t xml:space="preserve">10.5382566452026</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4698896408081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4405889511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3917570114136</t>
+    <t xml:space="preserve">10.4698905944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4405899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3917560577393</t>
   </si>
   <si>
     <t xml:space="preserve">10.4747734069824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6749897003174</t>
+    <t xml:space="preserve">10.6749906539917</t>
   </si>
   <si>
     <t xml:space="preserve">10.518723487854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6310405731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6261558532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7580070495605</t>
+    <t xml:space="preserve">10.6310396194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6261568069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7580080032349</t>
   </si>
   <si>
     <t xml:space="preserve">10.8703241348267</t>
@@ -4196,10 +4196,10 @@
     <t xml:space="preserve">10.7775402069092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.880090713501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8361406326294</t>
+    <t xml:space="preserve">10.8800897598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8361396789551</t>
   </si>
   <si>
     <t xml:space="preserve">10.9875240325928</t>
@@ -4211,19 +4211,19 @@
     <t xml:space="preserve">11.0070581436157</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1291408538818</t>
+    <t xml:space="preserve">11.1291418075562</t>
   </si>
   <si>
     <t xml:space="preserve">11.2463417053223</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2268085479736</t>
+    <t xml:space="preserve">11.2268075942993</t>
   </si>
   <si>
     <t xml:space="preserve">11.2121572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">11.207275390625</t>
+    <t xml:space="preserve">11.2072744369507</t>
   </si>
   <si>
     <t xml:space="preserve">11.2561082839966</t>
@@ -4244,16 +4244,16 @@
     <t xml:space="preserve">11.5295753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5737495422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6670074462891</t>
+    <t xml:space="preserve">11.5737504959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6670083999634</t>
   </si>
   <si>
     <t xml:space="preserve">11.5982913970947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6326503753662</t>
+    <t xml:space="preserve">11.6326494216919</t>
   </si>
   <si>
     <t xml:space="preserve">11.4657678604126</t>
@@ -4262,13 +4262,13 @@
     <t xml:space="preserve">11.7700815200806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9418716430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.902606010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0645790100098</t>
+    <t xml:space="preserve">11.9418725967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9026050567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0645799636841</t>
   </si>
   <si>
     <t xml:space="preserve">12.1038455963135</t>
@@ -4283,10 +4283,10 @@
     <t xml:space="preserve">12.054762840271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.162745475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9173307418823</t>
+    <t xml:space="preserve">12.1627445220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9173316955566</t>
   </si>
   <si>
     <t xml:space="preserve">11.9467802047729</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">11.9369640350342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9860458374023</t>
+    <t xml:space="preserve">11.9860467910767</t>
   </si>
   <si>
     <t xml:space="preserve">12.2314615249634</t>
@@ -4325,28 +4325,28 @@
     <t xml:space="preserve">12.467059135437</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4130687713623</t>
+    <t xml:space="preserve">12.413067817688</t>
   </si>
   <si>
     <t xml:space="preserve">12.5701332092285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5652256011963</t>
+    <t xml:space="preserve">12.565224647522</t>
   </si>
   <si>
     <t xml:space="preserve">12.6633901596069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6143074035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6241235733032</t>
+    <t xml:space="preserve">12.6143083572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6241245269775</t>
   </si>
   <si>
     <t xml:space="preserve">12.2658185958862</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0596704483032</t>
+    <t xml:space="preserve">12.0596714019775</t>
   </si>
   <si>
     <t xml:space="preserve">12.0694875717163</t>
@@ -4370,16 +4370,16 @@
     <t xml:space="preserve">12.3050851821899</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3296270370483</t>
+    <t xml:space="preserve">12.3296279907227</t>
   </si>
   <si>
     <t xml:space="preserve">12.2216444015503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1921939849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4376096725464</t>
+    <t xml:space="preserve">12.1921949386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4376087188721</t>
   </si>
   <si>
     <t xml:space="preserve">12.4228839874268</t>
@@ -4388,7 +4388,7 @@
     <t xml:space="preserve">12.4866924285889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6928415298462</t>
+    <t xml:space="preserve">12.6928405761719</t>
   </si>
   <si>
     <t xml:space="preserve">12.4817838668823</t>
@@ -4412,13 +4412,13 @@
     <t xml:space="preserve">12.0940284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9762306213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9124231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.794623374939</t>
+    <t xml:space="preserve">11.9762296676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9124221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7946243286133</t>
   </si>
   <si>
     <t xml:space="preserve">11.8044395446777</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">11.7995319366455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.819164276123</t>
+    <t xml:space="preserve">11.8191652297974</t>
   </si>
   <si>
     <t xml:space="preserve">11.8927888870239</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">11.4461345672607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3970508575439</t>
+    <t xml:space="preserve">11.3970518112183</t>
   </si>
   <si>
     <t xml:space="preserve">11.4706764221191</t>
@@ -4448,7 +4448,7 @@
     <t xml:space="preserve">11.3872356414795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5639324188232</t>
+    <t xml:space="preserve">11.5639333724976</t>
   </si>
   <si>
     <t xml:space="preserve">11.5835666656494</t>
@@ -4460,13 +4460,13 @@
     <t xml:space="preserve">11.9075136184692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0007724761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.848614692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7749900817871</t>
+    <t xml:space="preserve">12.000771522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8486137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7749891281128</t>
   </si>
   <si>
     <t xml:space="preserve">11.8535223007202</t>
@@ -4478,10 +4478,10 @@
     <t xml:space="preserve">11.5344839096069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.642466545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1516361236572</t>
+    <t xml:space="preserve">11.6424655914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1516370773315</t>
   </si>
   <si>
     <t xml:space="preserve">11.1025543212891</t>
@@ -4493,10 +4493,10 @@
     <t xml:space="preserve">11.1712703704834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.269434928894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.284161567688</t>
+    <t xml:space="preserve">11.2694358825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2841606140137</t>
   </si>
   <si>
     <t xml:space="preserve">11.54430103302</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">11.1909027099609</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0092964172363</t>
+    <t xml:space="preserve">11.0092973709106</t>
   </si>
   <si>
     <t xml:space="preserve">10.842414855957</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">10.68044090271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7687902450562</t>
+    <t xml:space="preserve">10.7687911987305</t>
   </si>
   <si>
     <t xml:space="preserve">10.9602136611938</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">10.9454879760742</t>
   </si>
   <si>
-    <t xml:space="preserve">11.254711151123</t>
+    <t xml:space="preserve">11.2547121047974</t>
   </si>
   <si>
     <t xml:space="preserve">11.3087024688721</t>
@@ -4556,7 +4556,7 @@
     <t xml:space="preserve">10.7786064147949</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7393398284912</t>
+    <t xml:space="preserve">10.7393407821655</t>
   </si>
   <si>
     <t xml:space="preserve">10.7344331741333</t>
@@ -4565,13 +4565,13 @@
     <t xml:space="preserve">10.7246160507202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7589731216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.886589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8571395874023</t>
+    <t xml:space="preserve">10.7589740753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8865900039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8571405410767</t>
   </si>
   <si>
     <t xml:space="preserve">10.1208963394165</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">9.98346424102783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1945199966431</t>
+    <t xml:space="preserve">10.1945209503174</t>
   </si>
   <si>
     <t xml:space="preserve">10.2386951446533</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">10.48410987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871829986572</t>
+    <t xml:space="preserve">10.5871839523315</t>
   </si>
   <si>
     <t xml:space="preserve">10.5381002426147</t>
@@ -4601,22 +4601,22 @@
     <t xml:space="preserve">10.7295246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7000741958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3466768264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2877779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4055776596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3270444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0669040679932</t>
+    <t xml:space="preserve">10.7000732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3466777801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2877769470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4055767059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3270454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0669050216675</t>
   </si>
   <si>
     <t xml:space="preserve">10.086537361145</t>
@@ -4640,13 +4640,13 @@
     <t xml:space="preserve">9.75375556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83621501922607</t>
+    <t xml:space="preserve">9.83621597290039</t>
   </si>
   <si>
     <t xml:space="preserve">9.83130741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86075592041016</t>
+    <t xml:space="preserve">9.86075687408447</t>
   </si>
   <si>
     <t xml:space="preserve">9.90493106842041</t>
@@ -4670,7 +4670,7 @@
     <t xml:space="preserve">9.8263988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9147481918335</t>
+    <t xml:space="preserve">9.91474723815918</t>
   </si>
   <si>
     <t xml:space="preserve">9.96382999420166</t>
@@ -4688,19 +4688,19 @@
     <t xml:space="preserve">10.0276384353638</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8902063369751</t>
+    <t xml:space="preserve">9.89020538330078</t>
   </si>
   <si>
     <t xml:space="preserve">9.76357269287109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86566543579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76553535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74001216888428</t>
+    <t xml:space="preserve">9.8656644821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76553630828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74001312255859</t>
   </si>
   <si>
     <t xml:space="preserve">9.74393844604492</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">9.10782432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15494441986084</t>
+    <t xml:space="preserve">9.15494537353516</t>
   </si>
   <si>
     <t xml:space="preserve">9.14905452728271</t>
@@ -4718,7 +4718,7 @@
     <t xml:space="preserve">9.00769519805908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08033752441406</t>
+    <t xml:space="preserve">9.08033847808838</t>
   </si>
   <si>
     <t xml:space="preserve">9.06463146209717</t>
@@ -4739,19 +4739,19 @@
     <t xml:space="preserve">8.85455799102783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8152904510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29630279541016</t>
+    <t xml:space="preserve">8.81528949737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29630374908447</t>
   </si>
   <si>
     <t xml:space="preserve">9.22758674621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23740386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21580600738525</t>
+    <t xml:space="preserve">9.23740291595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21580696105957</t>
   </si>
   <si>
     <t xml:space="preserve">9.37090873718262</t>
@@ -4775,19 +4775,19 @@
     <t xml:space="preserve">9.61043357849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56527709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76749897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78909492492676</t>
+    <t xml:space="preserve">9.56527805328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76749801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78909587860107</t>
   </si>
   <si>
     <t xml:space="preserve">9.63988304138184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63791942596436</t>
+    <t xml:space="preserve">9.63792037963867</t>
   </si>
   <si>
     <t xml:space="preserve">9.6909294128418</t>
@@ -4799,16 +4799,16 @@
     <t xml:space="preserve">9.59080123901367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3807258605957</t>
+    <t xml:space="preserve">9.38072490692139</t>
   </si>
   <si>
     <t xml:space="preserve">9.65559005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32967948913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20009994506836</t>
+    <t xml:space="preserve">9.32967853546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20010089874268</t>
   </si>
   <si>
     <t xml:space="preserve">9.30023002624512</t>
@@ -4829,7 +4829,7 @@
     <t xml:space="preserve">9.36109256744385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40232276916504</t>
+    <t xml:space="preserve">9.40232181549072</t>
   </si>
   <si>
     <t xml:space="preserve">9.39054203033447</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">9.47300148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47103786468506</t>
+    <t xml:space="preserve">9.47103881835938</t>
   </si>
   <si>
     <t xml:space="preserve">9.37876224517822</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">9.27667045593262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08426475524902</t>
+    <t xml:space="preserve">9.08426380157471</t>
   </si>
   <si>
     <t xml:space="preserve">9.1254940032959</t>
@@ -4865,7 +4865,7 @@
     <t xml:space="preserve">9.06855869293213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14316368103027</t>
+    <t xml:space="preserve">9.14316463470459</t>
   </si>
   <si>
     <t xml:space="preserve">9.00573253631592</t>
@@ -4874,7 +4874,7 @@
     <t xml:space="preserve">8.89382362365723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02340316772461</t>
+    <t xml:space="preserve">9.02340221405029</t>
   </si>
   <si>
     <t xml:space="preserve">8.92523670196533</t>
@@ -4886,7 +4886,7 @@
     <t xml:space="preserve">8.92327308654785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88400650024414</t>
+    <t xml:space="preserve">8.88400745391846</t>
   </si>
   <si>
     <t xml:space="preserve">8.80743789672852</t>
@@ -4895,7 +4895,7 @@
     <t xml:space="preserve">8.73479461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7681713104248</t>
+    <t xml:space="preserve">8.76817035675049</t>
   </si>
   <si>
     <t xml:space="preserve">8.77995109558105</t>
@@ -4904,10 +4904,10 @@
     <t xml:space="preserve">8.9821720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21188068389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30219268798828</t>
+    <t xml:space="preserve">9.21187973022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3021936416626</t>
   </si>
   <si>
     <t xml:space="preserve">9.42377090454102</t>
@@ -5952,6 +5952,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.95800018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96999979019165</t>
   </si>
 </sst>
 </file>
@@ -71368,7 +71371,7 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6920833333</v>
+        <v>45965.3333333333</v>
       </c>
       <c r="B2504" t="n">
         <v>8544884</v>
@@ -71389,6 +71392,32 @@
         <v>1979</v>
       </c>
       <c r="H2504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2505">
+      <c r="A2505" s="1" t="n">
+        <v>45966.6910532407</v>
+      </c>
+      <c r="B2505" t="n">
+        <v>5572053</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>5.99399995803833</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>5.86199998855591</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>5.92199993133545</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>5.96999979019165</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>1980</v>
+      </c>
+      <c r="H2505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -38,73 +38,73 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59865665435791</t>
+    <t xml:space="preserve">3.59865617752075</t>
   </si>
   <si>
     <t xml:space="preserve">CPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65898275375366</t>
+    <t xml:space="preserve">3.65898251533508</t>
   </si>
   <si>
     <t xml:space="preserve">3.60329699516296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51976919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51048851013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54993224143982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62881946563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68450474739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57313394546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52672982215881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48264575004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56617403030396</t>
+    <t xml:space="preserve">3.51976871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51048874855042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5499324798584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62881970405579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68450498580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57313418388367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52673006057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4826455116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5661735534668</t>
   </si>
   <si>
     <t xml:space="preserve">3.43392109870911</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5058479309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56153297424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64274072647095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66594290733337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56849384307861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74251008033752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72162818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70770668983459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47104477882385</t>
+    <t xml:space="preserve">3.50584816932678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56153345108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64274096488953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66594314575195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56849408149719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7425103187561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72162866592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70770692825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47104501724243</t>
   </si>
   <si>
     <t xml:space="preserve">3.44320201873779</t>
@@ -116,28 +116,28 @@
     <t xml:space="preserve">3.33183145523071</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40839862823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22046160697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26918601989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32487106323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24366354942322</t>
+    <t xml:space="preserve">3.40839886665344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22046113014221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26918578147888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32487058639526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2436637878418</t>
   </si>
   <si>
     <t xml:space="preserve">3.32255077362061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28774762153625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31791019439697</t>
+    <t xml:space="preserve">3.2877471446991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31791043281555</t>
   </si>
   <si>
     <t xml:space="preserve">3.36663508415222</t>
@@ -146,25 +146,25 @@
     <t xml:space="preserve">3.36199450492859</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40607857704163</t>
+    <t xml:space="preserve">3.40607881546021</t>
   </si>
   <si>
     <t xml:space="preserve">3.3828763961792</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36431479454041</t>
+    <t xml:space="preserve">3.36431503295898</t>
   </si>
   <si>
     <t xml:space="preserve">3.53137040138245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6056170463562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61257839202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5638530254364</t>
+    <t xml:space="preserve">3.60561752319336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61257791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56385374069214</t>
   </si>
   <si>
     <t xml:space="preserve">3.61489796638489</t>
@@ -173,55 +173,55 @@
     <t xml:space="preserve">3.63810038566589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6891450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476205825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95596933364868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00701570510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04877853393555</t>
+    <t xml:space="preserve">3.68914484977722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476325035095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95596957206726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00701475143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04877805709839</t>
   </si>
   <si>
     <t xml:space="preserve">4.03485727310181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04181718826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03717756271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05109930038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01861572265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0928635597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07662057876587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03949737548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08358240127563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02325677871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00005388259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06037998199463</t>
+    <t xml:space="preserve">4.04181814193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03717803955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05109834671021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01861667633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09286308288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07662105560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03949785232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08358192443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02325582504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00005435943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06037950515747</t>
   </si>
   <si>
     <t xml:space="preserve">3.99541401863098</t>
@@ -230,106 +230,106 @@
     <t xml:space="preserve">3.94436883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97453165054321</t>
+    <t xml:space="preserve">3.97453141212463</t>
   </si>
   <si>
     <t xml:space="preserve">4.00237464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93740916252136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94668960571289</t>
+    <t xml:space="preserve">3.93740820884705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94668936729431</t>
   </si>
   <si>
     <t xml:space="preserve">4.03021717071533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05341958999634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00933456420898</t>
+    <t xml:space="preserve">4.05341911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00933504104614</t>
   </si>
   <si>
     <t xml:space="preserve">3.9582896232605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98613262176514</t>
+    <t xml:space="preserve">3.98613381385803</t>
   </si>
   <si>
     <t xml:space="preserve">4.0255765914917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96989226341248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91188645362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89796495437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87708210945129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91420650482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92812776565552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9513304233551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06733989715576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0812611579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99309325218201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9675714969635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9814920425415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96293044090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88868355751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89332461357117</t>
+    <t xml:space="preserve">3.96989130973816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91188549995422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89796423912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87708258628845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91420674324036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92812824249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95132923126221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06734085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08126068115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99309349060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96757125854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98149275779724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96293020248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88868427276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89332413673401</t>
   </si>
   <si>
     <t xml:space="preserve">3.79587531089783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89309906959534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02677726745605</t>
+    <t xml:space="preserve">3.89309883117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02677774429321</t>
   </si>
   <si>
     <t xml:space="preserve">4.08540868759155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07602834701538</t>
+    <t xml:space="preserve">4.07602739334106</t>
   </si>
   <si>
     <t xml:space="preserve">4.08306360244751</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09947967529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07368230819702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0900993347168</t>
+    <t xml:space="preserve">4.09948015213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07368278503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09009981155396</t>
   </si>
   <si>
     <t xml:space="preserve">4.10182523727417</t>
@@ -338,22 +338,22 @@
     <t xml:space="preserve">4.08775424957275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1135516166687</t>
+    <t xml:space="preserve">4.11355113983154</t>
   </si>
   <si>
     <t xml:space="preserve">4.08071851730347</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01974201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90482544898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85557532310486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85792064666748</t>
+    <t xml:space="preserve">4.01974248886108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90482497215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85557556152344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85792016983032</t>
   </si>
   <si>
     <t xml:space="preserve">3.86495590209961</t>
@@ -362,28 +362,28 @@
     <t xml:space="preserve">3.87199211120605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86964631080627</t>
+    <t xml:space="preserve">3.86964654922485</t>
   </si>
   <si>
     <t xml:space="preserve">4.00567007064819</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00801563262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95876526832581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05961084365845</t>
+    <t xml:space="preserve">4.00801467895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95876502990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05961036682129</t>
   </si>
   <si>
     <t xml:space="preserve">3.88606286048889</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88840794563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04084873199463</t>
+    <t xml:space="preserve">3.88840770721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04084920883179</t>
   </si>
   <si>
     <t xml:space="preserve">4.16514682769775</t>
@@ -392,40 +392,40 @@
     <t xml:space="preserve">4.15576601028442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14873123168945</t>
+    <t xml:space="preserve">4.14873075485229</t>
   </si>
   <si>
     <t xml:space="preserve">4.13231372833252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00332593917847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04319429397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16045665740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15811109542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11589670181274</t>
+    <t xml:space="preserve">4.00332498550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04319477081299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16045618057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15811157226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1158971786499</t>
   </si>
   <si>
     <t xml:space="preserve">4.06899213790894</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13465881347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14169454574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18390846252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16280174255371</t>
+    <t xml:space="preserve">4.13465738296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14169502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18390893936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16280126571655</t>
   </si>
   <si>
     <t xml:space="preserve">4.21908760070801</t>
@@ -434,34 +434,34 @@
     <t xml:space="preserve">4.29178953170776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29648017883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31055116653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28710031509399</t>
+    <t xml:space="preserve">4.29648065567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31055164337158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28709983825684</t>
   </si>
   <si>
     <t xml:space="preserve">4.33165884017944</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33869409561157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5403847694397</t>
+    <t xml:space="preserve">4.33869457244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54038524627686</t>
   </si>
   <si>
     <t xml:space="preserve">4.51458787918091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5216236114502</t>
+    <t xml:space="preserve">4.52162408828735</t>
   </si>
   <si>
     <t xml:space="preserve">4.43719482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47940921783447</t>
+    <t xml:space="preserve">4.47940874099731</t>
   </si>
   <si>
     <t xml:space="preserve">4.45595645904541</t>
@@ -470,82 +470,82 @@
     <t xml:space="preserve">4.66233777999878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67171812057495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58963584899902</t>
+    <t xml:space="preserve">4.67171859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58963537216187</t>
   </si>
   <si>
     <t xml:space="preserve">4.55914735794067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56383752822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54976558685303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60370683670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59667110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62012386322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59432554244995</t>
+    <t xml:space="preserve">4.5638370513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54976654052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60370588302612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59667062759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57321882247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62012338638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59432649612427</t>
   </si>
   <si>
     <t xml:space="preserve">4.65061187744141</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57556390762329</t>
+    <t xml:space="preserve">4.57556438446045</t>
   </si>
   <si>
     <t xml:space="preserve">4.7045521736145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67406463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7092432975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60136222839355</t>
+    <t xml:space="preserve">4.67406368255615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70924282073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6013617515564</t>
   </si>
   <si>
     <t xml:space="preserve">4.48644351959229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46533823013306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39967012405396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43250370025635</t>
+    <t xml:space="preserve">4.46533727645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39967060089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43250417709351</t>
   </si>
   <si>
     <t xml:space="preserve">4.50520610809326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49113512039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51693296432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50286197662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48878955841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65295648574829</t>
+    <t xml:space="preserve">4.491135597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51693344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50286149978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4887900352478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65295696258545</t>
   </si>
   <si>
     <t xml:space="preserve">4.66468286514282</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">4.73269462585449</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71393394470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69048070907593</t>
+    <t xml:space="preserve">4.71393299102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69048118591309</t>
   </si>
   <si>
     <t xml:space="preserve">4.58728981018066</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">4.47471904754639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44657468795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54742050170898</t>
+    <t xml:space="preserve">4.44657516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54742002487183</t>
   </si>
   <si>
     <t xml:space="preserve">4.44188547134399</t>
@@ -587,16 +587,16 @@
     <t xml:space="preserve">4.36683750152588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37152767181396</t>
+    <t xml:space="preserve">4.37152814865112</t>
   </si>
   <si>
     <t xml:space="preserve">4.33400392532349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3293137550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30586099624634</t>
+    <t xml:space="preserve">4.32931327819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3058614730835</t>
   </si>
   <si>
     <t xml:space="preserve">4.30351591110229</t>
@@ -605,49 +605,49 @@
     <t xml:space="preserve">4.25661134719849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20736169815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09478950500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24253940582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20267105102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95642137527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9540753364563</t>
+    <t xml:space="preserve">4.20736122131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09478902816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24254035949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20267057418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95642113685608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95407485961914</t>
   </si>
   <si>
     <t xml:space="preserve">4.0338134765625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12527799606323</t>
+    <t xml:space="preserve">4.12527656555176</t>
   </si>
   <si>
     <t xml:space="preserve">4.01739645004272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12996912002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1721830368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21205186843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18860006332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2495756149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20501565933228</t>
+    <t xml:space="preserve">4.12996864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17218208312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21205139160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18859958648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24957609176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20501613616943</t>
   </si>
   <si>
     <t xml:space="preserve">4.26833820343018</t>
@@ -656,55 +656,55 @@
     <t xml:space="preserve">4.22846841812134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.247230052948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31993293762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36449241638184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28944492340088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27771806716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30117034912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32227802276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35745668411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34807586669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34338617324829</t>
+    <t xml:space="preserve">4.24723052978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31993198394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449337005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28944444656372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27771854400635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30117082595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32227754592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35745620727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34807538986206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34338521957397</t>
   </si>
   <si>
     <t xml:space="preserve">4.39028978347778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36214733123779</t>
+    <t xml:space="preserve">4.36214780807495</t>
   </si>
   <si>
     <t xml:space="preserve">4.32462310791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39732599258423</t>
+    <t xml:space="preserve">4.39732503890991</t>
   </si>
   <si>
     <t xml:space="preserve">4.37387323379517</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36918210983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47002840042114</t>
+    <t xml:space="preserve">4.36918258666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47002744674683</t>
   </si>
   <si>
     <t xml:space="preserve">4.45830202102661</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">4.43484973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46768236160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40201663970947</t>
+    <t xml:space="preserve">4.46768283843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40201568603516</t>
   </si>
   <si>
     <t xml:space="preserve">4.3527660369873</t>
@@ -728,13 +728,13 @@
     <t xml:space="preserve">4.3855996131897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43953943252563</t>
+    <t xml:space="preserve">4.43953990936279</t>
   </si>
   <si>
     <t xml:space="preserve">4.4301586151123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49348020553589</t>
+    <t xml:space="preserve">4.49348068237305</t>
   </si>
   <si>
     <t xml:space="preserve">4.47237300872803</t>
@@ -746,64 +746,64 @@
     <t xml:space="preserve">4.54273128509521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53804016113281</t>
+    <t xml:space="preserve">4.53803968429565</t>
   </si>
   <si>
     <t xml:space="preserve">4.54507493972778</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58260059356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57790946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55211162567139</t>
+    <t xml:space="preserve">4.58259963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57790994644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55211210250854</t>
   </si>
   <si>
     <t xml:space="preserve">4.57087326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53569459915161</t>
+    <t xml:space="preserve">4.53569555282593</t>
   </si>
   <si>
     <t xml:space="preserve">4.50755167007446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58494424819946</t>
+    <t xml:space="preserve">4.58494472503662</t>
   </si>
   <si>
     <t xml:space="preserve">4.65530204772949</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74207639694214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7561469078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80774307250977</t>
+    <t xml:space="preserve">4.74207544326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75614786148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80774354934692</t>
   </si>
   <si>
     <t xml:space="preserve">4.83119535446167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89686250686646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94845724105835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09855222702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05164813995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12200546264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04695701599121</t>
+    <t xml:space="preserve">4.89686155319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94845676422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09855270385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0516471862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12200498580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04695749282837</t>
   </si>
   <si>
     <t xml:space="preserve">5.0563383102417</t>
@@ -818,19 +818,19 @@
     <t xml:space="preserve">5.02819538116455</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03288507461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93907594680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9766001701355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92500448226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96721887588501</t>
+    <t xml:space="preserve">5.03288555145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9390754699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97659969329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92500495910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96721982955933</t>
   </si>
   <si>
     <t xml:space="preserve">5.08917188644409</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">5.17360019683838</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14545726776123</t>
+    <t xml:space="preserve">5.14545679092407</t>
   </si>
   <si>
     <t xml:space="preserve">5.15952920913696</t>
@@ -851,28 +851,28 @@
     <t xml:space="preserve">5.16421890258789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25333833694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18767166137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41750478744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6707911491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60043382644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6238865852356</t>
+    <t xml:space="preserve">5.25333786010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18767213821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41750574111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67079067230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60043430328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62388706207275</t>
   </si>
   <si>
     <t xml:space="preserve">5.66140985488892</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68486166000366</t>
+    <t xml:space="preserve">5.68486213684082</t>
   </si>
   <si>
     <t xml:space="preserve">5.57698154449463</t>
@@ -881,22 +881,22 @@
     <t xml:space="preserve">5.60512399673462</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72238683700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69403409957886</t>
+    <t xml:space="preserve">5.7223858833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69403505325317</t>
   </si>
   <si>
     <t xml:space="preserve">5.74128770828247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76491451263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75073862075806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87832260131836</t>
+    <t xml:space="preserve">5.76491403579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7507381439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8783221244812</t>
   </si>
   <si>
     <t xml:space="preserve">5.86887216567993</t>
@@ -911,43 +911,43 @@
     <t xml:space="preserve">5.99173069000244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00118017196655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9350266456604</t>
+    <t xml:space="preserve">6.00118160247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93502616882324</t>
   </si>
   <si>
     <t xml:space="preserve">5.85942125320435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8027172088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75546360015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73183727264404</t>
+    <t xml:space="preserve">5.80271816253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75546407699585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73183679580688</t>
   </si>
   <si>
     <t xml:space="preserve">5.84997081756592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81216812133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95865297317505</t>
+    <t xml:space="preserve">5.81216859817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95865345001221</t>
   </si>
   <si>
     <t xml:space="preserve">5.93030166625977</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98228025436401</t>
+    <t xml:space="preserve">5.98227977752686</t>
   </si>
   <si>
     <t xml:space="preserve">5.90194940567017</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91612577438354</t>
+    <t xml:space="preserve">5.91612529754639</t>
   </si>
   <si>
     <t xml:space="preserve">5.91139984130859</t>
@@ -959,64 +959,64 @@
     <t xml:space="preserve">5.88777303695679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78381633758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80744171142578</t>
+    <t xml:space="preserve">5.78381538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80744218826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.84524536132812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77436494827271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82634449005127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82161808013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85469532012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79326677322388</t>
+    <t xml:space="preserve">5.77436542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82634401321411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82161855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85469627380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79326629638672</t>
   </si>
   <si>
     <t xml:space="preserve">5.8357949256897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95392799377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92557621002197</t>
+    <t xml:space="preserve">5.95392847061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92557573318481</t>
   </si>
   <si>
     <t xml:space="preserve">5.94447708129883</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77908992767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74601268768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71766090393066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.65150594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66095638275146</t>
+    <t xml:space="preserve">5.7790904045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74601221084595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71766138076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6515064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66095733642578</t>
   </si>
   <si>
     <t xml:space="preserve">5.79799175262451</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76018905639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69876003265381</t>
+    <t xml:space="preserve">5.76018857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69875907897949</t>
   </si>
   <si>
     <t xml:space="preserve">5.66568231582642</t>
@@ -1031,19 +1031,19 @@
     <t xml:space="preserve">5.76963996887207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89249897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97282934188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15239238739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1476674079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28470230102539</t>
+    <t xml:space="preserve">5.89249849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97282981872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15239286422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14766645431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28470277786255</t>
   </si>
   <si>
     <t xml:space="preserve">6.13821601867676</t>
@@ -1052,37 +1052,37 @@
     <t xml:space="preserve">6.1240406036377</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02953386306763</t>
+    <t xml:space="preserve">6.02953338623047</t>
   </si>
   <si>
     <t xml:space="preserve">6.10513925552368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16656827926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11458873748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31777906417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34140634536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40756130218506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50206708908081</t>
+    <t xml:space="preserve">6.16656875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11458921432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31777954101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34140539169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4075608253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50206756591797</t>
   </si>
   <si>
     <t xml:space="preserve">6.42173671722412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30832815170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.478440284729</t>
+    <t xml:space="preserve">6.30832862854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47844076156616</t>
   </si>
   <si>
     <t xml:space="preserve">6.31305360794067</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">6.33668041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37448358535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17601871490479</t>
+    <t xml:space="preserve">6.37448263168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17601919174194</t>
   </si>
   <si>
     <t xml:space="preserve">6.09096336364746</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">6.23272275924683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0389838218689</t>
+    <t xml:space="preserve">6.03898334503174</t>
   </si>
   <si>
     <t xml:space="preserve">6.08623743057251</t>
@@ -1118,22 +1118,22 @@
     <t xml:space="preserve">6.00590705871582</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0342583656311</t>
+    <t xml:space="preserve">6.03425884246826</t>
   </si>
   <si>
     <t xml:space="preserve">6.09568786621094</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06261110305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18074417114258</t>
+    <t xml:space="preserve">6.0626106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18074369430542</t>
   </si>
   <si>
     <t xml:space="preserve">6.08151149749756</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15711784362793</t>
+    <t xml:space="preserve">6.15711736679077</t>
   </si>
   <si>
     <t xml:space="preserve">6.21382141113281</t>
@@ -1145,7 +1145,7 @@
     <t xml:space="preserve">6.24689912796021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20909643173218</t>
+    <t xml:space="preserve">6.20909690856934</t>
   </si>
   <si>
     <t xml:space="preserve">6.22799730300903</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">6.12876558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07206201553345</t>
+    <t xml:space="preserve">6.07206153869629</t>
   </si>
   <si>
     <t xml:space="preserve">6.05788564682007</t>
@@ -1166,58 +1166,58 @@
     <t xml:space="preserve">6.13349056243896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14294195175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01063299179077</t>
+    <t xml:space="preserve">6.14294147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01063251495361</t>
   </si>
   <si>
     <t xml:space="preserve">5.94920253753662</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97755527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05316066741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99645614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06733655929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93975162506104</t>
+    <t xml:space="preserve">5.97755479812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05316019058228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99645566940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0673360824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93975210189819</t>
   </si>
   <si>
     <t xml:space="preserve">5.71293544769287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72711133956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92085027694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57590055465698</t>
+    <t xml:space="preserve">5.72711181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92084980010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5759015083313</t>
   </si>
   <si>
     <t xml:space="preserve">5.52864742279053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42941522598267</t>
+    <t xml:space="preserve">5.42941474914551</t>
   </si>
   <si>
     <t xml:space="preserve">5.50502061843872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61370420455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63732957839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04370975494385</t>
+    <t xml:space="preserve">5.61370372772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63733005523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04370927810669</t>
   </si>
   <si>
     <t xml:space="preserve">5.98700523376465</t>
@@ -1235,19 +1235,19 @@
     <t xml:space="preserve">5.87359714508057</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86414575576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90667390823364</t>
+    <t xml:space="preserve">5.86414623260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9066743850708</t>
   </si>
   <si>
     <t xml:space="preserve">5.96810388565063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01550769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02027034759521</t>
+    <t xml:space="preserve">6.01550722122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02027082443237</t>
   </si>
   <si>
     <t xml:space="preserve">5.99169301986694</t>
@@ -1256,16 +1256,16 @@
     <t xml:space="preserve">6.08218765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20602226257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18697118759155</t>
+    <t xml:space="preserve">6.20602178573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18697071075439</t>
   </si>
   <si>
     <t xml:space="preserve">6.08695030212402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07266187667847</t>
+    <t xml:space="preserve">6.07266139984131</t>
   </si>
   <si>
     <t xml:space="preserve">6.16315603256226</t>
@@ -1274,61 +1274,61 @@
     <t xml:space="preserve">6.27270269393921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25365161895752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13934183120728</t>
+    <t xml:space="preserve">6.2536506652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13934230804443</t>
   </si>
   <si>
     <t xml:space="preserve">6.2917537689209</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38701057434082</t>
+    <t xml:space="preserve">6.38701105117798</t>
   </si>
   <si>
     <t xml:space="preserve">6.52513456344604</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59657716751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69183540344238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69659900665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62039279937744</t>
+    <t xml:space="preserve">6.59657764434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6918363571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69659852981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62039232254028</t>
   </si>
   <si>
     <t xml:space="preserve">6.57276391983032</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50608253479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58228874206543</t>
+    <t xml:space="preserve">6.50608348846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58228921890259</t>
   </si>
   <si>
     <t xml:space="preserve">6.65373229980469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71088743209839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77280426025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82995843887329</t>
+    <t xml:space="preserve">6.71088695526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82519578933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77280378341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82995891571045</t>
   </si>
   <si>
     <t xml:space="preserve">7.0252366065979</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92521572113037</t>
+    <t xml:space="preserve">6.92521524429321</t>
   </si>
   <si>
     <t xml:space="preserve">6.92045259475708</t>
@@ -1337,10 +1337,10 @@
     <t xml:space="preserve">7.01094770431519</t>
   </si>
   <si>
-    <t xml:space="preserve">6.96808195114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91092681884766</t>
+    <t xml:space="preserve">6.9680814743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91092729568481</t>
   </si>
   <si>
     <t xml:space="preserve">7.01570987701416</t>
@@ -1349,70 +1349,70 @@
     <t xml:space="preserve">7.04905033111572</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09667921066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17764759063721</t>
+    <t xml:space="preserve">7.09667873382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17764806747437</t>
   </si>
   <si>
     <t xml:space="preserve">7.28243112564087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22051429748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23956537246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27766799926758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12525701522827</t>
+    <t xml:space="preserve">7.22051477432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2395658493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27766847610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12525653839111</t>
   </si>
   <si>
     <t xml:space="preserve">6.94903087615967</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86806201934814</t>
+    <t xml:space="preserve">6.86806154251099</t>
   </si>
   <si>
     <t xml:space="preserve">7.0014214515686</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00618457794189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0633397102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760820388794</t>
+    <t xml:space="preserve">7.00618505477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06333923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760725021362</t>
   </si>
   <si>
     <t xml:space="preserve">6.9918966293335</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0395245552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02047348022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07762861251831</t>
+    <t xml:space="preserve">7.03952503204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02047300338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07762813568115</t>
   </si>
   <si>
     <t xml:space="preserve">7.18717432022095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21098804473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4157919883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29671955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26338005065918</t>
+    <t xml:space="preserve">7.21098899841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41579246520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29672002792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26338052749634</t>
   </si>
   <si>
     <t xml:space="preserve">7.24432849884033</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">7.30624580383301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18241119384766</t>
+    <t xml:space="preserve">7.1824107170105</t>
   </si>
   <si>
     <t xml:space="preserve">7.25385427474976</t>
@@ -1436,31 +1436,31 @@
     <t xml:space="preserve">7.10620498657227</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14907026290894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1681227684021</t>
+    <t xml:space="preserve">7.14907073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16812229156494</t>
   </si>
   <si>
     <t xml:space="preserve">6.90140199661255</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94426774978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06810283660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98713350296021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1300196647644</t>
+    <t xml:space="preserve">6.94426727294922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06810188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98713254928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13001918792725</t>
   </si>
   <si>
     <t xml:space="preserve">6.87758684158325</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7061243057251</t>
+    <t xml:space="preserve">6.70612382888794</t>
   </si>
   <si>
     <t xml:space="preserve">6.63944339752197</t>
@@ -1469,31 +1469,31 @@
     <t xml:space="preserve">6.65849494934082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32985734939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19649744033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11552762985229</t>
+    <t xml:space="preserve">6.32985687255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19649648666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11552667617798</t>
   </si>
   <si>
     <t xml:space="preserve">6.04884719848633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21554803848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3155689239502</t>
+    <t xml:space="preserve">6.21554851531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31556844711304</t>
   </si>
   <si>
     <t xml:space="preserve">6.33462047576904</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34414577484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12505340576172</t>
+    <t xml:space="preserve">6.34414529800415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12505388259888</t>
   </si>
   <si>
     <t xml:space="preserve">6.15363121032715</t>
@@ -1502,22 +1502,22 @@
     <t xml:space="preserve">6.30604267120361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35367107391357</t>
+    <t xml:space="preserve">6.35367059707642</t>
   </si>
   <si>
     <t xml:space="preserve">6.47274351119995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46798038482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42987728118896</t>
+    <t xml:space="preserve">6.4679799079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42987775802612</t>
   </si>
   <si>
     <t xml:space="preserve">6.52989816665649</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76804113388062</t>
+    <t xml:space="preserve">6.76804161071777</t>
   </si>
   <si>
     <t xml:space="preserve">7.08239078521729</t>
@@ -1526,13 +1526,13 @@
     <t xml:space="preserve">7.11096858978271</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12049388885498</t>
+    <t xml:space="preserve">7.12049341201782</t>
   </si>
   <si>
     <t xml:space="preserve">7.32529783248901</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31577157974243</t>
+    <t xml:space="preserve">7.31577110290527</t>
   </si>
   <si>
     <t xml:space="preserve">7.11573076248169</t>
@@ -1544,22 +1544,22 @@
     <t xml:space="preserve">7.15383434295654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04428815841675</t>
+    <t xml:space="preserve">7.04428720474243</t>
   </si>
   <si>
     <t xml:space="preserve">7.02999925613403</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17288589477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36339998245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14430856704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20622634887695</t>
+    <t xml:space="preserve">7.17288541793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36340045928955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14430904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20622587203979</t>
   </si>
   <si>
     <t xml:space="preserve">7.32053470611572</t>
@@ -1571,22 +1571,22 @@
     <t xml:space="preserve">6.98237037658691</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44913196563721</t>
+    <t xml:space="preserve">7.44913244247437</t>
   </si>
   <si>
     <t xml:space="preserve">7.3824520111084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33006000518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21575164794922</t>
+    <t xml:space="preserve">7.33006048202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21575117111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.33958578109741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35387468338013</t>
+    <t xml:space="preserve">7.35387516021729</t>
   </si>
   <si>
     <t xml:space="preserve">7.55391454696655</t>
@@ -1598,10 +1598,10 @@
     <t xml:space="preserve">7.46342039108276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49199771881104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44436979293823</t>
+    <t xml:space="preserve">7.49199724197388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44436931610107</t>
   </si>
   <si>
     <t xml:space="preserve">7.42055416107178</t>
@@ -1613,43 +1613,43 @@
     <t xml:space="preserve">7.53010129928589</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47294616699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48723554611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4681830406189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49676036834717</t>
+    <t xml:space="preserve">7.47294664382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48723459243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46818351745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49676084518433</t>
   </si>
   <si>
     <t xml:space="preserve">7.51581192016602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61106967926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56344127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6444091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73490381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80634641647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86826372146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85873889923096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88731670379639</t>
+    <t xml:space="preserve">7.6110692024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56344223022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64440965652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73490333557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80634689331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86826467514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85873985290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88731622695923</t>
   </si>
   <si>
     <t xml:space="preserve">7.92541933059692</t>
@@ -1664,19 +1664,19 @@
     <t xml:space="preserve">7.98733568191528</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01114940643311</t>
+    <t xml:space="preserve">8.01115131378174</t>
   </si>
   <si>
     <t xml:space="preserve">8.06354331970215</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53486347198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52057552337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54438924789429</t>
+    <t xml:space="preserve">7.53486394882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52057504653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54438972473145</t>
   </si>
   <si>
     <t xml:space="preserve">7.62059545516968</t>
@@ -1688,13 +1688,13 @@
     <t xml:space="preserve">7.77777099609375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76824426651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90636873245239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03496646881104</t>
+    <t xml:space="preserve">7.76824378967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90636730194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03496551513672</t>
   </si>
   <si>
     <t xml:space="preserve">8.00638771057129</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">8.20166492462158</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32549953460693</t>
+    <t xml:space="preserve">8.32550048828125</t>
   </si>
   <si>
     <t xml:space="preserve">8.44457149505615</t>
@@ -1721,151 +1721,151 @@
     <t xml:space="preserve">8.38265419006348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33502769470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27787208557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23500537872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25882053375244</t>
+    <t xml:space="preserve">8.33502674102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27787113189697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23500442504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25881958007812</t>
   </si>
   <si>
     <t xml:space="preserve">8.26358318328857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16832637786865</t>
+    <t xml:space="preserve">8.16832542419434</t>
   </si>
   <si>
     <t xml:space="preserve">8.31121158599854</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36836624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35407829284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37789249420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28739643096924</t>
+    <t xml:space="preserve">8.36836528778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35407733917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37789154052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28739738464355</t>
   </si>
   <si>
     <t xml:space="preserve">8.21119213104248</t>
   </si>
   <si>
+    <t xml:space="preserve">8.22071743011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43150424957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44587516784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56085300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5129451751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48899173736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60875797271729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44108772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49857330322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4842004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67103576660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81475639343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74289608001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83391761779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77643013000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7093620300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6854076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70457077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78122138977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80996322631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77163887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65187358856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53689765930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37880706787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37401676177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40755081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4123420715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32611083984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45545673370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41713237762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39318084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54648017883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58959579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27341365814209</t>
+  </si>
+  <si>
     <t xml:space="preserve">8.22071647644043</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43150520324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.445876121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56085300445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51294422149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48899269104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60875701904297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.441086769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49857425689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4842004776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6710376739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8147554397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74289512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83391761779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77643013000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70936107635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68540668487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70457077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78122043609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80996322631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77163887023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65187454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53689765930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37880802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37401676177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40755176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41234302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32611083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45545768737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41713237762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39318180084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54648017883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58959579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27341461181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22071743011475</t>
-  </si>
-  <si>
     <t xml:space="preserve">8.25425148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35485458374023</t>
+    <t xml:space="preserve">8.35485553741455</t>
   </si>
   <si>
     <t xml:space="preserve">8.47462177276611</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">8.42192363739014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36922740936279</t>
+    <t xml:space="preserve">8.36922645568848</t>
   </si>
   <si>
     <t xml:space="preserve">8.31653022766113</t>
@@ -1889,28 +1889,28 @@
     <t xml:space="preserve">8.17760181427002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2015552520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16322994232178</t>
+    <t xml:space="preserve">8.20155620574951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16323089599609</t>
   </si>
   <si>
     <t xml:space="preserve">8.24946022033691</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18239116668701</t>
+    <t xml:space="preserve">8.18239212036133</t>
   </si>
   <si>
     <t xml:space="preserve">8.17281055450439</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09616088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14885997772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06741809844971</t>
+    <t xml:space="preserve">8.09616184234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14885807037354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06741714477539</t>
   </si>
   <si>
     <t xml:space="preserve">8.03867435455322</t>
@@ -1919,16 +1919,16 @@
     <t xml:space="preserve">7.97160530090332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78956031799316</t>
+    <t xml:space="preserve">7.78956127166748</t>
   </si>
   <si>
     <t xml:space="preserve">7.62188911437988</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61709833145142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66021299362183</t>
+    <t xml:space="preserve">7.61709785461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66021347045898</t>
   </si>
   <si>
     <t xml:space="preserve">7.50212335586548</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">7.5931453704834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45900726318359</t>
+    <t xml:space="preserve">7.45900821685791</t>
   </si>
   <si>
     <t xml:space="preserve">7.51170444488525</t>
@@ -1952,10 +1952,10 @@
     <t xml:space="preserve">7.59793567657471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90932703018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95244264602661</t>
+    <t xml:space="preserve">7.90932655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95244216918945</t>
   </si>
   <si>
     <t xml:space="preserve">7.82309579849243</t>
@@ -1964,70 +1964,70 @@
     <t xml:space="preserve">7.88058280944824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10574340820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2063455581665</t>
+    <t xml:space="preserve">8.10574150085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20634460449219</t>
   </si>
   <si>
     <t xml:space="preserve">8.16802024841309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26383304595947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3452730178833</t>
+    <t xml:space="preserve">8.26383209228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34527397155762</t>
   </si>
   <si>
     <t xml:space="preserve">8.29257583618164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12011337280273</t>
+    <t xml:space="preserve">8.12011432647705</t>
   </si>
   <si>
     <t xml:space="preserve">8.03388214111328</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99555778503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80872297286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91411685943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88537359237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8278865814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84704828262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00034809112549</t>
+    <t xml:space="preserve">7.9955587387085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80872392654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91411733627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88537311553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82788610458374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84704780578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0003490447998</t>
   </si>
   <si>
     <t xml:space="preserve">7.89974451065063</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90453577041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94286108016968</t>
+    <t xml:space="preserve">7.90453624725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94286060333252</t>
   </si>
   <si>
     <t xml:space="preserve">7.71770191192627</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85662937164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04346561431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11532306671143</t>
+    <t xml:space="preserve">7.85662984848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04346466064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11532402038574</t>
   </si>
   <si>
     <t xml:space="preserve">8.12969493865967</t>
@@ -2039,100 +2039,100 @@
     <t xml:space="preserve">8.00992870330811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9332799911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7512354850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.578773021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64105081558228</t>
+    <t xml:space="preserve">7.93327951431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75123596191406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57877349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64105129241943</t>
   </si>
   <si>
     <t xml:space="preserve">7.69374752044678</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83746767044067</t>
+    <t xml:space="preserve">7.83746814727783</t>
   </si>
   <si>
     <t xml:space="preserve">7.81351327896118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87100172042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87579250335693</t>
+    <t xml:space="preserve">7.87100124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87579345703125</t>
   </si>
   <si>
     <t xml:space="preserve">7.92369890213013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89495372772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8518385887146</t>
+    <t xml:space="preserve">7.89495420455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85183906555176</t>
   </si>
   <si>
     <t xml:space="preserve">7.86621141433716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98597764968872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9668140411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92848873138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11053276062012</t>
+    <t xml:space="preserve">7.9859766960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96681308746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92848920822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11053371429443</t>
   </si>
   <si>
     <t xml:space="preserve">8.04825496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93806982040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77997922897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81830358505249</t>
+    <t xml:space="preserve">7.93807029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77997875213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81830453872681</t>
   </si>
   <si>
     <t xml:space="preserve">7.84225797653198</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79435157775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79914283752441</t>
+    <t xml:space="preserve">7.79435205459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79914236068726</t>
   </si>
   <si>
     <t xml:space="preserve">7.94765138626099</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91890811920166</t>
+    <t xml:space="preserve">7.9189076423645</t>
   </si>
   <si>
     <t xml:space="preserve">7.71291160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77518892288208</t>
+    <t xml:space="preserve">7.77518796920776</t>
   </si>
   <si>
     <t xml:space="preserve">7.86141920089722</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07699775695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21592712402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26862335205078</t>
+    <t xml:space="preserve">8.07699966430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21592617034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2686243057251</t>
   </si>
   <si>
     <t xml:space="preserve">8.33569240570068</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">8.36443519592285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47941207885742</t>
+    <t xml:space="preserve">8.47941112518311</t>
   </si>
   <si>
     <t xml:space="preserve">8.55127143859863</t>
@@ -2153,13 +2153,13 @@
     <t xml:space="preserve">8.59438610076904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66624546051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64229202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6901969909668</t>
+    <t xml:space="preserve">8.66624736785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64229297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69019794464111</t>
   </si>
   <si>
     <t xml:space="preserve">8.58480548858643</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">7.74165487289429</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70332908630371</t>
+    <t xml:space="preserve">7.70332956314087</t>
   </si>
   <si>
     <t xml:space="preserve">7.78477001190186</t>
@@ -2180,19 +2180,19 @@
     <t xml:space="preserve">7.44463634490967</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22426700592041</t>
+    <t xml:space="preserve">7.22426652908325</t>
   </si>
   <si>
     <t xml:space="preserve">7.1763596534729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30091714859009</t>
+    <t xml:space="preserve">7.30091667175293</t>
   </si>
   <si>
     <t xml:space="preserve">7.36319494247437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33924198150635</t>
+    <t xml:space="preserve">7.33924245834351</t>
   </si>
   <si>
     <t xml:space="preserve">7.09491968154907</t>
@@ -2201,25 +2201,25 @@
     <t xml:space="preserve">6.6972975730896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36195278167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33675909042358</t>
+    <t xml:space="preserve">6.3619532585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33675861358643</t>
   </si>
   <si>
     <t xml:space="preserve">5.54754686355591</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37987518310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30322456359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86851930618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45776557922363</t>
+    <t xml:space="preserve">5.37987470626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30322408676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8685188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45776605606079</t>
   </si>
   <si>
     <t xml:space="preserve">6.08409643173218</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">6.03619146347046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29967594146729</t>
+    <t xml:space="preserve">6.29967498779297</t>
   </si>
   <si>
     <t xml:space="preserve">6.76915693283081</t>
@@ -2237,25 +2237,25 @@
     <t xml:space="preserve">6.84101629257202</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53441619873047</t>
+    <t xml:space="preserve">6.53441667556763</t>
   </si>
   <si>
     <t xml:space="preserve">6.3715353012085</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27572298049927</t>
+    <t xml:space="preserve">6.27572250366211</t>
   </si>
   <si>
     <t xml:space="preserve">6.02852630615234</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11092472076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85606336593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45201730728149</t>
+    <t xml:space="preserve">6.11092519760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85606288909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45201778411865</t>
   </si>
   <si>
     <t xml:space="preserve">6.38111639022827</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">6.32171297073364</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35237312316895</t>
+    <t xml:space="preserve">6.35237264633179</t>
   </si>
   <si>
     <t xml:space="preserve">6.40986013412476</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">6.49962043762207</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44746923446655</t>
+    <t xml:space="preserve">6.44746971130371</t>
   </si>
   <si>
     <t xml:space="preserve">6.43008518218994</t>
   </si>
   <si>
-    <t xml:space="preserve">6.393385887146</t>
+    <t xml:space="preserve">6.39338636398315</t>
   </si>
   <si>
     <t xml:space="preserve">6.44360589981079</t>
@@ -2303,13 +2303,13 @@
     <t xml:space="preserve">6.79321384429932</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82798194885254</t>
+    <t xml:space="preserve">6.8279824256897</t>
   </si>
   <si>
     <t xml:space="preserve">6.62323951721191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.690842628479</t>
+    <t xml:space="preserve">6.69084310531616</t>
   </si>
   <si>
     <t xml:space="preserve">6.76617240905762</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">6.93807983398438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70629549026489</t>
+    <t xml:space="preserve">6.70629501342773</t>
   </si>
   <si>
     <t xml:space="preserve">6.66766452789307</t>
@@ -2357,7 +2357,7 @@
     <t xml:space="preserve">6.72947359085083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71209001541138</t>
+    <t xml:space="preserve">6.71208953857422</t>
   </si>
   <si>
     <t xml:space="preserve">7.1466851234436</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">7.142822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14475393295288</t>
+    <t xml:space="preserve">7.14475345611572</t>
   </si>
   <si>
     <t xml:space="preserve">7.13895988464355</t>
@@ -2387,13 +2387,13 @@
     <t xml:space="preserve">7.17758989334106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05976629257202</t>
+    <t xml:space="preserve">7.05976676940918</t>
   </si>
   <si>
     <t xml:space="preserve">7.20463132858276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06942415237427</t>
+    <t xml:space="preserve">7.06942367553711</t>
   </si>
   <si>
     <t xml:space="preserve">7.31279802322388</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">7.44027853012085</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58128070831299</t>
+    <t xml:space="preserve">7.58128118515015</t>
   </si>
   <si>
     <t xml:space="preserve">7.27223587036133</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">7.26837253570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24326229095459</t>
+    <t xml:space="preserve">7.24326276779175</t>
   </si>
   <si>
     <t xml:space="preserve">7.34370279312134</t>
@@ -2432,10 +2432,10 @@
     <t xml:space="preserve">7.45379972457886</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62667226791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67013168334961</t>
+    <t xml:space="preserve">7.62667179107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67013120651245</t>
   </si>
   <si>
     <t xml:space="preserve">7.70683097839355</t>
@@ -2444,7 +2444,7 @@
     <t xml:space="preserve">7.84203863143921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86425161361694</t>
+    <t xml:space="preserve">7.86425113677979</t>
   </si>
   <si>
     <t xml:space="preserve">7.81499767303467</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">7.75029039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92412757873535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91350555419922</t>
+    <t xml:space="preserve">7.92412805557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91350507736206</t>
   </si>
   <si>
     <t xml:space="preserve">7.82851791381836</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">7.98497247695923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87294435501099</t>
+    <t xml:space="preserve">7.87294387817383</t>
   </si>
   <si>
     <t xml:space="preserve">8.0265007019043</t>
@@ -2495,13 +2495,13 @@
     <t xml:space="preserve">8.28146362304688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23221015930176</t>
+    <t xml:space="preserve">8.23220920562744</t>
   </si>
   <si>
     <t xml:space="preserve">8.29594993591309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13659858703613</t>
+    <t xml:space="preserve">8.13659763336182</t>
   </si>
   <si>
     <t xml:space="preserve">8.2080659866333</t>
@@ -2516,10 +2516,10 @@
     <t xml:space="preserve">8.43598651885986</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39735507965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27760028839111</t>
+    <t xml:space="preserve">8.3973560333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2775993347168</t>
   </si>
   <si>
     <t xml:space="preserve">8.30753993988037</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">8.24283313751221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34423828125</t>
+    <t xml:space="preserve">8.34423923492432</t>
   </si>
   <si>
     <t xml:space="preserve">8.22834587097168</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">8.39059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34327220916748</t>
+    <t xml:space="preserve">8.3432731628418</t>
   </si>
   <si>
     <t xml:space="preserve">8.43405342102051</t>
@@ -2567,10 +2567,10 @@
     <t xml:space="preserve">8.71799182891846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65907859802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75565528869629</t>
+    <t xml:space="preserve">8.65907955169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75565624237061</t>
   </si>
   <si>
     <t xml:space="preserve">8.71412754058838</t>
@@ -2609,7 +2609,7 @@
     <t xml:space="preserve">9.08884525299072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0115852355957</t>
+    <t xml:space="preserve">9.01158428192139</t>
   </si>
   <si>
     <t xml:space="preserve">8.99999523162842</t>
@@ -2618,13 +2618,13 @@
     <t xml:space="preserve">9.04828357696533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04635238647461</t>
+    <t xml:space="preserve">9.04635143280029</t>
   </si>
   <si>
     <t xml:space="preserve">9.02896881103516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95460414886475</t>
+    <t xml:space="preserve">8.95460510253906</t>
   </si>
   <si>
     <t xml:space="preserve">8.99613094329834</t>
@@ -2639,7 +2639,7 @@
     <t xml:space="preserve">9.21342945098877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23854064941406</t>
+    <t xml:space="preserve">9.23853969573975</t>
   </si>
   <si>
     <t xml:space="preserve">9.1747989654541</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">9.07629013061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80008125305176</t>
+    <t xml:space="preserve">8.80008220672607</t>
   </si>
   <si>
     <t xml:space="preserve">8.93528842926025</t>
@@ -2666,7 +2666,7 @@
     <t xml:space="preserve">8.94687747955322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74020481109619</t>
+    <t xml:space="preserve">8.74020385742188</t>
   </si>
   <si>
     <t xml:space="preserve">8.88893222808838</t>
@@ -2675,16 +2675,16 @@
     <t xml:space="preserve">8.66294193267822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50262451171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65714645385742</t>
+    <t xml:space="preserve">8.50262355804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65714740753174</t>
   </si>
   <si>
     <t xml:space="preserve">8.51034927368164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59727001190186</t>
+    <t xml:space="preserve">8.59727096557617</t>
   </si>
   <si>
     <t xml:space="preserve">8.76724529266357</t>
@@ -2708,13 +2708,13 @@
     <t xml:space="preserve">9.35443115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29841709136963</t>
+    <t xml:space="preserve">9.29841804504395</t>
   </si>
   <si>
     <t xml:space="preserve">9.44328308105469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43169403076172</t>
+    <t xml:space="preserve">9.4316930770874</t>
   </si>
   <si>
     <t xml:space="preserve">9.25012874603271</t>
@@ -2726,10 +2726,10 @@
     <t xml:space="preserve">9.22501850128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06856536865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19411563873291</t>
+    <t xml:space="preserve">9.06856632232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19411468505859</t>
   </si>
   <si>
     <t xml:space="preserve">9.17286777496338</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">9.15934753417969</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12264823913574</t>
+    <t xml:space="preserve">9.12264919281006</t>
   </si>
   <si>
     <t xml:space="preserve">9.0048246383667</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">9.05890655517578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04538631439209</t>
+    <t xml:space="preserve">9.04538536071777</t>
   </si>
   <si>
     <t xml:space="preserve">8.8367805480957</t>
@@ -2777,13 +2777,13 @@
     <t xml:space="preserve">8.95267295837402</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93914985656738</t>
+    <t xml:space="preserve">8.9391508102417</t>
   </si>
   <si>
     <t xml:space="preserve">8.86961650848389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88120651245117</t>
+    <t xml:space="preserve">8.88120555877686</t>
   </si>
   <si>
     <t xml:space="preserve">8.96619319915771</t>
@@ -2816,16 +2816,16 @@
     <t xml:space="preserve">8.38093948364258</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47365188598633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42343044281006</t>
+    <t xml:space="preserve">8.47365283966064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42343139648438</t>
   </si>
   <si>
     <t xml:space="preserve">8.4253625869751</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54705047607422</t>
+    <t xml:space="preserve">8.5470495223999</t>
   </si>
   <si>
     <t xml:space="preserve">8.49296569824219</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">8.58568096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.512282371521</t>
+    <t xml:space="preserve">8.51228141784668</t>
   </si>
   <si>
     <t xml:space="preserve">8.5064868927002</t>
@@ -2849,13 +2849,13 @@
     <t xml:space="preserve">8.65328502655029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57215881347656</t>
+    <t xml:space="preserve">8.57215976715088</t>
   </si>
   <si>
     <t xml:space="preserve">8.57795429229736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82712364196777</t>
+    <t xml:space="preserve">8.82712268829346</t>
   </si>
   <si>
     <t xml:space="preserve">8.86768436431885</t>
@@ -2864,7 +2864,7 @@
     <t xml:space="preserve">8.94108295440674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33704853057861</t>
+    <t xml:space="preserve">9.3370475769043</t>
   </si>
   <si>
     <t xml:space="preserve">9.31773281097412</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">9.40272045135498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34477424621582</t>
+    <t xml:space="preserve">9.34477519989014</t>
   </si>
   <si>
     <t xml:space="preserve">9.38533592224121</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">9.44521331787109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58235263824463</t>
+    <t xml:space="preserve">9.58235359191895</t>
   </si>
   <si>
     <t xml:space="preserve">9.42976093292236</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">9.3158016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34091091156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05697536468506</t>
+    <t xml:space="preserve">9.34091186523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05697441101074</t>
   </si>
   <si>
     <t xml:space="preserve">9.19218254089355</t>
@@ -2927,7 +2927,7 @@
     <t xml:space="preserve">9.36795234680176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52440738677979</t>
+    <t xml:space="preserve">9.5244083404541</t>
   </si>
   <si>
     <t xml:space="preserve">9.76391792297363</t>
@@ -2936,7 +2936,7 @@
     <t xml:space="preserve">9.48963832855225</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46839332580566</t>
+    <t xml:space="preserve">9.46839237213135</t>
   </si>
   <si>
     <t xml:space="preserve">9.38726806640625</t>
@@ -2948,7 +2948,7 @@
     <t xml:space="preserve">9.36408996582031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28296661376953</t>
+    <t xml:space="preserve">9.28296566009521</t>
   </si>
   <si>
     <t xml:space="preserve">9.25978755950928</t>
@@ -2957,19 +2957,19 @@
     <t xml:space="preserve">9.24240207672119</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26364898681641</t>
+    <t xml:space="preserve">9.26364994049072</t>
   </si>
   <si>
     <t xml:space="preserve">9.28682804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3505687713623</t>
+    <t xml:space="preserve">9.35056972503662</t>
   </si>
   <si>
     <t xml:space="preserve">9.23081398010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39885711669922</t>
+    <t xml:space="preserve">9.39885807037354</t>
   </si>
   <si>
     <t xml:space="preserve">9.32932090759277</t>
@@ -2987,7 +2987,7 @@
     <t xml:space="preserve">9.47225379943848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56497001647949</t>
+    <t xml:space="preserve">9.56496906280518</t>
   </si>
   <si>
     <t xml:space="preserve">9.64416313171387</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">9.83255958557129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70340156555176</t>
+    <t xml:space="preserve">9.70340061187744</t>
   </si>
   <si>
     <t xml:space="preserve">9.62959575653076</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">9.60823154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52860069274902</t>
+    <t xml:space="preserve">9.52859973907471</t>
   </si>
   <si>
     <t xml:space="preserve">9.63348007202148</t>
@@ -3032,7 +3032,7 @@
     <t xml:space="preserve">9.98308181762695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94423770904541</t>
+    <t xml:space="preserve">9.94423675537109</t>
   </si>
   <si>
     <t xml:space="preserve">9.7742919921875</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">10.1675939559937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2355718612671</t>
+    <t xml:space="preserve">10.2355728149414</t>
   </si>
   <si>
     <t xml:space="preserve">10.254994392395</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">10.1870174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1481714248657</t>
+    <t xml:space="preserve">10.14817237854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2307176589966</t>
@@ -3080,34 +3080,34 @@
     <t xml:space="preserve">10.2792730331421</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2744169235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3132629394531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3909511566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5754642486572</t>
+    <t xml:space="preserve">10.2744178771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3132619857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3909502029419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5754632949829</t>
   </si>
   <si>
     <t xml:space="preserve">10.6337299346924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8133878707886</t>
+    <t xml:space="preserve">10.8133869171143</t>
   </si>
   <si>
     <t xml:space="preserve">10.8182420730591</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8328084945679</t>
+    <t xml:space="preserve">10.8328094482422</t>
   </si>
   <si>
     <t xml:space="preserve">10.8230991363525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8570880889893</t>
+    <t xml:space="preserve">10.8570871353149</t>
   </si>
   <si>
     <t xml:space="preserve">10.7551202774048</t>
@@ -3116,13 +3116,13 @@
     <t xml:space="preserve">10.7454080581665</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7842531204224</t>
+    <t xml:space="preserve">10.7842540740967</t>
   </si>
   <si>
     <t xml:space="preserve">11.0852994918823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0755891799927</t>
+    <t xml:space="preserve">11.0755882263184</t>
   </si>
   <si>
     <t xml:space="preserve">11.0610218048096</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">11.0464553833008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9687652587891</t>
+    <t xml:space="preserve">10.9687662124634</t>
   </si>
   <si>
     <t xml:space="preserve">11.0027551651001</t>
@@ -3140,13 +3140,13 @@
     <t xml:space="preserve">10.9104986190796</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8910779953003</t>
+    <t xml:space="preserve">10.891077041626</t>
   </si>
   <si>
     <t xml:space="preserve">10.997899055481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.827953338623</t>
+    <t xml:space="preserve">10.8279542922974</t>
   </si>
   <si>
     <t xml:space="preserve">10.9541988372803</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">10.6531534194946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7162761688232</t>
+    <t xml:space="preserve">10.7162752151489</t>
   </si>
   <si>
     <t xml:space="preserve">10.9930429458618</t>
@@ -3173,10 +3173,10 @@
     <t xml:space="preserve">11.0513105392456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4009122848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4688920974731</t>
+    <t xml:space="preserve">11.4009132385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4688911437988</t>
   </si>
   <si>
     <t xml:space="preserve">11.4931688308716</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">11.5028800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6048469543457</t>
+    <t xml:space="preserve">11.6048460006714</t>
   </si>
   <si>
     <t xml:space="preserve">11.5805702209473</t>
@@ -3212,13 +3212,13 @@
     <t xml:space="preserve">11.8621940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">11.745659828186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6922483444214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6825361251831</t>
+    <t xml:space="preserve">11.7456588745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6922473907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6825370788574</t>
   </si>
   <si>
     <t xml:space="preserve">11.3620681762695</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">11.5902805328369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6971035003662</t>
+    <t xml:space="preserve">11.6971025466919</t>
   </si>
   <si>
     <t xml:space="preserve">11.570858001709</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">11.5757141113281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5125913619995</t>
+    <t xml:space="preserve">11.5125904083252</t>
   </si>
   <si>
     <t xml:space="preserve">11.410623550415</t>
@@ -3272,106 +3272,106 @@
     <t xml:space="preserve">11.949595451355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9301719665527</t>
+    <t xml:space="preserve">11.9301710128784</t>
   </si>
   <si>
     <t xml:space="preserve">11.7942161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7602252960205</t>
+    <t xml:space="preserve">11.7602262496948</t>
   </si>
   <si>
     <t xml:space="preserve">11.8087816238403</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8282051086426</t>
+    <t xml:space="preserve">11.8282041549683</t>
   </si>
   <si>
     <t xml:space="preserve">11.7505159378052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9253158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0175724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0564165115356</t>
+    <t xml:space="preserve">11.9253149032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0175714492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0564155578613</t>
   </si>
   <si>
     <t xml:space="preserve">12.0369958877563</t>
   </si>
   <si>
-    <t xml:space="preserve">12.187518119812</t>
+    <t xml:space="preserve">12.1875171661377</t>
   </si>
   <si>
     <t xml:space="preserve">12.1486730575562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3865966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5565433502197</t>
+    <t xml:space="preserve">12.3865957260132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5565423965454</t>
   </si>
   <si>
     <t xml:space="preserve">12.425440788269</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5274085998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5322637557983</t>
+    <t xml:space="preserve">12.5274076461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5322647094727</t>
   </si>
   <si>
     <t xml:space="preserve">12.5662517547607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9350261688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.012716293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0758390426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1729507446289</t>
+    <t xml:space="preserve">11.9350271224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0127153396606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0758399963379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1729516983032</t>
   </si>
   <si>
     <t xml:space="preserve">12.3331842422485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3137626647949</t>
+    <t xml:space="preserve">12.3137636184692</t>
   </si>
   <si>
     <t xml:space="preserve">12.4205856323242</t>
   </si>
   <si>
-    <t xml:space="preserve">12.304051399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4108734130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4448623657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4157304763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5468320846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6439437866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7750434875488</t>
+    <t xml:space="preserve">12.3040523529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4108743667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.444863319397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4157295227051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5468311309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6439428329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7750425338745</t>
   </si>
   <si>
     <t xml:space="preserve">12.9644107818604</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9595565795898</t>
+    <t xml:space="preserve">12.9595556259155</t>
   </si>
   <si>
     <t xml:space="preserve">12.9401321411133</t>
@@ -3389,52 +3389,52 @@
     <t xml:space="preserve">12.9109992980957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4837083816528</t>
+    <t xml:space="preserve">12.4837074279785</t>
   </si>
   <si>
     <t xml:space="preserve">12.7070646286011</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4982738494873</t>
+    <t xml:space="preserve">12.4982748031616</t>
   </si>
   <si>
     <t xml:space="preserve">12.4739971160889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3428964614868</t>
+    <t xml:space="preserve">12.3428955078125</t>
   </si>
   <si>
     <t xml:space="preserve">12.639087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8721551895142</t>
+    <t xml:space="preserve">12.8721542358398</t>
   </si>
   <si>
     <t xml:space="preserve">12.6099519729614</t>
   </si>
   <si>
-    <t xml:space="preserve">12.585675239563</t>
+    <t xml:space="preserve">12.5856761932373</t>
   </si>
   <si>
     <t xml:space="preserve">12.3768854141235</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4885635375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2846298217773</t>
+    <t xml:space="preserve">12.488564491272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.284628868103</t>
   </si>
   <si>
     <t xml:space="preserve">12.2797737121582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2020845413208</t>
+    <t xml:space="preserve">12.2020835876465</t>
   </si>
   <si>
     <t xml:space="preserve">12.4400091171265</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3720302581787</t>
+    <t xml:space="preserve">12.3720293045044</t>
   </si>
   <si>
     <t xml:space="preserve">12.4351530075073</t>
@@ -3449,7 +3449,7 @@
     <t xml:space="preserve">11.7553701400757</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6728248596191</t>
+    <t xml:space="preserve">11.6728258132935</t>
   </si>
   <si>
     <t xml:space="preserve">11.6388368606567</t>
@@ -3461,7 +3461,7 @@
     <t xml:space="preserve">11.1532783508301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2164011001587</t>
+    <t xml:space="preserve">11.2164001464844</t>
   </si>
   <si>
     <t xml:space="preserve">11.0804433822632</t>
@@ -3470,19 +3470,19 @@
     <t xml:space="preserve">11.0658779144287</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6968536376953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6434412002563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6191644668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5171966552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7696876525879</t>
+    <t xml:space="preserve">10.6968545913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6434421539307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6191635131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5171976089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7696866989136</t>
   </si>
   <si>
     <t xml:space="preserve">10.9833326339722</t>
@@ -3500,10 +3500,10 @@
     <t xml:space="preserve">10.44921875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5317640304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4880628585815</t>
+    <t xml:space="preserve">10.5317630767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4880619049072</t>
   </si>
   <si>
     <t xml:space="preserve">10.3375406265259</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">10.1821613311768</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1918716430664</t>
+    <t xml:space="preserve">10.1918725967407</t>
   </si>
   <si>
     <t xml:space="preserve">10.2647047042847</t>
@@ -3530,7 +3530,7 @@
     <t xml:space="preserve">9.18870735168457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46644878387451</t>
+    <t xml:space="preserve">9.4664478302002</t>
   </si>
   <si>
     <t xml:space="preserve">9.04304218292236</t>
@@ -3539,13 +3539,13 @@
     <t xml:space="preserve">9.04498291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06246376037598</t>
+    <t xml:space="preserve">9.06246280670166</t>
   </si>
   <si>
     <t xml:space="preserve">8.84299182891846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8391056060791</t>
+    <t xml:space="preserve">8.83910655975342</t>
   </si>
   <si>
     <t xml:space="preserve">8.5438871383667</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">8.99836921691895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03138828277588</t>
+    <t xml:space="preserve">9.0313892364502</t>
   </si>
   <si>
     <t xml:space="preserve">9.58492469787598</t>
@@ -3590,25 +3590,25 @@
     <t xml:space="preserve">10.0801935195923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2598505020142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2501401901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4200830459595</t>
+    <t xml:space="preserve">10.2598495483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2501392364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4200839996338</t>
   </si>
   <si>
     <t xml:space="preserve">10.3860950469971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5074844360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346523284912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.415228843689</t>
+    <t xml:space="preserve">10.5074853897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4346513748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4152297973633</t>
   </si>
   <si>
     <t xml:space="preserve">10.3278293609619</t>
@@ -5954,7 +5954,7 @@
     <t xml:space="preserve">5.95800018310547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96999979019165</t>
+    <t xml:space="preserve">5.65000009536743</t>
   </si>
 </sst>
 </file>
@@ -71397,22 +71397,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6910532407</v>
+        <v>45967.6942708333</v>
       </c>
       <c r="B2505" t="n">
-        <v>5572053</v>
+        <v>10414835</v>
       </c>
       <c r="C2505" t="n">
-        <v>5.99399995803833</v>
+        <v>5.95599985122681</v>
       </c>
       <c r="D2505" t="n">
-        <v>5.86199998855591</v>
+        <v>5.63199996948242</v>
       </c>
       <c r="E2505" t="n">
         <v>5.92199993133545</v>
       </c>
       <c r="F2505" t="n">
-        <v>5.96999979019165</v>
+        <v>5.65000009536743</v>
       </c>
       <c r="G2505" t="s">
         <v>1980</v>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59865617752075</t>
+    <t xml:space="preserve">3.59865689277649</t>
   </si>
   <si>
     <t xml:space="preserve">CPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65898251533508</t>
+    <t xml:space="preserve">3.6589822769165</t>
   </si>
   <si>
     <t xml:space="preserve">3.60329699516296</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51976871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51048874855042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5499324798584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62881970405579</t>
+    <t xml:space="preserve">3.51976919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51048851013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54993224143982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62881922721863</t>
   </si>
   <si>
     <t xml:space="preserve">3.68450498580933</t>
@@ -68,43 +68,43 @@
     <t xml:space="preserve">3.57313418388367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52673006057739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4826455116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5661735534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43392109870911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50584816932678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56153345108032</t>
+    <t xml:space="preserve">3.52673029899597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48264598846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56617379188538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43392133712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50584769248962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56153321266174</t>
   </si>
   <si>
     <t xml:space="preserve">3.64274096488953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66594314575195</t>
+    <t xml:space="preserve">3.66594338417053</t>
   </si>
   <si>
     <t xml:space="preserve">3.56849408149719</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7425103187561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72162866592407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70770692825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47104501724243</t>
+    <t xml:space="preserve">3.74250960350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72162842750549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70770668983459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47104454040527</t>
   </si>
   <si>
     <t xml:space="preserve">3.44320201873779</t>
@@ -119,52 +119,52 @@
     <t xml:space="preserve">3.40839886665344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22046113014221</t>
+    <t xml:space="preserve">3.22046136856079</t>
   </si>
   <si>
     <t xml:space="preserve">3.26918578147888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32487058639526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2436637878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32255077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2877471446991</t>
+    <t xml:space="preserve">3.32487082481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24366331100464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32255125045776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28774738311768</t>
   </si>
   <si>
     <t xml:space="preserve">3.31791043281555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36663508415222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36199450492859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40607881546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3828763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36431503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53137040138245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60561752319336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61257791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56385374069214</t>
+    <t xml:space="preserve">3.3666353225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36199474334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40607857704163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38287591934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36431479454041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53137063980103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6056170463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61257815361023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56385326385498</t>
   </si>
   <si>
     <t xml:space="preserve">3.61489796638489</t>
@@ -173,70 +173,70 @@
     <t xml:space="preserve">3.63810038566589</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68914484977722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476325035095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95596957206726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00701475143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04877805709839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03485727310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04181814193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03717803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05109834671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01861667633057</t>
+    <t xml:space="preserve">3.68914532661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476205825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95597004890442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00701522827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04877948760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03485679626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0418176651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03717708587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05109882354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01861619949341</t>
   </si>
   <si>
     <t xml:space="preserve">4.09286308288574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07662105560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03949785232544</t>
+    <t xml:space="preserve">4.07662153244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03949737548828</t>
   </si>
   <si>
     <t xml:space="preserve">4.08358192443848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02325582504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00005435943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06037950515747</t>
+    <t xml:space="preserve">4.02325630187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00005388259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06038045883179</t>
   </si>
   <si>
     <t xml:space="preserve">3.99541401863098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94436883926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97453141212463</t>
+    <t xml:space="preserve">3.9443690776825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97453165054321</t>
   </si>
   <si>
     <t xml:space="preserve">4.00237464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93740820884705</t>
+    <t xml:space="preserve">3.93740844726562</t>
   </si>
   <si>
     <t xml:space="preserve">3.94668936729431</t>
@@ -245,25 +245,25 @@
     <t xml:space="preserve">4.03021717071533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05341911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00933504104614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9582896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98613381385803</t>
+    <t xml:space="preserve">4.05341958999634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00933456420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95828986167908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98613262176514</t>
   </si>
   <si>
     <t xml:space="preserve">4.0255765914917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96989130973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91188549995422</t>
+    <t xml:space="preserve">3.96989154815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91188645362854</t>
   </si>
   <si>
     <t xml:space="preserve">3.89796423912048</t>
@@ -272,43 +272,43 @@
     <t xml:space="preserve">3.87708258628845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91420674324036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92812824249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95132923126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06734085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08126068115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99309349060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96757125854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98149275779724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96293020248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88868427276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89332413673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79587531089783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89309883117676</t>
+    <t xml:space="preserve">3.91420650482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92812728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95132899284363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06733989715576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0812611579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99309325218201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96757173538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98149251937866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96292996406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88868403434753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89332461357117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79587554931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89309930801392</t>
   </si>
   <si>
     <t xml:space="preserve">4.02677774429321</t>
@@ -317,46 +317,46 @@
     <t xml:space="preserve">4.08540868759155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07602739334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08306360244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09948015213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07368278503418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09009981155396</t>
+    <t xml:space="preserve">4.07602834701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08306264877319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09948062896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07368326187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0900993347168</t>
   </si>
   <si>
     <t xml:space="preserve">4.10182523727417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08775424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11355113983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08071851730347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01974248886108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90482497215271</t>
+    <t xml:space="preserve">4.08775329589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1135516166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08071804046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01974201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90482544898987</t>
   </si>
   <si>
     <t xml:space="preserve">3.85557556152344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85792016983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86495590209961</t>
+    <t xml:space="preserve">3.8579204082489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86495542526245</t>
   </si>
   <si>
     <t xml:space="preserve">3.87199211120605</t>
@@ -365,73 +365,73 @@
     <t xml:space="preserve">3.86964654922485</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00567007064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00801467895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95876502990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05961036682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88606286048889</t>
+    <t xml:space="preserve">4.00567054748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00801563262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95876550674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05961084365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88606309890747</t>
   </si>
   <si>
     <t xml:space="preserve">3.88840770721436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04084920883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16514682769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15576601028442</t>
+    <t xml:space="preserve">4.04084825515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16514730453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15576553344727</t>
   </si>
   <si>
     <t xml:space="preserve">4.14873075485229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13231372833252</t>
+    <t xml:space="preserve">4.13231325149536</t>
   </si>
   <si>
     <t xml:space="preserve">4.00332498550415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04319477081299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16045618057251</t>
+    <t xml:space="preserve">4.04319381713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16045665740967</t>
   </si>
   <si>
     <t xml:space="preserve">4.15811157226562</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1158971786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06899213790894</t>
+    <t xml:space="preserve">4.11589765548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06899261474609</t>
   </si>
   <si>
     <t xml:space="preserve">4.13465738296509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14169502258301</t>
+    <t xml:space="preserve">4.14169454574585</t>
   </si>
   <si>
     <t xml:space="preserve">4.18390893936157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16280126571655</t>
+    <t xml:space="preserve">4.16280174255371</t>
   </si>
   <si>
     <t xml:space="preserve">4.21908760070801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29178953170776</t>
+    <t xml:space="preserve">4.29179000854492</t>
   </si>
   <si>
     <t xml:space="preserve">4.29648065567017</t>
@@ -446,13 +446,13 @@
     <t xml:space="preserve">4.33165884017944</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33869457244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54038524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51458787918091</t>
+    <t xml:space="preserve">4.33869409561157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5403847694397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51458740234375</t>
   </si>
   <si>
     <t xml:space="preserve">4.52162408828735</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">4.43719482421875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47940874099731</t>
+    <t xml:space="preserve">4.47940921783447</t>
   </si>
   <si>
     <t xml:space="preserve">4.45595645904541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66233777999878</t>
+    <t xml:space="preserve">4.66233730316162</t>
   </si>
   <si>
     <t xml:space="preserve">4.67171859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58963537216187</t>
+    <t xml:space="preserve">4.58963584899902</t>
   </si>
   <si>
     <t xml:space="preserve">4.55914735794067</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">4.60370588302612</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59667062759399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57321882247925</t>
+    <t xml:space="preserve">4.59667205810547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57321786880493</t>
   </si>
   <si>
     <t xml:space="preserve">4.62012338638306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59432649612427</t>
+    <t xml:space="preserve">4.59432554244995</t>
   </si>
   <si>
     <t xml:space="preserve">4.65061187744141</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">4.7045521736145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67406368255615</t>
+    <t xml:space="preserve">4.67406415939331</t>
   </si>
   <si>
     <t xml:space="preserve">4.70924282073975</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6013617515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48644351959229</t>
+    <t xml:space="preserve">4.60136222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48644399642944</t>
   </si>
   <si>
     <t xml:space="preserve">4.46533727645874</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">4.39967060089111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43250417709351</t>
+    <t xml:space="preserve">4.43250370025635</t>
   </si>
   <si>
     <t xml:space="preserve">4.50520610809326</t>
@@ -536,19 +536,19 @@
     <t xml:space="preserve">4.491135597229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51693344116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50286149978638</t>
+    <t xml:space="preserve">4.51693296432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50286245346069</t>
   </si>
   <si>
     <t xml:space="preserve">4.4887900352478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65295696258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66468286514282</t>
+    <t xml:space="preserve">4.65295648574829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66468334197998</t>
   </si>
   <si>
     <t xml:space="preserve">4.73269462585449</t>
@@ -557,37 +557,37 @@
     <t xml:space="preserve">4.71393299102783</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69048118591309</t>
+    <t xml:space="preserve">4.69048070907593</t>
   </si>
   <si>
     <t xml:space="preserve">4.58728981018066</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56852865219116</t>
+    <t xml:space="preserve">4.568528175354</t>
   </si>
   <si>
     <t xml:space="preserve">4.47471904754639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44657516479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54742002487183</t>
+    <t xml:space="preserve">4.44657468795776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54742097854614</t>
   </si>
   <si>
     <t xml:space="preserve">4.44188547134399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50051689147949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52631378173828</t>
+    <t xml:space="preserve">4.50051641464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52631330490112</t>
   </si>
   <si>
     <t xml:space="preserve">4.36683750152588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37152814865112</t>
+    <t xml:space="preserve">4.37152767181396</t>
   </si>
   <si>
     <t xml:space="preserve">4.33400392532349</t>
@@ -596,37 +596,37 @@
     <t xml:space="preserve">4.32931327819824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3058614730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30351591110229</t>
+    <t xml:space="preserve">4.30586099624634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30351638793945</t>
   </si>
   <si>
     <t xml:space="preserve">4.25661134719849</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20736122131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09478902816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24254035949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20267057418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95642113685608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95407485961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0338134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12527656555176</t>
+    <t xml:space="preserve">4.20736169815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09478950500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24253940582275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20267105102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9564208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95407462120056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03381395339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12527751922607</t>
   </si>
   <si>
     <t xml:space="preserve">4.01739645004272</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">4.12996864318848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17218208312988</t>
+    <t xml:space="preserve">4.17218255996704</t>
   </si>
   <si>
     <t xml:space="preserve">4.21205139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18859958648682</t>
+    <t xml:space="preserve">4.18859910964966</t>
   </si>
   <si>
     <t xml:space="preserve">4.24957609176636</t>
@@ -653,31 +653,31 @@
     <t xml:space="preserve">4.26833820343018</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22846841812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24723052978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31993198394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36449337005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28944444656372</t>
+    <t xml:space="preserve">4.2284688949585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24723100662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31993246078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449241638184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28944492340088</t>
   </si>
   <si>
     <t xml:space="preserve">4.27771854400635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30117082595825</t>
+    <t xml:space="preserve">4.30117034912109</t>
   </si>
   <si>
     <t xml:space="preserve">4.32227754592896</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35745620727539</t>
+    <t xml:space="preserve">4.35745668411255</t>
   </si>
   <si>
     <t xml:space="preserve">4.34807538986206</t>
@@ -686,43 +686,43 @@
     <t xml:space="preserve">4.34338521957397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39028978347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36214780807495</t>
+    <t xml:space="preserve">4.39028930664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36214828491211</t>
   </si>
   <si>
     <t xml:space="preserve">4.32462310791016</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39732503890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37387323379517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36918258666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47002744674683</t>
+    <t xml:space="preserve">4.39732551574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37387275695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36918210983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47002840042114</t>
   </si>
   <si>
     <t xml:space="preserve">4.45830202102661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42546892166138</t>
+    <t xml:space="preserve">4.42546939849854</t>
   </si>
   <si>
     <t xml:space="preserve">4.43484973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46768283843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40201568603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3527660369873</t>
+    <t xml:space="preserve">4.46768236160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40201616287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35276556015015</t>
   </si>
   <si>
     <t xml:space="preserve">4.3855996131897</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">4.43953990936279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4301586151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49348068237305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47237300872803</t>
+    <t xml:space="preserve">4.43015909194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49348020553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47237348556519</t>
   </si>
   <si>
     <t xml:space="preserve">4.5239691734314</t>
@@ -746,25 +746,25 @@
     <t xml:space="preserve">4.54273128509521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53803968429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54507493972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58259963989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57790994644165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55211210250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57087326049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53569555282593</t>
+    <t xml:space="preserve">4.53804016113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5450758934021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58260011672974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57790899276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55211114883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57087373733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53569459915161</t>
   </si>
   <si>
     <t xml:space="preserve">4.50755167007446</t>
@@ -779,34 +779,34 @@
     <t xml:space="preserve">4.74207544326782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75614786148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80774354934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83119535446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89686155319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94845676422119</t>
+    <t xml:space="preserve">4.7561469078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80774259567261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83119583129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8968620300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94845724105835</t>
   </si>
   <si>
     <t xml:space="preserve">5.09855270385742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0516471862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12200498580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04695749282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0563383102417</t>
+    <t xml:space="preserve">5.05164766311646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12200546264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04695701599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05633878707886</t>
   </si>
   <si>
     <t xml:space="preserve">4.99536180496216</t>
@@ -815,73 +815,73 @@
     <t xml:space="preserve">5.01881408691406</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02819538116455</t>
+    <t xml:space="preserve">5.02819585800171</t>
   </si>
   <si>
     <t xml:space="preserve">5.03288555145264</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9390754699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97659969329834</t>
+    <t xml:space="preserve">4.93907594680786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97659921646118</t>
   </si>
   <si>
     <t xml:space="preserve">4.92500495910645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96721982955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08917188644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17360019683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14545679092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15952920913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09386157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16421890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25333786010742</t>
+    <t xml:space="preserve">4.96721935272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08917140960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17359972000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14545726776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1595287322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09386205673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16421937942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25333833694458</t>
   </si>
   <si>
     <t xml:space="preserve">5.18767213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41750574111938</t>
+    <t xml:space="preserve">5.41750526428223</t>
   </si>
   <si>
     <t xml:space="preserve">5.67079067230225</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60043430328369</t>
+    <t xml:space="preserve">5.60043382644653</t>
   </si>
   <si>
     <t xml:space="preserve">5.62388706207275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66140985488892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68486213684082</t>
+    <t xml:space="preserve">5.66141080856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68486166000366</t>
   </si>
   <si>
     <t xml:space="preserve">5.57698154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60512399673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7223858833313</t>
+    <t xml:space="preserve">5.60512351989746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72238636016846</t>
   </si>
   <si>
     <t xml:space="preserve">5.69403505325317</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">5.74128770828247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76491403579712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7507381439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8783221244812</t>
+    <t xml:space="preserve">5.76491451263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75073862075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87832260131836</t>
   </si>
   <si>
     <t xml:space="preserve">5.86887216567993</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">5.99173069000244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00118160247803</t>
+    <t xml:space="preserve">6.00118064880371</t>
   </si>
   <si>
     <t xml:space="preserve">5.93502616882324</t>
@@ -920,25 +920,25 @@
     <t xml:space="preserve">5.85942125320435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80271816253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75546407699585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73183679580688</t>
+    <t xml:space="preserve">5.80271673202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75546360015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73183727264404</t>
   </si>
   <si>
     <t xml:space="preserve">5.84997081756592</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81216859817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95865345001221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93030166625977</t>
+    <t xml:space="preserve">5.81216812133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95865297317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93030118942261</t>
   </si>
   <si>
     <t xml:space="preserve">5.98227977752686</t>
@@ -953,61 +953,61 @@
     <t xml:space="preserve">5.91139984130859</t>
   </si>
   <si>
-    <t xml:space="preserve">5.83106899261475</t>
+    <t xml:space="preserve">5.8310694694519</t>
   </si>
   <si>
     <t xml:space="preserve">5.88777303695679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78381538391113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80744218826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84524536132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77436542510986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82634401321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82161855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85469627380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79326629638672</t>
+    <t xml:space="preserve">5.78381633758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8074426651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84524488449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77436590194702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82634353637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82161808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85469579696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79326677322388</t>
   </si>
   <si>
     <t xml:space="preserve">5.8357949256897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95392847061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92557573318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94447708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7790904045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74601221084595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71766138076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6515064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66095733642578</t>
+    <t xml:space="preserve">5.95392751693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92557668685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94447755813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77908945083618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74601268768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71766090393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65150594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66095638275146</t>
   </si>
   <si>
     <t xml:space="preserve">5.79799175262451</t>
@@ -1016,40 +1016,40 @@
     <t xml:space="preserve">5.76018857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69875907897949</t>
+    <t xml:space="preserve">5.69875955581665</t>
   </si>
   <si>
     <t xml:space="preserve">5.66568231582642</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73656272888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78854084014893</t>
+    <t xml:space="preserve">5.73656225204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78854131698608</t>
   </si>
   <si>
     <t xml:space="preserve">5.76963996887207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89249849319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97282981872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15239286422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14766645431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28470277786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13821601867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1240406036377</t>
+    <t xml:space="preserve">5.89249801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97282934188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15239238739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1476674079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28470182418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13821649551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12404108047485</t>
   </si>
   <si>
     <t xml:space="preserve">6.02953338623047</t>
@@ -1058,31 +1058,31 @@
     <t xml:space="preserve">6.10513925552368</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16656875610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11458921432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31777954101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34140539169312</t>
+    <t xml:space="preserve">6.16656827926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11458873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31777906417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34140586853027</t>
   </si>
   <si>
     <t xml:space="preserve">6.4075608253479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50206756591797</t>
+    <t xml:space="preserve">6.50206804275513</t>
   </si>
   <si>
     <t xml:space="preserve">6.42173671722412</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30832862854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47844076156616</t>
+    <t xml:space="preserve">6.30832815170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47843980789185</t>
   </si>
   <si>
     <t xml:space="preserve">6.31305360794067</t>
@@ -1091,19 +1091,19 @@
     <t xml:space="preserve">6.33668041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37448263168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17601919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09096336364746</t>
+    <t xml:space="preserve">6.37448358535767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17601823806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0909628868103</t>
   </si>
   <si>
     <t xml:space="preserve">6.23272275924683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03898334503174</t>
+    <t xml:space="preserve">6.0389838218689</t>
   </si>
   <si>
     <t xml:space="preserve">6.08623743057251</t>
@@ -1112,46 +1112,46 @@
     <t xml:space="preserve">6.10041379928589</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10986471176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00590705871582</t>
+    <t xml:space="preserve">6.10986423492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00590658187866</t>
   </si>
   <si>
     <t xml:space="preserve">6.03425884246826</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09568786621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0626106262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18074369430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08151149749756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15711736679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21382141113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24217319488525</t>
+    <t xml:space="preserve">6.09568738937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06261110305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18074464797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08151197433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15711688995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21382188796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2421727180481</t>
   </si>
   <si>
     <t xml:space="preserve">6.24689912796021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20909690856934</t>
+    <t xml:space="preserve">6.20909643173218</t>
   </si>
   <si>
     <t xml:space="preserve">6.22799730300903</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19964504241943</t>
+    <t xml:space="preserve">6.19964551925659</t>
   </si>
   <si>
     <t xml:space="preserve">6.12876558303833</t>
@@ -1166,40 +1166,40 @@
     <t xml:space="preserve">6.13349056243896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14294147491455</t>
+    <t xml:space="preserve">6.14294195175171</t>
   </si>
   <si>
     <t xml:space="preserve">6.01063251495361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94920253753662</t>
+    <t xml:space="preserve">5.94920349121094</t>
   </si>
   <si>
     <t xml:space="preserve">5.97755479812622</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05316019058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99645566940308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0673360824585</t>
+    <t xml:space="preserve">6.05316066741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99645614624023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06733560562134</t>
   </si>
   <si>
     <t xml:space="preserve">5.93975210189819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71293544769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72711181640625</t>
+    <t xml:space="preserve">5.71293497085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72711133956909</t>
   </si>
   <si>
     <t xml:space="preserve">5.92084980010986</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5759015083313</t>
+    <t xml:space="preserve">5.57590103149414</t>
   </si>
   <si>
     <t xml:space="preserve">5.52864742279053</t>
@@ -1208,19 +1208,19 @@
     <t xml:space="preserve">5.42941474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50502061843872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61370372772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63733005523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04370927810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98700523376465</t>
+    <t xml:space="preserve">5.50502014160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61370420455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63733053207397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04370975494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98700618743896</t>
   </si>
   <si>
     <t xml:space="preserve">6.01535701751709</t>
@@ -1232,40 +1232,40 @@
     <t xml:space="preserve">5.81689357757568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87359714508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86414623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9066743850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96810388565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01550722122192</t>
+    <t xml:space="preserve">5.87359666824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86414575576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90667486190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96810483932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01550769805908</t>
   </si>
   <si>
     <t xml:space="preserve">6.02027082443237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99169301986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08218765258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20602178573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18697071075439</t>
+    <t xml:space="preserve">5.99169397354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08218860626221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20602226257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18697118759155</t>
   </si>
   <si>
     <t xml:space="preserve">6.08695030212402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07266139984131</t>
+    <t xml:space="preserve">6.07266187667847</t>
   </si>
   <si>
     <t xml:space="preserve">6.16315603256226</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">6.27270269393921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2536506652832</t>
+    <t xml:space="preserve">6.25365114212036</t>
   </si>
   <si>
     <t xml:space="preserve">6.13934230804443</t>
@@ -1286,61 +1286,61 @@
     <t xml:space="preserve">6.38701105117798</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52513456344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59657764434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6918363571167</t>
+    <t xml:space="preserve">6.5251350402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59657716751099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69183588027954</t>
   </si>
   <si>
     <t xml:space="preserve">6.69659852981567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62039232254028</t>
+    <t xml:space="preserve">6.62039184570312</t>
   </si>
   <si>
     <t xml:space="preserve">6.57276391983032</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50608348846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58228921890259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65373229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71088695526123</t>
+    <t xml:space="preserve">6.5060830116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58228874206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65373277664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71088647842407</t>
   </si>
   <si>
     <t xml:space="preserve">6.82519578933716</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77280378341675</t>
+    <t xml:space="preserve">6.77280426025391</t>
   </si>
   <si>
     <t xml:space="preserve">6.82995891571045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0252366065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92521524429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92045259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01094770431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9680814743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91092729568481</t>
+    <t xml:space="preserve">7.02523612976074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92521619796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92045307159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0109486579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96808195114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91092681884766</t>
   </si>
   <si>
     <t xml:space="preserve">7.01570987701416</t>
@@ -1349,28 +1349,28 @@
     <t xml:space="preserve">7.04905033111572</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09667873382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17764806747437</t>
+    <t xml:space="preserve">7.0966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17764759063721</t>
   </si>
   <si>
     <t xml:space="preserve">7.28243112564087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22051477432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2395658493042</t>
+    <t xml:space="preserve">7.22051429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23956537246704</t>
   </si>
   <si>
     <t xml:space="preserve">7.27766847610474</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12525653839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94903087615967</t>
+    <t xml:space="preserve">7.12525701522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94903039932251</t>
   </si>
   <si>
     <t xml:space="preserve">6.86806154251099</t>
@@ -1385,16 +1385,16 @@
     <t xml:space="preserve">7.06333923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97760725021362</t>
+    <t xml:space="preserve">6.97760772705078</t>
   </si>
   <si>
     <t xml:space="preserve">6.9918966293335</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03952503204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02047300338745</t>
+    <t xml:space="preserve">7.0395245552063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02047348022461</t>
   </si>
   <si>
     <t xml:space="preserve">7.07762813568115</t>
@@ -1403,58 +1403,58 @@
     <t xml:space="preserve">7.18717432022095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21098899841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41579246520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29672002792358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26338052749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24432849884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27290630340576</t>
+    <t xml:space="preserve">7.21098852157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4157919883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29671955108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26338005065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24432802200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2729058265686</t>
   </si>
   <si>
     <t xml:space="preserve">7.30624580383301</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1824107170105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25385427474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05857610702515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.10620498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14907073974609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16812229156494</t>
+    <t xml:space="preserve">7.18241119384766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2538537979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0585765838623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.10620450973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14907026290894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1681227684021</t>
   </si>
   <si>
     <t xml:space="preserve">6.90140199661255</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94426727294922</t>
+    <t xml:space="preserve">6.94426774978638</t>
   </si>
   <si>
     <t xml:space="preserve">7.06810188293457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98713254928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13001918792725</t>
+    <t xml:space="preserve">6.98713302612305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1300196647644</t>
   </si>
   <si>
     <t xml:space="preserve">6.87758684158325</t>
@@ -1469,13 +1469,13 @@
     <t xml:space="preserve">6.65849494934082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32985687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19649648666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11552667617798</t>
+    <t xml:space="preserve">6.32985734939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19649744033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11552762985229</t>
   </si>
   <si>
     <t xml:space="preserve">6.04884719848633</t>
@@ -1484,100 +1484,100 @@
     <t xml:space="preserve">6.21554851531982</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31556844711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33462047576904</t>
+    <t xml:space="preserve">6.3155689239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33461999893188</t>
   </si>
   <si>
     <t xml:space="preserve">6.34414529800415</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12505388259888</t>
+    <t xml:space="preserve">6.12505435943604</t>
   </si>
   <si>
     <t xml:space="preserve">6.15363121032715</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30604267120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35367059707642</t>
+    <t xml:space="preserve">6.30604314804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35367107391357</t>
   </si>
   <si>
     <t xml:space="preserve">6.47274351119995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4679799079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42987775802612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52989816665649</t>
+    <t xml:space="preserve">6.46798038482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42987728118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52989768981934</t>
   </si>
   <si>
     <t xml:space="preserve">6.76804161071777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08239078521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11096858978271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12049341201782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32529783248901</t>
+    <t xml:space="preserve">7.08239030838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11096811294556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12049388885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32529735565186</t>
   </si>
   <si>
     <t xml:space="preserve">7.31577110290527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11573076248169</t>
+    <t xml:space="preserve">7.11573028564453</t>
   </si>
   <si>
     <t xml:space="preserve">7.03476238250732</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15383434295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04428720474243</t>
+    <t xml:space="preserve">7.15383386611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04428768157959</t>
   </si>
   <si>
     <t xml:space="preserve">7.02999925613403</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17288541793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36340045928955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14430904388428</t>
+    <t xml:space="preserve">7.17288589477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36339998245239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14430856704712</t>
   </si>
   <si>
     <t xml:space="preserve">7.20622587203979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32053470611572</t>
+    <t xml:space="preserve">7.32053422927856</t>
   </si>
   <si>
     <t xml:space="preserve">7.09191656112671</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98237037658691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44913244247437</t>
+    <t xml:space="preserve">6.98236989974976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44913196563721</t>
   </si>
   <si>
     <t xml:space="preserve">7.3824520111084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33006048202515</t>
+    <t xml:space="preserve">7.33006000518799</t>
   </si>
   <si>
     <t xml:space="preserve">7.21575117111206</t>
@@ -1586,13 +1586,13 @@
     <t xml:space="preserve">7.33958578109741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35387516021729</t>
+    <t xml:space="preserve">7.35387420654297</t>
   </si>
   <si>
     <t xml:space="preserve">7.55391454696655</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60630702972412</t>
+    <t xml:space="preserve">7.60630750656128</t>
   </si>
   <si>
     <t xml:space="preserve">7.46342039108276</t>
@@ -1607,55 +1607,55 @@
     <t xml:space="preserve">7.42055416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62535858154297</t>
+    <t xml:space="preserve">7.62535905838013</t>
   </si>
   <si>
     <t xml:space="preserve">7.53010129928589</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47294664382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48723459243774</t>
+    <t xml:space="preserve">7.47294569015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4872350692749</t>
   </si>
   <si>
     <t xml:space="preserve">7.46818351745605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49676084518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51581192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6110692024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56344223022461</t>
+    <t xml:space="preserve">7.49676036834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51581144332886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61106967926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56344127655029</t>
   </si>
   <si>
     <t xml:space="preserve">7.64440965652466</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73490333557129</t>
+    <t xml:space="preserve">7.73490428924561</t>
   </si>
   <si>
     <t xml:space="preserve">7.80634689331055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86826467514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85873985290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88731622695923</t>
+    <t xml:space="preserve">7.86826515197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85873937606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88731670379639</t>
   </si>
   <si>
     <t xml:space="preserve">7.92541933059692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95399713516235</t>
+    <t xml:space="preserve">7.95399761199951</t>
   </si>
   <si>
     <t xml:space="preserve">7.83492517471313</t>
@@ -1664,13 +1664,13 @@
     <t xml:space="preserve">7.98733568191528</t>
   </si>
   <si>
-    <t xml:space="preserve">8.01115131378174</t>
+    <t xml:space="preserve">8.01115036010742</t>
   </si>
   <si>
     <t xml:space="preserve">8.06354331970215</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53486394882202</t>
+    <t xml:space="preserve">7.53486347198486</t>
   </si>
   <si>
     <t xml:space="preserve">7.52057504653931</t>
@@ -1679,10 +1679,10 @@
     <t xml:space="preserve">7.54438972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62059545516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63964796066284</t>
+    <t xml:space="preserve">7.62059593200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63964748382568</t>
   </si>
   <si>
     <t xml:space="preserve">7.77777099609375</t>
@@ -1691,22 +1691,22 @@
     <t xml:space="preserve">7.76824378967285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90636730194092</t>
+    <t xml:space="preserve">7.90636825561523</t>
   </si>
   <si>
     <t xml:space="preserve">8.03496551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00638771057129</t>
+    <t xml:space="preserve">8.00638866424561</t>
   </si>
   <si>
     <t xml:space="preserve">8.04449081420898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06830501556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20166492462158</t>
+    <t xml:space="preserve">8.06830406188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20166397094727</t>
   </si>
   <si>
     <t xml:space="preserve">8.32550048828125</t>
@@ -1721,13 +1721,13 @@
     <t xml:space="preserve">8.38265419006348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33502674102783</t>
+    <t xml:space="preserve">8.33502578735352</t>
   </si>
   <si>
     <t xml:space="preserve">8.27787113189697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23500442504883</t>
+    <t xml:space="preserve">8.23500633239746</t>
   </si>
   <si>
     <t xml:space="preserve">8.25881958007812</t>
@@ -1736,13 +1736,13 @@
     <t xml:space="preserve">8.26358318328857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16832542419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31121158599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36836528778076</t>
+    <t xml:space="preserve">8.16832637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31121253967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36836624145508</t>
   </si>
   <si>
     <t xml:space="preserve">8.35407733917236</t>
@@ -1751,151 +1751,151 @@
     <t xml:space="preserve">8.37789154052734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28739738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21119213104248</t>
+    <t xml:space="preserve">8.28739547729492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21119117736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22071647644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43150424957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44587516784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56085205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51294422149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48899173736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60875701904297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.441086769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49857425689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4842004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67103672027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81475639343262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74289512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83391761779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77643013000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70936107635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68540859222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70457077026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78122043609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80996322631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77163887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65187454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53689765930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37880706787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3740177154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40755271911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41234302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32611179351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45545864105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41713333129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39318084716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54648113250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58959674835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27341461181641</t>
   </si>
   <si>
     <t xml:space="preserve">8.22071743011475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43150424957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44587516784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56085300445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5129451751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48899173736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60875797271729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44108772277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49857330322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4842004776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67103576660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81475639343262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74289608001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83391761779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77643013000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7093620300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6854076385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70457077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78122138977051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80996322631836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77163887023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65187358856201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53689765930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37880706787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37401676177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40755081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4123420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32611083984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45545673370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41713237762451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39318084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54648017883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58959579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27341365814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22071647644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25425148010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35485553741455</t>
+    <t xml:space="preserve">8.25425052642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35485458374023</t>
   </si>
   <si>
     <t xml:space="preserve">8.47462177276611</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42192363739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36922645568848</t>
+    <t xml:space="preserve">8.42192459106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36922740936279</t>
   </si>
   <si>
     <t xml:space="preserve">8.31653022766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29736709594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28299522399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17760181427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20155620574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16323089599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24946022033691</t>
+    <t xml:space="preserve">8.29736614227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28299617767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17760276794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20155429840088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16322994232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2494592666626</t>
   </si>
   <si>
     <t xml:space="preserve">8.18239212036133</t>
@@ -1907,7 +1907,7 @@
     <t xml:space="preserve">8.09616184234619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14885807037354</t>
+    <t xml:space="preserve">8.14885902404785</t>
   </si>
   <si>
     <t xml:space="preserve">8.06741714477539</t>
@@ -1919,28 +1919,28 @@
     <t xml:space="preserve">7.97160530090332</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78956127166748</t>
+    <t xml:space="preserve">7.78956031799316</t>
   </si>
   <si>
     <t xml:space="preserve">7.62188911437988</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61709785461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66021347045898</t>
+    <t xml:space="preserve">7.61709833145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66021299362183</t>
   </si>
   <si>
     <t xml:space="preserve">7.50212335586548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72249174118042</t>
+    <t xml:space="preserve">7.72249221801758</t>
   </si>
   <si>
     <t xml:space="preserve">7.5931453704834</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45900821685791</t>
+    <t xml:space="preserve">7.45900774002075</t>
   </si>
   <si>
     <t xml:space="preserve">7.51170444488525</t>
@@ -1952,10 +1952,10 @@
     <t xml:space="preserve">7.59793567657471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90932655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95244216918945</t>
+    <t xml:space="preserve">7.90932703018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95244312286377</t>
   </si>
   <si>
     <t xml:space="preserve">7.82309579849243</t>
@@ -1964,34 +1964,34 @@
     <t xml:space="preserve">7.88058280944824</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10574150085449</t>
+    <t xml:space="preserve">8.10574245452881</t>
   </si>
   <si>
     <t xml:space="preserve">8.20634460449219</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16802024841309</t>
+    <t xml:space="preserve">8.16801929473877</t>
   </si>
   <si>
     <t xml:space="preserve">8.26383209228516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34527397155762</t>
+    <t xml:space="preserve">8.3452730178833</t>
   </si>
   <si>
     <t xml:space="preserve">8.29257583618164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12011432647705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03388214111328</t>
+    <t xml:space="preserve">8.12011337280273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03388118743896</t>
   </si>
   <si>
     <t xml:space="preserve">7.9955587387085</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80872392654419</t>
+    <t xml:space="preserve">7.80872344970703</t>
   </si>
   <si>
     <t xml:space="preserve">7.91411733627319</t>
@@ -2003,34 +2003,34 @@
     <t xml:space="preserve">7.82788610458374</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84704780578613</t>
+    <t xml:space="preserve">7.84704828262329</t>
   </si>
   <si>
     <t xml:space="preserve">8.0003490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89974451065063</t>
+    <t xml:space="preserve">7.89974403381348</t>
   </si>
   <si>
     <t xml:space="preserve">7.90453624725342</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94286060333252</t>
+    <t xml:space="preserve">7.9428596496582</t>
   </si>
   <si>
     <t xml:space="preserve">7.71770191192627</t>
   </si>
   <si>
-    <t xml:space="preserve">7.85662984848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04346466064453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11532402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12969493865967</t>
+    <t xml:space="preserve">7.85662889480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04346561431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11532211303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12969589233398</t>
   </si>
   <si>
     <t xml:space="preserve">8.13448619842529</t>
@@ -2039,49 +2039,49 @@
     <t xml:space="preserve">8.00992870330811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93327951431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75123596191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57877349853516</t>
+    <t xml:space="preserve">7.9332799911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7512354850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.578773021698</t>
   </si>
   <si>
     <t xml:space="preserve">7.64105129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69374752044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83746814727783</t>
+    <t xml:space="preserve">7.69374799728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83746719360352</t>
   </si>
   <si>
     <t xml:space="preserve">7.81351327896118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87100124359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87579345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92369890213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89495420455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85183906555176</t>
+    <t xml:space="preserve">7.87100172042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87579298019409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92369842529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89495372772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8518385887146</t>
   </si>
   <si>
     <t xml:space="preserve">7.86621141433716</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9859766960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96681308746338</t>
+    <t xml:space="preserve">7.98597574234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9668140411377</t>
   </si>
   <si>
     <t xml:space="preserve">7.92848920822144</t>
@@ -2093,55 +2093,55 @@
     <t xml:space="preserve">8.04825496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93807029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77997875213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81830453872681</t>
+    <t xml:space="preserve">7.93806982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77997970581055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81830358505249</t>
   </si>
   <si>
     <t xml:space="preserve">7.84225797653198</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79435205459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79914236068726</t>
+    <t xml:space="preserve">7.79435157775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79914283752441</t>
   </si>
   <si>
     <t xml:space="preserve">7.94765138626099</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9189076423645</t>
+    <t xml:space="preserve">7.91890859603882</t>
   </si>
   <si>
     <t xml:space="preserve">7.71291160583496</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77518796920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86141920089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07699966430664</t>
+    <t xml:space="preserve">7.77518892288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86141967773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07699775695801</t>
   </si>
   <si>
     <t xml:space="preserve">8.21592617034912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2686243057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33569240570068</t>
+    <t xml:space="preserve">8.26862335205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33569145202637</t>
   </si>
   <si>
     <t xml:space="preserve">8.45066738128662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36443519592285</t>
+    <t xml:space="preserve">8.36443614959717</t>
   </si>
   <si>
     <t xml:space="preserve">8.47941112518311</t>
@@ -2153,28 +2153,28 @@
     <t xml:space="preserve">8.59438610076904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66624736785889</t>
+    <t xml:space="preserve">8.66624546051025</t>
   </si>
   <si>
     <t xml:space="preserve">8.64229297637939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69019794464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58480548858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19197368621826</t>
+    <t xml:space="preserve">8.6901969909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58480644226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19197463989258</t>
   </si>
   <si>
     <t xml:space="preserve">7.74165487289429</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70332956314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78477001190186</t>
+    <t xml:space="preserve">7.70332908630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78477048873901</t>
   </si>
   <si>
     <t xml:space="preserve">7.44463634490967</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">7.36319494247437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33924245834351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09491968154907</t>
+    <t xml:space="preserve">7.33924150466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09492015838623</t>
   </si>
   <si>
     <t xml:space="preserve">6.6972975730896</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">6.3619532585144</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33675861358643</t>
+    <t xml:space="preserve">5.33675909042358</t>
   </si>
   <si>
     <t xml:space="preserve">5.54754686355591</t>
@@ -2213,61 +2213,61 @@
     <t xml:space="preserve">5.37987470626831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30322408676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8685188293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45776605606079</t>
+    <t xml:space="preserve">5.30322456359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86851930618286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45776557922363</t>
   </si>
   <si>
     <t xml:space="preserve">6.08409643173218</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03619146347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29967498779297</t>
+    <t xml:space="preserve">6.0361909866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29967594146729</t>
   </si>
   <si>
     <t xml:space="preserve">6.76915693283081</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84101629257202</t>
+    <t xml:space="preserve">6.84101581573486</t>
   </si>
   <si>
     <t xml:space="preserve">6.53441667556763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3715353012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27572250366211</t>
+    <t xml:space="preserve">6.37153482437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27572345733643</t>
   </si>
   <si>
     <t xml:space="preserve">6.02852630615234</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11092519760132</t>
+    <t xml:space="preserve">6.110924243927</t>
   </si>
   <si>
     <t xml:space="preserve">5.85606288909912</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45201778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38111639022827</t>
+    <t xml:space="preserve">6.45201730728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38111591339111</t>
   </si>
   <si>
     <t xml:space="preserve">6.32171297073364</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35237264633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40986013412476</t>
+    <t xml:space="preserve">6.35237312316895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40986061096191</t>
   </si>
   <si>
     <t xml:space="preserve">6.40794372558594</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">6.47309589385986</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65897274017334</t>
+    <t xml:space="preserve">6.65897226333618</t>
   </si>
   <si>
     <t xml:space="preserve">6.49962043762207</t>
@@ -5954,7 +5954,7 @@
     <t xml:space="preserve">5.95800018310547</t>
   </si>
   <si>
-    <t xml:space="preserve">5.65000009536743</t>
+    <t xml:space="preserve">5.69399976730347</t>
   </si>
 </sst>
 </file>
@@ -71397,22 +71397,22 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45967.6942708333</v>
+        <v>45968.6918634259</v>
       </c>
       <c r="B2505" t="n">
-        <v>10414835</v>
+        <v>6175972</v>
       </c>
       <c r="C2505" t="n">
-        <v>5.95599985122681</v>
+        <v>5.71000003814697</v>
       </c>
       <c r="D2505" t="n">
-        <v>5.63199996948242</v>
+        <v>5.55800008773804</v>
       </c>
       <c r="E2505" t="n">
-        <v>5.92199993133545</v>
+        <v>5.67000007629395</v>
       </c>
       <c r="F2505" t="n">
-        <v>5.65000009536743</v>
+        <v>5.69399976730347</v>
       </c>
       <c r="G2505" t="s">
         <v>1980</v>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1981" uniqueCount="1981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1984" uniqueCount="1984">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,46 +44,46 @@
     <t xml:space="preserve">CPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6589822769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60329699516296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51976919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51048851013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54993224143982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62881922721863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68450498580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57313418388367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52673029899597</t>
+    <t xml:space="preserve">3.65898251533508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60329675674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51976943016052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51048827171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54993200302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62881970405579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68450450897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57313394546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52672982215881</t>
   </si>
   <si>
     <t xml:space="preserve">3.48264598846436</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56617379188538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43392133712769</t>
+    <t xml:space="preserve">3.56617307662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43392157554626</t>
   </si>
   <si>
     <t xml:space="preserve">3.50584769248962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56153321266174</t>
+    <t xml:space="preserve">3.56153297424316</t>
   </si>
   <si>
     <t xml:space="preserve">3.64274096488953</t>
@@ -92,34 +92,34 @@
     <t xml:space="preserve">3.66594338417053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56849408149719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74250960350037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72162842750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70770668983459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47104454040527</t>
+    <t xml:space="preserve">3.56849384307861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74251008033752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72162890434265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70770716667175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47104477882385</t>
   </si>
   <si>
     <t xml:space="preserve">3.44320201873779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28078722953796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33183145523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40839886665344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22046136856079</t>
+    <t xml:space="preserve">3.28078699111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33183121681213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40839862823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22046113014221</t>
   </si>
   <si>
     <t xml:space="preserve">3.26918578147888</t>
@@ -128,61 +128,61 @@
     <t xml:space="preserve">3.32487082481384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24366331100464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32255125045776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28774738311768</t>
+    <t xml:space="preserve">3.24366307258606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32255053520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28774762153625</t>
   </si>
   <si>
     <t xml:space="preserve">3.31791043281555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3666353225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36199474334717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40607857704163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38287591934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36431479454041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53137063980103</t>
+    <t xml:space="preserve">3.36663508415222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36199450492859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40607881546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38287663459778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36431455612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53137040138245</t>
   </si>
   <si>
     <t xml:space="preserve">3.6056170463562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61257815361023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56385326385498</t>
+    <t xml:space="preserve">3.61257767677307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56385350227356</t>
   </si>
   <si>
     <t xml:space="preserve">3.61489796638489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63810038566589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68914532661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476205825806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95597004890442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00701522827148</t>
+    <t xml:space="preserve">3.63809990882874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6891450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476301193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95596957206726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00701427459717</t>
   </si>
   <si>
     <t xml:space="preserve">4.04877948760986</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">4.03485679626465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0418176651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03717708587646</t>
+    <t xml:space="preserve">4.04181861877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03717756271362</t>
   </si>
   <si>
     <t xml:space="preserve">4.05109882354736</t>
@@ -203,49 +203,49 @@
     <t xml:space="preserve">4.01861619949341</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09286308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07662153244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03949737548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08358192443848</t>
+    <t xml:space="preserve">4.09286260604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07662105560303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03949785232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08358144760132</t>
   </si>
   <si>
     <t xml:space="preserve">4.02325630187988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00005388259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06038045883179</t>
+    <t xml:space="preserve">4.00005435943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06037998199463</t>
   </si>
   <si>
     <t xml:space="preserve">3.99541401863098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9443690776825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97453165054321</t>
+    <t xml:space="preserve">3.94436931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97453141212463</t>
   </si>
   <si>
     <t xml:space="preserve">4.00237464904785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93740844726562</t>
+    <t xml:space="preserve">3.93740820884705</t>
   </si>
   <si>
     <t xml:space="preserve">3.94668936729431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03021717071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05341958999634</t>
+    <t xml:space="preserve">4.03021669387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05341863632202</t>
   </si>
   <si>
     <t xml:space="preserve">4.00933456420898</t>
@@ -257,58 +257,58 @@
     <t xml:space="preserve">3.98613262176514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0255765914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96989154815674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91188645362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89796423912048</t>
+    <t xml:space="preserve">4.02557754516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96989107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91188597679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89796471595764</t>
   </si>
   <si>
     <t xml:space="preserve">3.87708258628845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91420650482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92812728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95132899284363</t>
+    <t xml:space="preserve">3.91420674324036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92812776565552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95132994651794</t>
   </si>
   <si>
     <t xml:space="preserve">4.06733989715576</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0812611579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99309325218201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96757173538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98149251937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96292996406555</t>
+    <t xml:space="preserve">4.08126068115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99309277534485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9675714969635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98149275779724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96293067932129</t>
   </si>
   <si>
     <t xml:space="preserve">3.88868403434753</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89332461357117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79587554931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89309930801392</t>
+    <t xml:space="preserve">3.89332389831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79587578773499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89309906959534</t>
   </si>
   <si>
     <t xml:space="preserve">4.02677774429321</t>
@@ -317,16 +317,16 @@
     <t xml:space="preserve">4.08540868759155</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07602834701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08306264877319</t>
+    <t xml:space="preserve">4.07602691650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08306312561035</t>
   </si>
   <si>
     <t xml:space="preserve">4.09948062896729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07368326187134</t>
+    <t xml:space="preserve">4.07368278503418</t>
   </si>
   <si>
     <t xml:space="preserve">4.0900993347168</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">4.10182523727417</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08775329589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1135516166687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08071804046631</t>
+    <t xml:space="preserve">4.0877537727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11355209350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08071851730347</t>
   </si>
   <si>
     <t xml:space="preserve">4.01974201202393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90482544898987</t>
+    <t xml:space="preserve">3.90482568740845</t>
   </si>
   <si>
     <t xml:space="preserve">3.85557556152344</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">3.8579204082489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86495542526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87199211120605</t>
+    <t xml:space="preserve">3.86495590209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8719916343689</t>
   </si>
   <si>
     <t xml:space="preserve">3.86964654922485</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">4.00567054748535</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00801563262939</t>
+    <t xml:space="preserve">4.00801515579224</t>
   </si>
   <si>
     <t xml:space="preserve">3.95876550674438</t>
@@ -377,61 +377,61 @@
     <t xml:space="preserve">4.05961084365845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88606309890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88840770721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04084825515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16514730453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15576553344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14873075485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13231325149536</t>
+    <t xml:space="preserve">3.88606333732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88840842247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04084873199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16514682769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15576601028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14873027801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13231372833252</t>
   </si>
   <si>
     <t xml:space="preserve">4.00332498550415</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04319381713867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16045665740967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15811157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11589765548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06899261474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13465738296509</t>
+    <t xml:space="preserve">4.04319429397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16045618057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15811109542847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11589670181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06899166107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13465881347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.14169454574585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18390893936157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16280174255371</t>
+    <t xml:space="preserve">4.18390846252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16280221939087</t>
   </si>
   <si>
     <t xml:space="preserve">4.21908760070801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29179000854492</t>
+    <t xml:space="preserve">4.29178953170776</t>
   </si>
   <si>
     <t xml:space="preserve">4.29648065567017</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">4.28709983825684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33165884017944</t>
+    <t xml:space="preserve">4.3316593170166</t>
   </si>
   <si>
     <t xml:space="preserve">4.33869409561157</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5403847694397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51458740234375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52162408828735</t>
+    <t xml:space="preserve">4.54038572311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51458787918091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5216236114502</t>
   </si>
   <si>
     <t xml:space="preserve">4.43719482421875</t>
@@ -473,28 +473,28 @@
     <t xml:space="preserve">4.67171859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58963584899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55914735794067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5638370513916</t>
+    <t xml:space="preserve">4.58963489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55914783477783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56383800506592</t>
   </si>
   <si>
     <t xml:space="preserve">4.54976654052734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60370588302612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59667205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57321786880493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62012338638306</t>
+    <t xml:space="preserve">4.60370635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59667110443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57321882247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62012386322021</t>
   </si>
   <si>
     <t xml:space="preserve">4.59432554244995</t>
@@ -503,61 +503,61 @@
     <t xml:space="preserve">4.65061187744141</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57556438446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7045521736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67406415939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70924282073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60136222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48644399642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46533727645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39967060089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43250370025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50520610809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.491135597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51693296432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50286245346069</t>
+    <t xml:space="preserve">4.57556390762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70455265045166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67406320571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70924234390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60136127471924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48644495010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4653377532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39967012405396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43250513076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50520658493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49113512039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51693344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50286197662354</t>
   </si>
   <si>
     <t xml:space="preserve">4.4887900352478</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65295648574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66468334197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73269462585449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71393299102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69048070907593</t>
+    <t xml:space="preserve">4.65295696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66468286514282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73269510269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71393346786499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69048118591309</t>
   </si>
   <si>
     <t xml:space="preserve">4.58728981018066</t>
@@ -569,19 +569,19 @@
     <t xml:space="preserve">4.47471904754639</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44657468795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54742097854614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44188547134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50051641464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52631330490112</t>
+    <t xml:space="preserve">4.44657564163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54742050170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44188594818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50051593780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52631378173828</t>
   </si>
   <si>
     <t xml:space="preserve">4.36683750152588</t>
@@ -590,37 +590,37 @@
     <t xml:space="preserve">4.37152767181396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33400392532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32931327819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30586099624634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30351638793945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25661134719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20736169815063</t>
+    <t xml:space="preserve">4.33400440216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32931280136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3058614730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30351591110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25661039352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20736122131348</t>
   </si>
   <si>
     <t xml:space="preserve">4.09478950500488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24253940582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20267105102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9564208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95407462120056</t>
+    <t xml:space="preserve">4.24253988265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20267009735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95642066001892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95407557487488</t>
   </si>
   <si>
     <t xml:space="preserve">4.03381395339966</t>
@@ -629,13 +629,13 @@
     <t xml:space="preserve">4.12527751922607</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01739645004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12996864318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17218255996704</t>
+    <t xml:space="preserve">4.01739597320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12996816635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17218351364136</t>
   </si>
   <si>
     <t xml:space="preserve">4.21205139160156</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">4.24957609176636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20501613616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26833820343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2284688949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24723100662231</t>
+    <t xml:space="preserve">4.20501661300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26833772659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22846794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24723052978516</t>
   </si>
   <si>
     <t xml:space="preserve">4.31993246078491</t>
@@ -671,16 +671,16 @@
     <t xml:space="preserve">4.27771854400635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30117034912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32227754592896</t>
+    <t xml:space="preserve">4.30117082595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32227802276611</t>
   </si>
   <si>
     <t xml:space="preserve">4.35745668411255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34807538986206</t>
+    <t xml:space="preserve">4.3480749130249</t>
   </si>
   <si>
     <t xml:space="preserve">4.34338521957397</t>
@@ -689,34 +689,34 @@
     <t xml:space="preserve">4.39028930664062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36214828491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32462310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39732551574707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37387275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36918210983276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47002840042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45830202102661</t>
+    <t xml:space="preserve">4.36214685440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32462358474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39732599258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37387323379517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36918306350708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47002792358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45830106735229</t>
   </si>
   <si>
     <t xml:space="preserve">4.42546939849854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43484973907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46768236160278</t>
+    <t xml:space="preserve">4.43484926223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46768283843994</t>
   </si>
   <si>
     <t xml:space="preserve">4.40201616287231</t>
@@ -728,37 +728,37 @@
     <t xml:space="preserve">4.3855996131897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43953990936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43015909194946</t>
+    <t xml:space="preserve">4.43954086303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4301586151123</t>
   </si>
   <si>
     <t xml:space="preserve">4.49348020553589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47237348556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5239691734314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54273128509521</t>
+    <t xml:space="preserve">4.47237253189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52396869659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54272985458374</t>
   </si>
   <si>
     <t xml:space="preserve">4.53804016113281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5450758934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58260011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57790899276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55211114883423</t>
+    <t xml:space="preserve">4.54507637023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58259963989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57790946960449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55211162567139</t>
   </si>
   <si>
     <t xml:space="preserve">4.57087373733521</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">4.50755167007446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58494472503662</t>
+    <t xml:space="preserve">4.58494520187378</t>
   </si>
   <si>
     <t xml:space="preserve">4.65530204772949</t>
@@ -779,43 +779,43 @@
     <t xml:space="preserve">4.74207544326782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7561469078064</t>
+    <t xml:space="preserve">4.75614786148071</t>
   </si>
   <si>
     <t xml:space="preserve">4.80774259567261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83119583129883</t>
+    <t xml:space="preserve">4.83119487762451</t>
   </si>
   <si>
     <t xml:space="preserve">4.8968620300293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94845724105835</t>
+    <t xml:space="preserve">4.94845628738403</t>
   </si>
   <si>
     <t xml:space="preserve">5.09855270385742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05164766311646</t>
+    <t xml:space="preserve">5.05164861679077</t>
   </si>
   <si>
     <t xml:space="preserve">5.12200546264648</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04695701599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05633878707886</t>
+    <t xml:space="preserve">5.04695749282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05633783340454</t>
   </si>
   <si>
     <t xml:space="preserve">4.99536180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01881408691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02819585800171</t>
+    <t xml:space="preserve">5.0188136100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02819538116455</t>
   </si>
   <si>
     <t xml:space="preserve">5.03288555145264</t>
@@ -824,16 +824,16 @@
     <t xml:space="preserve">4.93907594680786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97659921646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92500495910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96721935272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08917140960693</t>
+    <t xml:space="preserve">4.9766001701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92500448226929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96721887588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08917188644409</t>
   </si>
   <si>
     <t xml:space="preserve">5.17359972000122</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">5.14545726776123</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1595287322998</t>
+    <t xml:space="preserve">5.15952920913696</t>
   </si>
   <si>
     <t xml:space="preserve">5.09386205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16421937942505</t>
+    <t xml:space="preserve">5.16421985626221</t>
   </si>
   <si>
     <t xml:space="preserve">5.25333833694458</t>
@@ -857,40 +857,40 @@
     <t xml:space="preserve">5.18767213821411</t>
   </si>
   <si>
-    <t xml:space="preserve">5.41750526428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67079067230225</t>
+    <t xml:space="preserve">5.41750574111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6707911491394</t>
   </si>
   <si>
     <t xml:space="preserve">5.60043382644653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.62388706207275</t>
+    <t xml:space="preserve">5.6238865852356</t>
   </si>
   <si>
     <t xml:space="preserve">5.66141080856323</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68486166000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57698154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60512351989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72238636016846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69403505325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74128770828247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76491451263428</t>
+    <t xml:space="preserve">5.68486213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57698202133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60512495040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72238683700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69403409957886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74128723144531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76491403579712</t>
   </si>
   <si>
     <t xml:space="preserve">5.75073862075806</t>
@@ -899,13 +899,13 @@
     <t xml:space="preserve">5.87832260131836</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86887216567993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88304805755615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02008247375488</t>
+    <t xml:space="preserve">5.86887168884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88304710388184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02008199691772</t>
   </si>
   <si>
     <t xml:space="preserve">5.99173069000244</t>
@@ -914,31 +914,31 @@
     <t xml:space="preserve">6.00118064880371</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93502616882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85942125320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80271673202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75546360015869</t>
+    <t xml:space="preserve">5.93502712249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85942077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8027172088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75546407699585</t>
   </si>
   <si>
     <t xml:space="preserve">5.73183727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84997081756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81216812133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95865297317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93030118942261</t>
+    <t xml:space="preserve">5.84997034072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81216764450073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95865345001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93030166625977</t>
   </si>
   <si>
     <t xml:space="preserve">5.98227977752686</t>
@@ -950,16 +950,16 @@
     <t xml:space="preserve">5.91612529754639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91139984130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8310694694519</t>
+    <t xml:space="preserve">5.91140031814575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83106899261475</t>
   </si>
   <si>
     <t xml:space="preserve">5.88777303695679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78381633758545</t>
+    <t xml:space="preserve">5.78381586074829</t>
   </si>
   <si>
     <t xml:space="preserve">5.8074426651001</t>
@@ -968,37 +968,37 @@
     <t xml:space="preserve">5.84524488449097</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77436590194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82634353637695</t>
+    <t xml:space="preserve">5.77436542510986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82634401321411</t>
   </si>
   <si>
     <t xml:space="preserve">5.82161808013916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85469579696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79326677322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8357949256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95392751693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92557668685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94447755813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77908945083618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74601268768311</t>
+    <t xml:space="preserve">5.85469627380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79326629638672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83579444885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95392799377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92557621002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94447708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7790904045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74601316452026</t>
   </si>
   <si>
     <t xml:space="preserve">5.71766090393066</t>
@@ -1007,31 +1007,31 @@
     <t xml:space="preserve">5.65150594711304</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66095638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79799175262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76018857955933</t>
+    <t xml:space="preserve">5.66095685958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79799222946167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76018953323364</t>
   </si>
   <si>
     <t xml:space="preserve">5.69875955581665</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66568231582642</t>
+    <t xml:space="preserve">5.66568326950073</t>
   </si>
   <si>
     <t xml:space="preserve">5.73656225204468</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78854131698608</t>
+    <t xml:space="preserve">5.78854084014893</t>
   </si>
   <si>
     <t xml:space="preserve">5.76963996887207</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89249801635742</t>
+    <t xml:space="preserve">5.89249849319458</t>
   </si>
   <si>
     <t xml:space="preserve">5.97282934188843</t>
@@ -1040,49 +1040,49 @@
     <t xml:space="preserve">6.15239238739014</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1476674079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28470182418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13821649551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12404108047485</t>
+    <t xml:space="preserve">6.14766645431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28470230102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13821601867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12404012680054</t>
   </si>
   <si>
     <t xml:space="preserve">6.02953338623047</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10513925552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16656827926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11458873748779</t>
+    <t xml:space="preserve">6.10513877868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1665678024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11458921432495</t>
   </si>
   <si>
     <t xml:space="preserve">6.31777906417847</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34140586853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4075608253479</t>
+    <t xml:space="preserve">6.34140634536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40756130218506</t>
   </si>
   <si>
     <t xml:space="preserve">6.50206804275513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42173671722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30832815170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47843980789185</t>
+    <t xml:space="preserve">6.42173624038696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30832862854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47844076156616</t>
   </si>
   <si>
     <t xml:space="preserve">6.31305360794067</t>
@@ -1091,10 +1091,10 @@
     <t xml:space="preserve">6.33668041229248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.37448358535767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17601823806763</t>
+    <t xml:space="preserve">6.37448263168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17601919174194</t>
   </si>
   <si>
     <t xml:space="preserve">6.0909628868103</t>
@@ -1109,157 +1109,157 @@
     <t xml:space="preserve">6.08623743057251</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10041379928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10986423492432</t>
+    <t xml:space="preserve">6.10041332244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10986375808716</t>
   </si>
   <si>
     <t xml:space="preserve">6.00590658187866</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03425884246826</t>
+    <t xml:space="preserve">6.03425931930542</t>
   </si>
   <si>
     <t xml:space="preserve">6.09568738937378</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06261110305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18074464797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08151197433472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15711688995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21382188796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2421727180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24689912796021</t>
+    <t xml:space="preserve">6.0626106262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18074417114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08151245117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15711736679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21382141113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24217414855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24690008163452</t>
   </si>
   <si>
     <t xml:space="preserve">6.20909643173218</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22799730300903</t>
+    <t xml:space="preserve">6.22799777984619</t>
   </si>
   <si>
     <t xml:space="preserve">6.19964551925659</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12876558303833</t>
+    <t xml:space="preserve">6.12876605987549</t>
   </si>
   <si>
     <t xml:space="preserve">6.07206153869629</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05788564682007</t>
+    <t xml:space="preserve">6.05788516998291</t>
   </si>
   <si>
     <t xml:space="preserve">6.13349056243896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.14294195175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01063251495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94920349121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97755479812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05316066741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99645614624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06733560562134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93975210189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71293497085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72711133956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92084980010986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57590103149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.52864742279053</t>
+    <t xml:space="preserve">6.14294147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01063203811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94920301437378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97755432128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05315971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99645519256592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0673360824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93975114822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71293592453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72711181640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92085075378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57590055465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.52864694595337</t>
   </si>
   <si>
     <t xml:space="preserve">5.42941474914551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50502014160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.61370420455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.63733053207397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04370975494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98700618743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01535701751709</t>
+    <t xml:space="preserve">5.50502109527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.61370372772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63733005523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04370927810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98700571060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01535749435425</t>
   </si>
   <si>
     <t xml:space="preserve">5.89722394943237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81689357757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87359666824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86414575576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90667486190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96810483932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01550769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02027082443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99169397354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08218860626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20602226257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18697118759155</t>
+    <t xml:space="preserve">5.81689405441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87359809875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86414670944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90667390823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96810436248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01550722122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02027034759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99169254302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08218812942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20602178573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18697071075439</t>
   </si>
   <si>
     <t xml:space="preserve">6.08695030212402</t>
@@ -1268,55 +1268,55 @@
     <t xml:space="preserve">6.07266187667847</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16315603256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27270269393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.25365114212036</t>
+    <t xml:space="preserve">6.16315650939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27270221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2536506652832</t>
   </si>
   <si>
     <t xml:space="preserve">6.13934230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2917537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38701105117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5251350402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59657716751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69183588027954</t>
+    <t xml:space="preserve">6.29175472259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38701152801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52513456344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5965781211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69183540344238</t>
   </si>
   <si>
     <t xml:space="preserve">6.69659852981567</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62039184570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57276391983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5060830116272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58228874206543</t>
+    <t xml:space="preserve">6.62039232254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57276344299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50608348846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58228969573975</t>
   </si>
   <si>
     <t xml:space="preserve">6.65373277664185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71088647842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82519578933716</t>
+    <t xml:space="preserve">6.71088695526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8251953125</t>
   </si>
   <si>
     <t xml:space="preserve">6.77280426025391</t>
@@ -1325,46 +1325,46 @@
     <t xml:space="preserve">6.82995891571045</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02523612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92521619796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92045307159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0109486579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96808195114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91092681884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01570987701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04905033111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17764759063721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.28243112564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22051429748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23956537246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27766847610474</t>
+    <t xml:space="preserve">7.0252366065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92521715164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9204535484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01094818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96808242797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91092729568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01571035385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04905080795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09668016433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17764854431152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.28243160247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22051382064819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2395658493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27766799926758</t>
   </si>
   <si>
     <t xml:space="preserve">7.12525701522827</t>
@@ -1376,46 +1376,46 @@
     <t xml:space="preserve">6.86806154251099</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0014214515686</t>
+    <t xml:space="preserve">7.00142192840576</t>
   </si>
   <si>
     <t xml:space="preserve">7.00618505477905</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06333923339844</t>
+    <t xml:space="preserve">7.0633397102356</t>
   </si>
   <si>
     <t xml:space="preserve">6.97760772705078</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9918966293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0395245552063</t>
+    <t xml:space="preserve">6.99189710617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03952550888062</t>
   </si>
   <si>
     <t xml:space="preserve">7.02047348022461</t>
   </si>
   <si>
-    <t xml:space="preserve">7.07762813568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18717432022095</t>
+    <t xml:space="preserve">7.07762765884399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18717336654663</t>
   </si>
   <si>
     <t xml:space="preserve">7.21098852157593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4157919883728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29671955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26338005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24432802200317</t>
+    <t xml:space="preserve">7.41579151153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29672002792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26337957382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24432849884033</t>
   </si>
   <si>
     <t xml:space="preserve">7.2729058265686</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">7.0585765838623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10620450973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14907026290894</t>
+    <t xml:space="preserve">7.10620498657227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14907121658325</t>
   </si>
   <si>
     <t xml:space="preserve">7.1681227684021</t>
@@ -1451,28 +1451,28 @@
     <t xml:space="preserve">7.06810188293457</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98713302612305</t>
+    <t xml:space="preserve">6.98713350296021</t>
   </si>
   <si>
     <t xml:space="preserve">7.1300196647644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87758684158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70612382888794</t>
+    <t xml:space="preserve">6.87758731842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70612335205078</t>
   </si>
   <si>
     <t xml:space="preserve">6.63944339752197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65849494934082</t>
+    <t xml:space="preserve">6.65849447250366</t>
   </si>
   <si>
     <t xml:space="preserve">6.32985734939575</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19649744033813</t>
+    <t xml:space="preserve">6.19649600982666</t>
   </si>
   <si>
     <t xml:space="preserve">6.11552762985229</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">6.04884719848633</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21554851531982</t>
+    <t xml:space="preserve">6.21554803848267</t>
   </si>
   <si>
     <t xml:space="preserve">6.3155689239502</t>
@@ -1490,22 +1490,22 @@
     <t xml:space="preserve">6.33461999893188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34414529800415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12505435943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15363121032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30604314804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35367107391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47274351119995</t>
+    <t xml:space="preserve">6.34414577484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12505292892456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15363025665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30604267120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35367155075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47274255752563</t>
   </si>
   <si>
     <t xml:space="preserve">6.46798038482666</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">6.76804161071777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08239030838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11096811294556</t>
+    <t xml:space="preserve">7.08239078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11096858978271</t>
   </si>
   <si>
     <t xml:space="preserve">7.12049388885498</t>
@@ -1532,16 +1532,16 @@
     <t xml:space="preserve">7.32529735565186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31577110290527</t>
+    <t xml:space="preserve">7.31577157974243</t>
   </si>
   <si>
     <t xml:space="preserve">7.11573028564453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03476238250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15383386611938</t>
+    <t xml:space="preserve">7.03476285934448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15383434295654</t>
   </si>
   <si>
     <t xml:space="preserve">7.04428768157959</t>
@@ -1550,67 +1550,67 @@
     <t xml:space="preserve">7.02999925613403</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17288589477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36339998245239</t>
+    <t xml:space="preserve">7.17288541793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36340093612671</t>
   </si>
   <si>
     <t xml:space="preserve">7.14430856704712</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20622587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32053422927856</t>
+    <t xml:space="preserve">7.20622539520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32053375244141</t>
   </si>
   <si>
     <t xml:space="preserve">7.09191656112671</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98236989974976</t>
+    <t xml:space="preserve">6.98237085342407</t>
   </si>
   <si>
     <t xml:space="preserve">7.44913196563721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3824520111084</t>
+    <t xml:space="preserve">7.38245153427124</t>
   </si>
   <si>
     <t xml:space="preserve">7.33006000518799</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21575117111206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33958578109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.35387420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55391454696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60630750656128</t>
+    <t xml:space="preserve">7.2157506942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33958625793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.35387468338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55391502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60630702972412</t>
   </si>
   <si>
     <t xml:space="preserve">7.46342039108276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49199724197388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44436931610107</t>
+    <t xml:space="preserve">7.49199771881104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44436883926392</t>
   </si>
   <si>
     <t xml:space="preserve">7.42055416107178</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62535905838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53010129928589</t>
+    <t xml:space="preserve">7.62535810470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53010082244873</t>
   </si>
   <si>
     <t xml:space="preserve">7.47294569015503</t>
@@ -1619,13 +1619,13 @@
     <t xml:space="preserve">7.4872350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46818351745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49676036834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51581144332886</t>
+    <t xml:space="preserve">7.46818399429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49676132202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51581239700317</t>
   </si>
   <si>
     <t xml:space="preserve">7.61106967926025</t>
@@ -1634,148 +1634,148 @@
     <t xml:space="preserve">7.56344127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64440965652466</t>
+    <t xml:space="preserve">7.6444091796875</t>
   </si>
   <si>
     <t xml:space="preserve">7.73490428924561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80634689331055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86826515197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85873937606812</t>
+    <t xml:space="preserve">7.80634784698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8682656288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85873985290527</t>
   </si>
   <si>
     <t xml:space="preserve">7.88731670379639</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92541933059692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95399761199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83492517471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98733568191528</t>
+    <t xml:space="preserve">7.92541885375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95399713516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83492469787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9873366355896</t>
   </si>
   <si>
     <t xml:space="preserve">8.01115036010742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06354331970215</t>
+    <t xml:space="preserve">8.06354141235352</t>
   </si>
   <si>
     <t xml:space="preserve">7.53486347198486</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52057504653931</t>
+    <t xml:space="preserve">7.52057552337646</t>
   </si>
   <si>
     <t xml:space="preserve">7.54438972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62059593200684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63964748382568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77777099609375</t>
+    <t xml:space="preserve">7.62059545516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63964700698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77776956558228</t>
   </si>
   <si>
     <t xml:space="preserve">7.76824378967285</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90636825561523</t>
+    <t xml:space="preserve">7.90636920928955</t>
   </si>
   <si>
     <t xml:space="preserve">8.03496551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00638866424561</t>
+    <t xml:space="preserve">8.00638675689697</t>
   </si>
   <si>
     <t xml:space="preserve">8.04449081420898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06830406188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20166397094727</t>
+    <t xml:space="preserve">8.06830596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20166492462158</t>
   </si>
   <si>
     <t xml:space="preserve">8.32550048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44457149505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33978939056396</t>
+    <t xml:space="preserve">8.44457340240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33979034423828</t>
   </si>
   <si>
     <t xml:space="preserve">8.38265419006348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33502578735352</t>
+    <t xml:space="preserve">8.33502674102783</t>
   </si>
   <si>
     <t xml:space="preserve">8.27787113189697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23500633239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25881958007812</t>
+    <t xml:space="preserve">8.23500537872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25882053375244</t>
   </si>
   <si>
     <t xml:space="preserve">8.26358318328857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.16832637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31121253967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36836624145508</t>
+    <t xml:space="preserve">8.16832542419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31121349334717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36836528778076</t>
   </si>
   <si>
     <t xml:space="preserve">8.35407733917236</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37789154052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28739547729492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21119117736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22071647644043</t>
+    <t xml:space="preserve">8.37789058685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28739833831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21119213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22071838378906</t>
   </si>
   <si>
     <t xml:space="preserve">8.43150424957275</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44587516784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56085205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51294422149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48899173736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60875701904297</t>
+    <t xml:space="preserve">8.44587707519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56085300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5129451751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48899269104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6087589263916</t>
   </si>
   <si>
     <t xml:space="preserve">8.441086769104</t>
@@ -1784,37 +1784,37 @@
     <t xml:space="preserve">8.49857425689697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4842004776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67103672027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.81475639343262</t>
+    <t xml:space="preserve">8.48420238494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67103576660156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.81475448608398</t>
   </si>
   <si>
     <t xml:space="preserve">8.74289512634277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83391761779785</t>
+    <t xml:space="preserve">8.83391666412354</t>
   </si>
   <si>
     <t xml:space="preserve">8.77643013000488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70936107635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68540859222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70457077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78122043609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80996322631836</t>
+    <t xml:space="preserve">8.7093620300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6854076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70457172393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78122138977051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80996417999268</t>
   </si>
   <si>
     <t xml:space="preserve">8.77163887023926</t>
@@ -1823,7 +1823,7 @@
     <t xml:space="preserve">8.65187454223633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53689765930176</t>
+    <t xml:space="preserve">8.53689861297607</t>
   </si>
   <si>
     <t xml:space="preserve">8.37880706787109</t>
@@ -1832,28 +1832,28 @@
     <t xml:space="preserve">8.3740177154541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40755271911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41234302520752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32611179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45545864105225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41713333129883</t>
+    <t xml:space="preserve">8.40755081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4123420715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32611083984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45545768737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41713237762451</t>
   </si>
   <si>
     <t xml:space="preserve">8.39318084716797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54648113250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58959674835205</t>
+    <t xml:space="preserve">8.54648017883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58959579467773</t>
   </si>
   <si>
     <t xml:space="preserve">8.27341461181641</t>
@@ -1862,19 +1862,19 @@
     <t xml:space="preserve">8.22071743011475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25425052642822</t>
+    <t xml:space="preserve">8.25425148010254</t>
   </si>
   <si>
     <t xml:space="preserve">8.35485458374023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47462177276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42192459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36922740936279</t>
+    <t xml:space="preserve">8.4746208190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42192363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36922645568848</t>
   </si>
   <si>
     <t xml:space="preserve">8.31653022766113</t>
@@ -1883,25 +1883,25 @@
     <t xml:space="preserve">8.29736614227295</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28299617767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17760276794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20155429840088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16322994232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2494592666626</t>
+    <t xml:space="preserve">8.28299522399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17760181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2015552520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16323089599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24946022033691</t>
   </si>
   <si>
     <t xml:space="preserve">8.18239212036133</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17281055450439</t>
+    <t xml:space="preserve">8.17281150817871</t>
   </si>
   <si>
     <t xml:space="preserve">8.09616184234619</t>
@@ -1910,16 +1910,16 @@
     <t xml:space="preserve">8.14885902404785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06741714477539</t>
+    <t xml:space="preserve">8.06741905212402</t>
   </si>
   <si>
     <t xml:space="preserve">8.03867435455322</t>
   </si>
   <si>
-    <t xml:space="preserve">7.97160530090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78956031799316</t>
+    <t xml:space="preserve">7.971604347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78955984115601</t>
   </si>
   <si>
     <t xml:space="preserve">7.62188911437988</t>
@@ -1928,7 +1928,7 @@
     <t xml:space="preserve">7.61709833145142</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66021299362183</t>
+    <t xml:space="preserve">7.66021394729614</t>
   </si>
   <si>
     <t xml:space="preserve">7.50212335586548</t>
@@ -1937,13 +1937,13 @@
     <t xml:space="preserve">7.72249221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5931453704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45900774002075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51170444488525</t>
+    <t xml:space="preserve">7.59314584732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45900726318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51170492172241</t>
   </si>
   <si>
     <t xml:space="preserve">7.65542316436768</t>
@@ -1952,13 +1952,13 @@
     <t xml:space="preserve">7.59793567657471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90932703018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95244312286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82309579849243</t>
+    <t xml:space="preserve">7.90932607650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95244359970093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82309484481812</t>
   </si>
   <si>
     <t xml:space="preserve">7.88058280944824</t>
@@ -1973,7 +1973,7 @@
     <t xml:space="preserve">8.16801929473877</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26383209228516</t>
+    <t xml:space="preserve">8.26383304595947</t>
   </si>
   <si>
     <t xml:space="preserve">8.3452730178833</t>
@@ -1982,22 +1982,22 @@
     <t xml:space="preserve">8.29257583618164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12011337280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03388118743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9955587387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80872344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91411733627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88537311553955</t>
+    <t xml:space="preserve">8.12011432647705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0338830947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99555778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80872249603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91411781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88537359237671</t>
   </si>
   <si>
     <t xml:space="preserve">7.82788610458374</t>
@@ -2009,31 +2009,31 @@
     <t xml:space="preserve">8.0003490447998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89974403381348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90453624725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9428596496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71770191192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85662889480591</t>
+    <t xml:space="preserve">7.89974546432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90453672409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94286108016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71770143508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85663032531738</t>
   </si>
   <si>
     <t xml:space="preserve">8.04346561431885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.11532211303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12969589233398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13448619842529</t>
+    <t xml:space="preserve">8.11532402038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12969493865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13448524475098</t>
   </si>
   <si>
     <t xml:space="preserve">8.00992870330811</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">7.9332799911499</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7512354850769</t>
+    <t xml:space="preserve">7.75123596191406</t>
   </si>
   <si>
     <t xml:space="preserve">7.578773021698</t>
@@ -2051,55 +2051,55 @@
     <t xml:space="preserve">7.64105129241943</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69374799728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83746719360352</t>
+    <t xml:space="preserve">7.69374752044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83746767044067</t>
   </si>
   <si>
     <t xml:space="preserve">7.81351327896118</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87100172042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87579298019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92369842529297</t>
+    <t xml:space="preserve">7.87100124359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87579250335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92369890213013</t>
   </si>
   <si>
     <t xml:space="preserve">7.89495372772217</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8518385887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86621141433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98597574234009</t>
+    <t xml:space="preserve">7.85183954238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86621046066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9859766960144</t>
   </si>
   <si>
     <t xml:space="preserve">7.9668140411377</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92848920822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11053371429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04825496673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93806982040405</t>
+    <t xml:space="preserve">7.92848873138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1105318069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04825592041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93807077407837</t>
   </si>
   <si>
     <t xml:space="preserve">7.77997970581055</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81830358505249</t>
+    <t xml:space="preserve">7.81830406188965</t>
   </si>
   <si>
     <t xml:space="preserve">7.84225797653198</t>
@@ -2108,13 +2108,13 @@
     <t xml:space="preserve">7.79435157775879</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79914283752441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94765138626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91890859603882</t>
+    <t xml:space="preserve">7.79914236068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94765186309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91890811920166</t>
   </si>
   <si>
     <t xml:space="preserve">7.71291160583496</t>
@@ -2123,19 +2123,19 @@
     <t xml:space="preserve">7.77518892288208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86141967773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07699775695801</t>
+    <t xml:space="preserve">7.86142063140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07699871063232</t>
   </si>
   <si>
     <t xml:space="preserve">8.21592617034912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26862335205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33569145202637</t>
+    <t xml:space="preserve">8.2686243057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.335693359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.45066738128662</t>
@@ -2153,97 +2153,97 @@
     <t xml:space="preserve">8.59438610076904</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66624546051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64229297637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6901969909668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58480644226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19197463989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74165487289429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70332908630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78477048873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44463634490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22426652908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1763596534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30091667175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36319494247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33924150466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09492015838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6972975730896</t>
+    <t xml:space="preserve">8.66624641418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64229202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69019794464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58480548858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19197368621826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74165439605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70332956314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78477001190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44463586807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22426700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17636013031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30091714859009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36319446563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33924198150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09491968154907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69729709625244</t>
   </si>
   <si>
     <t xml:space="preserve">6.3619532585144</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33675909042358</t>
+    <t xml:space="preserve">5.33675956726074</t>
   </si>
   <si>
     <t xml:space="preserve">5.54754686355591</t>
   </si>
   <si>
-    <t xml:space="preserve">5.37987470626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30322456359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86851930618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45776557922363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08409643173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0361909866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29967594146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76915693283081</t>
+    <t xml:space="preserve">5.37987518310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30322504043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8685188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45776605606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08409690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03619146347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29967546463013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76915645599365</t>
   </si>
   <si>
     <t xml:space="preserve">6.84101581573486</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53441667556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37153482437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27572345733643</t>
+    <t xml:space="preserve">6.53441619873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3715353012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27572250366211</t>
   </si>
   <si>
     <t xml:space="preserve">6.02852630615234</t>
@@ -2252,13 +2252,13 @@
     <t xml:space="preserve">6.110924243927</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85606288909912</t>
+    <t xml:space="preserve">5.85606384277344</t>
   </si>
   <si>
     <t xml:space="preserve">6.45201730728149</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38111591339111</t>
+    <t xml:space="preserve">6.38111639022827</t>
   </si>
   <si>
     <t xml:space="preserve">6.32171297073364</t>
@@ -2270,49 +2270,49 @@
     <t xml:space="preserve">6.40986061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40794372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47309589385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65897226333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49962043762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44746971130371</t>
+    <t xml:space="preserve">6.4079442024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47309637069702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65897274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49962091445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44746923446655</t>
   </si>
   <si>
     <t xml:space="preserve">6.43008518218994</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39338636398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44360589981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59619760513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61551284790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79321384429932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8279824256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62323951721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69084310531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76617240905762</t>
+    <t xml:space="preserve">6.393385887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44360542297363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59619808197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61551237106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79321432113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82798194885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62323904037476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.690842628479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76617288589478</t>
   </si>
   <si>
     <t xml:space="preserve">6.78935146331787</t>
@@ -2333,10 +2333,10 @@
     <t xml:space="preserve">6.70629501342773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66766452789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94001054763794</t>
+    <t xml:space="preserve">6.66766500473022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9400110244751</t>
   </si>
   <si>
     <t xml:space="preserve">6.51121044158936</t>
@@ -2345,13 +2345,13 @@
     <t xml:space="preserve">6.67345857620239</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53245735168457</t>
+    <t xml:space="preserve">6.53245687484741</t>
   </si>
   <si>
     <t xml:space="preserve">6.6638011932373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67732238769531</t>
+    <t xml:space="preserve">6.67732191085815</t>
   </si>
   <si>
     <t xml:space="preserve">6.72947359085083</t>
@@ -2360,31 +2360,31 @@
     <t xml:space="preserve">6.71208953857422</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1466851234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05010843276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94387483596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11191749572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09839677810669</t>
+    <t xml:space="preserve">7.14668560028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05010890960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94387435913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1119179725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09839725494385</t>
   </si>
   <si>
     <t xml:space="preserve">7.142822265625</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14475345611572</t>
+    <t xml:space="preserve">7.14475393295288</t>
   </si>
   <si>
     <t xml:space="preserve">7.13895988464355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17758989334106</t>
+    <t xml:space="preserve">7.17759037017822</t>
   </si>
   <si>
     <t xml:space="preserve">7.05976676940918</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">7.20463132858276</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06942367553711</t>
+    <t xml:space="preserve">7.06942415237427</t>
   </si>
   <si>
     <t xml:space="preserve">7.31279802322388</t>
@@ -2402,37 +2402,37 @@
     <t xml:space="preserve">7.33018159866333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38619565963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44800519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44027853012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58128118515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27223587036133</t>
+    <t xml:space="preserve">7.38619518280029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44800472259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44027900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58128023147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27223539352417</t>
   </si>
   <si>
     <t xml:space="preserve">7.26837253570557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24326276779175</t>
+    <t xml:space="preserve">7.24326229095459</t>
   </si>
   <si>
     <t xml:space="preserve">7.34370279312134</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5484447479248</t>
+    <t xml:space="preserve">7.54844522476196</t>
   </si>
   <si>
     <t xml:space="preserve">7.45379972457886</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62667179107666</t>
+    <t xml:space="preserve">7.62667226791382</t>
   </si>
   <si>
     <t xml:space="preserve">7.67013120651245</t>
@@ -2444,40 +2444,40 @@
     <t xml:space="preserve">7.84203863143921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86425113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81499767303467</t>
+    <t xml:space="preserve">7.86425161361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81499814987183</t>
   </si>
   <si>
     <t xml:space="preserve">7.75029039382935</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92412805557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91350507736206</t>
+    <t xml:space="preserve">7.92412853240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91350555419922</t>
   </si>
   <si>
     <t xml:space="preserve">7.82851791381836</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89322423934937</t>
+    <t xml:space="preserve">7.89322519302368</t>
   </si>
   <si>
     <t xml:space="preserve">7.98497247695923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87294387817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0265007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88549900054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83817577362061</t>
+    <t xml:space="preserve">7.87294340133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02649974822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.885498046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83817672729492</t>
   </si>
   <si>
     <t xml:space="preserve">8.2631139755249</t>
@@ -2486,25 +2486,25 @@
     <t xml:space="preserve">8.42729473114014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21965503692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22158432006836</t>
+    <t xml:space="preserve">8.21965408325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22158527374268</t>
   </si>
   <si>
     <t xml:space="preserve">8.28146362304688</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23220920562744</t>
+    <t xml:space="preserve">8.23221015930176</t>
   </si>
   <si>
     <t xml:space="preserve">8.29594993591309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13659763336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2080659866333</t>
+    <t xml:space="preserve">8.13659858703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20806503295898</t>
   </si>
   <si>
     <t xml:space="preserve">8.21868896484375</t>
@@ -2513,22 +2513,22 @@
     <t xml:space="preserve">8.26601028442383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43598651885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3973560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2775993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30753993988037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24283313751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34423923492432</t>
+    <t xml:space="preserve">8.43598556518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39735507965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27760028839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30753898620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24283218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34423828125</t>
   </si>
   <si>
     <t xml:space="preserve">8.22834587097168</t>
@@ -2537,13 +2537,13 @@
     <t xml:space="preserve">8.39059448242188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3432731628418</t>
+    <t xml:space="preserve">8.34327220916748</t>
   </si>
   <si>
     <t xml:space="preserve">8.43405342102051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3104362487793</t>
+    <t xml:space="preserve">8.31043529510498</t>
   </si>
   <si>
     <t xml:space="preserve">8.18102359771729</t>
@@ -2555,64 +2555,64 @@
     <t xml:space="preserve">8.48330879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77110767364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58664512634277</t>
+    <t xml:space="preserve">8.77110862731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58664608001709</t>
   </si>
   <si>
     <t xml:space="preserve">8.47944641113281</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71799182891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65907955169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75565624237061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71412754058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82132625579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94784355163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01448059082031</t>
+    <t xml:space="preserve">8.71799087524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65907764434814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75565528869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71412658691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82132720947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94784450531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01448154449463</t>
   </si>
   <si>
     <t xml:space="preserve">9.03959083557129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06083869934082</t>
+    <t xml:space="preserve">9.0608377456665</t>
   </si>
   <si>
     <t xml:space="preserve">8.85319709777832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94011783599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01641368865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05117988586426</t>
+    <t xml:space="preserve">8.94011688232422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01641464233398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05118083953857</t>
   </si>
   <si>
     <t xml:space="preserve">8.80587577819824</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08884525299072</t>
+    <t xml:space="preserve">9.08884620666504</t>
   </si>
   <si>
     <t xml:space="preserve">9.01158428192139</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99999523162842</t>
+    <t xml:space="preserve">8.99999618530273</t>
   </si>
   <si>
     <t xml:space="preserve">9.04828357696533</t>
@@ -2621,10 +2621,10 @@
     <t xml:space="preserve">9.04635143280029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02896881103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95460510253906</t>
+    <t xml:space="preserve">9.02896785736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95460414886475</t>
   </si>
   <si>
     <t xml:space="preserve">8.99613094329834</t>
@@ -2633,16 +2633,16 @@
     <t xml:space="preserve">8.9719877243042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04441928863525</t>
+    <t xml:space="preserve">9.04442024230957</t>
   </si>
   <si>
     <t xml:space="preserve">9.21342945098877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23853969573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1747989654541</t>
+    <t xml:space="preserve">9.23854064941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17479991912842</t>
   </si>
   <si>
     <t xml:space="preserve">9.06180381774902</t>
@@ -2654,7 +2654,7 @@
     <t xml:space="preserve">9.0318660736084</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07629013061523</t>
+    <t xml:space="preserve">9.07629108428955</t>
   </si>
   <si>
     <t xml:space="preserve">8.80008220672607</t>
@@ -2669,13 +2669,13 @@
     <t xml:space="preserve">8.74020385742188</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88893222808838</t>
+    <t xml:space="preserve">8.88893127441406</t>
   </si>
   <si>
     <t xml:space="preserve">8.66294193267822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50262355804443</t>
+    <t xml:space="preserve">8.50262451171875</t>
   </si>
   <si>
     <t xml:space="preserve">8.65714740753174</t>
@@ -2684,10 +2684,10 @@
     <t xml:space="preserve">8.51034927368164</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59727096557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76724529266357</t>
+    <t xml:space="preserve">8.59727001190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76724433898926</t>
   </si>
   <si>
     <t xml:space="preserve">8.89086437225342</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">9.24626541137695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26171779632568</t>
+    <t xml:space="preserve">9.26171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.51281833648682</t>
@@ -2708,28 +2708,28 @@
     <t xml:space="preserve">9.35443115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29841804504395</t>
+    <t xml:space="preserve">9.29841709136963</t>
   </si>
   <si>
     <t xml:space="preserve">9.44328308105469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4316930770874</t>
+    <t xml:space="preserve">9.43169403076172</t>
   </si>
   <si>
     <t xml:space="preserve">9.25012874603271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13230514526367</t>
+    <t xml:space="preserve">9.13230609893799</t>
   </si>
   <si>
     <t xml:space="preserve">9.22501850128174</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06856632232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19411468505859</t>
+    <t xml:space="preserve">9.06856441497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19411563873291</t>
   </si>
   <si>
     <t xml:space="preserve">9.17286777496338</t>
@@ -2741,40 +2741,40 @@
     <t xml:space="preserve">9.36215877532959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12650966644287</t>
+    <t xml:space="preserve">9.12651062011719</t>
   </si>
   <si>
     <t xml:space="preserve">9.1477575302124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13037490844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15934753417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12264919281006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0048246383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13616847991943</t>
+    <t xml:space="preserve">9.13037395477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15934658050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12264823913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00482368469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13616752624512</t>
   </si>
   <si>
     <t xml:space="preserve">9.05890655517578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04538536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8367805480957</t>
+    <t xml:space="preserve">9.04538631439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83677959442139</t>
   </si>
   <si>
     <t xml:space="preserve">8.87347984313965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95267295837402</t>
+    <t xml:space="preserve">8.95267200469971</t>
   </si>
   <si>
     <t xml:space="preserve">8.9391508102417</t>
@@ -2783,13 +2783,13 @@
     <t xml:space="preserve">8.86961650848389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88120555877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96619319915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13809871673584</t>
+    <t xml:space="preserve">8.88120651245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96619415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13809967041016</t>
   </si>
   <si>
     <t xml:space="preserve">9.02027606964111</t>
@@ -2813,16 +2813,16 @@
     <t xml:space="preserve">8.42149925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38093948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47365283966064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42343139648438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4253625869751</t>
+    <t xml:space="preserve">8.38093852996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47365188598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42343044281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42536354064941</t>
   </si>
   <si>
     <t xml:space="preserve">8.5470495223999</t>
@@ -2831,13 +2831,13 @@
     <t xml:space="preserve">8.49296569824219</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58568096160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51228141784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5064868927002</t>
+    <t xml:space="preserve">8.58568000793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.512282371521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50648784637451</t>
   </si>
   <si>
     <t xml:space="preserve">8.63590049743652</t>
@@ -2846,10 +2846,10 @@
     <t xml:space="preserve">8.5953369140625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65328502655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57215976715088</t>
+    <t xml:space="preserve">8.65328407287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57215881347656</t>
   </si>
   <si>
     <t xml:space="preserve">8.57795429229736</t>
@@ -2861,10 +2861,10 @@
     <t xml:space="preserve">8.86768436431885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94108295440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3370475769043</t>
+    <t xml:space="preserve">8.94108390808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33704853057861</t>
   </si>
   <si>
     <t xml:space="preserve">9.31773281097412</t>
@@ -2873,16 +2873,16 @@
     <t xml:space="preserve">9.40272045135498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34477519989014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38533592224121</t>
+    <t xml:space="preserve">9.3447732925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38533687591553</t>
   </si>
   <si>
     <t xml:space="preserve">9.44521331787109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58235359191895</t>
+    <t xml:space="preserve">9.58235263824463</t>
   </si>
   <si>
     <t xml:space="preserve">9.42976093292236</t>
@@ -2903,10 +2903,10 @@
     <t xml:space="preserve">9.3158016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34091186523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05697441101074</t>
+    <t xml:space="preserve">9.34091091156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05697536468506</t>
   </si>
   <si>
     <t xml:space="preserve">9.19218254089355</t>
@@ -2915,28 +2915,28 @@
     <t xml:space="preserve">9.16320991516113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04924964904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26751136779785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16900444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36795234680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5244083404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76391792297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48963832855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46839237213135</t>
+    <t xml:space="preserve">9.04924869537354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26751232147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1690034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36795330047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52440738677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76391696929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48963928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46839332580566</t>
   </si>
   <si>
     <t xml:space="preserve">9.38726806640625</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">9.25978755950928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24240207672119</t>
+    <t xml:space="preserve">9.24240303039551</t>
   </si>
   <si>
     <t xml:space="preserve">9.26364994049072</t>
@@ -2963,13 +2963,13 @@
     <t xml:space="preserve">9.28682804107666</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35056972503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23081398010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39885807037354</t>
+    <t xml:space="preserve">9.3505687713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23081302642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39885711669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.32932090759277</t>
@@ -2978,7 +2978,7 @@
     <t xml:space="preserve">9.4645299911499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41624069213867</t>
+    <t xml:space="preserve">9.41624164581299</t>
   </si>
   <si>
     <t xml:space="preserve">9.63836765289307</t>
@@ -2987,16 +2987,16 @@
     <t xml:space="preserve">9.47225379943848</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56496906280518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64416313171387</t>
+    <t xml:space="preserve">9.56497001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64416217803955</t>
   </si>
   <si>
     <t xml:space="preserve">9.76943683624268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55384922027588</t>
+    <t xml:space="preserve">9.55384826660156</t>
   </si>
   <si>
     <t xml:space="preserve">9.73544692993164</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">9.83255958557129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70340061187744</t>
+    <t xml:space="preserve">9.70339965820312</t>
   </si>
   <si>
     <t xml:space="preserve">9.62959575653076</t>
@@ -3020,10 +3020,10 @@
     <t xml:space="preserve">9.63348007202148</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8811149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0025053024292</t>
+    <t xml:space="preserve">9.88111591339111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0025043487549</t>
   </si>
   <si>
     <t xml:space="preserve">10.0947618484497</t>
@@ -3038,19 +3038,19 @@
     <t xml:space="preserve">9.7742919921875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86654758453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82284736633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81313610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82770347595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79856872558594</t>
+    <t xml:space="preserve">9.86654853820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82284832000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81313705444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82770252227783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79856967926025</t>
   </si>
   <si>
     <t xml:space="preserve">9.79371452331543</t>
@@ -3062,34 +3062,34 @@
     <t xml:space="preserve">10.1675939559937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2355728149414</t>
+    <t xml:space="preserve">10.2355718612671</t>
   </si>
   <si>
     <t xml:space="preserve">10.254994392395</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1870174407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.14817237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2307176589966</t>
+    <t xml:space="preserve">10.1870164871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1481704711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2307167053223</t>
   </si>
   <si>
     <t xml:space="preserve">10.2792730331421</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2744178771973</t>
+    <t xml:space="preserve">10.2744169235229</t>
   </si>
   <si>
     <t xml:space="preserve">10.3132619857788</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3909502029419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5754632949829</t>
+    <t xml:space="preserve">10.3909511566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5754642486572</t>
   </si>
   <si>
     <t xml:space="preserve">10.6337299346924</t>
@@ -3098,31 +3098,31 @@
     <t xml:space="preserve">10.8133869171143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8182420730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8328094482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8230991363525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8570871353149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7551202774048</t>
+    <t xml:space="preserve">10.8182439804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8328084945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8230981826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8570880889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7551193237305</t>
   </si>
   <si>
     <t xml:space="preserve">10.7454080581665</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7842540740967</t>
+    <t xml:space="preserve">10.7842531204224</t>
   </si>
   <si>
     <t xml:space="preserve">11.0852994918823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0755882263184</t>
+    <t xml:space="preserve">11.0755891799927</t>
   </si>
   <si>
     <t xml:space="preserve">11.0610218048096</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">11.0027551651001</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9104986190796</t>
+    <t xml:space="preserve">10.9104976654053</t>
   </si>
   <si>
     <t xml:space="preserve">10.891077041626</t>
@@ -3146,10 +3146,10 @@
     <t xml:space="preserve">10.997899055481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8279542922974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9541988372803</t>
+    <t xml:space="preserve">10.827953338623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.954197883606</t>
   </si>
   <si>
     <t xml:space="preserve">10.9784774780273</t>
@@ -3161,19 +3161,19 @@
     <t xml:space="preserve">10.6531534194946</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7162752151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9930429458618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1629886627197</t>
+    <t xml:space="preserve">10.7162761688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9930438995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1629905700684</t>
   </si>
   <si>
     <t xml:space="preserve">11.0513105392456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4009132385254</t>
+    <t xml:space="preserve">11.4009113311768</t>
   </si>
   <si>
     <t xml:space="preserve">11.4688911437988</t>
@@ -3182,10 +3182,10 @@
     <t xml:space="preserve">11.4931688308716</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5174465179443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5951366424561</t>
+    <t xml:space="preserve">11.51744556427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5951356887817</t>
   </si>
   <si>
     <t xml:space="preserve">11.561146736145</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">11.5028800964355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6048460006714</t>
+    <t xml:space="preserve">11.60484790802</t>
   </si>
   <si>
     <t xml:space="preserve">11.5805702209473</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">11.5660028457642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6097030639648</t>
+    <t xml:space="preserve">11.6097040176392</t>
   </si>
   <si>
     <t xml:space="preserve">11.721381187439</t>
@@ -3215,7 +3215,7 @@
     <t xml:space="preserve">11.7456588745117</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6922473907471</t>
+    <t xml:space="preserve">11.6922483444214</t>
   </si>
   <si>
     <t xml:space="preserve">11.6825370788574</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">11.2552452087402</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4834575653076</t>
+    <t xml:space="preserve">11.4834585189819</t>
   </si>
   <si>
     <t xml:space="preserve">11.4251909255981</t>
@@ -3239,16 +3239,16 @@
     <t xml:space="preserve">11.3669233322144</t>
   </si>
   <si>
-    <t xml:space="preserve">11.332935333252</t>
+    <t xml:space="preserve">11.3329343795776</t>
   </si>
   <si>
     <t xml:space="preserve">11.3717794418335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5902805328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6971025466919</t>
+    <t xml:space="preserve">11.5902814865112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6971035003662</t>
   </si>
   <si>
     <t xml:space="preserve">11.570858001709</t>
@@ -3257,19 +3257,19 @@
     <t xml:space="preserve">11.5757141113281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5125904083252</t>
+    <t xml:space="preserve">11.5125913619995</t>
   </si>
   <si>
     <t xml:space="preserve">11.410623550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5514373779297</t>
+    <t xml:space="preserve">11.5514354705811</t>
   </si>
   <si>
     <t xml:space="preserve">11.7068157196045</t>
   </si>
   <si>
-    <t xml:space="preserve">11.949595451355</t>
+    <t xml:space="preserve">11.9495944976807</t>
   </si>
   <si>
     <t xml:space="preserve">11.9301710128784</t>
@@ -3281,103 +3281,103 @@
     <t xml:space="preserve">11.7602262496948</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8087816238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8282041549683</t>
+    <t xml:space="preserve">11.8087825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8282060623169</t>
   </si>
   <si>
     <t xml:space="preserve">11.7505159378052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9253149032593</t>
+    <t xml:space="preserve">11.9253168106079</t>
   </si>
   <si>
     <t xml:space="preserve">12.0175714492798</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0564155578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0369958877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1875171661377</t>
+    <t xml:space="preserve">12.0564165115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.036994934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.187518119812</t>
   </si>
   <si>
     <t xml:space="preserve">12.1486730575562</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3865957260132</t>
+    <t xml:space="preserve">12.3865966796875</t>
   </si>
   <si>
     <t xml:space="preserve">12.5565423965454</t>
   </si>
   <si>
-    <t xml:space="preserve">12.425440788269</t>
+    <t xml:space="preserve">12.4254417419434</t>
   </si>
   <si>
     <t xml:space="preserve">12.5274076461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5322647094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5662517547607</t>
+    <t xml:space="preserve">12.5322637557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5662527084351</t>
   </si>
   <si>
     <t xml:space="preserve">11.9350271224976</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0127153396606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0758399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1729516983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3331842422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3137636184692</t>
+    <t xml:space="preserve">12.0127172470093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0758390426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1729507446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3331851959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3137626647949</t>
   </si>
   <si>
     <t xml:space="preserve">12.4205856323242</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3040523529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4108743667603</t>
+    <t xml:space="preserve">12.304051399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4108734130859</t>
   </si>
   <si>
     <t xml:space="preserve">12.444863319397</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4157295227051</t>
+    <t xml:space="preserve">12.4157304763794</t>
   </si>
   <si>
     <t xml:space="preserve">12.5468311309814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6439428329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7750425338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9644107818604</t>
+    <t xml:space="preserve">12.6439437866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7750434875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.964412689209</t>
   </si>
   <si>
     <t xml:space="preserve">12.9595556259155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9401321411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0760898590088</t>
+    <t xml:space="preserve">12.9401330947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0760889053345</t>
   </si>
   <si>
     <t xml:space="preserve">12.5808200836182</t>
@@ -3389,7 +3389,7 @@
     <t xml:space="preserve">12.9109992980957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4837074279785</t>
+    <t xml:space="preserve">12.4837083816528</t>
   </si>
   <si>
     <t xml:space="preserve">12.7070646286011</t>
@@ -3398,46 +3398,46 @@
     <t xml:space="preserve">12.4982748031616</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4739971160889</t>
+    <t xml:space="preserve">12.4739980697632</t>
   </si>
   <si>
     <t xml:space="preserve">12.3428955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">12.639087677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8721542358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6099519729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5856761932373</t>
+    <t xml:space="preserve">12.6390867233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8721551895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6099529266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.585675239563</t>
   </si>
   <si>
     <t xml:space="preserve">12.3768854141235</t>
   </si>
   <si>
-    <t xml:space="preserve">12.488564491272</t>
+    <t xml:space="preserve">12.4885625839233</t>
   </si>
   <si>
     <t xml:space="preserve">12.284628868103</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2797737121582</t>
+    <t xml:space="preserve">12.2797746658325</t>
   </si>
   <si>
     <t xml:space="preserve">12.2020835876465</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4400091171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3720293045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4351530075073</t>
+    <t xml:space="preserve">12.4400081634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3720302581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.435152053833</t>
   </si>
   <si>
     <t xml:space="preserve">12.3963088989258</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">11.6728258132935</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6388368606567</t>
+    <t xml:space="preserve">11.6388359069824</t>
   </si>
   <si>
     <t xml:space="preserve">11.4397573471069</t>
@@ -3461,49 +3461,49 @@
     <t xml:space="preserve">11.1532783508301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2164001464844</t>
+    <t xml:space="preserve">11.2164011001587</t>
   </si>
   <si>
     <t xml:space="preserve">11.0804433822632</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0658779144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6968545913696</t>
+    <t xml:space="preserve">11.065878868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6968536376953</t>
   </si>
   <si>
     <t xml:space="preserve">10.6434421539307</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6191635131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5171976089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7696866989136</t>
+    <t xml:space="preserve">10.6191644668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5171957015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7696876525879</t>
   </si>
   <si>
     <t xml:space="preserve">10.9833326339722</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8619432449341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7114200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5269069671631</t>
+    <t xml:space="preserve">10.8619422912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7114191055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5269079208374</t>
   </si>
   <si>
     <t xml:space="preserve">10.44921875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5317630767822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4880619049072</t>
+    <t xml:space="preserve">10.5317640304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4880638122559</t>
   </si>
   <si>
     <t xml:space="preserve">10.3375406265259</t>
@@ -3515,7 +3515,7 @@
     <t xml:space="preserve">10.1821613311768</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1918725967407</t>
+    <t xml:space="preserve">10.1918716430664</t>
   </si>
   <si>
     <t xml:space="preserve">10.2647047042847</t>
@@ -3524,16 +3524,16 @@
     <t xml:space="preserve">9.95880508422852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02556133270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18870735168457</t>
+    <t xml:space="preserve">9.02556037902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18870830535889</t>
   </si>
   <si>
     <t xml:space="preserve">9.4664478302002</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04304218292236</t>
+    <t xml:space="preserve">9.04304122924805</t>
   </si>
   <si>
     <t xml:space="preserve">9.04498291015625</t>
@@ -3542,7 +3542,7 @@
     <t xml:space="preserve">9.06246280670166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84299182891846</t>
+    <t xml:space="preserve">8.84299087524414</t>
   </si>
   <si>
     <t xml:space="preserve">8.83910655975342</t>
@@ -3551,19 +3551,19 @@
     <t xml:space="preserve">8.5438871383667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14403629302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9906005859375</t>
+    <t xml:space="preserve">9.1440372467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99060153961182</t>
   </si>
   <si>
     <t xml:space="preserve">8.95369815826416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99836921691895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0313892364502</t>
+    <t xml:space="preserve">8.99837017059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03138732910156</t>
   </si>
   <si>
     <t xml:space="preserve">9.58492469787598</t>
@@ -3572,28 +3572,28 @@
     <t xml:space="preserve">9.55190658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75001430511475</t>
+    <t xml:space="preserve">9.75001335144043</t>
   </si>
   <si>
     <t xml:space="preserve">9.621826171875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68203639984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63736438751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62571144104004</t>
+    <t xml:space="preserve">9.68203735351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63736534118652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62571048736572</t>
   </si>
   <si>
     <t xml:space="preserve">10.0801935195923</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2598495483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2501392364502</t>
+    <t xml:space="preserve">10.2598505020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2501401901245</t>
   </si>
   <si>
     <t xml:space="preserve">10.4200839996338</t>
@@ -3602,13 +3602,13 @@
     <t xml:space="preserve">10.3860950469971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5074853897095</t>
+    <t xml:space="preserve">10.5074844360352</t>
   </si>
   <si>
     <t xml:space="preserve">10.4346513748169</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4152297973633</t>
+    <t xml:space="preserve">10.415228843689</t>
   </si>
   <si>
     <t xml:space="preserve">10.3278293609619</t>
@@ -5954,7 +5954,16 @@
     <t xml:space="preserve">5.95800018310547</t>
   </si>
   <si>
+    <t xml:space="preserve">5.96999979019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65000009536743</t>
+  </si>
+  <si>
     <t xml:space="preserve">5.69399976730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81400012969971</t>
   </si>
 </sst>
 </file>
@@ -71397,27 +71406,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6918634259</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
-        <v>6175972</v>
+        <v>5572053</v>
       </c>
       <c r="C2505" t="n">
-        <v>5.71000003814697</v>
+        <v>5.99399995803833</v>
       </c>
       <c r="D2505" t="n">
-        <v>5.55800008773804</v>
+        <v>5.86199998855591</v>
       </c>
       <c r="E2505" t="n">
-        <v>5.67000007629395</v>
+        <v>5.92199993133545</v>
       </c>
       <c r="F2505" t="n">
-        <v>5.69399976730347</v>
+        <v>5.96999979019165</v>
       </c>
       <c r="G2505" t="s">
         <v>1980</v>
       </c>
       <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>10414835</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>5.95599985122681</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>5.63199996948242</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>5.92199993133545</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>5.65000009536743</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>1981</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
+        <v>6175972</v>
+      </c>
+      <c r="C2507" t="n">
+        <v>5.71000003814697</v>
+      </c>
+      <c r="D2507" t="n">
+        <v>5.55800008773804</v>
+      </c>
+      <c r="E2507" t="n">
+        <v>5.67000007629395</v>
+      </c>
+      <c r="F2507" t="n">
+        <v>5.69399976730347</v>
+      </c>
+      <c r="G2507" t="s">
+        <v>1982</v>
+      </c>
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6928240741</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>5926768</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>5.89599990844727</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>5.73999977111816</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>5.73999977111816</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>5.81400012969971</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>1983</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1986" uniqueCount="1986">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1987" uniqueCount="1987">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59865689277649</t>
+    <t xml:space="preserve">3.59865665435791</t>
   </si>
   <si>
     <t xml:space="preserve">CPR.MI</t>
@@ -47,40 +47,40 @@
     <t xml:space="preserve">3.65898251533508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60329675674438</t>
+    <t xml:space="preserve">3.60329699516296</t>
   </si>
   <si>
     <t xml:space="preserve">3.51976919174194</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51048827171326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54993224143982</t>
+    <t xml:space="preserve">3.51048851013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54993200302124</t>
   </si>
   <si>
     <t xml:space="preserve">3.62881970405579</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68450474739075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57313418388367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52672958374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48264598846436</t>
+    <t xml:space="preserve">3.68450450897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57313394546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52673006057739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48264575004578</t>
   </si>
   <si>
     <t xml:space="preserve">3.5661735534668</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43392109870911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50584745407104</t>
+    <t xml:space="preserve">3.43392133712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50584769248962</t>
   </si>
   <si>
     <t xml:space="preserve">3.56153345108032</t>
@@ -89,25 +89,25 @@
     <t xml:space="preserve">3.64274072647095</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66594314575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56849408149719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74250984191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72162842750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70770668983459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47104501724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44320201873779</t>
+    <t xml:space="preserve">3.66594290733337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56849431991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74250960350037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72162866592407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70770692825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47104477882385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44320225715637</t>
   </si>
   <si>
     <t xml:space="preserve">3.28078699111938</t>
@@ -119,163 +119,163 @@
     <t xml:space="preserve">3.40839862823486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22046136856079</t>
+    <t xml:space="preserve">3.22046089172363</t>
   </si>
   <si>
     <t xml:space="preserve">3.26918601989746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32487082481384</t>
+    <t xml:space="preserve">3.32487106323242</t>
   </si>
   <si>
     <t xml:space="preserve">3.24366331100464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32255077362061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28774738311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31791067123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36663484573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36199450492859</t>
+    <t xml:space="preserve">3.32255053520203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28774785995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31791019439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36663508415222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36199426651001</t>
   </si>
   <si>
     <t xml:space="preserve">3.40607857704163</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38287663459778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36431503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53137016296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60561680793762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61257767677307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5638530254364</t>
+    <t xml:space="preserve">3.3828763961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36431479454041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53137040138245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6056170463562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61257791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56385326385498</t>
   </si>
   <si>
     <t xml:space="preserve">3.61489820480347</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63810014724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6891450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476301193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.955970287323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00701475143433</t>
+    <t xml:space="preserve">3.63810038566589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68914484977722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476277351379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95596981048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00701570510864</t>
   </si>
   <si>
     <t xml:space="preserve">4.04877901077271</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03485727310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04181909561157</t>
+    <t xml:space="preserve">4.03485774993896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04181814193726</t>
   </si>
   <si>
     <t xml:space="preserve">4.03717756271362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05109882354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01861524581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09286260604858</t>
+    <t xml:space="preserve">4.05109930038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01861667633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09286308288574</t>
   </si>
   <si>
     <t xml:space="preserve">4.07662153244019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03949785232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08358240127563</t>
+    <t xml:space="preserve">4.0394983291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08358144760132</t>
   </si>
   <si>
     <t xml:space="preserve">4.02325677871704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00005483627319</t>
+    <t xml:space="preserve">4.00005435943604</t>
   </si>
   <si>
     <t xml:space="preserve">4.06037950515747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9954137802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94436836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97453141212463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00237321853638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93740820884705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94668960571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03021669387817</t>
+    <t xml:space="preserve">3.99541306495667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94436860084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97453236579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00237417221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93740797042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94668936729431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03021621704102</t>
   </si>
   <si>
     <t xml:space="preserve">4.05341911315918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0093355178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95829081535339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98613238334656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02557611465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96989130973816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91188645362854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89796447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87708282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9142062664032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92812705039978</t>
+    <t xml:space="preserve">4.00933504104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95828938484192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98613309860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0255765914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96989226341248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91188621520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89796423912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87708210945129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91420531272888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92812728881836</t>
   </si>
   <si>
     <t xml:space="preserve">3.95132970809937</t>
@@ -284,43 +284,43 @@
     <t xml:space="preserve">4.06734085083008</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08126258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99309277534485</t>
+    <t xml:space="preserve">4.08126163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99309325218201</t>
   </si>
   <si>
     <t xml:space="preserve">3.96757173538208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98149228096008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96293091773987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88868379592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89332389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79587507247925</t>
+    <t xml:space="preserve">3.98149156570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96293044090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88868427276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89332413673401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79587531089783</t>
   </si>
   <si>
     <t xml:space="preserve">3.89309930801392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02677822113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08540916442871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07602787017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08306264877319</t>
+    <t xml:space="preserve">4.02677726745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08540868759155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07602691650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08306360244751</t>
   </si>
   <si>
     <t xml:space="preserve">4.09948015213013</t>
@@ -329,13 +329,13 @@
     <t xml:space="preserve">4.07368230819702</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09009981155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10182571411133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0877537727356</t>
+    <t xml:space="preserve">4.0900993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10182523727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08775424957275</t>
   </si>
   <si>
     <t xml:space="preserve">4.1135516166687</t>
@@ -347,22 +347,22 @@
     <t xml:space="preserve">4.01974201202393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90482568740845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85557556152344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85791993141174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86495614051819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8719916343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86964631080627</t>
+    <t xml:space="preserve">3.90482544898987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85557532310486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8579204082489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86495590209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87199187278748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86964654922485</t>
   </si>
   <si>
     <t xml:space="preserve">4.00567054748535</t>
@@ -374,64 +374,64 @@
     <t xml:space="preserve">3.95876526832581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05961036682129</t>
+    <t xml:space="preserve">4.05961084365845</t>
   </si>
   <si>
     <t xml:space="preserve">3.88606333732605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88840818405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04084873199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16514682769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15576553344727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14872980117798</t>
+    <t xml:space="preserve">3.88840866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04084968566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16514730453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15576505661011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14873075485229</t>
   </si>
   <si>
     <t xml:space="preserve">4.13231325149536</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00332450866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04319429397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16045618057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15811109542847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1158971786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06899118423462</t>
+    <t xml:space="preserve">4.00332546234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04319381713867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16045665740967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15811157226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11589622497559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06899261474609</t>
   </si>
   <si>
     <t xml:space="preserve">4.13465881347656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14169454574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18390846252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16280126571655</t>
+    <t xml:space="preserve">4.14169406890869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18390893936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16280174255371</t>
   </si>
   <si>
     <t xml:space="preserve">4.21908760070801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29179000854492</t>
+    <t xml:space="preserve">4.29178905487061</t>
   </si>
   <si>
     <t xml:space="preserve">4.29648065567017</t>
@@ -440,19 +440,19 @@
     <t xml:space="preserve">4.31055116653442</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28709983825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3316593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33869504928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54038524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51458740234375</t>
+    <t xml:space="preserve">4.28709936141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33165884017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33869457244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54038619995117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51458787918091</t>
   </si>
   <si>
     <t xml:space="preserve">4.5216236114502</t>
@@ -467,109 +467,109 @@
     <t xml:space="preserve">4.45595598220825</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66233730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67171907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58963441848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55914783477783</t>
+    <t xml:space="preserve">4.66233682632446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67171859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58963537216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55914688110352</t>
   </si>
   <si>
     <t xml:space="preserve">4.56383752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54976558685303</t>
+    <t xml:space="preserve">4.54976606369019</t>
   </si>
   <si>
     <t xml:space="preserve">4.60370635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59667110443115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57321929931641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62012386322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59432554244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65061235427856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57556343078613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7045521736145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67406368255615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70924186706543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60136127471924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48644495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4653377532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39967107772827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43250370025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50520658493042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.491135597229</t>
+    <t xml:space="preserve">4.59667062759399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57321786880493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62012434005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59432649612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65061187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57556438446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70455169677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67406415939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70924282073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6013617515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48644399642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46533727645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39967060089111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43250417709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50520610809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49113607406616</t>
   </si>
   <si>
     <t xml:space="preserve">4.51693248748779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50286197662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48879051208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65295743942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66468286514282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73269510269165</t>
+    <t xml:space="preserve">4.50286149978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48878955841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65295696258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66468238830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73269557952881</t>
   </si>
   <si>
     <t xml:space="preserve">4.71393251419067</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69048118591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58729028701782</t>
+    <t xml:space="preserve">4.69048070907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58728981018066</t>
   </si>
   <si>
     <t xml:space="preserve">4.568528175354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47471857070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44657516479492</t>
+    <t xml:space="preserve">4.47471952438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44657564163208</t>
   </si>
   <si>
     <t xml:space="preserve">4.54742097854614</t>
@@ -584,16 +584,16 @@
     <t xml:space="preserve">4.52631378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36683797836304</t>
+    <t xml:space="preserve">4.36683750152588</t>
   </si>
   <si>
     <t xml:space="preserve">4.37152767181396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33400440216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3293137550354</t>
+    <t xml:space="preserve">4.33400392532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32931327819824</t>
   </si>
   <si>
     <t xml:space="preserve">4.3058614730835</t>
@@ -605,40 +605,40 @@
     <t xml:space="preserve">4.25661087036133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20736074447632</t>
+    <t xml:space="preserve">4.20736122131348</t>
   </si>
   <si>
     <t xml:space="preserve">4.09478950500488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24253940582275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20267009735107</t>
+    <t xml:space="preserve">4.24254035949707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20267057418823</t>
   </si>
   <si>
     <t xml:space="preserve">3.95642066001892</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9540753364563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0338134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12527847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01739645004272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12996864318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1721830368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2120509147644</t>
+    <t xml:space="preserve">3.95407509803772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03381395339966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12527799606323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01739692687988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12996816635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17218255996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21205139160156</t>
   </si>
   <si>
     <t xml:space="preserve">4.18859958648682</t>
@@ -647,64 +647,64 @@
     <t xml:space="preserve">4.24957609176636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20501613616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26833820343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22846794128418</t>
+    <t xml:space="preserve">4.20501565933228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26833772659302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22846841812134</t>
   </si>
   <si>
     <t xml:space="preserve">4.247230052948</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31993293762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36449289321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28944444656372</t>
+    <t xml:space="preserve">4.31993246078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449193954468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28944492340088</t>
   </si>
   <si>
     <t xml:space="preserve">4.27771854400635</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30117034912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32227802276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35745668411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34807586669922</t>
+    <t xml:space="preserve">4.30117082595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32227849960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35745573043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34807538986206</t>
   </si>
   <si>
     <t xml:space="preserve">4.34338521957397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39028930664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36214685440063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32462358474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39732503890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37387275695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36918258666992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47002696990967</t>
+    <t xml:space="preserve">4.39028978347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36214780807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32462310791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39732599258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37387371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36918210983276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47002744674683</t>
   </si>
   <si>
     <t xml:space="preserve">4.45830202102661</t>
@@ -713,37 +713,37 @@
     <t xml:space="preserve">4.42546892166138</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43484926223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46768236160278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40201663970947</t>
+    <t xml:space="preserve">4.43484973907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46768283843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40201616287231</t>
   </si>
   <si>
     <t xml:space="preserve">4.3527660369873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38559913635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43954086303711</t>
+    <t xml:space="preserve">4.3855996131897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43954038619995</t>
   </si>
   <si>
     <t xml:space="preserve">4.4301586151123</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49348115921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47237300872803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52396965026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5427303314209</t>
+    <t xml:space="preserve">4.49348068237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47237348556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5239691734314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54273080825806</t>
   </si>
   <si>
     <t xml:space="preserve">4.53804063796997</t>
@@ -752,70 +752,70 @@
     <t xml:space="preserve">4.54507541656494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58260011672974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57790946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55211114883423</t>
+    <t xml:space="preserve">4.58259916305542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57790994644165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55211210250854</t>
   </si>
   <si>
     <t xml:space="preserve">4.57087373733521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53569459915161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50755214691162</t>
+    <t xml:space="preserve">4.53569412231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50755167007446</t>
   </si>
   <si>
     <t xml:space="preserve">4.58494424819946</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65530300140381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74207592010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75614738464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80774259567261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83119535446167</t>
+    <t xml:space="preserve">4.65530204772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74207544326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75614786148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80774211883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83119440078735</t>
   </si>
   <si>
     <t xml:space="preserve">4.8968620300293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94845676422119</t>
+    <t xml:space="preserve">4.94845724105835</t>
   </si>
   <si>
     <t xml:space="preserve">5.09855270385742</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05164861679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12200450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04695701599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05633783340454</t>
+    <t xml:space="preserve">5.05164813995361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12200498580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04695749282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05633735656738</t>
   </si>
   <si>
     <t xml:space="preserve">4.99536228179932</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01881456375122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02819585800171</t>
+    <t xml:space="preserve">5.01881408691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02819538116455</t>
   </si>
   <si>
     <t xml:space="preserve">5.03288555145264</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">4.9390754699707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97659969329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92500448226929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96721935272217</t>
+    <t xml:space="preserve">4.97659921646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92500495910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96721887588501</t>
   </si>
   <si>
     <t xml:space="preserve">5.08917188644409</t>
@@ -839,37 +839,37 @@
     <t xml:space="preserve">5.17360019683838</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14545631408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15952825546265</t>
+    <t xml:space="preserve">5.14545726776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15952920913696</t>
   </si>
   <si>
     <t xml:space="preserve">5.09386157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16421985626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25333786010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18767213821411</t>
+    <t xml:space="preserve">5.16421937942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25333833694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18767166137695</t>
   </si>
   <si>
     <t xml:space="preserve">5.41750526428223</t>
   </si>
   <si>
-    <t xml:space="preserve">5.67079067230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60043382644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62388610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6614089012146</t>
+    <t xml:space="preserve">5.6707911491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60043430328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6238865852356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66140985488892</t>
   </si>
   <si>
     <t xml:space="preserve">5.68486213684082</t>
@@ -878,19 +878,19 @@
     <t xml:space="preserve">5.57698154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60512495040894</t>
+    <t xml:space="preserve">5.60512399673462</t>
   </si>
   <si>
     <t xml:space="preserve">5.72238636016846</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6940336227417</t>
+    <t xml:space="preserve">5.69403505325317</t>
   </si>
   <si>
     <t xml:space="preserve">5.74128770828247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76491451263428</t>
+    <t xml:space="preserve">5.76491403579712</t>
   </si>
   <si>
     <t xml:space="preserve">5.75073862075806</t>
@@ -899,73 +899,73 @@
     <t xml:space="preserve">5.8783221244812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86887216567993</t>
+    <t xml:space="preserve">5.86887168884277</t>
   </si>
   <si>
     <t xml:space="preserve">5.88304758071899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02008247375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9917311668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00118160247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9350266456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85942125320435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8027172088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75546407699585</t>
+    <t xml:space="preserve">6.02008295059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99173069000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00118112564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93502712249756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85942077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80271768569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75546360015869</t>
   </si>
   <si>
     <t xml:space="preserve">5.73183727264404</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84997034072876</t>
+    <t xml:space="preserve">5.84997081756592</t>
   </si>
   <si>
     <t xml:space="preserve">5.81216812133789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95865249633789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93030118942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98228073120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90194892883301</t>
+    <t xml:space="preserve">5.95865297317505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93030166625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98228025436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90194940567017</t>
   </si>
   <si>
     <t xml:space="preserve">5.91612529754639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91139936447144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83106899261475</t>
+    <t xml:space="preserve">5.91139984130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83106851577759</t>
   </si>
   <si>
     <t xml:space="preserve">5.88777303695679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78381586074829</t>
+    <t xml:space="preserve">5.78381538391113</t>
   </si>
   <si>
     <t xml:space="preserve">5.8074426651001</t>
   </si>
   <si>
-    <t xml:space="preserve">5.84524536132812</t>
+    <t xml:space="preserve">5.84524488449097</t>
   </si>
   <si>
     <t xml:space="preserve">5.77436590194702</t>
@@ -974,25 +974,25 @@
     <t xml:space="preserve">5.82634401321411</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82161855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85469627380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79326677322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8357949256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95392847061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9255747795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94447708129883</t>
+    <t xml:space="preserve">5.82161903381348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85469579696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79326581954956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.83579444885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95392799377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92557525634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94447755813599</t>
   </si>
   <si>
     <t xml:space="preserve">5.7790904045105</t>
@@ -1004,28 +1004,28 @@
     <t xml:space="preserve">5.71766042709351</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6515064239502</t>
+    <t xml:space="preserve">5.65150594711304</t>
   </si>
   <si>
     <t xml:space="preserve">5.66095685958862</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79799127578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76018953323364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69875955581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66568231582642</t>
+    <t xml:space="preserve">5.79799175262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76018857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69876050949097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6656813621521</t>
   </si>
   <si>
     <t xml:space="preserve">5.73656272888184</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78854131698608</t>
+    <t xml:space="preserve">5.78854036331177</t>
   </si>
   <si>
     <t xml:space="preserve">5.76964044570923</t>
@@ -1034,37 +1034,37 @@
     <t xml:space="preserve">5.89249897003174</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97282934188843</t>
+    <t xml:space="preserve">5.97283029556274</t>
   </si>
   <si>
     <t xml:space="preserve">6.15239238739014</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1476674079895</t>
+    <t xml:space="preserve">6.14766645431519</t>
   </si>
   <si>
     <t xml:space="preserve">6.28470182418823</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1382155418396</t>
+    <t xml:space="preserve">6.13821697235107</t>
   </si>
   <si>
     <t xml:space="preserve">6.12404012680054</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02953386306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10513782501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16656827926636</t>
+    <t xml:space="preserve">6.02953338623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10513925552368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1665678024292</t>
   </si>
   <si>
     <t xml:space="preserve">6.11458969116211</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31777858734131</t>
+    <t xml:space="preserve">6.31777954101562</t>
   </si>
   <si>
     <t xml:space="preserve">6.34140586853027</t>
@@ -1073,28 +1073,28 @@
     <t xml:space="preserve">6.4075608253479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50206804275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42173624038696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3083291053772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47844076156616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31305313110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33668088912964</t>
+    <t xml:space="preserve">6.50206756591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42173719406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30832815170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47843980789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31305360794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33668041229248</t>
   </si>
   <si>
     <t xml:space="preserve">6.37448263168335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17601919174194</t>
+    <t xml:space="preserve">6.17601871490479</t>
   </si>
   <si>
     <t xml:space="preserve">6.0909628868103</t>
@@ -1127,22 +1127,22 @@
     <t xml:space="preserve">6.06261110305786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18074417114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08151245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15711784362793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2138204574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24217414855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24689912796021</t>
+    <t xml:space="preserve">6.18074464797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08151197433472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15711736679077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21382141113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24217367172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24689865112305</t>
   </si>
   <si>
     <t xml:space="preserve">6.20909643173218</t>
@@ -1151,25 +1151,25 @@
     <t xml:space="preserve">6.22799777984619</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19964551925659</t>
+    <t xml:space="preserve">6.19964504241943</t>
   </si>
   <si>
     <t xml:space="preserve">6.12876558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07206153869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05788469314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13349056243896</t>
+    <t xml:space="preserve">6.07206106185913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05788564682007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13349103927612</t>
   </si>
   <si>
     <t xml:space="preserve">6.14294147491455</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0106315612793</t>
+    <t xml:space="preserve">6.01063251495361</t>
   </si>
   <si>
     <t xml:space="preserve">5.94920253753662</t>
@@ -1178,64 +1178,64 @@
     <t xml:space="preserve">5.97755479812622</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05316019058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99645662307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06733655929565</t>
+    <t xml:space="preserve">6.05316066741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99645566940308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0673360824585</t>
   </si>
   <si>
     <t xml:space="preserve">5.93975210189819</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71293497085571</t>
+    <t xml:space="preserve">5.71293544769287</t>
   </si>
   <si>
     <t xml:space="preserve">5.72711133956909</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92085027694702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5759015083313</t>
+    <t xml:space="preserve">5.92084980010986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57590103149414</t>
   </si>
   <si>
     <t xml:space="preserve">5.52864742279053</t>
   </si>
   <si>
-    <t xml:space="preserve">5.42941570281982</t>
+    <t xml:space="preserve">5.42941522598267</t>
   </si>
   <si>
     <t xml:space="preserve">5.50502061843872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.61370372772217</t>
+    <t xml:space="preserve">5.61370420455933</t>
   </si>
   <si>
     <t xml:space="preserve">5.63733053207397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04370927810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98700618743896</t>
+    <t xml:space="preserve">6.04370975494385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98700523376465</t>
   </si>
   <si>
     <t xml:space="preserve">6.01535749435425</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89722299575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81689310073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87359714508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86414575576782</t>
+    <t xml:space="preserve">5.89722442626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81689357757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87359762191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86414670944214</t>
   </si>
   <si>
     <t xml:space="preserve">5.9066743850708</t>
@@ -1244,13 +1244,13 @@
     <t xml:space="preserve">5.96810388565063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01550769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02027034759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99169301986694</t>
+    <t xml:space="preserve">6.01550722122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02027130126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9916934967041</t>
   </si>
   <si>
     <t xml:space="preserve">6.08218812942505</t>
@@ -1259,13 +1259,13 @@
     <t xml:space="preserve">6.20602226257324</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18697071075439</t>
+    <t xml:space="preserve">6.18697118759155</t>
   </si>
   <si>
     <t xml:space="preserve">6.08695030212402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07266235351562</t>
+    <t xml:space="preserve">6.07266187667847</t>
   </si>
   <si>
     <t xml:space="preserve">6.16315650939941</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">6.27270269393921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2536506652832</t>
+    <t xml:space="preserve">6.25365161895752</t>
   </si>
   <si>
     <t xml:space="preserve">6.13934230804443</t>
@@ -1283,7 +1283,7 @@
     <t xml:space="preserve">6.29175424575806</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38701200485229</t>
+    <t xml:space="preserve">6.38701105117798</t>
   </si>
   <si>
     <t xml:space="preserve">6.52513456344604</t>
@@ -1292,85 +1292,85 @@
     <t xml:space="preserve">6.5965781211853</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69183492660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69659805297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62039136886597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57276344299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50608253479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58228921890259</t>
+    <t xml:space="preserve">6.69183588027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69659852981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62039232254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57276391983032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5060830116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58228874206543</t>
   </si>
   <si>
     <t xml:space="preserve">6.65373229980469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71088647842407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82519626617432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.77280473709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82995843887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02523612976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92521572113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9204535484314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01094770431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96808195114136</t>
+    <t xml:space="preserve">6.71088695526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82519578933716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.77280378341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82995939254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0252366065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92521619796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92045307159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01094818115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9680814743042</t>
   </si>
   <si>
     <t xml:space="preserve">6.91092777252197</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01571083068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04905033111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09667921066284</t>
+    <t xml:space="preserve">7.01571035385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04905080795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0966796875</t>
   </si>
   <si>
     <t xml:space="preserve">7.17764854431152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28243160247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22051334381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23956537246704</t>
+    <t xml:space="preserve">7.28243112564087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22051429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2395658493042</t>
   </si>
   <si>
     <t xml:space="preserve">7.27766895294189</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12525653839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94903039932251</t>
+    <t xml:space="preserve">7.12525701522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94903087615967</t>
   </si>
   <si>
     <t xml:space="preserve">6.86806154251099</t>
@@ -1385,40 +1385,40 @@
     <t xml:space="preserve">7.06333923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97760725021362</t>
+    <t xml:space="preserve">6.97760772705078</t>
   </si>
   <si>
     <t xml:space="preserve">6.99189615249634</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0395245552063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02047300338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07762765884399</t>
+    <t xml:space="preserve">7.03952503204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02047348022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07762813568115</t>
   </si>
   <si>
     <t xml:space="preserve">7.18717432022095</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21098804473877</t>
+    <t xml:space="preserve">7.21098852157593</t>
   </si>
   <si>
     <t xml:space="preserve">7.41579151153564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29671955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26338052749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24432849884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27290678024292</t>
+    <t xml:space="preserve">7.29672002792358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26337957382202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24432802200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2729058265686</t>
   </si>
   <si>
     <t xml:space="preserve">7.30624580383301</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">7.1824107170105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25385427474976</t>
+    <t xml:space="preserve">7.25385332107544</t>
   </si>
   <si>
     <t xml:space="preserve">7.05857563018799</t>
@@ -1442,16 +1442,16 @@
     <t xml:space="preserve">7.1681227684021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90140199661255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94426727294922</t>
+    <t xml:space="preserve">6.90140151977539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94426774978638</t>
   </si>
   <si>
     <t xml:space="preserve">7.06810235977173</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98713350296021</t>
+    <t xml:space="preserve">6.98713302612305</t>
   </si>
   <si>
     <t xml:space="preserve">7.1300196647644</t>
@@ -1460,31 +1460,31 @@
     <t xml:space="preserve">6.87758636474609</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70612287521362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63944339752197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65849447250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32985734939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19649744033813</t>
+    <t xml:space="preserve">6.70612382888794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63944387435913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65849494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32985687255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19649648666382</t>
   </si>
   <si>
     <t xml:space="preserve">6.11552810668945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.04884815216064</t>
+    <t xml:space="preserve">6.04884767532349</t>
   </si>
   <si>
     <t xml:space="preserve">6.21554803848267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31556797027588</t>
+    <t xml:space="preserve">6.3155689239502</t>
   </si>
   <si>
     <t xml:space="preserve">6.33461999893188</t>
@@ -1496,16 +1496,16 @@
     <t xml:space="preserve">6.12505340576172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15363025665283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30604267120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35367202758789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47274303436279</t>
+    <t xml:space="preserve">6.15363073348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30604314804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35367155075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47274351119995</t>
   </si>
   <si>
     <t xml:space="preserve">6.46798038482666</t>
@@ -1514,13 +1514,13 @@
     <t xml:space="preserve">6.42987728118896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52989816665649</t>
+    <t xml:space="preserve">6.52989721298218</t>
   </si>
   <si>
     <t xml:space="preserve">6.76804161071777</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08239126205444</t>
+    <t xml:space="preserve">7.08239030838013</t>
   </si>
   <si>
     <t xml:space="preserve">7.11096811294556</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">7.12049341201782</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32529783248901</t>
+    <t xml:space="preserve">7.3252968788147</t>
   </si>
   <si>
     <t xml:space="preserve">7.31577110290527</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">7.15383434295654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04428768157959</t>
+    <t xml:space="preserve">7.04428720474243</t>
   </si>
   <si>
     <t xml:space="preserve">7.02999925613403</t>
@@ -1556,37 +1556,37 @@
     <t xml:space="preserve">7.36339998245239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14430809020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20622539520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32053422927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09191703796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98237037658691</t>
+    <t xml:space="preserve">7.14430856704712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20622587203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32053470611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09191656112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98237085342407</t>
   </si>
   <si>
     <t xml:space="preserve">7.44913196563721</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38245105743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33006048202515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.2157506942749</t>
+    <t xml:space="preserve">7.3824520111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33006000518799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21575117111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.33958625793457</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35387420654297</t>
+    <t xml:space="preserve">7.35387468338013</t>
   </si>
   <si>
     <t xml:space="preserve">7.55391502380371</t>
@@ -1595,10 +1595,10 @@
     <t xml:space="preserve">7.60630702972412</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46342039108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49199676513672</t>
+    <t xml:space="preserve">7.46342086791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49199771881104</t>
   </si>
   <si>
     <t xml:space="preserve">7.44436883926392</t>
@@ -1607,13 +1607,13 @@
     <t xml:space="preserve">7.42055463790894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62535810470581</t>
+    <t xml:space="preserve">7.62535858154297</t>
   </si>
   <si>
     <t xml:space="preserve">7.53010129928589</t>
   </si>
   <si>
-    <t xml:space="preserve">7.47294569015503</t>
+    <t xml:space="preserve">7.47294616699219</t>
   </si>
   <si>
     <t xml:space="preserve">7.4872350692749</t>
@@ -1622,61 +1622,61 @@
     <t xml:space="preserve">7.46818351745605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49676084518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.51581239700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61106967926025</t>
+    <t xml:space="preserve">7.49676036834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.51581192016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61107015609741</t>
   </si>
   <si>
     <t xml:space="preserve">7.56344127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64440965652466</t>
+    <t xml:space="preserve">7.64440870285034</t>
   </si>
   <si>
     <t xml:space="preserve">7.73490428924561</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80634593963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86826467514038</t>
+    <t xml:space="preserve">7.80634689331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86826515197754</t>
   </si>
   <si>
     <t xml:space="preserve">7.85873889923096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88731527328491</t>
+    <t xml:space="preserve">7.88731670379639</t>
   </si>
   <si>
     <t xml:space="preserve">7.92541885375977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95399713516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83492422103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98733854293823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01115131378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06354236602783</t>
+    <t xml:space="preserve">7.95399618148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83492517471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9873366355896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01114940643311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06354141235352</t>
   </si>
   <si>
     <t xml:space="preserve">7.53486394882202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.52057504653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54438972473145</t>
+    <t xml:space="preserve">7.52057552337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54438924789429</t>
   </si>
   <si>
     <t xml:space="preserve">7.62059545516968</t>
@@ -1688,22 +1688,22 @@
     <t xml:space="preserve">7.77776956558228</t>
   </si>
   <si>
-    <t xml:space="preserve">7.76824426651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90636825561523</t>
+    <t xml:space="preserve">7.76824378967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90636730194092</t>
   </si>
   <si>
     <t xml:space="preserve">8.03496551513672</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00638866424561</t>
+    <t xml:space="preserve">8.00638771057129</t>
   </si>
   <si>
     <t xml:space="preserve">8.04449081420898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06830596923828</t>
+    <t xml:space="preserve">8.06830501556396</t>
   </si>
   <si>
     <t xml:space="preserve">8.2016658782959</t>
@@ -1712,19 +1712,19 @@
     <t xml:space="preserve">8.32550048828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44457340240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33978939056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38265419006348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33502578735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27787208557129</t>
+    <t xml:space="preserve">8.44457244873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3397912979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38265514373779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33502674102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27787017822266</t>
   </si>
   <si>
     <t xml:space="preserve">8.23500633239746</t>
@@ -1733,31 +1733,31 @@
     <t xml:space="preserve">8.25882053375244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26358222961426</t>
+    <t xml:space="preserve">8.26358318328857</t>
   </si>
   <si>
     <t xml:space="preserve">8.16832542419434</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31121253967285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36836719512939</t>
+    <t xml:space="preserve">8.31121158599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36836624145508</t>
   </si>
   <si>
     <t xml:space="preserve">8.35407829284668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37789344787598</t>
+    <t xml:space="preserve">8.37789249420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.28739738464355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21119022369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22071647644043</t>
+    <t xml:space="preserve">8.21119213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22071838378906</t>
   </si>
   <si>
     <t xml:space="preserve">8.43150520324707</t>
@@ -1775,34 +1775,34 @@
     <t xml:space="preserve">8.48899173736572</t>
   </si>
   <si>
-    <t xml:space="preserve">8.60875797271729</t>
+    <t xml:space="preserve">8.60875701904297</t>
   </si>
   <si>
     <t xml:space="preserve">8.441086769104</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49857425689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48420143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6710376739502</t>
+    <t xml:space="preserve">8.49857330322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4842004776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67103672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.8147554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74289608001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83391857147217</t>
+    <t xml:space="preserve">8.74289417266846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83391761779785</t>
   </si>
   <si>
     <t xml:space="preserve">8.77643013000488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70936107635498</t>
+    <t xml:space="preserve">8.7093620300293</t>
   </si>
   <si>
     <t xml:space="preserve">8.6854076385498</t>
@@ -1814,34 +1814,34 @@
     <t xml:space="preserve">8.78122138977051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80996417999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77163887023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6518726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53689765930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37880802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37401866912842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40755176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4123420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32611179351807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45545864105225</t>
+    <t xml:space="preserve">8.80996322631836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77164077758789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65187454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53689861297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37880706787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37401676177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40755081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.41234302520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32610988616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45545673370361</t>
   </si>
   <si>
     <t xml:space="preserve">8.41713333129883</t>
@@ -1853,19 +1853,19 @@
     <t xml:space="preserve">8.54648017883301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58959579467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27341365814209</t>
+    <t xml:space="preserve">8.58959674835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27341461181641</t>
   </si>
   <si>
     <t xml:space="preserve">8.22071743011475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25425052642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35485553741455</t>
+    <t xml:space="preserve">8.25425243377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35485458374023</t>
   </si>
   <si>
     <t xml:space="preserve">8.4746208190918</t>
@@ -1883,13 +1883,13 @@
     <t xml:space="preserve">8.29736709594727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28299522399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1776008605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20155620574951</t>
+    <t xml:space="preserve">8.28299617767334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17760181427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2015552520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.16322994232178</t>
@@ -1898,22 +1898,22 @@
     <t xml:space="preserve">8.24946117401123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18239307403564</t>
+    <t xml:space="preserve">8.18239116668701</t>
   </si>
   <si>
     <t xml:space="preserve">8.17281150817871</t>
   </si>
   <si>
-    <t xml:space="preserve">8.09615993499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14885807037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06741619110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03867340087891</t>
+    <t xml:space="preserve">8.09616088867188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14885902404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06741809844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03867435455322</t>
   </si>
   <si>
     <t xml:space="preserve">7.971604347229</t>
@@ -1928,34 +1928,34 @@
     <t xml:space="preserve">7.61709785461426</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66021394729614</t>
+    <t xml:space="preserve">7.66021347045898</t>
   </si>
   <si>
     <t xml:space="preserve">7.50212335586548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72249269485474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5931453704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45900678634644</t>
+    <t xml:space="preserve">7.72249174118042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59314584732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45900726318359</t>
   </si>
   <si>
     <t xml:space="preserve">7.51170444488525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.65542268753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59793519973755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90932655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95244216918945</t>
+    <t xml:space="preserve">7.65542364120483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59793567657471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90932703018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95244169235229</t>
   </si>
   <si>
     <t xml:space="preserve">7.82309484481812</t>
@@ -1967,55 +1967,55 @@
     <t xml:space="preserve">8.10574245452881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20634460449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16802024841309</t>
+    <t xml:space="preserve">8.2063455581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16801929473877</t>
   </si>
   <si>
     <t xml:space="preserve">8.26383304595947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34527492523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29257583618164</t>
+    <t xml:space="preserve">8.3452730178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29257678985596</t>
   </si>
   <si>
     <t xml:space="preserve">8.12011432647705</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03388404846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.99555826187134</t>
+    <t xml:space="preserve">8.0338830947876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.99555778503418</t>
   </si>
   <si>
     <t xml:space="preserve">7.80872297286987</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91411685943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88537311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82788610458374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84704828262329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0003490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89974451065063</t>
+    <t xml:space="preserve">7.91411781311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88537454605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82788562774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84704732894897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00034809112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89974546432495</t>
   </si>
   <si>
     <t xml:space="preserve">7.90453577041626</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94286012649536</t>
+    <t xml:space="preserve">7.94286108016968</t>
   </si>
   <si>
     <t xml:space="preserve">7.71770143508911</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">7.85662937164307</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04346466064453</t>
+    <t xml:space="preserve">8.04346561431885</t>
   </si>
   <si>
     <t xml:space="preserve">8.11532306671143</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12969493865967</t>
+    <t xml:space="preserve">8.12969589233398</t>
   </si>
   <si>
     <t xml:space="preserve">8.13448524475098</t>
@@ -2039,64 +2039,64 @@
     <t xml:space="preserve">8.00992965698242</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93327903747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75123596191406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.578773021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64105129241943</t>
+    <t xml:space="preserve">7.9332799911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75123643875122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57877349853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64105081558228</t>
   </si>
   <si>
     <t xml:space="preserve">7.69374752044678</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83746671676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81351375579834</t>
+    <t xml:space="preserve">7.83746767044067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81351327896118</t>
   </si>
   <si>
     <t xml:space="preserve">7.87100172042847</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87579298019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92369794845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89495468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85183763504028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86621046066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98597717285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9668140411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92848920822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11053276062012</t>
+    <t xml:space="preserve">7.87579250335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92369890213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89495372772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8518385887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86621141433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9859766960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96681308746338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92848873138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1105318069458</t>
   </si>
   <si>
     <t xml:space="preserve">8.04825496673584</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93807029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77997922897339</t>
+    <t xml:space="preserve">7.93806982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77997970581055</t>
   </si>
   <si>
     <t xml:space="preserve">7.81830453872681</t>
@@ -2105,16 +2105,16 @@
     <t xml:space="preserve">7.84225797653198</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79435110092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7991418838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94765043258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9189076423645</t>
+    <t xml:space="preserve">7.79435157775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79914236068726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94765186309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91890811920166</t>
   </si>
   <si>
     <t xml:space="preserve">7.7129111289978</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">7.77518844604492</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86141967773438</t>
+    <t xml:space="preserve">7.86142063140869</t>
   </si>
   <si>
     <t xml:space="preserve">8.07699871063232</t>
@@ -2132,19 +2132,19 @@
     <t xml:space="preserve">8.21592617034912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26862335205078</t>
+    <t xml:space="preserve">8.26862525939941</t>
   </si>
   <si>
     <t xml:space="preserve">8.33569240570068</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45066738128662</t>
+    <t xml:space="preserve">8.45066833496094</t>
   </si>
   <si>
     <t xml:space="preserve">8.36443519592285</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47941207885742</t>
+    <t xml:space="preserve">8.47941112518311</t>
   </si>
   <si>
     <t xml:space="preserve">8.55127143859863</t>
@@ -2156,16 +2156,16 @@
     <t xml:space="preserve">8.66624546051025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64229202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69019889831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58480358123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19197273254395</t>
+    <t xml:space="preserve">8.64229297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69019794464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58480453491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19197368621826</t>
   </si>
   <si>
     <t xml:space="preserve">7.74165487289429</t>
@@ -2177,13 +2177,13 @@
     <t xml:space="preserve">7.78477001190186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44463539123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22426605224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1763596534729</t>
+    <t xml:space="preserve">7.44463586807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22426652908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17635917663574</t>
   </si>
   <si>
     <t xml:space="preserve">7.30091667175293</t>
@@ -2192,22 +2192,22 @@
     <t xml:space="preserve">7.36319494247437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33924150466919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09492015838623</t>
+    <t xml:space="preserve">7.33924198150635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09491968154907</t>
   </si>
   <si>
     <t xml:space="preserve">6.69729709625244</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36195373535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3367600440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54754686355591</t>
+    <t xml:space="preserve">6.3619532585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33675956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54754638671875</t>
   </si>
   <si>
     <t xml:space="preserve">5.37987518310547</t>
@@ -2216,28 +2216,28 @@
     <t xml:space="preserve">5.30322456359863</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86851930618286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45776605606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08409738540649</t>
+    <t xml:space="preserve">5.8685188293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45776557922363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08409690856934</t>
   </si>
   <si>
     <t xml:space="preserve">6.03619146347046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29967498779297</t>
+    <t xml:space="preserve">6.29967546463013</t>
   </si>
   <si>
     <t xml:space="preserve">6.76915693283081</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84101676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53441619873047</t>
+    <t xml:space="preserve">6.84101581573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53441667556763</t>
   </si>
   <si>
     <t xml:space="preserve">6.37153482437134</t>
@@ -2246,13 +2246,13 @@
     <t xml:space="preserve">6.27572250366211</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02852535247803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11092519760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85606288909912</t>
+    <t xml:space="preserve">6.02852582931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11092472076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85606336593628</t>
   </si>
   <si>
     <t xml:space="preserve">6.45201778411865</t>
@@ -2264,7 +2264,7 @@
     <t xml:space="preserve">6.32171249389648</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35237216949463</t>
+    <t xml:space="preserve">6.35237312316895</t>
   </si>
   <si>
     <t xml:space="preserve">6.40986061096191</t>
@@ -2273,25 +2273,25 @@
     <t xml:space="preserve">6.40794372558594</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47309637069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65897178649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49962091445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44746971130371</t>
+    <t xml:space="preserve">6.47309541702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65897274017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49962043762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44746923446655</t>
   </si>
   <si>
     <t xml:space="preserve">6.4300856590271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.393385887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44360637664795</t>
+    <t xml:space="preserve">6.39338636398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44360589981079</t>
   </si>
   <si>
     <t xml:space="preserve">6.59619760513306</t>
@@ -2300,34 +2300,34 @@
     <t xml:space="preserve">6.61551284790039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79321479797363</t>
+    <t xml:space="preserve">6.79321384429932</t>
   </si>
   <si>
     <t xml:space="preserve">6.82798194885254</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62323904037476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69084310531616</t>
+    <t xml:space="preserve">6.62323951721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.690842628479</t>
   </si>
   <si>
     <t xml:space="preserve">6.76617288589478</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78935194015503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9477367401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95932626724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08487606048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93807983398438</t>
+    <t xml:space="preserve">6.78935098648071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94773721694946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95932674407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.084876537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93807935714722</t>
   </si>
   <si>
     <t xml:space="preserve">6.70629501342773</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">6.51121044158936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67345952987671</t>
+    <t xml:space="preserve">6.67345857620239</t>
   </si>
   <si>
     <t xml:space="preserve">6.53245687484741</t>
@@ -2351,34 +2351,34 @@
     <t xml:space="preserve">6.66380167007446</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67732238769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.72947311401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71208953857422</t>
+    <t xml:space="preserve">6.67732191085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.72947406768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71209001541138</t>
   </si>
   <si>
     <t xml:space="preserve">7.14668560028076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05010938644409</t>
+    <t xml:space="preserve">7.05010890960693</t>
   </si>
   <si>
     <t xml:space="preserve">6.94387435913086</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11191749572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09839773178101</t>
+    <t xml:space="preserve">7.1119179725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09839677810669</t>
   </si>
   <si>
     <t xml:space="preserve">7.14282274246216</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14475345611572</t>
+    <t xml:space="preserve">7.14475393295288</t>
   </si>
   <si>
     <t xml:space="preserve">7.13895988464355</t>
@@ -2390,13 +2390,13 @@
     <t xml:space="preserve">7.05976629257202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20463132858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06942367553711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31279802322388</t>
+    <t xml:space="preserve">7.20463180541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06942415237427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31279754638672</t>
   </si>
   <si>
     <t xml:space="preserve">7.33018159866333</t>
@@ -2405,64 +2405,64 @@
     <t xml:space="preserve">7.38619565963745</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44800567626953</t>
+    <t xml:space="preserve">7.44800519943237</t>
   </si>
   <si>
     <t xml:space="preserve">7.44027900695801</t>
   </si>
   <si>
-    <t xml:space="preserve">7.58128118515015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27223587036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26837253570557</t>
+    <t xml:space="preserve">7.58128070831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27223539352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26837301254272</t>
   </si>
   <si>
     <t xml:space="preserve">7.24326229095459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34370183944702</t>
+    <t xml:space="preserve">7.34370279312134</t>
   </si>
   <si>
     <t xml:space="preserve">7.54844522476196</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45379972457886</t>
+    <t xml:space="preserve">7.45380020141602</t>
   </si>
   <si>
     <t xml:space="preserve">7.62667226791382</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67013216018677</t>
+    <t xml:space="preserve">7.67013168334961</t>
   </si>
   <si>
     <t xml:space="preserve">7.70683145523071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84203863143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86425113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81499767303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75029039382935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92412853240967</t>
+    <t xml:space="preserve">7.84203910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86425161361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81499719619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75028991699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92412948608398</t>
   </si>
   <si>
     <t xml:space="preserve">7.91350650787354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8285174369812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89322471618652</t>
+    <t xml:space="preserve">7.82851886749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89322519302368</t>
   </si>
   <si>
     <t xml:space="preserve">7.98497247695923</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">7.87294340133667</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0265007019043</t>
+    <t xml:space="preserve">8.02649974822998</t>
   </si>
   <si>
     <t xml:space="preserve">7.885498046875</t>
@@ -2480,40 +2480,40 @@
     <t xml:space="preserve">7.83817577362061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26311302185059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42729473114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21965408325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22158622741699</t>
+    <t xml:space="preserve">8.2631139755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42729377746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21965503692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22158432006836</t>
   </si>
   <si>
     <t xml:space="preserve">8.28146266937256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23221015930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29594993591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13659954071045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20806407928467</t>
+    <t xml:space="preserve">8.23220920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29594898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13659763336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20806503295898</t>
   </si>
   <si>
     <t xml:space="preserve">8.21868896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26601123809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43598461151123</t>
+    <t xml:space="preserve">8.26601028442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43598556518555</t>
   </si>
   <si>
     <t xml:space="preserve">8.39735507965088</t>
@@ -2525,31 +2525,31 @@
     <t xml:space="preserve">8.30753898620605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24283123016357</t>
+    <t xml:space="preserve">8.24283313751221</t>
   </si>
   <si>
     <t xml:space="preserve">8.34423828125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.228346824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39059543609619</t>
+    <t xml:space="preserve">8.22834587097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39059352874756</t>
   </si>
   <si>
     <t xml:space="preserve">8.34327220916748</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43405437469482</t>
+    <t xml:space="preserve">8.43405342102051</t>
   </si>
   <si>
     <t xml:space="preserve">8.31043529510498</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18102359771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29788112640381</t>
+    <t xml:space="preserve">8.18102264404297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29788208007812</t>
   </si>
   <si>
     <t xml:space="preserve">8.48330879211426</t>
@@ -2558,37 +2558,37 @@
     <t xml:space="preserve">8.77110862731934</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58664512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4794454574585</t>
+    <t xml:space="preserve">8.58664608001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47944641113281</t>
   </si>
   <si>
     <t xml:space="preserve">8.71799182891846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65907764434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75565528869629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7141284942627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82132816314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94784355163574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01448059082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03959178924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06083965301514</t>
+    <t xml:space="preserve">8.65907859802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75565624237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71412658691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82132720947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94784450531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01448154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03959083557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06083869934082</t>
   </si>
   <si>
     <t xml:space="preserve">8.85319709777832</t>
@@ -2597,49 +2597,49 @@
     <t xml:space="preserve">8.94011783599854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01641273498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05117988586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80587482452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08884620666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01158332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9999942779541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04828453063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04635143280029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02896690368652</t>
+    <t xml:space="preserve">9.01641368865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05118083953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80587577819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08884525299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0115852355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99999523162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04828262329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04635238647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02896785736084</t>
   </si>
   <si>
     <t xml:space="preserve">8.95460414886475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99613094329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9719877243042</t>
+    <t xml:space="preserve">8.99613189697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97198867797852</t>
   </si>
   <si>
     <t xml:space="preserve">9.04442024230957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21343040466309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23853969573975</t>
+    <t xml:space="preserve">9.21342849731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23854064941406</t>
   </si>
   <si>
     <t xml:space="preserve">9.1747989654541</t>
@@ -2648,10 +2648,10 @@
     <t xml:space="preserve">9.06180477142334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12554550170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03186511993408</t>
+    <t xml:space="preserve">9.12554454803467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03186702728271</t>
   </si>
   <si>
     <t xml:space="preserve">9.07629108428955</t>
@@ -2660,13 +2660,13 @@
     <t xml:space="preserve">8.80008125305176</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93528842926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94687747955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74020290374756</t>
+    <t xml:space="preserve">8.93528938293457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94687843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74020385742188</t>
   </si>
   <si>
     <t xml:space="preserve">8.88893222808838</t>
@@ -2675,88 +2675,88 @@
     <t xml:space="preserve">8.66294193267822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50262355804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65714740753174</t>
+    <t xml:space="preserve">8.50262451171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65714645385742</t>
   </si>
   <si>
     <t xml:space="preserve">8.51035022735596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59727096557617</t>
+    <t xml:space="preserve">8.59726905822754</t>
   </si>
   <si>
     <t xml:space="preserve">8.76724529266357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8908634185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96426105499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24626731872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26171779632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51281833648682</t>
+    <t xml:space="preserve">8.89086437225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96426010131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24626541137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51281929016113</t>
   </si>
   <si>
     <t xml:space="preserve">9.35443115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29841804504395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44328212738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4316930770874</t>
+    <t xml:space="preserve">9.29841709136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.443284034729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43169403076172</t>
   </si>
   <si>
     <t xml:space="preserve">9.25012874603271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13230419158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22501945495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06856441497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19411468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17286777496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22695064544678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36215782165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12651062011719</t>
+    <t xml:space="preserve">9.13230609893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22501850128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06856536865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19411563873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17286682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22695159912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36215877532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12650966644287</t>
   </si>
   <si>
     <t xml:space="preserve">9.14775657653809</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13037395477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15934753417969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12264823913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0048246383667</t>
+    <t xml:space="preserve">9.13037490844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15934658050537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12264728546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00482368469238</t>
   </si>
   <si>
     <t xml:space="preserve">9.13616752624512</t>
@@ -2768,13 +2768,13 @@
     <t xml:space="preserve">9.04538631439209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83677864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87347984313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95267295837402</t>
+    <t xml:space="preserve">8.83677959442139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87347888946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95267200469971</t>
   </si>
   <si>
     <t xml:space="preserve">8.9391508102417</t>
@@ -2783,64 +2783,64 @@
     <t xml:space="preserve">8.86961650848389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88120555877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96619319915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13809967041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02027606964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90438461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66487312316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59340667724609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54125499725342</t>
+    <t xml:space="preserve">8.88120651245117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96619415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13809871673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02027702331543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90438365936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66487407684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59340572357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5412540435791</t>
   </si>
   <si>
     <t xml:space="preserve">8.55284404754639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42150020599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38093757629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47365093231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42343139648438</t>
+    <t xml:space="preserve">8.42149925231934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38093852996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47365188598633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42343044281006</t>
   </si>
   <si>
     <t xml:space="preserve">8.42536354064941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54705047607422</t>
+    <t xml:space="preserve">8.5470495223999</t>
   </si>
   <si>
     <t xml:space="preserve">8.49296569824219</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58568000793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.512282371521</t>
+    <t xml:space="preserve">8.58568096160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51228141784668</t>
   </si>
   <si>
     <t xml:space="preserve">8.5064868927002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63590049743652</t>
+    <t xml:space="preserve">8.63590145111084</t>
   </si>
   <si>
     <t xml:space="preserve">8.59533786773682</t>
@@ -2849,25 +2849,25 @@
     <t xml:space="preserve">8.65328407287598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5721607208252</t>
+    <t xml:space="preserve">8.57215881347656</t>
   </si>
   <si>
     <t xml:space="preserve">8.57795429229736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82712268829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86768627166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94108486175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33704853057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3177318572998</t>
+    <t xml:space="preserve">8.82712364196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86768341064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94108295440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33704948425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31773281097412</t>
   </si>
   <si>
     <t xml:space="preserve">9.40272045135498</t>
@@ -2876,28 +2876,28 @@
     <t xml:space="preserve">9.34477424621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38533782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44521427154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58235359191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42976188659668</t>
+    <t xml:space="preserve">9.38533687591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44521331787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58235263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42976093292236</t>
   </si>
   <si>
     <t xml:space="preserve">9.44135093688965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35249900817871</t>
+    <t xml:space="preserve">9.35250091552734</t>
   </si>
   <si>
     <t xml:space="preserve">9.20570278167725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2887601852417</t>
+    <t xml:space="preserve">9.28875923156738</t>
   </si>
   <si>
     <t xml:space="preserve">9.3158016204834</t>
@@ -2909,34 +2909,34 @@
     <t xml:space="preserve">9.05697631835938</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19218158721924</t>
+    <t xml:space="preserve">9.19218254089355</t>
   </si>
   <si>
     <t xml:space="preserve">9.16320991516113</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04924964904785</t>
+    <t xml:space="preserve">9.04924869537354</t>
   </si>
   <si>
     <t xml:space="preserve">9.26751232147217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16900444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36795234680176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52440643310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76391696929932</t>
+    <t xml:space="preserve">9.1690034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36795330047607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5244083404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76391792297363</t>
   </si>
   <si>
     <t xml:space="preserve">9.48963928222656</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46839237213135</t>
+    <t xml:space="preserve">9.46839332580566</t>
   </si>
   <si>
     <t xml:space="preserve">9.38726806640625</t>
@@ -2948,16 +2948,16 @@
     <t xml:space="preserve">9.364089012146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28296566009521</t>
+    <t xml:space="preserve">9.2829647064209</t>
   </si>
   <si>
     <t xml:space="preserve">9.25978755950928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24240303039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26365089416504</t>
+    <t xml:space="preserve">9.24240207672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26364994049072</t>
   </si>
   <si>
     <t xml:space="preserve">9.28682804107666</t>
@@ -2969,10 +2969,10 @@
     <t xml:space="preserve">9.23081398010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39885807037354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32932186126709</t>
+    <t xml:space="preserve">9.39885711669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32932090759277</t>
   </si>
   <si>
     <t xml:space="preserve">9.4645299911499</t>
@@ -2981,16 +2981,16 @@
     <t xml:space="preserve">9.41624164581299</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63836765289307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47225379943848</t>
+    <t xml:space="preserve">9.63836860656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47225475311279</t>
   </si>
   <si>
     <t xml:space="preserve">9.56497001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64416217803955</t>
+    <t xml:space="preserve">9.64416122436523</t>
   </si>
   <si>
     <t xml:space="preserve">9.76943683624268</t>
@@ -2999,25 +2999,25 @@
     <t xml:space="preserve">9.55384922027588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73544692993164</t>
+    <t xml:space="preserve">9.73544788360596</t>
   </si>
   <si>
     <t xml:space="preserve">9.83255958557129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70339965820312</t>
+    <t xml:space="preserve">9.70340061187744</t>
   </si>
   <si>
     <t xml:space="preserve">9.62959671020508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60823154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52859973907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63348007202148</t>
+    <t xml:space="preserve">9.60823059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52860069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63347911834717</t>
   </si>
   <si>
     <t xml:space="preserve">9.8811149597168</t>
@@ -3026,31 +3026,31 @@
     <t xml:space="preserve">10.0025053024292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0947608947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98308086395264</t>
+    <t xml:space="preserve">10.0947618484497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98308181762695</t>
   </si>
   <si>
     <t xml:space="preserve">9.94423770904541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7742919921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86654663085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82284736633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81313610076904</t>
+    <t xml:space="preserve">9.77429103851318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86654758453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82284832000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81313705444336</t>
   </si>
   <si>
     <t xml:space="preserve">9.82770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79857063293457</t>
+    <t xml:space="preserve">9.79856967926025</t>
   </si>
   <si>
     <t xml:space="preserve">9.79371356964111</t>
@@ -3071,46 +3071,46 @@
     <t xml:space="preserve">10.1870164871216</t>
   </si>
   <si>
-    <t xml:space="preserve">10.14817237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2307167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2792720794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2744178771973</t>
+    <t xml:space="preserve">10.1481714248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2307176589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2792730331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2744169235229</t>
   </si>
   <si>
     <t xml:space="preserve">10.3132610321045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3909521102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5754632949829</t>
+    <t xml:space="preserve">10.3909511566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5754642486572</t>
   </si>
   <si>
     <t xml:space="preserve">10.6337308883667</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8133869171143</t>
+    <t xml:space="preserve">10.8133878707886</t>
   </si>
   <si>
     <t xml:space="preserve">10.8182430267334</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8328094482422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8230991363525</t>
+    <t xml:space="preserve">10.8328084945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8230981826782</t>
   </si>
   <si>
     <t xml:space="preserve">10.8570871353149</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7551193237305</t>
+    <t xml:space="preserve">10.7551202774048</t>
   </si>
   <si>
     <t xml:space="preserve">10.7454090118408</t>
@@ -3122,16 +3122,16 @@
     <t xml:space="preserve">11.0852994918823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0755891799927</t>
+    <t xml:space="preserve">11.0755882263184</t>
   </si>
   <si>
     <t xml:space="preserve">11.0610218048096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0464544296265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9687652587891</t>
+    <t xml:space="preserve">11.0464553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9687662124634</t>
   </si>
   <si>
     <t xml:space="preserve">11.0027551651001</t>
@@ -3152,25 +3152,25 @@
     <t xml:space="preserve">10.954197883606</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9784784317017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8667974472046</t>
+    <t xml:space="preserve">10.978476524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8667984008789</t>
   </si>
   <si>
     <t xml:space="preserve">10.6531524658203</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7162742614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9930438995361</t>
+    <t xml:space="preserve">10.7162752151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9930429458618</t>
   </si>
   <si>
     <t xml:space="preserve">11.162989616394</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0513114929199</t>
+    <t xml:space="preserve">11.0513105392456</t>
   </si>
   <si>
     <t xml:space="preserve">11.4009122848511</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">11.4688920974731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4931697845459</t>
+    <t xml:space="preserve">11.4931688308716</t>
   </si>
   <si>
     <t xml:space="preserve">11.5174465179443</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5951366424561</t>
+    <t xml:space="preserve">11.5951356887817</t>
   </si>
   <si>
     <t xml:space="preserve">11.5611476898193</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">11.5660028457642</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6097030639648</t>
+    <t xml:space="preserve">11.6097040176392</t>
   </si>
   <si>
     <t xml:space="preserve">11.721381187439</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8621940612793</t>
+    <t xml:space="preserve">11.862193107605</t>
   </si>
   <si>
     <t xml:space="preserve">11.745659828186</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">11.6825370788574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3620672225952</t>
+    <t xml:space="preserve">11.3620681762695</t>
   </si>
   <si>
     <t xml:space="preserve">11.2552452087402</t>
@@ -3230,13 +3230,13 @@
     <t xml:space="preserve">11.4834575653076</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4251899719238</t>
+    <t xml:space="preserve">11.4251918792725</t>
   </si>
   <si>
     <t xml:space="preserve">11.3814907073975</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3669233322144</t>
+    <t xml:space="preserve">11.36692237854</t>
   </si>
   <si>
     <t xml:space="preserve">11.3329343795776</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">11.5902814865112</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6971035003662</t>
+    <t xml:space="preserve">11.6971044540405</t>
   </si>
   <si>
     <t xml:space="preserve">11.570858001709</t>
@@ -3257,7 +3257,7 @@
     <t xml:space="preserve">11.5757141113281</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5125904083252</t>
+    <t xml:space="preserve">11.5125913619995</t>
   </si>
   <si>
     <t xml:space="preserve">11.410623550415</t>
@@ -3266,19 +3266,19 @@
     <t xml:space="preserve">11.5514364242554</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7068147659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9495944976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9301710128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7942161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7602262496948</t>
+    <t xml:space="preserve">11.7068157196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.949595451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9301719665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7942171096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7602252960205</t>
   </si>
   <si>
     <t xml:space="preserve">11.8087825775146</t>
@@ -3287,22 +3287,22 @@
     <t xml:space="preserve">11.8282051086426</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7505159378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9253158569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0175724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0564165115356</t>
+    <t xml:space="preserve">11.7505149841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9253168106079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0175714492798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.05641746521</t>
   </si>
   <si>
     <t xml:space="preserve">12.036994934082</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1875171661377</t>
+    <t xml:space="preserve">12.187518119812</t>
   </si>
   <si>
     <t xml:space="preserve">12.1486730575562</t>
@@ -3320,7 +3320,7 @@
     <t xml:space="preserve">12.5274076461792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5322647094727</t>
+    <t xml:space="preserve">12.5322637557983</t>
   </si>
   <si>
     <t xml:space="preserve">12.5662527084351</t>
@@ -3332,16 +3332,16 @@
     <t xml:space="preserve">12.012716293335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0758399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1729507446289</t>
+    <t xml:space="preserve">12.0758390426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1729497909546</t>
   </si>
   <si>
     <t xml:space="preserve">12.3331851959229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3137626647949</t>
+    <t xml:space="preserve">12.3137636184692</t>
   </si>
   <si>
     <t xml:space="preserve">12.4205856323242</t>
@@ -3353,7 +3353,7 @@
     <t xml:space="preserve">12.4108743667603</t>
   </si>
   <si>
-    <t xml:space="preserve">12.444863319397</t>
+    <t xml:space="preserve">12.4448642730713</t>
   </si>
   <si>
     <t xml:space="preserve">12.4157295227051</t>
@@ -3362,34 +3362,34 @@
     <t xml:space="preserve">12.5468311309814</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6439428329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7750425338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9644117355347</t>
+    <t xml:space="preserve">12.6439437866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7750434875488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9644107818604</t>
   </si>
   <si>
     <t xml:space="preserve">12.9595556259155</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9401330947876</t>
+    <t xml:space="preserve">12.9401321411133</t>
   </si>
   <si>
     <t xml:space="preserve">13.0760898590088</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5808200836182</t>
+    <t xml:space="preserve">12.5808210372925</t>
   </si>
   <si>
     <t xml:space="preserve">12.5953874588013</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9110012054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4837074279785</t>
+    <t xml:space="preserve">12.9109992980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4837083816528</t>
   </si>
   <si>
     <t xml:space="preserve">12.7070655822754</t>
@@ -3407,13 +3407,13 @@
     <t xml:space="preserve">12.639087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8721542358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6099538803101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5856761932373</t>
+    <t xml:space="preserve">12.8721551895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6099529266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.585675239563</t>
   </si>
   <si>
     <t xml:space="preserve">12.3768854141235</t>
@@ -3425,37 +3425,37 @@
     <t xml:space="preserve">12.284628868103</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2797746658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2020845413208</t>
+    <t xml:space="preserve">12.2797737121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2020835876465</t>
   </si>
   <si>
     <t xml:space="preserve">12.4400081634521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3720293045044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4351530075073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3963079452515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4060192108154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7553691864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6728267669678</t>
+    <t xml:space="preserve">12.3720302581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.435152053833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3963088989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4060182571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7553701400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6728258132935</t>
   </si>
   <si>
     <t xml:space="preserve">11.6388359069824</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4397563934326</t>
+    <t xml:space="preserve">11.4397573471069</t>
   </si>
   <si>
     <t xml:space="preserve">11.1532783508301</t>
@@ -3464,58 +3464,58 @@
     <t xml:space="preserve">11.2164011001587</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0804433822632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0658779144287</t>
+    <t xml:space="preserve">11.0804443359375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.065878868103</t>
   </si>
   <si>
     <t xml:space="preserve">10.6968536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6434412002563</t>
+    <t xml:space="preserve">10.6434421539307</t>
   </si>
   <si>
     <t xml:space="preserve">10.6191654205322</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5171966552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7696866989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9833316802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8619441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7114200592041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5269069671631</t>
+    <t xml:space="preserve">10.5171957015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7696876525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9833326339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8619432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7114191055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5269079208374</t>
   </si>
   <si>
     <t xml:space="preserve">10.44921875</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5317640304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4880628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3375396728516</t>
+    <t xml:space="preserve">10.5317630767822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4880638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3375406265259</t>
   </si>
   <si>
     <t xml:space="preserve">10.0899057388306</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1821603775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1918725967407</t>
+    <t xml:space="preserve">10.1821613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1918706893921</t>
   </si>
   <si>
     <t xml:space="preserve">10.264705657959</t>
@@ -3527,16 +3527,16 @@
     <t xml:space="preserve">9.02556037902832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18870830535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46644878387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04304122924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04498291015625</t>
+    <t xml:space="preserve">9.18870735168457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4664478302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04304027557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04498386383057</t>
   </si>
   <si>
     <t xml:space="preserve">9.06246280670166</t>
@@ -3545,37 +3545,37 @@
     <t xml:space="preserve">8.84299087524414</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83910751342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5438871383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14403820037842</t>
+    <t xml:space="preserve">8.83910655975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54388618469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1440372467041</t>
   </si>
   <si>
     <t xml:space="preserve">8.9906005859375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95369911193848</t>
+    <t xml:space="preserve">8.95369815826416</t>
   </si>
   <si>
     <t xml:space="preserve">8.99836921691895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03138828277588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58492374420166</t>
+    <t xml:space="preserve">9.03138732910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58492469787598</t>
   </si>
   <si>
     <t xml:space="preserve">9.55190658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75001335144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62182712554932</t>
+    <t xml:space="preserve">9.75001430511475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.621826171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.68203639984131</t>
@@ -3584,25 +3584,25 @@
     <t xml:space="preserve">9.63736438751221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62571144104004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0801935195923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2598495483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2501392364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4200849533081</t>
+    <t xml:space="preserve">9.62571239471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0801944732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2598505020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2501401901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4200839996338</t>
   </si>
   <si>
     <t xml:space="preserve">10.3860950469971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5074863433838</t>
+    <t xml:space="preserve">10.5074844360352</t>
   </si>
   <si>
     <t xml:space="preserve">10.4346513748169</t>
@@ -3617,13 +3617,13 @@
     <t xml:space="preserve">10.2110719680786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.528489112854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3429222106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3819885253906</t>
+    <t xml:space="preserve">10.5284900665283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3429231643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3819894790649</t>
   </si>
   <si>
     <t xml:space="preserve">10.4308233261108</t>
@@ -3632,34 +3632,34 @@
     <t xml:space="preserve">10.4210567474365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4259395599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5333728790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2306060791016</t>
+    <t xml:space="preserve">10.4259405136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5333738327026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2306051254272</t>
   </si>
   <si>
     <t xml:space="preserve">10.4601230621338</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0645713806152</t>
+    <t xml:space="preserve">10.0645723342896</t>
   </si>
   <si>
     <t xml:space="preserve">10.1720056533813</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54986763000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33890819549561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58893394470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68855571746826</t>
+    <t xml:space="preserve">9.5498685836792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33890724182129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58893489837646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68855476379395</t>
   </si>
   <si>
     <t xml:space="preserve">9.669020652771</t>
@@ -3671,40 +3671,40 @@
     <t xml:space="preserve">10.0059728622437</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91318798065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.59870052337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39750576019287</t>
+    <t xml:space="preserve">9.91318893432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.59870147705078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39750671386719</t>
   </si>
   <si>
     <t xml:space="preserve">9.36234760284424</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61823463439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4053201675415</t>
+    <t xml:space="preserve">9.6182336807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40532112121582</t>
   </si>
   <si>
     <t xml:space="preserve">9.47173404693604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47368812561035</t>
+    <t xml:space="preserve">9.47368717193604</t>
   </si>
   <si>
     <t xml:space="preserve">9.659255027771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78622150421143</t>
+    <t xml:space="preserve">9.78622245788574</t>
   </si>
   <si>
     <t xml:space="preserve">9.71004199981689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51861381530762</t>
+    <t xml:space="preserve">9.51861476898193</t>
   </si>
   <si>
     <t xml:space="preserve">9.69441413879395</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">9.68074131011963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54791355133057</t>
+    <t xml:space="preserve">9.54791450500488</t>
   </si>
   <si>
     <t xml:space="preserve">9.03418636322021</t>
@@ -3731,22 +3731,22 @@
     <t xml:space="preserve">8.8154125213623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20608043670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11427307128906</t>
+    <t xml:space="preserve">9.20607948303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11427211761475</t>
   </si>
   <si>
     <t xml:space="preserve">9.52252101898193</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56744766235352</t>
+    <t xml:space="preserve">9.5674467086792</t>
   </si>
   <si>
     <t xml:space="preserve">9.46782779693604</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55572891235352</t>
+    <t xml:space="preserve">9.5557279586792</t>
   </si>
   <si>
     <t xml:space="preserve">9.4541540145874</t>
@@ -3755,19 +3755,19 @@
     <t xml:space="preserve">9.79110431671143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.85947227478027</t>
+    <t xml:space="preserve">9.85947132110596</t>
   </si>
   <si>
     <t xml:space="preserve">9.91807174682617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81552219390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80087184906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72566795349121</t>
+    <t xml:space="preserve">9.81552124023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80087089538574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72566890716553</t>
   </si>
   <si>
     <t xml:space="preserve">9.661208152771</t>
@@ -3785,7 +3785,7 @@
     <t xml:space="preserve">10.2989730834961</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0499210357666</t>
+    <t xml:space="preserve">10.0499229431152</t>
   </si>
   <si>
     <t xml:space="preserve">9.94248867034912</t>
@@ -3815,16 +3815,16 @@
     <t xml:space="preserve">10.167121887207</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5675573348999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3673391342163</t>
+    <t xml:space="preserve">10.5675563812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.367338180542</t>
   </si>
   <si>
     <t xml:space="preserve">10.1182880401611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.19642162323</t>
+    <t xml:space="preserve">10.1964225769043</t>
   </si>
   <si>
     <t xml:space="preserve">9.97667217254639</t>
@@ -3833,16 +3833,16 @@
     <t xml:space="preserve">9.81063747406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79598712921143</t>
+    <t xml:space="preserve">9.79598808288574</t>
   </si>
   <si>
     <t xml:space="preserve">9.78133869171143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87900447845459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0352725982666</t>
+    <t xml:space="preserve">9.87900543212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0352716445923</t>
   </si>
   <si>
     <t xml:space="preserve">10.1134052276611</t>
@@ -3851,16 +3851,16 @@
     <t xml:space="preserve">10.1475896835327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1524724960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9815559387207</t>
+    <t xml:space="preserve">10.152473449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98155498504639</t>
   </si>
   <si>
     <t xml:space="preserve">9.83505439758301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57916831970215</t>
+    <t xml:space="preserve">9.57916736602783</t>
   </si>
   <si>
     <t xml:space="preserve">9.4482946395874</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">9.46001434326172</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29593276977539</t>
+    <t xml:space="preserve">9.29593372344971</t>
   </si>
   <si>
     <t xml:space="preserve">9.31742000579834</t>
@@ -3893,7 +3893,7 @@
     <t xml:space="preserve">8.9658203125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00684070587158</t>
+    <t xml:space="preserve">9.00683975219727</t>
   </si>
   <si>
     <t xml:space="preserve">8.94042682647705</t>
@@ -3902,25 +3902,25 @@
     <t xml:space="preserve">9.0752067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78025245666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68649196624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89549922943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84471225738525</t>
+    <t xml:space="preserve">8.78025150299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68649291992188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89550018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84471321105957</t>
   </si>
   <si>
     <t xml:space="preserve">8.88377857208252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72360610961914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89940643310547</t>
+    <t xml:space="preserve">8.72360515594482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89940738677979</t>
   </si>
   <si>
     <t xml:space="preserve">8.73532581329346</t>
@@ -3935,25 +3935,25 @@
     <t xml:space="preserve">8.88964080810547</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79783248901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94628524780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98144721984863</t>
+    <t xml:space="preserve">8.79783344268799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94628715515137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98144626617432</t>
   </si>
   <si>
     <t xml:space="preserve">8.78611278533936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98535251617432</t>
+    <t xml:space="preserve">8.98535346984863</t>
   </si>
   <si>
     <t xml:space="preserve">8.96191215515137</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84080600738525</t>
+    <t xml:space="preserve">8.84080505371094</t>
   </si>
   <si>
     <t xml:space="preserve">8.60054492950439</t>
@@ -3965,10 +3965,10 @@
     <t xml:space="preserve">8.72165298461914</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90917205810547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79587841033936</t>
+    <t xml:space="preserve">8.90917301177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79587936401367</t>
   </si>
   <si>
     <t xml:space="preserve">8.80173969268799</t>
@@ -3977,10 +3977,10 @@
     <t xml:space="preserve">8.70798015594482</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88182640075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99707221984863</t>
+    <t xml:space="preserve">8.88182544708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99707317352295</t>
   </si>
   <si>
     <t xml:space="preserve">9.10841369628906</t>
@@ -3992,7 +3992,7 @@
     <t xml:space="preserve">9.09473991394043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11622714996338</t>
+    <t xml:space="preserve">9.11622619628906</t>
   </si>
   <si>
     <t xml:space="preserve">8.9755859375</t>
@@ -4007,7 +4007,7 @@
     <t xml:space="preserve">9.54205513000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49322032928467</t>
+    <t xml:space="preserve">9.4932222366333</t>
   </si>
   <si>
     <t xml:space="preserve">9.5654935836792</t>
@@ -4016,10 +4016,10 @@
     <t xml:space="preserve">9.73543548583984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76278114318848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1280555725098</t>
+    <t xml:space="preserve">9.76278209686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1280546188354</t>
   </si>
   <si>
     <t xml:space="preserve">9.96202182769775</t>
@@ -4031,16 +4031,16 @@
     <t xml:space="preserve">9.80575466156006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69050693511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72371482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.75692081451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9278392791748</t>
+    <t xml:space="preserve">9.69050788879395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72371387481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.75692176818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92783832550049</t>
   </si>
   <si>
     <t xml:space="preserve">9.95225429534912</t>
@@ -4049,7 +4049,7 @@
     <t xml:space="preserve">9.58502769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62214183807373</t>
+    <t xml:space="preserve">9.62214088439941</t>
   </si>
   <si>
     <t xml:space="preserve">9.31546783447266</t>
@@ -4061,10 +4061,10 @@
     <t xml:space="preserve">9.40336799621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38774108886719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42290019989014</t>
+    <t xml:space="preserve">9.38774013519287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42290115356445</t>
   </si>
   <si>
     <t xml:space="preserve">9.45806121826172</t>
@@ -4076,7 +4076,7 @@
     <t xml:space="preserve">9.33500003814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43462085723877</t>
+    <t xml:space="preserve">9.43461990356445</t>
   </si>
   <si>
     <t xml:space="preserve">9.59088706970215</t>
@@ -4085,10 +4085,10 @@
     <t xml:space="preserve">9.63190841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64948749542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65730094909668</t>
+    <t xml:space="preserve">9.64948844909668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65729999542236</t>
   </si>
   <si>
     <t xml:space="preserve">9.74324798583984</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">9.71199512481689</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71785449981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4443883895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42876148223877</t>
+    <t xml:space="preserve">9.71785354614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44438648223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42876052856445</t>
   </si>
   <si>
     <t xml:space="preserve">9.43852615356445</t>
@@ -4112,7 +4112,7 @@
     <t xml:space="preserve">9.71590137481689</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0303897857666</t>
+    <t xml:space="preserve">10.0303888320923</t>
   </si>
   <si>
     <t xml:space="preserve">9.90342235565186</t>
@@ -4121,10 +4121,10 @@
     <t xml:space="preserve">9.83017158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1427049636841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2696723937988</t>
+    <t xml:space="preserve">10.1427068710327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2696733474731</t>
   </si>
   <si>
     <t xml:space="preserve">10.2452554702759</t>
@@ -4148,7 +4148,7 @@
     <t xml:space="preserve">10.3722219467163</t>
   </si>
   <si>
-    <t xml:space="preserve">10.347806930542</t>
+    <t xml:space="preserve">10.3478059768677</t>
   </si>
   <si>
     <t xml:space="preserve">10.5870895385742</t>
@@ -4157,28 +4157,28 @@
     <t xml:space="preserve">10.5382566452026</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4698896408081</t>
+    <t xml:space="preserve">10.4698905944824</t>
   </si>
   <si>
     <t xml:space="preserve">10.4405889511108</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3917570114136</t>
+    <t xml:space="preserve">10.3917560577393</t>
   </si>
   <si>
     <t xml:space="preserve">10.4747734069824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6749897003174</t>
+    <t xml:space="preserve">10.6749906539917</t>
   </si>
   <si>
     <t xml:space="preserve">10.518723487854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6310405731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6261558532715</t>
+    <t xml:space="preserve">10.6310396194458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6261568069458</t>
   </si>
   <si>
     <t xml:space="preserve">10.7580070495605</t>
@@ -4187,13 +4187,13 @@
     <t xml:space="preserve">10.8703241348267</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8605575561523</t>
+    <t xml:space="preserve">10.860556602478</t>
   </si>
   <si>
     <t xml:space="preserve">10.8312568664551</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7775402069092</t>
+    <t xml:space="preserve">10.7775392532349</t>
   </si>
   <si>
     <t xml:space="preserve">10.880090713501</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">11.0070581436157</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1291408538818</t>
+    <t xml:space="preserve">11.1291418075562</t>
   </si>
   <si>
     <t xml:space="preserve">11.2463417053223</t>
@@ -4220,22 +4220,22 @@
     <t xml:space="preserve">11.2268085479736</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2121572494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.207275390625</t>
+    <t xml:space="preserve">11.212158203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2072744369507</t>
   </si>
   <si>
     <t xml:space="preserve">11.2561082839966</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2854089736938</t>
+    <t xml:space="preserve">11.2854080200195</t>
   </si>
   <si>
     <t xml:space="preserve">11.3195915222168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3488912582397</t>
+    <t xml:space="preserve">11.3488922119141</t>
   </si>
   <si>
     <t xml:space="preserve">11.373309135437</t>
@@ -4244,16 +4244,16 @@
     <t xml:space="preserve">11.5295753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5737495422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6670074462891</t>
+    <t xml:space="preserve">11.5737504959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6670083999634</t>
   </si>
   <si>
     <t xml:space="preserve">11.5982913970947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6326503753662</t>
+    <t xml:space="preserve">11.6326494216919</t>
   </si>
   <si>
     <t xml:space="preserve">11.4657678604126</t>
@@ -4262,13 +4262,13 @@
     <t xml:space="preserve">11.7700815200806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9418716430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.902606010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0645790100098</t>
+    <t xml:space="preserve">11.9418725967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9026050567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0645799636841</t>
   </si>
   <si>
     <t xml:space="preserve">12.1038455963135</t>
@@ -4283,10 +4283,10 @@
     <t xml:space="preserve">12.054762840271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.162745475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9173307418823</t>
+    <t xml:space="preserve">12.1627445220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9173316955566</t>
   </si>
   <si>
     <t xml:space="preserve">11.9467802047729</t>
@@ -4310,7 +4310,7 @@
     <t xml:space="preserve">11.9369640350342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9860458374023</t>
+    <t xml:space="preserve">11.9860467910767</t>
   </si>
   <si>
     <t xml:space="preserve">12.2314615249634</t>
@@ -4325,28 +4325,28 @@
     <t xml:space="preserve">12.467059135437</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4130687713623</t>
+    <t xml:space="preserve">12.413067817688</t>
   </si>
   <si>
     <t xml:space="preserve">12.5701332092285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5652256011963</t>
+    <t xml:space="preserve">12.565224647522</t>
   </si>
   <si>
     <t xml:space="preserve">12.6633901596069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6143074035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6241235733032</t>
+    <t xml:space="preserve">12.6143083572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6241245269775</t>
   </si>
   <si>
     <t xml:space="preserve">12.2658185958862</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0596704483032</t>
+    <t xml:space="preserve">12.0596714019775</t>
   </si>
   <si>
     <t xml:space="preserve">12.0694875717163</t>
@@ -4370,16 +4370,16 @@
     <t xml:space="preserve">12.3050851821899</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3296270370483</t>
+    <t xml:space="preserve">12.3296279907227</t>
   </si>
   <si>
     <t xml:space="preserve">12.2216444015503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1921939849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4376096725464</t>
+    <t xml:space="preserve">12.1921949386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4376087188721</t>
   </si>
   <si>
     <t xml:space="preserve">12.4228839874268</t>
@@ -4388,7 +4388,7 @@
     <t xml:space="preserve">12.4866924285889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6928415298462</t>
+    <t xml:space="preserve">12.6928405761719</t>
   </si>
   <si>
     <t xml:space="preserve">12.4817838668823</t>
@@ -4412,13 +4412,13 @@
     <t xml:space="preserve">12.0940284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9762306213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9124231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.794623374939</t>
+    <t xml:space="preserve">11.9762296676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9124221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7946243286133</t>
   </si>
   <si>
     <t xml:space="preserve">11.8044395446777</t>
@@ -4427,7 +4427,7 @@
     <t xml:space="preserve">11.7995319366455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.819164276123</t>
+    <t xml:space="preserve">11.8191652297974</t>
   </si>
   <si>
     <t xml:space="preserve">11.8927888870239</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">11.4461345672607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3970508575439</t>
+    <t xml:space="preserve">11.3970518112183</t>
   </si>
   <si>
     <t xml:space="preserve">11.4706764221191</t>
@@ -4448,7 +4448,7 @@
     <t xml:space="preserve">11.3872356414795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5639324188232</t>
+    <t xml:space="preserve">11.5639333724976</t>
   </si>
   <si>
     <t xml:space="preserve">11.5835666656494</t>
@@ -4460,13 +4460,13 @@
     <t xml:space="preserve">11.9075136184692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0007724761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.848614692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7749900817871</t>
+    <t xml:space="preserve">12.000771522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8486137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7749891281128</t>
   </si>
   <si>
     <t xml:space="preserve">11.8535223007202</t>
@@ -4478,10 +4478,10 @@
     <t xml:space="preserve">11.5344839096069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.642466545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1516361236572</t>
+    <t xml:space="preserve">11.6424655914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1516370773315</t>
   </si>
   <si>
     <t xml:space="preserve">11.1025543212891</t>
@@ -4493,10 +4493,10 @@
     <t xml:space="preserve">11.1712703704834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.269434928894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.284161567688</t>
+    <t xml:space="preserve">11.2694358825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2841606140137</t>
   </si>
   <si>
     <t xml:space="preserve">11.54430103302</t>
@@ -4505,7 +4505,7 @@
     <t xml:space="preserve">11.1909027099609</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0092964172363</t>
+    <t xml:space="preserve">11.0092973709106</t>
   </si>
   <si>
     <t xml:space="preserve">10.842414855957</t>
@@ -4514,7 +4514,7 @@
     <t xml:space="preserve">10.68044090271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7687902450562</t>
+    <t xml:space="preserve">10.7687911987305</t>
   </si>
   <si>
     <t xml:space="preserve">10.9602136611938</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">10.9454879760742</t>
   </si>
   <si>
-    <t xml:space="preserve">11.254711151123</t>
+    <t xml:space="preserve">11.2547121047974</t>
   </si>
   <si>
     <t xml:space="preserve">11.3087024688721</t>
@@ -4556,7 +4556,7 @@
     <t xml:space="preserve">10.7786064147949</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7393398284912</t>
+    <t xml:space="preserve">10.7393407821655</t>
   </si>
   <si>
     <t xml:space="preserve">10.7344331741333</t>
@@ -4565,13 +4565,13 @@
     <t xml:space="preserve">10.7246160507202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7589731216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.886589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8571395874023</t>
+    <t xml:space="preserve">10.7589740753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8865900039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8571405410767</t>
   </si>
   <si>
     <t xml:space="preserve">10.1208963394165</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">9.98346424102783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1945199966431</t>
+    <t xml:space="preserve">10.1945209503174</t>
   </si>
   <si>
     <t xml:space="preserve">10.2386951446533</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">10.48410987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871829986572</t>
+    <t xml:space="preserve">10.5871839523315</t>
   </si>
   <si>
     <t xml:space="preserve">10.5381002426147</t>
@@ -4601,22 +4601,22 @@
     <t xml:space="preserve">10.7295246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7000741958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3466768264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2877779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4055776596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3270444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0669040679932</t>
+    <t xml:space="preserve">10.7000732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3466777801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2877769470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4055767059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3270454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0669050216675</t>
   </si>
   <si>
     <t xml:space="preserve">10.086537361145</t>
@@ -4640,13 +4640,13 @@
     <t xml:space="preserve">9.75375556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83621501922607</t>
+    <t xml:space="preserve">9.83621597290039</t>
   </si>
   <si>
     <t xml:space="preserve">9.83130741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86075592041016</t>
+    <t xml:space="preserve">9.86075687408447</t>
   </si>
   <si>
     <t xml:space="preserve">9.90493106842041</t>
@@ -4670,7 +4670,7 @@
     <t xml:space="preserve">9.8263988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9147481918335</t>
+    <t xml:space="preserve">9.91474723815918</t>
   </si>
   <si>
     <t xml:space="preserve">9.96382999420166</t>
@@ -4688,19 +4688,19 @@
     <t xml:space="preserve">10.0276384353638</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8902063369751</t>
+    <t xml:space="preserve">9.89020538330078</t>
   </si>
   <si>
     <t xml:space="preserve">9.76357269287109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86566543579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76553535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74001216888428</t>
+    <t xml:space="preserve">9.8656644821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76553630828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74001312255859</t>
   </si>
   <si>
     <t xml:space="preserve">9.74393844604492</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">9.10782432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15494441986084</t>
+    <t xml:space="preserve">9.15494537353516</t>
   </si>
   <si>
     <t xml:space="preserve">9.14905452728271</t>
@@ -4718,7 +4718,7 @@
     <t xml:space="preserve">9.00769519805908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08033752441406</t>
+    <t xml:space="preserve">9.08033847808838</t>
   </si>
   <si>
     <t xml:space="preserve">9.06463146209717</t>
@@ -4739,19 +4739,19 @@
     <t xml:space="preserve">8.85455799102783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8152904510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29630279541016</t>
+    <t xml:space="preserve">8.81528949737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29630374908447</t>
   </si>
   <si>
     <t xml:space="preserve">9.22758674621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23740386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21580600738525</t>
+    <t xml:space="preserve">9.23740291595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21580696105957</t>
   </si>
   <si>
     <t xml:space="preserve">9.37090873718262</t>
@@ -4775,19 +4775,19 @@
     <t xml:space="preserve">9.61043357849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56527709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76749897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78909492492676</t>
+    <t xml:space="preserve">9.56527805328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76749801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78909587860107</t>
   </si>
   <si>
     <t xml:space="preserve">9.63988304138184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63791942596436</t>
+    <t xml:space="preserve">9.63792037963867</t>
   </si>
   <si>
     <t xml:space="preserve">9.6909294128418</t>
@@ -4799,16 +4799,16 @@
     <t xml:space="preserve">9.59080123901367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3807258605957</t>
+    <t xml:space="preserve">9.38072490692139</t>
   </si>
   <si>
     <t xml:space="preserve">9.65559005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32967948913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20009994506836</t>
+    <t xml:space="preserve">9.32967853546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20010089874268</t>
   </si>
   <si>
     <t xml:space="preserve">9.30023002624512</t>
@@ -4829,7 +4829,7 @@
     <t xml:space="preserve">9.36109256744385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40232276916504</t>
+    <t xml:space="preserve">9.40232181549072</t>
   </si>
   <si>
     <t xml:space="preserve">9.39054203033447</t>
@@ -4838,7 +4838,7 @@
     <t xml:space="preserve">9.47300148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47103786468506</t>
+    <t xml:space="preserve">9.47103881835938</t>
   </si>
   <si>
     <t xml:space="preserve">9.37876224517822</t>
@@ -4847,7 +4847,7 @@
     <t xml:space="preserve">9.27667045593262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08426475524902</t>
+    <t xml:space="preserve">9.08426380157471</t>
   </si>
   <si>
     <t xml:space="preserve">9.1254940032959</t>
@@ -4865,7 +4865,7 @@
     <t xml:space="preserve">9.06855869293213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14316368103027</t>
+    <t xml:space="preserve">9.14316463470459</t>
   </si>
   <si>
     <t xml:space="preserve">9.00573253631592</t>
@@ -4874,7 +4874,7 @@
     <t xml:space="preserve">8.89382362365723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02340316772461</t>
+    <t xml:space="preserve">9.02340221405029</t>
   </si>
   <si>
     <t xml:space="preserve">8.92523670196533</t>
@@ -4886,7 +4886,7 @@
     <t xml:space="preserve">8.92327308654785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88400650024414</t>
+    <t xml:space="preserve">8.88400745391846</t>
   </si>
   <si>
     <t xml:space="preserve">8.80743789672852</t>
@@ -4895,7 +4895,7 @@
     <t xml:space="preserve">8.73479461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7681713104248</t>
+    <t xml:space="preserve">8.76817035675049</t>
   </si>
   <si>
     <t xml:space="preserve">8.77995109558105</t>
@@ -4904,10 +4904,10 @@
     <t xml:space="preserve">8.9821720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21188068389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30219268798828</t>
+    <t xml:space="preserve">9.21187973022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3021936416626</t>
   </si>
   <si>
     <t xml:space="preserve">9.42377090454102</t>
@@ -5970,6 +5970,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.93400001525879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.63800001144409</t>
   </si>
 </sst>
 </file>
@@ -71594,7 +71597,7 @@
     </row>
     <row r="2512">
       <c r="A2512" s="1" t="n">
-        <v>45975.6910300926</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2512" t="n">
         <v>4999052</v>
@@ -71615,6 +71618,32 @@
         <v>1900</v>
       </c>
       <c r="H2512" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2513">
+      <c r="A2513" s="1" t="n">
+        <v>45978.6913078704</v>
+      </c>
+      <c r="B2513" t="n">
+        <v>4305162</v>
+      </c>
+      <c r="C2513" t="n">
+        <v>5.78599977493286</v>
+      </c>
+      <c r="D2513" t="n">
+        <v>5.61600017547607</v>
+      </c>
+      <c r="E2513" t="n">
+        <v>5.77400016784668</v>
+      </c>
+      <c r="F2513" t="n">
+        <v>5.63800001144409</v>
+      </c>
+      <c r="G2513" t="s">
+        <v>1986</v>
+      </c>
+      <c r="H2513" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1987" uniqueCount="1987">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="1988">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59865641593933</t>
+    <t xml:space="preserve">3.59865665435791</t>
   </si>
   <si>
     <t xml:space="preserve">CPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6589822769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60329699516296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51976895332336</t>
+    <t xml:space="preserve">3.65898275375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60329723358154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51976943016052</t>
   </si>
   <si>
     <t xml:space="preserve">3.51048827171326</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">3.54993224143982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62881970405579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68450474739075</t>
+    <t xml:space="preserve">3.62881898880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68450450897217</t>
   </si>
   <si>
     <t xml:space="preserve">3.57313394546509</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">3.52672958374023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48264575004578</t>
+    <t xml:space="preserve">3.48264598846436</t>
   </si>
   <si>
     <t xml:space="preserve">3.5661735534668</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">3.50584769248962</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56153321266174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64274072647095</t>
+    <t xml:space="preserve">3.56153345108032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64274048805237</t>
   </si>
   <si>
     <t xml:space="preserve">3.66594314575195</t>
@@ -101,10 +101,10 @@
     <t xml:space="preserve">3.72162818908691</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70770668983459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47104454040527</t>
+    <t xml:space="preserve">3.70770645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47104477882385</t>
   </si>
   <si>
     <t xml:space="preserve">3.44320201873779</t>
@@ -113,16 +113,16 @@
     <t xml:space="preserve">3.28078699111938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33183145523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40839886665344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22046160697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26918601989746</t>
+    <t xml:space="preserve">3.33183169364929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40839862823486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22046136856079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2691855430603</t>
   </si>
   <si>
     <t xml:space="preserve">3.32487106323242</t>
@@ -131,10 +131,10 @@
     <t xml:space="preserve">3.24366331100464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32255053520203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28774762153625</t>
+    <t xml:space="preserve">3.32255077362061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28774785995483</t>
   </si>
   <si>
     <t xml:space="preserve">3.31791043281555</t>
@@ -143,10 +143,10 @@
     <t xml:space="preserve">3.36663484573364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36199450492859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40607905387878</t>
+    <t xml:space="preserve">3.36199426651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40607857704163</t>
   </si>
   <si>
     <t xml:space="preserve">3.3828763961792</t>
@@ -155,34 +155,34 @@
     <t xml:space="preserve">3.36431479454041</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53137063980103</t>
+    <t xml:space="preserve">3.53136992454529</t>
   </si>
   <si>
     <t xml:space="preserve">3.60561728477478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61257767677307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56385326385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61489820480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63810014724731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6891450881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476301193237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95597076416016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00701522827148</t>
+    <t xml:space="preserve">3.61257791519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56385350227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61489844322205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63810038566589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68914532661438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476229667664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95596981048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00701427459717</t>
   </si>
   <si>
     <t xml:space="preserve">4.04877853393555</t>
@@ -191,70 +191,70 @@
     <t xml:space="preserve">4.03485727310181</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0418176651001</t>
+    <t xml:space="preserve">4.04181718826294</t>
   </si>
   <si>
     <t xml:space="preserve">4.03717803955078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05109834671021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01861524581909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09286308288574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07662105560303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03949785232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08358240127563</t>
+    <t xml:space="preserve">4.05109930038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01861619949341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09286260604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07662200927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03949737548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08358192443848</t>
   </si>
   <si>
     <t xml:space="preserve">4.02325677871704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00005435943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06037902832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99541425704956</t>
+    <t xml:space="preserve">4.00005388259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06037998199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99541306495667</t>
   </si>
   <si>
     <t xml:space="preserve">3.9443690776825</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97453236579895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00237464904785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93740773200989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94668960571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03021669387817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0534200668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00933456420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95829010009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98613333702087</t>
+    <t xml:space="preserve">3.97453165054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00237417221069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93740797042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94668865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03021717071533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05341815948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0093355178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9582896232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98613309860229</t>
   </si>
   <si>
     <t xml:space="preserve">4.0255765914917</t>
@@ -266,34 +266,34 @@
     <t xml:space="preserve">3.9118857383728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89796423912048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87708234786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91420650482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92812752723694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95132923126221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06734085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08126163482666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99309277534485</t>
+    <t xml:space="preserve">3.89796447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87708282470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91420578956604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92812728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95133018493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06734037399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08126306533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99309372901917</t>
   </si>
   <si>
     <t xml:space="preserve">3.96757102012634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98149228096008</t>
+    <t xml:space="preserve">3.98149251937866</t>
   </si>
   <si>
     <t xml:space="preserve">3.96293044090271</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">3.88868379592896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89332389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79587507247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89309883117676</t>
+    <t xml:space="preserve">3.89332485198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79587531089783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89309930801392</t>
   </si>
   <si>
     <t xml:space="preserve">4.02677822113037</t>
@@ -320,25 +320,25 @@
     <t xml:space="preserve">4.07602739334106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08306360244751</t>
+    <t xml:space="preserve">4.08306312561035</t>
   </si>
   <si>
     <t xml:space="preserve">4.09948062896729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07368183135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09009981155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10182523727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0877537727356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11355209350586</t>
+    <t xml:space="preserve">4.07368326187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0900993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10182476043701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08775329589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1135516166687</t>
   </si>
   <si>
     <t xml:space="preserve">4.08071804046631</t>
@@ -347,49 +347,49 @@
     <t xml:space="preserve">4.01974201202393</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90482473373413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85557508468628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8579204082489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86495590209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8719916343689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8696460723877</t>
+    <t xml:space="preserve">3.90482521057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85557532310486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85792088508606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86495614051819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87199139595032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86964631080627</t>
   </si>
   <si>
     <t xml:space="preserve">4.00567054748535</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00801515579224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95876622200012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05961132049561</t>
+    <t xml:space="preserve">4.00801563262939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95876574516296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05960988998413</t>
   </si>
   <si>
     <t xml:space="preserve">3.88606309890747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88840818405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04084920883179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16514587402344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15576648712158</t>
+    <t xml:space="preserve">3.88840866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04084873199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16514682769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15576553344727</t>
   </si>
   <si>
     <t xml:space="preserve">4.14873027801514</t>
@@ -398,64 +398,64 @@
     <t xml:space="preserve">4.13231372833252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00332498550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04319429397583</t>
+    <t xml:space="preserve">4.00332546234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04319381713867</t>
   </si>
   <si>
     <t xml:space="preserve">4.16045618057251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15811157226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1158971786499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06899213790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1346583366394</t>
+    <t xml:space="preserve">4.15811204910278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11589765548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06899261474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13465881347656</t>
   </si>
   <si>
     <t xml:space="preserve">4.14169454574585</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18390846252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16280174255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21908664703369</t>
+    <t xml:space="preserve">4.18390893936157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16280126571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21908712387085</t>
   </si>
   <si>
     <t xml:space="preserve">4.29178905487061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29648017883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31055164337158</t>
+    <t xml:space="preserve">4.29647970199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31055212020874</t>
   </si>
   <si>
     <t xml:space="preserve">4.28709936141968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3316593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33869504928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54038619995117</t>
+    <t xml:space="preserve">4.33165836334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33869457244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54038524627686</t>
   </si>
   <si>
     <t xml:space="preserve">4.51458787918091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52162408828735</t>
+    <t xml:space="preserve">4.5216236114502</t>
   </si>
   <si>
     <t xml:space="preserve">4.43719482421875</t>
@@ -464,19 +464,19 @@
     <t xml:space="preserve">4.47940921783447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45595598220825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66233682632446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67171907424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58963537216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55914735794067</t>
+    <t xml:space="preserve">4.45595645904541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66233777999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67171859741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58963489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55914688110352</t>
   </si>
   <si>
     <t xml:space="preserve">4.56383752822876</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">4.54976606369019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60370683670044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59667062759399</t>
+    <t xml:space="preserve">4.60370635986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59667158126831</t>
   </si>
   <si>
     <t xml:space="preserve">4.57321882247925</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">4.62012386322021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59432649612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65061187744141</t>
+    <t xml:space="preserve">4.59432506561279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65061140060425</t>
   </si>
   <si>
     <t xml:space="preserve">4.57556390762329</t>
@@ -512,19 +512,19 @@
     <t xml:space="preserve">4.67406415939331</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70924234390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60136127471924</t>
+    <t xml:space="preserve">4.70924282073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60136222839355</t>
   </si>
   <si>
     <t xml:space="preserve">4.48644495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46533727645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39967107772827</t>
+    <t xml:space="preserve">4.4653377532959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39967060089111</t>
   </si>
   <si>
     <t xml:space="preserve">4.43250417709351</t>
@@ -533,16 +533,16 @@
     <t xml:space="preserve">4.50520610809326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49113512039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51693391799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50286149978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48878955841064</t>
+    <t xml:space="preserve">4.49113464355469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51693344116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50286245346069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48879051208496</t>
   </si>
   <si>
     <t xml:space="preserve">4.65295648574829</t>
@@ -560,52 +560,52 @@
     <t xml:space="preserve">4.69048070907593</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58728981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56852769851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47471809387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44657611846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54742097854614</t>
+    <t xml:space="preserve">4.58729028701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.568528175354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47471761703491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44657516479492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54742050170898</t>
   </si>
   <si>
     <t xml:space="preserve">4.44188547134399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50051641464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52631425857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36683797836304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37152767181396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33400440216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32931423187256</t>
+    <t xml:space="preserve">4.50051593780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52631330490112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36683750152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37152719497681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33400392532349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3293137550354</t>
   </si>
   <si>
     <t xml:space="preserve">4.30586099624634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30351591110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25661039352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20736169815063</t>
+    <t xml:space="preserve">4.30351638793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25661134719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20736122131348</t>
   </si>
   <si>
     <t xml:space="preserve">4.09478950500488</t>
@@ -614,25 +614,25 @@
     <t xml:space="preserve">4.24253988265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20267105102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9564208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95407605171204</t>
+    <t xml:space="preserve">4.20267057418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95642042160034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95407462120056</t>
   </si>
   <si>
     <t xml:space="preserve">4.0338134765625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12527799606323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01739692687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12996864318848</t>
+    <t xml:space="preserve">4.12527847290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01739597320557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12996816635132</t>
   </si>
   <si>
     <t xml:space="preserve">4.1721830368042</t>
@@ -641,64 +641,64 @@
     <t xml:space="preserve">4.21205139160156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18859910964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24957656860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20501565933228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26833820343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22846794128418</t>
+    <t xml:space="preserve">4.18859958648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24957609176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20501661300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26833724975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22846841812134</t>
   </si>
   <si>
     <t xml:space="preserve">4.24723052978516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31993246078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36449193954468</t>
+    <t xml:space="preserve">4.31993341445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449241638184</t>
   </si>
   <si>
     <t xml:space="preserve">4.28944492340088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27771806716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30117034912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32227802276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35745620727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34807586669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34338521957397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39029026031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36214685440063</t>
+    <t xml:space="preserve">4.27771902084351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30116987228394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32227754592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35745668411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34807634353638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34338569641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39028930664062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36214733123779</t>
   </si>
   <si>
     <t xml:space="preserve">4.32462406158447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39732503890991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37387275695801</t>
+    <t xml:space="preserve">4.39732599258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37387323379517</t>
   </si>
   <si>
     <t xml:space="preserve">4.36918210983276</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">4.45830154418945</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42546892166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43484926223755</t>
+    <t xml:space="preserve">4.42546844482422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43484973907471</t>
   </si>
   <si>
     <t xml:space="preserve">4.46768283843994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40201663970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3527660369873</t>
+    <t xml:space="preserve">4.40201616287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35276651382446</t>
   </si>
   <si>
     <t xml:space="preserve">4.3855996131897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43954086303711</t>
+    <t xml:space="preserve">4.43953990936279</t>
   </si>
   <si>
     <t xml:space="preserve">4.43015909194946</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">4.49348068237305</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47237253189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52396869659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54273080825806</t>
+    <t xml:space="preserve">4.47237348556519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52396965026855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5427303314209</t>
   </si>
   <si>
     <t xml:space="preserve">4.53804016113281</t>
@@ -752,49 +752,49 @@
     <t xml:space="preserve">4.54507541656494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58259916305542</t>
+    <t xml:space="preserve">4.58260011672974</t>
   </si>
   <si>
     <t xml:space="preserve">4.57790946960449</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55211114883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57087373733521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53569507598877</t>
+    <t xml:space="preserve">4.55211210250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57087326049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53569459915161</t>
   </si>
   <si>
     <t xml:space="preserve">4.50755214691162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58494472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65530204772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74207544326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7561469078064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80774307250977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83119535446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89686155319214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94845819473267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09855270385742</t>
+    <t xml:space="preserve">4.58494424819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65530252456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74207592010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75614786148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80774211883545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83119583129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89686107635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94845676422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09855222702026</t>
   </si>
   <si>
     <t xml:space="preserve">5.05164813995361</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">5.12200498580933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04695701599121</t>
+    <t xml:space="preserve">5.04695749282837</t>
   </si>
   <si>
     <t xml:space="preserve">5.0563383102417</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">4.99536180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01881408691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02819538116455</t>
+    <t xml:space="preserve">5.01881456375122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02819490432739</t>
   </si>
   <si>
     <t xml:space="preserve">5.03288507461548</t>
@@ -824,52 +824,52 @@
     <t xml:space="preserve">4.93907594680786</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97659969329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92500495910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96721935272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08917140960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17360019683838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14545726776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1595287322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09386157989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16421985626221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25333881378174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18767261505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41750478744507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67079162597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60043334960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62388610839844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66140985488892</t>
+    <t xml:space="preserve">4.97660064697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92500352859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96721982955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08917188644409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1735987663269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14545774459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15952920913696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09386205673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16421890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25333786010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18767118453979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41750526428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67079067230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60043430328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62388563156128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66140937805176</t>
   </si>
   <si>
     <t xml:space="preserve">5.68486261367798</t>
@@ -878,16 +878,16 @@
     <t xml:space="preserve">5.57698154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">5.60512399673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7223858833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69403457641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74128675460815</t>
+    <t xml:space="preserve">5.60512495040894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72238683700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6940336227417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74128818511963</t>
   </si>
   <si>
     <t xml:space="preserve">5.76491451263428</t>
@@ -896,10 +896,10 @@
     <t xml:space="preserve">5.75073862075806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87832260131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86887216567993</t>
+    <t xml:space="preserve">5.87832164764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86887168884277</t>
   </si>
   <si>
     <t xml:space="preserve">5.88304758071899</t>
@@ -908,22 +908,22 @@
     <t xml:space="preserve">6.02008247375488</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9917311668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00118112564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9350266456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85942220687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80271768569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75546407699585</t>
+    <t xml:space="preserve">5.99173069000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00118207931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93502616882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85942077636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8027172088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75546360015869</t>
   </si>
   <si>
     <t xml:space="preserve">5.73183727264404</t>
@@ -935,13 +935,13 @@
     <t xml:space="preserve">5.81216812133789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95865297317505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93030166625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.98228025436401</t>
+    <t xml:space="preserve">5.95865345001221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93030118942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.98227977752686</t>
   </si>
   <si>
     <t xml:space="preserve">5.90194892883301</t>
@@ -950,19 +950,19 @@
     <t xml:space="preserve">5.91612577438354</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91139984130859</t>
+    <t xml:space="preserve">5.91140031814575</t>
   </si>
   <si>
     <t xml:space="preserve">5.83106899261475</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88777351379395</t>
+    <t xml:space="preserve">5.88777303695679</t>
   </si>
   <si>
     <t xml:space="preserve">5.78381586074829</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80744218826294</t>
+    <t xml:space="preserve">5.8074426651001</t>
   </si>
   <si>
     <t xml:space="preserve">5.84524488449097</t>
@@ -974,136 +974,136 @@
     <t xml:space="preserve">5.82634401321411</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82161808013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85469532012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79326677322388</t>
+    <t xml:space="preserve">5.82161855697632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85469627380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79326725006104</t>
   </si>
   <si>
     <t xml:space="preserve">5.83579444885254</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95392847061157</t>
+    <t xml:space="preserve">5.95392799377441</t>
   </si>
   <si>
     <t xml:space="preserve">5.92557573318481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.94447755813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7790904045105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74601364135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71766138076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6515064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66095685958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79799127578735</t>
+    <t xml:space="preserve">5.94447708129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77909088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74601268768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71766090393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.65150594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66095638275146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79799175262451</t>
   </si>
   <si>
     <t xml:space="preserve">5.76018857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69876003265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66568279266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73656272888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78854131698608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76963996887207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89249753952026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97282886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15239286422729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14766693115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28470230102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1382155418396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1240406036377</t>
+    <t xml:space="preserve">5.69875955581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6656813621521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73656320571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78854179382324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76963949203491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89249897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97282934188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15239238739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14766645431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28470182418823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13821601867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12404012680054</t>
   </si>
   <si>
     <t xml:space="preserve">6.02953386306763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10513925552368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16656827926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11459016799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31777858734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34140586853027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40756130218506</t>
+    <t xml:space="preserve">6.10513877868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16656875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11458873748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31777954101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34140634536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40756034851074</t>
   </si>
   <si>
     <t xml:space="preserve">6.50206756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42173671722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.30832767486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47844076156616</t>
+    <t xml:space="preserve">6.42173719406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30832862854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.478440284729</t>
   </si>
   <si>
     <t xml:space="preserve">6.31305360794067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33668088912964</t>
+    <t xml:space="preserve">6.33667993545532</t>
   </si>
   <si>
     <t xml:space="preserve">6.37448310852051</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17601871490479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09096384048462</t>
+    <t xml:space="preserve">6.17601919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09096336364746</t>
   </si>
   <si>
     <t xml:space="preserve">6.23272275924683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03898477554321</t>
+    <t xml:space="preserve">6.03898429870605</t>
   </si>
   <si>
     <t xml:space="preserve">6.08623743057251</t>
@@ -1121,16 +1121,16 @@
     <t xml:space="preserve">6.03425931930542</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0956883430481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0626106262207</t>
+    <t xml:space="preserve">6.09568786621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06261110305786</t>
   </si>
   <si>
     <t xml:space="preserve">6.18074417114258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08151245117188</t>
+    <t xml:space="preserve">6.08151197433472</t>
   </si>
   <si>
     <t xml:space="preserve">6.15711736679077</t>
@@ -1145,16 +1145,16 @@
     <t xml:space="preserve">6.24689912796021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20909690856934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22799777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19964599609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12876558303833</t>
+    <t xml:space="preserve">6.20909643173218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22799825668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19964551925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12876510620117</t>
   </si>
   <si>
     <t xml:space="preserve">6.07206201553345</t>
@@ -1163,16 +1163,16 @@
     <t xml:space="preserve">6.05788564682007</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13349103927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14294195175171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01063299179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94920206069946</t>
+    <t xml:space="preserve">6.13349056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14294147491455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01063203811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94920253753662</t>
   </si>
   <si>
     <t xml:space="preserve">5.97755432128906</t>
@@ -1181,25 +1181,25 @@
     <t xml:space="preserve">6.05316066741943</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99645566940308</t>
+    <t xml:space="preserve">5.99645614624023</t>
   </si>
   <si>
     <t xml:space="preserve">6.06733655929565</t>
   </si>
   <si>
-    <t xml:space="preserve">5.93975210189819</t>
+    <t xml:space="preserve">5.93975114822388</t>
   </si>
   <si>
     <t xml:space="preserve">5.71293544769287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72711181640625</t>
+    <t xml:space="preserve">5.72711133956909</t>
   </si>
   <si>
     <t xml:space="preserve">5.92085075378418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57590103149414</t>
+    <t xml:space="preserve">5.57590055465698</t>
   </si>
   <si>
     <t xml:space="preserve">5.52864742279053</t>
@@ -1208,46 +1208,46 @@
     <t xml:space="preserve">5.42941522598267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50502061843872</t>
+    <t xml:space="preserve">5.50502109527588</t>
   </si>
   <si>
     <t xml:space="preserve">5.61370372772217</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63733053207397</t>
+    <t xml:space="preserve">5.63733100891113</t>
   </si>
   <si>
     <t xml:space="preserve">6.04370927810669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98700523376465</t>
+    <t xml:space="preserve">5.98700571060181</t>
   </si>
   <si>
     <t xml:space="preserve">6.01535701751709</t>
   </si>
   <si>
-    <t xml:space="preserve">5.89722394943237</t>
+    <t xml:space="preserve">5.89722442626953</t>
   </si>
   <si>
     <t xml:space="preserve">5.81689357757568</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87359714508057</t>
+    <t xml:space="preserve">5.87359666824341</t>
   </si>
   <si>
     <t xml:space="preserve">5.86414623260498</t>
   </si>
   <si>
-    <t xml:space="preserve">5.9066743850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96810340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01550722122192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02026987075806</t>
+    <t xml:space="preserve">5.90667486190796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96810388565063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01550769805908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0202693939209</t>
   </si>
   <si>
     <t xml:space="preserve">5.99169301986694</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">6.08218812942505</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20602178573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.18697023391724</t>
+    <t xml:space="preserve">6.2060227394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.18697071075439</t>
   </si>
   <si>
     <t xml:space="preserve">6.08695077896118</t>
@@ -1268,52 +1268,52 @@
     <t xml:space="preserve">6.07266187667847</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16315650939941</t>
+    <t xml:space="preserve">6.16315603256226</t>
   </si>
   <si>
     <t xml:space="preserve">6.27270269393921</t>
   </si>
   <si>
-    <t xml:space="preserve">6.25365114212036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13934278488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2917537689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38701200485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52513456344604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59657764434814</t>
+    <t xml:space="preserve">6.2536506652832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13934230804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29175424575806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38701105117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5251350402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59657859802246</t>
   </si>
   <si>
     <t xml:space="preserve">6.69183492660522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69659757614136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62039232254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57276296615601</t>
+    <t xml:space="preserve">6.69659852981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62039184570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57276391983032</t>
   </si>
   <si>
     <t xml:space="preserve">6.50608348846436</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58228921890259</t>
+    <t xml:space="preserve">6.58228874206543</t>
   </si>
   <si>
     <t xml:space="preserve">6.65373229980469</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71088647842407</t>
+    <t xml:space="preserve">6.71088600158691</t>
   </si>
   <si>
     <t xml:space="preserve">6.82519626617432</t>
@@ -1322,52 +1322,52 @@
     <t xml:space="preserve">6.77280473709106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82995891571045</t>
+    <t xml:space="preserve">6.82995843887329</t>
   </si>
   <si>
     <t xml:space="preserve">7.02523612976074</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92521572113037</t>
+    <t xml:space="preserve">6.92521619796753</t>
   </si>
   <si>
     <t xml:space="preserve">6.92045307159424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01094770431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.96808195114136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91092729568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01570987701416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04905033111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09667921066284</t>
+    <t xml:space="preserve">7.0109486579895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9680814743042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91092777252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01571083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04905080795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0966796875</t>
   </si>
   <si>
     <t xml:space="preserve">7.17764806747437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.28243112564087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22051382064819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23956489562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27766895294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12525606155396</t>
+    <t xml:space="preserve">7.28243160247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22051334381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23956537246704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27766847610474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12525653839111</t>
   </si>
   <si>
     <t xml:space="preserve">6.94903039932251</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">6.86806201934814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00142192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00618410110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06333923339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760772705078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99189615249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0395245552063</t>
+    <t xml:space="preserve">7.00142097473145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00618505477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0633397102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760725021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9918966293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03952503204346</t>
   </si>
   <si>
     <t xml:space="preserve">7.02047348022461</t>
@@ -1400,28 +1400,28 @@
     <t xml:space="preserve">7.07762765884399</t>
   </si>
   <si>
-    <t xml:space="preserve">7.18717432022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21098899841309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.41579103469849</t>
+    <t xml:space="preserve">7.18717384338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21098852157593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.41579151153564</t>
   </si>
   <si>
     <t xml:space="preserve">7.29672002792358</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26337957382202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.24432849884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27290630340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30624628067017</t>
+    <t xml:space="preserve">7.2633810043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.24432802200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2729058265686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30624580383301</t>
   </si>
   <si>
     <t xml:space="preserve">7.18241119384766</t>
@@ -1442,22 +1442,22 @@
     <t xml:space="preserve">7.1681227684021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90140151977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94426727294922</t>
+    <t xml:space="preserve">6.90140104293823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94426774978638</t>
   </si>
   <si>
     <t xml:space="preserve">7.06810235977173</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98713302612305</t>
+    <t xml:space="preserve">6.98713350296021</t>
   </si>
   <si>
     <t xml:space="preserve">7.1300196647644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87758731842041</t>
+    <t xml:space="preserve">6.87758684158325</t>
   </si>
   <si>
     <t xml:space="preserve">6.70612287521362</t>
@@ -1466,16 +1466,16 @@
     <t xml:space="preserve">6.63944339752197</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65849447250366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32985734939575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19649696350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11552810668945</t>
+    <t xml:space="preserve">6.65849494934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32985687255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19649600982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11552858352661</t>
   </si>
   <si>
     <t xml:space="preserve">6.04884767532349</t>
@@ -1490,22 +1490,22 @@
     <t xml:space="preserve">6.33461999893188</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34414577484131</t>
+    <t xml:space="preserve">6.34414625167847</t>
   </si>
   <si>
     <t xml:space="preserve">6.12505292892456</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15363073348999</t>
+    <t xml:space="preserve">6.15363121032715</t>
   </si>
   <si>
     <t xml:space="preserve">6.30604267120361</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35367107391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47274303436279</t>
+    <t xml:space="preserve">6.35367155075073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47274351119995</t>
   </si>
   <si>
     <t xml:space="preserve">6.46798038482666</t>
@@ -1514,7 +1514,7 @@
     <t xml:space="preserve">6.42987775802612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52989768981934</t>
+    <t xml:space="preserve">6.52989816665649</t>
   </si>
   <si>
     <t xml:space="preserve">6.76804161071777</t>
@@ -1523,10 +1523,10 @@
     <t xml:space="preserve">7.08239078521729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11096811294556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12049341201782</t>
+    <t xml:space="preserve">7.1109676361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12049436569214</t>
   </si>
   <si>
     <t xml:space="preserve">7.32529735565186</t>
@@ -1535,40 +1535,40 @@
     <t xml:space="preserve">7.31577157974243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11573028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03476142883301</t>
+    <t xml:space="preserve">7.11573123931885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03476285934448</t>
   </si>
   <si>
     <t xml:space="preserve">7.15383434295654</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04428768157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02999877929688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17288637161255</t>
+    <t xml:space="preserve">7.04428815841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02999973297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17288494110107</t>
   </si>
   <si>
     <t xml:space="preserve">7.36340045928955</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14430856704712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20622587203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32053422927856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09191656112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98237037658691</t>
+    <t xml:space="preserve">7.14430809020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20622539520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32053470611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09191703796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98236989974976</t>
   </si>
   <si>
     <t xml:space="preserve">7.44913196563721</t>
@@ -1577,22 +1577,22 @@
     <t xml:space="preserve">7.3824520111084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33006000518799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21575164794922</t>
+    <t xml:space="preserve">7.33006048202515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21575117111206</t>
   </si>
   <si>
     <t xml:space="preserve">7.33958578109741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35387372970581</t>
+    <t xml:space="preserve">7.35387420654297</t>
   </si>
   <si>
     <t xml:space="preserve">7.55391550064087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60630702972412</t>
+    <t xml:space="preserve">7.60630655288696</t>
   </si>
   <si>
     <t xml:space="preserve">7.46342039108276</t>
@@ -1601,94 +1601,94 @@
     <t xml:space="preserve">7.49199771881104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44436931610107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42055511474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62535858154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53010082244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47294521331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48723554611206</t>
+    <t xml:space="preserve">7.44436836242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42055463790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62535810470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53010129928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47294616699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4872350692749</t>
   </si>
   <si>
     <t xml:space="preserve">7.46818351745605</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49676084518433</t>
+    <t xml:space="preserve">7.49675989151001</t>
   </si>
   <si>
     <t xml:space="preserve">7.51581192016602</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61107015609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.56344127655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6444091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73490381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80634737014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86826467514038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85873937606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88731527328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92541837692261</t>
+    <t xml:space="preserve">7.61106967926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.56344079971313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64440965652466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73490428924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80634641647339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8682656288147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85873794555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88731575012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92541790008545</t>
   </si>
   <si>
     <t xml:space="preserve">7.95399618148804</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83492517471313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98733758926392</t>
+    <t xml:space="preserve">7.83492469787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9873366355896</t>
   </si>
   <si>
     <t xml:space="preserve">8.01115131378174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06354236602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53486347198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52057504653931</t>
+    <t xml:space="preserve">8.06354331970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53486394882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52057552337646</t>
   </si>
   <si>
     <t xml:space="preserve">7.54438972473145</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62059545516968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63964700698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77777051925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.76824474334717</t>
+    <t xml:space="preserve">7.62059497833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63964748382568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77776956558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.76824426651001</t>
   </si>
   <si>
     <t xml:space="preserve">7.90636825561523</t>
@@ -1697,16 +1697,16 @@
     <t xml:space="preserve">8.0349645614624</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00638771057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04448986053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06830596923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20166492462158</t>
+    <t xml:space="preserve">8.00638866424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04449081420898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06830406188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2016658782959</t>
   </si>
   <si>
     <t xml:space="preserve">8.32550048828125</t>
@@ -1715,10 +1715,10 @@
     <t xml:space="preserve">8.44457244873047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33979034423828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38265419006348</t>
+    <t xml:space="preserve">8.33978939056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38265514373779</t>
   </si>
   <si>
     <t xml:space="preserve">8.33502674102783</t>
@@ -1730,28 +1730,28 @@
     <t xml:space="preserve">8.23500633239746</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25881958007812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26358318328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16832542419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31121253967285</t>
+    <t xml:space="preserve">8.25882244110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26358222961426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16832637786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31121063232422</t>
   </si>
   <si>
     <t xml:space="preserve">8.36836624145508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.354079246521</t>
+    <t xml:space="preserve">8.35407829284668</t>
   </si>
   <si>
     <t xml:space="preserve">8.37789344787598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28739643096924</t>
+    <t xml:space="preserve">8.28739738464355</t>
   </si>
   <si>
     <t xml:space="preserve">8.21119213104248</t>
@@ -1766,10 +1766,10 @@
     <t xml:space="preserve">8.445876121521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56085300445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51294612884521</t>
+    <t xml:space="preserve">8.56085205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51294708251953</t>
   </si>
   <si>
     <t xml:space="preserve">8.48899173736572</t>
@@ -1784,10 +1784,10 @@
     <t xml:space="preserve">8.49857425689697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48420143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67103672027588</t>
+    <t xml:space="preserve">8.48420238494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6710376739502</t>
   </si>
   <si>
     <t xml:space="preserve">8.8147554397583</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">8.74289512634277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83391761779785</t>
+    <t xml:space="preserve">8.83391857147217</t>
   </si>
   <si>
     <t xml:space="preserve">8.77643013000488</t>
@@ -1805,22 +1805,22 @@
     <t xml:space="preserve">8.7093620300293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68540859222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70457077026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78122138977051</t>
+    <t xml:space="preserve">8.6854076385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70456981658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78122043609619</t>
   </si>
   <si>
     <t xml:space="preserve">8.80996417999268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77163887023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65187454223633</t>
+    <t xml:space="preserve">8.77163982391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6518726348877</t>
   </si>
   <si>
     <t xml:space="preserve">8.53689765930176</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">8.37880706787109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.37401676177979</t>
+    <t xml:space="preserve">8.3740177154541</t>
   </si>
   <si>
     <t xml:space="preserve">8.40755176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41234111785889</t>
+    <t xml:space="preserve">8.41234302520752</t>
   </si>
   <si>
     <t xml:space="preserve">8.32611083984375</t>
@@ -1844,13 +1844,13 @@
     <t xml:space="preserve">8.45545864105225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41713333129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39318084716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54648017883301</t>
+    <t xml:space="preserve">8.41713428497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39317989349365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54647922515869</t>
   </si>
   <si>
     <t xml:space="preserve">8.58959674835205</t>
@@ -1859,25 +1859,25 @@
     <t xml:space="preserve">8.27341365814209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25425052642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35485553741455</t>
+    <t xml:space="preserve">8.25425148010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35485458374023</t>
   </si>
   <si>
     <t xml:space="preserve">8.4746208190918</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42192459106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36922645568848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31652927398682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29736804962158</t>
+    <t xml:space="preserve">8.42192363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36922550201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31653118133545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29736709594727</t>
   </si>
   <si>
     <t xml:space="preserve">8.28299522399902</t>
@@ -1886,7 +1886,7 @@
     <t xml:space="preserve">8.1776008605957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2015552520752</t>
+    <t xml:space="preserve">8.20155620574951</t>
   </si>
   <si>
     <t xml:space="preserve">8.16322994232178</t>
@@ -1895,49 +1895,49 @@
     <t xml:space="preserve">8.24946117401123</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18239212036133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17281055450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09616184234619</t>
+    <t xml:space="preserve">8.18239307403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17281150817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09615993499756</t>
   </si>
   <si>
     <t xml:space="preserve">8.14885807037354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06741809844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03867244720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97160530090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78956079483032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62188911437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61709785461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66021394729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.50212335586548</t>
+    <t xml:space="preserve">8.06741714477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03867435455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97160482406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78956127166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62188863754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61709833145142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66021347045898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.50212287902832</t>
   </si>
   <si>
     <t xml:space="preserve">7.72249221801758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59314489364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45900726318359</t>
+    <t xml:space="preserve">7.5931453704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45900774002075</t>
   </si>
   <si>
     <t xml:space="preserve">7.51170444488525</t>
@@ -1949,37 +1949,37 @@
     <t xml:space="preserve">7.59793567657471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90932750701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95244121551514</t>
+    <t xml:space="preserve">7.90932655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95244264602661</t>
   </si>
   <si>
     <t xml:space="preserve">7.82309532165527</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8805832862854</t>
+    <t xml:space="preserve">7.88058185577393</t>
   </si>
   <si>
     <t xml:space="preserve">8.10574245452881</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2063455581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1680212020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26383399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34527397155762</t>
+    <t xml:space="preserve">8.20634365081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16802024841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26383304595947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3452730178833</t>
   </si>
   <si>
     <t xml:space="preserve">8.29257678985596</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12011432647705</t>
+    <t xml:space="preserve">8.12011528015137</t>
   </si>
   <si>
     <t xml:space="preserve">8.0338830947876</t>
@@ -1988,13 +1988,13 @@
     <t xml:space="preserve">7.99555730819702</t>
   </si>
   <si>
-    <t xml:space="preserve">7.80872297286987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91411638259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88537168502808</t>
+    <t xml:space="preserve">7.80872344970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91411733627319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88537263870239</t>
   </si>
   <si>
     <t xml:space="preserve">7.82788610458374</t>
@@ -2003,49 +2003,49 @@
     <t xml:space="preserve">7.84704780578613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0003490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89974451065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90453624725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94286108016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71770191192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85662937164307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04346561431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11532306671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12969589233398</t>
+    <t xml:space="preserve">8.00034809112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89974498748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90453577041626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94286060333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71770143508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85662984848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04346370697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11532402038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12969493865967</t>
   </si>
   <si>
     <t xml:space="preserve">8.13448619842529</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00992965698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93327951431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7512354850769</t>
+    <t xml:space="preserve">8.00992870330811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93327856063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75123596191406</t>
   </si>
   <si>
     <t xml:space="preserve">7.578773021698</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64105129241943</t>
+    <t xml:space="preserve">7.64105176925659</t>
   </si>
   <si>
     <t xml:space="preserve">7.69374799728394</t>
@@ -2060,31 +2060,31 @@
     <t xml:space="preserve">7.87100124359131</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87579298019409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92369890213013</t>
+    <t xml:space="preserve">7.87579250335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92369937896729</t>
   </si>
   <si>
     <t xml:space="preserve">7.89495468139648</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8518385887146</t>
+    <t xml:space="preserve">7.85183811187744</t>
   </si>
   <si>
     <t xml:space="preserve">7.8662109375</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98597717285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96681308746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9284873008728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11053276062012</t>
+    <t xml:space="preserve">7.98597621917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9668140411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92848873138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1105318069458</t>
   </si>
   <si>
     <t xml:space="preserve">8.04825401306152</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">7.93807077407837</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77997922897339</t>
+    <t xml:space="preserve">7.77997970581055</t>
   </si>
   <si>
     <t xml:space="preserve">7.81830453872681</t>
@@ -2102,22 +2102,22 @@
     <t xml:space="preserve">7.84225845336914</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79435205459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79914236068726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94765138626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91890811920166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71291160583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77518844604492</t>
+    <t xml:space="preserve">7.79435110092163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7991418838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94765186309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9189076423645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71291065216064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77518892288208</t>
   </si>
   <si>
     <t xml:space="preserve">7.86141967773438</t>
@@ -2132,7 +2132,7 @@
     <t xml:space="preserve">8.26862335205078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33569240570068</t>
+    <t xml:space="preserve">8.335693359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.45066738128662</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">8.47941207885742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55127048492432</t>
+    <t xml:space="preserve">8.55127143859863</t>
   </si>
   <si>
     <t xml:space="preserve">8.59438705444336</t>
@@ -2153,43 +2153,43 @@
     <t xml:space="preserve">8.66624546051025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64229297637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69019794464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58480548858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19197463989258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74165487289429</t>
+    <t xml:space="preserve">8.64229202270508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69019889831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58480453491211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19197273254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74165439605713</t>
   </si>
   <si>
     <t xml:space="preserve">7.70332956314087</t>
   </si>
   <si>
-    <t xml:space="preserve">7.78477048873901</t>
+    <t xml:space="preserve">7.78477001190186</t>
   </si>
   <si>
     <t xml:space="preserve">7.44463539123535</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22426652908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17636013031006</t>
+    <t xml:space="preserve">7.22426605224609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1763596534729</t>
   </si>
   <si>
     <t xml:space="preserve">7.30091667175293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36319541931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33924150466919</t>
+    <t xml:space="preserve">7.36319494247437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33924198150635</t>
   </si>
   <si>
     <t xml:space="preserve">7.09491968154907</t>
@@ -2201,16 +2201,16 @@
     <t xml:space="preserve">6.36195421218872</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33675956726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54754734039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37987518310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30322456359863</t>
+    <t xml:space="preserve">5.3367600440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54754638671875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37987422943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30322504043579</t>
   </si>
   <si>
     <t xml:space="preserve">5.86851930618286</t>
@@ -2219,31 +2219,31 @@
     <t xml:space="preserve">6.45776605606079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08409690856934</t>
+    <t xml:space="preserve">6.08409786224365</t>
   </si>
   <si>
     <t xml:space="preserve">6.03619146347046</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29967546463013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76915645599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84101676940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53441667556763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3715353012085</t>
+    <t xml:space="preserve">6.29967498779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76915740966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84101629257202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53441619873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37153577804565</t>
   </si>
   <si>
     <t xml:space="preserve">6.27572298049927</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02852630615234</t>
+    <t xml:space="preserve">6.02852582931519</t>
   </si>
   <si>
     <t xml:space="preserve">6.11092472076416</t>
@@ -2252,40 +2252,40 @@
     <t xml:space="preserve">5.85606288909912</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45201778411865</t>
+    <t xml:space="preserve">6.45201730728149</t>
   </si>
   <si>
     <t xml:space="preserve">6.38111591339111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32171249389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35237216949463</t>
+    <t xml:space="preserve">6.32171297073364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35237264633179</t>
   </si>
   <si>
     <t xml:space="preserve">6.40986061096191</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40794372558594</t>
+    <t xml:space="preserve">6.4079442024231</t>
   </si>
   <si>
     <t xml:space="preserve">6.47309637069702</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65897178649902</t>
+    <t xml:space="preserve">6.65897226333618</t>
   </si>
   <si>
     <t xml:space="preserve">6.49962091445923</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44746971130371</t>
+    <t xml:space="preserve">6.44746923446655</t>
   </si>
   <si>
     <t xml:space="preserve">6.43008518218994</t>
   </si>
   <si>
-    <t xml:space="preserve">6.393385887146</t>
+    <t xml:space="preserve">6.39338636398315</t>
   </si>
   <si>
     <t xml:space="preserve">6.44360589981079</t>
@@ -2297,19 +2297,19 @@
     <t xml:space="preserve">6.61551284790039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79321432113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82798194885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62323904037476</t>
+    <t xml:space="preserve">6.79321479797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8279824256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6232385635376</t>
   </si>
   <si>
     <t xml:space="preserve">6.690842628479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76617288589478</t>
+    <t xml:space="preserve">6.76617240905762</t>
   </si>
   <si>
     <t xml:space="preserve">6.78935194015503</t>
@@ -2318,13 +2318,13 @@
     <t xml:space="preserve">6.9477367401123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95932674407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.084876537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93807983398438</t>
+    <t xml:space="preserve">6.95932626724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08487606048584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93807935714722</t>
   </si>
   <si>
     <t xml:space="preserve">6.70629501342773</t>
@@ -2333,13 +2333,13 @@
     <t xml:space="preserve">6.66766452789307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9400110244751</t>
+    <t xml:space="preserve">6.94001054763794</t>
   </si>
   <si>
     <t xml:space="preserve">6.5112099647522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67345905303955</t>
+    <t xml:space="preserve">6.67345857620239</t>
   </si>
   <si>
     <t xml:space="preserve">6.53245687484741</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">6.72947311401367</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71208906173706</t>
+    <t xml:space="preserve">6.71209001541138</t>
   </si>
   <si>
     <t xml:space="preserve">7.14668560028076</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">7.09839725494385</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14282178878784</t>
+    <t xml:space="preserve">7.142822265625</t>
   </si>
   <si>
     <t xml:space="preserve">7.14475393295288</t>
@@ -2381,55 +2381,55 @@
     <t xml:space="preserve">7.13895988464355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17758989334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05976629257202</t>
+    <t xml:space="preserve">7.17759037017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05976676940918</t>
   </si>
   <si>
     <t xml:space="preserve">7.20463180541992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06942415237427</t>
+    <t xml:space="preserve">7.06942367553711</t>
   </si>
   <si>
     <t xml:space="preserve">7.31279754638672</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33018112182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38619565963745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44800519943237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44027853012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.58128070831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27223587036133</t>
+    <t xml:space="preserve">7.33018207550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38619613647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44800567626953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44027900695801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5812816619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27223539352417</t>
   </si>
   <si>
     <t xml:space="preserve">7.26837205886841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24326276779175</t>
+    <t xml:space="preserve">7.24326229095459</t>
   </si>
   <si>
     <t xml:space="preserve">7.34370231628418</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54844570159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45380020141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62667274475098</t>
+    <t xml:space="preserve">7.5484447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45379972457886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62667226791382</t>
   </si>
   <si>
     <t xml:space="preserve">7.67013168334961</t>
@@ -2438,64 +2438,64 @@
     <t xml:space="preserve">7.70683145523071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84203815460205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86425113677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81499814987183</t>
+    <t xml:space="preserve">7.84203910827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86425065994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81499719619751</t>
   </si>
   <si>
     <t xml:space="preserve">7.7502908706665</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92412853240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9135046005249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82851791381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89322471618652</t>
+    <t xml:space="preserve">7.92412900924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91350650787354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82851839065552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89322519302368</t>
   </si>
   <si>
     <t xml:space="preserve">7.98497247695923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87294387817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0265007019043</t>
+    <t xml:space="preserve">7.87294340133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02649974822998</t>
   </si>
   <si>
     <t xml:space="preserve">7.88549852371216</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83817625045776</t>
+    <t xml:space="preserve">7.83817577362061</t>
   </si>
   <si>
     <t xml:space="preserve">8.2631139755249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42729473114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21965408325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22158622741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28146362304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23220920562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29594993591309</t>
+    <t xml:space="preserve">8.42729377746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21965312957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22158527374268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28146266937256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23221015930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2959508895874</t>
   </si>
   <si>
     <t xml:space="preserve">8.13659858703613</t>
@@ -2507,16 +2507,16 @@
     <t xml:space="preserve">8.21868896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26601028442383</t>
+    <t xml:space="preserve">8.26601123809814</t>
   </si>
   <si>
     <t xml:space="preserve">8.43598556518555</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3973560333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27760028839111</t>
+    <t xml:space="preserve">8.39735507965088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2775993347168</t>
   </si>
   <si>
     <t xml:space="preserve">8.30753898620605</t>
@@ -2525,55 +2525,55 @@
     <t xml:space="preserve">8.24283218383789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.34423828125</t>
+    <t xml:space="preserve">8.34423923492432</t>
   </si>
   <si>
     <t xml:space="preserve">8.228346824646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39059448242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34327125549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43405342102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31043529510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18102264404297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29788112640381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48330974578857</t>
+    <t xml:space="preserve">8.39059543609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3432731628418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43405437469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3104362487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18102359771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29788208007812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48330879211426</t>
   </si>
   <si>
     <t xml:space="preserve">8.77110767364502</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58664512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47944450378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71799087524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65907859802246</t>
+    <t xml:space="preserve">8.58664608001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47944641113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71799182891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65907764434814</t>
   </si>
   <si>
     <t xml:space="preserve">8.75565624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71412754058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82132720947266</t>
+    <t xml:space="preserve">8.71412658691406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82132625579834</t>
   </si>
   <si>
     <t xml:space="preserve">8.94784355163574</t>
@@ -2582,13 +2582,13 @@
     <t xml:space="preserve">9.01448059082031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03959178924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06083869934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.853196144104</t>
+    <t xml:space="preserve">9.03959083557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06083965301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85319805145264</t>
   </si>
   <si>
     <t xml:space="preserve">8.94011783599854</t>
@@ -2597,25 +2597,25 @@
     <t xml:space="preserve">9.01641368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05118083953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80587577819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08884620666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01158332824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9999942779541</t>
+    <t xml:space="preserve">9.05117988586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80587482452393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08884525299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01158428192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99999523162842</t>
   </si>
   <si>
     <t xml:space="preserve">9.04828453063965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04635143280029</t>
+    <t xml:space="preserve">9.04635047912598</t>
   </si>
   <si>
     <t xml:space="preserve">9.02896785736084</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">9.04442024230957</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21343040466309</t>
+    <t xml:space="preserve">9.21342945098877</t>
   </si>
   <si>
     <t xml:space="preserve">9.23853969573975</t>
@@ -2648,31 +2648,31 @@
     <t xml:space="preserve">9.12554550170898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0318660736084</t>
+    <t xml:space="preserve">9.03186511993408</t>
   </si>
   <si>
     <t xml:space="preserve">9.07629013061523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80008220672607</t>
+    <t xml:space="preserve">8.80008125305176</t>
   </si>
   <si>
     <t xml:space="preserve">8.93528842926025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94687747955322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74020385742188</t>
+    <t xml:space="preserve">8.94687652587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74020290374756</t>
   </si>
   <si>
     <t xml:space="preserve">8.88893127441406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66294193267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50262355804443</t>
+    <t xml:space="preserve">8.66294288635254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50262451171875</t>
   </si>
   <si>
     <t xml:space="preserve">8.65714645385742</t>
@@ -2684,25 +2684,25 @@
     <t xml:space="preserve">8.59727001190186</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76724529266357</t>
+    <t xml:space="preserve">8.76724433898926</t>
   </si>
   <si>
     <t xml:space="preserve">8.89086437225342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96426105499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24626636505127</t>
+    <t xml:space="preserve">8.96426010131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24626541137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.26171779632568</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5128173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35443115234375</t>
+    <t xml:space="preserve">9.51281833648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35443210601807</t>
   </si>
   <si>
     <t xml:space="preserve">9.29841804504395</t>
@@ -2711,34 +2711,34 @@
     <t xml:space="preserve">9.44328212738037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43169212341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25012874603271</t>
+    <t xml:space="preserve">9.4316930770874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25012969970703</t>
   </si>
   <si>
     <t xml:space="preserve">9.13230514526367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22502040863037</t>
+    <t xml:space="preserve">9.22501945495605</t>
   </si>
   <si>
     <t xml:space="preserve">9.06856536865234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19411373138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17286682128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22695064544678</t>
+    <t xml:space="preserve">9.19411468505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17286777496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22694873809814</t>
   </si>
   <si>
     <t xml:space="preserve">9.36215782165527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12650966644287</t>
+    <t xml:space="preserve">9.12651062011719</t>
   </si>
   <si>
     <t xml:space="preserve">9.1477575302124</t>
@@ -2747,28 +2747,28 @@
     <t xml:space="preserve">9.13037395477295</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15934658050537</t>
+    <t xml:space="preserve">9.15934753417969</t>
   </si>
   <si>
     <t xml:space="preserve">9.12264823913574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0048246383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13616752624512</t>
+    <t xml:space="preserve">9.00482368469238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13616847991943</t>
   </si>
   <si>
     <t xml:space="preserve">9.05890655517578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04538631439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83677959442139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87347984313965</t>
+    <t xml:space="preserve">9.04538536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8367805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87347888946533</t>
   </si>
   <si>
     <t xml:space="preserve">8.95267295837402</t>
@@ -2777,67 +2777,67 @@
     <t xml:space="preserve">8.9391508102417</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86961650848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88120651245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96619319915771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13809871673584</t>
+    <t xml:space="preserve">8.86961555480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88120555877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96619415283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13809967041016</t>
   </si>
   <si>
     <t xml:space="preserve">9.02027606964111</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90438365936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66487312316895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59340572357178</t>
+    <t xml:space="preserve">8.90438461303711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66487216949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59340667724609</t>
   </si>
   <si>
     <t xml:space="preserve">8.54125499725342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5528450012207</t>
+    <t xml:space="preserve">8.55284404754639</t>
   </si>
   <si>
     <t xml:space="preserve">8.42150020599365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38093948364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47365093231201</t>
+    <t xml:space="preserve">8.38093757629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47365188598633</t>
   </si>
   <si>
     <t xml:space="preserve">8.42343139648438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4253625869751</t>
+    <t xml:space="preserve">8.42536354064941</t>
   </si>
   <si>
     <t xml:space="preserve">8.54705047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49296569824219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5856819152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51228141784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5064868927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63590049743652</t>
+    <t xml:space="preserve">8.4929666519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58568096160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51228332519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50648784637451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63590145111084</t>
   </si>
   <si>
     <t xml:space="preserve">8.59533786773682</t>
@@ -2849,19 +2849,19 @@
     <t xml:space="preserve">8.57215976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57795429229736</t>
+    <t xml:space="preserve">8.57795333862305</t>
   </si>
   <si>
     <t xml:space="preserve">8.82712268829346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86768627166748</t>
+    <t xml:space="preserve">8.86768531799316</t>
   </si>
   <si>
     <t xml:space="preserve">8.94108390808105</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33704853057861</t>
+    <t xml:space="preserve">9.3370475769043</t>
   </si>
   <si>
     <t xml:space="preserve">9.31773281097412</t>
@@ -2876,31 +2876,31 @@
     <t xml:space="preserve">9.38533687591553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44521427154541</t>
+    <t xml:space="preserve">9.44521331787109</t>
   </si>
   <si>
     <t xml:space="preserve">9.58235359191895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.429762840271</t>
+    <t xml:space="preserve">9.42976093292236</t>
   </si>
   <si>
     <t xml:space="preserve">9.44135189056396</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35249996185303</t>
+    <t xml:space="preserve">9.35249900817871</t>
   </si>
   <si>
     <t xml:space="preserve">9.20570278167725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2887601852417</t>
+    <t xml:space="preserve">9.28875923156738</t>
   </si>
   <si>
     <t xml:space="preserve">9.3158016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34090995788574</t>
+    <t xml:space="preserve">9.34091186523438</t>
   </si>
   <si>
     <t xml:space="preserve">9.05697536468506</t>
@@ -2909,13 +2909,13 @@
     <t xml:space="preserve">9.19218254089355</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16320991516113</t>
+    <t xml:space="preserve">9.16320896148682</t>
   </si>
   <si>
     <t xml:space="preserve">9.04924964904785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26751232147217</t>
+    <t xml:space="preserve">9.26751327514648</t>
   </si>
   <si>
     <t xml:space="preserve">9.16900444030762</t>
@@ -2930,52 +2930,52 @@
     <t xml:space="preserve">9.76391792297363</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48964023590088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46839332580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38726806640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42589855194092</t>
+    <t xml:space="preserve">9.48963928222656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46839141845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38726902008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42589950561523</t>
   </si>
   <si>
     <t xml:space="preserve">9.364089012146</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28296566009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25978660583496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24240398406982</t>
+    <t xml:space="preserve">9.2829647064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25978755950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24240303039551</t>
   </si>
   <si>
     <t xml:space="preserve">9.26364994049072</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28682899475098</t>
+    <t xml:space="preserve">9.28682804107666</t>
   </si>
   <si>
     <t xml:space="preserve">9.3505687713623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23081398010254</t>
+    <t xml:space="preserve">9.23081302642822</t>
   </si>
   <si>
     <t xml:space="preserve">9.39885807037354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32932090759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46452903747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41624069213867</t>
+    <t xml:space="preserve">9.32932186126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4645299911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41624164581299</t>
   </si>
   <si>
     <t xml:space="preserve">9.63836765289307</t>
@@ -2984,37 +2984,37 @@
     <t xml:space="preserve">9.47225475311279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56497097015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64416313171387</t>
+    <t xml:space="preserve">9.56497001647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64416217803955</t>
   </si>
   <si>
     <t xml:space="preserve">9.76943683624268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55384826660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73544788360596</t>
+    <t xml:space="preserve">9.55384922027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73544692993164</t>
   </si>
   <si>
     <t xml:space="preserve">9.83255958557129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70340061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62959671020508</t>
+    <t xml:space="preserve">9.70340156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62959575653076</t>
   </si>
   <si>
     <t xml:space="preserve">9.60823154449463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52859973907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63347911834717</t>
+    <t xml:space="preserve">9.52860069274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63348007202148</t>
   </si>
   <si>
     <t xml:space="preserve">9.8811149597168</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">9.7742919921875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86654663085938</t>
+    <t xml:space="preserve">9.86654758453369</t>
   </si>
   <si>
     <t xml:space="preserve">9.82284736633301</t>
@@ -3047,64 +3047,64 @@
     <t xml:space="preserve">9.82770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79857063293457</t>
+    <t xml:space="preserve">9.79856872558594</t>
   </si>
   <si>
     <t xml:space="preserve">9.79371452331543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656280517578</t>
+    <t xml:space="preserve">10.0656270980835</t>
   </si>
   <si>
     <t xml:space="preserve">10.1675939559937</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2355728149414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2549953460693</t>
+    <t xml:space="preserve">10.2355718612671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.254994392395</t>
   </si>
   <si>
     <t xml:space="preserve">10.1870174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.14817237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2307167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2792720794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2744178771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3132619857788</t>
+    <t xml:space="preserve">10.1481714248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2307176589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2792730331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2744169235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3132629394531</t>
   </si>
   <si>
     <t xml:space="preserve">10.3909511566162</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5754632949829</t>
+    <t xml:space="preserve">10.5754642486572</t>
   </si>
   <si>
     <t xml:space="preserve">10.6337299346924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8133869171143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8182430267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8328094482422</t>
+    <t xml:space="preserve">10.8133878707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8182420730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8328084945679</t>
   </si>
   <si>
     <t xml:space="preserve">10.8230991363525</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8570871353149</t>
+    <t xml:space="preserve">10.8570880889893</t>
   </si>
   <si>
     <t xml:space="preserve">10.7551202774048</t>
@@ -3116,16 +3116,16 @@
     <t xml:space="preserve">10.7842531204224</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0853004455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0755882263184</t>
+    <t xml:space="preserve">11.0852994918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0755891799927</t>
   </si>
   <si>
     <t xml:space="preserve">11.0610218048096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0464544296265</t>
+    <t xml:space="preserve">11.0464553833008</t>
   </si>
   <si>
     <t xml:space="preserve">10.9687652587891</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">10.9104986190796</t>
   </si>
   <si>
-    <t xml:space="preserve">10.891077041626</t>
+    <t xml:space="preserve">10.8910779953003</t>
   </si>
   <si>
     <t xml:space="preserve">10.997899055481</t>
@@ -3146,22 +3146,22 @@
     <t xml:space="preserve">10.827953338623</t>
   </si>
   <si>
-    <t xml:space="preserve">10.954197883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9784784317017</t>
+    <t xml:space="preserve">10.9541988372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9784774780273</t>
   </si>
   <si>
     <t xml:space="preserve">10.8667984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6531524658203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7162742614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9930438995361</t>
+    <t xml:space="preserve">10.6531534194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7162761688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9930429458618</t>
   </si>
   <si>
     <t xml:space="preserve">11.1629886627197</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">11.0513105392456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4009132385254</t>
+    <t xml:space="preserve">11.4009122848511</t>
   </si>
   <si>
     <t xml:space="preserve">11.4688920974731</t>
@@ -3179,13 +3179,13 @@
     <t xml:space="preserve">11.4931688308716</t>
   </si>
   <si>
-    <t xml:space="preserve">11.51744556427</t>
+    <t xml:space="preserve">11.5174465179443</t>
   </si>
   <si>
     <t xml:space="preserve">11.5951366424561</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5611476898193</t>
+    <t xml:space="preserve">11.561146736145</t>
   </si>
   <si>
     <t xml:space="preserve">11.5028800964355</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">11.6048469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5805692672729</t>
+    <t xml:space="preserve">11.5805702209473</t>
   </si>
   <si>
     <t xml:space="preserve">11.5660028457642</t>
@@ -3206,19 +3206,19 @@
     <t xml:space="preserve">11.721381187439</t>
   </si>
   <si>
-    <t xml:space="preserve">11.862193107605</t>
+    <t xml:space="preserve">11.8621940612793</t>
   </si>
   <si>
     <t xml:space="preserve">11.745659828186</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6922473907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6825370788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3620672225952</t>
+    <t xml:space="preserve">11.6922483444214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6825361251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3620681762695</t>
   </si>
   <si>
     <t xml:space="preserve">11.2552452087402</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">11.4834575653076</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4251899719238</t>
+    <t xml:space="preserve">11.4251909255981</t>
   </si>
   <si>
     <t xml:space="preserve">11.3814907073975</t>
@@ -3236,13 +3236,13 @@
     <t xml:space="preserve">11.3669233322144</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3329343795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3717803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5902814865112</t>
+    <t xml:space="preserve">11.332935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3717794418335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5902805328369</t>
   </si>
   <si>
     <t xml:space="preserve">11.6971035003662</t>
@@ -3260,31 +3260,31 @@
     <t xml:space="preserve">11.410623550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5514364242554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7068147659302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9495944976807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9301710128784</t>
+    <t xml:space="preserve">11.5514373779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7068157196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.949595451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9301719665527</t>
   </si>
   <si>
     <t xml:space="preserve">11.7942161560059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7602262496948</t>
+    <t xml:space="preserve">11.7602252960205</t>
   </si>
   <si>
     <t xml:space="preserve">11.8087816238403</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8282060623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7505149841309</t>
+    <t xml:space="preserve">11.8282051086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7505159378052</t>
   </si>
   <si>
     <t xml:space="preserve">11.9253158569336</t>
@@ -3296,7 +3296,7 @@
     <t xml:space="preserve">12.0564165115356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0369939804077</t>
+    <t xml:space="preserve">12.0369958877563</t>
   </si>
   <si>
     <t xml:space="preserve">12.187518119812</t>
@@ -3308,61 +3308,61 @@
     <t xml:space="preserve">12.3865966796875</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5565423965454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4254417419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5274076461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5322647094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5662527084351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9350271224976</t>
+    <t xml:space="preserve">12.5565433502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.425440788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5274085998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5322637557983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5662517547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9350261688232</t>
   </si>
   <si>
     <t xml:space="preserve">12.012716293335</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0758399963379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1729516983032</t>
+    <t xml:space="preserve">12.0758390426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1729507446289</t>
   </si>
   <si>
     <t xml:space="preserve">12.3331842422485</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3137636184692</t>
+    <t xml:space="preserve">12.3137626647949</t>
   </si>
   <si>
     <t xml:space="preserve">12.4205856323242</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3040504455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4108753204346</t>
+    <t xml:space="preserve">12.304051399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4108734130859</t>
   </si>
   <si>
     <t xml:space="preserve">12.4448623657227</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4157295227051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5468311309814</t>
+    <t xml:space="preserve">12.4157304763794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5468320846558</t>
   </si>
   <si>
     <t xml:space="preserve">12.6439437866211</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7750415802002</t>
+    <t xml:space="preserve">12.7750434875488</t>
   </si>
   <si>
     <t xml:space="preserve">12.9644107818604</t>
@@ -3371,10 +3371,10 @@
     <t xml:space="preserve">12.9595565795898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9401330947876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0760889053345</t>
+    <t xml:space="preserve">12.9401321411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0760898590088</t>
   </si>
   <si>
     <t xml:space="preserve">12.5808200836182</t>
@@ -3383,19 +3383,19 @@
     <t xml:space="preserve">12.595386505127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.91100025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4837074279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7070655822754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4982748031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4739990234375</t>
+    <t xml:space="preserve">12.9109992980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4837083816528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7070646286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4982738494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4739971160889</t>
   </si>
   <si>
     <t xml:space="preserve">12.3428964614868</t>
@@ -3404,19 +3404,19 @@
     <t xml:space="preserve">12.639087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8721542358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6099529266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5856761932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3768863677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.488564491272</t>
+    <t xml:space="preserve">12.8721551895142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6099519729614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.585675239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3768854141235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4885635375977</t>
   </si>
   <si>
     <t xml:space="preserve">12.2846298217773</t>
@@ -3431,34 +3431,34 @@
     <t xml:space="preserve">12.4400091171265</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3720293045044</t>
+    <t xml:space="preserve">12.3720302581787</t>
   </si>
   <si>
     <t xml:space="preserve">12.4351530075073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3963079452515</t>
+    <t xml:space="preserve">12.3963088989258</t>
   </si>
   <si>
     <t xml:space="preserve">12.4060192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7553691864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6728258132935</t>
+    <t xml:space="preserve">11.7553701400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6728248596191</t>
   </si>
   <si>
     <t xml:space="preserve">11.6388368606567</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4397563934326</t>
+    <t xml:space="preserve">11.4397573471069</t>
   </si>
   <si>
     <t xml:space="preserve">11.1532783508301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2164001464844</t>
+    <t xml:space="preserve">11.2164011001587</t>
   </si>
   <si>
     <t xml:space="preserve">11.0804433822632</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">10.6968536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6434421539307</t>
+    <t xml:space="preserve">10.6434412002563</t>
   </si>
   <si>
     <t xml:space="preserve">10.6191644668579</t>
@@ -3482,13 +3482,13 @@
     <t xml:space="preserve">10.7696876525879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9833316802979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8619441986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7114210128784</t>
+    <t xml:space="preserve">10.9833326339722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8619432449341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7114200592041</t>
   </si>
   <si>
     <t xml:space="preserve">10.5269069671631</t>
@@ -3503,58 +3503,58 @@
     <t xml:space="preserve">10.4880628585815</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3375396728516</t>
+    <t xml:space="preserve">10.3375406265259</t>
   </si>
   <si>
     <t xml:space="preserve">10.0899047851562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1821603775024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1918725967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.264705657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9588041305542</t>
+    <t xml:space="preserve">10.1821613311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1918716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2647047042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95880508422852</t>
   </si>
   <si>
     <t xml:space="preserve">9.02556133270264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18870830535889</t>
+    <t xml:space="preserve">9.18870735168457</t>
   </si>
   <si>
     <t xml:space="preserve">9.46644878387451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04304122924805</t>
+    <t xml:space="preserve">9.04304218292236</t>
   </si>
   <si>
     <t xml:space="preserve">9.04498291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06246280670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84299087524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83910655975342</t>
+    <t xml:space="preserve">9.06246376037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84299182891846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8391056060791</t>
   </si>
   <si>
     <t xml:space="preserve">8.5438871383667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1440372467041</t>
+    <t xml:space="preserve">9.14403629302979</t>
   </si>
   <si>
     <t xml:space="preserve">8.9906005859375</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95369911193848</t>
+    <t xml:space="preserve">8.95369815826416</t>
   </si>
   <si>
     <t xml:space="preserve">8.99836921691895</t>
@@ -3563,7 +3563,7 @@
     <t xml:space="preserve">9.03138828277588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58492374420166</t>
+    <t xml:space="preserve">9.58492469787598</t>
   </si>
   <si>
     <t xml:space="preserve">9.55190658569336</t>
@@ -3572,7 +3572,7 @@
     <t xml:space="preserve">9.75001430511475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62182712554932</t>
+    <t xml:space="preserve">9.621826171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.68203639984131</t>
@@ -3581,31 +3581,31 @@
     <t xml:space="preserve">9.63736438751221</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62571048736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0801944732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2598495483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2501392364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4200839996338</t>
+    <t xml:space="preserve">9.62571144104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0801935195923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2598505020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2501401901245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4200830459595</t>
   </si>
   <si>
     <t xml:space="preserve">10.3860950469971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5074853897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4346513748169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4152297973633</t>
+    <t xml:space="preserve">10.5074844360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4346523284912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.415228843689</t>
   </si>
   <si>
     <t xml:space="preserve">10.3278293609619</t>
@@ -3614,13 +3614,13 @@
     <t xml:space="preserve">10.2110719680786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.528489112854</t>
+    <t xml:space="preserve">10.5284900665283</t>
   </si>
   <si>
     <t xml:space="preserve">10.3429231643677</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3819885253906</t>
+    <t xml:space="preserve">10.3819894790649</t>
   </si>
   <si>
     <t xml:space="preserve">10.4308233261108</t>
@@ -3629,22 +3629,22 @@
     <t xml:space="preserve">10.4210567474365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4259395599365</t>
+    <t xml:space="preserve">10.4259405136108</t>
   </si>
   <si>
     <t xml:space="preserve">10.5333728790283</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2306060791016</t>
+    <t xml:space="preserve">10.2306051254272</t>
   </si>
   <si>
     <t xml:space="preserve">10.4601230621338</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0645723342896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.172004699707</t>
+    <t xml:space="preserve">10.0645732879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1720056533813</t>
   </si>
   <si>
     <t xml:space="preserve">9.54986763000488</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">9.33890724182129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58893394470215</t>
+    <t xml:space="preserve">9.58893489837646</t>
   </si>
   <si>
     <t xml:space="preserve">9.68855476379395</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">9.669020652771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97178840637207</t>
+    <t xml:space="preserve">9.97178936004639</t>
   </si>
   <si>
     <t xml:space="preserve">10.0059719085693</t>
@@ -3686,19 +3686,19 @@
     <t xml:space="preserve">9.40532112121582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47173500061035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47368812561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.659255027771</t>
+    <t xml:space="preserve">9.47173404693604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47368717193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.65925407409668</t>
   </si>
   <si>
     <t xml:space="preserve">9.78622150421143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71004199981689</t>
+    <t xml:space="preserve">9.71004104614258</t>
   </si>
   <si>
     <t xml:space="preserve">9.51861476898193</t>
@@ -3707,13 +3707,13 @@
     <t xml:space="preserve">9.69441413879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66511344909668</t>
+    <t xml:space="preserve">9.665114402771</t>
   </si>
   <si>
     <t xml:space="preserve">9.87412166595459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68074035644531</t>
+    <t xml:space="preserve">9.68074131011963</t>
   </si>
   <si>
     <t xml:space="preserve">9.54791450500488</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">9.52252006530762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56744766235352</t>
+    <t xml:space="preserve">9.5674467086792</t>
   </si>
   <si>
     <t xml:space="preserve">9.46782779693604</t>
@@ -3749,13 +3749,13 @@
     <t xml:space="preserve">9.4541540145874</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79110527038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85947227478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91807079315186</t>
+    <t xml:space="preserve">9.79110431671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85947132110596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91807174682617</t>
   </si>
   <si>
     <t xml:space="preserve">9.81552219390869</t>
@@ -3767,10 +3767,10 @@
     <t xml:space="preserve">9.72566890716553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66120910644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95713806152344</t>
+    <t xml:space="preserve">9.661208152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95713901519775</t>
   </si>
   <si>
     <t xml:space="preserve">10.001088142395</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">10.2989721298218</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0499210357666</t>
+    <t xml:space="preserve">10.0499219894409</t>
   </si>
   <si>
     <t xml:space="preserve">9.94248867034912</t>
@@ -3800,28 +3800,28 @@
     <t xml:space="preserve">10.1329383850098</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2354879379272</t>
+    <t xml:space="preserve">10.2354888916016</t>
   </si>
   <si>
     <t xml:space="preserve">10.4161729812622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.18665599823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1671228408813</t>
+    <t xml:space="preserve">10.1866550445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.167121887207</t>
   </si>
   <si>
     <t xml:space="preserve">10.5675563812256</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3673391342163</t>
+    <t xml:space="preserve">10.367338180542</t>
   </si>
   <si>
     <t xml:space="preserve">10.1182880401611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.19642162323</t>
+    <t xml:space="preserve">10.1964225769043</t>
   </si>
   <si>
     <t xml:space="preserve">9.97667217254639</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">9.81063747406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79598712921143</t>
+    <t xml:space="preserve">9.79598808288574</t>
   </si>
   <si>
     <t xml:space="preserve">9.78133869171143</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">9.87900447845459</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0352716445923</t>
+    <t xml:space="preserve">10.035270690918</t>
   </si>
   <si>
     <t xml:space="preserve">10.1134052276611</t>
@@ -3854,10 +3854,10 @@
     <t xml:space="preserve">9.9815559387207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83505535125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57916736602783</t>
+    <t xml:space="preserve">9.83505439758301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57916641235352</t>
   </si>
   <si>
     <t xml:space="preserve">9.44829368591309</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">9.20803356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32914161682129</t>
+    <t xml:space="preserve">9.32914066314697</t>
   </si>
   <si>
     <t xml:space="preserve">9.1298999786377</t>
@@ -3884,10 +3884,10 @@
     <t xml:space="preserve">9.29593372344971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31742000579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9658203125</t>
+    <t xml:space="preserve">9.31742095947266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96581935882568</t>
   </si>
   <si>
     <t xml:space="preserve">9.00683975219727</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">8.68649196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89549922943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84471225738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88377952575684</t>
+    <t xml:space="preserve">8.89550018310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84471321105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88377857208252</t>
   </si>
   <si>
     <t xml:space="preserve">8.72360610961914</t>
@@ -3932,25 +3932,25 @@
     <t xml:space="preserve">8.88963985443115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79783248901367</t>
+    <t xml:space="preserve">8.79783344268799</t>
   </si>
   <si>
     <t xml:space="preserve">8.94628620147705</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98144721984863</t>
+    <t xml:space="preserve">8.98144626617432</t>
   </si>
   <si>
     <t xml:space="preserve">8.78611278533936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98535251617432</t>
+    <t xml:space="preserve">8.98535346984863</t>
   </si>
   <si>
     <t xml:space="preserve">8.96191310882568</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84080600738525</t>
+    <t xml:space="preserve">8.84080505371094</t>
   </si>
   <si>
     <t xml:space="preserve">8.60054492950439</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">8.79587936401367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80173969268799</t>
+    <t xml:space="preserve">8.8017406463623</t>
   </si>
   <si>
     <t xml:space="preserve">8.70797920227051</t>
@@ -3986,16 +3986,16 @@
     <t xml:space="preserve">8.9638671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09473991394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11622619628906</t>
+    <t xml:space="preserve">9.09474086761475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11622524261475</t>
   </si>
   <si>
     <t xml:space="preserve">8.9755859375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05958080291748</t>
+    <t xml:space="preserve">9.05957984924316</t>
   </si>
   <si>
     <t xml:space="preserve">9.41704082489014</t>
@@ -4004,10 +4004,10 @@
     <t xml:space="preserve">9.54205513000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49322032928467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56549453735352</t>
+    <t xml:space="preserve">9.49322128295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5654935836792</t>
   </si>
   <si>
     <t xml:space="preserve">9.73543548583984</t>
@@ -4022,16 +4022,16 @@
     <t xml:space="preserve">9.96202182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83993721008301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80575561523438</t>
+    <t xml:space="preserve">9.83993816375732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80575466156006</t>
   </si>
   <si>
     <t xml:space="preserve">9.69050788879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72371482849121</t>
+    <t xml:space="preserve">9.72371387481689</t>
   </si>
   <si>
     <t xml:space="preserve">9.75692081451416</t>
@@ -4046,10 +4046,10 @@
     <t xml:space="preserve">9.58502769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62214183807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31546783447266</t>
+    <t xml:space="preserve">9.62214088439941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31546688079834</t>
   </si>
   <si>
     <t xml:space="preserve">9.5108003616333</t>
@@ -4073,7 +4073,7 @@
     <t xml:space="preserve">9.33500003814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43462085723877</t>
+    <t xml:space="preserve">9.43461990356445</t>
   </si>
   <si>
     <t xml:space="preserve">9.59088706970215</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">9.63190841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64948749542236</t>
+    <t xml:space="preserve">9.64948844909668</t>
   </si>
   <si>
     <t xml:space="preserve">9.65730094909668</t>
@@ -4091,7 +4091,7 @@
     <t xml:space="preserve">9.74324798583984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71199512481689</t>
+    <t xml:space="preserve">9.71199417114258</t>
   </si>
   <si>
     <t xml:space="preserve">9.71785354614258</t>
@@ -4106,7 +4106,7 @@
     <t xml:space="preserve">9.43852710723877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71590137481689</t>
+    <t xml:space="preserve">9.71590042114258</t>
   </si>
   <si>
     <t xml:space="preserve">10.0303888320923</t>
@@ -4118,7 +4118,7 @@
     <t xml:space="preserve">9.83017158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1427049636841</t>
+    <t xml:space="preserve">10.1427059173584</t>
   </si>
   <si>
     <t xml:space="preserve">10.2696723937988</t>
@@ -4157,10 +4157,10 @@
     <t xml:space="preserve">10.4698905944824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405889511108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3917570114136</t>
+    <t xml:space="preserve">10.4405899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3917560577393</t>
   </si>
   <si>
     <t xml:space="preserve">10.4747734069824</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">10.6261568069458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7580070495605</t>
+    <t xml:space="preserve">10.7580080032349</t>
   </si>
   <si>
     <t xml:space="preserve">10.8703241348267</t>
@@ -4187,13 +4187,13 @@
     <t xml:space="preserve">10.8605575561523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8312578201294</t>
+    <t xml:space="preserve">10.8312568664551</t>
   </si>
   <si>
     <t xml:space="preserve">10.7775402069092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.880090713501</t>
+    <t xml:space="preserve">10.8800897598267</t>
   </si>
   <si>
     <t xml:space="preserve">10.8361396789551</t>
@@ -4205,13 +4205,13 @@
     <t xml:space="preserve">11.0314741134644</t>
   </si>
   <si>
-    <t xml:space="preserve">11.00705909729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1291408538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2463426589966</t>
+    <t xml:space="preserve">11.0070581436157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1291418075562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2463417053223</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268075942993</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">11.2121572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">11.207275390625</t>
+    <t xml:space="preserve">11.2072744369507</t>
   </si>
   <si>
     <t xml:space="preserve">11.2561082839966</t>
@@ -4241,16 +4241,16 @@
     <t xml:space="preserve">11.5295753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5737495422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6670074462891</t>
+    <t xml:space="preserve">11.5737504959106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6670083999634</t>
   </si>
   <si>
     <t xml:space="preserve">11.5982913970947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6326503753662</t>
+    <t xml:space="preserve">11.6326494216919</t>
   </si>
   <si>
     <t xml:space="preserve">11.4657678604126</t>
@@ -4259,13 +4259,13 @@
     <t xml:space="preserve">11.7700815200806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9418716430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.902606010437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0645790100098</t>
+    <t xml:space="preserve">11.9418725967407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9026050567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0645799636841</t>
   </si>
   <si>
     <t xml:space="preserve">12.1038455963135</t>
@@ -4280,10 +4280,10 @@
     <t xml:space="preserve">12.054762840271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.162745475769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9173307418823</t>
+    <t xml:space="preserve">12.1627445220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9173316955566</t>
   </si>
   <si>
     <t xml:space="preserve">11.9467802047729</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">11.9369640350342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9860458374023</t>
+    <t xml:space="preserve">11.9860467910767</t>
   </si>
   <si>
     <t xml:space="preserve">12.2314615249634</t>
@@ -4322,28 +4322,28 @@
     <t xml:space="preserve">12.467059135437</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4130687713623</t>
+    <t xml:space="preserve">12.413067817688</t>
   </si>
   <si>
     <t xml:space="preserve">12.5701332092285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5652256011963</t>
+    <t xml:space="preserve">12.565224647522</t>
   </si>
   <si>
     <t xml:space="preserve">12.6633901596069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6143074035645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6241235733032</t>
+    <t xml:space="preserve">12.6143083572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6241245269775</t>
   </si>
   <si>
     <t xml:space="preserve">12.2658185958862</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0596704483032</t>
+    <t xml:space="preserve">12.0596714019775</t>
   </si>
   <si>
     <t xml:space="preserve">12.0694875717163</t>
@@ -4367,16 +4367,16 @@
     <t xml:space="preserve">12.3050851821899</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3296270370483</t>
+    <t xml:space="preserve">12.3296279907227</t>
   </si>
   <si>
     <t xml:space="preserve">12.2216444015503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1921939849854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4376096725464</t>
+    <t xml:space="preserve">12.1921949386597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4376087188721</t>
   </si>
   <si>
     <t xml:space="preserve">12.4228839874268</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">12.4866924285889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6928415298462</t>
+    <t xml:space="preserve">12.6928405761719</t>
   </si>
   <si>
     <t xml:space="preserve">12.4817838668823</t>
@@ -4409,13 +4409,13 @@
     <t xml:space="preserve">12.0940284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9762306213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9124231338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.794623374939</t>
+    <t xml:space="preserve">11.9762296676636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9124221801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7946243286133</t>
   </si>
   <si>
     <t xml:space="preserve">11.8044395446777</t>
@@ -4424,7 +4424,7 @@
     <t xml:space="preserve">11.7995319366455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.819164276123</t>
+    <t xml:space="preserve">11.8191652297974</t>
   </si>
   <si>
     <t xml:space="preserve">11.8927888870239</t>
@@ -4436,7 +4436,7 @@
     <t xml:space="preserve">11.4461345672607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3970508575439</t>
+    <t xml:space="preserve">11.3970518112183</t>
   </si>
   <si>
     <t xml:space="preserve">11.4706764221191</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">11.3872356414795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5639324188232</t>
+    <t xml:space="preserve">11.5639333724976</t>
   </si>
   <si>
     <t xml:space="preserve">11.5835666656494</t>
@@ -4457,13 +4457,13 @@
     <t xml:space="preserve">11.9075136184692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0007724761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.848614692688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7749900817871</t>
+    <t xml:space="preserve">12.000771522522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8486137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7749891281128</t>
   </si>
   <si>
     <t xml:space="preserve">11.8535223007202</t>
@@ -4475,10 +4475,10 @@
     <t xml:space="preserve">11.5344839096069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.642466545105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1516361236572</t>
+    <t xml:space="preserve">11.6424655914307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1516370773315</t>
   </si>
   <si>
     <t xml:space="preserve">11.1025543212891</t>
@@ -4490,10 +4490,10 @@
     <t xml:space="preserve">11.1712703704834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.269434928894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.284161567688</t>
+    <t xml:space="preserve">11.2694358825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2841606140137</t>
   </si>
   <si>
     <t xml:space="preserve">11.54430103302</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">11.1909027099609</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0092964172363</t>
+    <t xml:space="preserve">11.0092973709106</t>
   </si>
   <si>
     <t xml:space="preserve">10.842414855957</t>
@@ -4511,7 +4511,7 @@
     <t xml:space="preserve">10.68044090271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7687902450562</t>
+    <t xml:space="preserve">10.7687911987305</t>
   </si>
   <si>
     <t xml:space="preserve">10.9602136611938</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">10.9454879760742</t>
   </si>
   <si>
-    <t xml:space="preserve">11.254711151123</t>
+    <t xml:space="preserve">11.2547121047974</t>
   </si>
   <si>
     <t xml:space="preserve">11.3087024688721</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">10.7786064147949</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7393398284912</t>
+    <t xml:space="preserve">10.7393407821655</t>
   </si>
   <si>
     <t xml:space="preserve">10.7344331741333</t>
@@ -4562,13 +4562,13 @@
     <t xml:space="preserve">10.7246160507202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7589731216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.886589050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8571395874023</t>
+    <t xml:space="preserve">10.7589740753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8865900039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8571405410767</t>
   </si>
   <si>
     <t xml:space="preserve">10.1208963394165</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">9.98346424102783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1945199966431</t>
+    <t xml:space="preserve">10.1945209503174</t>
   </si>
   <si>
     <t xml:space="preserve">10.2386951446533</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">10.48410987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871829986572</t>
+    <t xml:space="preserve">10.5871839523315</t>
   </si>
   <si>
     <t xml:space="preserve">10.5381002426147</t>
@@ -4598,22 +4598,22 @@
     <t xml:space="preserve">10.7295246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7000741958618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3466768264771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2877779006958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4055776596069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3270444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0669040679932</t>
+    <t xml:space="preserve">10.7000732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3466777801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2877769470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4055767059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3270454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0669050216675</t>
   </si>
   <si>
     <t xml:space="preserve">10.086537361145</t>
@@ -4637,13 +4637,13 @@
     <t xml:space="preserve">9.75375556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83621501922607</t>
+    <t xml:space="preserve">9.83621597290039</t>
   </si>
   <si>
     <t xml:space="preserve">9.83130741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86075592041016</t>
+    <t xml:space="preserve">9.86075687408447</t>
   </si>
   <si>
     <t xml:space="preserve">9.90493106842041</t>
@@ -4667,7 +4667,7 @@
     <t xml:space="preserve">9.8263988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9147481918335</t>
+    <t xml:space="preserve">9.91474723815918</t>
   </si>
   <si>
     <t xml:space="preserve">9.96382999420166</t>
@@ -4685,19 +4685,19 @@
     <t xml:space="preserve">10.0276384353638</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8902063369751</t>
+    <t xml:space="preserve">9.89020538330078</t>
   </si>
   <si>
     <t xml:space="preserve">9.76357269287109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86566543579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76553535461426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74001216888428</t>
+    <t xml:space="preserve">9.8656644821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76553630828857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74001312255859</t>
   </si>
   <si>
     <t xml:space="preserve">9.74393844604492</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">9.10782432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15494441986084</t>
+    <t xml:space="preserve">9.15494537353516</t>
   </si>
   <si>
     <t xml:space="preserve">9.14905452728271</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">9.00769519805908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08033752441406</t>
+    <t xml:space="preserve">9.08033847808838</t>
   </si>
   <si>
     <t xml:space="preserve">9.06463146209717</t>
@@ -4736,19 +4736,19 @@
     <t xml:space="preserve">8.85455799102783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8152904510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29630279541016</t>
+    <t xml:space="preserve">8.81528949737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29630374908447</t>
   </si>
   <si>
     <t xml:space="preserve">9.22758674621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23740386962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21580600738525</t>
+    <t xml:space="preserve">9.23740291595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21580696105957</t>
   </si>
   <si>
     <t xml:space="preserve">9.37090873718262</t>
@@ -4772,19 +4772,19 @@
     <t xml:space="preserve">9.61043357849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56527709960938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76749897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78909492492676</t>
+    <t xml:space="preserve">9.56527805328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76749801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78909587860107</t>
   </si>
   <si>
     <t xml:space="preserve">9.63988304138184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63791942596436</t>
+    <t xml:space="preserve">9.63792037963867</t>
   </si>
   <si>
     <t xml:space="preserve">9.6909294128418</t>
@@ -4796,16 +4796,16 @@
     <t xml:space="preserve">9.59080123901367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3807258605957</t>
+    <t xml:space="preserve">9.38072490692139</t>
   </si>
   <si>
     <t xml:space="preserve">9.65559005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32967948913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20009994506836</t>
+    <t xml:space="preserve">9.32967853546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20010089874268</t>
   </si>
   <si>
     <t xml:space="preserve">9.30023002624512</t>
@@ -4826,7 +4826,7 @@
     <t xml:space="preserve">9.36109256744385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40232276916504</t>
+    <t xml:space="preserve">9.40232181549072</t>
   </si>
   <si>
     <t xml:space="preserve">9.39054203033447</t>
@@ -4835,7 +4835,7 @@
     <t xml:space="preserve">9.47300148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47103786468506</t>
+    <t xml:space="preserve">9.47103881835938</t>
   </si>
   <si>
     <t xml:space="preserve">9.37876224517822</t>
@@ -4844,7 +4844,7 @@
     <t xml:space="preserve">9.27667045593262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08426475524902</t>
+    <t xml:space="preserve">9.08426380157471</t>
   </si>
   <si>
     <t xml:space="preserve">9.1254940032959</t>
@@ -4862,7 +4862,7 @@
     <t xml:space="preserve">9.06855869293213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14316368103027</t>
+    <t xml:space="preserve">9.14316463470459</t>
   </si>
   <si>
     <t xml:space="preserve">9.00573253631592</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">8.89382362365723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02340316772461</t>
+    <t xml:space="preserve">9.02340221405029</t>
   </si>
   <si>
     <t xml:space="preserve">8.92523670196533</t>
@@ -4883,7 +4883,7 @@
     <t xml:space="preserve">8.92327308654785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88400650024414</t>
+    <t xml:space="preserve">8.88400745391846</t>
   </si>
   <si>
     <t xml:space="preserve">8.80743789672852</t>
@@ -4892,7 +4892,7 @@
     <t xml:space="preserve">8.73479461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7681713104248</t>
+    <t xml:space="preserve">8.76817035675049</t>
   </si>
   <si>
     <t xml:space="preserve">8.77995109558105</t>
@@ -4901,10 +4901,10 @@
     <t xml:space="preserve">8.9821720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21188068389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30219268798828</t>
+    <t xml:space="preserve">9.21187973022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3021936416626</t>
   </si>
   <si>
     <t xml:space="preserve">9.42377090454102</t>
@@ -5973,6 +5973,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.48799991607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.40999984741211</t>
   </si>
 </sst>
 </file>
@@ -71649,7 +71652,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6935532407</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>5151377</v>
@@ -71670,6 +71673,32 @@
         <v>1986</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6923148148</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>4255004</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>5.52600002288818</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>5.40999984741211</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>5.50799989700317</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>5.40999984741211</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>1987</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1988" uniqueCount="1988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="1989">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59865665435791</t>
+    <t xml:space="preserve">3.59865641593933</t>
   </si>
   <si>
     <t xml:space="preserve">CPR.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65898275375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60329723358154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51976943016052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51048827171326</t>
+    <t xml:space="preserve">3.6589822769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60329699516296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51976919174194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51048851013184</t>
   </si>
   <si>
     <t xml:space="preserve">3.54993224143982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62881898880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68450450897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57313394546509</t>
+    <t xml:space="preserve">3.62881970405579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68450474739075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57313418388367</t>
   </si>
   <si>
     <t xml:space="preserve">3.52672958374023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48264598846436</t>
+    <t xml:space="preserve">3.48264575004578</t>
   </si>
   <si>
     <t xml:space="preserve">3.5661735534668</t>
@@ -80,40 +80,40 @@
     <t xml:space="preserve">3.43392133712769</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50584769248962</t>
+    <t xml:space="preserve">3.50584745407104</t>
   </si>
   <si>
     <t xml:space="preserve">3.56153345108032</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64274048805237</t>
+    <t xml:space="preserve">3.64274096488953</t>
   </si>
   <si>
     <t xml:space="preserve">3.66594314575195</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56849384307861</t>
+    <t xml:space="preserve">3.56849408149719</t>
   </si>
   <si>
     <t xml:space="preserve">3.74250984191895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72162818908691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70770645141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47104477882385</t>
+    <t xml:space="preserve">3.72162842750549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70770692825317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47104454040527</t>
   </si>
   <si>
     <t xml:space="preserve">3.44320201873779</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28078699111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33183169364929</t>
+    <t xml:space="preserve">3.28078675270081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33183121681213</t>
   </si>
   <si>
     <t xml:space="preserve">3.40839862823486</t>
@@ -122,40 +122,40 @@
     <t xml:space="preserve">3.22046136856079</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2691855430603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32487106323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24366331100464</t>
+    <t xml:space="preserve">3.26918578147888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32487082481384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2436637878418</t>
   </si>
   <si>
     <t xml:space="preserve">3.32255077362061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28774785995483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31791043281555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36663484573364</t>
+    <t xml:space="preserve">3.28774762153625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31791019439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36663460731506</t>
   </si>
   <si>
     <t xml:space="preserve">3.36199426651001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40607857704163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3828763961792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36431479454041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53136992454529</t>
+    <t xml:space="preserve">3.40607881546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38287663459778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36431455612183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53137063980103</t>
   </si>
   <si>
     <t xml:space="preserve">3.60561728477478</t>
@@ -167,37 +167,37 @@
     <t xml:space="preserve">3.56385350227356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61489844322205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63810038566589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68914532661438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476229667664</t>
+    <t xml:space="preserve">3.61489820480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63809990882874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68914484977722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476277351379</t>
   </si>
   <si>
     <t xml:space="preserve">3.95596981048584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00701427459717</t>
+    <t xml:space="preserve">4.00701475143433</t>
   </si>
   <si>
     <t xml:space="preserve">4.04877853393555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03485727310181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04181718826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03717803955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05109930038452</t>
+    <t xml:space="preserve">4.03485822677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04181814193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03717756271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05109786987305</t>
   </si>
   <si>
     <t xml:space="preserve">4.01861619949341</t>
@@ -206,148 +206,148 @@
     <t xml:space="preserve">4.09286260604858</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07662200927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03949737548828</t>
+    <t xml:space="preserve">4.07662153244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03949785232544</t>
   </si>
   <si>
     <t xml:space="preserve">4.08358192443848</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02325677871704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00005388259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06037998199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99541306495667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9443690776825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97453165054321</t>
+    <t xml:space="preserve">4.02325630187988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00005435943604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06037950515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99541330337524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94436812400818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97453188896179</t>
   </si>
   <si>
     <t xml:space="preserve">4.00237417221069</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93740797042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94668865203857</t>
+    <t xml:space="preserve">3.9374086856842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94669008255005</t>
   </si>
   <si>
     <t xml:space="preserve">4.03021717071533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05341815948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0093355178833</t>
+    <t xml:space="preserve">4.05341863632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00933456420898</t>
   </si>
   <si>
     <t xml:space="preserve">3.9582896232605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98613309860229</t>
+    <t xml:space="preserve">3.98613333702087</t>
   </si>
   <si>
     <t xml:space="preserve">4.0255765914917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96989178657532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9118857383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89796447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87708282470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91420578956604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92812728881836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95133018493652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06734037399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08126306533813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99309372901917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96757102012634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98149251937866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96293044090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88868379592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89332485198975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79587531089783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89309930801392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02677822113037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08540821075439</t>
+    <t xml:space="preserve">3.96989154815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91188621520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89796495437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87708234786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91420650482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92812705039978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95132946968079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06734085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08126163482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99309325218201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96757125854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98149275779724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96293091773987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88868427276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89332389831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79587554931641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89309883117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02677774429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08540868759155</t>
   </si>
   <si>
     <t xml:space="preserve">4.07602739334106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08306312561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09948062896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07368326187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0900993347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10182476043701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08775329589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1135516166687</t>
+    <t xml:space="preserve">4.08306360244751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09948015213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07368230819702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09009981155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10182571411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0877537727356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11355113983154</t>
   </si>
   <si>
     <t xml:space="preserve">4.08071804046631</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01974201202393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90482521057129</t>
+    <t xml:space="preserve">4.01974153518677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90482544898987</t>
   </si>
   <si>
     <t xml:space="preserve">3.85557532310486</t>
@@ -356,13 +356,13 @@
     <t xml:space="preserve">3.85792088508606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86495614051819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87199139595032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86964631080627</t>
+    <t xml:space="preserve">3.86495590209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87199211120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8696460723877</t>
   </si>
   <si>
     <t xml:space="preserve">4.00567054748535</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">3.95876574516296</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05960988998413</t>
+    <t xml:space="preserve">4.05961036682129</t>
   </si>
   <si>
     <t xml:space="preserve">3.88606309890747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88840866088867</t>
+    <t xml:space="preserve">3.88840842247009</t>
   </si>
   <si>
     <t xml:space="preserve">4.04084873199463</t>
@@ -398,31 +398,31 @@
     <t xml:space="preserve">4.13231372833252</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00332546234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04319381713867</t>
+    <t xml:space="preserve">4.00332498550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04319429397583</t>
   </si>
   <si>
     <t xml:space="preserve">4.16045618057251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15811204910278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11589765548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06899261474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13465881347656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14169454574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18390893936157</t>
+    <t xml:space="preserve">4.15811014175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11589670181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06899213790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1346583366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14169502258301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18390941619873</t>
   </si>
   <si>
     <t xml:space="preserve">4.16280126571655</t>
@@ -431,19 +431,19 @@
     <t xml:space="preserve">4.21908712387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29178905487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29647970199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31055212020874</t>
+    <t xml:space="preserve">4.29179000854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29648017883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31055164337158</t>
   </si>
   <si>
     <t xml:space="preserve">4.28709936141968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33165836334229</t>
+    <t xml:space="preserve">4.3316593170166</t>
   </si>
   <si>
     <t xml:space="preserve">4.33869457244873</t>
@@ -455,25 +455,25 @@
     <t xml:space="preserve">4.51458787918091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5216236114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43719482421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47940921783447</t>
+    <t xml:space="preserve">4.52162408828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43719530105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47940969467163</t>
   </si>
   <si>
     <t xml:space="preserve">4.45595645904541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66233777999878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67171859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58963489532471</t>
+    <t xml:space="preserve">4.66233730316162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67171955108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58963537216187</t>
   </si>
   <si>
     <t xml:space="preserve">4.55914688110352</t>
@@ -482,37 +482,37 @@
     <t xml:space="preserve">4.56383752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54976606369019</t>
+    <t xml:space="preserve">4.54976654052734</t>
   </si>
   <si>
     <t xml:space="preserve">4.60370635986328</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59667158126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57321882247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62012386322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59432506561279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65061140060425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57556390762329</t>
+    <t xml:space="preserve">4.59667110443115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57321834564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6201229095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59432601928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65061187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57556438446045</t>
   </si>
   <si>
     <t xml:space="preserve">4.70455169677734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67406415939331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70924282073975</t>
+    <t xml:space="preserve">4.67406463623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70924234390259</t>
   </si>
   <si>
     <t xml:space="preserve">4.60136222839355</t>
@@ -521,25 +521,25 @@
     <t xml:space="preserve">4.48644495010376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4653377532959</t>
+    <t xml:space="preserve">4.46533727645874</t>
   </si>
   <si>
     <t xml:space="preserve">4.39967060089111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43250417709351</t>
+    <t xml:space="preserve">4.43250370025635</t>
   </si>
   <si>
     <t xml:space="preserve">4.50520610809326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49113464355469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51693344116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50286245346069</t>
+    <t xml:space="preserve">4.491135597229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51693296432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50286197662354</t>
   </si>
   <si>
     <t xml:space="preserve">4.48879051208496</t>
@@ -551,22 +551,22 @@
     <t xml:space="preserve">4.66468334197998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73269510269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71393299102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69048070907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58729028701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.568528175354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47471761703491</t>
+    <t xml:space="preserve">4.73269557952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71393394470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69048023223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58728981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56852769851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47471809387207</t>
   </si>
   <si>
     <t xml:space="preserve">4.44657516479492</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">4.54742050170898</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44188547134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50051593780518</t>
+    <t xml:space="preserve">4.44188499450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50051641464233</t>
   </si>
   <si>
     <t xml:space="preserve">4.52631330490112</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">4.36683750152588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37152719497681</t>
+    <t xml:space="preserve">4.37152814865112</t>
   </si>
   <si>
     <t xml:space="preserve">4.33400392532349</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">4.30586099624634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30351638793945</t>
+    <t xml:space="preserve">4.30351591110229</t>
   </si>
   <si>
     <t xml:space="preserve">4.25661134719849</t>
@@ -608,49 +608,49 @@
     <t xml:space="preserve">4.20736122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09478950500488</t>
+    <t xml:space="preserve">4.09478902816772</t>
   </si>
   <si>
     <t xml:space="preserve">4.24253988265991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20267057418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95642042160034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95407462120056</t>
+    <t xml:space="preserve">4.20267105102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9564208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95407557487488</t>
   </si>
   <si>
     <t xml:space="preserve">4.0338134765625</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12527847290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01739597320557</t>
+    <t xml:space="preserve">4.12527751922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01739692687988</t>
   </si>
   <si>
     <t xml:space="preserve">4.12996816635132</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1721830368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21205139160156</t>
+    <t xml:space="preserve">4.17218255996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2120509147644</t>
   </si>
   <si>
     <t xml:space="preserve">4.18859958648682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24957609176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20501661300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26833724975586</t>
+    <t xml:space="preserve">4.24957656860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20501613616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26833820343018</t>
   </si>
   <si>
     <t xml:space="preserve">4.22846841812134</t>
@@ -659,31 +659,31 @@
     <t xml:space="preserve">4.24723052978516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31993341445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36449241638184</t>
+    <t xml:space="preserve">4.31993246078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36449289321899</t>
   </si>
   <si>
     <t xml:space="preserve">4.28944492340088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27771902084351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30116987228394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32227754592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35745668411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34807634353638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34338569641113</t>
+    <t xml:space="preserve">4.27771806716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30117082595825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32227849960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35745620727539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34807586669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34338521957397</t>
   </si>
   <si>
     <t xml:space="preserve">4.39028930664062</t>
@@ -692,85 +692,85 @@
     <t xml:space="preserve">4.36214733123779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32462406158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39732599258423</t>
+    <t xml:space="preserve">4.32462310791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39732551574707</t>
   </si>
   <si>
     <t xml:space="preserve">4.37387323379517</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36918210983276</t>
+    <t xml:space="preserve">4.36918258666992</t>
   </si>
   <si>
     <t xml:space="preserve">4.47002792358398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45830154418945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42546844482422</t>
+    <t xml:space="preserve">4.45830202102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42546892166138</t>
   </si>
   <si>
     <t xml:space="preserve">4.43484973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46768283843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40201616287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35276651382446</t>
+    <t xml:space="preserve">4.46768236160278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40201663970947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3527660369873</t>
   </si>
   <si>
     <t xml:space="preserve">4.3855996131897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43953990936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43015909194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49348068237305</t>
+    <t xml:space="preserve">4.43954038619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43015956878662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49348115921021</t>
   </si>
   <si>
     <t xml:space="preserve">4.47237348556519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52396965026855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5427303314209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53804016113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54507541656494</t>
+    <t xml:space="preserve">4.52396869659424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54273080825806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53803968429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5450758934021</t>
   </si>
   <si>
     <t xml:space="preserve">4.58260011672974</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57790946960449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55211210250854</t>
+    <t xml:space="preserve">4.57790899276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55211114883423</t>
   </si>
   <si>
     <t xml:space="preserve">4.57087326049805</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53569459915161</t>
+    <t xml:space="preserve">4.53569507598877</t>
   </si>
   <si>
     <t xml:space="preserve">4.50755214691162</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58494424819946</t>
+    <t xml:space="preserve">4.58494472503662</t>
   </si>
   <si>
     <t xml:space="preserve">4.65530252456665</t>
@@ -782,31 +782,31 @@
     <t xml:space="preserve">4.75614786148071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80774211883545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83119583129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89686107635498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94845676422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09855222702026</t>
+    <t xml:space="preserve">4.80774307250977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83119487762451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89686155319214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94845771789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09855175018311</t>
   </si>
   <si>
     <t xml:space="preserve">5.05164813995361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12200498580933</t>
+    <t xml:space="preserve">5.12200546264648</t>
   </si>
   <si>
     <t xml:space="preserve">5.04695749282837</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0563383102417</t>
+    <t xml:space="preserve">5.05633783340454</t>
   </si>
   <si>
     <t xml:space="preserve">4.99536180496216</t>
@@ -815,34 +815,34 @@
     <t xml:space="preserve">5.01881456375122</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02819490432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03288507461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93907594680786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97660064697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92500352859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96721982955933</t>
+    <t xml:space="preserve">5.02819585800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03288555145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93907499313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9766001701355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92500495910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96722030639648</t>
   </si>
   <si>
     <t xml:space="preserve">5.08917188644409</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1735987663269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14545774459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15952920913696</t>
+    <t xml:space="preserve">5.17359924316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14545726776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15952825546265</t>
   </si>
   <si>
     <t xml:space="preserve">5.09386205673218</t>
@@ -851,82 +851,82 @@
     <t xml:space="preserve">5.16421890258789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25333786010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18767118453979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41750526428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67079067230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60043430328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62388563156128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66140937805176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68486261367798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57698154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60512495040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72238683700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6940336227417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74128818511963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76491451263428</t>
+    <t xml:space="preserve">5.25333833694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18767261505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41750574111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6707911491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60043478012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62388515472412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66141080856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68486213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57698202133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60512447357178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7223858833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69403457641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74128770828247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76491403579712</t>
   </si>
   <si>
     <t xml:space="preserve">5.75073862075806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87832164764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86887168884277</t>
+    <t xml:space="preserve">5.87832260131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86887216567993</t>
   </si>
   <si>
     <t xml:space="preserve">5.88304758071899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.02008247375488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99173069000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00118207931519</t>
+    <t xml:space="preserve">6.02008199691772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9917311668396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00118064880371</t>
   </si>
   <si>
     <t xml:space="preserve">5.93502616882324</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85942077636719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8027172088623</t>
+    <t xml:space="preserve">5.85942125320435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80271673202515</t>
   </si>
   <si>
     <t xml:space="preserve">5.75546360015869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73183727264404</t>
+    <t xml:space="preserve">5.7318377494812</t>
   </si>
   <si>
     <t xml:space="preserve">5.84997034072876</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">5.81216812133789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95865345001221</t>
+    <t xml:space="preserve">5.95865297317505</t>
   </si>
   <si>
     <t xml:space="preserve">5.93030118942261</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">5.98227977752686</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90194892883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91612577438354</t>
+    <t xml:space="preserve">5.90194988250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91612529754639</t>
   </si>
   <si>
     <t xml:space="preserve">5.91140031814575</t>
@@ -959,49 +959,49 @@
     <t xml:space="preserve">5.88777303695679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78381586074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8074426651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84524488449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77436542510986</t>
+    <t xml:space="preserve">5.78381633758545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80744171142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84524536132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77436590194702</t>
   </si>
   <si>
     <t xml:space="preserve">5.82634401321411</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82161855697632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85469627380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79326725006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83579444885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95392799377441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92557573318481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94447708129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77909088134766</t>
+    <t xml:space="preserve">5.82161808013916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85469579696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79326677322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8357949256897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95392847061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92557621002197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94447755813599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.77908992767334</t>
   </si>
   <si>
     <t xml:space="preserve">5.74601268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71766090393066</t>
+    <t xml:space="preserve">5.71766138076782</t>
   </si>
   <si>
     <t xml:space="preserve">5.65150594711304</t>
@@ -1010,43 +1010,43 @@
     <t xml:space="preserve">5.66095638275146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79799175262451</t>
+    <t xml:space="preserve">5.79799127578735</t>
   </si>
   <si>
     <t xml:space="preserve">5.76018857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69875955581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6656813621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73656320571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78854179382324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76963949203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89249897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97282934188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15239238739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14766645431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.28470182418823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13821601867676</t>
+    <t xml:space="preserve">5.69876003265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66568183898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73656272888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78854084014893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76963996887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89249801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97282981872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15239286422729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14766693115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.28470230102539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13821506500244</t>
   </si>
   <si>
     <t xml:space="preserve">6.12404012680054</t>
@@ -1055,25 +1055,25 @@
     <t xml:space="preserve">6.02953386306763</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10513877868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16656875610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11458873748779</t>
+    <t xml:space="preserve">6.10513830184937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16656923294067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11458969116211</t>
   </si>
   <si>
     <t xml:space="preserve">6.31777954101562</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34140634536743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40756034851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50206756591797</t>
+    <t xml:space="preserve">6.34140539169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4075608253479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50206708908081</t>
   </si>
   <si>
     <t xml:space="preserve">6.42173719406128</t>
@@ -1082,76 +1082,76 @@
     <t xml:space="preserve">6.30832862854004</t>
   </si>
   <si>
-    <t xml:space="preserve">6.478440284729</t>
+    <t xml:space="preserve">6.47844076156616</t>
   </si>
   <si>
     <t xml:space="preserve">6.31305360794067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33667993545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37448310852051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17601919174194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09096336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.23272275924683</t>
+    <t xml:space="preserve">6.33668041229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37448263168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17601871490479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0909628868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.23272228240967</t>
   </si>
   <si>
     <t xml:space="preserve">6.03898429870605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08623743057251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10041332244873</t>
+    <t xml:space="preserve">6.08623695373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10041379928589</t>
   </si>
   <si>
     <t xml:space="preserve">6.10986423492432</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00590658187866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03425931930542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.09568786621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.06261110305786</t>
+    <t xml:space="preserve">6.00590705871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0342583656311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.09568738937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.06261157989502</t>
   </si>
   <si>
     <t xml:space="preserve">6.18074417114258</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08151197433472</t>
+    <t xml:space="preserve">6.08151245117188</t>
   </si>
   <si>
     <t xml:space="preserve">6.15711736679077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.21382141113281</t>
+    <t xml:space="preserve">6.21382093429565</t>
   </si>
   <si>
     <t xml:space="preserve">6.24217414855957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24689912796021</t>
+    <t xml:space="preserve">6.24689865112305</t>
   </si>
   <si>
     <t xml:space="preserve">6.20909643173218</t>
   </si>
   <si>
-    <t xml:space="preserve">6.22799825668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19964551925659</t>
+    <t xml:space="preserve">6.22799777984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19964647293091</t>
   </si>
   <si>
     <t xml:space="preserve">6.12876510620117</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">6.05788564682007</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13349056243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14294147491455</t>
+    <t xml:space="preserve">6.13349103927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14294099807739</t>
   </si>
   <si>
     <t xml:space="preserve">6.01063203811646</t>
@@ -1178,16 +1178,16 @@
     <t xml:space="preserve">5.97755432128906</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05316066741943</t>
+    <t xml:space="preserve">6.05316019058228</t>
   </si>
   <si>
     <t xml:space="preserve">5.99645614624023</t>
   </si>
   <si>
-    <t xml:space="preserve">6.06733655929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93975114822388</t>
+    <t xml:space="preserve">6.06733560562134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93975162506104</t>
   </si>
   <si>
     <t xml:space="preserve">5.71293544769287</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">5.92085075378418</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57590055465698</t>
+    <t xml:space="preserve">5.57590103149414</t>
   </si>
   <si>
     <t xml:space="preserve">5.52864742279053</t>
@@ -1208,184 +1208,184 @@
     <t xml:space="preserve">5.42941522598267</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50502109527588</t>
+    <t xml:space="preserve">5.50502061843872</t>
   </si>
   <si>
     <t xml:space="preserve">5.61370372772217</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63733100891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.04370927810669</t>
+    <t xml:space="preserve">5.63733005523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.04370975494385</t>
   </si>
   <si>
     <t xml:space="preserve">5.98700571060181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.01535701751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.89722442626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81689357757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.87359666824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86414623260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90667486190796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96810388565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01550769805908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0202693939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99169301986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08218812942505</t>
+    <t xml:space="preserve">6.01535654067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.89722394943237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81689405441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.87359714508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86414670944214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.9066743850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96810340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01550722122192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02027082443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99169397354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08218765258789</t>
   </si>
   <si>
     <t xml:space="preserve">6.2060227394104</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18697071075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08695077896118</t>
+    <t xml:space="preserve">6.18697023391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08695030212402</t>
   </si>
   <si>
     <t xml:space="preserve">6.07266187667847</t>
   </si>
   <si>
-    <t xml:space="preserve">6.16315603256226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.27270269393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2536506652832</t>
+    <t xml:space="preserve">6.16315650939941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.27270221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.25365114212036</t>
   </si>
   <si>
     <t xml:space="preserve">6.13934230804443</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29175424575806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38701105117798</t>
+    <t xml:space="preserve">6.2917537689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38701152801514</t>
   </si>
   <si>
     <t xml:space="preserve">6.5251350402832</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59657859802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69183492660522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.69659852981567</t>
+    <t xml:space="preserve">6.5965781211853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69183540344238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69659805297852</t>
   </si>
   <si>
     <t xml:space="preserve">6.62039184570312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57276391983032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50608348846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58228874206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65373229980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71088600158691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82519626617432</t>
+    <t xml:space="preserve">6.57276439666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5060830116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58228921890259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65373277664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71088647842407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8251953125</t>
   </si>
   <si>
     <t xml:space="preserve">6.77280473709106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.82995843887329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02523612976074</t>
+    <t xml:space="preserve">6.82995939254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02523565292358</t>
   </si>
   <si>
     <t xml:space="preserve">6.92521619796753</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92045307159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0109486579895</t>
+    <t xml:space="preserve">6.92045259475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01094770431519</t>
   </si>
   <si>
     <t xml:space="preserve">6.9680814743042</t>
   </si>
   <si>
-    <t xml:space="preserve">6.91092777252197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01571083068848</t>
+    <t xml:space="preserve">6.91092729568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01570987701416</t>
   </si>
   <si>
     <t xml:space="preserve">7.04905080795288</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0966796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17764806747437</t>
+    <t xml:space="preserve">7.09667921066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17764854431152</t>
   </si>
   <si>
     <t xml:space="preserve">7.28243160247803</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22051334381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23956537246704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27766847610474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12525653839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94903039932251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86806201934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00142097473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00618505477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0633397102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97760725021362</t>
+    <t xml:space="preserve">7.22051429748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2395658493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27766895294189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12525606155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94903087615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86806154251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00142192840576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00618457794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06333923339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97760772705078</t>
   </si>
   <si>
     <t xml:space="preserve">6.9918966293335</t>
@@ -1394,10 +1394,10 @@
     <t xml:space="preserve">7.03952503204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02047348022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07762765884399</t>
+    <t xml:space="preserve">7.02047300338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07762813568115</t>
   </si>
   <si>
     <t xml:space="preserve">7.18717384338379</t>
@@ -1406,19 +1406,19 @@
     <t xml:space="preserve">7.21098852157593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.41579151153564</t>
+    <t xml:space="preserve">7.4157919883728</t>
   </si>
   <si>
     <t xml:space="preserve">7.29672002792358</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2633810043335</t>
+    <t xml:space="preserve">7.26337957382202</t>
   </si>
   <si>
     <t xml:space="preserve">7.24432802200317</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2729058265686</t>
+    <t xml:space="preserve">7.27290630340576</t>
   </si>
   <si>
     <t xml:space="preserve">7.30624580383301</t>
@@ -1427,10 +1427,10 @@
     <t xml:space="preserve">7.18241119384766</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25385427474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05857610702515</t>
+    <t xml:space="preserve">7.2538537979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0585765838623</t>
   </si>
   <si>
     <t xml:space="preserve">7.10620498657227</t>
@@ -1442,25 +1442,25 @@
     <t xml:space="preserve">7.1681227684021</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90140104293823</t>
+    <t xml:space="preserve">6.90140151977539</t>
   </si>
   <si>
     <t xml:space="preserve">6.94426774978638</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06810235977173</t>
+    <t xml:space="preserve">7.06810188293457</t>
   </si>
   <si>
     <t xml:space="preserve">6.98713350296021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1300196647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87758684158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70612287521362</t>
+    <t xml:space="preserve">7.13001918792725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87758731842041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70612382888794</t>
   </si>
   <si>
     <t xml:space="preserve">6.63944339752197</t>
@@ -1469,13 +1469,13 @@
     <t xml:space="preserve">6.65849494934082</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32985687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19649600982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11552858352661</t>
+    <t xml:space="preserve">6.32985734939575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19649648666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11552762985229</t>
   </si>
   <si>
     <t xml:space="preserve">6.04884767532349</t>
@@ -1484,25 +1484,25 @@
     <t xml:space="preserve">6.21554803848267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31556844711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33461999893188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34414625167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12505292892456</t>
+    <t xml:space="preserve">6.31556749343872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3346209526062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34414577484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12505340576172</t>
   </si>
   <si>
     <t xml:space="preserve">6.15363121032715</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30604267120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35367155075073</t>
+    <t xml:space="preserve">6.3060417175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35367202758789</t>
   </si>
   <si>
     <t xml:space="preserve">6.47274351119995</t>
@@ -1517,25 +1517,25 @@
     <t xml:space="preserve">6.52989816665649</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76804161071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08239078521729</t>
+    <t xml:space="preserve">6.76804113388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08239030838013</t>
   </si>
   <si>
     <t xml:space="preserve">7.1109676361084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12049436569214</t>
+    <t xml:space="preserve">7.12049388885498</t>
   </si>
   <si>
     <t xml:space="preserve">7.32529735565186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31577157974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11573123931885</t>
+    <t xml:space="preserve">7.31577110290527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11573028564453</t>
   </si>
   <si>
     <t xml:space="preserve">7.03476285934448</t>
@@ -1547,37 +1547,37 @@
     <t xml:space="preserve">7.04428815841675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02999973297119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17288494110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36340045928955</t>
+    <t xml:space="preserve">7.02999925613403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17288589477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36339998245239</t>
   </si>
   <si>
     <t xml:space="preserve">7.14430809020996</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20622539520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32053470611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09191703796387</t>
+    <t xml:space="preserve">7.20622587203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32053518295288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09191656112671</t>
   </si>
   <si>
     <t xml:space="preserve">6.98236989974976</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44913196563721</t>
+    <t xml:space="preserve">7.44913244247437</t>
   </si>
   <si>
     <t xml:space="preserve">7.3824520111084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33006048202515</t>
+    <t xml:space="preserve">7.33006000518799</t>
   </si>
   <si>
     <t xml:space="preserve">7.21575117111206</t>
@@ -1586,43 +1586,43 @@
     <t xml:space="preserve">7.33958578109741</t>
   </si>
   <si>
-    <t xml:space="preserve">7.35387420654297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.55391550064087</t>
+    <t xml:space="preserve">7.35387468338013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.55391502380371</t>
   </si>
   <si>
     <t xml:space="preserve">7.60630655288696</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46342039108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49199771881104</t>
+    <t xml:space="preserve">7.46342086791992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49199724197388</t>
   </si>
   <si>
     <t xml:space="preserve">7.44436836242676</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42055463790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62535810470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53010129928589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.47294616699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4872350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46818351745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49675989151001</t>
+    <t xml:space="preserve">7.42055511474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62535905838013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53010082244873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.47294569015503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48723411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4681830406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49676084518433</t>
   </si>
   <si>
     <t xml:space="preserve">7.51581192016602</t>
@@ -1631,58 +1631,58 @@
     <t xml:space="preserve">7.61106967926025</t>
   </si>
   <si>
-    <t xml:space="preserve">7.56344079971313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64440965652466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73490428924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80634641647339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8682656288147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85873794555664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88731575012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92541790008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95399618148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83492469787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9873366355896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01115131378174</t>
+    <t xml:space="preserve">7.56344127655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64441013336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73490333557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80634737014771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86826467514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85873889923096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88731527328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92541885375977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95399713516235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83492565155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98733568191528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01115036010742</t>
   </si>
   <si>
     <t xml:space="preserve">8.06354331970215</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53486394882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52057552337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.54438972473145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62059497833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63964748382568</t>
+    <t xml:space="preserve">7.53486299514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52057504653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54438924789429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62059545516968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63964796066284</t>
   </si>
   <si>
     <t xml:space="preserve">7.77776956558228</t>
@@ -1691,10 +1691,10 @@
     <t xml:space="preserve">7.76824426651001</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90636825561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0349645614624</t>
+    <t xml:space="preserve">7.90636730194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03496551513672</t>
   </si>
   <si>
     <t xml:space="preserve">8.00638866424561</t>
@@ -1703,91 +1703,91 @@
     <t xml:space="preserve">8.04449081420898</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06830406188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2016658782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32550048828125</t>
+    <t xml:space="preserve">8.06830596923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20166492462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32549953460693</t>
   </si>
   <si>
     <t xml:space="preserve">8.44457244873047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33978939056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38265514373779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33502674102783</t>
+    <t xml:space="preserve">8.33978843688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38265419006348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3350248336792</t>
   </si>
   <si>
     <t xml:space="preserve">8.27787113189697</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23500633239746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25882244110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26358222961426</t>
+    <t xml:space="preserve">8.23500537872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25882053375244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26358318328857</t>
   </si>
   <si>
     <t xml:space="preserve">8.16832637786865</t>
   </si>
   <si>
-    <t xml:space="preserve">8.31121063232422</t>
+    <t xml:space="preserve">8.31121158599854</t>
   </si>
   <si>
     <t xml:space="preserve">8.36836624145508</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35407829284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37789344787598</t>
+    <t xml:space="preserve">8.35407733917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37789249420166</t>
   </si>
   <si>
     <t xml:space="preserve">8.28739738464355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21119213104248</t>
+    <t xml:space="preserve">8.21119117736816</t>
   </si>
   <si>
     <t xml:space="preserve">8.22071743011475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43150520324707</t>
+    <t xml:space="preserve">8.43150329589844</t>
   </si>
   <si>
     <t xml:space="preserve">8.445876121521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56085205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51294708251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48899173736572</t>
+    <t xml:space="preserve">8.56085300445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51294612884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48899269104004</t>
   </si>
   <si>
     <t xml:space="preserve">8.60875797271729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44108581542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49857425689697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48420238494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6710376739502</t>
+    <t xml:space="preserve">8.441086769104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49857330322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48420143127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67103672027588</t>
   </si>
   <si>
     <t xml:space="preserve">8.8147554397583</t>
@@ -1796,13 +1796,13 @@
     <t xml:space="preserve">8.74289512634277</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83391857147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77643013000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7093620300293</t>
+    <t xml:space="preserve">8.83391666412354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77642917633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70936012268066</t>
   </si>
   <si>
     <t xml:space="preserve">8.6854076385498</t>
@@ -1811,31 +1811,31 @@
     <t xml:space="preserve">8.70456981658936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78122043609619</t>
+    <t xml:space="preserve">8.78122138977051</t>
   </si>
   <si>
     <t xml:space="preserve">8.80996417999268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77163982391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6518726348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53689765930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37880706787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3740177154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40755176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.41234302520752</t>
+    <t xml:space="preserve">8.77163887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65187454223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53689861297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37880802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37401676177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40755081176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4123420715332</t>
   </si>
   <si>
     <t xml:space="preserve">8.32611083984375</t>
@@ -1844,25 +1844,25 @@
     <t xml:space="preserve">8.45545864105225</t>
   </si>
   <si>
-    <t xml:space="preserve">8.41713428497314</t>
+    <t xml:space="preserve">8.41713237762451</t>
   </si>
   <si>
     <t xml:space="preserve">8.39317989349365</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54647922515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58959674835205</t>
+    <t xml:space="preserve">8.54648017883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58959770202637</t>
   </si>
   <si>
     <t xml:space="preserve">8.27341365814209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25425148010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35485458374023</t>
+    <t xml:space="preserve">8.25425052642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35485649108887</t>
   </si>
   <si>
     <t xml:space="preserve">8.4746208190918</t>
@@ -1871,25 +1871,25 @@
     <t xml:space="preserve">8.42192363739014</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36922550201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31653118133545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29736709594727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28299522399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.1776008605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20155620574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16322994232178</t>
+    <t xml:space="preserve">8.36922740936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31653022766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29736614227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28299427032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17760276794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2015552520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16323089599609</t>
   </si>
   <si>
     <t xml:space="preserve">8.24946117401123</t>
@@ -1898,46 +1898,46 @@
     <t xml:space="preserve">8.18239307403564</t>
   </si>
   <si>
-    <t xml:space="preserve">8.17281150817871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09615993499756</t>
+    <t xml:space="preserve">8.17281055450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09616088867188</t>
   </si>
   <si>
     <t xml:space="preserve">8.14885807037354</t>
   </si>
   <si>
-    <t xml:space="preserve">8.06741714477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.03867435455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.97160482406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78956127166748</t>
+    <t xml:space="preserve">8.06741809844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.03867340087891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.971604347229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78956079483032</t>
   </si>
   <si>
     <t xml:space="preserve">7.62188863754272</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61709833145142</t>
+    <t xml:space="preserve">7.61709785461426</t>
   </si>
   <si>
     <t xml:space="preserve">7.66021347045898</t>
   </si>
   <si>
-    <t xml:space="preserve">7.50212287902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72249221801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5931453704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45900774002075</t>
+    <t xml:space="preserve">7.50212335586548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72249269485474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59314489364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45900726318359</t>
   </si>
   <si>
     <t xml:space="preserve">7.51170444488525</t>
@@ -1949,94 +1949,94 @@
     <t xml:space="preserve">7.59793567657471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90932655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95244264602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82309532165527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88058185577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10574245452881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20634365081787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16802024841309</t>
+    <t xml:space="preserve">7.90932750701904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95244121551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82309579849243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88058376312256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10574150085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2063455581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1680212020874</t>
   </si>
   <si>
     <t xml:space="preserve">8.26383304595947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3452730178833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29257678985596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12011528015137</t>
+    <t xml:space="preserve">8.34527397155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29257583618164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12011337280273</t>
   </si>
   <si>
     <t xml:space="preserve">8.0338830947876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99555730819702</t>
+    <t xml:space="preserve">7.99555683135986</t>
   </si>
   <si>
     <t xml:space="preserve">7.80872344970703</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91411733627319</t>
+    <t xml:space="preserve">7.91411685943604</t>
   </si>
   <si>
     <t xml:space="preserve">7.88537263870239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82788610458374</t>
+    <t xml:space="preserve">7.82788515090942</t>
   </si>
   <si>
     <t xml:space="preserve">7.84704780578613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.00034809112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89974498748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90453577041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94286060333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71770143508911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85662984848022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04346370697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11532402038574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12969493865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13448619842529</t>
+    <t xml:space="preserve">8.0003490447998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89974451065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90453672409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94286155700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71770191192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85662889480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04346561431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11532306671143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12969398498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13448715209961</t>
   </si>
   <si>
     <t xml:space="preserve">8.00992870330811</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93327856063843</t>
+    <t xml:space="preserve">7.93328046798706</t>
   </si>
   <si>
     <t xml:space="preserve">7.75123596191406</t>
@@ -2045,52 +2045,52 @@
     <t xml:space="preserve">7.578773021698</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64105176925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69374799728394</t>
+    <t xml:space="preserve">7.64105081558228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69374752044678</t>
   </si>
   <si>
     <t xml:space="preserve">7.83746719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81351375579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87100124359131</t>
+    <t xml:space="preserve">7.81351327896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87100076675415</t>
   </si>
   <si>
     <t xml:space="preserve">7.87579250335693</t>
   </si>
   <si>
-    <t xml:space="preserve">7.92369937896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89495468139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85183811187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8662109375</t>
+    <t xml:space="preserve">7.92369890213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89495515823364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8518385887146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86621046066284</t>
   </si>
   <si>
     <t xml:space="preserve">7.98597621917725</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9668140411377</t>
+    <t xml:space="preserve">7.96681308746338</t>
   </si>
   <si>
     <t xml:space="preserve">7.92848873138428</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1105318069458</t>
+    <t xml:space="preserve">8.11053371429443</t>
   </si>
   <si>
     <t xml:space="preserve">8.04825401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93807077407837</t>
+    <t xml:space="preserve">7.93806982040405</t>
   </si>
   <si>
     <t xml:space="preserve">7.77997970581055</t>
@@ -2099,31 +2099,31 @@
     <t xml:space="preserve">7.81830453872681</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84225845336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79435110092163</t>
+    <t xml:space="preserve">7.84225749969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79435205459595</t>
   </si>
   <si>
     <t xml:space="preserve">7.7991418838501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94765186309814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9189076423645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71291065216064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77518892288208</t>
+    <t xml:space="preserve">7.94765138626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91890859603882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71291208267212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77518844604492</t>
   </si>
   <si>
     <t xml:space="preserve">7.86141967773438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07699775695801</t>
+    <t xml:space="preserve">8.07699871063232</t>
   </si>
   <si>
     <t xml:space="preserve">8.21592712402344</t>
@@ -2132,85 +2132,85 @@
     <t xml:space="preserve">8.26862335205078</t>
   </si>
   <si>
-    <t xml:space="preserve">8.335693359375</t>
+    <t xml:space="preserve">8.33569145202637</t>
   </si>
   <si>
     <t xml:space="preserve">8.45066738128662</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36443519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47941207885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.55127143859863</t>
+    <t xml:space="preserve">8.36443424224854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47941303253174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.55127048492432</t>
   </si>
   <si>
     <t xml:space="preserve">8.59438705444336</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66624546051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64229202270508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69019889831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58480453491211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.19197273254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74165439605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70332956314087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78477001190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44463539123535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22426605224609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1763596534729</t>
+    <t xml:space="preserve">8.66624450683594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64229297637939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69019794464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58480548858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.19197463989258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74165487289429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70332908630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78477096557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44463586807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22426652908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17636060714722</t>
   </si>
   <si>
     <t xml:space="preserve">7.30091667175293</t>
   </si>
   <si>
-    <t xml:space="preserve">7.36319494247437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33924198150635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09491968154907</t>
+    <t xml:space="preserve">7.36319541931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33924150466919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09492015838623</t>
   </si>
   <si>
     <t xml:space="preserve">6.6972975730896</t>
   </si>
   <si>
-    <t xml:space="preserve">6.36195421218872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3367600440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.54754638671875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.37987422943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30322504043579</t>
+    <t xml:space="preserve">6.3619532585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33675956726074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.54754686355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.37987470626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30322456359863</t>
   </si>
   <si>
     <t xml:space="preserve">5.86851930618286</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">6.45776605606079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.08409786224365</t>
+    <t xml:space="preserve">6.08409690856934</t>
   </si>
   <si>
     <t xml:space="preserve">6.03619146347046</t>
@@ -2228,16 +2228,16 @@
     <t xml:space="preserve">6.29967498779297</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76915740966797</t>
+    <t xml:space="preserve">6.76915693283081</t>
   </si>
   <si>
     <t xml:space="preserve">6.84101629257202</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53441619873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37153577804565</t>
+    <t xml:space="preserve">6.53441667556763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3715353012085</t>
   </si>
   <si>
     <t xml:space="preserve">6.27572298049927</t>
@@ -2246,25 +2246,25 @@
     <t xml:space="preserve">6.02852582931519</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11092472076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85606288909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45201730728149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38111591339111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32171297073364</t>
+    <t xml:space="preserve">6.11092519760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85606336593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45201778411865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38111639022827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32171249389648</t>
   </si>
   <si>
     <t xml:space="preserve">6.35237264633179</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40986061096191</t>
+    <t xml:space="preserve">6.40986013412476</t>
   </si>
   <si>
     <t xml:space="preserve">6.4079442024231</t>
@@ -2279,37 +2279,37 @@
     <t xml:space="preserve">6.49962091445923</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44746923446655</t>
+    <t xml:space="preserve">6.44746971130371</t>
   </si>
   <si>
     <t xml:space="preserve">6.43008518218994</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39338636398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44360589981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59619760513306</t>
+    <t xml:space="preserve">6.39338541030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44360637664795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59619808197021</t>
   </si>
   <si>
     <t xml:space="preserve">6.61551284790039</t>
   </si>
   <si>
-    <t xml:space="preserve">6.79321479797363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8279824256897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6232385635376</t>
+    <t xml:space="preserve">6.79321432113647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82798194885254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62323904037476</t>
   </si>
   <si>
     <t xml:space="preserve">6.690842628479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76617240905762</t>
+    <t xml:space="preserve">6.76617288589478</t>
   </si>
   <si>
     <t xml:space="preserve">6.78935194015503</t>
@@ -2321,10 +2321,10 @@
     <t xml:space="preserve">6.95932626724243</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08487606048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93807935714722</t>
+    <t xml:space="preserve">7.084876537323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93807983398438</t>
   </si>
   <si>
     <t xml:space="preserve">6.70629501342773</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">6.66766452789307</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94001054763794</t>
+    <t xml:space="preserve">6.9400110244751</t>
   </si>
   <si>
     <t xml:space="preserve">6.5112099647522</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67345857620239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53245687484741</t>
+    <t xml:space="preserve">6.67345905303955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53245735168457</t>
   </si>
   <si>
     <t xml:space="preserve">6.6638011932373</t>
@@ -2351,28 +2351,28 @@
     <t xml:space="preserve">6.67732238769531</t>
   </si>
   <si>
-    <t xml:space="preserve">6.72947311401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71209001541138</t>
+    <t xml:space="preserve">6.72947359085083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71208953857422</t>
   </si>
   <si>
     <t xml:space="preserve">7.14668560028076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05010890960693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94387435913086</t>
+    <t xml:space="preserve">7.05010843276978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94387483596802</t>
   </si>
   <si>
     <t xml:space="preserve">7.11191749572754</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09839725494385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.142822265625</t>
+    <t xml:space="preserve">7.09839677810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14282274246216</t>
   </si>
   <si>
     <t xml:space="preserve">7.14475393295288</t>
@@ -2381,22 +2381,22 @@
     <t xml:space="preserve">7.13895988464355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17759037017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05976676940918</t>
+    <t xml:space="preserve">7.17758989334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05976629257202</t>
   </si>
   <si>
     <t xml:space="preserve">7.20463180541992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06942367553711</t>
+    <t xml:space="preserve">7.06942415237427</t>
   </si>
   <si>
     <t xml:space="preserve">7.31279754638672</t>
   </si>
   <si>
-    <t xml:space="preserve">7.33018207550049</t>
+    <t xml:space="preserve">7.33018159866333</t>
   </si>
   <si>
     <t xml:space="preserve">7.38619613647461</t>
@@ -2405,10 +2405,10 @@
     <t xml:space="preserve">7.44800567626953</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44027900695801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5812816619873</t>
+    <t xml:space="preserve">7.44027853012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.58128118515015</t>
   </si>
   <si>
     <t xml:space="preserve">7.27223539352417</t>
@@ -2438,40 +2438,40 @@
     <t xml:space="preserve">7.70683145523071</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84203910827637</t>
+    <t xml:space="preserve">7.84203863143921</t>
   </si>
   <si>
     <t xml:space="preserve">7.86425065994263</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81499719619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7502908706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92412900924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91350650787354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82851839065552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89322519302368</t>
+    <t xml:space="preserve">7.81499767303467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75029039382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92412853240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91350555419922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82851791381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89322423934937</t>
   </si>
   <si>
     <t xml:space="preserve">7.98497247695923</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87294340133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02649974822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88549852371216</t>
+    <t xml:space="preserve">7.87294387817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0265007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88549900054932</t>
   </si>
   <si>
     <t xml:space="preserve">7.83817577362061</t>
@@ -2480,10 +2480,10 @@
     <t xml:space="preserve">8.2631139755249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42729377746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21965312957764</t>
+    <t xml:space="preserve">8.42729473114014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21965408325195</t>
   </si>
   <si>
     <t xml:space="preserve">8.22158527374268</t>
@@ -2492,10 +2492,10 @@
     <t xml:space="preserve">8.28146266937256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.23221015930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2959508895874</t>
+    <t xml:space="preserve">8.23220920562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29594993591309</t>
   </si>
   <si>
     <t xml:space="preserve">8.13659858703613</t>
@@ -2510,34 +2510,34 @@
     <t xml:space="preserve">8.26601123809814</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43598556518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39735507965088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2775993347168</t>
+    <t xml:space="preserve">8.43598651885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3973560333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27760028839111</t>
   </si>
   <si>
     <t xml:space="preserve">8.30753898620605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24283218383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34423923492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.228346824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39059543609619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3432731628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43405437469482</t>
+    <t xml:space="preserve">8.24283313751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34423828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22834777832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39059448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34327125549316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43405342102051</t>
   </si>
   <si>
     <t xml:space="preserve">8.3104362487793</t>
@@ -2546,76 +2546,76 @@
     <t xml:space="preserve">8.18102359771729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29788208007812</t>
+    <t xml:space="preserve">8.29788112640381</t>
   </si>
   <si>
     <t xml:space="preserve">8.48330879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77110767364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58664608001709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47944641113281</t>
+    <t xml:space="preserve">8.7711067199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58664512634277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4794454574585</t>
   </si>
   <si>
     <t xml:space="preserve">8.71799182891846</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65907764434814</t>
+    <t xml:space="preserve">8.65907859802246</t>
   </si>
   <si>
     <t xml:space="preserve">8.75565624237061</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71412658691406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82132625579834</t>
+    <t xml:space="preserve">8.71412754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82132720947266</t>
   </si>
   <si>
     <t xml:space="preserve">8.94784355163574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01448059082031</t>
+    <t xml:space="preserve">9.014479637146</t>
   </si>
   <si>
     <t xml:space="preserve">9.03959083557129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06083965301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85319805145264</t>
+    <t xml:space="preserve">9.06083869934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85319709777832</t>
   </si>
   <si>
     <t xml:space="preserve">8.94011783599854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01641368865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05117988586426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80587482452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08884525299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01158428192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99999523162842</t>
+    <t xml:space="preserve">9.01641273498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05118083953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80587577819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08884620666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01158332824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9999942779541</t>
   </si>
   <si>
     <t xml:space="preserve">9.04828453063965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04635047912598</t>
+    <t xml:space="preserve">9.04635238647461</t>
   </si>
   <si>
     <t xml:space="preserve">9.02896785736084</t>
@@ -2624,16 +2624,16 @@
     <t xml:space="preserve">8.95460414886475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99613094329834</t>
+    <t xml:space="preserve">8.99613189697266</t>
   </si>
   <si>
     <t xml:space="preserve">8.9719877243042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04442024230957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21342945098877</t>
+    <t xml:space="preserve">9.04441928863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2134313583374</t>
   </si>
   <si>
     <t xml:space="preserve">9.23853969573975</t>
@@ -2648,34 +2648,34 @@
     <t xml:space="preserve">9.12554550170898</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03186511993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07629013061523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80008125305176</t>
+    <t xml:space="preserve">9.0318660736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07629108428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80008220672607</t>
   </si>
   <si>
     <t xml:space="preserve">8.93528842926025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94687652587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74020290374756</t>
+    <t xml:space="preserve">8.94687843322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74020385742188</t>
   </si>
   <si>
     <t xml:space="preserve">8.88893127441406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66294288635254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50262451171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65714645385742</t>
+    <t xml:space="preserve">8.66294193267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50262260437012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65714740753174</t>
   </si>
   <si>
     <t xml:space="preserve">8.51035022735596</t>
@@ -2687,22 +2687,22 @@
     <t xml:space="preserve">8.76724433898926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89086437225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96426010131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24626541137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26171779632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51281833648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35443210601807</t>
+    <t xml:space="preserve">8.8908634185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96426200866699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24626636505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5128173828125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35443115234375</t>
   </si>
   <si>
     <t xml:space="preserve">9.29841804504395</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">9.4316930770874</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25012969970703</t>
+    <t xml:space="preserve">9.25012874603271</t>
   </si>
   <si>
     <t xml:space="preserve">9.13230514526367</t>
@@ -2726,34 +2726,34 @@
     <t xml:space="preserve">9.06856536865234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19411468505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17286777496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22694873809814</t>
+    <t xml:space="preserve">9.19411373138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17286682128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22695159912109</t>
   </si>
   <si>
     <t xml:space="preserve">9.36215782165527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12651062011719</t>
+    <t xml:space="preserve">9.12650966644287</t>
   </si>
   <si>
     <t xml:space="preserve">9.1477575302124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13037395477295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15934753417969</t>
+    <t xml:space="preserve">9.13037490844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15934658050537</t>
   </si>
   <si>
     <t xml:space="preserve">9.12264823913574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00482368469238</t>
+    <t xml:space="preserve">9.0048246383667</t>
   </si>
   <si>
     <t xml:space="preserve">9.13616847991943</t>
@@ -2762,85 +2762,85 @@
     <t xml:space="preserve">9.05890655517578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04538536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8367805480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87347888946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95267295837402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9391508102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86961555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88120555877686</t>
+    <t xml:space="preserve">9.04538726806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83677864074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87347984313965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95267391204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93915176391602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86961650848389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88120651245117</t>
   </si>
   <si>
     <t xml:space="preserve">8.96619415283203</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13809967041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02027606964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90438461303711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66487216949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59340667724609</t>
+    <t xml:space="preserve">9.13809871673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0202751159668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90438365936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66487407684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59340572357178</t>
   </si>
   <si>
     <t xml:space="preserve">8.54125499725342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.55284404754639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42150020599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38093757629395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47365188598633</t>
+    <t xml:space="preserve">8.5528450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42150115966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38093948364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47365093231201</t>
   </si>
   <si>
     <t xml:space="preserve">8.42343139648438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42536354064941</t>
+    <t xml:space="preserve">8.4253625869751</t>
   </si>
   <si>
     <t xml:space="preserve">8.54705047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4929666519165</t>
+    <t xml:space="preserve">8.49296569824219</t>
   </si>
   <si>
     <t xml:space="preserve">8.58568096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51228332519531</t>
+    <t xml:space="preserve">8.512282371521</t>
   </si>
   <si>
     <t xml:space="preserve">8.50648784637451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63590145111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59533786773682</t>
+    <t xml:space="preserve">8.63590049743652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5953369140625</t>
   </si>
   <si>
     <t xml:space="preserve">8.65328407287598</t>
@@ -2849,31 +2849,31 @@
     <t xml:space="preserve">8.57215976715088</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57795333862305</t>
+    <t xml:space="preserve">8.57795429229736</t>
   </si>
   <si>
     <t xml:space="preserve">8.82712268829346</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86768531799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94108390808105</t>
+    <t xml:space="preserve">8.86768627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94108295440674</t>
   </si>
   <si>
     <t xml:space="preserve">9.3370475769043</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31773281097412</t>
+    <t xml:space="preserve">9.3177318572998</t>
   </si>
   <si>
     <t xml:space="preserve">9.40272045135498</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34477424621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38533687591553</t>
+    <t xml:space="preserve">9.3447732925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38533782958984</t>
   </si>
   <si>
     <t xml:space="preserve">9.44521331787109</t>
@@ -2882,13 +2882,13 @@
     <t xml:space="preserve">9.58235359191895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42976093292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44135189056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35249900817871</t>
+    <t xml:space="preserve">9.42976188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44135093688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35250091552734</t>
   </si>
   <si>
     <t xml:space="preserve">9.20570278167725</t>
@@ -2897,19 +2897,19 @@
     <t xml:space="preserve">9.28875923156738</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3158016204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34091186523438</t>
+    <t xml:space="preserve">9.31580066680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34090995788574</t>
   </si>
   <si>
     <t xml:space="preserve">9.05697536468506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19218254089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16320896148682</t>
+    <t xml:space="preserve">9.19218158721924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16320991516113</t>
   </si>
   <si>
     <t xml:space="preserve">9.04924964904785</t>
@@ -2927,25 +2927,25 @@
     <t xml:space="preserve">9.52440738677979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76391792297363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48963928222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46839141845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38726902008057</t>
+    <t xml:space="preserve">9.76391696929932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48964023590088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46839237213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38726806640625</t>
   </si>
   <si>
     <t xml:space="preserve">9.42589950561523</t>
   </si>
   <si>
-    <t xml:space="preserve">9.364089012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2829647064209</t>
+    <t xml:space="preserve">9.36408996582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28296566009521</t>
   </si>
   <si>
     <t xml:space="preserve">9.25978755950928</t>
@@ -2954,46 +2954,46 @@
     <t xml:space="preserve">9.24240303039551</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26364994049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28682804107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3505687713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23081302642822</t>
+    <t xml:space="preserve">9.26364898681641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28682899475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35056972503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23081398010254</t>
   </si>
   <si>
     <t xml:space="preserve">9.39885807037354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32932186126709</t>
+    <t xml:space="preserve">9.32932090759277</t>
   </si>
   <si>
     <t xml:space="preserve">9.4645299911499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41624164581299</t>
+    <t xml:space="preserve">9.41624069213867</t>
   </si>
   <si>
     <t xml:space="preserve">9.63836765289307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47225475311279</t>
+    <t xml:space="preserve">9.47225379943848</t>
   </si>
   <si>
     <t xml:space="preserve">9.56497001647949</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64416217803955</t>
+    <t xml:space="preserve">9.64416313171387</t>
   </si>
   <si>
     <t xml:space="preserve">9.76943683624268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55384922027588</t>
+    <t xml:space="preserve">9.55384826660156</t>
   </si>
   <si>
     <t xml:space="preserve">9.73544692993164</t>
@@ -3002,19 +3002,19 @@
     <t xml:space="preserve">9.83255958557129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70340156555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62959575653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60823154449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52860069274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63348007202148</t>
+    <t xml:space="preserve">9.70340061187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62959671020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60823059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52859973907471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63347911834717</t>
   </si>
   <si>
     <t xml:space="preserve">9.8811149597168</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">10.0025053024292</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0947618484497</t>
+    <t xml:space="preserve">10.0947608947754</t>
   </si>
   <si>
     <t xml:space="preserve">9.98308181762695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94423770904541</t>
+    <t xml:space="preserve">9.94423675537109</t>
   </si>
   <si>
     <t xml:space="preserve">9.7742919921875</t>
@@ -3041,13 +3041,13 @@
     <t xml:space="preserve">9.82284736633301</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81313610076904</t>
+    <t xml:space="preserve">9.81313514709473</t>
   </si>
   <si>
     <t xml:space="preserve">9.82770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79856872558594</t>
+    <t xml:space="preserve">9.79856967926025</t>
   </si>
   <si>
     <t xml:space="preserve">9.79371452331543</t>
@@ -3062,25 +3062,25 @@
     <t xml:space="preserve">10.2355718612671</t>
   </si>
   <si>
-    <t xml:space="preserve">10.254994392395</t>
+    <t xml:space="preserve">10.2549953460693</t>
   </si>
   <si>
     <t xml:space="preserve">10.1870174407959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1481714248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2307176589966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2792730331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2744169235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3132629394531</t>
+    <t xml:space="preserve">10.14817237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2307167053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2792720794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2744178771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3132619857788</t>
   </si>
   <si>
     <t xml:space="preserve">10.3909511566162</t>
@@ -3092,13 +3092,13 @@
     <t xml:space="preserve">10.6337299346924</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8133878707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8182420730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8328084945679</t>
+    <t xml:space="preserve">10.8133869171143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8182430267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8328094482422</t>
   </si>
   <si>
     <t xml:space="preserve">10.8230991363525</t>
@@ -3119,16 +3119,16 @@
     <t xml:space="preserve">11.0852994918823</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0755891799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0610218048096</t>
+    <t xml:space="preserve">11.0755882263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0610227584839</t>
   </si>
   <si>
     <t xml:space="preserve">11.0464553833008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9687652587891</t>
+    <t xml:space="preserve">10.9687662124634</t>
   </si>
   <si>
     <t xml:space="preserve">11.0027551651001</t>
@@ -3137,31 +3137,31 @@
     <t xml:space="preserve">10.9104986190796</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8910779953003</t>
+    <t xml:space="preserve">10.891077041626</t>
   </si>
   <si>
     <t xml:space="preserve">10.997899055481</t>
   </si>
   <si>
-    <t xml:space="preserve">10.827953338623</t>
+    <t xml:space="preserve">10.8279542922974</t>
   </si>
   <si>
     <t xml:space="preserve">10.9541988372803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9784774780273</t>
+    <t xml:space="preserve">10.9784784317017</t>
   </si>
   <si>
     <t xml:space="preserve">10.8667984008789</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6531534194946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7162761688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9930429458618</t>
+    <t xml:space="preserve">10.6531524658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7162752151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9930438995361</t>
   </si>
   <si>
     <t xml:space="preserve">11.1629886627197</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">11.0513105392456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4009122848511</t>
+    <t xml:space="preserve">11.4009132385254</t>
   </si>
   <si>
     <t xml:space="preserve">11.4688920974731</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">11.4931688308716</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5174465179443</t>
+    <t xml:space="preserve">11.51744556427</t>
   </si>
   <si>
     <t xml:space="preserve">11.5951366424561</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">11.721381187439</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8621940612793</t>
+    <t xml:space="preserve">11.862193107605</t>
   </si>
   <si>
     <t xml:space="preserve">11.745659828186</t>
@@ -3215,10 +3215,10 @@
     <t xml:space="preserve">11.6922483444214</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6825361251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3620681762695</t>
+    <t xml:space="preserve">11.6825370788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3620672225952</t>
   </si>
   <si>
     <t xml:space="preserve">11.2552452087402</t>
@@ -3230,19 +3230,19 @@
     <t xml:space="preserve">11.4251909255981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3814907073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3669233322144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.332935333252</t>
+    <t xml:space="preserve">11.3814916610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.36692237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3329343795776</t>
   </si>
   <si>
     <t xml:space="preserve">11.3717794418335</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5902805328369</t>
+    <t xml:space="preserve">11.5902814865112</t>
   </si>
   <si>
     <t xml:space="preserve">11.6971035003662</t>
@@ -3251,13 +3251,13 @@
     <t xml:space="preserve">11.570858001709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5757141113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5125913619995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.410623550415</t>
+    <t xml:space="preserve">11.5757131576538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5125904083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4106245040894</t>
   </si>
   <si>
     <t xml:space="preserve">11.5514373779297</t>
@@ -3266,46 +3266,46 @@
     <t xml:space="preserve">11.7068157196045</t>
   </si>
   <si>
-    <t xml:space="preserve">11.949595451355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9301719665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7942161560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7602252960205</t>
+    <t xml:space="preserve">11.9495944976807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9301710128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7942152023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7602262496948</t>
   </si>
   <si>
     <t xml:space="preserve">11.8087816238403</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8282051086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7505159378052</t>
+    <t xml:space="preserve">11.8282060623169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7505149841309</t>
   </si>
   <si>
     <t xml:space="preserve">11.9253158569336</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0175724029541</t>
+    <t xml:space="preserve">12.0175714492798</t>
   </si>
   <si>
     <t xml:space="preserve">12.0564165115356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0369958877563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.187518119812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1486730575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3865966796875</t>
+    <t xml:space="preserve">12.036994934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1875171661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1486740112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3865976333618</t>
   </si>
   <si>
     <t xml:space="preserve">12.5565433502197</t>
@@ -3317,10 +3317,10 @@
     <t xml:space="preserve">12.5274085998535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5322637557983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5662517547607</t>
+    <t xml:space="preserve">12.5322647094727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5662527084351</t>
   </si>
   <si>
     <t xml:space="preserve">11.9350261688232</t>
@@ -3347,31 +3347,31 @@
     <t xml:space="preserve">12.304051399231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4108734130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4448623657227</t>
+    <t xml:space="preserve">12.4108743667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.444863319397</t>
   </si>
   <si>
     <t xml:space="preserve">12.4157304763794</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5468320846558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6439437866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7750434875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9644107818604</t>
+    <t xml:space="preserve">12.5468311309814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6439428329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7750425338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9644117355347</t>
   </si>
   <si>
     <t xml:space="preserve">12.9595565795898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9401321411133</t>
+    <t xml:space="preserve">12.9401330947876</t>
   </si>
   <si>
     <t xml:space="preserve">13.0760898590088</t>
@@ -3386,16 +3386,16 @@
     <t xml:space="preserve">12.9109992980957</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4837083816528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7070646286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4982738494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4739971160889</t>
+    <t xml:space="preserve">12.4837074279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7070655822754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4982748031616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4739980697632</t>
   </si>
   <si>
     <t xml:space="preserve">12.3428964614868</t>
@@ -3404,31 +3404,31 @@
     <t xml:space="preserve">12.639087677002</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8721551895142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6099519729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.585675239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3768854141235</t>
+    <t xml:space="preserve">12.8721542358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6099529266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5856761932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3768863677979</t>
   </si>
   <si>
     <t xml:space="preserve">12.4885635375977</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2846298217773</t>
+    <t xml:space="preserve">12.284628868103</t>
   </si>
   <si>
     <t xml:space="preserve">12.2797737121582</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2020845413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4400091171265</t>
+    <t xml:space="preserve">12.2020835876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4400081634521</t>
   </si>
   <si>
     <t xml:space="preserve">12.3720302581787</t>
@@ -3437,19 +3437,19 @@
     <t xml:space="preserve">12.4351530075073</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3963088989258</t>
+    <t xml:space="preserve">12.3963079452515</t>
   </si>
   <si>
     <t xml:space="preserve">12.4060192108154</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7553701400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6728248596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6388368606567</t>
+    <t xml:space="preserve">11.7553691864014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6728258132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6388359069824</t>
   </si>
   <si>
     <t xml:space="preserve">11.4397573471069</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">11.1532783508301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2164011001587</t>
+    <t xml:space="preserve">11.2164001464844</t>
   </si>
   <si>
     <t xml:space="preserve">11.0804433822632</t>
@@ -3470,7 +3470,7 @@
     <t xml:space="preserve">10.6968536376953</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6434412002563</t>
+    <t xml:space="preserve">10.6434421539307</t>
   </si>
   <si>
     <t xml:space="preserve">10.6191644668579</t>
@@ -3485,7 +3485,7 @@
     <t xml:space="preserve">10.9833326339722</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8619432449341</t>
+    <t xml:space="preserve">10.8619441986084</t>
   </si>
   <si>
     <t xml:space="preserve">10.7114200592041</t>
@@ -3494,40 +3494,40 @@
     <t xml:space="preserve">10.5269069671631</t>
   </si>
   <si>
-    <t xml:space="preserve">10.44921875</t>
+    <t xml:space="preserve">10.4492197036743</t>
   </si>
   <si>
     <t xml:space="preserve">10.5317640304565</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4880628585815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3375406265259</t>
+    <t xml:space="preserve">10.4880619049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3375396728516</t>
   </si>
   <si>
     <t xml:space="preserve">10.0899047851562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1821613311768</t>
+    <t xml:space="preserve">10.1821603775024</t>
   </si>
   <si>
     <t xml:space="preserve">10.1918716430664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2647047042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95880508422852</t>
+    <t xml:space="preserve">10.264705657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95880317687988</t>
   </si>
   <si>
     <t xml:space="preserve">9.02556133270264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18870735168457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46644878387451</t>
+    <t xml:space="preserve">9.18870830535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4664478302002</t>
   </si>
   <si>
     <t xml:space="preserve">9.04304218292236</t>
@@ -3536,19 +3536,19 @@
     <t xml:space="preserve">9.04498291015625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06246376037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84299182891846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8391056060791</t>
+    <t xml:space="preserve">9.06246280670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84299087524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83910751342773</t>
   </si>
   <si>
     <t xml:space="preserve">8.5438871383667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14403629302979</t>
+    <t xml:space="preserve">9.1440372467041</t>
   </si>
   <si>
     <t xml:space="preserve">8.9906005859375</t>
@@ -3557,7 +3557,7 @@
     <t xml:space="preserve">8.95369815826416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99836921691895</t>
+    <t xml:space="preserve">8.99837017059326</t>
   </si>
   <si>
     <t xml:space="preserve">9.03138828277588</t>
@@ -3569,7 +3569,7 @@
     <t xml:space="preserve">9.55190658569336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.75001430511475</t>
+    <t xml:space="preserve">9.75001335144043</t>
   </si>
   <si>
     <t xml:space="preserve">9.621826171875</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">9.68203639984131</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63736438751221</t>
+    <t xml:space="preserve">9.63736343383789</t>
   </si>
   <si>
     <t xml:space="preserve">9.62571144104004</t>
@@ -3590,22 +3590,22 @@
     <t xml:space="preserve">10.2598505020142</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2501401901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4200830459595</t>
+    <t xml:space="preserve">10.2501392364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4200849533081</t>
   </si>
   <si>
     <t xml:space="preserve">10.3860950469971</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5074844360352</t>
+    <t xml:space="preserve">10.5074853897095</t>
   </si>
   <si>
     <t xml:space="preserve">10.4346523284912</t>
   </si>
   <si>
-    <t xml:space="preserve">10.415228843689</t>
+    <t xml:space="preserve">10.4152297973633</t>
   </si>
   <si>
     <t xml:space="preserve">10.3278293609619</t>
@@ -3614,13 +3614,13 @@
     <t xml:space="preserve">10.2110719680786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5284900665283</t>
+    <t xml:space="preserve">10.528489112854</t>
   </si>
   <si>
     <t xml:space="preserve">10.3429231643677</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3819894790649</t>
+    <t xml:space="preserve">10.3819885253906</t>
   </si>
   <si>
     <t xml:space="preserve">10.4308233261108</t>
@@ -3629,22 +3629,22 @@
     <t xml:space="preserve">10.4210567474365</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4259405136108</t>
+    <t xml:space="preserve">10.4259395599365</t>
   </si>
   <si>
     <t xml:space="preserve">10.5333728790283</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2306051254272</t>
+    <t xml:space="preserve">10.2306060791016</t>
   </si>
   <si>
     <t xml:space="preserve">10.4601230621338</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0645732879639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1720056533813</t>
+    <t xml:space="preserve">10.0645723342896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.172004699707</t>
   </si>
   <si>
     <t xml:space="preserve">9.54986763000488</t>
@@ -3653,7 +3653,7 @@
     <t xml:space="preserve">9.33890724182129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58893489837646</t>
+    <t xml:space="preserve">9.58893394470215</t>
   </si>
   <si>
     <t xml:space="preserve">9.68855476379395</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">9.669020652771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97178936004639</t>
+    <t xml:space="preserve">9.97178840637207</t>
   </si>
   <si>
     <t xml:space="preserve">10.0059719085693</t>
@@ -3686,19 +3686,19 @@
     <t xml:space="preserve">9.40532112121582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47173404693604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47368717193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.65925407409668</t>
+    <t xml:space="preserve">9.47173500061035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47368812561035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.659255027771</t>
   </si>
   <si>
     <t xml:space="preserve">9.78622150421143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71004104614258</t>
+    <t xml:space="preserve">9.71004199981689</t>
   </si>
   <si>
     <t xml:space="preserve">9.51861476898193</t>
@@ -3707,13 +3707,13 @@
     <t xml:space="preserve">9.69441413879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.665114402771</t>
+    <t xml:space="preserve">9.66511344909668</t>
   </si>
   <si>
     <t xml:space="preserve">9.87412166595459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68074131011963</t>
+    <t xml:space="preserve">9.68074035644531</t>
   </si>
   <si>
     <t xml:space="preserve">9.54791450500488</t>
@@ -3737,7 +3737,7 @@
     <t xml:space="preserve">9.52252006530762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5674467086792</t>
+    <t xml:space="preserve">9.56744766235352</t>
   </si>
   <si>
     <t xml:space="preserve">9.46782779693604</t>
@@ -3749,13 +3749,13 @@
     <t xml:space="preserve">9.4541540145874</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79110431671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.85947132110596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91807174682617</t>
+    <t xml:space="preserve">9.79110527038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.85947227478027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91807079315186</t>
   </si>
   <si>
     <t xml:space="preserve">9.81552219390869</t>
@@ -3767,10 +3767,10 @@
     <t xml:space="preserve">9.72566890716553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.661208152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95713901519775</t>
+    <t xml:space="preserve">9.66120910644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95713806152344</t>
   </si>
   <si>
     <t xml:space="preserve">10.001088142395</t>
@@ -3782,7 +3782,7 @@
     <t xml:space="preserve">10.2989721298218</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0499219894409</t>
+    <t xml:space="preserve">10.0499210357666</t>
   </si>
   <si>
     <t xml:space="preserve">9.94248867034912</t>
@@ -3800,28 +3800,28 @@
     <t xml:space="preserve">10.1329383850098</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2354888916016</t>
+    <t xml:space="preserve">10.2354879379272</t>
   </si>
   <si>
     <t xml:space="preserve">10.4161729812622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1866550445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.167121887207</t>
+    <t xml:space="preserve">10.18665599823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1671228408813</t>
   </si>
   <si>
     <t xml:space="preserve">10.5675563812256</t>
   </si>
   <si>
-    <t xml:space="preserve">10.367338180542</t>
+    <t xml:space="preserve">10.3673391342163</t>
   </si>
   <si>
     <t xml:space="preserve">10.1182880401611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1964225769043</t>
+    <t xml:space="preserve">10.19642162323</t>
   </si>
   <si>
     <t xml:space="preserve">9.97667217254639</t>
@@ -3830,7 +3830,7 @@
     <t xml:space="preserve">9.81063747406006</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79598808288574</t>
+    <t xml:space="preserve">9.79598712921143</t>
   </si>
   <si>
     <t xml:space="preserve">9.78133869171143</t>
@@ -3839,7 +3839,7 @@
     <t xml:space="preserve">9.87900447845459</t>
   </si>
   <si>
-    <t xml:space="preserve">10.035270690918</t>
+    <t xml:space="preserve">10.0352716445923</t>
   </si>
   <si>
     <t xml:space="preserve">10.1134052276611</t>
@@ -3854,10 +3854,10 @@
     <t xml:space="preserve">9.9815559387207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83505439758301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57916641235352</t>
+    <t xml:space="preserve">9.83505535125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57916736602783</t>
   </si>
   <si>
     <t xml:space="preserve">9.44829368591309</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">9.20803356170654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32914066314697</t>
+    <t xml:space="preserve">9.32914161682129</t>
   </si>
   <si>
     <t xml:space="preserve">9.1298999786377</t>
@@ -3884,10 +3884,10 @@
     <t xml:space="preserve">9.29593372344971</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31742095947266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96581935882568</t>
+    <t xml:space="preserve">9.31742000579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9658203125</t>
   </si>
   <si>
     <t xml:space="preserve">9.00683975219727</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">8.68649196624756</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89550018310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84471321105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88377857208252</t>
+    <t xml:space="preserve">8.89549922943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84471225738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88377952575684</t>
   </si>
   <si>
     <t xml:space="preserve">8.72360610961914</t>
@@ -3932,25 +3932,25 @@
     <t xml:space="preserve">8.88963985443115</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79783344268799</t>
+    <t xml:space="preserve">8.79783248901367</t>
   </si>
   <si>
     <t xml:space="preserve">8.94628620147705</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98144626617432</t>
+    <t xml:space="preserve">8.98144721984863</t>
   </si>
   <si>
     <t xml:space="preserve">8.78611278533936</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98535346984863</t>
+    <t xml:space="preserve">8.98535251617432</t>
   </si>
   <si>
     <t xml:space="preserve">8.96191310882568</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84080505371094</t>
+    <t xml:space="preserve">8.84080600738525</t>
   </si>
   <si>
     <t xml:space="preserve">8.60054492950439</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">8.79587936401367</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8017406463623</t>
+    <t xml:space="preserve">8.80173969268799</t>
   </si>
   <si>
     <t xml:space="preserve">8.70797920227051</t>
@@ -3986,16 +3986,16 @@
     <t xml:space="preserve">8.9638671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09474086761475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11622524261475</t>
+    <t xml:space="preserve">9.09473991394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11622619628906</t>
   </si>
   <si>
     <t xml:space="preserve">8.9755859375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05957984924316</t>
+    <t xml:space="preserve">9.05958080291748</t>
   </si>
   <si>
     <t xml:space="preserve">9.41704082489014</t>
@@ -4004,10 +4004,10 @@
     <t xml:space="preserve">9.54205513000488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49322128295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5654935836792</t>
+    <t xml:space="preserve">9.49322032928467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56549453735352</t>
   </si>
   <si>
     <t xml:space="preserve">9.73543548583984</t>
@@ -4022,16 +4022,16 @@
     <t xml:space="preserve">9.96202182769775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83993816375732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.80575466156006</t>
+    <t xml:space="preserve">9.83993721008301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.80575561523438</t>
   </si>
   <si>
     <t xml:space="preserve">9.69050788879395</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72371387481689</t>
+    <t xml:space="preserve">9.72371482849121</t>
   </si>
   <si>
     <t xml:space="preserve">9.75692081451416</t>
@@ -4046,10 +4046,10 @@
     <t xml:space="preserve">9.58502769470215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62214088439941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31546688079834</t>
+    <t xml:space="preserve">9.62214183807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31546783447266</t>
   </si>
   <si>
     <t xml:space="preserve">9.5108003616333</t>
@@ -4073,7 +4073,7 @@
     <t xml:space="preserve">9.33500003814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43461990356445</t>
+    <t xml:space="preserve">9.43462085723877</t>
   </si>
   <si>
     <t xml:space="preserve">9.59088706970215</t>
@@ -4082,7 +4082,7 @@
     <t xml:space="preserve">9.63190841674805</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64948844909668</t>
+    <t xml:space="preserve">9.64948749542236</t>
   </si>
   <si>
     <t xml:space="preserve">9.65730094909668</t>
@@ -4091,7 +4091,7 @@
     <t xml:space="preserve">9.74324798583984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71199417114258</t>
+    <t xml:space="preserve">9.71199512481689</t>
   </si>
   <si>
     <t xml:space="preserve">9.71785354614258</t>
@@ -4106,7 +4106,7 @@
     <t xml:space="preserve">9.43852710723877</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71590042114258</t>
+    <t xml:space="preserve">9.71590137481689</t>
   </si>
   <si>
     <t xml:space="preserve">10.0303888320923</t>
@@ -4118,7 +4118,7 @@
     <t xml:space="preserve">9.83017158508301</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1427059173584</t>
+    <t xml:space="preserve">10.1427049636841</t>
   </si>
   <si>
     <t xml:space="preserve">10.2696723937988</t>
@@ -4157,10 +4157,10 @@
     <t xml:space="preserve">10.4698905944824</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4405899047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3917560577393</t>
+    <t xml:space="preserve">10.4405889511108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3917570114136</t>
   </si>
   <si>
     <t xml:space="preserve">10.4747734069824</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">10.6261568069458</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7580080032349</t>
+    <t xml:space="preserve">10.7580070495605</t>
   </si>
   <si>
     <t xml:space="preserve">10.8703241348267</t>
@@ -4187,13 +4187,13 @@
     <t xml:space="preserve">10.8605575561523</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8312568664551</t>
+    <t xml:space="preserve">10.8312578201294</t>
   </si>
   <si>
     <t xml:space="preserve">10.7775402069092</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8800897598267</t>
+    <t xml:space="preserve">10.880090713501</t>
   </si>
   <si>
     <t xml:space="preserve">10.8361396789551</t>
@@ -4205,13 +4205,13 @@
     <t xml:space="preserve">11.0314741134644</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0070581436157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1291418075562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2463417053223</t>
+    <t xml:space="preserve">11.00705909729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1291408538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2463426589966</t>
   </si>
   <si>
     <t xml:space="preserve">11.2268075942993</t>
@@ -4220,7 +4220,7 @@
     <t xml:space="preserve">11.2121572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2072744369507</t>
+    <t xml:space="preserve">11.207275390625</t>
   </si>
   <si>
     <t xml:space="preserve">11.2561082839966</t>
@@ -4241,16 +4241,16 @@
     <t xml:space="preserve">11.5295753479004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5737504959106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6670083999634</t>
+    <t xml:space="preserve">11.5737495422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6670074462891</t>
   </si>
   <si>
     <t xml:space="preserve">11.5982913970947</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6326494216919</t>
+    <t xml:space="preserve">11.6326503753662</t>
   </si>
   <si>
     <t xml:space="preserve">11.4657678604126</t>
@@ -4259,13 +4259,13 @@
     <t xml:space="preserve">11.7700815200806</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9418725967407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9026050567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0645799636841</t>
+    <t xml:space="preserve">11.9418716430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.902606010437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0645790100098</t>
   </si>
   <si>
     <t xml:space="preserve">12.1038455963135</t>
@@ -4280,10 +4280,10 @@
     <t xml:space="preserve">12.054762840271</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1627445220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9173316955566</t>
+    <t xml:space="preserve">12.162745475769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9173307418823</t>
   </si>
   <si>
     <t xml:space="preserve">11.9467802047729</t>
@@ -4307,7 +4307,7 @@
     <t xml:space="preserve">11.9369640350342</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9860467910767</t>
+    <t xml:space="preserve">11.9860458374023</t>
   </si>
   <si>
     <t xml:space="preserve">12.2314615249634</t>
@@ -4322,28 +4322,28 @@
     <t xml:space="preserve">12.467059135437</t>
   </si>
   <si>
-    <t xml:space="preserve">12.413067817688</t>
+    <t xml:space="preserve">12.4130687713623</t>
   </si>
   <si>
     <t xml:space="preserve">12.5701332092285</t>
   </si>
   <si>
-    <t xml:space="preserve">12.565224647522</t>
+    <t xml:space="preserve">12.5652256011963</t>
   </si>
   <si>
     <t xml:space="preserve">12.6633901596069</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6143083572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6241245269775</t>
+    <t xml:space="preserve">12.6143074035645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6241235733032</t>
   </si>
   <si>
     <t xml:space="preserve">12.2658185958862</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0596714019775</t>
+    <t xml:space="preserve">12.0596704483032</t>
   </si>
   <si>
     <t xml:space="preserve">12.0694875717163</t>
@@ -4367,16 +4367,16 @@
     <t xml:space="preserve">12.3050851821899</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3296279907227</t>
+    <t xml:space="preserve">12.3296270370483</t>
   </si>
   <si>
     <t xml:space="preserve">12.2216444015503</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1921949386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4376087188721</t>
+    <t xml:space="preserve">12.1921939849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4376096725464</t>
   </si>
   <si>
     <t xml:space="preserve">12.4228839874268</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">12.4866924285889</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6928405761719</t>
+    <t xml:space="preserve">12.6928415298462</t>
   </si>
   <si>
     <t xml:space="preserve">12.4817838668823</t>
@@ -4409,13 +4409,13 @@
     <t xml:space="preserve">12.0940284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9762296676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9124221801758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7946243286133</t>
+    <t xml:space="preserve">11.9762306213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9124231338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.794623374939</t>
   </si>
   <si>
     <t xml:space="preserve">11.8044395446777</t>
@@ -4424,7 +4424,7 @@
     <t xml:space="preserve">11.7995319366455</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8191652297974</t>
+    <t xml:space="preserve">11.819164276123</t>
   </si>
   <si>
     <t xml:space="preserve">11.8927888870239</t>
@@ -4436,7 +4436,7 @@
     <t xml:space="preserve">11.4461345672607</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3970518112183</t>
+    <t xml:space="preserve">11.3970508575439</t>
   </si>
   <si>
     <t xml:space="preserve">11.4706764221191</t>
@@ -4445,7 +4445,7 @@
     <t xml:space="preserve">11.3872356414795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5639333724976</t>
+    <t xml:space="preserve">11.5639324188232</t>
   </si>
   <si>
     <t xml:space="preserve">11.5835666656494</t>
@@ -4457,13 +4457,13 @@
     <t xml:space="preserve">11.9075136184692</t>
   </si>
   <si>
-    <t xml:space="preserve">12.000771522522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8486137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7749891281128</t>
+    <t xml:space="preserve">12.0007724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.848614692688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7749900817871</t>
   </si>
   <si>
     <t xml:space="preserve">11.8535223007202</t>
@@ -4475,10 +4475,10 @@
     <t xml:space="preserve">11.5344839096069</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6424655914307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1516370773315</t>
+    <t xml:space="preserve">11.642466545105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1516361236572</t>
   </si>
   <si>
     <t xml:space="preserve">11.1025543212891</t>
@@ -4490,10 +4490,10 @@
     <t xml:space="preserve">11.1712703704834</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2694358825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2841606140137</t>
+    <t xml:space="preserve">11.269434928894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.284161567688</t>
   </si>
   <si>
     <t xml:space="preserve">11.54430103302</t>
@@ -4502,7 +4502,7 @@
     <t xml:space="preserve">11.1909027099609</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0092973709106</t>
+    <t xml:space="preserve">11.0092964172363</t>
   </si>
   <si>
     <t xml:space="preserve">10.842414855957</t>
@@ -4511,7 +4511,7 @@
     <t xml:space="preserve">10.68044090271</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7687911987305</t>
+    <t xml:space="preserve">10.7687902450562</t>
   </si>
   <si>
     <t xml:space="preserve">10.9602136611938</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">10.9454879760742</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2547121047974</t>
+    <t xml:space="preserve">11.254711151123</t>
   </si>
   <si>
     <t xml:space="preserve">11.3087024688721</t>
@@ -4553,7 +4553,7 @@
     <t xml:space="preserve">10.7786064147949</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7393407821655</t>
+    <t xml:space="preserve">10.7393398284912</t>
   </si>
   <si>
     <t xml:space="preserve">10.7344331741333</t>
@@ -4562,13 +4562,13 @@
     <t xml:space="preserve">10.7246160507202</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7589740753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8865900039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8571405410767</t>
+    <t xml:space="preserve">10.7589731216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.886589050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8571395874023</t>
   </si>
   <si>
     <t xml:space="preserve">10.1208963394165</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">9.98346424102783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1945209503174</t>
+    <t xml:space="preserve">10.1945199966431</t>
   </si>
   <si>
     <t xml:space="preserve">10.2386951446533</t>
@@ -4589,7 +4589,7 @@
     <t xml:space="preserve">10.48410987854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5871839523315</t>
+    <t xml:space="preserve">10.5871829986572</t>
   </si>
   <si>
     <t xml:space="preserve">10.5381002426147</t>
@@ -4598,22 +4598,22 @@
     <t xml:space="preserve">10.7295246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7000732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3466777801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2877769470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4055767059326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3270454406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0669050216675</t>
+    <t xml:space="preserve">10.7000741958618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3466768264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2877779006958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4055776596069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3270444869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0669040679932</t>
   </si>
   <si>
     <t xml:space="preserve">10.086537361145</t>
@@ -4637,13 +4637,13 @@
     <t xml:space="preserve">9.75375556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83621597290039</t>
+    <t xml:space="preserve">9.83621501922607</t>
   </si>
   <si>
     <t xml:space="preserve">9.83130741119385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86075687408447</t>
+    <t xml:space="preserve">9.86075592041016</t>
   </si>
   <si>
     <t xml:space="preserve">9.90493106842041</t>
@@ -4667,7 +4667,7 @@
     <t xml:space="preserve">9.8263988494873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91474723815918</t>
+    <t xml:space="preserve">9.9147481918335</t>
   </si>
   <si>
     <t xml:space="preserve">9.96382999420166</t>
@@ -4685,19 +4685,19 @@
     <t xml:space="preserve">10.0276384353638</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89020538330078</t>
+    <t xml:space="preserve">9.8902063369751</t>
   </si>
   <si>
     <t xml:space="preserve">9.76357269287109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8656644821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76553630828857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74001312255859</t>
+    <t xml:space="preserve">9.86566543579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76553535461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74001216888428</t>
   </si>
   <si>
     <t xml:space="preserve">9.74393844604492</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">9.10782432556152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15494537353516</t>
+    <t xml:space="preserve">9.15494441986084</t>
   </si>
   <si>
     <t xml:space="preserve">9.14905452728271</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">9.00769519805908</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08033847808838</t>
+    <t xml:space="preserve">9.08033752441406</t>
   </si>
   <si>
     <t xml:space="preserve">9.06463146209717</t>
@@ -4736,19 +4736,19 @@
     <t xml:space="preserve">8.85455799102783</t>
   </si>
   <si>
-    <t xml:space="preserve">8.81528949737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29630374908447</t>
+    <t xml:space="preserve">8.8152904510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29630279541016</t>
   </si>
   <si>
     <t xml:space="preserve">9.22758674621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23740291595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21580696105957</t>
+    <t xml:space="preserve">9.23740386962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21580600738525</t>
   </si>
   <si>
     <t xml:space="preserve">9.37090873718262</t>
@@ -4772,19 +4772,19 @@
     <t xml:space="preserve">9.61043357849121</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56527805328369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76749801635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78909587860107</t>
+    <t xml:space="preserve">9.56527709960938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76749897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78909492492676</t>
   </si>
   <si>
     <t xml:space="preserve">9.63988304138184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63792037963867</t>
+    <t xml:space="preserve">9.63791942596436</t>
   </si>
   <si>
     <t xml:space="preserve">9.6909294128418</t>
@@ -4796,16 +4796,16 @@
     <t xml:space="preserve">9.59080123901367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38072490692139</t>
+    <t xml:space="preserve">9.3807258605957</t>
   </si>
   <si>
     <t xml:space="preserve">9.65559005737305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32967853546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20010089874268</t>
+    <t xml:space="preserve">9.32967948913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20009994506836</t>
   </si>
   <si>
     <t xml:space="preserve">9.30023002624512</t>
@@ -4826,7 +4826,7 @@
     <t xml:space="preserve">9.36109256744385</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40232181549072</t>
+    <t xml:space="preserve">9.40232276916504</t>
   </si>
   <si>
     <t xml:space="preserve">9.39054203033447</t>
@@ -4835,7 +4835,7 @@
     <t xml:space="preserve">9.47300148010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47103881835938</t>
+    <t xml:space="preserve">9.47103786468506</t>
   </si>
   <si>
     <t xml:space="preserve">9.37876224517822</t>
@@ -4844,7 +4844,7 @@
     <t xml:space="preserve">9.27667045593262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08426380157471</t>
+    <t xml:space="preserve">9.08426475524902</t>
   </si>
   <si>
     <t xml:space="preserve">9.1254940032959</t>
@@ -4862,7 +4862,7 @@
     <t xml:space="preserve">9.06855869293213</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14316463470459</t>
+    <t xml:space="preserve">9.14316368103027</t>
   </si>
   <si>
     <t xml:space="preserve">9.00573253631592</t>
@@ -4871,7 +4871,7 @@
     <t xml:space="preserve">8.89382362365723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02340221405029</t>
+    <t xml:space="preserve">9.02340316772461</t>
   </si>
   <si>
     <t xml:space="preserve">8.92523670196533</t>
@@ -4883,7 +4883,7 @@
     <t xml:space="preserve">8.92327308654785</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88400745391846</t>
+    <t xml:space="preserve">8.88400650024414</t>
   </si>
   <si>
     <t xml:space="preserve">8.80743789672852</t>
@@ -4892,7 +4892,7 @@
     <t xml:space="preserve">8.73479461669922</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76817035675049</t>
+    <t xml:space="preserve">8.7681713104248</t>
   </si>
   <si>
     <t xml:space="preserve">8.77995109558105</t>
@@ -4901,10 +4901,10 @@
     <t xml:space="preserve">8.9821720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21187973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3021936416626</t>
+    <t xml:space="preserve">9.21188068389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30219268798828</t>
   </si>
   <si>
     <t xml:space="preserve">9.42377090454102</t>
@@ -5976,6 +5976,9 @@
   </si>
   <si>
     <t xml:space="preserve">5.40999984741211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.36399984359741</t>
   </si>
 </sst>
 </file>
@@ -71678,7 +71681,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6923148148</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>4255004</v>
@@ -71699,6 +71702,32 @@
         <v>1987</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6914583333</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>7418523</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>5.46799993515015</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>5.32800006866455</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>5.44000005722046</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>5.36399984359741</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>1988</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CPR.MI.xlsx
+++ b/data/CPR.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="1989">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1990" uniqueCount="1990">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59865641593933</t>
+    <t xml:space="preserve">3.59865665435791</t>
   </si>
   <si>
     <t xml:space="preserve">CPR.MI</t>
@@ -56,25 +56,25 @@
     <t xml:space="preserve">3.51048851013184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54993224143982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62881970405579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68450474739075</t>
+    <t xml:space="preserve">3.54993200302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62881946563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68450450897217</t>
   </si>
   <si>
     <t xml:space="preserve">3.57313418388367</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52672958374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48264575004578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5661735534668</t>
+    <t xml:space="preserve">3.52672982215881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4826455116272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56617331504822</t>
   </si>
   <si>
     <t xml:space="preserve">3.43392133712769</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">3.50584745407104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56153345108032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64274096488953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66594314575195</t>
+    <t xml:space="preserve">3.56153321266174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64274072647095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66594290733337</t>
   </si>
   <si>
     <t xml:space="preserve">3.56849408149719</t>
@@ -98,22 +98,22 @@
     <t xml:space="preserve">3.74250984191895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72162842750549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70770692825317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47104454040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44320201873779</t>
+    <t xml:space="preserve">3.72162818908691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70770645141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47104477882385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44320225715637</t>
   </si>
   <si>
     <t xml:space="preserve">3.28078675270081</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33183121681213</t>
+    <t xml:space="preserve">3.33183193206787</t>
   </si>
   <si>
     <t xml:space="preserve">3.40839862823486</t>
@@ -125,22 +125,22 @@
     <t xml:space="preserve">3.26918578147888</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32487082481384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2436637878418</t>
+    <t xml:space="preserve">3.324871301651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24366307258606</t>
   </si>
   <si>
     <t xml:space="preserve">3.32255077362061</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28774762153625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31791019439697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36663460731506</t>
+    <t xml:space="preserve">3.28774785995483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31791043281555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36663484573364</t>
   </si>
   <si>
     <t xml:space="preserve">3.36199426651001</t>
@@ -149,70 +149,70 @@
     <t xml:space="preserve">3.40607881546021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38287663459778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36431455612183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53137063980103</t>
+    <t xml:space="preserve">3.3828763961792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36431479454041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53137040138245</t>
   </si>
   <si>
     <t xml:space="preserve">3.60561728477478</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61257791519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56385350227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61489820480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63809990882874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68914484977722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87476277351379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95596981048584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00701475143433</t>
+    <t xml:space="preserve">3.61257767677307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56385374069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61489796638489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63810014724731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6891450881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87476301193237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95597004890442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00701522827148</t>
   </si>
   <si>
     <t xml:space="preserve">4.04877853393555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03485822677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04181814193726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03717756271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05109786987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01861619949341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09286260604858</t>
+    <t xml:space="preserve">4.03485727310181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0418176651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03717708587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05109882354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01861572265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0928635597229</t>
   </si>
   <si>
     <t xml:space="preserve">4.07662153244019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03949785232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08358192443848</t>
+    <t xml:space="preserve">4.0394983291626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08358240127563</t>
   </si>
   <si>
     <t xml:space="preserve">4.02325630187988</t>
@@ -221,106 +221,106 @@
     <t xml:space="preserve">4.00005435943604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06037950515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99541330337524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94436812400818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97453188896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00237417221069</t>
+    <t xml:space="preserve">4.06037998199463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99541306495667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9443690776825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97453212738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00237369537354</t>
   </si>
   <si>
     <t xml:space="preserve">3.9374086856842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94669008255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03021717071533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05341863632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00933456420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9582896232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98613333702087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0255765914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96989154815674</t>
+    <t xml:space="preserve">3.94668984413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03021669387817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05341911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00933504104614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95828986167908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98613262176514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02557706832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96989178657532</t>
   </si>
   <si>
     <t xml:space="preserve">3.91188621520996</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89796495437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87708234786987</t>
+    <t xml:space="preserve">3.89796423912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87708210945129</t>
   </si>
   <si>
     <t xml:space="preserve">3.91420650482178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92812705039978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95132946968079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06734085083008</t>
+    <t xml:space="preserve">3.92812728881836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95132970809937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06733989715576</t>
   </si>
   <si>
     <t xml:space="preserve">4.08126163482666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99309325218201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96757125854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98149275779724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96293091773987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88868427276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89332389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79587554931641</t>
+    <t xml:space="preserve">3.99309372901917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96757173538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98149132728577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96293044090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88868403434753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89332485198975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79587507247925</t>
   </si>
   <si>
     <t xml:space="preserve">3.89309883117676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02677774429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08540868759155</t>
+    <t xml:space="preserve">4.02677726745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08540821075439</t>
   </si>
   <si>
     <t xml:space="preserve">4.07602739334106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08306360244751</t>
+    <t xml:space="preserve">4.08306312561035</t>
   </si>
   <si>
     <t xml:space="preserve">4.09948015213013</t>
@@ -329,10 +329,10 @@
     <t xml:space="preserve">4.07368230819702</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09009981155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10182571411133</t>
+    <t xml:space="preserve">4.0900993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10182523727417</t>
   </si>
   <si>
     <t xml:space="preserve">4.0877537727356</t>
@@ -341,25 +341,25 @@
     <t xml:space="preserve">4.11355113983154</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08071804046631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01974153518677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90482544898987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85557532310486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85792088508606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86495590209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87199211120605</t>
+    <t xml:space="preserve">4.08071851730347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01974201202393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90482497215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85557508468628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8579204082489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86495566368103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8719916343689</t>
   </si>
   <si>
     <t xml:space="preserve">3.8696460723877</t>
@@ -368,25 +368,25 @@
     <t xml:space="preserve">4.00567054748535</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00801563262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95876574516296</t>
+    <t xml:space="preserve">4.00801658630371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95876526832581</t>
   </si>
   <si>
     <t xml:space="preserve">4.05961036682129</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88606309890747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88840842247009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04084873199463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16514682769775</t>
+    <t xml:space="preserve">3.88606286048889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88840866088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04084920883179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1651463508606</t>
   </si>
   <si>
     <t xml:space="preserve">4.15576553344727</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">4.16045618057251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15811014175415</t>
+    <t xml:space="preserve">4.15811157226562</t>
   </si>
   <si>
     <t xml:space="preserve">4.11589670181274</t>
@@ -419,19 +419,19 @@
     <t xml:space="preserve">4.1346583366394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14169502258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18390941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16280126571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21908712387085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29179000854492</t>
+    <t xml:space="preserve">4.14169454574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18390846252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16280221939087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21908664703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29178953170776</t>
   </si>
   <si>
     <t xml:space="preserve">4.29648017883301</t>
@@ -443,58 +443,58 @@
     <t xml:space="preserve">4.28709936141968</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3316593170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33869457244873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54038524627686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51458787918091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52162408828735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43719530105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47940969467163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45595645904541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66233730316162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67171955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58963537216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55914688110352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56383752822876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54976654052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60370635986328</t>
+    <t xml:space="preserve">4.33165884017944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33869504928589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54038572311401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51458740234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52162265777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43719482421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47940874099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45595693588257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66233777999878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67171907424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58963489532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55914735794067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56383800506592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54976558685303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60370683670044</t>
   </si>
   <si>
     <t xml:space="preserve">4.59667110443115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6201229095459</t>
+    <t xml:space="preserve">4.57321882247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62012386322021</t>
   </si>
   <si>
     <t xml:space="preserve">4.59432601928711</t>
@@ -503,115 +503,115 @@
     <t xml:space="preserve">4.65061187744141</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57556438446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70455169677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67406463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70924234390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60136222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48644495010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46533727645874</t>
+    <t xml:space="preserve">4.57556390762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7045521736145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67406415939331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70924186706543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6013617515564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48644399642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4653377532959</t>
   </si>
   <si>
     <t xml:space="preserve">4.39967060089111</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43250370025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50520610809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.491135597229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51693296432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50286197662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48879051208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65295648574829</t>
+    <t xml:space="preserve">4.43250465393066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50520706176758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49113512039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51693248748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50286149978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48878908157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65295696258545</t>
   </si>
   <si>
     <t xml:space="preserve">4.66468334197998</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73269557952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71393394470215</t>
+    <t xml:space="preserve">4.73269462585449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71393299102783</t>
   </si>
   <si>
     <t xml:space="preserve">4.69048023223877</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58728981018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56852769851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47471809387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44657516479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54742050170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44188499450684</t>
+    <t xml:space="preserve">4.58729028701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56852722167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47471904754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44657564163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54742097854614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44188547134399</t>
   </si>
   <si>
     <t xml:space="preserve">4.50051641464233</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52631330490112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36683750152588</t>
+    <t xml:space="preserve">4.52631425857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36683797836304</t>
   </si>
   <si>
     <t xml:space="preserve">4.37152814865112</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33400392532349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3293137550354</t>
+    <t xml:space="preserve">4.33400344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32931280136108</t>
   </si>
   <si>
     <t xml:space="preserve">4.30586099624634</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30351591110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25661134719849</t>
+    <t xml:space="preserve">4.30351638793945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25661039352417</t>
   </si>
   <si>
     <t xml:space="preserve">4.20736122131348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09478902816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24253988265991</t>
+    <t xml:space="preserve">4.09478950500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24254035949707</t>
   </si>
   <si>
     <t xml:space="preserve">4.20267105102539</t>
@@ -620,43 +620,43 @@
     <t xml:space="preserve">3.9564208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95407557487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0338134765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12527751922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01739692687988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12996816635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17218255996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2120509147644</t>
+    <t xml:space="preserve">3.95407605171204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03381299972534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12527704238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01739645004272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12996864318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1721830368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21205139160156</t>
   </si>
   <si>
     <t xml:space="preserve">4.18859958648682</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24957656860352</t>
+    <t xml:space="preserve">4.24957513809204</t>
   </si>
   <si>
     <t xml:space="preserve">4.20501613616943</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26833820343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22846841812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24723052978516</t>
+    <t xml:space="preserve">4.26833724975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22846937179565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.247230052948</t>
   </si>
   <si>
     <t xml:space="preserve">4.31993246078491</t>
@@ -668,34 +668,34 @@
     <t xml:space="preserve">4.28944492340088</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27771806716919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30117082595825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32227849960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35745620727539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34807586669922</t>
+    <t xml:space="preserve">4.27771759033203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30117034912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32227802276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35745573043823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34807634353638</t>
   </si>
   <si>
     <t xml:space="preserve">4.34338521957397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39028930664062</t>
+    <t xml:space="preserve">4.39029026031494</t>
   </si>
   <si>
     <t xml:space="preserve">4.36214733123779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32462310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39732551574707</t>
+    <t xml:space="preserve">4.32462358474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39732599258423</t>
   </si>
   <si>
     <t xml:space="preserve">4.37387323379517</t>
@@ -704,55 +704,55 @@
     <t xml:space="preserve">4.36918258666992</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47002792358398</t>
+    <t xml:space="preserve">4.47002840042114</t>
   </si>
   <si>
     <t xml:space="preserve">4.45830202102661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42546892166138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43484973907471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46768236160278</t>
+    <t xml:space="preserve">4.42546939849854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43484878540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46768283843994</t>
   </si>
   <si>
     <t xml:space="preserve">4.40201663970947</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3527660369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3855996131897</t>
+    <t xml:space="preserve">4.35276651382446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38559913635254</t>
   </si>
   <si>
     <t xml:space="preserve">4.43954038619995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43015956878662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49348115921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47237348556519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52396869659424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54273080825806</t>
+    <t xml:space="preserve">4.43015909194946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49348020553589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47237396240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52396821975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5427303314209</t>
   </si>
   <si>
     <t xml:space="preserve">4.53803968429565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5450758934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58260011672974</t>
+    <t xml:space="preserve">4.54507541656494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58259963989258</t>
   </si>
   <si>
     <t xml:space="preserve">4.57790899276733</t>
@@ -761,31 +761,31 @@
     <t xml:space="preserve">4.55211114883423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57087326049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53569507598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50755214691162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58494472503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65530252456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74207592010498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75614786148071</t>
+    <t xml:space="preserve">4.57087373733521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53569459915161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5075511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58494520187378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65530157089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74207544326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75614738464355</t>
   </si>
   <si>
     <t xml:space="preserve">4.80774307250977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83119487762451</t>
+    <t xml:space="preserve">4.83119535446167</t>
   </si>
   <si>
     <t xml:space="preserve">4.89686155319214</t>
@@ -794,34 +794,34 @@
     <t xml:space="preserve">4.94845771789551</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09855175018311</t>
+    <t xml:space="preserve">5.09855222702026</t>
   </si>
   <si>
     <t xml:space="preserve">5.05164813995361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12200546264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04695749282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05633783340454</t>
+    <t xml:space="preserve">5.12200498580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04695701599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0563383102417</t>
   </si>
   <si>
     <t xml:space="preserve">4.99536180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01881456375122</t>
+    <t xml:space="preserve">5.01881408691406</t>
   </si>
   <si>
     <t xml:space="preserve">5.02819585800171</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03288555145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93907499313354</t>
+    <t xml:space="preserve">5.03288507461548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93907594680786</t>
   </si>
   <si>
     <t xml:space="preserve">4.9766001701355</t>
@@ -830,55 +830,55 @@
     <t xml:space="preserve">4.92500495910645</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96722030639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08917188644409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17359924316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14545726776123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15952825546265</t>
+    <t xml:space="preserve">4.96721887588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08917140960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17359972000122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14545774459839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15952920913696</t>
   </si>
   <si>
     <t xml:space="preserve">5.09386205673218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16421890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25333833694458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18767261505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.41750574111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6707911491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60043478012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.62388515472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66141080856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68486213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57698202133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.60512447357178</t>
+    <t xml:space="preserve">5.16421937942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25333786010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18767213821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.41750478744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67079067230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60043430328369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.62388610839844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66141033172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68486261367798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57698154449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.60512495040894</t>
   </si>
   <si>
     <t xml:space="preserve">5.7223858833313</t>
@@ -890,142 +890,142 @@
     <t xml:space="preserve">5.74128770828247</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76491403579712</t>
+    <t xml:space="preserve">5.76491451263428</t>
   </si>
   <si>
     <t xml:space="preserve">5.75073862075806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.87832260131836</t>
+    <t xml:space="preserve">5.87832164764404</t>
   </si>
   <si>
     <t xml:space="preserve">5.86887216567993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88304758071899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02008199691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9917311668396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00118064880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.93502616882324</t>
+    <t xml:space="preserve">5.88304805755615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02008295059204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99173069000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00118160247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.93502712249756</t>
   </si>
   <si>
     <t xml:space="preserve">5.85942125320435</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80271673202515</t>
+    <t xml:space="preserve">5.8027172088623</t>
   </si>
   <si>
     <t xml:space="preserve">5.75546360015869</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7318377494812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.84997034072876</t>
+    <t xml:space="preserve">5.73183727264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.84997129440308</t>
   </si>
   <si>
     <t xml:space="preserve">5.81216812133789</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95865297317505</t>
+    <t xml:space="preserve">5.95865345001221</t>
   </si>
   <si>
     <t xml:space="preserve">5.93030118942261</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98227977752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90194988250732</t>
+    <t xml:space="preserve">5.9822793006897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90194845199585</t>
   </si>
   <si>
     <t xml:space="preserve">5.91612529754639</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91140031814575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.83106899261475</t>
+    <t xml:space="preserve">5.91139936447144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8310694694519</t>
   </si>
   <si>
     <t xml:space="preserve">5.88777303695679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.78381633758545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80744171142578</t>
+    <t xml:space="preserve">5.78381538391113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80744218826294</t>
   </si>
   <si>
     <t xml:space="preserve">5.84524536132812</t>
   </si>
   <si>
-    <t xml:space="preserve">5.77436590194702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82634401321411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82161808013916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85469579696655</t>
+    <t xml:space="preserve">5.77436447143555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82634353637695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.821617603302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85469627380371</t>
   </si>
   <si>
     <t xml:space="preserve">5.79326677322388</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8357949256897</t>
+    <t xml:space="preserve">5.83579540252686</t>
   </si>
   <si>
     <t xml:space="preserve">5.95392847061157</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92557621002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94447755813599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.77908992767334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.74601268768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.71766138076782</t>
+    <t xml:space="preserve">5.92557573318481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94447660446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7790904045105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.74601316452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.71766090393066</t>
   </si>
   <si>
     <t xml:space="preserve">5.65150594711304</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66095638275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79799127578735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76018857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69876003265381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66568183898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73656272888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.78854084014893</t>
+    <t xml:space="preserve">5.66095685958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79799175262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76018905639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69875955581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66568231582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73656177520752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.78854036331177</t>
   </si>
   <si>
     <t xml:space="preserve">5.76963996887207</t>
@@ -1037,49 +1037,49 @@
     <t xml:space="preserve">5.97282981872559</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15239286422729</t>
+    <t xml:space="preserve">6.15239238739014</t>
   </si>
   <si>
     <t xml:space="preserve">6.14766693115234</t>
   </si>
   <si>
-    <t xml:space="preserve">6.28470230102539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13821506500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12404012680054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.02953386306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10513830184937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.16656923294067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11458969116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.31777954101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34140539169312</t>
+    <t xml:space="preserve">6.28470134735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13821601867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1240406036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.02953338623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10513877868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.16656875610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11458921432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.31777906417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34140586853027</t>
   </si>
   <si>
     <t xml:space="preserve">6.4075608253479</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50206708908081</t>
+    <t xml:space="preserve">6.50206756591797</t>
   </si>
   <si>
     <t xml:space="preserve">6.42173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">6.30832862854004</t>
+    <t xml:space="preserve">6.30832815170288</t>
   </si>
   <si>
     <t xml:space="preserve">6.47844076156616</t>
@@ -1088,28 +1088,28 @@
     <t xml:space="preserve">6.31305360794067</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33668041229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.37448263168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17601871490479</t>
+    <t xml:space="preserve">6.33668088912964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.37448310852051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17601919174194</t>
   </si>
   <si>
     <t xml:space="preserve">6.0909628868103</t>
   </si>
   <si>
-    <t xml:space="preserve">6.23272228240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03898429870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08623695373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10041379928589</t>
+    <t xml:space="preserve">6.23272275924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03898477554321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.08623743057251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10041332244873</t>
   </si>
   <si>
     <t xml:space="preserve">6.10986423492432</t>
@@ -1121,67 +1121,67 @@
     <t xml:space="preserve">6.0342583656311</t>
   </si>
   <si>
-    <t xml:space="preserve">6.09568738937378</t>
+    <t xml:space="preserve">6.0956883430481</t>
   </si>
   <si>
     <t xml:space="preserve">6.06261157989502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.18074417114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.08151245117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15711736679077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.21382093429565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24217414855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24689865112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20909643173218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.22799777984619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19964647293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12876510620117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07206201553345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.05788564682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.13349103927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.14294099807739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01063203811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.94920253753662</t>
+    <t xml:space="preserve">6.18074464797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0815110206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15711784362793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.21382141113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24217367172241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24689912796021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20909690856934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.22799825668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19964551925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12876605987549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07206153869629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.05788516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.13349056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.14294195175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01063251495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.94920301437378</t>
   </si>
   <si>
     <t xml:space="preserve">5.97755432128906</t>
   </si>
   <si>
-    <t xml:space="preserve">6.05316019058228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.99645614624023</t>
+    <t xml:space="preserve">6.05316066741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.99645566940308</t>
   </si>
   <si>
     <t xml:space="preserve">6.06733560562134</t>
@@ -1190,10 +1190,10 @@
     <t xml:space="preserve">5.93975162506104</t>
   </si>
   <si>
-    <t xml:space="preserve">5.71293544769287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72711133956909</t>
+    <t xml:space="preserve">5.71293592453003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72711181640625</t>
   </si>
   <si>
     <t xml:space="preserve">5.92085075378418</t>
@@ -1202,7 +1202,7 @@
     <t xml:space="preserve">5.57590103149414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.52864742279053</t>
+    <t xml:space="preserve">5.52864694595337</t>
   </si>
   <si>
     <t xml:space="preserve">5.42941522598267</t>
@@ -1214,22 +1214,22 @@
     <t xml:space="preserve">5.61370372772217</t>
   </si>
   <si>
-    <t xml:space="preserve">5.63733005523682</t>
+    <t xml:space="preserve">5.63733053207397</t>
   </si>
   <si>
     <t xml:space="preserve">6.04370975494385</t>
   </si>
   <si>
-    <t xml:space="preserve">5.98700571060181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01535654067993</t>
+    <t xml:space="preserve">5.98700523376465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01535701751709</t>
   </si>
   <si>
     <t xml:space="preserve">5.89722394943237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81689405441284</t>
+    <t xml:space="preserve">5.81689310073853</t>
   </si>
   <si>
     <t xml:space="preserve">5.87359714508057</t>
@@ -1241,22 +1241,22 @@
     <t xml:space="preserve">5.9066743850708</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96810340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.01550722122192</t>
+    <t xml:space="preserve">5.96810436248779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.01550769805908</t>
   </si>
   <si>
     <t xml:space="preserve">6.02027082443237</t>
   </si>
   <si>
-    <t xml:space="preserve">5.99169397354126</t>
+    <t xml:space="preserve">5.99169301986694</t>
   </si>
   <si>
     <t xml:space="preserve">6.08218765258789</t>
   </si>
   <si>
-    <t xml:space="preserve">6.2060227394104</t>
+    <t xml:space="preserve">6.20602226257324</t>
   </si>
   <si>
     <t xml:space="preserve">6.18697023391724</t>
@@ -1265,19 +1265,19 @@
     <t xml:space="preserve">6.08695030212402</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07266187667847</t>
+    <t xml:space="preserve">6.07266139984131</t>
   </si>
   <si>
     <t xml:space="preserve">6.16315650939941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.27270221710205</t>
+    <t xml:space="preserve">6.27270317077637</t>
   </si>
   <si>
     <t xml:space="preserve">6.25365114212036</t>
   </si>
   <si>
-    <t xml:space="preserve">6.13934230804443</t>
+    <t xml:space="preserve">6.13934278488159</t>
   </si>
   <si>
     <t xml:space="preserve">6.2917537689209</t>
@@ -1286,22 +1286,22 @@
     <t xml:space="preserve">6.38701152801514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5251350402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5965781211853</t>
+    <t xml:space="preserve">6.52513456344604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59657859802246</t>
   </si>
   <si>
     <t xml:space="preserve">6.69183540344238</t>
   </si>
   <si>
-    <t xml:space="preserve">6.69659805297852</t>
+    <t xml:space="preserve">6.69659852981567</t>
   </si>
   <si>
     <t xml:space="preserve">6.62039184570312</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57276439666748</t>
+    <t xml:space="preserve">6.57276296615601</t>
   </si>
   <si>
     <t xml:space="preserve">6.5060830116272</t>
@@ -1313,37 +1313,37 @@
     <t xml:space="preserve">6.65373277664185</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71088647842407</t>
+    <t xml:space="preserve">6.71088743209839</t>
   </si>
   <si>
     <t xml:space="preserve">6.8251953125</t>
   </si>
   <si>
-    <t xml:space="preserve">6.77280473709106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.82995939254761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02523565292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92521619796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92045259475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01094770431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9680814743042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.91092729568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01570987701416</t>
+    <t xml:space="preserve">6.77280378341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.82995843887329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0252366065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92521572113037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9204535484314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01094722747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.96808195114136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.91092777252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01571035385132</t>
   </si>
   <si>
     <t xml:space="preserve">7.04905080795288</t>
@@ -1352,40 +1352,40 @@
     <t xml:space="preserve">7.09667921066284</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17764854431152</t>
+    <t xml:space="preserve">7.17764806747437</t>
   </si>
   <si>
     <t xml:space="preserve">7.28243160247803</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22051429748535</t>
+    <t xml:space="preserve">7.22051382064819</t>
   </si>
   <si>
     <t xml:space="preserve">7.2395658493042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27766895294189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.12525606155396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94903087615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86806154251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00142192840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00618457794189</t>
+    <t xml:space="preserve">7.27766799926758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.12525701522827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94903039932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86806201934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00142240524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00618505477905</t>
   </si>
   <si>
     <t xml:space="preserve">7.06333923339844</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97760772705078</t>
+    <t xml:space="preserve">6.97760725021362</t>
   </si>
   <si>
     <t xml:space="preserve">6.9918966293335</t>
@@ -1394,19 +1394,19 @@
     <t xml:space="preserve">7.03952503204346</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02047300338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.07762813568115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.18717384338379</t>
+    <t xml:space="preserve">7.02047395706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.07762718200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.18717336654663</t>
   </si>
   <si>
     <t xml:space="preserve">7.21098852157593</t>
   </si>
   <si>
-    <t xml:space="preserve">7.4157919883728</t>
+    <t xml:space="preserve">7.41579246520996</t>
   </si>
   <si>
     <t xml:space="preserve">7.29672002792358</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">7.26337957382202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.24432802200317</t>
+    <t xml:space="preserve">7.24432849884033</t>
   </si>
   <si>
     <t xml:space="preserve">7.27290630340576</t>
@@ -1433,19 +1433,19 @@
     <t xml:space="preserve">7.0585765838623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.10620498657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.14907121658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1681227684021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90140151977539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94426774978638</t>
+    <t xml:space="preserve">7.10620546340942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.14907073974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16812181472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90140199661255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94426727294922</t>
   </si>
   <si>
     <t xml:space="preserve">7.06810188293457</t>
@@ -1463,7 +1463,7 @@
     <t xml:space="preserve">6.70612382888794</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63944339752197</t>
+    <t xml:space="preserve">6.63944292068481</t>
   </si>
   <si>
     <t xml:space="preserve">6.65849494934082</t>
@@ -1472,10 +1472,10 @@
     <t xml:space="preserve">6.32985734939575</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19649648666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11552762985229</t>
+    <t xml:space="preserve">6.19649696350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11552810668945</t>
   </si>
   <si>
     <t xml:space="preserve">6.04884767532349</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">6.21554803848267</t>
   </si>
   <si>
-    <t xml:space="preserve">6.31556749343872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3346209526062</t>
+    <t xml:space="preserve">6.31556844711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33461952209473</t>
   </si>
   <si>
     <t xml:space="preserve">6.34414577484131</t>
@@ -1496,58 +1496,58 @@
     <t xml:space="preserve">6.12505340576172</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15363121032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3060417175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35367202758789</t>
+    <t xml:space="preserve">6.15363073348999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.30604267120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35367155075073</t>
   </si>
   <si>
     <t xml:space="preserve">6.47274351119995</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46798038482666</t>
+    <t xml:space="preserve">6.4679799079895</t>
   </si>
   <si>
     <t xml:space="preserve">6.42987775802612</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52989816665649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76804113388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08239030838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1109676361084</t>
+    <t xml:space="preserve">6.52989768981934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76804208755493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08239078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11096811294556</t>
   </si>
   <si>
     <t xml:space="preserve">7.12049388885498</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32529735565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31577110290527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11573028564453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03476285934448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15383434295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04428815841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02999925613403</t>
+    <t xml:space="preserve">7.32529783248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31577157974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11573076248169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03476238250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15383386611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04428720474243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02999973297119</t>
   </si>
   <si>
     <t xml:space="preserve">7.17288589477539</t>
@@ -1556,28 +1556,28 @@
     <t xml:space="preserve">7.36339998245239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14430809020996</t>
+    <t xml:space="preserve">7.1443076133728</t>
   </si>
   <si>
     <t xml:space="preserve">7.20622587203979</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32053518295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09191656112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98236989974976</t>
+    <t xml:space="preserve">7.32053375244141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09191703796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98237037658691</t>
   </si>
   <si>
     <t xml:space="preserve">7.44913244247437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3824520111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.33006000518799</t>
+    <t xml:space="preserve">7.38245248794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.33006048202515</t>
   </si>
   <si>
     <t xml:space="preserve">7.21575117111206</t>
@@ -1601,22 +1601,22 @@
     <t xml:space="preserve">7.49199724197388</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44436836242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42055511474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62535905838013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53010082244873</t>
+    <t xml:space="preserve">7.44436931610107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42055463790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62535762786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53010129928589</t>
   </si>
   <si>
     <t xml:space="preserve">7.47294569015503</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48723411560059</t>
+    <t xml:space="preserve">7.4872350692749</t>
   </si>
   <si>
     <t xml:space="preserve">7.4681830406189</t>
@@ -1625,7 +1625,7 @@
     <t xml:space="preserve">7.49676084518433</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51581192016602</t>
+    <t xml:space="preserve">7.51581239700317</t>
   </si>
   <si>
     <t xml:space="preserve">7.61106967926025</t>
@@ -1634,58 +1634,58 @@
     <t xml:space="preserve">7.56344127655029</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64441013336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73490333557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80634737014771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86826467514038</t>
+    <t xml:space="preserve">7.6444091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73490381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80634689331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86826515197754</t>
   </si>
   <si>
     <t xml:space="preserve">7.85873889923096</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88731527328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92541885375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95399713516235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83492565155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98733568191528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.01115036010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06354331970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53486299514771</t>
+    <t xml:space="preserve">7.88731575012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92541790008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9539966583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83492422103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98733711242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.01115226745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06354236602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53486394882202</t>
   </si>
   <si>
     <t xml:space="preserve">7.52057504653931</t>
   </si>
   <si>
-    <t xml:space="preserve">7.54438924789429</t>
+    <t xml:space="preserve">7.54438972473145</t>
   </si>
   <si>
     <t xml:space="preserve">7.62059545516968</t>
   </si>
   <si>
-    <t xml:space="preserve">7.63964796066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77776956558228</t>
+    <t xml:space="preserve">7.63964700698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77777051925659</t>
   </si>
   <si>
     <t xml:space="preserve">7.76824426651001</t>
@@ -1694,16 +1694,16 @@
     <t xml:space="preserve">7.90636730194092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03496551513672</t>
+    <t xml:space="preserve">8.03496646881104</t>
   </si>
   <si>
     <t xml:space="preserve">8.00638866424561</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04449081420898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06830596923828</t>
+    <t xml:space="preserve">8.0444917678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06830501556396</t>
   </si>
   <si>
     <t xml:space="preserve">8.20166492462158</t>
@@ -1715,16 +1715,16 @@
     <t xml:space="preserve">8.44457244873047</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33978843688965</t>
+    <t xml:space="preserve">8.33978939056396</t>
   </si>
   <si>
     <t xml:space="preserve">8.38265419006348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3350248336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27787113189697</t>
+    <t xml:space="preserve">8.33502578735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27787208557129</t>
   </si>
   <si>
     <t xml:space="preserve">8.23500537872314</t>
@@ -1733,19 +1733,19 @@
     <t xml:space="preserve">8.25882053375244</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26358318328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.16832637786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.31121158599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36836624145508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35407733917236</t>
+    <t xml:space="preserve">8.26358413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.16832447052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.31121253967285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36836528778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.354079246521</t>
   </si>
   <si>
     <t xml:space="preserve">8.37789249420166</t>
@@ -1754,64 +1754,64 @@
     <t xml:space="preserve">8.28739738464355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21119117736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22071743011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43150329589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.445876121521</t>
+    <t xml:space="preserve">8.21119213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22071838378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43150520324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44587707519531</t>
   </si>
   <si>
     <t xml:space="preserve">8.56085300445557</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51294612884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48899269104004</t>
+    <t xml:space="preserve">8.5129451751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48899078369141</t>
   </si>
   <si>
     <t xml:space="preserve">8.60875797271729</t>
   </si>
   <si>
-    <t xml:space="preserve">8.441086769104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49857330322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48420143127441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67103672027588</t>
+    <t xml:space="preserve">8.44108772277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49857425689697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48420238494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67103576660156</t>
   </si>
   <si>
     <t xml:space="preserve">8.8147554397583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.74289512634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83391666412354</t>
+    <t xml:space="preserve">8.74289608001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83391761779785</t>
   </si>
   <si>
     <t xml:space="preserve">8.77642917633057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70936012268066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6854076385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70456981658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78122138977051</t>
+    <t xml:space="preserve">8.70936107635498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68540859222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70457172393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78122043609619</t>
   </si>
   <si>
     <t xml:space="preserve">8.80996417999268</t>
@@ -1820,19 +1820,19 @@
     <t xml:space="preserve">8.77163887023926</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65187454223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53689861297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.37880802154541</t>
+    <t xml:space="preserve">8.65187358856201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53689765930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.37880897521973</t>
   </si>
   <si>
     <t xml:space="preserve">8.37401676177979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40755081176758</t>
+    <t xml:space="preserve">8.40755176544189</t>
   </si>
   <si>
     <t xml:space="preserve">8.4123420715332</t>
@@ -1853,16 +1853,16 @@
     <t xml:space="preserve">8.54648017883301</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58959770202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.27341365814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25425052642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35485649108887</t>
+    <t xml:space="preserve">8.58959579467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.27341461181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25425148010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35485553741455</t>
   </si>
   <si>
     <t xml:space="preserve">8.4746208190918</t>
@@ -1877,46 +1877,46 @@
     <t xml:space="preserve">8.31653022766113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29736614227295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28299427032471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17760276794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2015552520752</t>
+    <t xml:space="preserve">8.29736804962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28299522399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1776008605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20155429840088</t>
   </si>
   <si>
     <t xml:space="preserve">8.16323089599609</t>
   </si>
   <si>
-    <t xml:space="preserve">8.24946117401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.18239307403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.17281055450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.09616088867188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14885807037354</t>
+    <t xml:space="preserve">8.2494592666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.18239212036133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.17281150817871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.09616184234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14885902404785</t>
   </si>
   <si>
     <t xml:space="preserve">8.06741809844971</t>
   </si>
   <si>
-    <t xml:space="preserve">8.03867340087891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.971604347229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78956079483032</t>
+    <t xml:space="preserve">8.03867435455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.97160387039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78956031799316</t>
   </si>
   <si>
     <t xml:space="preserve">7.62188863754272</t>
@@ -1925,13 +1925,13 @@
     <t xml:space="preserve">7.61709785461426</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66021347045898</t>
+    <t xml:space="preserve">7.66021394729614</t>
   </si>
   <si>
     <t xml:space="preserve">7.50212335586548</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72249269485474</t>
+    <t xml:space="preserve">7.72249221801758</t>
   </si>
   <si>
     <t xml:space="preserve">7.59314489364624</t>
@@ -1940,103 +1940,103 @@
     <t xml:space="preserve">7.45900726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">7.51170444488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.65542316436768</t>
+    <t xml:space="preserve">7.5117039680481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.65542268753052</t>
   </si>
   <si>
     <t xml:space="preserve">7.59793567657471</t>
   </si>
   <si>
-    <t xml:space="preserve">7.90932750701904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95244121551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82309579849243</t>
+    <t xml:space="preserve">7.90932703018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95244264602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82309436798096</t>
   </si>
   <si>
     <t xml:space="preserve">7.88058376312256</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10574150085449</t>
+    <t xml:space="preserve">8.10574245452881</t>
   </si>
   <si>
     <t xml:space="preserve">8.2063455581665</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1680212020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26383304595947</t>
+    <t xml:space="preserve">8.16802024841309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26383209228516</t>
   </si>
   <si>
     <t xml:space="preserve">8.34527397155762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29257583618164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12011337280273</t>
+    <t xml:space="preserve">8.29257678985596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12011528015137</t>
   </si>
   <si>
     <t xml:space="preserve">8.0338830947876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.99555683135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.80872344970703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91411685943604</t>
+    <t xml:space="preserve">7.99555778503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.80872297286987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91411733627319</t>
   </si>
   <si>
     <t xml:space="preserve">7.88537263870239</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82788515090942</t>
+    <t xml:space="preserve">7.8278865814209</t>
   </si>
   <si>
     <t xml:space="preserve">7.84704780578613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0003490447998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89974451065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.90453672409058</t>
+    <t xml:space="preserve">8.00034713745117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89974498748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.90453577041626</t>
   </si>
   <si>
     <t xml:space="preserve">7.94286155700684</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71770191192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.85662889480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04346561431885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11532306671143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12969398498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.13448715209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.00992870330811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93328046798706</t>
+    <t xml:space="preserve">7.71770143508911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85662984848022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04346466064453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11532402038574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12969493865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.13448524475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.00992965698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93327951431274</t>
   </si>
   <si>
     <t xml:space="preserve">7.75123596191406</t>
@@ -2045,76 +2045,76 @@
     <t xml:space="preserve">7.578773021698</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64105081558228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69374752044678</t>
+    <t xml:space="preserve">7.64105129241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69374799728394</t>
   </si>
   <si>
     <t xml:space="preserve">7.83746719360352</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81351327896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87100076675415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87579250335693</t>
+    <t xml:space="preserve">7.81351375579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87100267410278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87579154968262</t>
   </si>
   <si>
     <t xml:space="preserve">7.92369890213013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89495515823364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8518385887146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86621046066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98597621917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.96681308746338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.92848873138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.11053371429443</t>
+    <t xml:space="preserve">7.89495420455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.85183763504028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8662109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9859766960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.96681451797485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.92848920822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11053276062012</t>
   </si>
   <si>
     <t xml:space="preserve">8.04825401306152</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93806982040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77997970581055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81830453872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84225749969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79435205459595</t>
+    <t xml:space="preserve">7.93807029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77998065948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81830501556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84225845336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79435157775879</t>
   </si>
   <si>
     <t xml:space="preserve">7.7991418838501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94765138626099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91890859603882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71291208267212</t>
+    <t xml:space="preserve">7.94765090942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91890716552734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7129111289978</t>
   </si>
   <si>
     <t xml:space="preserve">7.77518844604492</t>
@@ -2129,25 +2129,25 @@
     <t xml:space="preserve">8.21592712402344</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26862335205078</t>
+    <t xml:space="preserve">8.2686243057251</t>
   </si>
   <si>
     <t xml:space="preserve">8.33569145202637</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45066738128662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36443424224854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47941303253174</t>
+    <t xml:space="preserve">8.4506664276123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36443519592285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47941207885742</t>
   </si>
   <si>
     <t xml:space="preserve">8.55127048492432</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59438705444336</t>
+    <t xml:space="preserve">8.59438610076904</t>
   </si>
   <si>
     <t xml:space="preserve">8.66624450683594</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">8.64229297637939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69019794464111</t>
+    <t xml:space="preserve">8.69019985198975</t>
   </si>
   <si>
     <t xml:space="preserve">8.58480548858643</t>
@@ -2168,22 +2168,22 @@
     <t xml:space="preserve">7.74165487289429</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70332908630371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.78477096557617</t>
+    <t xml:space="preserve">7.70332956314087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.78477001190186</t>
   </si>
   <si>
     <t xml:space="preserve">7.44463586807251</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22426652908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17636060714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30091667175293</t>
+    <t xml:space="preserve">7.22426700592041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17636013031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30091714859009</t>
   </si>
   <si>
     <t xml:space="preserve">7.36319541931152</t>
@@ -2192,10 +2192,10 @@
     <t xml:space="preserve">7.33924150466919</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09492015838623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6972975730896</t>
+    <t xml:space="preserve">7.09492063522339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.69729709625244</t>
   </si>
   <si>
     <t xml:space="preserve">6.3619532585144</t>
@@ -2210,10 +2210,10 @@
     <t xml:space="preserve">5.37987470626831</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30322456359863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86851930618286</t>
+    <t xml:space="preserve">5.30322504043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8685188293457</t>
   </si>
   <si>
     <t xml:space="preserve">6.45776605606079</t>
@@ -2231,10 +2231,10 @@
     <t xml:space="preserve">6.76915693283081</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84101629257202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53441667556763</t>
+    <t xml:space="preserve">6.84101581573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53441619873047</t>
   </si>
   <si>
     <t xml:space="preserve">6.3715353012085</t>
@@ -2246,37 +2246,37 @@
     <t xml:space="preserve">6.02852582931519</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11092519760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85606336593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45201778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38111639022827</t>
+    <t xml:space="preserve">6.110924243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85606384277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45201730728149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38111543655396</t>
   </si>
   <si>
     <t xml:space="preserve">6.32171249389648</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35237264633179</t>
+    <t xml:space="preserve">6.35237216949463</t>
   </si>
   <si>
     <t xml:space="preserve">6.40986013412476</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4079442024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47309637069702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65897226333618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.49962091445923</t>
+    <t xml:space="preserve">6.40794372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47309684753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65897178649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.49962139129639</t>
   </si>
   <si>
     <t xml:space="preserve">6.44746971130371</t>
@@ -2285,19 +2285,19 @@
     <t xml:space="preserve">6.43008518218994</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39338541030884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44360637664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59619808197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.61551284790039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79321432113647</t>
+    <t xml:space="preserve">6.39338636398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44360685348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59619760513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.61551332473755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79321384429932</t>
   </si>
   <si>
     <t xml:space="preserve">6.82798194885254</t>
@@ -2306,106 +2306,106 @@
     <t xml:space="preserve">6.62323904037476</t>
   </si>
   <si>
-    <t xml:space="preserve">6.690842628479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76617288589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78935194015503</t>
+    <t xml:space="preserve">6.69084215164185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76617240905762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78935146331787</t>
   </si>
   <si>
     <t xml:space="preserve">6.9477367401123</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95932626724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.084876537323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93807983398438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70629501342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66766452789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9400110244751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5112099647522</t>
+    <t xml:space="preserve">6.95932674407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08487701416016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93807935714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70629453659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66766405105591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94001150131226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.51120948791504</t>
   </si>
   <si>
     <t xml:space="preserve">6.67345905303955</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53245735168457</t>
+    <t xml:space="preserve">6.53245687484741</t>
   </si>
   <si>
     <t xml:space="preserve">6.6638011932373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67732238769531</t>
+    <t xml:space="preserve">6.67732191085815</t>
   </si>
   <si>
     <t xml:space="preserve">6.72947359085083</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71208953857422</t>
+    <t xml:space="preserve">6.71208906173706</t>
   </si>
   <si>
     <t xml:space="preserve">7.14668560028076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05010843276978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94387483596802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11191749572754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09839677810669</t>
+    <t xml:space="preserve">7.05010890960693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94387435913086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1119179725647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09839725494385</t>
   </si>
   <si>
     <t xml:space="preserve">7.14282274246216</t>
   </si>
   <si>
-    <t xml:space="preserve">7.14475393295288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13895988464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17758989334106</t>
+    <t xml:space="preserve">7.14475345611572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1389594078064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17759037017822</t>
   </si>
   <si>
     <t xml:space="preserve">7.05976629257202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20463180541992</t>
+    <t xml:space="preserve">7.20463228225708</t>
   </si>
   <si>
     <t xml:space="preserve">7.06942415237427</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31279754638672</t>
+    <t xml:space="preserve">7.31279802322388</t>
   </si>
   <si>
     <t xml:space="preserve">7.33018159866333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38619613647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44800567626953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44027853012085</t>
+    <t xml:space="preserve">7.38619565963745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44800472259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44027948379517</t>
   </si>
   <si>
     <t xml:space="preserve">7.58128118515015</t>
@@ -2414,40 +2414,40 @@
     <t xml:space="preserve">7.27223539352417</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26837205886841</t>
+    <t xml:space="preserve">7.26837253570557</t>
   </si>
   <si>
     <t xml:space="preserve">7.24326229095459</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34370231628418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5484447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45379972457886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62667226791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67013168334961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70683145523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84203863143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86425065994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81499767303467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75029039382935</t>
+    <t xml:space="preserve">7.34370279312134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.54844522476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45380020141602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62667179107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67013120651245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70683097839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84203958511353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86425113677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81499671936035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7502908706665</t>
   </si>
   <si>
     <t xml:space="preserve">7.92412853240967</t>
@@ -2462,16 +2462,16 @@
     <t xml:space="preserve">7.89322423934937</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98497247695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87294387817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0265007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88549900054932</t>
+    <t xml:space="preserve">7.98497152328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87294435501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02649974822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88549757003784</t>
   </si>
   <si>
     <t xml:space="preserve">7.83817577362061</t>
@@ -2480,28 +2480,28 @@
     <t xml:space="preserve">8.2631139755249</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42729473114014</t>
+    <t xml:space="preserve">8.42729377746582</t>
   </si>
   <si>
     <t xml:space="preserve">8.21965408325195</t>
   </si>
   <si>
-    <t xml:space="preserve">8.22158527374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28146266937256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23220920562744</t>
+    <t xml:space="preserve">8.22158432006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28146362304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23220825195312</t>
   </si>
   <si>
     <t xml:space="preserve">8.29594993591309</t>
   </si>
   <si>
-    <t xml:space="preserve">8.13659858703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20806503295898</t>
+    <t xml:space="preserve">8.1365966796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20806407928467</t>
   </si>
   <si>
     <t xml:space="preserve">8.21868896484375</t>
@@ -2516,34 +2516,34 @@
     <t xml:space="preserve">8.3973560333252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.27760028839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.30753898620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.24283313751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34423828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22834777832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39059448242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.34327125549316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43405342102051</t>
+    <t xml:space="preserve">8.2775993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.30753993988037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.24283218383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34423923492432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.228346824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39059543609619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.34327220916748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43405437469482</t>
   </si>
   <si>
     <t xml:space="preserve">8.3104362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.18102359771729</t>
+    <t xml:space="preserve">8.18102264404297</t>
   </si>
   <si>
     <t xml:space="preserve">8.29788112640381</t>
@@ -2552,10 +2552,10 @@
     <t xml:space="preserve">8.48330879211426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7711067199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58664512634277</t>
+    <t xml:space="preserve">8.77110767364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58664703369141</t>
   </si>
   <si>
     <t xml:space="preserve">8.4794454574585</t>
@@ -2567,40 +2567,40 @@
     <t xml:space="preserve">8.65907859802246</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75565624237061</t>
+    <t xml:space="preserve">8.75565528869629</t>
   </si>
   <si>
     <t xml:space="preserve">8.71412754058838</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82132720947266</t>
+    <t xml:space="preserve">8.82132816314697</t>
   </si>
   <si>
     <t xml:space="preserve">8.94784355163574</t>
   </si>
   <si>
-    <t xml:space="preserve">9.014479637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03959083557129</t>
+    <t xml:space="preserve">9.01448059082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03959178924561</t>
   </si>
   <si>
     <t xml:space="preserve">9.06083869934082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85319709777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94011783599854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01641273498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05118083953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80587577819824</t>
+    <t xml:space="preserve">8.85319900512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9401159286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01641368865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05117988586426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80587482452393</t>
   </si>
   <si>
     <t xml:space="preserve">9.08884620666504</t>
@@ -2615,34 +2615,34 @@
     <t xml:space="preserve">9.04828453063965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04635238647461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02896785736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95460414886475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99613189697266</t>
+    <t xml:space="preserve">9.04635047912598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02896690368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95460510253906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99613094329834</t>
   </si>
   <si>
     <t xml:space="preserve">8.9719877243042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04441928863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2134313583374</t>
+    <t xml:space="preserve">9.04442024230957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21342945098877</t>
   </si>
   <si>
     <t xml:space="preserve">9.23853969573975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1747989654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06180477142334</t>
+    <t xml:space="preserve">9.17479991912842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06180381774902</t>
   </si>
   <si>
     <t xml:space="preserve">9.12554550170898</t>
@@ -2654,16 +2654,16 @@
     <t xml:space="preserve">9.07629108428955</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80008220672607</t>
+    <t xml:space="preserve">8.80008125305176</t>
   </si>
   <si>
     <t xml:space="preserve">8.93528842926025</t>
   </si>
   <si>
-    <t xml:space="preserve">8.94687843322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.74020385742188</t>
+    <t xml:space="preserve">8.94687747955322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.74020290374756</t>
   </si>
   <si>
     <t xml:space="preserve">8.88893127441406</t>
@@ -2672,7 +2672,7 @@
     <t xml:space="preserve">8.66294193267822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50262260437012</t>
+    <t xml:space="preserve">8.50262355804443</t>
   </si>
   <si>
     <t xml:space="preserve">8.65714740753174</t>
@@ -2690,19 +2690,19 @@
     <t xml:space="preserve">8.8908634185791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96426200866699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24626636505127</t>
+    <t xml:space="preserve">8.96426010131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24626541137695</t>
   </si>
   <si>
     <t xml:space="preserve">9.26171875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5128173828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35443115234375</t>
+    <t xml:space="preserve">9.51281833648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35443210601807</t>
   </si>
   <si>
     <t xml:space="preserve">9.29841804504395</t>
@@ -2711,31 +2711,31 @@
     <t xml:space="preserve">9.44328212738037</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4316930770874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25012874603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13230514526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22501945495605</t>
+    <t xml:space="preserve">9.43169403076172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25012969970703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13230609893799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22501754760742</t>
   </si>
   <si>
     <t xml:space="preserve">9.06856536865234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19411373138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17286682128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22695159912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36215782165527</t>
+    <t xml:space="preserve">9.19411563873291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17286777496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22695064544678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36215877532959</t>
   </si>
   <si>
     <t xml:space="preserve">9.12650966644287</t>
@@ -2744,52 +2744,52 @@
     <t xml:space="preserve">9.1477575302124</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13037490844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15934658050537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12264823913574</t>
+    <t xml:space="preserve">9.13037395477295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15934753417969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12264728546143</t>
   </si>
   <si>
     <t xml:space="preserve">9.0048246383667</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13616847991943</t>
+    <t xml:space="preserve">9.13616752624512</t>
   </si>
   <si>
     <t xml:space="preserve">9.05890655517578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04538726806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83677864074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87347984313965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95267391204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93915176391602</t>
+    <t xml:space="preserve">9.04538536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8367805480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87347888946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95267295837402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9391508102417</t>
   </si>
   <si>
     <t xml:space="preserve">8.86961650848389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88120651245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96619415283203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13809871673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0202751159668</t>
+    <t xml:space="preserve">8.88120555877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96619319915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13810062408447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02027606964111</t>
   </si>
   <si>
     <t xml:space="preserve">8.90438365936279</t>
@@ -2798,19 +2798,19 @@
     <t xml:space="preserve">8.66487407684326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59340572357178</t>
+    <t xml:space="preserve">8.59340667724609</t>
   </si>
   <si>
     <t xml:space="preserve">8.54125499725342</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5528450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42150115966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38093948364258</t>
+    <t xml:space="preserve">8.55284404754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42150020599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38093852996826</t>
   </si>
   <si>
     <t xml:space="preserve">8.47365093231201</t>
@@ -2819,85 +2819,85 @@
     <t xml:space="preserve">8.42343139648438</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4253625869751</t>
+    <t xml:space="preserve">8.42536354064941</t>
   </si>
   <si>
     <t xml:space="preserve">8.54705047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49296569824219</t>
+    <t xml:space="preserve">8.4929666519165</t>
   </si>
   <si>
     <t xml:space="preserve">8.58568096160889</t>
   </si>
   <si>
-    <t xml:space="preserve">8.512282371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50648784637451</t>
+    <t xml:space="preserve">8.51228141784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5064868927002</t>
   </si>
   <si>
     <t xml:space="preserve">8.63590049743652</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5953369140625</t>
+    <t xml:space="preserve">8.59533786773682</t>
   </si>
   <si>
     <t xml:space="preserve">8.65328407287598</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57215976715088</t>
+    <t xml:space="preserve">8.57215881347656</t>
   </si>
   <si>
     <t xml:space="preserve">8.57795429229736</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82712268829346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86768627166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.94108295440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3370475769043</t>
+    <t xml:space="preserve">8.82712364196777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86768436431885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.94108390808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33704853057861</t>
   </si>
   <si>
     <t xml:space="preserve">9.3177318572998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40272045135498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3447732925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38533782958984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44521331787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58235359191895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42976188659668</t>
+    <t xml:space="preserve">9.40271949768066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34477424621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38533687591553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44521427154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58235263824463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42976093292236</t>
   </si>
   <si>
     <t xml:space="preserve">9.44135093688965</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35250091552734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20570278167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28875923156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31580066680908</t>
+    <t xml:space="preserve">9.35249996185303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20570373535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2887601852417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31580257415771</t>
   </si>
   <si>
     <t xml:space="preserve">9.34090995788574</t>
@@ -2906,22 +2906,22 @@
     <t xml:space="preserve">9.05697536468506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19218158721924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16320991516113</t>
+    <t xml:space="preserve">9.19218254089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16320896148682</t>
   </si>
   <si>
     <t xml:space="preserve">9.04924964904785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26751327514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16900444030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36795234680176</t>
+    <t xml:space="preserve">9.26751136779785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1690034866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.36795139312744</t>
   </si>
   <si>
     <t xml:space="preserve">9.52440738677979</t>
@@ -2930,7 +2930,7 @@
     <t xml:space="preserve">9.76391696929932</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48964023590088</t>
+    <t xml:space="preserve">9.48963928222656</t>
   </si>
   <si>
     <t xml:space="preserve">9.46839237213135</t>
@@ -2939,10 +2939,10 @@
     <t xml:space="preserve">9.38726806640625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42589950561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.36408996582031</t>
+    <t xml:space="preserve">9.42589855194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.364089012146</t>
   </si>
   <si>
     <t xml:space="preserve">9.28296566009521</t>
@@ -2951,61 +2951,61 @@
     <t xml:space="preserve">9.25978755950928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24240303039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26364898681641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28682899475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35056972503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23081398010254</t>
+    <t xml:space="preserve">9.24240207672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26364994049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28682804107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3505687713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23081302642822</t>
   </si>
   <si>
     <t xml:space="preserve">9.39885807037354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32932090759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4645299911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41624069213867</t>
+    <t xml:space="preserve">9.32932186126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46452903747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41624164581299</t>
   </si>
   <si>
     <t xml:space="preserve">9.63836765289307</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47225379943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56497001647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64416313171387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76943683624268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55384826660156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73544692993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83255958557129</t>
+    <t xml:space="preserve">9.47225570678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56496906280518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64416217803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76943588256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55384922027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73544788360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83255863189697</t>
   </si>
   <si>
     <t xml:space="preserve">9.70340061187744</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62959671020508</t>
+    <t xml:space="preserve">9.62959575653076</t>
   </si>
   <si>
     <t xml:space="preserve">9.60823059082031</t>
@@ -3014,19 +3014,19 @@
     <t xml:space="preserve">9.52859973907471</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63347911834717</t>
+    <t xml:space="preserve">9.63348007202148</t>
   </si>
   <si>
     <t xml:space="preserve">9.8811149597168</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0025053024292</t>
+    <t xml:space="preserve">10.0025043487549</t>
   </si>
   <si>
     <t xml:space="preserve">10.0947608947754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98308181762695</t>
+    <t xml:space="preserve">9.98308086395264</t>
   </si>
   <si>
     <t xml:space="preserve">9.94423675537109</t>
@@ -3038,61 +3038,61 @@
     <t xml:space="preserve">9.86654758453369</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82284736633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81313514709473</t>
+    <t xml:space="preserve">9.82284832000732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81313610076904</t>
   </si>
   <si>
     <t xml:space="preserve">9.82770347595215</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79856967926025</t>
+    <t xml:space="preserve">9.79857063293457</t>
   </si>
   <si>
     <t xml:space="preserve">9.79371452331543</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0656270980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1675939559937</t>
+    <t xml:space="preserve">10.0656261444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.167594909668</t>
   </si>
   <si>
     <t xml:space="preserve">10.2355718612671</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2549953460693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1870174407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.14817237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2307167053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2792720794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2744178771973</t>
+    <t xml:space="preserve">10.2549962997437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1870164871216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1481714248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2307176589966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2792730331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2744169235229</t>
   </si>
   <si>
     <t xml:space="preserve">10.3132619857788</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3909511566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5754642486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6337299346924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8133869171143</t>
+    <t xml:space="preserve">10.3909521102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5754632949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6337308883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8133878707886</t>
   </si>
   <si>
     <t xml:space="preserve">10.8182430267334</t>
@@ -3107,13 +3107,13 @@
     <t xml:space="preserve">10.8570880889893</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7551202774048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7454080581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7842531204224</t>
+    <t xml:space="preserve">10.7551193237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7454090118408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7842540740967</t>
   </si>
   <si>
     <t xml:space="preserve">11.0852994918823</t>
@@ -3122,13 +3122,13 @@
     <t xml:space="preserve">11.0755882263184</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0610227584839</t>
+    <t xml:space="preserve">11.0610208511353</t>
   </si>
   <si>
     <t xml:space="preserve">11.0464553833008</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9687662124634</t>
+    <t xml:space="preserve">10.9687652587891</t>
   </si>
   <si>
     <t xml:space="preserve">11.0027551651001</t>
@@ -3137,19 +3137,19 @@
     <t xml:space="preserve">10.9104986190796</t>
   </si>
   <si>
-    <t xml:space="preserve">10.891077041626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.997899055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8279542922974</t>
+    <t xml:space="preserve">10.8910760879517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9978981018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.827953338623</t>
   </si>
   <si>
     <t xml:space="preserve">10.9541988372803</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9784784317017</t>
+    <t xml:space="preserve">10.978476524353</t>
   </si>
   <si>
     <t xml:space="preserve">10.8667984008789</t>
@@ -3161,25 +3161,25 @@
     <t xml:space="preserve">10.7162752151489</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9930438995361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1629886627197</t>
+    <t xml:space="preserve">10.9930429458618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.162989616394</t>
   </si>
   <si>
     <t xml:space="preserve">11.0513105392456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4009132385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4688920974731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4931688308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.51744556427</t>
+    <t xml:space="preserve">11.4009113311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4688911437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4931697845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5174465179443</t>
   </si>
   <si>
     <t xml:space="preserve">11.5951366424561</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">11.6048469543457</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5805702209473</t>
+    <t xml:space="preserve">11.5805692672729</t>
   </si>
   <si>
     <t xml:space="preserve">11.5660028457642</t>
@@ -3203,13 +3203,13 @@
     <t xml:space="preserve">11.6097030639648</t>
   </si>
   <si>
-    <t xml:space="preserve">11.721381187439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.862193107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.745659828186</t>
+    <t xml:space="preserve">11.7213821411133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8621940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7456607818604</t>
   </si>
   <si>
     <t xml:space="preserve">11.6922483444214</t>
@@ -3218,10 +3218,10 @@
     <t xml:space="preserve">11.6825370788574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3620672225952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2552452087402</t>
+    <t xml:space="preserve">11.3620681762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2552461624146</t>
   </si>
   <si>
     <t xml:space="preserve">11.4834575653076</t>
@@ -3230,19 +3230,19 @@
     <t xml:space="preserve">11.4251909255981</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3814916610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.36692237854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3329343795776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3717794418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5902814865112</t>
+    <t xml:space="preserve">11.3814907073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3669242858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.332935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3717784881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5902805328369</t>
   </si>
   <si>
     <t xml:space="preserve">11.6971035003662</t>
@@ -3251,19 +3251,19 @@
     <t xml:space="preserve">11.570858001709</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5757131576538</t>
+    <t xml:space="preserve">11.5757141113281</t>
   </si>
   <si>
     <t xml:space="preserve">11.5125904083252</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4106245040894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5514373779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7068157196045</t>
+    <t xml:space="preserve">11.410623550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5514364242554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7068147659302</t>
   </si>
   <si>
     <t xml:space="preserve">11.9495944976807</t>
@@ -3278,10 +3278,10 @@
     <t xml:space="preserve">11.7602262496948</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8087816238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8282060623169</t>
+    <t xml:space="preserve">11.8087825775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8282051086426</t>
   </si>
   <si>
     <t xml:space="preserve">11.7505149841309</t>
@@ -3302,40 +3302,40 @@
     <t xml:space="preserv